--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="11_59E7F83CB950300335F1978AAF9AFBF8F7C5E86B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225A6C7D-A5AF-46E8-859F-D7E44E660016}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="11_59E7F83CB950300335F1978AAF9AFBF8F7C5E86B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BF681E-9E08-4F2F-BB14-F0F71681333A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_01435B37FA98B62C87F097B9571AC07EF6C3C536" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1298C7-EAE6-4D82-AC43-7CDDE3C4D91A}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_01435B37FA98B62C87F097B9571AC07EF6C3C536" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1071CB9A-2D5A-4C83-A332-6FA47C2EED04}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14683,8 +14683,8 @@
       <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>31</v>
+      <c r="I3" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>47</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>OGC-CHR-CAF-CSE-SEC</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>OGC-CHR-CAF-CSE-SEC</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Corporate Secretary</t>
+          <t>OGC-CHR-CAF-CSE</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Corporate Affairs</t>
+          <t>OGC-CHR-CAF-RIS-CAF</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Risk &amp; Compliance</t>
+          <t>OGC-CHR-CAF-RIS</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Compensation &amp; Benefits</t>
+          <t>OGC-CHR-HRS-CBB-COM</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Compensation &amp; Benefits</t>
+          <t>OGC-CHR-HRS-CBB-COM</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Facilities - Factory</t>
+          <t>OGC-CHR-HRS-CBB-FCF</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>HR Business Partner</t>
+          <t>OGC-CHR-HRS-CBB-BPN</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Ocean Glass Savings Corperative</t>
+          <t>OGC-CHR-HRS-CBB-SAV</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Compensation &amp; Benefits and HR Business Partner</t>
+          <t>OGC-CHR-HRS-CBB</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Compensation &amp; Benefits and HR Business Partner</t>
+          <t>OGC-CHR-HRS-CBB</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Employee Experience</t>
+          <t>OGC-CHR-HRS-TAL-EEX</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Facilities - Head Office</t>
+          <t>OGC-CHR-HRS-TAL-FCH</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Facilities - Head Office</t>
+          <t>OGC-CHR-HRS-TAL-FCH</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Learning Development</t>
+          <t>OGC-CHR-HRS-TAL-LND</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Learning Development</t>
+          <t>OGC-CHR-HRS-TAL-LND</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Talent Acquisition</t>
+          <t>OGC-CHR-HRS-TAL-TAC</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Talent Acquisition</t>
+          <t>OGC-CHR-HRS-TAL-TAC</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Talent Acquisition</t>
+          <t>OGC-CHR-HRS-TAL-TAC</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Talent Acquisition &amp; Learning Development</t>
+          <t>OGC-CHR-HRS-TAL</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Corporate  Affairs and Human Resources</t>
+          <t>OGC-CHR</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Agent - Thailand &amp; CLM</t>
+          <t>OGC-CCD-THA-AGE</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Agent - Thailand &amp; CLM</t>
+          <t>OGC-CCD-THA-AGE</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Agent - Thailand &amp; CLM</t>
+          <t>OGC-CCD-THA-AGE</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Agent - Thailand &amp; CLM</t>
+          <t>OGC-CCD-THA-AGE</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Agent - Thailand &amp; CLM</t>
+          <t>OGC-CCD-THA-AGE</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>B2B - Thailand</t>
+          <t>OGC-CCD-THA-B2B</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Food Service - Bangkok</t>
+          <t>OGC-CCD-THA-FSV</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Inside Sales - Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA-ISS</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Modern Trade</t>
+          <t>OGC-CCD-THA-MTT</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Modern Trade</t>
+          <t>OGC-CCD-THA-MTT</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Modern Trade</t>
+          <t>OGC-CCD-THA-MTT</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Modern Trade</t>
+          <t>OGC-CCD-THA-MTT</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>SIMVP</t>
+          <t>OGC-CCD-THA-SIM</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>SIMVP</t>
+          <t>OGC-CCD-THA-SIM</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>SIMVP</t>
+          <t>OGC-CCD-THA-SIM</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Omni - Channel</t>
+          <t>OGC-CCD-THA-OMN</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Omni - Channel</t>
+          <t>OGC-CCD-THA-OMN</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Omni - Channel</t>
+          <t>OGC-CCD-THA-OMN</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Omni - Channel</t>
+          <t>OGC-CCD-THA-OMN</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Thailand &amp; ASEAN</t>
+          <t>OGC-CCD-THA</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>OGC-CCD-000-APC</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>OGC-CCD-000-APC</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>OGC-CCD-000-APC</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>America &amp; Africa</t>
+          <t>OGC-CCD-000-ATL-AMR</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>America &amp; Africa</t>
+          <t>OGC-CCD-000-ATL-AMR</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>OGC-CCD-000-ATL-EUR</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>OGC-CCD-000-ATL-EUR</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>OGC-CCD-000-ATL</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>OGC-CCD-ECM</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>Strategic Demand Planning &amp; Shipping</t>
+          <t>OGC-CCD-000-DMP</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; South Asia Operations</t>
+          <t>OGC-CCD-000-TMC-TMS</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>Trade Marketing &amp; CCD Operations</t>
+          <t>OGC-CCD-000-TMC</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Customer and Channel Development</t>
+          <t>OGC-CCD</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Corporate Information Technology</t>
+          <t>OGC-FAD-CIT</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Finance &amp; Account</t>
+          <t>OGC-FAD-FAC</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>OGC-FAD-PCM-PCM</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>Batch &amp; Furnace</t>
+          <t>OGC-MFG-BFN</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Batch &amp; Furnace</t>
+          <t>OGC-MFG-BFN</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>Batch Section</t>
+          <t>OGC-MFG-BFN-BAT</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>Batch Section</t>
+          <t>OGC-MFG-BFN-BAT</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>Furnace A</t>
+          <t>OGC-MFG-BFN-FNS-FNA</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>Furnace B</t>
+          <t>OGC-MFG-BFN-FNS-FNB</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>Furnace C</t>
+          <t>OGC-MFG-BFN-FNS-FNC</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>Furnace C</t>
+          <t>OGC-MFG-BFN-FNS-FNC</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>Furnace C</t>
+          <t>OGC-MFG-BFN-FNS-FNC</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Furnace C</t>
+          <t>OGC-MFG-BFN-FNS-FNC</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Furnace Support &amp; Maintenance</t>
+          <t>OGC-MFG-BFN-FSM</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>Batch &amp; Furnace</t>
+          <t>OGC-MFG-BFN</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="H168" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I168" s="5" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -17902,7 +17902,7 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -18090,7 +18090,7 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>Electrical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-EMS</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>Engineering Development</t>
+          <t>OGC-MFG-ENG-ENG</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MED</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MED</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MED</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I198" s="5" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="H200" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I200" s="5" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="H202" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I202" s="5" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="H204" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I204" s="5" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I208" s="5" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I210" s="5" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I212" s="5" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I214" s="5" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I216" s="5" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="H218" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I218" s="5" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="H220" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I220" s="5" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I222" s="5" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Engineering</t>
+          <t>OGC-MFG-ENG-MCS</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="H224" s="5" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I224" s="5" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -22582,7 +22582,7 @@
       </c>
       <c r="H226" s="5" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I226" s="5" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="H228" s="5" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I228" s="5" t="inlineStr">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="H230" s="5" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I230" s="5" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr">
@@ -23194,7 +23194,7 @@
       </c>
       <c r="H232" s="5" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I232" s="5" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>Utility Engineering</t>
+          <t>OGC-MFG-ENG-UTS</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
@@ -23390,7 +23390,7 @@
       </c>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>Engineering Department</t>
+          <t>OGC-MFG-ENG</t>
         </is>
       </c>
       <c r="I234" s="5" t="inlineStr">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>(H28-1)</t>
+          <t>OGC-MFG-PRD-FM1-H281</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>(H28-1)</t>
+          <t>OGC-MFG-PRD-FM1-H281</t>
         </is>
       </c>
       <c r="I236" s="5" t="inlineStr">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I238" s="5" t="inlineStr">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I242" s="5" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I244" s="5" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
@@ -24518,7 +24518,7 @@
       </c>
       <c r="H246" s="5" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I246" s="5" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>(H28-2)</t>
+          <t>OGC-MFG-PRD-FM1-H282</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I248" s="5" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I250" s="5" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I254" s="5" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>(H28-5)</t>
+          <t>OGC-MFG-PRD-FM1-H285</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I258" s="5" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I262" s="5" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I264" s="5" t="inlineStr">
@@ -26280,7 +26280,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>(H28-7)</t>
+          <t>OGC-MFG-PRD-FM1-H287</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
@@ -26374,7 +26374,7 @@
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I266" s="5" t="inlineStr">
@@ -26480,7 +26480,7 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
@@ -26582,7 +26582,7 @@
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I268" s="5" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I270" s="5" t="inlineStr">
@@ -26876,7 +26876,7 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr">
@@ -27178,7 +27178,7 @@
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I274" s="5" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I276" s="5" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I278" s="5" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I280" s="5" t="inlineStr">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
@@ -27922,7 +27922,7 @@
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I282" s="5" t="inlineStr">
@@ -28020,7 +28020,7 @@
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I284" s="5" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>Forming 1</t>
+          <t>OGC-MFG-FMD-FM1</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I286" s="5" t="inlineStr">
@@ -28412,7 +28412,7 @@
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr">
@@ -28510,7 +28510,7 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
@@ -28702,7 +28702,7 @@
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>(MDP-1)</t>
+          <t>OGC-MFG-PRD-FM2-MDP1</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
@@ -29192,7 +29192,7 @@
       </c>
       <c r="H295" s="3" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I295" s="3" t="inlineStr">
@@ -29290,7 +29290,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
@@ -29388,7 +29388,7 @@
       </c>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I297" s="3" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I298" s="5" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I299" s="3" t="inlineStr">
@@ -29682,7 +29682,7 @@
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I300" s="5" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>(MDP-2)</t>
+          <t>OGC-MFG-PRD-FM2-MDP2</t>
         </is>
       </c>
       <c r="I301" s="3" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
@@ -29968,7 +29968,7 @@
       </c>
       <c r="H303" s="3" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I303" s="3" t="inlineStr">
@@ -30062,7 +30062,7 @@
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I304" s="5" t="inlineStr">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="H305" s="3" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I305" s="3" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I306" s="5" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="H307" s="3" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I307" s="3" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I308" s="5" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="H309" s="3" t="inlineStr">
         <is>
-          <t>(MDP-4)</t>
+          <t>OGC-MFG-PRD-FM2-MDP4</t>
         </is>
       </c>
       <c r="I309" s="3" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>Forming 2</t>
+          <t>OGC-MFG-FMD-FM2</t>
         </is>
       </c>
       <c r="I310" s="5" t="inlineStr">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="H311" s="3" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I311" s="3" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
@@ -30936,7 +30936,7 @@
       </c>
       <c r="H313" s="3" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I313" s="3" t="inlineStr">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I314" s="5" t="inlineStr">
@@ -31140,7 +31140,7 @@
       </c>
       <c r="H315" s="3" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I315" s="3" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I316" s="5" t="inlineStr">
@@ -31328,7 +31328,7 @@
       </c>
       <c r="H317" s="3" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I317" s="3" t="inlineStr">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="H319" s="3" t="inlineStr">
         <is>
-          <t>(STW-1)</t>
+          <t>OGC-MFG-PRD-FM3-STW1</t>
         </is>
       </c>
       <c r="I319" s="3" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I320" s="5" t="inlineStr">
@@ -31708,7 +31708,7 @@
       </c>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I321" s="3" t="inlineStr">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I322" s="5" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="H323" s="3" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I323" s="3" t="inlineStr">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I324" s="5" t="inlineStr">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I325" s="3" t="inlineStr">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="H326" s="5" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I326" s="5" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="H327" s="3" t="inlineStr">
         <is>
-          <t>(STW-2)</t>
+          <t>OGC-MFG-PRD-FM3-STW2</t>
         </is>
       </c>
       <c r="I327" s="3" t="inlineStr">
@@ -32382,7 +32382,7 @@
       </c>
       <c r="H328" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I328" s="5" t="inlineStr">
@@ -32480,7 +32480,7 @@
       </c>
       <c r="H329" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I329" s="3" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="H330" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I330" s="5" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="H331" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I331" s="3" t="inlineStr">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="H332" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I332" s="5" t="inlineStr">
@@ -32876,7 +32876,7 @@
       </c>
       <c r="H333" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I333" s="3" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="H334" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I334" s="5" t="inlineStr">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="H335" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I335" s="3" t="inlineStr">
@@ -33158,7 +33158,7 @@
       </c>
       <c r="H336" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I336" s="5" t="inlineStr">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
@@ -33346,7 +33346,7 @@
       </c>
       <c r="H338" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I338" s="5" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H339" s="3" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I339" s="3" t="inlineStr">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>(STW-3)</t>
+          <t>OGC-MFG-PRD-FM3-STW3</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
@@ -33640,7 +33640,7 @@
       </c>
       <c r="H341" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 2</t>
+          <t>OGC-MFG-PRD-FM3-CC2</t>
         </is>
       </c>
       <c r="I341" s="3" t="inlineStr">
@@ -33734,7 +33734,7 @@
       </c>
       <c r="H342" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 2</t>
+          <t>OGC-MFG-PRD-FM3-CC2</t>
         </is>
       </c>
       <c r="I342" s="5" t="inlineStr">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="H343" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I343" s="3" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="H344" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I344" s="5" t="inlineStr">
@@ -34024,7 +34024,7 @@
       </c>
       <c r="H345" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I345" s="3" t="inlineStr">
@@ -34122,7 +34122,7 @@
       </c>
       <c r="H346" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I346" s="5" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="H347" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I347" s="3" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="H348" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 5</t>
+          <t>OGC-MFG-PRD-FM3-CC5</t>
         </is>
       </c>
       <c r="I348" s="5" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H349" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I349" s="3" t="inlineStr">
@@ -34506,7 +34506,7 @@
       </c>
       <c r="H350" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I350" s="5" t="inlineStr">
@@ -34608,7 +34608,7 @@
       </c>
       <c r="H351" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I351" s="3" t="inlineStr">
@@ -34706,7 +34706,7 @@
       </c>
       <c r="H352" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I352" s="5" t="inlineStr">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="H353" s="3" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I353" s="3" t="inlineStr">
@@ -34894,7 +34894,7 @@
       </c>
       <c r="H354" s="5" t="inlineStr">
         <is>
-          <t>Cold Cut 6</t>
+          <t>OGC-MFG-PRD-FM3-CC6</t>
         </is>
       </c>
       <c r="I354" s="5" t="inlineStr">
@@ -34988,7 +34988,7 @@
       </c>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I355" s="3" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="H356" s="5" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I356" s="5" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="H358" s="5" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I358" s="5" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I359" s="3" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="H360" s="5" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I360" s="5" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="H361" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I361" s="3" t="inlineStr">
@@ -35682,7 +35682,7 @@
       </c>
       <c r="H362" s="5" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I362" s="5" t="inlineStr">
@@ -35780,7 +35780,7 @@
       </c>
       <c r="H363" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I363" s="3" t="inlineStr">
@@ -35874,7 +35874,7 @@
       </c>
       <c r="H364" s="5" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I364" s="5" t="inlineStr">
@@ -35968,7 +35968,7 @@
       </c>
       <c r="H365" s="3" t="inlineStr">
         <is>
-          <t>Forming 3</t>
+          <t>OGC-MFG-FMD-FM3</t>
         </is>
       </c>
       <c r="I365" s="3" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="H366" s="5" t="inlineStr">
         <is>
-          <t>Forming Department</t>
+          <t>OGC-MFG-FMD</t>
         </is>
       </c>
       <c r="I366" s="5" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="H367" s="3" t="inlineStr">
         <is>
-          <t>Mold Design</t>
+          <t>OGC-MFG-MDI-MDS</t>
         </is>
       </c>
       <c r="I367" s="3" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="H368" s="5" t="inlineStr">
         <is>
-          <t>Mold Design</t>
+          <t>OGC-MFG-MDI-MDS</t>
         </is>
       </c>
       <c r="I368" s="5" t="inlineStr">
@@ -36368,7 +36368,7 @@
       </c>
       <c r="H369" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I369" s="3" t="inlineStr">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="H370" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I370" s="5" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="H371" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I371" s="3" t="inlineStr">
@@ -36654,7 +36654,7 @@
       </c>
       <c r="H372" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I372" s="5" t="inlineStr">
@@ -36740,7 +36740,7 @@
       </c>
       <c r="H373" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I373" s="3" t="inlineStr">
@@ -36830,7 +36830,7 @@
       </c>
       <c r="H374" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I374" s="5" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="H375" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I375" s="3" t="inlineStr">
@@ -37010,7 +37010,7 @@
       </c>
       <c r="H376" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I376" s="5" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H377" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I377" s="3" t="inlineStr">
@@ -37186,7 +37186,7 @@
       </c>
       <c r="H378" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I378" s="5" t="inlineStr">
@@ -37272,7 +37272,7 @@
       </c>
       <c r="H379" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I379" s="3" t="inlineStr">
@@ -37362,7 +37362,7 @@
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
@@ -37452,7 +37452,7 @@
       </c>
       <c r="H381" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I381" s="3" t="inlineStr">
@@ -37538,7 +37538,7 @@
       </c>
       <c r="H382" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I382" s="5" t="inlineStr">
@@ -37624,7 +37624,7 @@
       </c>
       <c r="H383" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I383" s="3" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="H384" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I384" s="5" t="inlineStr">
@@ -37796,7 +37796,7 @@
       </c>
       <c r="H385" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I385" s="3" t="inlineStr">
@@ -37890,7 +37890,7 @@
       </c>
       <c r="H386" s="5" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I386" s="5" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="H387" s="3" t="inlineStr">
         <is>
-          <t>Job Change</t>
+          <t>OGC-MFG-MDI-MMJ-JCS</t>
         </is>
       </c>
       <c r="I387" s="3" t="inlineStr">
@@ -38070,7 +38070,7 @@
       </c>
       <c r="H388" s="5" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I388" s="5" t="inlineStr">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="H389" s="3" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I389" s="3" t="inlineStr">
@@ -38250,7 +38250,7 @@
       </c>
       <c r="H390" s="5" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I390" s="5" t="inlineStr">
@@ -38344,7 +38344,7 @@
       </c>
       <c r="H391" s="3" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I391" s="3" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H392" s="5" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I392" s="5" t="inlineStr">
@@ -38524,7 +38524,7 @@
       </c>
       <c r="H393" s="3" t="inlineStr">
         <is>
-          <t>Mold Baking</t>
+          <t>OGC-MFG-MDI-MMJ-MBK</t>
         </is>
       </c>
       <c r="I393" s="3" t="inlineStr">
@@ -38622,7 +38622,7 @@
       </c>
       <c r="H394" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I394" s="5" t="inlineStr">
@@ -38716,7 +38716,7 @@
       </c>
       <c r="H395" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I395" s="3" t="inlineStr">
@@ -38806,7 +38806,7 @@
       </c>
       <c r="H396" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I396" s="5" t="inlineStr">
@@ -38896,7 +38896,7 @@
       </c>
       <c r="H397" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I397" s="3" t="inlineStr">
@@ -38986,7 +38986,7 @@
       </c>
       <c r="H398" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I398" s="5" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="H399" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I399" s="3" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H400" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I400" s="5" t="inlineStr">
@@ -39264,7 +39264,7 @@
       </c>
       <c r="H401" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I401" s="3" t="inlineStr">
@@ -39354,7 +39354,7 @@
       </c>
       <c r="H402" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I402" s="5" t="inlineStr">
@@ -39448,7 +39448,7 @@
       </c>
       <c r="H403" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I403" s="3" t="inlineStr">
@@ -39538,7 +39538,7 @@
       </c>
       <c r="H404" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I404" s="5" t="inlineStr">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="H405" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I405" s="3" t="inlineStr">
@@ -39722,7 +39722,7 @@
       </c>
       <c r="H406" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I406" s="5" t="inlineStr">
@@ -39808,7 +39808,7 @@
       </c>
       <c r="H407" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I407" s="3" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="H408" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I408" s="5" t="inlineStr">
@@ -39988,7 +39988,7 @@
       </c>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr">
@@ -40074,7 +40074,7 @@
       </c>
       <c r="H410" s="5" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I410" s="5" t="inlineStr">
@@ -40168,7 +40168,7 @@
       </c>
       <c r="H411" s="3" t="inlineStr">
         <is>
-          <t>Mold Repair</t>
+          <t>OGC-MFG-MDI-MMJ-MRP</t>
         </is>
       </c>
       <c r="I411" s="3" t="inlineStr">
@@ -40262,7 +40262,7 @@
       </c>
       <c r="H412" s="5" t="inlineStr">
         <is>
-          <t>Mold Maintenance &amp; Job Change</t>
+          <t>OGC-MFG-MDI-MMJ</t>
         </is>
       </c>
       <c r="I412" s="5" t="inlineStr">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="H413" s="3" t="inlineStr">
         <is>
-          <t>Mold Maintenance &amp; Job Change</t>
+          <t>OGC-MFG-MDI-MMJ</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="H414" s="5" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>OGC-MFG-MDI-MSS-ICM</t>
         </is>
       </c>
       <c r="I414" s="5" t="inlineStr">
@@ -40568,7 +40568,7 @@
       </c>
       <c r="H415" s="3" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>OGC-MFG-MDI-MSS-ICM</t>
         </is>
       </c>
       <c r="I415" s="3" t="inlineStr">
@@ -40670,7 +40670,7 @@
       </c>
       <c r="H416" s="5" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>OGC-MFG-MDI-MSS-ICM</t>
         </is>
       </c>
       <c r="I416" s="5" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>OGC-MFG-MDI-MSS-ICM</t>
         </is>
       </c>
       <c r="I417" s="3" t="inlineStr">
@@ -40866,7 +40866,7 @@
       </c>
       <c r="H418" s="5" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>OGC-MFG-MDI-MSS-ICM</t>
         </is>
       </c>
       <c r="I418" s="5" t="inlineStr">
@@ -40964,7 +40964,7 @@
       </c>
       <c r="H419" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I419" s="3" t="inlineStr">
@@ -41058,7 +41058,7 @@
       </c>
       <c r="H420" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I420" s="5" t="inlineStr">
@@ -41160,7 +41160,7 @@
       </c>
       <c r="H421" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I421" s="3" t="inlineStr">
@@ -41262,7 +41262,7 @@
       </c>
       <c r="H422" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I422" s="5" t="inlineStr">
@@ -41356,7 +41356,7 @@
       </c>
       <c r="H423" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I423" s="3" t="inlineStr">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="H424" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I424" s="5" t="inlineStr">
@@ -41556,7 +41556,7 @@
       </c>
       <c r="H425" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I425" s="3" t="inlineStr">
@@ -41654,7 +41654,7 @@
       </c>
       <c r="H426" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I426" s="5" t="inlineStr">
@@ -41752,7 +41752,7 @@
       </c>
       <c r="H427" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I427" s="3" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="H428" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I428" s="5" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H429" s="3" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I429" s="3" t="inlineStr">
@@ -42046,7 +42046,7 @@
       </c>
       <c r="H430" s="5" t="inlineStr">
         <is>
-          <t>Mold Services</t>
+          <t>OGC-MFG-MDI-MSS</t>
         </is>
       </c>
       <c r="I430" s="5" t="inlineStr">
@@ -42152,7 +42152,7 @@
       </c>
       <c r="H431" s="3" t="inlineStr">
         <is>
-          <t>Mold Design &amp; Innovation</t>
+          <t>OGC-MFG-MDI</t>
         </is>
       </c>
       <c r="I431" s="3" t="inlineStr">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="H432" s="5" t="inlineStr">
         <is>
-          <t>Data Administration</t>
+          <t>OGC-MFG-PFP-PII-DAM</t>
         </is>
       </c>
       <c r="I432" s="5" t="inlineStr">
@@ -42360,7 +42360,7 @@
       </c>
       <c r="H433" s="3" t="inlineStr">
         <is>
-          <t>Data Administration</t>
+          <t>OGC-MFG-PFP-PII-DAM</t>
         </is>
       </c>
       <c r="I433" s="3" t="inlineStr">
@@ -42462,7 +42462,7 @@
       </c>
       <c r="H434" s="5" t="inlineStr">
         <is>
-          <t>Data Administration</t>
+          <t>OGC-MFG-PFP-PII-DAM</t>
         </is>
       </c>
       <c r="I434" s="5" t="inlineStr">
@@ -42552,7 +42552,7 @@
       </c>
       <c r="H435" s="3" t="inlineStr">
         <is>
-          <t>Data Administration</t>
+          <t>OGC-MFG-PFP-PII-DAM</t>
         </is>
       </c>
       <c r="I435" s="3" t="inlineStr">
@@ -42650,7 +42650,7 @@
       </c>
       <c r="H436" s="5" t="inlineStr">
         <is>
-          <t>Data Administration</t>
+          <t>OGC-MFG-PFP-PII-DAM</t>
         </is>
       </c>
       <c r="I436" s="5" t="inlineStr">
@@ -42748,7 +42748,7 @@
       </c>
       <c r="H437" s="3" t="inlineStr">
         <is>
-          <t>Manufacturing Data Analytics</t>
+          <t>OGC-MFG-PFP-PII-DAM-MDA</t>
         </is>
       </c>
       <c r="I437" s="3" t="inlineStr">
@@ -42842,7 +42842,7 @@
       </c>
       <c r="H438" s="5" t="inlineStr">
         <is>
-          <t>Plant information &amp; Improvement</t>
+          <t>OGC-MFG-PFP-PII</t>
         </is>
       </c>
       <c r="I438" s="5" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="H439" s="3" t="inlineStr">
         <is>
-          <t>Plant information &amp; Improvement</t>
+          <t>OGC-MFG-PFP-PII</t>
         </is>
       </c>
       <c r="I439" s="3" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="H440" s="5" t="inlineStr">
         <is>
-          <t>Plant information &amp; Improvement</t>
+          <t>OGC-MFG-PFP-PII</t>
         </is>
       </c>
       <c r="I440" s="5" t="inlineStr">
@@ -43144,7 +43144,7 @@
       </c>
       <c r="H441" s="3" t="inlineStr">
         <is>
-          <t>Decorating</t>
+          <t>OGC-MFG-PFP-PTD-DEC</t>
         </is>
       </c>
       <c r="I441" s="3" t="inlineStr">
@@ -43238,7 +43238,7 @@
       </c>
       <c r="H442" s="5" t="inlineStr">
         <is>
-          <t>Decorating</t>
+          <t>OGC-MFG-PFP-PTD-DEC</t>
         </is>
       </c>
       <c r="I442" s="5" t="inlineStr">
@@ -43336,7 +43336,7 @@
       </c>
       <c r="H443" s="3" t="inlineStr">
         <is>
-          <t>Decorating</t>
+          <t>OGC-MFG-PFP-PTD-DEC</t>
         </is>
       </c>
       <c r="I443" s="3" t="inlineStr">
@@ -43430,7 +43430,7 @@
       </c>
       <c r="H444" s="5" t="inlineStr">
         <is>
-          <t>Decorating</t>
+          <t>OGC-MFG-PFP-PTD-DEC</t>
         </is>
       </c>
       <c r="I444" s="5" t="inlineStr">
@@ -43520,7 +43520,7 @@
       </c>
       <c r="H445" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I445" s="3" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="H446" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I446" s="5" t="inlineStr">
@@ -43712,7 +43712,7 @@
       </c>
       <c r="H447" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I447" s="3" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="H448" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I448" s="5" t="inlineStr">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="H449" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I449" s="3" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="H450" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I450" s="5" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="H451" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I451" s="3" t="inlineStr">
@@ -44174,7 +44174,7 @@
       </c>
       <c r="H452" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I452" s="5" t="inlineStr">
@@ -44276,7 +44276,7 @@
       </c>
       <c r="H453" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I453" s="3" t="inlineStr">
@@ -44366,7 +44366,7 @@
       </c>
       <c r="H454" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I454" s="5" t="inlineStr">
@@ -44452,7 +44452,7 @@
       </c>
       <c r="H455" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I455" s="3" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="H456" s="5" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I456" s="5" t="inlineStr">
@@ -44644,7 +44644,7 @@
       </c>
       <c r="H457" s="3" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>OGC-MFG-PFP-PTD-PRT</t>
         </is>
       </c>
       <c r="I457" s="3" t="inlineStr">
@@ -44730,7 +44730,7 @@
       </c>
       <c r="H458" s="5" t="inlineStr">
         <is>
-          <t>Printing &amp; Decorating Support</t>
+          <t>OGC-MFG-PFP-PTD-SUP</t>
         </is>
       </c>
       <c r="I458" s="5" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="H459" s="3" t="inlineStr">
         <is>
-          <t>Printing &amp; Decorating Support</t>
+          <t>OGC-MFG-PFP-PTD-SUP</t>
         </is>
       </c>
       <c r="I459" s="3" t="inlineStr">
@@ -44922,7 +44922,7 @@
       </c>
       <c r="H460" s="5" t="inlineStr">
         <is>
-          <t>Printing &amp; Decorating Support</t>
+          <t>OGC-MFG-PFP-PTD-SUP</t>
         </is>
       </c>
       <c r="I460" s="5" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="H461" s="3" t="inlineStr">
         <is>
-          <t>Printing &amp; Decorating</t>
+          <t>OGC-MFG-PFP-PTD</t>
         </is>
       </c>
       <c r="I461" s="3" t="inlineStr">
@@ -45126,7 +45126,7 @@
       </c>
       <c r="H462" s="5" t="inlineStr">
         <is>
-          <t>Printing &amp; Decorating</t>
+          <t>OGC-MFG-PFP-PTD</t>
         </is>
       </c>
       <c r="I462" s="5" t="inlineStr">
@@ -45216,7 +45216,7 @@
       </c>
       <c r="H463" s="3" t="inlineStr">
         <is>
-          <t>TQM &amp; TPM</t>
+          <t>OGC-MFG-PFP-TQM</t>
         </is>
       </c>
       <c r="I463" s="3" t="inlineStr">
@@ -45314,7 +45314,7 @@
       </c>
       <c r="H464" s="5" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I464" s="5" t="inlineStr">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="H465" s="3" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I465" s="3" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="H466" s="5" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I466" s="5" t="inlineStr">
@@ -45620,7 +45620,7 @@
       </c>
       <c r="H467" s="3" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I467" s="3" t="inlineStr">
@@ -45726,7 +45726,7 @@
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
@@ -45828,7 +45828,7 @@
       </c>
       <c r="H469" s="3" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I469" s="3" t="inlineStr">
@@ -45930,7 +45930,7 @@
       </c>
       <c r="H470" s="5" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I470" s="5" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="H471" s="3" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I471" s="3" t="inlineStr">
@@ -46126,7 +46126,7 @@
       </c>
       <c r="H472" s="5" t="inlineStr">
         <is>
-          <t>Production Planning</t>
+          <t>OGC-MFG-SPN-PPN</t>
         </is>
       </c>
       <c r="I472" s="5" t="inlineStr">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="H473" s="3" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I473" s="3" t="inlineStr">
@@ -46314,7 +46314,7 @@
       </c>
       <c r="H474" s="5" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I474" s="5" t="inlineStr">
@@ -46412,7 +46412,7 @@
       </c>
       <c r="H475" s="3" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I475" s="3" t="inlineStr">
@@ -46510,7 +46510,7 @@
       </c>
       <c r="H476" s="5" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I476" s="5" t="inlineStr">
@@ -46612,7 +46612,7 @@
       </c>
       <c r="H477" s="3" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I477" s="3" t="inlineStr">
@@ -46714,7 +46714,7 @@
       </c>
       <c r="H478" s="5" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Distribution</t>
+          <t>OGC-MFG-SPN-WHD</t>
         </is>
       </c>
       <c r="I478" s="5" t="inlineStr">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="H479" s="3" t="inlineStr">
         <is>
-          <t>Supply Planning</t>
+          <t>OGC-MFG-SPN</t>
         </is>
       </c>
       <c r="I479" s="3" t="inlineStr">
@@ -46910,7 +46910,7 @@
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>Internatinal Standards &amp; Compliance</t>
+          <t>OGC-MFG-000-SCI</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
@@ -47012,7 +47012,7 @@
       </c>
       <c r="H481" s="3" t="inlineStr">
         <is>
-          <t>Internatinal Standards &amp; Compliance</t>
+          <t>OGC-MFG-000-SCI</t>
         </is>
       </c>
       <c r="I481" s="3" t="inlineStr">
@@ -47110,7 +47110,7 @@
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>SHE</t>
+          <t>OGC-MFG-000-SHE</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="H483" s="3" t="inlineStr">
         <is>
-          <t>SHE</t>
+          <t>OGC-MFG-000-SHE</t>
         </is>
       </c>
       <c r="I483" s="3" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="H484" s="5" t="inlineStr">
         <is>
-          <t>SHE</t>
+          <t>OGC-MFG-000-SHE</t>
         </is>
       </c>
       <c r="I484" s="5" t="inlineStr">
@@ -47424,7 +47424,7 @@
       </c>
       <c r="H485" s="3" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I485" s="3" t="inlineStr">
@@ -47526,7 +47526,7 @@
       </c>
       <c r="H486" s="5" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I486" s="5" t="inlineStr">
@@ -47632,7 +47632,7 @@
       </c>
       <c r="H487" s="3" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I487" s="3" t="inlineStr">
@@ -47738,7 +47738,7 @@
       </c>
       <c r="H488" s="5" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I488" s="5" t="inlineStr">
@@ -47844,7 +47844,7 @@
       </c>
       <c r="H489" s="3" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I489" s="3" t="inlineStr">
@@ -47950,7 +47950,7 @@
       </c>
       <c r="H490" s="5" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I490" s="5" t="inlineStr">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="H491" s="3" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I491" s="3" t="inlineStr">
@@ -48162,7 +48162,7 @@
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>Shift Management</t>
+          <t>OGC-MFG-000-SMG</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
@@ -48268,7 +48268,7 @@
       </c>
       <c r="H493" s="3" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>OGC-MFG</t>
         </is>
       </c>
       <c r="I493" s="3" t="inlineStr">
@@ -48358,7 +48358,7 @@
       </c>
       <c r="H494" s="5" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I494" s="5" t="inlineStr">
@@ -48452,7 +48452,7 @@
       </c>
       <c r="H495" s="3" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I495" s="3" t="inlineStr">
@@ -48558,7 +48558,7 @@
       </c>
       <c r="H496" s="5" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I496" s="5" t="inlineStr">
@@ -48656,7 +48656,7 @@
       </c>
       <c r="H497" s="3" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I497" s="3" t="inlineStr">
@@ -48754,7 +48754,7 @@
       </c>
       <c r="H498" s="5" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I498" s="5" t="inlineStr">
@@ -48852,7 +48852,7 @@
       </c>
       <c r="H499" s="3" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I499" s="3" t="inlineStr">
@@ -48946,7 +48946,7 @@
       </c>
       <c r="H500" s="5" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I500" s="5" t="inlineStr">
@@ -49036,7 +49036,7 @@
       </c>
       <c r="H501" s="3" t="inlineStr">
         <is>
-          <t>Creative Works</t>
+          <t>OGC-MKT-DSC-GCD</t>
         </is>
       </c>
       <c r="I501" s="3" t="inlineStr">
@@ -49126,7 +49126,7 @@
       </c>
       <c r="H502" s="5" t="inlineStr">
         <is>
-          <t>Product &amp; Packaging</t>
+          <t>OGC-MKT-DSC-PPD</t>
         </is>
       </c>
       <c r="I502" s="5" t="inlineStr">
@@ -49220,7 +49220,7 @@
       </c>
       <c r="H503" s="3" t="inlineStr">
         <is>
-          <t>Product &amp; Packaging</t>
+          <t>OGC-MKT-DSC-PPD</t>
         </is>
       </c>
       <c r="I503" s="3" t="inlineStr">
@@ -49326,7 +49326,7 @@
       </c>
       <c r="H504" s="5" t="inlineStr">
         <is>
-          <t>Product &amp; Packaging</t>
+          <t>OGC-MKT-DSC-PPD</t>
         </is>
       </c>
       <c r="I504" s="5" t="inlineStr">
@@ -49432,7 +49432,7 @@
       </c>
       <c r="H505" s="3" t="inlineStr">
         <is>
-          <t>Product &amp; Packaging</t>
+          <t>OGC-MKT-DSC-PPD</t>
         </is>
       </c>
       <c r="I505" s="3" t="inlineStr">
@@ -49522,7 +49522,7 @@
       </c>
       <c r="H506" s="5" t="inlineStr">
         <is>
-          <t>Design &amp; Creative</t>
+          <t>OGC-MKT-DSC</t>
         </is>
       </c>
       <c r="I506" s="5" t="inlineStr">
@@ -49612,7 +49612,7 @@
       </c>
       <c r="H507" s="3" t="inlineStr">
         <is>
-          <t>Design &amp; Creative</t>
+          <t>OGC-MKT-DSC</t>
         </is>
       </c>
       <c r="I507" s="3" t="inlineStr">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="H508" s="5" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>OGC-MKT-MKT-BRA</t>
         </is>
       </c>
       <c r="I508" s="5" t="inlineStr">
@@ -49812,7 +49812,7 @@
       </c>
       <c r="H509" s="3" t="inlineStr">
         <is>
-          <t>Ocean &amp; Posh</t>
+          <t>OGC-MKT-MKT-BRA-OCP</t>
         </is>
       </c>
       <c r="I509" s="3" t="inlineStr">
@@ -49910,7 +49910,7 @@
       </c>
       <c r="H510" s="5" t="inlineStr">
         <is>
-          <t>CXM</t>
+          <t>OGC-MKT-MKT-CXM</t>
         </is>
       </c>
       <c r="I510" s="5" t="inlineStr">
@@ -50008,7 +50008,7 @@
       </c>
       <c r="H511" s="3" t="inlineStr">
         <is>
-          <t>Marcom &amp; CRM</t>
+          <t>OGC-MKT-MKT-CXM-CRM</t>
         </is>
       </c>
       <c r="I511" s="3" t="inlineStr">
@@ -50106,7 +50106,7 @@
       </c>
       <c r="H512" s="5" t="inlineStr">
         <is>
-          <t>Merchandising</t>
+          <t>OGC-MKT-MKT-CXM-MCD</t>
         </is>
       </c>
       <c r="I512" s="5" t="inlineStr">
@@ -50204,7 +50204,7 @@
       </c>
       <c r="H513" s="3" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>OGC-MKT-MKT-PRD</t>
         </is>
       </c>
       <c r="I513" s="3" t="inlineStr">
@@ -50306,7 +50306,7 @@
       </c>
       <c r="H514" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>OGC-MKT-MKT-PRD</t>
         </is>
       </c>
       <c r="I514" s="5" t="inlineStr">
@@ -50396,7 +50396,7 @@
       </c>
       <c r="H515" s="3" t="inlineStr">
         <is>
-          <t>Sodalime</t>
+          <t>OGC-MKT-MKT-PRD-SDM</t>
         </is>
       </c>
       <c r="I515" s="3" t="inlineStr">
@@ -50498,7 +50498,7 @@
       </c>
       <c r="H516" s="5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>OGC-MKT</t>
         </is>
       </c>
       <c r="I516" s="5" t="inlineStr">
@@ -50604,7 +50604,7 @@
       </c>
       <c r="H517" s="3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>OGC-MKT</t>
         </is>
       </c>
       <c r="I517" s="3" t="inlineStr">
@@ -50702,7 +50702,7 @@
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>OGC-MKT</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
@@ -50792,7 +50792,7 @@
       </c>
       <c r="H519" s="3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>OGC-MKT</t>
         </is>
       </c>
       <c r="I519" s="3" t="inlineStr">
@@ -50890,7 +50890,7 @@
       </c>
       <c r="H520" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I520" s="5" t="inlineStr">
@@ -50992,7 +50992,7 @@
       </c>
       <c r="H521" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I521" s="3" t="inlineStr">
@@ -51090,7 +51090,7 @@
       </c>
       <c r="H522" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I522" s="5" t="inlineStr">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="H523" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I523" s="3" t="inlineStr">
@@ -51282,7 +51282,7 @@
       </c>
       <c r="H524" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I524" s="5" t="inlineStr">
@@ -51380,7 +51380,7 @@
       </c>
       <c r="H525" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I525" s="3" t="inlineStr">
@@ -51474,7 +51474,7 @@
       </c>
       <c r="H526" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I526" s="5" t="inlineStr">
@@ -51568,7 +51568,7 @@
       </c>
       <c r="H527" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I527" s="3" t="inlineStr">
@@ -51662,7 +51662,7 @@
       </c>
       <c r="H528" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I528" s="5" t="inlineStr">
@@ -51760,7 +51760,7 @@
       </c>
       <c r="H529" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I529" s="3" t="inlineStr">
@@ -51862,7 +51862,7 @@
       </c>
       <c r="H530" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I530" s="5" t="inlineStr">
@@ -51960,7 +51960,7 @@
       </c>
       <c r="H531" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I531" s="3" t="inlineStr">
@@ -52058,7 +52058,7 @@
       </c>
       <c r="H532" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I532" s="5" t="inlineStr">
@@ -52156,7 +52156,7 @@
       </c>
       <c r="H533" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I533" s="3" t="inlineStr">
@@ -52250,7 +52250,7 @@
       </c>
       <c r="H534" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I534" s="5" t="inlineStr">
@@ -52344,7 +52344,7 @@
       </c>
       <c r="H535" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I535" s="3" t="inlineStr">
@@ -52438,7 +52438,7 @@
       </c>
       <c r="H536" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I536" s="5" t="inlineStr">
@@ -52532,7 +52532,7 @@
       </c>
       <c r="H537" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I537" s="3" t="inlineStr">
@@ -52630,7 +52630,7 @@
       </c>
       <c r="H538" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I538" s="5" t="inlineStr">
@@ -52728,7 +52728,7 @@
       </c>
       <c r="H539" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I539" s="3" t="inlineStr">
@@ -52822,7 +52822,7 @@
       </c>
       <c r="H540" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I540" s="5" t="inlineStr">
@@ -52916,7 +52916,7 @@
       </c>
       <c r="H541" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I541" s="3" t="inlineStr">
@@ -53010,7 +53010,7 @@
       </c>
       <c r="H542" s="5" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I542" s="5" t="inlineStr">
@@ -53104,7 +53104,7 @@
       </c>
       <c r="H543" s="3" t="inlineStr">
         <is>
-          <t>Inspection &amp; Packing</t>
+          <t>OGC-000-QMT-IPK</t>
         </is>
       </c>
       <c r="I543" s="3" t="inlineStr">
@@ -53202,7 +53202,7 @@
       </c>
       <c r="H544" s="5" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>OGC-000-QMT-LAB</t>
         </is>
       </c>
       <c r="I544" s="5" t="inlineStr">
@@ -53304,7 +53304,7 @@
       </c>
       <c r="H545" s="3" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>OGC-000-QMT-LAB</t>
         </is>
       </c>
       <c r="I545" s="3" t="inlineStr">
@@ -53402,7 +53402,7 @@
       </c>
       <c r="H546" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I546" s="5" t="inlineStr">
@@ -53508,7 +53508,7 @@
       </c>
       <c r="H547" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I547" s="3" t="inlineStr">
@@ -53602,7 +53602,7 @@
       </c>
       <c r="H548" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I548" s="5" t="inlineStr">
@@ -53688,7 +53688,7 @@
       </c>
       <c r="H549" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I549" s="3" t="inlineStr">
@@ -53790,7 +53790,7 @@
       </c>
       <c r="H550" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I550" s="5" t="inlineStr">
@@ -53892,7 +53892,7 @@
       </c>
       <c r="H551" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I551" s="3" t="inlineStr">
@@ -53994,7 +53994,7 @@
       </c>
       <c r="H552" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I552" s="5" t="inlineStr">
@@ -54092,7 +54092,7 @@
       </c>
       <c r="H553" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I553" s="3" t="inlineStr">
@@ -54190,7 +54190,7 @@
       </c>
       <c r="H554" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I554" s="5" t="inlineStr">
@@ -54284,7 +54284,7 @@
       </c>
       <c r="H555" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I555" s="3" t="inlineStr">
@@ -54378,7 +54378,7 @@
       </c>
       <c r="H556" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I556" s="5" t="inlineStr">
@@ -54472,7 +54472,7 @@
       </c>
       <c r="H557" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I557" s="3" t="inlineStr">
@@ -54558,7 +54558,7 @@
       </c>
       <c r="H558" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I558" s="5" t="inlineStr">
@@ -54644,7 +54644,7 @@
       </c>
       <c r="H559" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I559" s="3" t="inlineStr">
@@ -54730,7 +54730,7 @@
       </c>
       <c r="H560" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I560" s="5" t="inlineStr">
@@ -54824,7 +54824,7 @@
       </c>
       <c r="H561" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I561" s="3" t="inlineStr">
@@ -54922,7 +54922,7 @@
       </c>
       <c r="H562" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I562" s="5" t="inlineStr">
@@ -55020,7 +55020,7 @@
       </c>
       <c r="H563" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I563" s="3" t="inlineStr">
@@ -55114,7 +55114,7 @@
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
@@ -55208,7 +55208,7 @@
       </c>
       <c r="H565" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I565" s="3" t="inlineStr">
@@ -55302,7 +55302,7 @@
       </c>
       <c r="H566" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I566" s="5" t="inlineStr">
@@ -55396,7 +55396,7 @@
       </c>
       <c r="H567" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I567" s="3" t="inlineStr">
@@ -55490,7 +55490,7 @@
       </c>
       <c r="H568" s="5" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I568" s="5" t="inlineStr">
@@ -55584,7 +55584,7 @@
       </c>
       <c r="H569" s="3" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>OGC-000-QMT-QCS</t>
         </is>
       </c>
       <c r="I569" s="3" t="inlineStr">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="H570" s="5" t="inlineStr">
         <is>
-          <t>Quality System</t>
+          <t>OGC-000-QMT-QST</t>
         </is>
       </c>
       <c r="I570" s="5" t="inlineStr">
@@ -55776,7 +55776,7 @@
       </c>
       <c r="H571" s="3" t="inlineStr">
         <is>
-          <t>Quality System</t>
+          <t>OGC-000-QMT-QST</t>
         </is>
       </c>
       <c r="I571" s="3" t="inlineStr">
@@ -55882,7 +55882,7 @@
       </c>
       <c r="H572" s="5" t="inlineStr">
         <is>
-          <t>Quality Management</t>
+          <t>OGC-000-QMT</t>
         </is>
       </c>
       <c r="I572" s="5" t="inlineStr">
@@ -55988,7 +55988,7 @@
       </c>
       <c r="H573" s="3" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>OGC-000-000-STR</t>
         </is>
       </c>
       <c r="I573" s="3" t="inlineStr">
@@ -56086,7 +56086,7 @@
       </c>
       <c r="H574" s="5" t="inlineStr">
         <is>
-          <t>บริษัท โอเชียนกลาส จำกัด (มหาชน)</t>
+          <t>OGC</t>
         </is>
       </c>
       <c r="I574" s="5" t="inlineStr"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C64191B-0B35-4BB9-9560-9986F1AA4F73}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20879,9 +20879,7 @@
       <c r="X97" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y97" s="6">
-        <v>11111</v>
-      </c>
+      <c r="Y97" s="6"/>
     </row>
     <row r="98" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C64191B-0B35-4BB9-9560-9986F1AA4F73}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C15A56AE-0EAD-42CF-B0E0-09D068B152EA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14235,6 +14235,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20879,7 +20883,9 @@
       <c r="X97" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y97" s="6"/>
+      <c r="Y97" s="6">
+        <v>168015</v>
+      </c>
     </row>
     <row r="98" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C15A56AE-0EAD-42CF-B0E0-09D068B152EA}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF998899-4113-4BDC-BE89-E91C874FAA83}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14743,8 +14743,8 @@
       <c r="G4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>32</v>
+      <c r="H4" s="2" t="s">
+        <v>3946</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>48</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF998899-4113-4BDC-BE89-E91C874FAA83}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FB9C0D-2387-4796-8A1C-DB7C3FF01D2B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15410,8 +15410,8 @@
       <c r="H14" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>100</v>
+      <c r="I14" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>168</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -10,13 +10,24 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FB9C0D-2387-4796-8A1C-DB7C3FF01D2B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FB9C0D-2387-4796-8A1C-DB7C3FF01D2B}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99D7226-0DFF-4715-9E22-998FADE3D3A9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="4693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="4694">
   <si>
     <t>as_of_date=3 เมษายน 2569</t>
   </si>
@@ -14111,6 +14111,9 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>RP90</t>
   </si>
 </sst>
 </file>
@@ -16116,7 +16119,7 @@
         <v>41</v>
       </c>
       <c r="Y24" s="7" t="s">
-        <v>33</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="14_{615F6A89-3BDB-4CC6-A1F5-370B53371313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99D7226-0DFF-4715-9E22-998FADE3D3A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$574</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="4694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="4692">
   <si>
     <t>as_of_date=3 เมษายน 2569</t>
   </si>
@@ -11869,9 +11872,6 @@
     <t>Executive Director - Manufacturing</t>
   </si>
   <si>
-    <t>6(17C)</t>
-  </si>
-  <si>
     <t>OGC-MFG</t>
   </si>
   <si>
@@ -12527,9 +12527,6 @@
   </si>
   <si>
     <t>Executive Director - Marketing</t>
-  </si>
-  <si>
-    <t>6(17A)</t>
   </si>
   <si>
     <t>07/02/1971</t>
@@ -14249,10 +14246,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14758,7 +14751,7 @@
         <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>48</v>
@@ -16119,7 +16112,7 @@
         <v>41</v>
       </c>
       <c r="Y24" s="7" t="s">
-        <v>4693</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -46328,16 +46321,16 @@
         <v>3944</v>
       </c>
       <c r="G493" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="H493" s="2" t="s">
         <v>3945</v>
-      </c>
-      <c r="H493" s="2" t="s">
-        <v>3946</v>
       </c>
       <c r="I493" s="2" t="s">
         <v>272</v>
       </c>
       <c r="J493" s="2" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="K493" s="2" t="s">
         <v>955</v>
@@ -46349,10 +46342,10 @@
         <v>0.93</v>
       </c>
       <c r="N493" s="2" t="s">
+        <v>3947</v>
+      </c>
+      <c r="O493" s="2" t="s">
         <v>3948</v>
-      </c>
-      <c r="O493" s="2" t="s">
-        <v>3949</v>
       </c>
       <c r="P493" s="2"/>
       <c r="Q493" s="2"/>
@@ -46377,33 +46370,33 @@
     </row>
     <row r="494" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B494" s="4" t="s">
         <v>3950</v>
       </c>
-      <c r="B494" s="4" t="s">
+      <c r="C494" s="4" t="s">
         <v>3951</v>
-      </c>
-      <c r="C494" s="4" t="s">
-        <v>3952</v>
       </c>
       <c r="D494" s="4"/>
       <c r="E494" s="4"/>
       <c r="F494" s="4" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="G494" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H494" s="4" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I494" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="I494" s="4" t="s">
+      <c r="J494" s="4" t="s">
         <v>3955</v>
       </c>
-      <c r="J494" s="4" t="s">
+      <c r="K494" s="4" t="s">
         <v>3956</v>
-      </c>
-      <c r="K494" s="4" t="s">
-        <v>3957</v>
       </c>
       <c r="L494" s="5">
         <v>54.52</v>
@@ -46412,10 +46405,10 @@
         <v>21.3</v>
       </c>
       <c r="N494" s="4" t="s">
+        <v>3957</v>
+      </c>
+      <c r="O494" s="4" t="s">
         <v>3958</v>
-      </c>
-      <c r="O494" s="4" t="s">
-        <v>3959</v>
       </c>
       <c r="P494" s="4"/>
       <c r="Q494" s="4"/>
@@ -46425,7 +46418,7 @@
         <v>38</v>
       </c>
       <c r="U494" s="4" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="V494" s="4" t="s">
         <v>41</v>
@@ -46440,33 +46433,33 @@
     </row>
     <row r="495" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="2" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B495" s="2" t="s">
         <v>3961</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="C495" s="2" t="s">
         <v>3962</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>3963</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" s="2"/>
       <c r="F495" s="2" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="G495" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H495" s="2" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I495" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="I495" s="2" t="s">
-        <v>3955</v>
-      </c>
       <c r="J495" s="2" t="s">
+        <v>3964</v>
+      </c>
+      <c r="K495" s="2" t="s">
         <v>3965</v>
-      </c>
-      <c r="K495" s="2" t="s">
-        <v>3966</v>
       </c>
       <c r="L495" s="3">
         <v>48.93</v>
@@ -46475,10 +46468,10 @@
         <v>19.510000000000002</v>
       </c>
       <c r="N495" s="2" t="s">
+        <v>3966</v>
+      </c>
+      <c r="O495" s="2" t="s">
         <v>3967</v>
-      </c>
-      <c r="O495" s="2" t="s">
-        <v>3968</v>
       </c>
       <c r="P495" s="2"/>
       <c r="Q495" s="2"/>
@@ -46505,13 +46498,13 @@
     </row>
     <row r="496" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="B496" s="4" t="s">
+        <v>3968</v>
+      </c>
+      <c r="C496" s="4" t="s">
         <v>3969</v>
-      </c>
-      <c r="C496" s="4" t="s">
-        <v>3970</v>
       </c>
       <c r="D496" s="4" t="s">
         <v>447</v>
@@ -46520,19 +46513,19 @@
         <v>447</v>
       </c>
       <c r="F496" s="4" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="G496" s="4" t="s">
         <v>868</v>
       </c>
       <c r="H496" s="4" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="I496" s="4" t="s">
+        <v>3971</v>
+      </c>
+      <c r="J496" s="4" t="s">
         <v>3972</v>
-      </c>
-      <c r="J496" s="4" t="s">
-        <v>3973</v>
       </c>
       <c r="K496" s="4" t="s">
         <v>2029</v>
@@ -46544,10 +46537,10 @@
         <v>17.850000000000001</v>
       </c>
       <c r="N496" s="4" t="s">
+        <v>3973</v>
+      </c>
+      <c r="O496" s="4" t="s">
         <v>3974</v>
-      </c>
-      <c r="O496" s="4" t="s">
-        <v>3975</v>
       </c>
       <c r="P496" s="4"/>
       <c r="Q496" s="4"/>
@@ -46559,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="U496" s="4" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="V496" s="4" t="s">
         <v>41</v>
@@ -46574,33 +46567,33 @@
     </row>
     <row r="497" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="2" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B497" s="2" t="s">
         <v>3977</v>
       </c>
-      <c r="B497" s="2" t="s">
+      <c r="C497" s="2" t="s">
         <v>3978</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>3979</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" s="2"/>
       <c r="F497" s="2" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="G497" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H497" s="2" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I497" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="I497" s="2" t="s">
-        <v>3955</v>
-      </c>
       <c r="J497" s="2" t="s">
+        <v>3979</v>
+      </c>
+      <c r="K497" s="2" t="s">
         <v>3980</v>
-      </c>
-      <c r="K497" s="2" t="s">
-        <v>3981</v>
       </c>
       <c r="L497" s="3">
         <v>37.630000000000003</v>
@@ -46609,10 +46602,10 @@
         <v>9.08</v>
       </c>
       <c r="N497" s="2" t="s">
+        <v>3981</v>
+      </c>
+      <c r="O497" s="2" t="s">
         <v>3982</v>
-      </c>
-      <c r="O497" s="2" t="s">
-        <v>3983</v>
       </c>
       <c r="P497" s="2"/>
       <c r="Q497" s="2"/>
@@ -46624,7 +46617,7 @@
         <v>1787</v>
       </c>
       <c r="U497" s="2" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="V497" s="2" t="s">
         <v>41</v>
@@ -46639,33 +46632,33 @@
     </row>
     <row r="498" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
+        <v>3984</v>
+      </c>
+      <c r="B498" s="4" t="s">
         <v>3985</v>
       </c>
-      <c r="B498" s="4" t="s">
+      <c r="C498" s="4" t="s">
         <v>3986</v>
-      </c>
-      <c r="C498" s="4" t="s">
-        <v>3987</v>
       </c>
       <c r="D498" s="4"/>
       <c r="E498" s="4"/>
       <c r="F498" s="4" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="G498" s="4" t="s">
         <v>177</v>
       </c>
       <c r="H498" s="4" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I498" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="I498" s="4" t="s">
-        <v>3955</v>
-      </c>
       <c r="J498" s="4" t="s">
+        <v>3987</v>
+      </c>
+      <c r="K498" s="4" t="s">
         <v>3988</v>
-      </c>
-      <c r="K498" s="4" t="s">
-        <v>3989</v>
       </c>
       <c r="L498" s="5">
         <v>36.35</v>
@@ -46674,10 +46667,10 @@
         <v>8.01</v>
       </c>
       <c r="N498" s="4" t="s">
+        <v>3989</v>
+      </c>
+      <c r="O498" s="4" t="s">
         <v>3990</v>
-      </c>
-      <c r="O498" s="4" t="s">
-        <v>3991</v>
       </c>
       <c r="P498" s="4"/>
       <c r="Q498" s="4"/>
@@ -46689,7 +46682,7 @@
         <v>67</v>
       </c>
       <c r="U498" s="4" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="V498" s="4" t="s">
         <v>41</v>
@@ -46704,33 +46697,33 @@
     </row>
     <row r="499" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="2" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B499" s="2" t="s">
         <v>3993</v>
       </c>
-      <c r="B499" s="2" t="s">
+      <c r="C499" s="2" t="s">
         <v>3994</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>3995</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" s="2"/>
       <c r="F499" s="2" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="G499" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H499" s="2" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I499" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="I499" s="2" t="s">
-        <v>3955</v>
-      </c>
       <c r="J499" s="2" t="s">
+        <v>3996</v>
+      </c>
+      <c r="K499" s="2" t="s">
         <v>3997</v>
-      </c>
-      <c r="K499" s="2" t="s">
-        <v>3998</v>
       </c>
       <c r="L499" s="3">
         <v>31.31</v>
@@ -46739,10 +46732,10 @@
         <v>2.63</v>
       </c>
       <c r="N499" s="2" t="s">
+        <v>3998</v>
+      </c>
+      <c r="O499" s="2" t="s">
         <v>3999</v>
-      </c>
-      <c r="O499" s="2" t="s">
-        <v>4000</v>
       </c>
       <c r="P499" s="2"/>
       <c r="Q499" s="2"/>
@@ -46767,30 +46760,30 @@
     </row>
     <row r="500" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B500" s="4" t="s">
         <v>4001</v>
       </c>
-      <c r="B500" s="4" t="s">
+      <c r="C500" s="4" t="s">
         <v>4002</v>
-      </c>
-      <c r="C500" s="4" t="s">
-        <v>4003</v>
       </c>
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
       <c r="F500" s="4" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="G500" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H500" s="4" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I500" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="I500" s="4" t="s">
-        <v>3955</v>
-      </c>
       <c r="J500" s="4" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="K500" s="4" t="s">
         <v>212</v>
@@ -46802,10 +46795,10 @@
         <v>2.39</v>
       </c>
       <c r="N500" s="4" t="s">
+        <v>4004</v>
+      </c>
+      <c r="O500" s="4" t="s">
         <v>4005</v>
-      </c>
-      <c r="O500" s="4" t="s">
-        <v>4006</v>
       </c>
       <c r="P500" s="4"/>
       <c r="Q500" s="4"/>
@@ -46828,33 +46821,33 @@
     </row>
     <row r="501" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B501" s="2" t="s">
         <v>4007</v>
       </c>
-      <c r="B501" s="2" t="s">
+      <c r="C501" s="2" t="s">
         <v>4008</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>4009</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" s="2"/>
       <c r="F501" s="2" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="G501" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H501" s="2" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I501" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="I501" s="2" t="s">
-        <v>3955</v>
-      </c>
       <c r="J501" s="2" t="s">
+        <v>4009</v>
+      </c>
+      <c r="K501" s="2" t="s">
         <v>4010</v>
-      </c>
-      <c r="K501" s="2" t="s">
-        <v>4011</v>
       </c>
       <c r="L501" s="3">
         <v>29.86</v>
@@ -46863,10 +46856,10 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="N501" s="2" t="s">
+        <v>4011</v>
+      </c>
+      <c r="O501" s="2" t="s">
         <v>4012</v>
-      </c>
-      <c r="O501" s="2" t="s">
-        <v>4013</v>
       </c>
       <c r="P501" s="2"/>
       <c r="Q501" s="2"/>
@@ -46889,33 +46882,33 @@
     </row>
     <row r="502" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B502" s="4" t="s">
         <v>4014</v>
       </c>
-      <c r="B502" s="4" t="s">
+      <c r="C502" s="4" t="s">
         <v>4015</v>
-      </c>
-      <c r="C502" s="4" t="s">
-        <v>4016</v>
       </c>
       <c r="D502" s="4"/>
       <c r="E502" s="4"/>
       <c r="F502" s="4" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="G502" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H502" s="4" t="s">
+        <v>4017</v>
+      </c>
+      <c r="I502" s="4" t="s">
         <v>4018</v>
       </c>
-      <c r="I502" s="4" t="s">
+      <c r="J502" s="4" t="s">
         <v>4019</v>
       </c>
-      <c r="J502" s="4" t="s">
+      <c r="K502" s="4" t="s">
         <v>4020</v>
-      </c>
-      <c r="K502" s="4" t="s">
-        <v>4021</v>
       </c>
       <c r="L502" s="5">
         <v>55.25</v>
@@ -46924,10 +46917,10 @@
         <v>32.75</v>
       </c>
       <c r="N502" s="4" t="s">
+        <v>4021</v>
+      </c>
+      <c r="O502" s="4" t="s">
         <v>4022</v>
-      </c>
-      <c r="O502" s="4" t="s">
-        <v>4023</v>
       </c>
       <c r="P502" s="4"/>
       <c r="Q502" s="4"/>
@@ -46937,7 +46930,7 @@
         <v>358</v>
       </c>
       <c r="U502" s="4" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="V502" s="4" t="s">
         <v>41</v>
@@ -46952,33 +46945,33 @@
     </row>
     <row r="503" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="2" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B503" s="2" t="s">
         <v>4025</v>
       </c>
-      <c r="B503" s="2" t="s">
+      <c r="C503" s="2" t="s">
         <v>4026</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>4027</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" s="2"/>
       <c r="F503" s="2" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="G503" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H503" s="2" t="s">
+        <v>4017</v>
+      </c>
+      <c r="I503" s="2" t="s">
         <v>4018</v>
       </c>
-      <c r="I503" s="2" t="s">
-        <v>4019</v>
-      </c>
       <c r="J503" s="2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="K503" s="2" t="s">
         <v>4029</v>
-      </c>
-      <c r="K503" s="2" t="s">
-        <v>4030</v>
       </c>
       <c r="L503" s="3">
         <v>50.68</v>
@@ -46987,10 +46980,10 @@
         <v>18.64</v>
       </c>
       <c r="N503" s="2" t="s">
+        <v>4030</v>
+      </c>
+      <c r="O503" s="2" t="s">
         <v>4031</v>
-      </c>
-      <c r="O503" s="2" t="s">
-        <v>4032</v>
       </c>
       <c r="P503" s="2"/>
       <c r="Q503" s="2"/>
@@ -47017,13 +47010,13 @@
     </row>
     <row r="504" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B504" s="4" t="s">
+        <v>4032</v>
+      </c>
+      <c r="C504" s="4" t="s">
         <v>4033</v>
-      </c>
-      <c r="C504" s="4" t="s">
-        <v>4034</v>
       </c>
       <c r="D504" s="4" t="s">
         <v>2874</v>
@@ -47032,19 +47025,19 @@
         <v>2874</v>
       </c>
       <c r="F504" s="4" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="G504" s="4" t="s">
         <v>868</v>
       </c>
       <c r="H504" s="4" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="I504" s="4" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="J504" s="4" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="K504" s="4" t="s">
         <v>1534</v>
@@ -47056,10 +47049,10 @@
         <v>23.97</v>
       </c>
       <c r="N504" s="4" t="s">
+        <v>4036</v>
+      </c>
+      <c r="O504" s="4" t="s">
         <v>4037</v>
-      </c>
-      <c r="O504" s="4" t="s">
-        <v>4038</v>
       </c>
       <c r="P504" s="4"/>
       <c r="Q504" s="4"/>
@@ -47068,10 +47061,10 @@
         <v>148</v>
       </c>
       <c r="T504" s="4" t="s">
+        <v>4038</v>
+      </c>
+      <c r="U504" s="4" t="s">
         <v>4039</v>
-      </c>
-      <c r="U504" s="4" t="s">
-        <v>4040</v>
       </c>
       <c r="V504" s="4" t="s">
         <v>41</v>
@@ -47086,13 +47079,13 @@
     </row>
     <row r="505" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="2" t="s">
+        <v>4040</v>
+      </c>
+      <c r="B505" s="2" t="s">
         <v>4041</v>
       </c>
-      <c r="B505" s="2" t="s">
+      <c r="C505" s="2" t="s">
         <v>4042</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>4043</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>2874</v>
@@ -47101,22 +47094,22 @@
         <v>2874</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="G505" s="2" t="s">
         <v>167</v>
       </c>
       <c r="H505" s="2" t="s">
+        <v>4017</v>
+      </c>
+      <c r="I505" s="2" t="s">
         <v>4018</v>
       </c>
-      <c r="I505" s="2" t="s">
-        <v>4019</v>
-      </c>
       <c r="J505" s="2" t="s">
+        <v>4044</v>
+      </c>
+      <c r="K505" s="2" t="s">
         <v>4045</v>
-      </c>
-      <c r="K505" s="2" t="s">
-        <v>4046</v>
       </c>
       <c r="L505" s="3">
         <v>43.31</v>
@@ -47125,10 +47118,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N505" s="2" t="s">
+        <v>4046</v>
+      </c>
+      <c r="O505" s="2" t="s">
         <v>4047</v>
-      </c>
-      <c r="O505" s="2" t="s">
-        <v>4048</v>
       </c>
       <c r="P505" s="2"/>
       <c r="Q505" s="2"/>
@@ -47151,33 +47144,33 @@
     </row>
     <row r="506" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
+        <v>4048</v>
+      </c>
+      <c r="B506" s="4" t="s">
         <v>4049</v>
       </c>
-      <c r="B506" s="4" t="s">
+      <c r="C506" s="4" t="s">
         <v>4050</v>
-      </c>
-      <c r="C506" s="4" t="s">
-        <v>4051</v>
       </c>
       <c r="D506" s="4"/>
       <c r="E506" s="4"/>
       <c r="F506" s="4" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="G506" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H506" s="4" t="s">
+        <v>4052</v>
+      </c>
+      <c r="I506" s="4" t="s">
+        <v>3954</v>
+      </c>
+      <c r="J506" s="4" t="s">
         <v>4053</v>
       </c>
-      <c r="I506" s="4" t="s">
-        <v>3955</v>
-      </c>
-      <c r="J506" s="4" t="s">
+      <c r="K506" s="4" t="s">
         <v>4054</v>
-      </c>
-      <c r="K506" s="4" t="s">
-        <v>4055</v>
       </c>
       <c r="L506" s="5">
         <v>29.2</v>
@@ -47186,10 +47179,10 @@
         <v>0.09</v>
       </c>
       <c r="N506" s="4" t="s">
+        <v>4055</v>
+      </c>
+      <c r="O506" s="4" t="s">
         <v>4056</v>
-      </c>
-      <c r="O506" s="4" t="s">
-        <v>4057</v>
       </c>
       <c r="P506" s="4"/>
       <c r="Q506" s="4"/>
@@ -47197,7 +47190,7 @@
       <c r="S506" s="4"/>
       <c r="T506" s="4"/>
       <c r="U506" s="4" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="V506" s="4" t="s">
         <v>55</v>
@@ -47212,33 +47205,33 @@
     </row>
     <row r="507" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="2" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="B507" s="2" t="s">
+        <v>4058</v>
+      </c>
+      <c r="C507" s="2" t="s">
         <v>4059</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>4060</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" s="2"/>
       <c r="F507" s="2" t="s">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="G507" s="2" t="s">
         <v>86</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="I507" s="2" t="s">
+        <v>4061</v>
+      </c>
+      <c r="J507" s="2" t="s">
         <v>4062</v>
       </c>
-      <c r="J507" s="2" t="s">
+      <c r="K507" s="2" t="s">
         <v>4063</v>
-      </c>
-      <c r="K507" s="2" t="s">
-        <v>4064</v>
       </c>
       <c r="L507" s="3">
         <v>48.74</v>
@@ -47247,20 +47240,20 @@
         <v>27.84</v>
       </c>
       <c r="N507" s="2" t="s">
+        <v>4064</v>
+      </c>
+      <c r="O507" s="2" t="s">
         <v>4065</v>
-      </c>
-      <c r="O507" s="2" t="s">
-        <v>4066</v>
       </c>
       <c r="P507" s="2"/>
       <c r="Q507" s="2"/>
       <c r="R507" s="2"/>
       <c r="S507" s="2" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="T507" s="2"/>
       <c r="U507" s="2" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="V507" s="2" t="s">
         <v>41</v>
@@ -47275,13 +47268,13 @@
     </row>
     <row r="508" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
+        <v>4068</v>
+      </c>
+      <c r="B508" s="4" t="s">
         <v>4069</v>
       </c>
-      <c r="B508" s="4" t="s">
+      <c r="C508" s="4" t="s">
         <v>4070</v>
-      </c>
-      <c r="C508" s="4" t="s">
-        <v>4071</v>
       </c>
       <c r="D508" s="4" t="s">
         <v>2780</v>
@@ -47290,22 +47283,22 @@
         <v>2780</v>
       </c>
       <c r="F508" s="4" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="G508" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H508" s="4" t="s">
+        <v>4072</v>
+      </c>
+      <c r="I508" s="4" t="s">
         <v>4073</v>
       </c>
-      <c r="I508" s="4" t="s">
+      <c r="J508" s="4" t="s">
         <v>4074</v>
       </c>
-      <c r="J508" s="4" t="s">
+      <c r="K508" s="4" t="s">
         <v>4075</v>
-      </c>
-      <c r="K508" s="4" t="s">
-        <v>4076</v>
       </c>
       <c r="L508" s="5">
         <v>42.95</v>
@@ -47314,10 +47307,10 @@
         <v>10.31</v>
       </c>
       <c r="N508" s="4" t="s">
+        <v>4076</v>
+      </c>
+      <c r="O508" s="4" t="s">
         <v>4077</v>
-      </c>
-      <c r="O508" s="4" t="s">
-        <v>4078</v>
       </c>
       <c r="P508" s="4"/>
       <c r="Q508" s="4"/>
@@ -47344,30 +47337,30 @@
     </row>
     <row r="509" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="2" t="s">
+        <v>4078</v>
+      </c>
+      <c r="B509" s="2" t="s">
         <v>4079</v>
       </c>
-      <c r="B509" s="2" t="s">
+      <c r="C509" s="2" t="s">
         <v>4080</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>4081</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" s="2"/>
       <c r="F509" s="2" t="s">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="G509" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H509" s="2" t="s">
+        <v>4082</v>
+      </c>
+      <c r="I509" s="2" t="s">
+        <v>4068</v>
+      </c>
+      <c r="J509" s="2" t="s">
         <v>4083</v>
-      </c>
-      <c r="I509" s="2" t="s">
-        <v>4069</v>
-      </c>
-      <c r="J509" s="2" t="s">
-        <v>4084</v>
       </c>
       <c r="K509" s="2" t="s">
         <v>494</v>
@@ -47379,10 +47372,10 @@
         <v>2.83</v>
       </c>
       <c r="N509" s="2" t="s">
+        <v>4084</v>
+      </c>
+      <c r="O509" s="2" t="s">
         <v>4085</v>
-      </c>
-      <c r="O509" s="2" t="s">
-        <v>4086</v>
       </c>
       <c r="P509" s="2"/>
       <c r="Q509" s="2"/>
@@ -47405,37 +47398,37 @@
     </row>
     <row r="510" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
+        <v>4086</v>
+      </c>
+      <c r="B510" s="4" t="s">
         <v>4087</v>
       </c>
-      <c r="B510" s="4" t="s">
+      <c r="C510" s="4" t="s">
         <v>4088</v>
       </c>
-      <c r="C510" s="4" t="s">
+      <c r="D510" s="4" t="s">
         <v>4089</v>
       </c>
-      <c r="D510" s="4" t="s">
+      <c r="E510" s="4" t="s">
+        <v>4089</v>
+      </c>
+      <c r="F510" s="4" t="s">
         <v>4090</v>
-      </c>
-      <c r="E510" s="4" t="s">
-        <v>4090</v>
-      </c>
-      <c r="F510" s="4" t="s">
-        <v>4091</v>
       </c>
       <c r="G510" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H510" s="4" t="s">
+        <v>4091</v>
+      </c>
+      <c r="I510" s="4" t="s">
+        <v>4073</v>
+      </c>
+      <c r="J510" s="4" t="s">
         <v>4092</v>
       </c>
-      <c r="I510" s="4" t="s">
-        <v>4074</v>
-      </c>
-      <c r="J510" s="4" t="s">
+      <c r="K510" s="4" t="s">
         <v>4093</v>
-      </c>
-      <c r="K510" s="4" t="s">
-        <v>4094</v>
       </c>
       <c r="L510" s="5">
         <v>36.74</v>
@@ -47444,10 +47437,10 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="N510" s="4" t="s">
+        <v>4094</v>
+      </c>
+      <c r="O510" s="4" t="s">
         <v>4095</v>
-      </c>
-      <c r="O510" s="4" t="s">
-        <v>4096</v>
       </c>
       <c r="P510" s="4"/>
       <c r="Q510" s="4"/>
@@ -47455,7 +47448,7 @@
       <c r="S510" s="4"/>
       <c r="T510" s="4"/>
       <c r="U510" s="4" t="s">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="V510" s="4" t="s">
         <v>41</v>
@@ -47470,34 +47463,34 @@
     </row>
     <row r="511" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="2" t="s">
+        <v>4097</v>
+      </c>
+      <c r="B511" s="2" t="s">
         <v>4098</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="C511" s="2" t="s">
         <v>4099</v>
       </c>
-      <c r="C511" s="2" t="s">
+      <c r="D511" s="2" t="s">
         <v>4100</v>
       </c>
-      <c r="D511" s="2" t="s">
+      <c r="E511" s="2" t="s">
+        <v>4100</v>
+      </c>
+      <c r="F511" s="2" t="s">
         <v>4101</v>
-      </c>
-      <c r="E511" s="2" t="s">
-        <v>4101</v>
-      </c>
-      <c r="F511" s="2" t="s">
-        <v>4102</v>
       </c>
       <c r="G511" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H511" s="2" t="s">
+        <v>4102</v>
+      </c>
+      <c r="I511" s="2" t="s">
+        <v>4086</v>
+      </c>
+      <c r="J511" s="2" t="s">
         <v>4103</v>
-      </c>
-      <c r="I511" s="2" t="s">
-        <v>4087</v>
-      </c>
-      <c r="J511" s="2" t="s">
-        <v>4104</v>
       </c>
       <c r="K511" s="2" t="s">
         <v>277</v>
@@ -47509,10 +47502,10 @@
         <v>2.1</v>
       </c>
       <c r="N511" s="2" t="s">
+        <v>4104</v>
+      </c>
+      <c r="O511" s="2" t="s">
         <v>4105</v>
-      </c>
-      <c r="O511" s="2" t="s">
-        <v>4106</v>
       </c>
       <c r="P511" s="2"/>
       <c r="Q511" s="2"/>
@@ -47535,31 +47528,31 @@
     </row>
     <row r="512" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
+        <v>4106</v>
+      </c>
+      <c r="B512" s="4" t="s">
         <v>4107</v>
       </c>
-      <c r="B512" s="4" t="s">
+      <c r="C512" s="4" t="s">
         <v>4108</v>
       </c>
-      <c r="C512" s="4" t="s">
+      <c r="D512" s="4" t="s">
         <v>4109</v>
       </c>
-      <c r="D512" s="4" t="s">
+      <c r="E512" s="4" t="s">
+        <v>4109</v>
+      </c>
+      <c r="F512" s="4" t="s">
         <v>4110</v>
-      </c>
-      <c r="E512" s="4" t="s">
-        <v>4110</v>
-      </c>
-      <c r="F512" s="4" t="s">
-        <v>4111</v>
       </c>
       <c r="G512" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H512" s="4" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="I512" s="4" t="s">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="J512" s="4" t="s">
         <v>2009</v>
@@ -47574,10 +47567,10 @@
         <v>0.01</v>
       </c>
       <c r="N512" s="4" t="s">
+        <v>4112</v>
+      </c>
+      <c r="O512" s="4" t="s">
         <v>4113</v>
-      </c>
-      <c r="O512" s="4" t="s">
-        <v>4114</v>
       </c>
       <c r="P512" s="4"/>
       <c r="Q512" s="4"/>
@@ -47600,13 +47593,13 @@
     </row>
     <row r="513" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="2" t="s">
+        <v>4114</v>
+      </c>
+      <c r="B513" s="2" t="s">
         <v>4115</v>
       </c>
-      <c r="B513" s="2" t="s">
+      <c r="C513" s="2" t="s">
         <v>4116</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>4117</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>2238</v>
@@ -47615,19 +47608,19 @@
         <v>2238</v>
       </c>
       <c r="F513" s="2" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="G513" s="2" t="s">
         <v>189</v>
       </c>
       <c r="H513" s="2" t="s">
+        <v>4117</v>
+      </c>
+      <c r="I513" s="2" t="s">
+        <v>4073</v>
+      </c>
+      <c r="J513" s="2" t="s">
         <v>4118</v>
-      </c>
-      <c r="I513" s="2" t="s">
-        <v>4074</v>
-      </c>
-      <c r="J513" s="2" t="s">
-        <v>4119</v>
       </c>
       <c r="K513" s="2" t="s">
         <v>694</v>
@@ -47639,10 +47632,10 @@
         <v>7.93</v>
       </c>
       <c r="N513" s="2" t="s">
+        <v>4119</v>
+      </c>
+      <c r="O513" s="2" t="s">
         <v>4120</v>
-      </c>
-      <c r="O513" s="2" t="s">
-        <v>4121</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" s="2"/>
@@ -47652,7 +47645,7 @@
       </c>
       <c r="T513" s="2"/>
       <c r="U513" s="2" t="s">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="V513" s="2" t="s">
         <v>41</v>
@@ -47667,13 +47660,13 @@
     </row>
     <row r="514" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B514" s="4" t="s">
         <v>4123</v>
       </c>
-      <c r="B514" s="4" t="s">
+      <c r="C514" s="4" t="s">
         <v>4124</v>
-      </c>
-      <c r="C514" s="4" t="s">
-        <v>4125</v>
       </c>
       <c r="D514" s="4" t="s">
         <v>3744</v>
@@ -47682,19 +47675,19 @@
         <v>3744</v>
       </c>
       <c r="F514" s="4" t="s">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="G514" s="4" t="s">
         <v>177</v>
       </c>
       <c r="H514" s="4" t="s">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="I514" s="4" t="s">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="J514" s="4" t="s">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="K514" s="4" t="s">
         <v>242</v>
@@ -47706,10 +47699,10 @@
         <v>0.01</v>
       </c>
       <c r="N514" s="4" t="s">
+        <v>4127</v>
+      </c>
+      <c r="O514" s="4" t="s">
         <v>4128</v>
-      </c>
-      <c r="O514" s="4" t="s">
-        <v>4129</v>
       </c>
       <c r="P514" s="4"/>
       <c r="Q514" s="4"/>
@@ -47732,30 +47725,30 @@
     </row>
     <row r="515" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="2" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B515" s="2" t="s">
         <v>4130</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="C515" s="2" t="s">
         <v>4131</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>4132</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" s="2"/>
       <c r="F515" s="2" t="s">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="G515" s="2" t="s">
         <v>189</v>
       </c>
       <c r="H515" s="2" t="s">
+        <v>4133</v>
+      </c>
+      <c r="I515" s="2" t="s">
+        <v>4114</v>
+      </c>
+      <c r="J515" s="2" t="s">
         <v>4134</v>
-      </c>
-      <c r="I515" s="2" t="s">
-        <v>4115</v>
-      </c>
-      <c r="J515" s="2" t="s">
-        <v>4135</v>
       </c>
       <c r="K515" s="2" t="s">
         <v>3126</v>
@@ -47767,10 +47760,10 @@
         <v>1.34</v>
       </c>
       <c r="N515" s="2" t="s">
+        <v>4135</v>
+      </c>
+      <c r="O515" s="2" t="s">
         <v>4136</v>
-      </c>
-      <c r="O515" s="2" t="s">
-        <v>4137</v>
       </c>
       <c r="P515" s="2"/>
       <c r="Q515" s="2"/>
@@ -47780,7 +47773,7 @@
         <v>38</v>
       </c>
       <c r="U515" s="2" t="s">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="V515" s="2" t="s">
         <v>40</v>
@@ -47795,13 +47788,13 @@
     </row>
     <row r="516" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="B516" s="4" t="s">
+        <v>4138</v>
+      </c>
+      <c r="C516" s="4" t="s">
         <v>4139</v>
-      </c>
-      <c r="C516" s="4" t="s">
-        <v>4140</v>
       </c>
       <c r="D516" s="4" t="s">
         <v>3720</v>
@@ -47810,22 +47803,22 @@
         <v>3720</v>
       </c>
       <c r="F516" s="4" t="s">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="G516" s="4" t="s">
         <v>270</v>
       </c>
       <c r="H516" s="4" t="s">
+        <v>4141</v>
+      </c>
+      <c r="I516" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="J516" s="4" t="s">
         <v>4142</v>
       </c>
-      <c r="I516" s="4" t="s">
-        <v>4062</v>
-      </c>
-      <c r="J516" s="4" t="s">
+      <c r="K516" s="4" t="s">
         <v>4143</v>
-      </c>
-      <c r="K516" s="4" t="s">
-        <v>4144</v>
       </c>
       <c r="L516" s="5">
         <v>51.44</v>
@@ -47834,10 +47827,10 @@
         <v>20.93</v>
       </c>
       <c r="N516" s="4" t="s">
+        <v>4144</v>
+      </c>
+      <c r="O516" s="4" t="s">
         <v>4145</v>
-      </c>
-      <c r="O516" s="4" t="s">
-        <v>4146</v>
       </c>
       <c r="P516" s="4"/>
       <c r="Q516" s="4"/>
@@ -47864,13 +47857,13 @@
     </row>
     <row r="517" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="2" t="s">
+        <v>4146</v>
+      </c>
+      <c r="B517" s="2" t="s">
         <v>4147</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="C517" s="2" t="s">
         <v>4148</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>4149</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>3501</v>
@@ -47879,19 +47872,19 @@
         <v>3501</v>
       </c>
       <c r="F517" s="2" t="s">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="G517" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="I517" s="2" t="s">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="K517" s="2" t="s">
         <v>3739</v>
@@ -47903,10 +47896,10 @@
         <v>1.26</v>
       </c>
       <c r="N517" s="2" t="s">
+        <v>4151</v>
+      </c>
+      <c r="O517" s="2" t="s">
         <v>4152</v>
-      </c>
-      <c r="O517" s="2" t="s">
-        <v>4153</v>
       </c>
       <c r="P517" s="2"/>
       <c r="Q517" s="2"/>
@@ -47929,13 +47922,13 @@
     </row>
     <row r="518" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
+        <v>4153</v>
+      </c>
+      <c r="B518" s="4" t="s">
         <v>4154</v>
       </c>
-      <c r="B518" s="4" t="s">
+      <c r="C518" s="4" t="s">
         <v>4155</v>
-      </c>
-      <c r="C518" s="4" t="s">
-        <v>4156</v>
       </c>
       <c r="D518" s="4" t="s">
         <v>581</v>
@@ -47944,22 +47937,22 @@
         <v>581</v>
       </c>
       <c r="F518" s="4" t="s">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="G518" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H518" s="4" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="I518" s="4" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="J518" s="4" t="s">
+        <v>4157</v>
+      </c>
+      <c r="K518" s="4" t="s">
         <v>4158</v>
-      </c>
-      <c r="K518" s="4" t="s">
-        <v>4159</v>
       </c>
       <c r="L518" s="5">
         <v>27.56</v>
@@ -47968,10 +47961,10 @@
         <v>0.08</v>
       </c>
       <c r="N518" s="4" t="s">
+        <v>4159</v>
+      </c>
+      <c r="O518" s="4" t="s">
         <v>4160</v>
-      </c>
-      <c r="O518" s="4" t="s">
-        <v>4161</v>
       </c>
       <c r="P518" s="4"/>
       <c r="Q518" s="4"/>
@@ -47994,33 +47987,33 @@
     </row>
     <row r="519" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="2" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="B519" s="2" t="s">
+        <v>4161</v>
+      </c>
+      <c r="C519" s="2" t="s">
         <v>4162</v>
-      </c>
-      <c r="C519" s="2" t="s">
-        <v>4163</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" s="2"/>
       <c r="F519" s="2" t="s">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="G519" s="2" t="s">
-        <v>4165</v>
+        <v>952</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="I519" s="2" t="s">
         <v>272</v>
       </c>
       <c r="J519" s="2" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="K519" s="2" t="s">
-        <v>4167</v>
+        <v>4165</v>
       </c>
       <c r="L519" s="3">
         <v>55.16</v>
@@ -48029,10 +48022,10 @@
         <v>3.05</v>
       </c>
       <c r="N519" s="2" t="s">
-        <v>4168</v>
+        <v>4166</v>
       </c>
       <c r="O519" s="2" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" s="2"/>
@@ -48052,39 +48045,39 @@
         <v>41</v>
       </c>
       <c r="Y519" s="6" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="520" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
+        <v>4168</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>4169</v>
+      </c>
+      <c r="C520" s="4" t="s">
         <v>4170</v>
       </c>
-      <c r="B520" s="4" t="s">
+      <c r="D520" s="4" t="s">
         <v>4171</v>
       </c>
-      <c r="C520" s="4" t="s">
+      <c r="E520" s="4" t="s">
+        <v>4171</v>
+      </c>
+      <c r="F520" s="4" t="s">
         <v>4172</v>
-      </c>
-      <c r="D520" s="4" t="s">
-        <v>4173</v>
-      </c>
-      <c r="E520" s="4" t="s">
-        <v>4173</v>
-      </c>
-      <c r="F520" s="4" t="s">
-        <v>4174</v>
       </c>
       <c r="G520" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H520" s="4" t="s">
+        <v>4173</v>
+      </c>
+      <c r="I520" s="4" t="s">
+        <v>4174</v>
+      </c>
+      <c r="J520" s="4" t="s">
         <v>4175</v>
-      </c>
-      <c r="I520" s="4" t="s">
-        <v>4176</v>
-      </c>
-      <c r="J520" s="4" t="s">
-        <v>4177</v>
       </c>
       <c r="K520" s="4" t="s">
         <v>1029</v>
@@ -48096,10 +48089,10 @@
         <v>34.590000000000003</v>
       </c>
       <c r="N520" s="4" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
       <c r="O520" s="4" t="s">
-        <v>4179</v>
+        <v>4177</v>
       </c>
       <c r="P520" s="4"/>
       <c r="Q520" s="4"/>
@@ -48109,7 +48102,7 @@
       </c>
       <c r="T520" s="4"/>
       <c r="U520" s="4" t="s">
-        <v>4180</v>
+        <v>4178</v>
       </c>
       <c r="V520" s="4" t="s">
         <v>301</v>
@@ -48124,34 +48117,34 @@
     </row>
     <row r="521" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="2" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C521" s="2" t="s">
         <v>4181</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="D521" s="2" t="s">
         <v>4182</v>
       </c>
-      <c r="C521" s="2" t="s">
+      <c r="E521" s="2" t="s">
+        <v>4182</v>
+      </c>
+      <c r="F521" s="2" t="s">
         <v>4183</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>4184</v>
-      </c>
-      <c r="E521" s="2" t="s">
-        <v>4184</v>
-      </c>
-      <c r="F521" s="2" t="s">
-        <v>4185</v>
       </c>
       <c r="G521" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I521" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J521" s="2" t="s">
-        <v>4186</v>
+        <v>4184</v>
       </c>
       <c r="K521" s="2" t="s">
         <v>3244</v>
@@ -48163,7 +48156,7 @@
         <v>15.06</v>
       </c>
       <c r="N521" s="2" t="s">
-        <v>4187</v>
+        <v>4185</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -48189,13 +48182,13 @@
     </row>
     <row r="522" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
+        <v>4186</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>4187</v>
+      </c>
+      <c r="C522" s="4" t="s">
         <v>4188</v>
-      </c>
-      <c r="B522" s="4" t="s">
-        <v>4189</v>
-      </c>
-      <c r="C522" s="4" t="s">
-        <v>4190</v>
       </c>
       <c r="D522" s="4" t="s">
         <v>2721</v>
@@ -48204,19 +48197,19 @@
         <v>2721</v>
       </c>
       <c r="F522" s="4" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G522" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H522" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I522" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J522" s="4" t="s">
-        <v>4192</v>
+        <v>4190</v>
       </c>
       <c r="K522" s="4" t="s">
         <v>1612</v>
@@ -48228,7 +48221,7 @@
         <v>5.17</v>
       </c>
       <c r="N522" s="4" t="s">
-        <v>4193</v>
+        <v>4191</v>
       </c>
       <c r="O522" s="4"/>
       <c r="P522" s="4"/>
@@ -48254,13 +48247,13 @@
     </row>
     <row r="523" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>4193</v>
+      </c>
+      <c r="C523" s="2" t="s">
         <v>4194</v>
-      </c>
-      <c r="B523" s="2" t="s">
-        <v>4195</v>
-      </c>
-      <c r="C523" s="2" t="s">
-        <v>4196</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>1808</v>
@@ -48269,16 +48262,16 @@
         <v>1808</v>
       </c>
       <c r="F523" s="2" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G523" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J523" s="2" t="s">
         <v>2714</v>
@@ -48293,7 +48286,7 @@
         <v>4.96</v>
       </c>
       <c r="N523" s="2" t="s">
-        <v>4197</v>
+        <v>4195</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -48317,34 +48310,34 @@
     </row>
     <row r="524" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>4197</v>
+      </c>
+      <c r="C524" s="4" t="s">
         <v>4198</v>
       </c>
-      <c r="B524" s="4" t="s">
+      <c r="D524" s="4" t="s">
         <v>4199</v>
       </c>
-      <c r="C524" s="4" t="s">
+      <c r="E524" s="4" t="s">
+        <v>4199</v>
+      </c>
+      <c r="F524" s="4" t="s">
         <v>4200</v>
-      </c>
-      <c r="D524" s="4" t="s">
-        <v>4201</v>
-      </c>
-      <c r="E524" s="4" t="s">
-        <v>4201</v>
-      </c>
-      <c r="F524" s="4" t="s">
-        <v>4202</v>
       </c>
       <c r="G524" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H524" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I524" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J524" s="4" t="s">
-        <v>4203</v>
+        <v>4201</v>
       </c>
       <c r="K524" s="4" t="s">
         <v>2715</v>
@@ -48356,7 +48349,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="N524" s="4" t="s">
-        <v>4204</v>
+        <v>4202</v>
       </c>
       <c r="O524" s="4"/>
       <c r="P524" s="4"/>
@@ -48382,31 +48375,31 @@
     </row>
     <row r="525" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
+        <v>4203</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>4204</v>
+      </c>
+      <c r="C525" s="2" t="s">
         <v>4205</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="D525" s="2" t="s">
         <v>4206</v>
       </c>
-      <c r="C525" s="2" t="s">
-        <v>4207</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>4208</v>
-      </c>
       <c r="E525" s="2" t="s">
-        <v>4208</v>
+        <v>4206</v>
       </c>
       <c r="F525" s="2" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G525" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J525" s="2" t="s">
         <v>703</v>
@@ -48421,7 +48414,7 @@
         <v>4.93</v>
       </c>
       <c r="N525" s="2" t="s">
-        <v>4209</v>
+        <v>4207</v>
       </c>
       <c r="O525" s="2"/>
       <c r="P525" s="2"/>
@@ -48430,7 +48423,7 @@
       <c r="S525" s="2"/>
       <c r="T525" s="2"/>
       <c r="U525" s="2" t="s">
-        <v>4210</v>
+        <v>4208</v>
       </c>
       <c r="V525" s="2" t="s">
         <v>41</v>
@@ -48445,13 +48438,13 @@
     </row>
     <row r="526" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
+        <v>4209</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>4210</v>
+      </c>
+      <c r="C526" s="4" t="s">
         <v>4211</v>
-      </c>
-      <c r="B526" s="4" t="s">
-        <v>4212</v>
-      </c>
-      <c r="C526" s="4" t="s">
-        <v>4213</v>
       </c>
       <c r="D526" s="4" t="s">
         <v>2131</v>
@@ -48460,19 +48453,19 @@
         <v>2131</v>
       </c>
       <c r="F526" s="4" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G526" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H526" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I526" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J526" s="4" t="s">
-        <v>4214</v>
+        <v>4212</v>
       </c>
       <c r="K526" s="4" t="s">
         <v>102</v>
@@ -48484,7 +48477,7 @@
         <v>4.76</v>
       </c>
       <c r="N526" s="4" t="s">
-        <v>4215</v>
+        <v>4213</v>
       </c>
       <c r="O526" s="4"/>
       <c r="P526" s="4"/>
@@ -48508,13 +48501,13 @@
     </row>
     <row r="527" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
+        <v>4214</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>4215</v>
+      </c>
+      <c r="C527" s="2" t="s">
         <v>4216</v>
-      </c>
-      <c r="B527" s="2" t="s">
-        <v>4217</v>
-      </c>
-      <c r="C527" s="2" t="s">
-        <v>4218</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>199</v>
@@ -48523,19 +48516,19 @@
         <v>199</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G527" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I527" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>4219</v>
+        <v>4217</v>
       </c>
       <c r="K527" s="2" t="s">
         <v>1902</v>
@@ -48547,7 +48540,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="N527" s="2" t="s">
-        <v>4220</v>
+        <v>4218</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -48571,13 +48564,13 @@
     </row>
     <row r="528" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
+        <v>4219</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>4220</v>
+      </c>
+      <c r="C528" s="4" t="s">
         <v>4221</v>
-      </c>
-      <c r="B528" s="4" t="s">
-        <v>4222</v>
-      </c>
-      <c r="C528" s="4" t="s">
-        <v>4223</v>
       </c>
       <c r="D528" s="4" t="s">
         <v>516</v>
@@ -48586,19 +48579,19 @@
         <v>516</v>
       </c>
       <c r="F528" s="4" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="G528" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H528" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I528" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>4225</v>
+        <v>4223</v>
       </c>
       <c r="K528" s="4" t="s">
         <v>2674</v>
@@ -48610,10 +48603,10 @@
         <v>3.47</v>
       </c>
       <c r="N528" s="4" t="s">
-        <v>4226</v>
+        <v>4224</v>
       </c>
       <c r="O528" s="4" t="s">
-        <v>4227</v>
+        <v>4225</v>
       </c>
       <c r="P528" s="4"/>
       <c r="Q528" s="4"/>
@@ -48636,34 +48629,34 @@
     </row>
     <row r="529" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>4227</v>
+      </c>
+      <c r="C529" s="2" t="s">
         <v>4228</v>
       </c>
-      <c r="B529" s="2" t="s">
+      <c r="D529" s="2" t="s">
         <v>4229</v>
       </c>
-      <c r="C529" s="2" t="s">
-        <v>4230</v>
-      </c>
-      <c r="D529" s="2" t="s">
-        <v>4231</v>
-      </c>
       <c r="E529" s="2" t="s">
-        <v>4231</v>
+        <v>4229</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="G529" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I529" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J529" s="2" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="K529" s="2" t="s">
         <v>67</v>
@@ -48675,10 +48668,10 @@
         <v>3.26</v>
       </c>
       <c r="N529" s="2" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="O529" s="2" t="s">
-        <v>4234</v>
+        <v>4232</v>
       </c>
       <c r="P529" s="2"/>
       <c r="Q529" s="2"/>
@@ -48688,7 +48681,7 @@
         <v>38</v>
       </c>
       <c r="U529" s="2" t="s">
-        <v>4235</v>
+        <v>4233</v>
       </c>
       <c r="V529" s="2" t="s">
         <v>40</v>
@@ -48703,34 +48696,34 @@
     </row>
     <row r="530" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
+        <v>4234</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>4235</v>
+      </c>
+      <c r="C530" s="4" t="s">
         <v>4236</v>
       </c>
-      <c r="B530" s="4" t="s">
+      <c r="D530" s="4" t="s">
         <v>4237</v>
       </c>
-      <c r="C530" s="4" t="s">
-        <v>4238</v>
-      </c>
-      <c r="D530" s="4" t="s">
-        <v>4239</v>
-      </c>
       <c r="E530" s="4" t="s">
-        <v>4239</v>
+        <v>4237</v>
       </c>
       <c r="F530" s="4" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G530" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H530" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I530" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>4240</v>
+        <v>4238</v>
       </c>
       <c r="K530" s="4" t="s">
         <v>1409</v>
@@ -48742,10 +48735,10 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="N530" s="4" t="s">
-        <v>4241</v>
+        <v>4239</v>
       </c>
       <c r="O530" s="4" t="s">
-        <v>4242</v>
+        <v>4240</v>
       </c>
       <c r="P530" s="4"/>
       <c r="Q530" s="4"/>
@@ -48768,34 +48761,34 @@
     </row>
     <row r="531" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>4241</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>4242</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>4243</v>
       </c>
-      <c r="C531" s="2" t="s">
+      <c r="E531" s="2" t="s">
+        <v>4243</v>
+      </c>
+      <c r="F531" s="2" t="s">
         <v>4244</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>4245</v>
-      </c>
-      <c r="E531" s="2" t="s">
-        <v>4245</v>
-      </c>
-      <c r="F531" s="2" t="s">
-        <v>4246</v>
       </c>
       <c r="G531" s="2" t="s">
         <v>86</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I531" s="2" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="J531" s="2" t="s">
-        <v>4248</v>
+        <v>4246</v>
       </c>
       <c r="K531" s="2" t="s">
         <v>1941</v>
@@ -48807,10 +48800,10 @@
         <v>1.72</v>
       </c>
       <c r="N531" s="2" t="s">
-        <v>4249</v>
+        <v>4247</v>
       </c>
       <c r="O531" s="2" t="s">
-        <v>4250</v>
+        <v>4248</v>
       </c>
       <c r="P531" s="2"/>
       <c r="Q531" s="2"/>
@@ -48818,7 +48811,7 @@
       <c r="S531" s="2"/>
       <c r="T531" s="2"/>
       <c r="U531" s="2" t="s">
-        <v>4251</v>
+        <v>4249</v>
       </c>
       <c r="V531" s="2" t="s">
         <v>301</v>
@@ -48833,34 +48826,34 @@
     </row>
     <row r="532" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
+        <v>4250</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>4251</v>
+      </c>
+      <c r="C532" s="4" t="s">
         <v>4252</v>
       </c>
-      <c r="B532" s="4" t="s">
+      <c r="D532" s="4" t="s">
         <v>4253</v>
       </c>
-      <c r="C532" s="4" t="s">
-        <v>4254</v>
-      </c>
-      <c r="D532" s="4" t="s">
-        <v>4255</v>
-      </c>
       <c r="E532" s="4" t="s">
-        <v>4255</v>
+        <v>4253</v>
       </c>
       <c r="F532" s="4" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
       <c r="G532" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H532" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I532" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J532" s="4" t="s">
-        <v>4256</v>
+        <v>4254</v>
       </c>
       <c r="K532" s="4" t="s">
         <v>1949</v>
@@ -48872,10 +48865,10 @@
         <v>1.64</v>
       </c>
       <c r="N532" s="4" t="s">
-        <v>4257</v>
+        <v>4255</v>
       </c>
       <c r="O532" s="4" t="s">
-        <v>4258</v>
+        <v>4256</v>
       </c>
       <c r="P532" s="4"/>
       <c r="Q532" s="4"/>
@@ -48898,34 +48891,34 @@
     </row>
     <row r="533" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
+        <v>4257</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>4258</v>
+      </c>
+      <c r="C533" s="2" t="s">
         <v>4259</v>
       </c>
-      <c r="B533" s="2" t="s">
+      <c r="D533" s="2" t="s">
         <v>4260</v>
       </c>
-      <c r="C533" s="2" t="s">
-        <v>4261</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>4262</v>
-      </c>
       <c r="E533" s="2" t="s">
-        <v>4262</v>
+        <v>4260</v>
       </c>
       <c r="F533" s="2" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="G533" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>4263</v>
+        <v>4261</v>
       </c>
       <c r="K533" s="2" t="s">
         <v>850</v>
@@ -48937,7 +48930,7 @@
         <v>1.59</v>
       </c>
       <c r="N533" s="2" t="s">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -48961,13 +48954,13 @@
     </row>
     <row r="534" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
+        <v>4263</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>4264</v>
+      </c>
+      <c r="C534" s="4" t="s">
         <v>4265</v>
-      </c>
-      <c r="B534" s="4" t="s">
-        <v>4266</v>
-      </c>
-      <c r="C534" s="4" t="s">
-        <v>4267</v>
       </c>
       <c r="D534" s="4" t="s">
         <v>492</v>
@@ -48976,19 +48969,19 @@
         <v>492</v>
       </c>
       <c r="F534" s="4" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="G534" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H534" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I534" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J534" s="4" t="s">
-        <v>4268</v>
+        <v>4266</v>
       </c>
       <c r="K534" s="4" t="s">
         <v>850</v>
@@ -49000,7 +48993,7 @@
         <v>1.59</v>
       </c>
       <c r="N534" s="4" t="s">
-        <v>4269</v>
+        <v>4267</v>
       </c>
       <c r="O534" s="4"/>
       <c r="P534" s="4"/>
@@ -49024,34 +49017,34 @@
     </row>
     <row r="535" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>4269</v>
+      </c>
+      <c r="C535" s="2" t="s">
         <v>4270</v>
       </c>
-      <c r="B535" s="2" t="s">
+      <c r="D535" s="2" t="s">
         <v>4271</v>
       </c>
-      <c r="C535" s="2" t="s">
-        <v>4272</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>4273</v>
-      </c>
       <c r="E535" s="2" t="s">
-        <v>4273</v>
+        <v>4271</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="G535" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>4274</v>
+        <v>4272</v>
       </c>
       <c r="K535" s="2" t="s">
         <v>675</v>
@@ -49063,7 +49056,7 @@
         <v>1.22</v>
       </c>
       <c r="N535" s="2" t="s">
-        <v>4275</v>
+        <v>4273</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -49087,34 +49080,34 @@
     </row>
     <row r="536" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
+        <v>4274</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>4275</v>
+      </c>
+      <c r="C536" s="4" t="s">
         <v>4276</v>
       </c>
-      <c r="B536" s="4" t="s">
+      <c r="D536" s="4" t="s">
         <v>4277</v>
       </c>
-      <c r="C536" s="4" t="s">
-        <v>4278</v>
-      </c>
-      <c r="D536" s="4" t="s">
-        <v>4279</v>
-      </c>
       <c r="E536" s="4" t="s">
-        <v>4279</v>
+        <v>4277</v>
       </c>
       <c r="F536" s="4" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G536" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H536" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I536" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J536" s="4" t="s">
-        <v>4280</v>
+        <v>4278</v>
       </c>
       <c r="K536" s="4" t="s">
         <v>675</v>
@@ -49126,7 +49119,7 @@
         <v>1.22</v>
       </c>
       <c r="N536" s="4" t="s">
-        <v>4281</v>
+        <v>4279</v>
       </c>
       <c r="O536" s="4"/>
       <c r="P536" s="4"/>
@@ -49135,7 +49128,7 @@
       <c r="S536" s="4"/>
       <c r="T536" s="4"/>
       <c r="U536" s="4" t="s">
-        <v>4282</v>
+        <v>4280</v>
       </c>
       <c r="V536" s="4" t="s">
         <v>41</v>
@@ -49150,13 +49143,13 @@
     </row>
     <row r="537" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>4282</v>
+      </c>
+      <c r="C537" s="2" t="s">
         <v>4283</v>
-      </c>
-      <c r="B537" s="2" t="s">
-        <v>4284</v>
-      </c>
-      <c r="C537" s="2" t="s">
-        <v>4285</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>2324</v>
@@ -49165,19 +49158,19 @@
         <v>2324</v>
       </c>
       <c r="F537" s="2" t="s">
-        <v>4286</v>
+        <v>4284</v>
       </c>
       <c r="G537" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I537" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
       <c r="K537" s="2" t="s">
         <v>400</v>
@@ -49189,10 +49182,10 @@
         <v>0.76</v>
       </c>
       <c r="N537" s="2" t="s">
-        <v>4288</v>
+        <v>4286</v>
       </c>
       <c r="O537" s="2" t="s">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537" s="2"/>
@@ -49215,34 +49208,34 @@
     </row>
     <row r="538" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
+        <v>4288</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>4289</v>
+      </c>
+      <c r="C538" s="4" t="s">
         <v>4290</v>
       </c>
-      <c r="B538" s="4" t="s">
+      <c r="D538" s="4" t="s">
         <v>4291</v>
       </c>
-      <c r="C538" s="4" t="s">
-        <v>4292</v>
-      </c>
-      <c r="D538" s="4" t="s">
-        <v>4293</v>
-      </c>
       <c r="E538" s="4" t="s">
-        <v>4293</v>
+        <v>4291</v>
       </c>
       <c r="F538" s="4" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
       <c r="G538" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H538" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I538" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J538" s="4" t="s">
-        <v>4294</v>
+        <v>4292</v>
       </c>
       <c r="K538" s="4" t="s">
         <v>2420</v>
@@ -49254,10 +49247,10 @@
         <v>0.68</v>
       </c>
       <c r="N538" s="4" t="s">
-        <v>4295</v>
+        <v>4293</v>
       </c>
       <c r="O538" s="4" t="s">
-        <v>4296</v>
+        <v>4294</v>
       </c>
       <c r="P538" s="4"/>
       <c r="Q538" s="4"/>
@@ -49280,34 +49273,34 @@
     </row>
     <row r="539" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
+        <v>4295</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>4296</v>
+      </c>
+      <c r="C539" s="2" t="s">
         <v>4297</v>
       </c>
-      <c r="B539" s="2" t="s">
+      <c r="D539" s="2" t="s">
         <v>4298</v>
       </c>
-      <c r="C539" s="2" t="s">
+      <c r="E539" s="2" t="s">
+        <v>4298</v>
+      </c>
+      <c r="F539" s="2" t="s">
         <v>4299</v>
-      </c>
-      <c r="D539" s="2" t="s">
-        <v>4300</v>
-      </c>
-      <c r="E539" s="2" t="s">
-        <v>4300</v>
-      </c>
-      <c r="F539" s="2" t="s">
-        <v>4301</v>
       </c>
       <c r="G539" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H539" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I539" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J539" s="2" t="s">
-        <v>4302</v>
+        <v>4300</v>
       </c>
       <c r="K539" s="2" t="s">
         <v>2420</v>
@@ -49319,7 +49312,7 @@
         <v>0.68</v>
       </c>
       <c r="N539" s="2" t="s">
-        <v>4303</v>
+        <v>4301</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" s="2"/>
@@ -49328,7 +49321,7 @@
       <c r="S539" s="2"/>
       <c r="T539" s="2"/>
       <c r="U539" s="2" t="s">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="V539" s="2" t="s">
         <v>41</v>
@@ -49343,34 +49336,34 @@
     </row>
     <row r="540" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>4304</v>
+      </c>
+      <c r="C540" s="4" t="s">
         <v>4305</v>
       </c>
-      <c r="B540" s="4" t="s">
+      <c r="D540" s="4" t="s">
         <v>4306</v>
       </c>
-      <c r="C540" s="4" t="s">
-        <v>4307</v>
-      </c>
-      <c r="D540" s="4" t="s">
-        <v>4308</v>
-      </c>
       <c r="E540" s="4" t="s">
-        <v>4308</v>
+        <v>4306</v>
       </c>
       <c r="F540" s="4" t="s">
-        <v>4301</v>
+        <v>4299</v>
       </c>
       <c r="G540" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H540" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I540" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J540" s="4" t="s">
-        <v>4309</v>
+        <v>4307</v>
       </c>
       <c r="K540" s="4" t="s">
         <v>2420</v>
@@ -49382,7 +49375,7 @@
         <v>0.68</v>
       </c>
       <c r="N540" s="4" t="s">
-        <v>4310</v>
+        <v>4308</v>
       </c>
       <c r="O540" s="4"/>
       <c r="P540" s="4"/>
@@ -49406,13 +49399,13 @@
     </row>
     <row r="541" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>4310</v>
+      </c>
+      <c r="C541" s="2" t="s">
         <v>4311</v>
-      </c>
-      <c r="B541" s="2" t="s">
-        <v>4312</v>
-      </c>
-      <c r="C541" s="2" t="s">
-        <v>4313</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>3858</v>
@@ -49421,19 +49414,19 @@
         <v>3858</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>4301</v>
+        <v>4299</v>
       </c>
       <c r="G541" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J541" s="2" t="s">
-        <v>4314</v>
+        <v>4312</v>
       </c>
       <c r="K541" s="2" t="s">
         <v>2420</v>
@@ -49445,7 +49438,7 @@
         <v>0.68</v>
       </c>
       <c r="N541" s="2" t="s">
-        <v>4315</v>
+        <v>4313</v>
       </c>
       <c r="O541" s="2"/>
       <c r="P541" s="2"/>
@@ -49469,34 +49462,34 @@
     </row>
     <row r="542" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
+        <v>4314</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>4315</v>
+      </c>
+      <c r="C542" s="4" t="s">
         <v>4316</v>
       </c>
-      <c r="B542" s="4" t="s">
+      <c r="D542" s="4" t="s">
         <v>4317</v>
       </c>
-      <c r="C542" s="4" t="s">
-        <v>4318</v>
-      </c>
-      <c r="D542" s="4" t="s">
-        <v>4319</v>
-      </c>
       <c r="E542" s="4" t="s">
-        <v>4319</v>
+        <v>4317</v>
       </c>
       <c r="F542" s="4" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="G542" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H542" s="4" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I542" s="4" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J542" s="4" t="s">
-        <v>4320</v>
+        <v>4318</v>
       </c>
       <c r="K542" s="4" t="s">
         <v>1730</v>
@@ -49508,7 +49501,7 @@
         <v>0.42</v>
       </c>
       <c r="N542" s="4" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="O542" s="4"/>
       <c r="P542" s="4"/>
@@ -49532,34 +49525,34 @@
     </row>
     <row r="543" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
+        <v>4320</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>4321</v>
+      </c>
+      <c r="C543" s="2" t="s">
         <v>4322</v>
       </c>
-      <c r="B543" s="2" t="s">
+      <c r="D543" s="2" t="s">
         <v>4323</v>
       </c>
-      <c r="C543" s="2" t="s">
-        <v>4324</v>
-      </c>
-      <c r="D543" s="2" t="s">
-        <v>4325</v>
-      </c>
       <c r="E543" s="2" t="s">
-        <v>4325</v>
+        <v>4323</v>
       </c>
       <c r="F543" s="2" t="s">
-        <v>4286</v>
+        <v>4284</v>
       </c>
       <c r="G543" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="I543" s="2" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="J543" s="2" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
       <c r="K543" s="2" t="s">
         <v>242</v>
@@ -49571,10 +49564,10 @@
         <v>0.01</v>
       </c>
       <c r="N543" s="2" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="O543" s="2" t="s">
-        <v>4327</v>
+        <v>4325</v>
       </c>
       <c r="P543" s="2"/>
       <c r="Q543" s="2"/>
@@ -49597,13 +49590,13 @@
     </row>
     <row r="544" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>4327</v>
+      </c>
+      <c r="C544" s="4" t="s">
         <v>4328</v>
-      </c>
-      <c r="B544" s="4" t="s">
-        <v>4329</v>
-      </c>
-      <c r="C544" s="4" t="s">
-        <v>4330</v>
       </c>
       <c r="D544" s="4" t="s">
         <v>3869</v>
@@ -49612,22 +49605,22 @@
         <v>3869</v>
       </c>
       <c r="F544" s="4" t="s">
-        <v>4331</v>
+        <v>4329</v>
       </c>
       <c r="G544" s="4" t="s">
         <v>98</v>
       </c>
       <c r="H544" s="4" t="s">
+        <v>4330</v>
+      </c>
+      <c r="I544" s="4" t="s">
+        <v>4245</v>
+      </c>
+      <c r="J544" s="4" t="s">
+        <v>4331</v>
+      </c>
+      <c r="K544" s="4" t="s">
         <v>4332</v>
-      </c>
-      <c r="I544" s="4" t="s">
-        <v>4247</v>
-      </c>
-      <c r="J544" s="4" t="s">
-        <v>4333</v>
-      </c>
-      <c r="K544" s="4" t="s">
-        <v>4334</v>
       </c>
       <c r="L544" s="5">
         <v>53.51</v>
@@ -49636,10 +49629,10 @@
         <v>34.090000000000003</v>
       </c>
       <c r="N544" s="4" t="s">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="O544" s="4" t="s">
-        <v>4336</v>
+        <v>4334</v>
       </c>
       <c r="P544" s="4"/>
       <c r="Q544" s="4"/>
@@ -49649,7 +49642,7 @@
       </c>
       <c r="T544" s="4"/>
       <c r="U544" s="4" t="s">
-        <v>4337</v>
+        <v>4335</v>
       </c>
       <c r="V544" s="4" t="s">
         <v>41</v>
@@ -49664,37 +49657,37 @@
     </row>
     <row r="545" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
+        <v>4336</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>4337</v>
+      </c>
+      <c r="C545" s="2" t="s">
         <v>4338</v>
       </c>
-      <c r="B545" s="2" t="s">
+      <c r="D545" s="2" t="s">
         <v>4339</v>
       </c>
-      <c r="C545" s="2" t="s">
-        <v>4340</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>4341</v>
-      </c>
       <c r="E545" s="2" t="s">
-        <v>4341</v>
+        <v>4339</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>4331</v>
+        <v>4329</v>
       </c>
       <c r="G545" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>4332</v>
+        <v>4330</v>
       </c>
       <c r="I545" s="2" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="J545" s="2" t="s">
-        <v>4342</v>
+        <v>4340</v>
       </c>
       <c r="K545" s="2" t="s">
-        <v>4343</v>
+        <v>4341</v>
       </c>
       <c r="L545" s="3">
         <v>41.25</v>
@@ -49703,10 +49696,10 @@
         <v>15.83</v>
       </c>
       <c r="N545" s="2" t="s">
-        <v>4344</v>
+        <v>4342</v>
       </c>
       <c r="O545" s="2" t="s">
-        <v>4345</v>
+        <v>4343</v>
       </c>
       <c r="P545" s="2"/>
       <c r="Q545" s="2"/>
@@ -49714,7 +49707,7 @@
       <c r="S545" s="2"/>
       <c r="T545" s="2"/>
       <c r="U545" s="2" t="s">
-        <v>4346</v>
+        <v>4344</v>
       </c>
       <c r="V545" s="2" t="s">
         <v>41</v>
@@ -49729,34 +49722,34 @@
     </row>
     <row r="546" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
+        <v>4345</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>4346</v>
+      </c>
+      <c r="C546" s="4" t="s">
         <v>4347</v>
       </c>
-      <c r="B546" s="4" t="s">
+      <c r="D546" s="4" t="s">
         <v>4348</v>
       </c>
-      <c r="C546" s="4" t="s">
+      <c r="E546" s="4" t="s">
+        <v>4348</v>
+      </c>
+      <c r="F546" s="4" t="s">
         <v>4349</v>
-      </c>
-      <c r="D546" s="4" t="s">
-        <v>4350</v>
-      </c>
-      <c r="E546" s="4" t="s">
-        <v>4350</v>
-      </c>
-      <c r="F546" s="4" t="s">
-        <v>4351</v>
       </c>
       <c r="G546" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H546" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I546" s="4" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="J546" s="4" t="s">
-        <v>4353</v>
+        <v>4351</v>
       </c>
       <c r="K546" s="4" t="s">
         <v>1453</v>
@@ -49768,10 +49761,10 @@
         <v>18.600000000000001</v>
       </c>
       <c r="N546" s="4" t="s">
-        <v>4354</v>
+        <v>4352</v>
       </c>
       <c r="O546" s="4" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
       <c r="P546" s="4"/>
       <c r="Q546" s="4"/>
@@ -49783,7 +49776,7 @@
         <v>478</v>
       </c>
       <c r="U546" s="4" t="s">
-        <v>4356</v>
+        <v>4354</v>
       </c>
       <c r="V546" s="4" t="s">
         <v>41</v>
@@ -49798,13 +49791,13 @@
     </row>
     <row r="547" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
+        <v>4355</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>4356</v>
+      </c>
+      <c r="C547" s="2" t="s">
         <v>4357</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>4358</v>
-      </c>
-      <c r="C547" s="2" t="s">
-        <v>4359</v>
       </c>
       <c r="D547" s="2" t="s">
         <v>3249</v>
@@ -49813,22 +49806,22 @@
         <v>3249</v>
       </c>
       <c r="F547" s="2" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
       <c r="G547" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H547" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I547" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J547" s="2" t="s">
-        <v>4361</v>
+        <v>4359</v>
       </c>
       <c r="K547" s="2" t="s">
-        <v>4362</v>
+        <v>4360</v>
       </c>
       <c r="L547" s="3">
         <v>45.04</v>
@@ -49837,7 +49830,7 @@
         <v>15.18</v>
       </c>
       <c r="N547" s="2" t="s">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="O547" s="2"/>
       <c r="P547" s="2"/>
@@ -49861,34 +49854,34 @@
     </row>
     <row r="548" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>4363</v>
+      </c>
+      <c r="C548" s="4" t="s">
         <v>4364</v>
       </c>
-      <c r="B548" s="4" t="s">
+      <c r="D548" s="4" t="s">
         <v>4365</v>
       </c>
-      <c r="C548" s="4" t="s">
+      <c r="E548" s="4" t="s">
+        <v>4365</v>
+      </c>
+      <c r="F548" s="4" t="s">
         <v>4366</v>
-      </c>
-      <c r="D548" s="4" t="s">
-        <v>4367</v>
-      </c>
-      <c r="E548" s="4" t="s">
-        <v>4367</v>
-      </c>
-      <c r="F548" s="4" t="s">
-        <v>4368</v>
       </c>
       <c r="G548" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H548" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I548" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J548" s="4" t="s">
-        <v>4369</v>
+        <v>4367</v>
       </c>
       <c r="K548" s="4" t="s">
         <v>1597</v>
@@ -49900,7 +49893,7 @@
         <v>14.81</v>
       </c>
       <c r="N548" s="4" t="s">
-        <v>4370</v>
+        <v>4368</v>
       </c>
       <c r="O548" s="4"/>
       <c r="P548" s="4"/>
@@ -49924,30 +49917,30 @@
     </row>
     <row r="549" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
+        <v>4369</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>4370</v>
+      </c>
+      <c r="C549" s="2" t="s">
         <v>4371</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>4372</v>
-      </c>
-      <c r="C549" s="2" t="s">
-        <v>4373</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" s="2"/>
       <c r="F549" s="2" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
       <c r="G549" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I549" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J549" s="2" t="s">
-        <v>4374</v>
+        <v>4372</v>
       </c>
       <c r="K549" s="2" t="s">
         <v>2262</v>
@@ -49959,7 +49952,7 @@
         <v>14.26</v>
       </c>
       <c r="N549" s="2" t="s">
-        <v>4375</v>
+        <v>4373</v>
       </c>
       <c r="O549" s="2"/>
       <c r="P549" s="2"/>
@@ -49972,7 +49965,7 @@
         <v>618</v>
       </c>
       <c r="U549" s="2" t="s">
-        <v>4376</v>
+        <v>4374</v>
       </c>
       <c r="V549" s="2" t="s">
         <v>41</v>
@@ -49987,13 +49980,13 @@
     </row>
     <row r="550" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
+        <v>4375</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>4376</v>
+      </c>
+      <c r="C550" s="4" t="s">
         <v>4377</v>
-      </c>
-      <c r="B550" s="4" t="s">
-        <v>4378</v>
-      </c>
-      <c r="C550" s="4" t="s">
-        <v>4379</v>
       </c>
       <c r="D550" s="4" t="s">
         <v>152</v>
@@ -50002,22 +49995,22 @@
         <v>152</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>4380</v>
+        <v>4378</v>
       </c>
       <c r="G550" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H550" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I550" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J550" s="4" t="s">
-        <v>4381</v>
+        <v>4379</v>
       </c>
       <c r="K550" s="4" t="s">
-        <v>4382</v>
+        <v>4380</v>
       </c>
       <c r="L550" s="5">
         <v>44.94</v>
@@ -50026,10 +50019,10 @@
         <v>13.59</v>
       </c>
       <c r="N550" s="4" t="s">
-        <v>4383</v>
+        <v>4381</v>
       </c>
       <c r="O550" s="4" t="s">
-        <v>4384</v>
+        <v>4382</v>
       </c>
       <c r="P550" s="4"/>
       <c r="Q550" s="4"/>
@@ -50039,7 +50032,7 @@
       </c>
       <c r="T550" s="4"/>
       <c r="U550" s="4" t="s">
-        <v>4385</v>
+        <v>4383</v>
       </c>
       <c r="V550" s="4" t="s">
         <v>41</v>
@@ -50054,13 +50047,13 @@
     </row>
     <row r="551" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
+        <v>4384</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>4385</v>
+      </c>
+      <c r="C551" s="2" t="s">
         <v>4386</v>
-      </c>
-      <c r="B551" s="2" t="s">
-        <v>4387</v>
-      </c>
-      <c r="C551" s="2" t="s">
-        <v>4388</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>2094</v>
@@ -50069,22 +50062,22 @@
         <v>2094</v>
       </c>
       <c r="F551" s="2" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
       <c r="G551" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I551" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J551" s="2" t="s">
-        <v>4389</v>
+        <v>4387</v>
       </c>
       <c r="K551" s="2" t="s">
-        <v>4390</v>
+        <v>4388</v>
       </c>
       <c r="L551" s="3">
         <v>37.82</v>
@@ -50093,10 +50086,10 @@
         <v>12.05</v>
       </c>
       <c r="N551" s="2" t="s">
-        <v>4391</v>
+        <v>4389</v>
       </c>
       <c r="O551" s="2" t="s">
-        <v>4392</v>
+        <v>4390</v>
       </c>
       <c r="P551" s="2"/>
       <c r="Q551" s="2"/>
@@ -50121,13 +50114,13 @@
     </row>
     <row r="552" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="C552" s="4" t="s">
         <v>4393</v>
-      </c>
-      <c r="B552" s="4" t="s">
-        <v>4394</v>
-      </c>
-      <c r="C552" s="4" t="s">
-        <v>4395</v>
       </c>
       <c r="D552" s="4" t="s">
         <v>2823</v>
@@ -50136,22 +50129,22 @@
         <v>2823</v>
       </c>
       <c r="F552" s="4" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
       <c r="G552" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H552" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I552" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J552" s="4" t="s">
-        <v>4396</v>
+        <v>4394</v>
       </c>
       <c r="K552" s="4" t="s">
-        <v>4397</v>
+        <v>4395</v>
       </c>
       <c r="L552" s="5">
         <v>34.69</v>
@@ -50160,7 +50153,7 @@
         <v>11.81</v>
       </c>
       <c r="N552" s="4" t="s">
-        <v>4398</v>
+        <v>4396</v>
       </c>
       <c r="O552" s="4"/>
       <c r="P552" s="4"/>
@@ -50186,13 +50179,13 @@
     </row>
     <row r="553" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
+        <v>4397</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>4398</v>
+      </c>
+      <c r="C553" s="2" t="s">
         <v>4399</v>
-      </c>
-      <c r="B553" s="2" t="s">
-        <v>4400</v>
-      </c>
-      <c r="C553" s="2" t="s">
-        <v>4401</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>2060</v>
@@ -50201,22 +50194,22 @@
         <v>2060</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G553" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H553" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I553" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J553" s="2" t="s">
-        <v>4402</v>
+        <v>4400</v>
       </c>
       <c r="K553" s="2" t="s">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="L553" s="3">
         <v>32.21</v>
@@ -50225,7 +50218,7 @@
         <v>7.85</v>
       </c>
       <c r="N553" s="2" t="s">
-        <v>4404</v>
+        <v>4402</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
@@ -50236,7 +50229,7 @@
       </c>
       <c r="T553" s="2"/>
       <c r="U553" s="2" t="s">
-        <v>4405</v>
+        <v>4403</v>
       </c>
       <c r="V553" s="2" t="s">
         <v>41</v>
@@ -50251,34 +50244,34 @@
     </row>
     <row r="554" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
+        <v>4404</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>4405</v>
+      </c>
+      <c r="C554" s="4" t="s">
         <v>4406</v>
       </c>
-      <c r="B554" s="4" t="s">
+      <c r="D554" s="4" t="s">
         <v>4407</v>
       </c>
-      <c r="C554" s="4" t="s">
-        <v>4408</v>
-      </c>
-      <c r="D554" s="4" t="s">
-        <v>4409</v>
-      </c>
       <c r="E554" s="4" t="s">
-        <v>4409</v>
+        <v>4407</v>
       </c>
       <c r="F554" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G554" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H554" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I554" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J554" s="4" t="s">
-        <v>4410</v>
+        <v>4408</v>
       </c>
       <c r="K554" s="4" t="s">
         <v>373</v>
@@ -50290,7 +50283,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="N554" s="4" t="s">
-        <v>4411</v>
+        <v>4409</v>
       </c>
       <c r="O554" s="4"/>
       <c r="P554" s="4"/>
@@ -50314,34 +50307,34 @@
     </row>
     <row r="555" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
+        <v>4410</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>4411</v>
+      </c>
+      <c r="C555" s="2" t="s">
         <v>4412</v>
       </c>
-      <c r="B555" s="2" t="s">
+      <c r="D555" s="2" t="s">
         <v>4413</v>
       </c>
-      <c r="C555" s="2" t="s">
-        <v>4414</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>4415</v>
-      </c>
       <c r="E555" s="2" t="s">
-        <v>4415</v>
+        <v>4413</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G555" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H555" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I555" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J555" s="2" t="s">
-        <v>4416</v>
+        <v>4414</v>
       </c>
       <c r="K555" s="2" t="s">
         <v>373</v>
@@ -50353,7 +50346,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="N555" s="2" t="s">
-        <v>4417</v>
+        <v>4415</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -50362,7 +50355,7 @@
       <c r="S555" s="2"/>
       <c r="T555" s="2"/>
       <c r="U555" s="2" t="s">
-        <v>4418</v>
+        <v>4416</v>
       </c>
       <c r="V555" s="2" t="s">
         <v>41</v>
@@ -50377,13 +50370,13 @@
     </row>
     <row r="556" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C556" s="4" t="s">
         <v>4419</v>
-      </c>
-      <c r="B556" s="4" t="s">
-        <v>4420</v>
-      </c>
-      <c r="C556" s="4" t="s">
-        <v>4421</v>
       </c>
       <c r="D556" s="4" t="s">
         <v>904</v>
@@ -50392,19 +50385,19 @@
         <v>904</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G556" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H556" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I556" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J556" s="4" t="s">
-        <v>4422</v>
+        <v>4420</v>
       </c>
       <c r="K556" s="4" t="s">
         <v>373</v>
@@ -50416,7 +50409,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="N556" s="4" t="s">
-        <v>4423</v>
+        <v>4421</v>
       </c>
       <c r="O556" s="4"/>
       <c r="P556" s="4"/>
@@ -50425,7 +50418,7 @@
       <c r="S556" s="4"/>
       <c r="T556" s="4"/>
       <c r="U556" s="4" t="s">
-        <v>4418</v>
+        <v>4416</v>
       </c>
       <c r="V556" s="4" t="s">
         <v>41</v>
@@ -50440,13 +50433,13 @@
     </row>
     <row r="557" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
+        <v>4422</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>4423</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>4424</v>
-      </c>
-      <c r="B557" s="2" t="s">
-        <v>4425</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>4426</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>2728</v>
@@ -50455,19 +50448,19 @@
         <v>2728</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G557" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I557" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J557" s="2" t="s">
-        <v>4427</v>
+        <v>4425</v>
       </c>
       <c r="K557" s="2" t="s">
         <v>1110</v>
@@ -50479,7 +50472,7 @@
         <v>1.68</v>
       </c>
       <c r="N557" s="2" t="s">
-        <v>4428</v>
+        <v>4426</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -50488,7 +50481,7 @@
       <c r="S557" s="2"/>
       <c r="T557" s="2"/>
       <c r="U557" s="2" t="s">
-        <v>4429</v>
+        <v>4427</v>
       </c>
       <c r="V557" s="2" t="s">
         <v>41</v>
@@ -50503,30 +50496,30 @@
     </row>
     <row r="558" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C558" s="4" t="s">
         <v>4430</v>
-      </c>
-      <c r="B558" s="4" t="s">
-        <v>4431</v>
-      </c>
-      <c r="C558" s="4" t="s">
-        <v>4432</v>
       </c>
       <c r="D558" s="4"/>
       <c r="E558" s="4"/>
       <c r="F558" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G558" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H558" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I558" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J558" s="4" t="s">
-        <v>4433</v>
+        <v>4431</v>
       </c>
       <c r="K558" s="4" t="s">
         <v>424</v>
@@ -50538,7 +50531,7 @@
         <v>1.43</v>
       </c>
       <c r="N558" s="4" t="s">
-        <v>4434</v>
+        <v>4432</v>
       </c>
       <c r="O558" s="4"/>
       <c r="P558" s="4"/>
@@ -50547,7 +50540,7 @@
       <c r="S558" s="4"/>
       <c r="T558" s="4"/>
       <c r="U558" s="4" t="s">
-        <v>4435</v>
+        <v>4433</v>
       </c>
       <c r="V558" s="4" t="s">
         <v>41</v>
@@ -50562,33 +50555,33 @@
     </row>
     <row r="559" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>4435</v>
+      </c>
+      <c r="C559" s="2" t="s">
         <v>4436</v>
-      </c>
-      <c r="B559" s="2" t="s">
-        <v>4437</v>
-      </c>
-      <c r="C559" s="2" t="s">
-        <v>4438</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" s="2"/>
       <c r="F559" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G559" s="2" t="s">
         <v>330</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I559" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J559" s="2" t="s">
         <v>2875</v>
       </c>
       <c r="K559" s="2" t="s">
-        <v>4439</v>
+        <v>4437</v>
       </c>
       <c r="L559" s="3">
         <v>24.58</v>
@@ -50597,7 +50590,7 @@
         <v>1.38</v>
       </c>
       <c r="N559" s="2" t="s">
-        <v>4440</v>
+        <v>4438</v>
       </c>
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
@@ -50621,30 +50614,30 @@
     </row>
     <row r="560" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>4440</v>
+      </c>
+      <c r="C560" s="4" t="s">
         <v>4441</v>
-      </c>
-      <c r="B560" s="4" t="s">
-        <v>4442</v>
-      </c>
-      <c r="C560" s="4" t="s">
-        <v>4443</v>
       </c>
       <c r="D560" s="4"/>
       <c r="E560" s="4"/>
       <c r="F560" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G560" s="4" t="s">
         <v>330</v>
       </c>
       <c r="H560" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I560" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J560" s="4" t="s">
-        <v>4444</v>
+        <v>4442</v>
       </c>
       <c r="K560" s="4" t="s">
         <v>3126</v>
@@ -50656,7 +50649,7 @@
         <v>1.34</v>
       </c>
       <c r="N560" s="4" t="s">
-        <v>4445</v>
+        <v>4443</v>
       </c>
       <c r="O560" s="4"/>
       <c r="P560" s="4"/>
@@ -50680,13 +50673,13 @@
     </row>
     <row r="561" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
+        <v>4444</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>4445</v>
+      </c>
+      <c r="C561" s="2" t="s">
         <v>4446</v>
-      </c>
-      <c r="B561" s="2" t="s">
-        <v>4447</v>
-      </c>
-      <c r="C561" s="2" t="s">
-        <v>4448</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>1677</v>
@@ -50695,22 +50688,22 @@
         <v>1677</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>4449</v>
+        <v>4447</v>
       </c>
       <c r="G561" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H561" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I561" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J561" s="2" t="s">
-        <v>4450</v>
+        <v>4448</v>
       </c>
       <c r="K561" s="2" t="s">
-        <v>4451</v>
+        <v>4449</v>
       </c>
       <c r="L561" s="3">
         <v>29.71</v>
@@ -50719,10 +50712,10 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="N561" s="2" t="s">
-        <v>4452</v>
+        <v>4450</v>
       </c>
       <c r="O561" s="2" t="s">
-        <v>4453</v>
+        <v>4451</v>
       </c>
       <c r="P561" s="2"/>
       <c r="Q561" s="2"/>
@@ -50730,7 +50723,7 @@
       <c r="S561" s="2"/>
       <c r="T561" s="2"/>
       <c r="U561" s="2" t="s">
-        <v>4235</v>
+        <v>4233</v>
       </c>
       <c r="V561" s="2" t="s">
         <v>41</v>
@@ -50745,13 +50738,13 @@
     </row>
     <row r="562" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
+        <v>4452</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>4453</v>
+      </c>
+      <c r="C562" s="4" t="s">
         <v>4454</v>
-      </c>
-      <c r="B562" s="4" t="s">
-        <v>4455</v>
-      </c>
-      <c r="C562" s="4" t="s">
-        <v>4456</v>
       </c>
       <c r="D562" s="4" t="s">
         <v>2324</v>
@@ -50760,19 +50753,19 @@
         <v>2324</v>
       </c>
       <c r="F562" s="4" t="s">
-        <v>4449</v>
+        <v>4447</v>
       </c>
       <c r="G562" s="4" t="s">
         <v>177</v>
       </c>
       <c r="H562" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I562" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J562" s="4" t="s">
-        <v>4457</v>
+        <v>4455</v>
       </c>
       <c r="K562" s="4" t="s">
         <v>2420</v>
@@ -50784,10 +50777,10 @@
         <v>0.68</v>
       </c>
       <c r="N562" s="4" t="s">
-        <v>4458</v>
+        <v>4456</v>
       </c>
       <c r="O562" s="4" t="s">
-        <v>4459</v>
+        <v>4457</v>
       </c>
       <c r="P562" s="4"/>
       <c r="Q562" s="4"/>
@@ -50795,7 +50788,7 @@
       <c r="S562" s="4"/>
       <c r="T562" s="4"/>
       <c r="U562" s="4" t="s">
-        <v>4460</v>
+        <v>4458</v>
       </c>
       <c r="V562" s="4" t="s">
         <v>41</v>
@@ -50810,34 +50803,34 @@
     </row>
     <row r="563" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
+        <v>4459</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>4460</v>
+      </c>
+      <c r="C563" s="2" t="s">
         <v>4461</v>
       </c>
-      <c r="B563" s="2" t="s">
+      <c r="D563" s="2" t="s">
         <v>4462</v>
       </c>
-      <c r="C563" s="2" t="s">
-        <v>4463</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>4464</v>
-      </c>
       <c r="E563" s="2" t="s">
-        <v>4464</v>
+        <v>4462</v>
       </c>
       <c r="F563" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G563" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H563" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I563" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J563" s="2" t="s">
-        <v>4465</v>
+        <v>4463</v>
       </c>
       <c r="K563" s="2" t="s">
         <v>2420</v>
@@ -50849,7 +50842,7 @@
         <v>0.68</v>
       </c>
       <c r="N563" s="2" t="s">
-        <v>4466</v>
+        <v>4464</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" s="2"/>
@@ -50858,7 +50851,7 @@
       <c r="S563" s="2"/>
       <c r="T563" s="2"/>
       <c r="U563" s="2" t="s">
-        <v>4435</v>
+        <v>4433</v>
       </c>
       <c r="V563" s="2" t="s">
         <v>41</v>
@@ -50873,34 +50866,34 @@
     </row>
     <row r="564" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>4466</v>
+      </c>
+      <c r="C564" s="4" t="s">
         <v>4467</v>
       </c>
-      <c r="B564" s="4" t="s">
+      <c r="D564" s="4" t="s">
         <v>4468</v>
       </c>
-      <c r="C564" s="4" t="s">
-        <v>4469</v>
-      </c>
-      <c r="D564" s="4" t="s">
-        <v>4470</v>
-      </c>
       <c r="E564" s="4" t="s">
-        <v>4470</v>
+        <v>4468</v>
       </c>
       <c r="F564" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G564" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H564" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I564" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J564" s="4" t="s">
-        <v>4471</v>
+        <v>4469</v>
       </c>
       <c r="K564" s="4" t="s">
         <v>3537</v>
@@ -50912,7 +50905,7 @@
         <v>0.51</v>
       </c>
       <c r="N564" s="4" t="s">
-        <v>4472</v>
+        <v>4470</v>
       </c>
       <c r="O564" s="4"/>
       <c r="P564" s="4"/>
@@ -50936,13 +50929,13 @@
     </row>
     <row r="565" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>4472</v>
+      </c>
+      <c r="C565" s="2" t="s">
         <v>4473</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>4474</v>
-      </c>
-      <c r="C565" s="2" t="s">
-        <v>4475</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>3815</v>
@@ -50951,19 +50944,19 @@
         <v>3815</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G565" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I565" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J565" s="2" t="s">
-        <v>4476</v>
+        <v>4474</v>
       </c>
       <c r="K565" s="2" t="s">
         <v>409</v>
@@ -50975,7 +50968,7 @@
         <v>0.47</v>
       </c>
       <c r="N565" s="2" t="s">
-        <v>4477</v>
+        <v>4475</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -50984,7 +50977,7 @@
       <c r="S565" s="2"/>
       <c r="T565" s="2"/>
       <c r="U565" s="2" t="s">
-        <v>4435</v>
+        <v>4433</v>
       </c>
       <c r="V565" s="2" t="s">
         <v>413</v>
@@ -50999,13 +50992,13 @@
     </row>
     <row r="566" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
+        <v>4476</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>4477</v>
+      </c>
+      <c r="C566" s="4" t="s">
         <v>4478</v>
-      </c>
-      <c r="B566" s="4" t="s">
-        <v>4479</v>
-      </c>
-      <c r="C566" s="4" t="s">
-        <v>4480</v>
       </c>
       <c r="D566" s="4" t="s">
         <v>962</v>
@@ -51014,19 +51007,19 @@
         <v>962</v>
       </c>
       <c r="F566" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G566" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H566" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I566" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J566" s="4" t="s">
-        <v>4481</v>
+        <v>4479</v>
       </c>
       <c r="K566" s="4" t="s">
         <v>1738</v>
@@ -51038,7 +51031,7 @@
         <v>0.06</v>
       </c>
       <c r="N566" s="4" t="s">
-        <v>4482</v>
+        <v>4480</v>
       </c>
       <c r="O566" s="4"/>
       <c r="P566" s="4"/>
@@ -51062,34 +51055,34 @@
     </row>
     <row r="567" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>4482</v>
+      </c>
+      <c r="C567" s="2" t="s">
         <v>4483</v>
       </c>
-      <c r="B567" s="2" t="s">
+      <c r="D567" s="2" t="s">
         <v>4484</v>
       </c>
-      <c r="C567" s="2" t="s">
-        <v>4485</v>
-      </c>
-      <c r="D567" s="2" t="s">
-        <v>4486</v>
-      </c>
       <c r="E567" s="2" t="s">
-        <v>4486</v>
+        <v>4484</v>
       </c>
       <c r="F567" s="2" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
       <c r="G567" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="H567" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I567" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J567" s="2" t="s">
-        <v>4487</v>
+        <v>4485</v>
       </c>
       <c r="K567" s="2" t="s">
         <v>242</v>
@@ -51101,7 +51094,7 @@
         <v>0.01</v>
       </c>
       <c r="N567" s="2" t="s">
-        <v>4488</v>
+        <v>4486</v>
       </c>
       <c r="O567" s="2"/>
       <c r="P567" s="2"/>
@@ -51125,13 +51118,13 @@
     </row>
     <row r="568" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>4488</v>
+      </c>
+      <c r="C568" s="4" t="s">
         <v>4489</v>
-      </c>
-      <c r="B568" s="4" t="s">
-        <v>4490</v>
-      </c>
-      <c r="C568" s="4" t="s">
-        <v>4491</v>
       </c>
       <c r="D568" s="4" t="s">
         <v>1135</v>
@@ -51140,19 +51133,19 @@
         <v>1135</v>
       </c>
       <c r="F568" s="4" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G568" s="4" t="s">
         <v>2735</v>
       </c>
       <c r="H568" s="4" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I568" s="4" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J568" s="4" t="s">
-        <v>4492</v>
+        <v>4490</v>
       </c>
       <c r="K568" s="4" t="s">
         <v>242</v>
@@ -51164,7 +51157,7 @@
         <v>0.01</v>
       </c>
       <c r="N568" s="4" t="s">
-        <v>4493</v>
+        <v>4491</v>
       </c>
       <c r="O568" s="4"/>
       <c r="P568" s="4"/>
@@ -51173,7 +51166,7 @@
       <c r="S568" s="4"/>
       <c r="T568" s="4"/>
       <c r="U568" s="4" t="s">
-        <v>4494</v>
+        <v>4492</v>
       </c>
       <c r="V568" s="4" t="s">
         <v>55</v>
@@ -51188,13 +51181,13 @@
     </row>
     <row r="569" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C569" s="2" t="s">
         <v>4495</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>4496</v>
-      </c>
-      <c r="C569" s="2" t="s">
-        <v>4497</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>1617</v>
@@ -51203,19 +51196,19 @@
         <v>1617</v>
       </c>
       <c r="F569" s="2" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="G569" s="2" t="s">
         <v>2735</v>
       </c>
       <c r="H569" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="I569" s="2" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="J569" s="2" t="s">
-        <v>4498</v>
+        <v>4496</v>
       </c>
       <c r="K569" s="2" t="s">
         <v>242</v>
@@ -51227,7 +51220,7 @@
         <v>0.01</v>
       </c>
       <c r="N569" s="2" t="s">
-        <v>4499</v>
+        <v>4497</v>
       </c>
       <c r="O569" s="2"/>
       <c r="P569" s="2"/>
@@ -51236,7 +51229,7 @@
       <c r="S569" s="2"/>
       <c r="T569" s="2"/>
       <c r="U569" s="2" t="s">
-        <v>4435</v>
+        <v>4433</v>
       </c>
       <c r="V569" s="2" t="s">
         <v>55</v>
@@ -51251,33 +51244,33 @@
     </row>
     <row r="570" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
+        <v>4498</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>4499</v>
+      </c>
+      <c r="C570" s="4" t="s">
         <v>4500</v>
-      </c>
-      <c r="B570" s="4" t="s">
-        <v>4501</v>
-      </c>
-      <c r="C570" s="4" t="s">
-        <v>4502</v>
       </c>
       <c r="D570" s="4"/>
       <c r="E570" s="4"/>
       <c r="F570" s="4" t="s">
-        <v>4503</v>
+        <v>4501</v>
       </c>
       <c r="G570" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="H570" s="4" t="s">
+        <v>4502</v>
+      </c>
+      <c r="I570" s="4" t="s">
+        <v>4503</v>
+      </c>
+      <c r="J570" s="4" t="s">
         <v>4504</v>
       </c>
-      <c r="I570" s="4" t="s">
+      <c r="K570" s="4" t="s">
         <v>4505</v>
-      </c>
-      <c r="J570" s="4" t="s">
-        <v>4506</v>
-      </c>
-      <c r="K570" s="4" t="s">
-        <v>4507</v>
       </c>
       <c r="L570" s="5">
         <v>48.62</v>
@@ -51286,10 +51279,10 @@
         <v>14.1</v>
       </c>
       <c r="N570" s="4" t="s">
-        <v>4508</v>
+        <v>4506</v>
       </c>
       <c r="O570" s="4" t="s">
-        <v>4509</v>
+        <v>4507</v>
       </c>
       <c r="P570" s="4"/>
       <c r="Q570" s="4"/>
@@ -51301,7 +51294,7 @@
         <v>694</v>
       </c>
       <c r="U570" s="4" t="s">
-        <v>4510</v>
+        <v>4508</v>
       </c>
       <c r="V570" s="4" t="s">
         <v>41</v>
@@ -51316,37 +51309,37 @@
     </row>
     <row r="571" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
-        <v>4505</v>
+        <v>4503</v>
       </c>
       <c r="B571" s="2" t="s">
+        <v>4509</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>4510</v>
+      </c>
+      <c r="D571" s="2" t="s">
         <v>4511</v>
       </c>
-      <c r="C571" s="2" t="s">
+      <c r="E571" s="2" t="s">
+        <v>4511</v>
+      </c>
+      <c r="F571" s="2" t="s">
         <v>4512</v>
-      </c>
-      <c r="D571" s="2" t="s">
-        <v>4513</v>
-      </c>
-      <c r="E571" s="2" t="s">
-        <v>4513</v>
-      </c>
-      <c r="F571" s="2" t="s">
-        <v>4514</v>
       </c>
       <c r="G571" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H571" s="2" t="s">
-        <v>4504</v>
+        <v>4502</v>
       </c>
       <c r="I571" s="2" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="J571" s="2" t="s">
-        <v>4515</v>
+        <v>4513</v>
       </c>
       <c r="K571" s="2" t="s">
-        <v>4516</v>
+        <v>4514</v>
       </c>
       <c r="L571" s="3">
         <v>38.26</v>
@@ -51355,10 +51348,10 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="N571" s="2" t="s">
-        <v>4517</v>
+        <v>4515</v>
       </c>
       <c r="O571" s="2" t="s">
-        <v>4518</v>
+        <v>4516</v>
       </c>
       <c r="P571" s="2"/>
       <c r="Q571" s="2"/>
@@ -51370,7 +51363,7 @@
         <v>478</v>
       </c>
       <c r="U571" s="2" t="s">
-        <v>4519</v>
+        <v>4517</v>
       </c>
       <c r="V571" s="2" t="s">
         <v>41</v>
@@ -51385,37 +51378,37 @@
     </row>
     <row r="572" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="B572" s="4" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>4519</v>
+      </c>
+      <c r="D572" s="4" t="s">
         <v>4520</v>
       </c>
-      <c r="C572" s="4" t="s">
+      <c r="E572" s="4" t="s">
+        <v>4520</v>
+      </c>
+      <c r="F572" s="4" t="s">
         <v>4521</v>
-      </c>
-      <c r="D572" s="4" t="s">
-        <v>4522</v>
-      </c>
-      <c r="E572" s="4" t="s">
-        <v>4522</v>
-      </c>
-      <c r="F572" s="4" t="s">
-        <v>4523</v>
       </c>
       <c r="G572" s="4" t="s">
         <v>154</v>
       </c>
       <c r="H572" s="4" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="I572" s="4" t="s">
         <v>272</v>
       </c>
       <c r="J572" s="4" t="s">
-        <v>4525</v>
+        <v>4523</v>
       </c>
       <c r="K572" s="4" t="s">
-        <v>4526</v>
+        <v>4524</v>
       </c>
       <c r="L572" s="5">
         <v>41.32</v>
@@ -51424,10 +51417,10 @@
         <v>10.85</v>
       </c>
       <c r="N572" s="4" t="s">
-        <v>4527</v>
+        <v>4525</v>
       </c>
       <c r="O572" s="4" t="s">
-        <v>4528</v>
+        <v>4526</v>
       </c>
       <c r="P572" s="4"/>
       <c r="Q572" s="4"/>
@@ -51454,34 +51447,34 @@
     </row>
     <row r="573" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
+        <v>4527</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>4528</v>
+      </c>
+      <c r="C573" s="2" t="s">
         <v>4529</v>
       </c>
-      <c r="B573" s="2" t="s">
+      <c r="D573" s="2" t="s">
         <v>4530</v>
       </c>
-      <c r="C573" s="2" t="s">
+      <c r="E573" s="2" t="s">
+        <v>4530</v>
+      </c>
+      <c r="F573" s="2" t="s">
         <v>4531</v>
-      </c>
-      <c r="D573" s="2" t="s">
-        <v>4532</v>
-      </c>
-      <c r="E573" s="2" t="s">
-        <v>4532</v>
-      </c>
-      <c r="F573" s="2" t="s">
-        <v>4533</v>
       </c>
       <c r="G573" s="2" t="s">
         <v>86</v>
       </c>
       <c r="H573" s="2" t="s">
-        <v>4534</v>
+        <v>4532</v>
       </c>
       <c r="I573" s="2" t="s">
         <v>272</v>
       </c>
       <c r="J573" s="2" t="s">
-        <v>4535</v>
+        <v>4533</v>
       </c>
       <c r="K573" s="2" t="s">
         <v>955</v>
@@ -51493,10 +51486,10 @@
         <v>0.93</v>
       </c>
       <c r="N573" s="2" t="s">
-        <v>4536</v>
+        <v>4534</v>
       </c>
       <c r="O573" s="2" t="s">
-        <v>4537</v>
+        <v>4535</v>
       </c>
       <c r="P573" s="2"/>
       <c r="Q573" s="2"/>
@@ -51504,7 +51497,7 @@
       <c r="S573" s="2"/>
       <c r="T573" s="2"/>
       <c r="U573" s="2" t="s">
-        <v>4538</v>
+        <v>4536</v>
       </c>
       <c r="V573" s="2" t="s">
         <v>40</v>
@@ -51522,32 +51515,32 @@
         <v>272</v>
       </c>
       <c r="B574" s="4" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>4538</v>
+      </c>
+      <c r="D574" s="4" t="s">
         <v>4539</v>
       </c>
-      <c r="C574" s="4" t="s">
+      <c r="E574" s="4" t="s">
+        <v>4539</v>
+      </c>
+      <c r="F574" s="4" t="s">
         <v>4540</v>
       </c>
-      <c r="D574" s="4" t="s">
+      <c r="G574" s="4" t="s">
         <v>4541</v>
       </c>
-      <c r="E574" s="4" t="s">
-        <v>4541</v>
-      </c>
-      <c r="F574" s="4" t="s">
+      <c r="H574" s="4" t="s">
         <v>4542</v>
-      </c>
-      <c r="G574" s="4" t="s">
-        <v>4543</v>
-      </c>
-      <c r="H574" s="4" t="s">
-        <v>4544</v>
       </c>
       <c r="I574" s="4"/>
       <c r="J574" s="4" t="s">
-        <v>4545</v>
+        <v>4543</v>
       </c>
       <c r="K574" s="4" t="s">
-        <v>4546</v>
+        <v>4544</v>
       </c>
       <c r="L574" s="5">
         <v>46.21</v>
@@ -51556,10 +51549,10 @@
         <v>1.25</v>
       </c>
       <c r="N574" s="4" t="s">
-        <v>4547</v>
+        <v>4545</v>
       </c>
       <c r="O574" s="4" t="s">
-        <v>4548</v>
+        <v>4546</v>
       </c>
       <c r="P574" s="4"/>
       <c r="Q574" s="4"/>
@@ -51567,7 +51560,7 @@
       <c r="S574" s="4"/>
       <c r="T574" s="4"/>
       <c r="U574" s="4" t="s">
-        <v>4549</v>
+        <v>4547</v>
       </c>
       <c r="V574" s="4" t="s">
         <v>55</v>
@@ -51606,37 +51599,37 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4548</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4549</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4550</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4551</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4553</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4554</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4555</v>
+        <v>4553</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4555</v>
+        <v>4553</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>4556</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51644,19 +51637,19 @@
         <v>953</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>4557</v>
+        <v>4555</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4557</v>
+        <v>4555</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>301</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51664,99 +51657,99 @@
         <v>271</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4559</v>
+        <v>4557</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4559</v>
+        <v>4557</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>4561</v>
+        <v>4559</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>4561</v>
+        <v>4559</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>301</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4563</v>
+        <v>4561</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>4563</v>
+        <v>4561</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>301</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>4565</v>
+        <v>4563</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>4566</v>
+        <v>4564</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>4566</v>
+        <v>4564</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>301</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4567</v>
+        <v>4565</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4567</v>
+        <v>4565</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51764,10 +51757,10 @@
         <v>740</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>4569</v>
+        <v>4567</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>4569</v>
+        <v>4567</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>953</v>
@@ -51776,7 +51769,7 @@
         <v>41</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51784,10 +51777,10 @@
         <v>649</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>4570</v>
+        <v>4568</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>4570</v>
+        <v>4568</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>953</v>
@@ -51796,7 +51789,7 @@
         <v>41</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51804,19 +51797,19 @@
         <v>964</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>4565</v>
+        <v>4563</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>4572</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51824,19 +51817,19 @@
         <v>1054</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4573</v>
+        <v>4571</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>4573</v>
+        <v>4571</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>4565</v>
+        <v>4563</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>4572</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51844,19 +51837,19 @@
         <v>1282</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>4574</v>
+        <v>4572</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>4574</v>
+        <v>4572</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51864,19 +51857,19 @@
         <v>2084</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4575</v>
+        <v>4573</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>4575</v>
+        <v>4573</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51884,19 +51877,19 @@
         <v>3006</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>4576</v>
+        <v>4574</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>4576</v>
+        <v>4574</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51904,39 +51897,39 @@
         <v>3457</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>4577</v>
+        <v>4575</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>4577</v>
+        <v>4575</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>4578</v>
+        <v>4576</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>4579</v>
+        <v>4577</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>4579</v>
+        <v>4577</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -51944,159 +51937,159 @@
         <v>3832</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>4580</v>
+        <v>4578</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>4580</v>
+        <v>4578</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>4581</v>
+        <v>4579</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>4581</v>
+        <v>4579</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>4582</v>
+        <v>4580</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>4563</v>
+        <v>4561</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>4563</v>
+        <v>4561</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>4534</v>
+        <v>4532</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>4583</v>
+        <v>4581</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>4583</v>
+        <v>4581</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>4544</v>
+        <v>4542</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>4584</v>
+        <v>4582</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>4584</v>
+        <v>4582</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>4332</v>
+        <v>4330</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>4585</v>
+        <v>4583</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>4585</v>
+        <v>4583</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>4586</v>
+        <v>4584</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>4586</v>
+        <v>4584</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>4504</v>
+        <v>4502</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>4587</v>
+        <v>4585</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>4587</v>
+        <v>4585</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>4524</v>
+        <v>4522</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52104,10 +52097,10 @@
         <v>662</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>4588</v>
+        <v>4586</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>4588</v>
+        <v>4586</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>953</v>
@@ -52116,7 +52109,7 @@
         <v>40</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52124,10 +52117,10 @@
         <v>729</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>4589</v>
+        <v>4587</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>4589</v>
+        <v>4587</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>953</v>
@@ -52136,7 +52129,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52144,10 +52137,10 @@
         <v>802</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>4590</v>
+        <v>4588</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>4590</v>
+        <v>4588</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>953</v>
@@ -52156,7 +52149,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52164,10 +52157,10 @@
         <v>880</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>4591</v>
+        <v>4589</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>4591</v>
+        <v>4589</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>953</v>
@@ -52176,7 +52169,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52184,10 +52177,10 @@
         <v>284</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>4592</v>
+        <v>4590</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>4592</v>
+        <v>4590</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>649</v>
@@ -52196,7 +52189,7 @@
         <v>40</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52204,10 +52197,10 @@
         <v>331</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>4593</v>
+        <v>4591</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>4593</v>
+        <v>4591</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>649</v>
@@ -52216,7 +52209,7 @@
         <v>40</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52224,10 +52217,10 @@
         <v>419</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>4594</v>
+        <v>4592</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>4594</v>
+        <v>4592</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>649</v>
@@ -52236,7 +52229,7 @@
         <v>40</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52244,10 +52237,10 @@
         <v>473</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>4595</v>
+        <v>4593</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>4595</v>
+        <v>4593</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>649</v>
@@ -52256,7 +52249,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52264,10 +52257,10 @@
         <v>543</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>4596</v>
+        <v>4594</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>4596</v>
+        <v>4594</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>649</v>
@@ -52276,7 +52269,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52284,10 +52277,10 @@
         <v>612</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>4597</v>
+        <v>4595</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>4597</v>
+        <v>4595</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>649</v>
@@ -52296,7 +52289,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52304,10 +52297,10 @@
         <v>583</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>4598</v>
+        <v>4596</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>4598</v>
+        <v>4596</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>649</v>
@@ -52316,7 +52309,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52324,10 +52317,10 @@
         <v>61</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>4599</v>
+        <v>4597</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>4599</v>
+        <v>4597</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>271</v>
@@ -52336,7 +52329,7 @@
         <v>40</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52344,10 +52337,10 @@
         <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>4600</v>
+        <v>4598</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>4600</v>
+        <v>4598</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>271</v>
@@ -52356,7 +52349,7 @@
         <v>40</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52364,10 +52357,10 @@
         <v>155</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>4601</v>
+        <v>4599</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>4601</v>
+        <v>4599</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>271</v>
@@ -52376,7 +52369,7 @@
         <v>40</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52384,10 +52377,10 @@
         <v>260</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>4602</v>
+        <v>4600</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>4602</v>
+        <v>4600</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>271</v>
@@ -52396,18 +52389,18 @@
         <v>40</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>4603</v>
+        <v>4601</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>964</v>
@@ -52416,18 +52409,18 @@
         <v>40</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>4572</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>4604</v>
+        <v>4602</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>4573</v>
+        <v>4571</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>4573</v>
+        <v>4571</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>1054</v>
@@ -52436,7 +52429,7 @@
         <v>40</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>4572</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52444,19 +52437,19 @@
         <v>1215</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>4605</v>
+        <v>4603</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>4605</v>
+        <v>4603</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>4565</v>
+        <v>4563</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>4572</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52464,19 +52457,19 @@
         <v>3842</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>4606</v>
+        <v>4604</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>4606</v>
+        <v>4604</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52484,19 +52477,19 @@
         <v>3860</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>4607</v>
+        <v>4605</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>4607</v>
+        <v>4605</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52504,19 +52497,19 @@
         <v>3887</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>4608</v>
+        <v>4606</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>4608</v>
+        <v>4606</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52524,10 +52517,10 @@
         <v>1304</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>4609</v>
+        <v>4607</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>4609</v>
+        <v>4607</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>1282</v>
@@ -52536,18 +52529,18 @@
         <v>40</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>4610</v>
+        <v>4608</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4574</v>
+        <v>4572</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>4574</v>
+        <v>4572</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>1282</v>
@@ -52556,7 +52549,7 @@
         <v>40</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52564,10 +52557,10 @@
         <v>1451</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>4611</v>
+        <v>4609</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>4611</v>
+        <v>4609</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1282</v>
@@ -52576,7 +52569,7 @@
         <v>40</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52584,10 +52577,10 @@
         <v>1509</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>4612</v>
+        <v>4610</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>4612</v>
+        <v>4610</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>2084</v>
@@ -52596,7 +52589,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52604,10 +52597,10 @@
         <v>1693</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>4613</v>
+        <v>4611</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>4613</v>
+        <v>4611</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>2084</v>
@@ -52616,7 +52609,7 @@
         <v>40</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52624,10 +52617,10 @@
         <v>1774</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>4614</v>
+        <v>4612</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>4614</v>
+        <v>4612</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>2084</v>
@@ -52636,7 +52629,7 @@
         <v>40</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52644,10 +52637,10 @@
         <v>1747</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>4615</v>
+        <v>4613</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>4615</v>
+        <v>4613</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>2084</v>
@@ -52656,7 +52649,7 @@
         <v>40</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52664,10 +52657,10 @@
         <v>1997</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4616</v>
+        <v>4614</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>4616</v>
+        <v>4614</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>2084</v>
@@ -52676,7 +52669,7 @@
         <v>40</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52684,10 +52677,10 @@
         <v>2316</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>4617</v>
+        <v>4615</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>4617</v>
+        <v>4615</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>3006</v>
@@ -52696,7 +52689,7 @@
         <v>40</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52704,10 +52697,10 @@
         <v>2622</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>4618</v>
+        <v>4616</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>4618</v>
+        <v>4616</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>3006</v>
@@ -52716,7 +52709,7 @@
         <v>40</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52724,10 +52717,10 @@
         <v>2927</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>4619</v>
+        <v>4617</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>4619</v>
+        <v>4617</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>3006</v>
@@ -52736,7 +52729,7 @@
         <v>40</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52744,10 +52737,10 @@
         <v>3017</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>4620</v>
+        <v>4618</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>4620</v>
+        <v>4618</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>3457</v>
@@ -52756,7 +52749,7 @@
         <v>40</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52764,10 +52757,10 @@
         <v>3305</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>4621</v>
+        <v>4619</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>4621</v>
+        <v>4619</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>3457</v>
@@ -52776,7 +52769,7 @@
         <v>40</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52784,10 +52777,10 @@
         <v>3365</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>4622</v>
+        <v>4620</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>4622</v>
+        <v>4620</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>3457</v>
@@ -52796,7 +52789,7 @@
         <v>40</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52804,19 +52797,19 @@
         <v>3518</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>4623</v>
+        <v>4621</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>4623</v>
+        <v>4621</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>4578</v>
+        <v>4576</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52824,19 +52817,19 @@
         <v>3685</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>4624</v>
+        <v>4622</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>4624</v>
+        <v>4622</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>4578</v>
+        <v>4576</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52844,19 +52837,19 @@
         <v>3702</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>4625</v>
+        <v>4623</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>4625</v>
+        <v>4623</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>4578</v>
+        <v>4576</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52864,10 +52857,10 @@
         <v>3711</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>4626</v>
+        <v>4624</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>4626</v>
+        <v>4624</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>3832</v>
@@ -52876,7 +52869,7 @@
         <v>40</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -52884,10 +52877,10 @@
         <v>3782</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>4627</v>
+        <v>4625</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>4627</v>
+        <v>4625</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>3832</v>
@@ -52896,118 +52889,118 @@
         <v>40</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>4628</v>
+        <v>4626</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>4628</v>
+        <v>4626</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>4629</v>
+        <v>4627</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>4629</v>
+        <v>4627</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>4630</v>
+        <v>4628</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>4630</v>
+        <v>4628</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>4582</v>
+        <v>4580</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>4631</v>
+        <v>4629</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>4631</v>
+        <v>4629</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>4582</v>
+        <v>4580</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>4632</v>
+        <v>4630</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>4632</v>
+        <v>4630</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>4582</v>
+        <v>4580</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>4633</v>
+        <v>4631</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>4588</v>
+        <v>4586</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>4588</v>
+        <v>4586</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>662</v>
@@ -53016,7 +53009,7 @@
         <v>413</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53024,10 +53017,10 @@
         <v>691</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>4634</v>
+        <v>4632</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>4634</v>
+        <v>4632</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>729</v>
@@ -53036,7 +53029,7 @@
         <v>413</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53044,10 +53037,10 @@
         <v>712</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>4635</v>
+        <v>4633</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>4635</v>
+        <v>4633</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>729</v>
@@ -53056,7 +53049,7 @@
         <v>413</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53064,10 +53057,10 @@
         <v>869</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>4636</v>
+        <v>4634</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>4636</v>
+        <v>4634</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>880</v>
@@ -53076,18 +53069,18 @@
         <v>413</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>4637</v>
+        <v>4635</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>4596</v>
+        <v>4594</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>4596</v>
+        <v>4594</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>543</v>
@@ -53096,7 +53089,7 @@
         <v>413</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>4558</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53116,7 +53109,7 @@
         <v>413</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53124,10 +53117,10 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>4638</v>
+        <v>4636</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>4638</v>
+        <v>4636</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>87</v>
@@ -53136,7 +53129,7 @@
         <v>413</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53144,10 +53137,10 @@
         <v>132</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>4639</v>
+        <v>4637</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>4639</v>
+        <v>4637</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>155</v>
@@ -53156,7 +53149,7 @@
         <v>413</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53164,10 +53157,10 @@
         <v>99</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>4640</v>
+        <v>4638</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>4640</v>
+        <v>4638</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>155</v>
@@ -53176,7 +53169,7 @@
         <v>413</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53184,10 +53177,10 @@
         <v>121</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>4641</v>
+        <v>4639</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>4641</v>
+        <v>4639</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>155</v>
@@ -53196,7 +53189,7 @@
         <v>413</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53204,10 +53197,10 @@
         <v>143</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>4642</v>
+        <v>4640</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>4642</v>
+        <v>4640</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>155</v>
@@ -53216,7 +53209,7 @@
         <v>413</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53224,10 +53217,10 @@
         <v>178</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>4643</v>
+        <v>4641</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>4643</v>
+        <v>4641</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>260</v>
@@ -53236,7 +53229,7 @@
         <v>413</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53244,10 +53237,10 @@
         <v>190</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>4644</v>
+        <v>4642</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>4644</v>
+        <v>4642</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>260</v>
@@ -53256,7 +53249,7 @@
         <v>413</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53264,10 +53257,10 @@
         <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>4645</v>
+        <v>4643</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>4645</v>
+        <v>4643</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>260</v>
@@ -53276,7 +53269,7 @@
         <v>413</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53284,10 +53277,10 @@
         <v>230</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>4646</v>
+        <v>4644</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>4646</v>
+        <v>4644</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>260</v>
@@ -53296,7 +53289,7 @@
         <v>413</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53304,10 +53297,10 @@
         <v>1322</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>4647</v>
+        <v>4645</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>4647</v>
+        <v>4645</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>1282</v>
@@ -53316,7 +53309,7 @@
         <v>413</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53324,10 +53317,10 @@
         <v>1371</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>4648</v>
+        <v>4646</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>4648</v>
+        <v>4646</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>1282</v>
@@ -53336,7 +53329,7 @@
         <v>413</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53344,10 +53337,10 @@
         <v>1423</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>4649</v>
+        <v>4647</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>4649</v>
+        <v>4647</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>1282</v>
@@ -53356,7 +53349,7 @@
         <v>413</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53364,10 +53357,10 @@
         <v>3034</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>4650</v>
+        <v>4648</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>4650</v>
+        <v>4648</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>3305</v>
@@ -53376,7 +53369,7 @@
         <v>413</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53384,10 +53377,10 @@
         <v>3150</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>4651</v>
+        <v>4649</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>4651</v>
+        <v>4649</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>3305</v>
@@ -53396,7 +53389,7 @@
         <v>413</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53404,10 +53397,10 @@
         <v>3191</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>4652</v>
+        <v>4650</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>4652</v>
+        <v>4650</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>3305</v>
@@ -53416,7 +53409,7 @@
         <v>413</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53424,10 +53417,10 @@
         <v>3321</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>4653</v>
+        <v>4651</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>4653</v>
+        <v>4651</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>3365</v>
@@ -53436,18 +53429,18 @@
         <v>413</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>4654</v>
+        <v>4652</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>4622</v>
+        <v>4620</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>4622</v>
+        <v>4620</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>3365</v>
@@ -53456,7 +53449,7 @@
         <v>413</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53464,10 +53457,10 @@
         <v>3467</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>4655</v>
+        <v>4653</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>4655</v>
+        <v>4653</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>3518</v>
@@ -53476,7 +53469,7 @@
         <v>413</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53484,10 +53477,10 @@
         <v>3544</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>4656</v>
+        <v>4654</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>4656</v>
+        <v>4654</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>3685</v>
@@ -53496,7 +53489,7 @@
         <v>413</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53504,10 +53497,10 @@
         <v>3574</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>4657</v>
+        <v>4655</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>4657</v>
+        <v>4655</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>3685</v>
@@ -53516,7 +53509,7 @@
         <v>413</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53524,10 +53517,10 @@
         <v>3665</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>4658</v>
+        <v>4656</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>4658</v>
+        <v>4656</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>3685</v>
@@ -53536,18 +53529,18 @@
         <v>413</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>4659</v>
+        <v>4657</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>4617</v>
+        <v>4615</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>4617</v>
+        <v>4615</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>2316</v>
@@ -53556,18 +53549,18 @@
         <v>413</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>4660</v>
+        <v>4658</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>4661</v>
+        <v>4659</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>4661</v>
+        <v>4659</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>2316</v>
@@ -53576,18 +53569,18 @@
         <v>413</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>4662</v>
+        <v>4660</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>4663</v>
+        <v>4661</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>4663</v>
+        <v>4661</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>2316</v>
@@ -53596,18 +53589,18 @@
         <v>413</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>4664</v>
+        <v>4662</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>4665</v>
+        <v>4663</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>4665</v>
+        <v>4663</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>2316</v>
@@ -53616,18 +53609,18 @@
         <v>413</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>4666</v>
+        <v>4664</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>4667</v>
+        <v>4665</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>4667</v>
+        <v>4665</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>2316</v>
@@ -53636,18 +53629,18 @@
         <v>413</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>4668</v>
+        <v>4666</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>4669</v>
+        <v>4667</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>4669</v>
+        <v>4667</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>2622</v>
@@ -53656,18 +53649,18 @@
         <v>413</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>4670</v>
+        <v>4668</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>4671</v>
+        <v>4669</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>4671</v>
+        <v>4669</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>2622</v>
@@ -53676,18 +53669,18 @@
         <v>413</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>4672</v>
+        <v>4670</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>4673</v>
+        <v>4671</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>4673</v>
+        <v>4671</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>2622</v>
@@ -53696,18 +53689,18 @@
         <v>413</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>4674</v>
+        <v>4672</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>4675</v>
+        <v>4673</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>4675</v>
+        <v>4673</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>2927</v>
@@ -53716,18 +53709,18 @@
         <v>413</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>4676</v>
+        <v>4674</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>4677</v>
+        <v>4675</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>4677</v>
+        <v>4675</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>2927</v>
@@ -53736,18 +53729,18 @@
         <v>413</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>4678</v>
+        <v>4676</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>4679</v>
+        <v>4677</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>4679</v>
+        <v>4677</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>2927</v>
@@ -53756,18 +53749,18 @@
         <v>413</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>4680</v>
+        <v>4678</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>4619</v>
+        <v>4617</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>4619</v>
+        <v>4617</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>2927</v>
@@ -53776,18 +53769,18 @@
         <v>413</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>4681</v>
+        <v>4679</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>4682</v>
+        <v>4680</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>4682</v>
+        <v>4680</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>2927</v>
@@ -53796,18 +53789,18 @@
         <v>413</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>4683</v>
+        <v>4681</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>4684</v>
+        <v>4682</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>4684</v>
+        <v>4682</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>2927</v>
@@ -53816,18 +53809,18 @@
         <v>413</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>4685</v>
+        <v>4683</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>4686</v>
+        <v>4684</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>4686</v>
+        <v>4684</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>2927</v>
@@ -53836,87 +53829,87 @@
         <v>413</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>4687</v>
+        <v>4685</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>4687</v>
+        <v>4685</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>413</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>4688</v>
+        <v>4686</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>4688</v>
+        <v>4686</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>413</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>4689</v>
+        <v>4687</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>4689</v>
+        <v>4687</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>413</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>4690</v>
+        <v>4688</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>4690</v>
+        <v>4688</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>413</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -53924,19 +53917,19 @@
         <v>3510</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>4691</v>
+        <v>4689</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>4691</v>
+        <v>4689</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>3467</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>4692</v>
+        <v>4690</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>4562</v>
+        <v>4560</v>
       </c>
     </row>
   </sheetData>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B746D38-C6B6-4F37-96CE-BA652F6CC719}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$574</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$575</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="4692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10335" uniqueCount="4694">
   <si>
     <t>as_of_date=3 เมษายน 2569</t>
   </si>
@@ -14111,6 +14111,12 @@
   </si>
   <si>
     <t>RP90</t>
+  </si>
+  <si>
+    <t>168001 A</t>
+  </si>
+  <si>
+    <t>Acting Executive Director - Finance Accounting, Information Technology and Procurement</t>
   </si>
 </sst>
 </file>
@@ -14154,7 +14160,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -14174,6 +14180,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -14204,7 +14216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -14231,6 +14243,16 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14533,7 +14555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y574"/>
+  <dimension ref="A1:Y575"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -51575,7 +51597,75 @@
         <v>272</v>
       </c>
     </row>
+    <row r="575" spans="1:25" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="10" t="s">
+        <v>4692</v>
+      </c>
+      <c r="B575" s="10" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C575" s="10" t="s">
+        <v>4538</v>
+      </c>
+      <c r="D575" s="10" t="s">
+        <v>4539</v>
+      </c>
+      <c r="E575" s="10" t="s">
+        <v>4539</v>
+      </c>
+      <c r="F575" s="10" t="s">
+        <v>4693</v>
+      </c>
+      <c r="G575" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="H575" s="10" t="s">
+        <v>4563</v>
+      </c>
+      <c r="I575" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J575" s="10" t="s">
+        <v>4543</v>
+      </c>
+      <c r="K575" s="10" t="s">
+        <v>4544</v>
+      </c>
+      <c r="L575" s="11">
+        <v>46.21</v>
+      </c>
+      <c r="M575" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="N575" s="10" t="s">
+        <v>4545</v>
+      </c>
+      <c r="O575" s="10" t="s">
+        <v>4546</v>
+      </c>
+      <c r="P575" s="10"/>
+      <c r="Q575" s="10"/>
+      <c r="R575" s="10"/>
+      <c r="S575" s="10"/>
+      <c r="T575" s="10"/>
+      <c r="U575" s="10" t="s">
+        <v>4547</v>
+      </c>
+      <c r="V575" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="W575" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="X575" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y575" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A2:Y575" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B746D38-C6B6-4F37-96CE-BA652F6CC719}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9A30F8-6240-4EA3-8B74-0A6AE2D0A7A5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14239,10 +14239,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -14253,6 +14249,10 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14268,6 +14268,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14579,32 +14583,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
     </row>
     <row r="2" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -21543,7 +21547,7 @@
         <v>964</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>272</v>
+        <v>4692</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>1045</v>
@@ -22333,7 +22337,7 @@
         <v>1054</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>272</v>
+        <v>4692</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>1156</v>
@@ -22463,7 +22467,7 @@
         <v>1054</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>272</v>
+        <v>4692</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>251</v>
@@ -22725,7 +22729,7 @@
         <v>1054</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>272</v>
+        <v>4692</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>1206</v>
@@ -51597,70 +51601,70 @@
         <v>272</v>
       </c>
     </row>
-    <row r="575" spans="1:25" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="10" t="s">
+    <row r="575" spans="1:25" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="8" t="s">
         <v>4692</v>
       </c>
-      <c r="B575" s="10" t="s">
+      <c r="B575" s="8" t="s">
         <v>4537</v>
       </c>
-      <c r="C575" s="10" t="s">
+      <c r="C575" s="8" t="s">
         <v>4538</v>
       </c>
-      <c r="D575" s="10" t="s">
+      <c r="D575" s="8" t="s">
         <v>4539</v>
       </c>
-      <c r="E575" s="10" t="s">
+      <c r="E575" s="8" t="s">
         <v>4539</v>
       </c>
-      <c r="F575" s="10" t="s">
+      <c r="F575" s="8" t="s">
         <v>4693</v>
       </c>
       <c r="G575" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="H575" s="10" t="s">
+      <c r="H575" s="8" t="s">
         <v>4563</v>
       </c>
       <c r="I575" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="J575" s="10" t="s">
+      <c r="J575" s="8" t="s">
         <v>4543</v>
       </c>
-      <c r="K575" s="10" t="s">
+      <c r="K575" s="8" t="s">
         <v>4544</v>
       </c>
-      <c r="L575" s="11">
+      <c r="L575" s="9">
         <v>46.21</v>
       </c>
-      <c r="M575" s="11">
+      <c r="M575" s="9">
         <v>1.25</v>
       </c>
-      <c r="N575" s="10" t="s">
+      <c r="N575" s="8" t="s">
         <v>4545</v>
       </c>
-      <c r="O575" s="10" t="s">
+      <c r="O575" s="8" t="s">
         <v>4546</v>
       </c>
-      <c r="P575" s="10"/>
-      <c r="Q575" s="10"/>
-      <c r="R575" s="10"/>
-      <c r="S575" s="10"/>
-      <c r="T575" s="10"/>
-      <c r="U575" s="10" t="s">
+      <c r="P575" s="8"/>
+      <c r="Q575" s="8"/>
+      <c r="R575" s="8"/>
+      <c r="S575" s="8"/>
+      <c r="T575" s="8"/>
+      <c r="U575" s="8" t="s">
         <v>4547</v>
       </c>
-      <c r="V575" s="10" t="s">
+      <c r="V575" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="W575" s="10" t="s">
+      <c r="W575" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="X575" s="10" t="s">
+      <c r="X575" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="Y575" s="12" t="s">
+      <c r="Y575" s="10" t="s">
         <v>272</v>
       </c>
     </row>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9A30F8-6240-4EA3-8B74-0A6AE2D0A7A5}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{34A4C5B7-2331-4CD6-B73E-ABD98EBE9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D851E3-163E-4DD3-8A4B-9AD06496C82F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$575</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10335" uniqueCount="4694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10353" uniqueCount="4696">
   <si>
     <t>as_of_date=3 เมษายน 2569</t>
   </si>
@@ -14117,6 +14117,12 @@
   </si>
   <si>
     <t>Acting Executive Director - Finance Accounting, Information Technology and Procurement</t>
+  </si>
+  <si>
+    <t>268029 A</t>
+  </si>
+  <si>
+    <t>Acting Department Manager - Production Support &amp; Finished Products</t>
   </si>
 </sst>
 </file>
@@ -14559,7 +14565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y575"/>
+  <dimension ref="A1:Y576"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -42759,8 +42765,8 @@
       <c r="H438" s="4" t="s">
         <v>3518</v>
       </c>
-      <c r="I438" s="4" t="s">
-        <v>48</v>
+      <c r="I438" s="2" t="s">
+        <v>4694</v>
       </c>
       <c r="J438" s="4" t="s">
         <v>3519</v>
@@ -44217,7 +44223,7 @@
         <v>3685</v>
       </c>
       <c r="I461" s="2" t="s">
-        <v>48</v>
+        <v>4694</v>
       </c>
       <c r="J461" s="2" t="s">
         <v>3686</v>
@@ -44347,7 +44353,7 @@
         <v>3702</v>
       </c>
       <c r="I463" s="2" t="s">
-        <v>48</v>
+        <v>4694</v>
       </c>
       <c r="J463" s="2" t="s">
         <v>3703</v>
@@ -46395,5281 +46401,5348 @@
       </c>
     </row>
     <row r="494" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A494" s="4" t="s">
+      <c r="A494" s="2" t="s">
+        <v>4694</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>3942</v>
+      </c>
+      <c r="C494" s="2" t="s">
+        <v>3943</v>
+      </c>
+      <c r="D494" s="2" t="s">
+        <v>2844</v>
+      </c>
+      <c r="E494" s="2" t="s">
+        <v>2844</v>
+      </c>
+      <c r="F494" s="2" t="s">
+        <v>4695</v>
+      </c>
+      <c r="G494" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="H494" s="2" t="s">
+        <v>4576</v>
+      </c>
+      <c r="I494" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J494" s="2" t="s">
+        <v>3946</v>
+      </c>
+      <c r="K494" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="L494" s="3">
+        <v>52.01</v>
+      </c>
+      <c r="M494" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="N494" s="2" t="s">
+        <v>3947</v>
+      </c>
+      <c r="O494" s="2" t="s">
+        <v>3948</v>
+      </c>
+      <c r="P494" s="2"/>
+      <c r="Q494" s="2"/>
+      <c r="R494" s="2"/>
+      <c r="S494" s="2"/>
+      <c r="T494" s="2"/>
+      <c r="U494" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="V494" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W494" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X494" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y494" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="495" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A495" s="4" t="s">
         <v>3949</v>
       </c>
-      <c r="B494" s="4" t="s">
+      <c r="B495" s="4" t="s">
         <v>3950</v>
       </c>
-      <c r="C494" s="4" t="s">
+      <c r="C495" s="4" t="s">
         <v>3951</v>
       </c>
-      <c r="D494" s="4"/>
-      <c r="E494" s="4"/>
-      <c r="F494" s="4" t="s">
+      <c r="D495" s="4"/>
+      <c r="E495" s="4"/>
+      <c r="F495" s="4" t="s">
         <v>3952</v>
       </c>
-      <c r="G494" s="4" t="s">
+      <c r="G495" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H494" s="4" t="s">
+      <c r="H495" s="4" t="s">
         <v>3953</v>
       </c>
-      <c r="I494" s="4" t="s">
+      <c r="I495" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="J494" s="4" t="s">
+      <c r="J495" s="4" t="s">
         <v>3955</v>
       </c>
-      <c r="K494" s="4" t="s">
+      <c r="K495" s="4" t="s">
         <v>3956</v>
       </c>
-      <c r="L494" s="5">
+      <c r="L495" s="5">
         <v>54.52</v>
       </c>
-      <c r="M494" s="5">
+      <c r="M495" s="5">
         <v>21.3</v>
       </c>
-      <c r="N494" s="4" t="s">
+      <c r="N495" s="4" t="s">
         <v>3957</v>
       </c>
-      <c r="O494" s="4" t="s">
+      <c r="O495" s="4" t="s">
         <v>3958</v>
       </c>
-      <c r="P494" s="4"/>
-      <c r="Q494" s="4"/>
-      <c r="R494" s="4"/>
-      <c r="S494" s="4"/>
-      <c r="T494" s="4" t="s">
+      <c r="P495" s="4"/>
+      <c r="Q495" s="4"/>
+      <c r="R495" s="4"/>
+      <c r="S495" s="4"/>
+      <c r="T495" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U494" s="4" t="s">
+      <c r="U495" s="4" t="s">
         <v>3959</v>
       </c>
-      <c r="V494" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W494" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X494" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y494" s="4"/>
-    </row>
-    <row r="495" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A495" s="2" t="s">
+      <c r="V495" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W495" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X495" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y495" s="4"/>
+    </row>
+    <row r="496" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A496" s="2" t="s">
         <v>3960</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="B496" s="2" t="s">
         <v>3961</v>
       </c>
-      <c r="C495" s="2" t="s">
+      <c r="C496" s="2" t="s">
         <v>3962</v>
       </c>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
-      <c r="F495" s="2" t="s">
+      <c r="D496" s="2"/>
+      <c r="E496" s="2"/>
+      <c r="F496" s="2" t="s">
         <v>3963</v>
       </c>
-      <c r="G495" s="2" t="s">
+      <c r="G496" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H495" s="2" t="s">
+      <c r="H496" s="2" t="s">
         <v>3953</v>
       </c>
-      <c r="I495" s="2" t="s">
+      <c r="I496" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="J495" s="2" t="s">
+      <c r="J496" s="2" t="s">
         <v>3964</v>
       </c>
-      <c r="K495" s="2" t="s">
+      <c r="K496" s="2" t="s">
         <v>3965</v>
       </c>
-      <c r="L495" s="3">
+      <c r="L496" s="3">
         <v>48.93</v>
       </c>
-      <c r="M495" s="3">
+      <c r="M496" s="3">
         <v>19.510000000000002</v>
       </c>
-      <c r="N495" s="2" t="s">
+      <c r="N496" s="2" t="s">
         <v>3966</v>
       </c>
-      <c r="O495" s="2" t="s">
+      <c r="O496" s="2" t="s">
         <v>3967</v>
       </c>
-      <c r="P495" s="2"/>
-      <c r="Q495" s="2"/>
-      <c r="R495" s="2"/>
-      <c r="S495" s="2" t="s">
+      <c r="P496" s="2"/>
+      <c r="Q496" s="2"/>
+      <c r="R496" s="2"/>
+      <c r="S496" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T495" s="2" t="s">
+      <c r="T496" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="U495" s="2" t="s">
+      <c r="U496" s="2" t="s">
         <v>3796</v>
       </c>
-      <c r="V495" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W495" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X495" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y495" s="2"/>
-    </row>
-    <row r="496" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A496" s="4" t="s">
+      <c r="V496" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W496" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X496" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y496" s="2"/>
+    </row>
+    <row r="497" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A497" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="B496" s="4" t="s">
+      <c r="B497" s="4" t="s">
         <v>3968</v>
       </c>
-      <c r="C496" s="4" t="s">
+      <c r="C497" s="4" t="s">
         <v>3969</v>
       </c>
-      <c r="D496" s="4" t="s">
+      <c r="D497" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E496" s="4" t="s">
+      <c r="E497" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F496" s="4" t="s">
+      <c r="F497" s="4" t="s">
         <v>3970</v>
       </c>
-      <c r="G496" s="4" t="s">
+      <c r="G497" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="H496" s="4" t="s">
+      <c r="H497" s="4" t="s">
         <v>3953</v>
       </c>
-      <c r="I496" s="4" t="s">
+      <c r="I497" s="4" t="s">
         <v>3971</v>
       </c>
-      <c r="J496" s="4" t="s">
+      <c r="J497" s="4" t="s">
         <v>3972</v>
       </c>
-      <c r="K496" s="4" t="s">
+      <c r="K497" s="4" t="s">
         <v>2029</v>
       </c>
-      <c r="L496" s="5">
+      <c r="L497" s="5">
         <v>48.78</v>
       </c>
-      <c r="M496" s="5">
+      <c r="M497" s="5">
         <v>17.850000000000001</v>
       </c>
-      <c r="N496" s="4" t="s">
+      <c r="N497" s="4" t="s">
         <v>3973</v>
       </c>
-      <c r="O496" s="4" t="s">
+      <c r="O497" s="4" t="s">
         <v>3974</v>
       </c>
-      <c r="P496" s="4"/>
-      <c r="Q496" s="4"/>
-      <c r="R496" s="4"/>
-      <c r="S496" s="4" t="s">
+      <c r="P497" s="4"/>
+      <c r="Q497" s="4"/>
+      <c r="R497" s="4"/>
+      <c r="S497" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="T496" s="4" t="s">
+      <c r="T497" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="U496" s="4" t="s">
+      <c r="U497" s="4" t="s">
         <v>3975</v>
       </c>
-      <c r="V496" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W496" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X496" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y496" s="4"/>
-    </row>
-    <row r="497" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A497" s="2" t="s">
+      <c r="V497" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W497" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X497" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y497" s="4"/>
+    </row>
+    <row r="498" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A498" s="2" t="s">
         <v>3976</v>
       </c>
-      <c r="B497" s="2" t="s">
+      <c r="B498" s="2" t="s">
         <v>3977</v>
       </c>
-      <c r="C497" s="2" t="s">
+      <c r="C498" s="2" t="s">
         <v>3978</v>
       </c>
-      <c r="D497" s="2"/>
-      <c r="E497" s="2"/>
-      <c r="F497" s="2" t="s">
+      <c r="D498" s="2"/>
+      <c r="E498" s="2"/>
+      <c r="F498" s="2" t="s">
         <v>3963</v>
       </c>
-      <c r="G497" s="2" t="s">
+      <c r="G498" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H497" s="2" t="s">
+      <c r="H498" s="2" t="s">
         <v>3953</v>
       </c>
-      <c r="I497" s="2" t="s">
+      <c r="I498" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="J497" s="2" t="s">
+      <c r="J498" s="2" t="s">
         <v>3979</v>
       </c>
-      <c r="K497" s="2" t="s">
+      <c r="K498" s="2" t="s">
         <v>3980</v>
       </c>
-      <c r="L497" s="3">
+      <c r="L498" s="3">
         <v>37.630000000000003</v>
       </c>
-      <c r="M497" s="3">
+      <c r="M498" s="3">
         <v>9.08</v>
       </c>
-      <c r="N497" s="2" t="s">
+      <c r="N498" s="2" t="s">
         <v>3981</v>
       </c>
-      <c r="O497" s="2" t="s">
+      <c r="O498" s="2" t="s">
         <v>3982</v>
       </c>
-      <c r="P497" s="2"/>
-      <c r="Q497" s="2"/>
-      <c r="R497" s="2"/>
-      <c r="S497" s="2" t="s">
+      <c r="P498" s="2"/>
+      <c r="Q498" s="2"/>
+      <c r="R498" s="2"/>
+      <c r="S498" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T497" s="2" t="s">
+      <c r="T498" s="2" t="s">
         <v>1787</v>
       </c>
-      <c r="U497" s="2" t="s">
+      <c r="U498" s="2" t="s">
         <v>3983</v>
       </c>
-      <c r="V497" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W497" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X497" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y497" s="2"/>
-    </row>
-    <row r="498" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A498" s="4" t="s">
+      <c r="V498" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W498" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X498" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y498" s="2"/>
+    </row>
+    <row r="499" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A499" s="4" t="s">
         <v>3984</v>
       </c>
-      <c r="B498" s="4" t="s">
+      <c r="B499" s="4" t="s">
         <v>3985</v>
       </c>
-      <c r="C498" s="4" t="s">
+      <c r="C499" s="4" t="s">
         <v>3986</v>
       </c>
-      <c r="D498" s="4"/>
-      <c r="E498" s="4"/>
-      <c r="F498" s="4" t="s">
+      <c r="D499" s="4"/>
+      <c r="E499" s="4"/>
+      <c r="F499" s="4" t="s">
         <v>3963</v>
       </c>
-      <c r="G498" s="4" t="s">
+      <c r="G499" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H498" s="4" t="s">
+      <c r="H499" s="4" t="s">
         <v>3953</v>
       </c>
-      <c r="I498" s="4" t="s">
+      <c r="I499" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="J498" s="4" t="s">
+      <c r="J499" s="4" t="s">
         <v>3987</v>
       </c>
-      <c r="K498" s="4" t="s">
+      <c r="K499" s="4" t="s">
         <v>3988</v>
       </c>
-      <c r="L498" s="5">
+      <c r="L499" s="5">
         <v>36.35</v>
       </c>
-      <c r="M498" s="5">
+      <c r="M499" s="5">
         <v>8.01</v>
       </c>
-      <c r="N498" s="4" t="s">
+      <c r="N499" s="4" t="s">
         <v>3989</v>
       </c>
-      <c r="O498" s="4" t="s">
+      <c r="O499" s="4" t="s">
         <v>3990</v>
       </c>
-      <c r="P498" s="4"/>
-      <c r="Q498" s="4"/>
-      <c r="R498" s="4"/>
-      <c r="S498" s="4" t="s">
+      <c r="P499" s="4"/>
+      <c r="Q499" s="4"/>
+      <c r="R499" s="4"/>
+      <c r="S499" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="T498" s="4" t="s">
+      <c r="T499" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="U498" s="4" t="s">
+      <c r="U499" s="4" t="s">
         <v>3991</v>
       </c>
-      <c r="V498" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W498" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X498" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y498" s="4"/>
-    </row>
-    <row r="499" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A499" s="2" t="s">
+      <c r="V499" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W499" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X499" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y499" s="4"/>
+    </row>
+    <row r="500" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A500" s="2" t="s">
         <v>3992</v>
       </c>
-      <c r="B499" s="2" t="s">
+      <c r="B500" s="2" t="s">
         <v>3993</v>
       </c>
-      <c r="C499" s="2" t="s">
+      <c r="C500" s="2" t="s">
         <v>3994</v>
       </c>
-      <c r="D499" s="2"/>
-      <c r="E499" s="2"/>
-      <c r="F499" s="2" t="s">
+      <c r="D500" s="2"/>
+      <c r="E500" s="2"/>
+      <c r="F500" s="2" t="s">
         <v>3995</v>
       </c>
-      <c r="G499" s="2" t="s">
+      <c r="G500" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H499" s="2" t="s">
+      <c r="H500" s="2" t="s">
         <v>3953</v>
       </c>
-      <c r="I499" s="2" t="s">
+      <c r="I500" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="J499" s="2" t="s">
+      <c r="J500" s="2" t="s">
         <v>3996</v>
       </c>
-      <c r="K499" s="2" t="s">
+      <c r="K500" s="2" t="s">
         <v>3997</v>
       </c>
-      <c r="L499" s="3">
+      <c r="L500" s="3">
         <v>31.31</v>
       </c>
-      <c r="M499" s="3">
+      <c r="M500" s="3">
         <v>2.63</v>
       </c>
-      <c r="N499" s="2" t="s">
+      <c r="N500" s="2" t="s">
         <v>3998</v>
       </c>
-      <c r="O499" s="2" t="s">
+      <c r="O500" s="2" t="s">
         <v>3999</v>
       </c>
-      <c r="P499" s="2"/>
-      <c r="Q499" s="2"/>
-      <c r="R499" s="2"/>
-      <c r="S499" s="2"/>
-      <c r="T499" s="2" t="s">
+      <c r="P500" s="2"/>
+      <c r="Q500" s="2"/>
+      <c r="R500" s="2"/>
+      <c r="S500" s="2"/>
+      <c r="T500" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U499" s="2" t="s">
+      <c r="U500" s="2" t="s">
         <v>3257</v>
       </c>
-      <c r="V499" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W499" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X499" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y499" s="2"/>
-    </row>
-    <row r="500" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A500" s="4" t="s">
+      <c r="V500" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W500" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X500" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y500" s="2"/>
+    </row>
+    <row r="501" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A501" s="4" t="s">
         <v>4000</v>
       </c>
-      <c r="B500" s="4" t="s">
+      <c r="B501" s="4" t="s">
         <v>4001</v>
       </c>
-      <c r="C500" s="4" t="s">
+      <c r="C501" s="4" t="s">
         <v>4002</v>
       </c>
-      <c r="D500" s="4"/>
-      <c r="E500" s="4"/>
-      <c r="F500" s="4" t="s">
+      <c r="D501" s="4"/>
+      <c r="E501" s="4"/>
+      <c r="F501" s="4" t="s">
         <v>3995</v>
       </c>
-      <c r="G500" s="4" t="s">
+      <c r="G501" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H500" s="4" t="s">
+      <c r="H501" s="4" t="s">
         <v>3953</v>
       </c>
-      <c r="I500" s="4" t="s">
+      <c r="I501" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="J500" s="4" t="s">
+      <c r="J501" s="4" t="s">
         <v>4003</v>
       </c>
-      <c r="K500" s="4" t="s">
+      <c r="K501" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="L500" s="5">
+      <c r="L501" s="5">
         <v>31.6</v>
       </c>
-      <c r="M500" s="5">
+      <c r="M501" s="5">
         <v>2.39</v>
       </c>
-      <c r="N500" s="4" t="s">
+      <c r="N501" s="4" t="s">
         <v>4004</v>
       </c>
-      <c r="O500" s="4" t="s">
+      <c r="O501" s="4" t="s">
         <v>4005</v>
       </c>
-      <c r="P500" s="4"/>
-      <c r="Q500" s="4"/>
-      <c r="R500" s="4"/>
-      <c r="S500" s="4"/>
-      <c r="T500" s="4"/>
-      <c r="U500" s="4" t="s">
+      <c r="P501" s="4"/>
+      <c r="Q501" s="4"/>
+      <c r="R501" s="4"/>
+      <c r="S501" s="4"/>
+      <c r="T501" s="4"/>
+      <c r="U501" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="V500" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W500" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X500" s="4" t="s">
+      <c r="V501" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W501" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X501" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y500" s="4"/>
-    </row>
-    <row r="501" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A501" s="2" t="s">
+      <c r="Y501" s="4"/>
+    </row>
+    <row r="502" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A502" s="2" t="s">
         <v>4006</v>
       </c>
-      <c r="B501" s="2" t="s">
+      <c r="B502" s="2" t="s">
         <v>4007</v>
       </c>
-      <c r="C501" s="2" t="s">
+      <c r="C502" s="2" t="s">
         <v>4008</v>
       </c>
-      <c r="D501" s="2"/>
-      <c r="E501" s="2"/>
-      <c r="F501" s="2" t="s">
+      <c r="D502" s="2"/>
+      <c r="E502" s="2"/>
+      <c r="F502" s="2" t="s">
         <v>3995</v>
       </c>
-      <c r="G501" s="2" t="s">
+      <c r="G502" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H501" s="2" t="s">
+      <c r="H502" s="2" t="s">
         <v>3953</v>
       </c>
-      <c r="I501" s="2" t="s">
+      <c r="I502" s="2" t="s">
         <v>3954</v>
       </c>
-      <c r="J501" s="2" t="s">
+      <c r="J502" s="2" t="s">
         <v>4009</v>
       </c>
-      <c r="K501" s="2" t="s">
+      <c r="K502" s="2" t="s">
         <v>4010</v>
       </c>
-      <c r="L501" s="3">
+      <c r="L502" s="3">
         <v>29.86</v>
       </c>
-      <c r="M501" s="3">
+      <c r="M502" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="N501" s="2" t="s">
+      <c r="N502" s="2" t="s">
         <v>4011</v>
       </c>
-      <c r="O501" s="2" t="s">
+      <c r="O502" s="2" t="s">
         <v>4012</v>
       </c>
-      <c r="P501" s="2"/>
-      <c r="Q501" s="2"/>
-      <c r="R501" s="2"/>
-      <c r="S501" s="2"/>
-      <c r="T501" s="2"/>
-      <c r="U501" s="2" t="s">
+      <c r="P502" s="2"/>
+      <c r="Q502" s="2"/>
+      <c r="R502" s="2"/>
+      <c r="S502" s="2"/>
+      <c r="T502" s="2"/>
+      <c r="U502" s="2" t="s">
         <v>2032</v>
       </c>
-      <c r="V501" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W501" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X501" s="2" t="s">
+      <c r="V502" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W502" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X502" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y501" s="2"/>
-    </row>
-    <row r="502" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A502" s="4" t="s">
+      <c r="Y502" s="2"/>
+    </row>
+    <row r="503" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A503" s="4" t="s">
         <v>4013</v>
       </c>
-      <c r="B502" s="4" t="s">
+      <c r="B503" s="4" t="s">
         <v>4014</v>
       </c>
-      <c r="C502" s="4" t="s">
+      <c r="C503" s="4" t="s">
         <v>4015</v>
       </c>
-      <c r="D502" s="4"/>
-      <c r="E502" s="4"/>
-      <c r="F502" s="4" t="s">
+      <c r="D503" s="4"/>
+      <c r="E503" s="4"/>
+      <c r="F503" s="4" t="s">
         <v>4016</v>
       </c>
-      <c r="G502" s="4" t="s">
+      <c r="G503" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H502" s="4" t="s">
+      <c r="H503" s="4" t="s">
         <v>4017</v>
       </c>
-      <c r="I502" s="4" t="s">
+      <c r="I503" s="4" t="s">
         <v>4018</v>
       </c>
-      <c r="J502" s="4" t="s">
+      <c r="J503" s="4" t="s">
         <v>4019</v>
       </c>
-      <c r="K502" s="4" t="s">
+      <c r="K503" s="4" t="s">
         <v>4020</v>
       </c>
-      <c r="L502" s="5">
+      <c r="L503" s="5">
         <v>55.25</v>
       </c>
-      <c r="M502" s="5">
+      <c r="M503" s="5">
         <v>32.75</v>
       </c>
-      <c r="N502" s="4" t="s">
+      <c r="N503" s="4" t="s">
         <v>4021</v>
       </c>
-      <c r="O502" s="4" t="s">
+      <c r="O503" s="4" t="s">
         <v>4022</v>
       </c>
-      <c r="P502" s="4"/>
-      <c r="Q502" s="4"/>
-      <c r="R502" s="4"/>
-      <c r="S502" s="4"/>
-      <c r="T502" s="4" t="s">
+      <c r="P503" s="4"/>
+      <c r="Q503" s="4"/>
+      <c r="R503" s="4"/>
+      <c r="S503" s="4"/>
+      <c r="T503" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="U502" s="4" t="s">
+      <c r="U503" s="4" t="s">
         <v>4023</v>
       </c>
-      <c r="V502" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W502" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X502" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y502" s="4"/>
-    </row>
-    <row r="503" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A503" s="2" t="s">
+      <c r="V503" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W503" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X503" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y503" s="4"/>
+    </row>
+    <row r="504" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A504" s="2" t="s">
         <v>4024</v>
       </c>
-      <c r="B503" s="2" t="s">
+      <c r="B504" s="2" t="s">
         <v>4025</v>
       </c>
-      <c r="C503" s="2" t="s">
+      <c r="C504" s="2" t="s">
         <v>4026</v>
       </c>
-      <c r="D503" s="2"/>
-      <c r="E503" s="2"/>
-      <c r="F503" s="2" t="s">
+      <c r="D504" s="2"/>
+      <c r="E504" s="2"/>
+      <c r="F504" s="2" t="s">
         <v>4027</v>
       </c>
-      <c r="G503" s="2" t="s">
+      <c r="G504" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H503" s="2" t="s">
+      <c r="H504" s="2" t="s">
         <v>4017</v>
       </c>
-      <c r="I503" s="2" t="s">
+      <c r="I504" s="2" t="s">
         <v>4018</v>
       </c>
-      <c r="J503" s="2" t="s">
+      <c r="J504" s="2" t="s">
         <v>4028</v>
       </c>
-      <c r="K503" s="2" t="s">
+      <c r="K504" s="2" t="s">
         <v>4029</v>
       </c>
-      <c r="L503" s="3">
+      <c r="L504" s="3">
         <v>50.68</v>
       </c>
-      <c r="M503" s="3">
+      <c r="M504" s="3">
         <v>18.64</v>
       </c>
-      <c r="N503" s="2" t="s">
+      <c r="N504" s="2" t="s">
         <v>4030</v>
       </c>
-      <c r="O503" s="2" t="s">
+      <c r="O504" s="2" t="s">
         <v>4031</v>
       </c>
-      <c r="P503" s="2"/>
-      <c r="Q503" s="2"/>
-      <c r="R503" s="2"/>
-      <c r="S503" s="2" t="s">
+      <c r="P504" s="2"/>
+      <c r="Q504" s="2"/>
+      <c r="R504" s="2"/>
+      <c r="S504" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="T503" s="2" t="s">
+      <c r="T504" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="U503" s="2" t="s">
+      <c r="U504" s="2" t="s">
         <v>2056</v>
       </c>
-      <c r="V503" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W503" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X503" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y503" s="2"/>
-    </row>
-    <row r="504" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A504" s="4" t="s">
+      <c r="V504" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W504" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X504" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y504" s="2"/>
+    </row>
+    <row r="505" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A505" s="4" t="s">
         <v>4018</v>
       </c>
-      <c r="B504" s="4" t="s">
+      <c r="B505" s="4" t="s">
         <v>4032</v>
       </c>
-      <c r="C504" s="4" t="s">
+      <c r="C505" s="4" t="s">
         <v>4033</v>
       </c>
-      <c r="D504" s="4" t="s">
+      <c r="D505" s="4" t="s">
         <v>2874</v>
       </c>
-      <c r="E504" s="4" t="s">
+      <c r="E505" s="4" t="s">
         <v>2874</v>
       </c>
-      <c r="F504" s="4" t="s">
+      <c r="F505" s="4" t="s">
         <v>4034</v>
       </c>
-      <c r="G504" s="4" t="s">
+      <c r="G505" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="H504" s="4" t="s">
+      <c r="H505" s="4" t="s">
         <v>4017</v>
       </c>
-      <c r="I504" s="4" t="s">
+      <c r="I505" s="4" t="s">
         <v>3971</v>
       </c>
-      <c r="J504" s="4" t="s">
+      <c r="J505" s="4" t="s">
         <v>4035</v>
       </c>
-      <c r="K504" s="4" t="s">
+      <c r="K505" s="4" t="s">
         <v>1534</v>
       </c>
-      <c r="L504" s="5">
+      <c r="L505" s="5">
         <v>49.99</v>
       </c>
-      <c r="M504" s="5">
+      <c r="M505" s="5">
         <v>23.97</v>
       </c>
-      <c r="N504" s="4" t="s">
+      <c r="N505" s="4" t="s">
         <v>4036</v>
       </c>
-      <c r="O504" s="4" t="s">
+      <c r="O505" s="4" t="s">
         <v>4037</v>
       </c>
-      <c r="P504" s="4"/>
-      <c r="Q504" s="4"/>
-      <c r="R504" s="4"/>
-      <c r="S504" s="4" t="s">
+      <c r="P505" s="4"/>
+      <c r="Q505" s="4"/>
+      <c r="R505" s="4"/>
+      <c r="S505" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="T504" s="4" t="s">
+      <c r="T505" s="4" t="s">
         <v>4038</v>
       </c>
-      <c r="U504" s="4" t="s">
+      <c r="U505" s="4" t="s">
         <v>4039</v>
       </c>
-      <c r="V504" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W504" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X504" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y504" s="4"/>
-    </row>
-    <row r="505" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A505" s="2" t="s">
+      <c r="V505" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W505" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X505" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y505" s="4"/>
+    </row>
+    <row r="506" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A506" s="2" t="s">
         <v>4040</v>
       </c>
-      <c r="B505" s="2" t="s">
+      <c r="B506" s="2" t="s">
         <v>4041</v>
       </c>
-      <c r="C505" s="2" t="s">
+      <c r="C506" s="2" t="s">
         <v>4042</v>
       </c>
-      <c r="D505" s="2" t="s">
+      <c r="D506" s="2" t="s">
         <v>2874</v>
       </c>
-      <c r="E505" s="2" t="s">
+      <c r="E506" s="2" t="s">
         <v>2874</v>
       </c>
-      <c r="F505" s="2" t="s">
+      <c r="F506" s="2" t="s">
         <v>4043</v>
       </c>
-      <c r="G505" s="2" t="s">
+      <c r="G506" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H505" s="2" t="s">
+      <c r="H506" s="2" t="s">
         <v>4017</v>
       </c>
-      <c r="I505" s="2" t="s">
+      <c r="I506" s="2" t="s">
         <v>4018</v>
       </c>
-      <c r="J505" s="2" t="s">
+      <c r="J506" s="2" t="s">
         <v>4044</v>
       </c>
-      <c r="K505" s="2" t="s">
+      <c r="K506" s="2" t="s">
         <v>4045</v>
       </c>
-      <c r="L505" s="3">
+      <c r="L506" s="3">
         <v>43.31</v>
       </c>
-      <c r="M505" s="3">
+      <c r="M506" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N505" s="2" t="s">
+      <c r="N506" s="2" t="s">
         <v>4046</v>
       </c>
-      <c r="O505" s="2" t="s">
+      <c r="O506" s="2" t="s">
         <v>4047</v>
       </c>
-      <c r="P505" s="2"/>
-      <c r="Q505" s="2"/>
-      <c r="R505" s="2"/>
-      <c r="S505" s="2"/>
-      <c r="T505" s="2"/>
-      <c r="U505" s="2" t="s">
+      <c r="P506" s="2"/>
+      <c r="Q506" s="2"/>
+      <c r="R506" s="2"/>
+      <c r="S506" s="2"/>
+      <c r="T506" s="2"/>
+      <c r="U506" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V505" s="2" t="s">
+      <c r="V506" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="W505" s="2" t="s">
+      <c r="W506" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X505" s="2" t="s">
+      <c r="X506" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y505" s="2"/>
-    </row>
-    <row r="506" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A506" s="4" t="s">
+      <c r="Y506" s="2"/>
+    </row>
+    <row r="507" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A507" s="4" t="s">
         <v>4048</v>
       </c>
-      <c r="B506" s="4" t="s">
+      <c r="B507" s="4" t="s">
         <v>4049</v>
       </c>
-      <c r="C506" s="4" t="s">
+      <c r="C507" s="4" t="s">
         <v>4050</v>
       </c>
-      <c r="D506" s="4"/>
-      <c r="E506" s="4"/>
-      <c r="F506" s="4" t="s">
+      <c r="D507" s="4"/>
+      <c r="E507" s="4"/>
+      <c r="F507" s="4" t="s">
         <v>4051</v>
       </c>
-      <c r="G506" s="4" t="s">
+      <c r="G507" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H506" s="4" t="s">
+      <c r="H507" s="4" t="s">
         <v>4052</v>
       </c>
-      <c r="I506" s="4" t="s">
+      <c r="I507" s="4" t="s">
         <v>3954</v>
       </c>
-      <c r="J506" s="4" t="s">
+      <c r="J507" s="4" t="s">
         <v>4053</v>
       </c>
-      <c r="K506" s="4" t="s">
+      <c r="K507" s="4" t="s">
         <v>4054</v>
       </c>
-      <c r="L506" s="5">
+      <c r="L507" s="5">
         <v>29.2</v>
       </c>
-      <c r="M506" s="5">
+      <c r="M507" s="5">
         <v>0.09</v>
       </c>
-      <c r="N506" s="4" t="s">
+      <c r="N507" s="4" t="s">
         <v>4055</v>
       </c>
-      <c r="O506" s="4" t="s">
+      <c r="O507" s="4" t="s">
         <v>4056</v>
       </c>
-      <c r="P506" s="4"/>
-      <c r="Q506" s="4"/>
-      <c r="R506" s="4"/>
-      <c r="S506" s="4"/>
-      <c r="T506" s="4"/>
-      <c r="U506" s="4" t="s">
+      <c r="P507" s="4"/>
+      <c r="Q507" s="4"/>
+      <c r="R507" s="4"/>
+      <c r="S507" s="4"/>
+      <c r="T507" s="4"/>
+      <c r="U507" s="4" t="s">
         <v>4057</v>
       </c>
-      <c r="V506" s="4" t="s">
+      <c r="V507" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W506" s="4" t="s">
+      <c r="W507" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X506" s="4" t="s">
+      <c r="X507" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y506" s="4"/>
-    </row>
-    <row r="507" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A507" s="2" t="s">
+      <c r="Y507" s="4"/>
+    </row>
+    <row r="508" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A508" s="2" t="s">
         <v>3971</v>
       </c>
-      <c r="B507" s="2" t="s">
+      <c r="B508" s="2" t="s">
         <v>4058</v>
       </c>
-      <c r="C507" s="2" t="s">
+      <c r="C508" s="2" t="s">
         <v>4059</v>
       </c>
-      <c r="D507" s="2"/>
-      <c r="E507" s="2"/>
-      <c r="F507" s="2" t="s">
+      <c r="D508" s="2"/>
+      <c r="E508" s="2"/>
+      <c r="F508" s="2" t="s">
         <v>4060</v>
       </c>
-      <c r="G507" s="2" t="s">
+      <c r="G508" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H507" s="2" t="s">
+      <c r="H508" s="2" t="s">
         <v>4052</v>
       </c>
-      <c r="I507" s="2" t="s">
+      <c r="I508" s="2" t="s">
         <v>4061</v>
       </c>
-      <c r="J507" s="2" t="s">
+      <c r="J508" s="2" t="s">
         <v>4062</v>
       </c>
-      <c r="K507" s="2" t="s">
+      <c r="K508" s="2" t="s">
         <v>4063</v>
       </c>
-      <c r="L507" s="3">
+      <c r="L508" s="3">
         <v>48.74</v>
       </c>
-      <c r="M507" s="3">
+      <c r="M508" s="3">
         <v>27.84</v>
       </c>
-      <c r="N507" s="2" t="s">
+      <c r="N508" s="2" t="s">
         <v>4064</v>
       </c>
-      <c r="O507" s="2" t="s">
+      <c r="O508" s="2" t="s">
         <v>4065</v>
       </c>
-      <c r="P507" s="2"/>
-      <c r="Q507" s="2"/>
-      <c r="R507" s="2"/>
-      <c r="S507" s="2" t="s">
+      <c r="P508" s="2"/>
+      <c r="Q508" s="2"/>
+      <c r="R508" s="2"/>
+      <c r="S508" s="2" t="s">
         <v>4066</v>
       </c>
-      <c r="T507" s="2"/>
-      <c r="U507" s="2" t="s">
+      <c r="T508" s="2"/>
+      <c r="U508" s="2" t="s">
         <v>4067</v>
       </c>
-      <c r="V507" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W507" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X507" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y507" s="2"/>
-    </row>
-    <row r="508" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A508" s="4" t="s">
+      <c r="V508" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W508" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X508" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y508" s="2"/>
+    </row>
+    <row r="509" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A509" s="4" t="s">
         <v>4068</v>
       </c>
-      <c r="B508" s="4" t="s">
+      <c r="B509" s="4" t="s">
         <v>4069</v>
       </c>
-      <c r="C508" s="4" t="s">
+      <c r="C509" s="4" t="s">
         <v>4070</v>
       </c>
-      <c r="D508" s="4" t="s">
+      <c r="D509" s="4" t="s">
         <v>2780</v>
       </c>
-      <c r="E508" s="4" t="s">
+      <c r="E509" s="4" t="s">
         <v>2780</v>
       </c>
-      <c r="F508" s="4" t="s">
+      <c r="F509" s="4" t="s">
         <v>4071</v>
       </c>
-      <c r="G508" s="4" t="s">
+      <c r="G509" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H508" s="4" t="s">
+      <c r="H509" s="4" t="s">
         <v>4072</v>
       </c>
-      <c r="I508" s="4" t="s">
+      <c r="I509" s="4" t="s">
         <v>4073</v>
       </c>
-      <c r="J508" s="4" t="s">
+      <c r="J509" s="4" t="s">
         <v>4074</v>
       </c>
-      <c r="K508" s="4" t="s">
+      <c r="K509" s="4" t="s">
         <v>4075</v>
       </c>
-      <c r="L508" s="5">
+      <c r="L509" s="5">
         <v>42.95</v>
       </c>
-      <c r="M508" s="5">
+      <c r="M509" s="5">
         <v>10.31</v>
       </c>
-      <c r="N508" s="4" t="s">
+      <c r="N509" s="4" t="s">
         <v>4076</v>
       </c>
-      <c r="O508" s="4" t="s">
+      <c r="O509" s="4" t="s">
         <v>4077</v>
       </c>
-      <c r="P508" s="4"/>
-      <c r="Q508" s="4"/>
-      <c r="R508" s="4"/>
-      <c r="S508" s="4" t="s">
+      <c r="P509" s="4"/>
+      <c r="Q509" s="4"/>
+      <c r="R509" s="4"/>
+      <c r="S509" s="4" t="s">
         <v>2161</v>
       </c>
-      <c r="T508" s="4" t="s">
+      <c r="T509" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U508" s="4" t="s">
+      <c r="U509" s="4" t="s">
         <v>1796</v>
       </c>
-      <c r="V508" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W508" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X508" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y508" s="4"/>
-    </row>
-    <row r="509" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A509" s="2" t="s">
+      <c r="V509" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W509" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X509" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y509" s="4"/>
+    </row>
+    <row r="510" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A510" s="2" t="s">
         <v>4078</v>
       </c>
-      <c r="B509" s="2" t="s">
+      <c r="B510" s="2" t="s">
         <v>4079</v>
       </c>
-      <c r="C509" s="2" t="s">
+      <c r="C510" s="2" t="s">
         <v>4080</v>
       </c>
-      <c r="D509" s="2"/>
-      <c r="E509" s="2"/>
-      <c r="F509" s="2" t="s">
+      <c r="D510" s="2"/>
+      <c r="E510" s="2"/>
+      <c r="F510" s="2" t="s">
         <v>4081</v>
       </c>
-      <c r="G509" s="2" t="s">
+      <c r="G510" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H509" s="2" t="s">
+      <c r="H510" s="2" t="s">
         <v>4082</v>
       </c>
-      <c r="I509" s="2" t="s">
+      <c r="I510" s="2" t="s">
         <v>4068</v>
       </c>
-      <c r="J509" s="2" t="s">
+      <c r="J510" s="2" t="s">
         <v>4083</v>
       </c>
-      <c r="K509" s="2" t="s">
+      <c r="K510" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="L509" s="3">
+      <c r="L510" s="3">
         <v>29.82</v>
       </c>
-      <c r="M509" s="3">
+      <c r="M510" s="3">
         <v>2.83</v>
       </c>
-      <c r="N509" s="2" t="s">
+      <c r="N510" s="2" t="s">
         <v>4084</v>
       </c>
-      <c r="O509" s="2" t="s">
+      <c r="O510" s="2" t="s">
         <v>4085</v>
       </c>
-      <c r="P509" s="2"/>
-      <c r="Q509" s="2"/>
-      <c r="R509" s="2"/>
-      <c r="S509" s="2"/>
-      <c r="T509" s="2"/>
-      <c r="U509" s="2" t="s">
+      <c r="P510" s="2"/>
+      <c r="Q510" s="2"/>
+      <c r="R510" s="2"/>
+      <c r="S510" s="2"/>
+      <c r="T510" s="2"/>
+      <c r="U510" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="V509" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W509" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X509" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y509" s="2"/>
-    </row>
-    <row r="510" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A510" s="4" t="s">
+      <c r="V510" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W510" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X510" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y510" s="2"/>
+    </row>
+    <row r="511" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A511" s="4" t="s">
         <v>4086</v>
       </c>
-      <c r="B510" s="4" t="s">
+      <c r="B511" s="4" t="s">
         <v>4087</v>
       </c>
-      <c r="C510" s="4" t="s">
+      <c r="C511" s="4" t="s">
         <v>4088</v>
       </c>
-      <c r="D510" s="4" t="s">
+      <c r="D511" s="4" t="s">
         <v>4089</v>
       </c>
-      <c r="E510" s="4" t="s">
+      <c r="E511" s="4" t="s">
         <v>4089</v>
       </c>
-      <c r="F510" s="4" t="s">
+      <c r="F511" s="4" t="s">
         <v>4090</v>
       </c>
-      <c r="G510" s="4" t="s">
+      <c r="G511" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H510" s="4" t="s">
+      <c r="H511" s="4" t="s">
         <v>4091</v>
       </c>
-      <c r="I510" s="4" t="s">
+      <c r="I511" s="4" t="s">
         <v>4073</v>
       </c>
-      <c r="J510" s="4" t="s">
+      <c r="J511" s="4" t="s">
         <v>4092</v>
       </c>
-      <c r="K510" s="4" t="s">
+      <c r="K511" s="4" t="s">
         <v>4093</v>
       </c>
-      <c r="L510" s="5">
+      <c r="L511" s="5">
         <v>36.74</v>
       </c>
-      <c r="M510" s="5">
+      <c r="M511" s="5">
         <v>2.0099999999999998</v>
       </c>
-      <c r="N510" s="4" t="s">
+      <c r="N511" s="4" t="s">
         <v>4094</v>
       </c>
-      <c r="O510" s="4" t="s">
+      <c r="O511" s="4" t="s">
         <v>4095</v>
       </c>
-      <c r="P510" s="4"/>
-      <c r="Q510" s="4"/>
-      <c r="R510" s="4"/>
-      <c r="S510" s="4"/>
-      <c r="T510" s="4"/>
-      <c r="U510" s="4" t="s">
+      <c r="P511" s="4"/>
+      <c r="Q511" s="4"/>
+      <c r="R511" s="4"/>
+      <c r="S511" s="4"/>
+      <c r="T511" s="4"/>
+      <c r="U511" s="4" t="s">
         <v>4096</v>
       </c>
-      <c r="V510" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W510" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X510" s="4" t="s">
+      <c r="V511" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W511" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X511" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y510" s="4"/>
-    </row>
-    <row r="511" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A511" s="2" t="s">
+      <c r="Y511" s="4"/>
+    </row>
+    <row r="512" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A512" s="2" t="s">
         <v>4097</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="B512" s="2" t="s">
         <v>4098</v>
       </c>
-      <c r="C511" s="2" t="s">
+      <c r="C512" s="2" t="s">
         <v>4099</v>
       </c>
-      <c r="D511" s="2" t="s">
+      <c r="D512" s="2" t="s">
         <v>4100</v>
       </c>
-      <c r="E511" s="2" t="s">
+      <c r="E512" s="2" t="s">
         <v>4100</v>
       </c>
-      <c r="F511" s="2" t="s">
+      <c r="F512" s="2" t="s">
         <v>4101</v>
       </c>
-      <c r="G511" s="2" t="s">
+      <c r="G512" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H511" s="2" t="s">
+      <c r="H512" s="2" t="s">
         <v>4102</v>
       </c>
-      <c r="I511" s="2" t="s">
+      <c r="I512" s="2" t="s">
         <v>4086</v>
       </c>
-      <c r="J511" s="2" t="s">
+      <c r="J512" s="2" t="s">
         <v>4103</v>
       </c>
-      <c r="K511" s="2" t="s">
+      <c r="K512" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="L511" s="3">
+      <c r="L512" s="3">
         <v>27.89</v>
       </c>
-      <c r="M511" s="3">
+      <c r="M512" s="3">
         <v>2.1</v>
       </c>
-      <c r="N511" s="2" t="s">
+      <c r="N512" s="2" t="s">
         <v>4104</v>
       </c>
-      <c r="O511" s="2" t="s">
+      <c r="O512" s="2" t="s">
         <v>4105</v>
       </c>
-      <c r="P511" s="2"/>
-      <c r="Q511" s="2"/>
-      <c r="R511" s="2"/>
-      <c r="S511" s="2"/>
-      <c r="T511" s="2"/>
-      <c r="U511" s="2" t="s">
+      <c r="P512" s="2"/>
+      <c r="Q512" s="2"/>
+      <c r="R512" s="2"/>
+      <c r="S512" s="2"/>
+      <c r="T512" s="2"/>
+      <c r="U512" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="V511" s="2" t="s">
+      <c r="V512" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W511" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X511" s="2" t="s">
+      <c r="W512" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X512" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y511" s="2"/>
-    </row>
-    <row r="512" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A512" s="4" t="s">
+      <c r="Y512" s="2"/>
+    </row>
+    <row r="513" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A513" s="4" t="s">
         <v>4106</v>
       </c>
-      <c r="B512" s="4" t="s">
+      <c r="B513" s="4" t="s">
         <v>4107</v>
       </c>
-      <c r="C512" s="4" t="s">
+      <c r="C513" s="4" t="s">
         <v>4108</v>
       </c>
-      <c r="D512" s="4" t="s">
+      <c r="D513" s="4" t="s">
         <v>4109</v>
       </c>
-      <c r="E512" s="4" t="s">
+      <c r="E513" s="4" t="s">
         <v>4109</v>
       </c>
-      <c r="F512" s="4" t="s">
+      <c r="F513" s="4" t="s">
         <v>4110</v>
       </c>
-      <c r="G512" s="4" t="s">
+      <c r="G513" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H512" s="4" t="s">
+      <c r="H513" s="4" t="s">
         <v>4111</v>
       </c>
-      <c r="I512" s="4" t="s">
+      <c r="I513" s="4" t="s">
         <v>4086</v>
       </c>
-      <c r="J512" s="4" t="s">
+      <c r="J513" s="4" t="s">
         <v>2009</v>
       </c>
-      <c r="K512" s="4" t="s">
+      <c r="K513" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L512" s="5">
+      <c r="L513" s="5">
         <v>28.84</v>
       </c>
-      <c r="M512" s="5">
+      <c r="M513" s="5">
         <v>0.01</v>
       </c>
-      <c r="N512" s="4" t="s">
+      <c r="N513" s="4" t="s">
         <v>4112</v>
       </c>
-      <c r="O512" s="4" t="s">
+      <c r="O513" s="4" t="s">
         <v>4113</v>
       </c>
-      <c r="P512" s="4"/>
-      <c r="Q512" s="4"/>
-      <c r="R512" s="4"/>
-      <c r="S512" s="4"/>
-      <c r="T512" s="4"/>
-      <c r="U512" s="4" t="s">
+      <c r="P513" s="4"/>
+      <c r="Q513" s="4"/>
+      <c r="R513" s="4"/>
+      <c r="S513" s="4"/>
+      <c r="T513" s="4"/>
+      <c r="U513" s="4" t="s">
         <v>2848</v>
       </c>
-      <c r="V512" s="4" t="s">
+      <c r="V513" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W512" s="4" t="s">
+      <c r="W513" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X512" s="4" t="s">
+      <c r="X513" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y512" s="4"/>
-    </row>
-    <row r="513" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A513" s="2" t="s">
+      <c r="Y513" s="4"/>
+    </row>
+    <row r="514" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A514" s="2" t="s">
         <v>4114</v>
       </c>
-      <c r="B513" s="2" t="s">
+      <c r="B514" s="2" t="s">
         <v>4115</v>
       </c>
-      <c r="C513" s="2" t="s">
+      <c r="C514" s="2" t="s">
         <v>4116</v>
       </c>
-      <c r="D513" s="2" t="s">
+      <c r="D514" s="2" t="s">
         <v>2238</v>
       </c>
-      <c r="E513" s="2" t="s">
+      <c r="E514" s="2" t="s">
         <v>2238</v>
       </c>
-      <c r="F513" s="2" t="s">
+      <c r="F514" s="2" t="s">
         <v>4071</v>
       </c>
-      <c r="G513" s="2" t="s">
+      <c r="G514" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H513" s="2" t="s">
+      <c r="H514" s="2" t="s">
         <v>4117</v>
       </c>
-      <c r="I513" s="2" t="s">
+      <c r="I514" s="2" t="s">
         <v>4073</v>
       </c>
-      <c r="J513" s="2" t="s">
+      <c r="J514" s="2" t="s">
         <v>4118</v>
       </c>
-      <c r="K513" s="2" t="s">
+      <c r="K514" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="L513" s="3">
+      <c r="L514" s="3">
         <v>37.03</v>
       </c>
-      <c r="M513" s="3">
+      <c r="M514" s="3">
         <v>7.93</v>
       </c>
-      <c r="N513" s="2" t="s">
+      <c r="N514" s="2" t="s">
         <v>4119</v>
       </c>
-      <c r="O513" s="2" t="s">
+      <c r="O514" s="2" t="s">
         <v>4120</v>
       </c>
-      <c r="P513" s="2"/>
-      <c r="Q513" s="2"/>
-      <c r="R513" s="2"/>
-      <c r="S513" s="2" t="s">
+      <c r="P514" s="2"/>
+      <c r="Q514" s="2"/>
+      <c r="R514" s="2"/>
+      <c r="S514" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="T513" s="2"/>
-      <c r="U513" s="2" t="s">
+      <c r="T514" s="2"/>
+      <c r="U514" s="2" t="s">
         <v>4121</v>
       </c>
-      <c r="V513" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W513" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X513" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y513" s="2"/>
-    </row>
-    <row r="514" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A514" s="4" t="s">
+      <c r="V514" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W514" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X514" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y514" s="2"/>
+    </row>
+    <row r="515" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A515" s="4" t="s">
         <v>4122</v>
       </c>
-      <c r="B514" s="4" t="s">
+      <c r="B515" s="4" t="s">
         <v>4123</v>
       </c>
-      <c r="C514" s="4" t="s">
+      <c r="C515" s="4" t="s">
         <v>4124</v>
       </c>
-      <c r="D514" s="4" t="s">
+      <c r="D515" s="4" t="s">
         <v>3744</v>
       </c>
-      <c r="E514" s="4" t="s">
+      <c r="E515" s="4" t="s">
         <v>3744</v>
       </c>
-      <c r="F514" s="4" t="s">
+      <c r="F515" s="4" t="s">
         <v>4125</v>
       </c>
-      <c r="G514" s="4" t="s">
+      <c r="G515" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H514" s="4" t="s">
+      <c r="H515" s="4" t="s">
         <v>4117</v>
       </c>
-      <c r="I514" s="4" t="s">
+      <c r="I515" s="4" t="s">
         <v>4114</v>
       </c>
-      <c r="J514" s="4" t="s">
+      <c r="J515" s="4" t="s">
         <v>4126</v>
       </c>
-      <c r="K514" s="4" t="s">
+      <c r="K515" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L514" s="5">
+      <c r="L515" s="5">
         <v>25.87</v>
       </c>
-      <c r="M514" s="5">
+      <c r="M515" s="5">
         <v>0.01</v>
       </c>
-      <c r="N514" s="4" t="s">
+      <c r="N515" s="4" t="s">
         <v>4127</v>
       </c>
-      <c r="O514" s="4" t="s">
+      <c r="O515" s="4" t="s">
         <v>4128</v>
       </c>
-      <c r="P514" s="4"/>
-      <c r="Q514" s="4"/>
-      <c r="R514" s="4"/>
-      <c r="S514" s="4"/>
-      <c r="T514" s="4"/>
-      <c r="U514" s="4" t="s">
+      <c r="P515" s="4"/>
+      <c r="Q515" s="4"/>
+      <c r="R515" s="4"/>
+      <c r="S515" s="4"/>
+      <c r="T515" s="4"/>
+      <c r="U515" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="V514" s="4" t="s">
+      <c r="V515" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W514" s="4" t="s">
+      <c r="W515" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X514" s="4" t="s">
+      <c r="X515" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y514" s="4"/>
-    </row>
-    <row r="515" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A515" s="2" t="s">
+      <c r="Y515" s="4"/>
+    </row>
+    <row r="516" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A516" s="2" t="s">
         <v>4129</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="B516" s="2" t="s">
         <v>4130</v>
       </c>
-      <c r="C515" s="2" t="s">
+      <c r="C516" s="2" t="s">
         <v>4131</v>
       </c>
-      <c r="D515" s="2"/>
-      <c r="E515" s="2"/>
-      <c r="F515" s="2" t="s">
+      <c r="D516" s="2"/>
+      <c r="E516" s="2"/>
+      <c r="F516" s="2" t="s">
         <v>4132</v>
       </c>
-      <c r="G515" s="2" t="s">
+      <c r="G516" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H515" s="2" t="s">
+      <c r="H516" s="2" t="s">
         <v>4133</v>
       </c>
-      <c r="I515" s="2" t="s">
+      <c r="I516" s="2" t="s">
         <v>4114</v>
       </c>
-      <c r="J515" s="2" t="s">
+      <c r="J516" s="2" t="s">
         <v>4134</v>
       </c>
-      <c r="K515" s="2" t="s">
+      <c r="K516" s="2" t="s">
         <v>3126</v>
       </c>
-      <c r="L515" s="3">
+      <c r="L516" s="3">
         <v>31.09</v>
       </c>
-      <c r="M515" s="3">
+      <c r="M516" s="3">
         <v>1.34</v>
       </c>
-      <c r="N515" s="2" t="s">
+      <c r="N516" s="2" t="s">
         <v>4135</v>
       </c>
-      <c r="O515" s="2" t="s">
+      <c r="O516" s="2" t="s">
         <v>4136</v>
       </c>
-      <c r="P515" s="2"/>
-      <c r="Q515" s="2"/>
-      <c r="R515" s="2"/>
-      <c r="S515" s="2"/>
-      <c r="T515" s="2" t="s">
+      <c r="P516" s="2"/>
+      <c r="Q516" s="2"/>
+      <c r="R516" s="2"/>
+      <c r="S516" s="2"/>
+      <c r="T516" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U515" s="2" t="s">
+      <c r="U516" s="2" t="s">
         <v>4137</v>
       </c>
-      <c r="V515" s="2" t="s">
+      <c r="V516" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W515" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X515" s="2" t="s">
+      <c r="W516" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X516" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y515" s="2"/>
-    </row>
-    <row r="516" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A516" s="4" t="s">
+      <c r="Y516" s="2"/>
+    </row>
+    <row r="517" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A517" s="4" t="s">
         <v>4073</v>
       </c>
-      <c r="B516" s="4" t="s">
+      <c r="B517" s="4" t="s">
         <v>4138</v>
       </c>
-      <c r="C516" s="4" t="s">
+      <c r="C517" s="4" t="s">
         <v>4139</v>
       </c>
-      <c r="D516" s="4" t="s">
+      <c r="D517" s="4" t="s">
         <v>3720</v>
       </c>
-      <c r="E516" s="4" t="s">
+      <c r="E517" s="4" t="s">
         <v>3720</v>
       </c>
-      <c r="F516" s="4" t="s">
+      <c r="F517" s="4" t="s">
         <v>4140</v>
       </c>
-      <c r="G516" s="4" t="s">
+      <c r="G517" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="H516" s="4" t="s">
+      <c r="H517" s="4" t="s">
         <v>4141</v>
       </c>
-      <c r="I516" s="4" t="s">
+      <c r="I517" s="4" t="s">
         <v>4061</v>
       </c>
-      <c r="J516" s="4" t="s">
+      <c r="J517" s="4" t="s">
         <v>4142</v>
       </c>
-      <c r="K516" s="4" t="s">
+      <c r="K517" s="4" t="s">
         <v>4143</v>
       </c>
-      <c r="L516" s="5">
+      <c r="L517" s="5">
         <v>51.44</v>
       </c>
-      <c r="M516" s="5">
+      <c r="M517" s="5">
         <v>20.93</v>
       </c>
-      <c r="N516" s="4" t="s">
+      <c r="N517" s="4" t="s">
         <v>4144</v>
       </c>
-      <c r="O516" s="4" t="s">
+      <c r="O517" s="4" t="s">
         <v>4145</v>
       </c>
-      <c r="P516" s="4"/>
-      <c r="Q516" s="4"/>
-      <c r="R516" s="4"/>
-      <c r="S516" s="4" t="s">
+      <c r="P517" s="4"/>
+      <c r="Q517" s="4"/>
+      <c r="R517" s="4"/>
+      <c r="S517" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="T516" s="4" t="s">
+      <c r="T517" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U516" s="4" t="s">
+      <c r="U517" s="4" t="s">
         <v>3046</v>
       </c>
-      <c r="V516" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W516" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X516" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y516" s="4"/>
-    </row>
-    <row r="517" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A517" s="2" t="s">
+      <c r="V517" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W517" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X517" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y517" s="4"/>
+    </row>
+    <row r="518" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A518" s="2" t="s">
         <v>4146</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="B518" s="2" t="s">
         <v>4147</v>
       </c>
-      <c r="C517" s="2" t="s">
+      <c r="C518" s="2" t="s">
         <v>4148</v>
       </c>
-      <c r="D517" s="2" t="s">
+      <c r="D518" s="2" t="s">
         <v>3501</v>
       </c>
-      <c r="E517" s="2" t="s">
+      <c r="E518" s="2" t="s">
         <v>3501</v>
       </c>
-      <c r="F517" s="2" t="s">
+      <c r="F518" s="2" t="s">
         <v>4149</v>
       </c>
-      <c r="G517" s="2" t="s">
+      <c r="G518" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H517" s="2" t="s">
+      <c r="H518" s="2" t="s">
         <v>4141</v>
       </c>
-      <c r="I517" s="2" t="s">
+      <c r="I518" s="2" t="s">
         <v>4073</v>
       </c>
-      <c r="J517" s="2" t="s">
+      <c r="J518" s="2" t="s">
         <v>4150</v>
       </c>
-      <c r="K517" s="2" t="s">
+      <c r="K518" s="2" t="s">
         <v>3739</v>
       </c>
-      <c r="L517" s="3">
+      <c r="L518" s="3">
         <v>25.15</v>
       </c>
-      <c r="M517" s="3">
+      <c r="M518" s="3">
         <v>1.26</v>
       </c>
-      <c r="N517" s="2" t="s">
+      <c r="N518" s="2" t="s">
         <v>4151</v>
       </c>
-      <c r="O517" s="2" t="s">
+      <c r="O518" s="2" t="s">
         <v>4152</v>
       </c>
-      <c r="P517" s="2"/>
-      <c r="Q517" s="2"/>
-      <c r="R517" s="2"/>
-      <c r="S517" s="2"/>
-      <c r="T517" s="2"/>
-      <c r="U517" s="2" t="s">
+      <c r="P518" s="2"/>
+      <c r="Q518" s="2"/>
+      <c r="R518" s="2"/>
+      <c r="S518" s="2"/>
+      <c r="T518" s="2"/>
+      <c r="U518" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="V517" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W517" s="2" t="s">
+      <c r="V518" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W518" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X517" s="2" t="s">
+      <c r="X518" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y517" s="2"/>
-    </row>
-    <row r="518" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A518" s="4" t="s">
+      <c r="Y518" s="2"/>
+    </row>
+    <row r="519" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A519" s="4" t="s">
         <v>4153</v>
       </c>
-      <c r="B518" s="4" t="s">
+      <c r="B519" s="4" t="s">
         <v>4154</v>
       </c>
-      <c r="C518" s="4" t="s">
+      <c r="C519" s="4" t="s">
         <v>4155</v>
       </c>
-      <c r="D518" s="4" t="s">
+      <c r="D519" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="E518" s="4" t="s">
+      <c r="E519" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="F518" s="4" t="s">
+      <c r="F519" s="4" t="s">
         <v>4156</v>
       </c>
-      <c r="G518" s="4" t="s">
+      <c r="G519" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H518" s="4" t="s">
+      <c r="H519" s="4" t="s">
         <v>4141</v>
       </c>
-      <c r="I518" s="4" t="s">
+      <c r="I519" s="4" t="s">
         <v>4068</v>
       </c>
-      <c r="J518" s="4" t="s">
+      <c r="J519" s="4" t="s">
         <v>4157</v>
       </c>
-      <c r="K518" s="4" t="s">
+      <c r="K519" s="4" t="s">
         <v>4158</v>
       </c>
-      <c r="L518" s="5">
+      <c r="L519" s="5">
         <v>27.56</v>
       </c>
-      <c r="M518" s="5">
+      <c r="M519" s="5">
         <v>0.08</v>
       </c>
-      <c r="N518" s="4" t="s">
+      <c r="N519" s="4" t="s">
         <v>4159</v>
       </c>
-      <c r="O518" s="4" t="s">
+      <c r="O519" s="4" t="s">
         <v>4160</v>
       </c>
-      <c r="P518" s="4"/>
-      <c r="Q518" s="4"/>
-      <c r="R518" s="4"/>
-      <c r="S518" s="4"/>
-      <c r="T518" s="4"/>
-      <c r="U518" s="4" t="s">
+      <c r="P519" s="4"/>
+      <c r="Q519" s="4"/>
+      <c r="R519" s="4"/>
+      <c r="S519" s="4"/>
+      <c r="T519" s="4"/>
+      <c r="U519" s="4" t="s">
         <v>3642</v>
       </c>
-      <c r="V518" s="4" t="s">
+      <c r="V519" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W518" s="4" t="s">
+      <c r="W519" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X518" s="4" t="s">
+      <c r="X519" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y518" s="4"/>
-    </row>
-    <row r="519" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A519" s="2" t="s">
+      <c r="Y519" s="4"/>
+    </row>
+    <row r="520" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A520" s="2" t="s">
         <v>4061</v>
       </c>
-      <c r="B519" s="2" t="s">
+      <c r="B520" s="2" t="s">
         <v>4161</v>
       </c>
-      <c r="C519" s="2" t="s">
+      <c r="C520" s="2" t="s">
         <v>4162</v>
       </c>
-      <c r="D519" s="2"/>
-      <c r="E519" s="2"/>
-      <c r="F519" s="2" t="s">
+      <c r="D520" s="2"/>
+      <c r="E520" s="2"/>
+      <c r="F520" s="2" t="s">
         <v>4163</v>
       </c>
-      <c r="G519" s="2" t="s">
+      <c r="G520" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="H519" s="2" t="s">
+      <c r="H520" s="2" t="s">
         <v>4141</v>
       </c>
-      <c r="I519" s="2" t="s">
+      <c r="I520" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="J519" s="2" t="s">
+      <c r="J520" s="2" t="s">
         <v>4164</v>
       </c>
-      <c r="K519" s="2" t="s">
+      <c r="K520" s="2" t="s">
         <v>4165</v>
       </c>
-      <c r="L519" s="3">
+      <c r="L520" s="3">
         <v>55.16</v>
       </c>
-      <c r="M519" s="3">
+      <c r="M520" s="3">
         <v>3.05</v>
       </c>
-      <c r="N519" s="2" t="s">
+      <c r="N520" s="2" t="s">
         <v>4166</v>
       </c>
-      <c r="O519" s="2" t="s">
+      <c r="O520" s="2" t="s">
         <v>4167</v>
       </c>
-      <c r="P519" s="2"/>
-      <c r="Q519" s="2"/>
-      <c r="R519" s="2"/>
-      <c r="S519" s="2"/>
-      <c r="T519" s="2"/>
-      <c r="U519" s="2" t="s">
+      <c r="P520" s="2"/>
+      <c r="Q520" s="2"/>
+      <c r="R520" s="2"/>
+      <c r="S520" s="2"/>
+      <c r="T520" s="2"/>
+      <c r="U520" s="2" t="s">
         <v>3788</v>
       </c>
-      <c r="V519" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W519" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X519" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y519" s="6" t="s">
+      <c r="V520" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W520" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X520" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y520" s="6" t="s">
         <v>4061</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A520" s="4" t="s">
+    <row r="521" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A521" s="4" t="s">
         <v>4168</v>
       </c>
-      <c r="B520" s="4" t="s">
+      <c r="B521" s="4" t="s">
         <v>4169</v>
       </c>
-      <c r="C520" s="4" t="s">
+      <c r="C521" s="4" t="s">
         <v>4170</v>
       </c>
-      <c r="D520" s="4" t="s">
+      <c r="D521" s="4" t="s">
         <v>4171</v>
       </c>
-      <c r="E520" s="4" t="s">
+      <c r="E521" s="4" t="s">
         <v>4171</v>
       </c>
-      <c r="F520" s="4" t="s">
+      <c r="F521" s="4" t="s">
         <v>4172</v>
       </c>
-      <c r="G520" s="4" t="s">
+      <c r="G521" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H520" s="4" t="s">
+      <c r="H521" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I520" s="4" t="s">
+      <c r="I521" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J520" s="4" t="s">
+      <c r="J521" s="4" t="s">
         <v>4175</v>
       </c>
-      <c r="K520" s="4" t="s">
+      <c r="K521" s="4" t="s">
         <v>1029</v>
       </c>
-      <c r="L520" s="5">
+      <c r="L521" s="5">
         <v>53.47</v>
       </c>
-      <c r="M520" s="5">
+      <c r="M521" s="5">
         <v>34.590000000000003</v>
       </c>
-      <c r="N520" s="4" t="s">
+      <c r="N521" s="4" t="s">
         <v>4176</v>
       </c>
-      <c r="O520" s="4" t="s">
+      <c r="O521" s="4" t="s">
         <v>4177</v>
       </c>
-      <c r="P520" s="4"/>
-      <c r="Q520" s="4"/>
-      <c r="R520" s="4"/>
-      <c r="S520" s="4" t="s">
+      <c r="P521" s="4"/>
+      <c r="Q521" s="4"/>
+      <c r="R521" s="4"/>
+      <c r="S521" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="T520" s="4"/>
-      <c r="U520" s="4" t="s">
+      <c r="T521" s="4"/>
+      <c r="U521" s="4" t="s">
         <v>4178</v>
       </c>
-      <c r="V520" s="4" t="s">
+      <c r="V521" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="W520" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X520" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y520" s="4"/>
-    </row>
-    <row r="521" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A521" s="2" t="s">
+      <c r="W521" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X521" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y521" s="4"/>
+    </row>
+    <row r="522" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A522" s="2" t="s">
         <v>4179</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="B522" s="2" t="s">
         <v>4180</v>
       </c>
-      <c r="C521" s="2" t="s">
+      <c r="C522" s="2" t="s">
         <v>4181</v>
       </c>
-      <c r="D521" s="2" t="s">
+      <c r="D522" s="2" t="s">
         <v>4182</v>
       </c>
-      <c r="E521" s="2" t="s">
+      <c r="E522" s="2" t="s">
         <v>4182</v>
       </c>
-      <c r="F521" s="2" t="s">
+      <c r="F522" s="2" t="s">
         <v>4183</v>
       </c>
-      <c r="G521" s="2" t="s">
+      <c r="G522" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H521" s="2" t="s">
+      <c r="H522" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I521" s="2" t="s">
+      <c r="I522" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J521" s="2" t="s">
+      <c r="J522" s="2" t="s">
         <v>4184</v>
       </c>
-      <c r="K521" s="2" t="s">
+      <c r="K522" s="2" t="s">
         <v>3244</v>
       </c>
-      <c r="L521" s="3">
+      <c r="L522" s="3">
         <v>39.229999999999997</v>
       </c>
-      <c r="M521" s="3">
+      <c r="M522" s="3">
         <v>15.06</v>
       </c>
-      <c r="N521" s="2" t="s">
+      <c r="N522" s="2" t="s">
         <v>4185</v>
       </c>
-      <c r="O521" s="2"/>
-      <c r="P521" s="2"/>
-      <c r="Q521" s="2"/>
-      <c r="R521" s="2"/>
-      <c r="S521" s="2"/>
-      <c r="T521" s="2" t="s">
+      <c r="O522" s="2"/>
+      <c r="P522" s="2"/>
+      <c r="Q522" s="2"/>
+      <c r="R522" s="2"/>
+      <c r="S522" s="2"/>
+      <c r="T522" s="2" t="s">
         <v>2161</v>
       </c>
-      <c r="U521" s="2" t="s">
+      <c r="U522" s="2" t="s">
         <v>2559</v>
       </c>
-      <c r="V521" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W521" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X521" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y521" s="2"/>
-    </row>
-    <row r="522" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A522" s="4" t="s">
+      <c r="V522" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W522" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X522" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y522" s="2"/>
+    </row>
+    <row r="523" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A523" s="4" t="s">
         <v>4186</v>
       </c>
-      <c r="B522" s="4" t="s">
+      <c r="B523" s="4" t="s">
         <v>4187</v>
       </c>
-      <c r="C522" s="4" t="s">
+      <c r="C523" s="4" t="s">
         <v>4188</v>
       </c>
-      <c r="D522" s="4" t="s">
+      <c r="D523" s="4" t="s">
         <v>2721</v>
       </c>
-      <c r="E522" s="4" t="s">
+      <c r="E523" s="4" t="s">
         <v>2721</v>
       </c>
-      <c r="F522" s="4" t="s">
+      <c r="F523" s="4" t="s">
         <v>4189</v>
       </c>
-      <c r="G522" s="4" t="s">
+      <c r="G523" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H522" s="4" t="s">
+      <c r="H523" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I522" s="4" t="s">
+      <c r="I523" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J522" s="4" t="s">
+      <c r="J523" s="4" t="s">
         <v>4190</v>
       </c>
-      <c r="K522" s="4" t="s">
+      <c r="K523" s="4" t="s">
         <v>1612</v>
       </c>
-      <c r="L522" s="5">
+      <c r="L523" s="5">
         <v>27.55</v>
       </c>
-      <c r="M522" s="5">
+      <c r="M523" s="5">
         <v>5.17</v>
       </c>
-      <c r="N522" s="4" t="s">
+      <c r="N523" s="4" t="s">
         <v>4191</v>
       </c>
-      <c r="O522" s="4"/>
-      <c r="P522" s="4"/>
-      <c r="Q522" s="4"/>
-      <c r="R522" s="4"/>
-      <c r="S522" s="4"/>
-      <c r="T522" s="4" t="s">
+      <c r="O523" s="4"/>
+      <c r="P523" s="4"/>
+      <c r="Q523" s="4"/>
+      <c r="R523" s="4"/>
+      <c r="S523" s="4"/>
+      <c r="T523" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="U522" s="4" t="s">
+      <c r="U523" s="4" t="s">
         <v>3927</v>
       </c>
-      <c r="V522" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W522" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X522" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y522" s="4"/>
-    </row>
-    <row r="523" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A523" s="2" t="s">
+      <c r="V523" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W523" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X523" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y523" s="4"/>
+    </row>
+    <row r="524" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A524" s="2" t="s">
         <v>4192</v>
       </c>
-      <c r="B523" s="2" t="s">
+      <c r="B524" s="2" t="s">
         <v>4193</v>
       </c>
-      <c r="C523" s="2" t="s">
+      <c r="C524" s="2" t="s">
         <v>4194</v>
       </c>
-      <c r="D523" s="2" t="s">
+      <c r="D524" s="2" t="s">
         <v>1808</v>
       </c>
-      <c r="E523" s="2" t="s">
+      <c r="E524" s="2" t="s">
         <v>1808</v>
       </c>
-      <c r="F523" s="2" t="s">
+      <c r="F524" s="2" t="s">
         <v>4189</v>
       </c>
-      <c r="G523" s="2" t="s">
+      <c r="G524" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H523" s="2" t="s">
+      <c r="H524" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I523" s="2" t="s">
+      <c r="I524" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J523" s="2" t="s">
+      <c r="J524" s="2" t="s">
         <v>2714</v>
       </c>
-      <c r="K523" s="2" t="s">
+      <c r="K524" s="2" t="s">
         <v>2143</v>
       </c>
-      <c r="L523" s="3">
+      <c r="L524" s="3">
         <v>29.28</v>
       </c>
-      <c r="M523" s="3">
+      <c r="M524" s="3">
         <v>4.96</v>
       </c>
-      <c r="N523" s="2" t="s">
+      <c r="N524" s="2" t="s">
         <v>4195</v>
       </c>
-      <c r="O523" s="2"/>
-      <c r="P523" s="2"/>
-      <c r="Q523" s="2"/>
-      <c r="R523" s="2"/>
-      <c r="S523" s="2"/>
-      <c r="T523" s="2"/>
-      <c r="U523" s="2" t="s">
+      <c r="O524" s="2"/>
+      <c r="P524" s="2"/>
+      <c r="Q524" s="2"/>
+      <c r="R524" s="2"/>
+      <c r="S524" s="2"/>
+      <c r="T524" s="2"/>
+      <c r="U524" s="2" t="s">
         <v>2938</v>
       </c>
-      <c r="V523" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W523" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X523" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y523" s="2"/>
-    </row>
-    <row r="524" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A524" s="4" t="s">
+      <c r="V524" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W524" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X524" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y524" s="2"/>
+    </row>
+    <row r="525" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A525" s="4" t="s">
         <v>4196</v>
       </c>
-      <c r="B524" s="4" t="s">
+      <c r="B525" s="4" t="s">
         <v>4197</v>
       </c>
-      <c r="C524" s="4" t="s">
+      <c r="C525" s="4" t="s">
         <v>4198</v>
       </c>
-      <c r="D524" s="4" t="s">
+      <c r="D525" s="4" t="s">
         <v>4199</v>
       </c>
-      <c r="E524" s="4" t="s">
+      <c r="E525" s="4" t="s">
         <v>4199</v>
       </c>
-      <c r="F524" s="4" t="s">
+      <c r="F525" s="4" t="s">
         <v>4200</v>
       </c>
-      <c r="G524" s="4" t="s">
+      <c r="G525" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H524" s="4" t="s">
+      <c r="H525" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I524" s="4" t="s">
+      <c r="I525" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J524" s="4" t="s">
+      <c r="J525" s="4" t="s">
         <v>4201</v>
       </c>
-      <c r="K524" s="4" t="s">
+      <c r="K525" s="4" t="s">
         <v>2715</v>
       </c>
-      <c r="L524" s="5">
+      <c r="L525" s="5">
         <v>35.21</v>
       </c>
-      <c r="M524" s="5">
+      <c r="M525" s="5">
         <v>4.9400000000000004</v>
       </c>
-      <c r="N524" s="4" t="s">
+      <c r="N525" s="4" t="s">
         <v>4202</v>
       </c>
-      <c r="O524" s="4"/>
-      <c r="P524" s="4"/>
-      <c r="Q524" s="4"/>
-      <c r="R524" s="4"/>
-      <c r="S524" s="4"/>
-      <c r="T524" s="4" t="s">
+      <c r="O525" s="4"/>
+      <c r="P525" s="4"/>
+      <c r="Q525" s="4"/>
+      <c r="R525" s="4"/>
+      <c r="S525" s="4"/>
+      <c r="T525" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U524" s="4" t="s">
+      <c r="U525" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="V524" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W524" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X524" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y524" s="4"/>
-    </row>
-    <row r="525" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A525" s="2" t="s">
+      <c r="V525" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W525" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X525" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y525" s="4"/>
+    </row>
+    <row r="526" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A526" s="2" t="s">
         <v>4203</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="B526" s="2" t="s">
         <v>4204</v>
       </c>
-      <c r="C525" s="2" t="s">
+      <c r="C526" s="2" t="s">
         <v>4205</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="D526" s="2" t="s">
         <v>4206</v>
       </c>
-      <c r="E525" s="2" t="s">
+      <c r="E526" s="2" t="s">
         <v>4206</v>
       </c>
-      <c r="F525" s="2" t="s">
+      <c r="F526" s="2" t="s">
         <v>4189</v>
       </c>
-      <c r="G525" s="2" t="s">
+      <c r="G526" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H525" s="2" t="s">
+      <c r="H526" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I525" s="2" t="s">
+      <c r="I526" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J525" s="2" t="s">
+      <c r="J526" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="K525" s="2" t="s">
+      <c r="K526" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="L525" s="3">
+      <c r="L526" s="3">
         <v>26.59</v>
       </c>
-      <c r="M525" s="3">
+      <c r="M526" s="3">
         <v>4.93</v>
       </c>
-      <c r="N525" s="2" t="s">
+      <c r="N526" s="2" t="s">
         <v>4207</v>
       </c>
-      <c r="O525" s="2"/>
-      <c r="P525" s="2"/>
-      <c r="Q525" s="2"/>
-      <c r="R525" s="2"/>
-      <c r="S525" s="2"/>
-      <c r="T525" s="2"/>
-      <c r="U525" s="2" t="s">
+      <c r="O526" s="2"/>
+      <c r="P526" s="2"/>
+      <c r="Q526" s="2"/>
+      <c r="R526" s="2"/>
+      <c r="S526" s="2"/>
+      <c r="T526" s="2"/>
+      <c r="U526" s="2" t="s">
         <v>4208</v>
       </c>
-      <c r="V525" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W525" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X525" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y525" s="2"/>
-    </row>
-    <row r="526" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A526" s="4" t="s">
+      <c r="V526" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W526" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X526" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y526" s="2"/>
+    </row>
+    <row r="527" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A527" s="4" t="s">
         <v>4209</v>
       </c>
-      <c r="B526" s="4" t="s">
+      <c r="B527" s="4" t="s">
         <v>4210</v>
       </c>
-      <c r="C526" s="4" t="s">
+      <c r="C527" s="4" t="s">
         <v>4211</v>
       </c>
-      <c r="D526" s="4" t="s">
+      <c r="D527" s="4" t="s">
         <v>2131</v>
       </c>
-      <c r="E526" s="4" t="s">
+      <c r="E527" s="4" t="s">
         <v>2131</v>
       </c>
-      <c r="F526" s="4" t="s">
+      <c r="F527" s="4" t="s">
         <v>4189</v>
       </c>
-      <c r="G526" s="4" t="s">
+      <c r="G527" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H526" s="4" t="s">
+      <c r="H527" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I526" s="4" t="s">
+      <c r="I527" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J526" s="4" t="s">
+      <c r="J527" s="4" t="s">
         <v>4212</v>
       </c>
-      <c r="K526" s="4" t="s">
+      <c r="K527" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="L526" s="5">
+      <c r="L527" s="5">
         <v>29.97</v>
       </c>
-      <c r="M526" s="5">
+      <c r="M527" s="5">
         <v>4.76</v>
       </c>
-      <c r="N526" s="4" t="s">
+      <c r="N527" s="4" t="s">
         <v>4213</v>
       </c>
-      <c r="O526" s="4"/>
-      <c r="P526" s="4"/>
-      <c r="Q526" s="4"/>
-      <c r="R526" s="4"/>
-      <c r="S526" s="4"/>
-      <c r="T526" s="4"/>
-      <c r="U526" s="4" t="s">
+      <c r="O527" s="4"/>
+      <c r="P527" s="4"/>
+      <c r="Q527" s="4"/>
+      <c r="R527" s="4"/>
+      <c r="S527" s="4"/>
+      <c r="T527" s="4"/>
+      <c r="U527" s="4" t="s">
         <v>2784</v>
       </c>
-      <c r="V526" s="4" t="s">
+      <c r="V527" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="W526" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X526" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y526" s="4"/>
-    </row>
-    <row r="527" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A527" s="2" t="s">
+      <c r="W527" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X527" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y527" s="4"/>
+    </row>
+    <row r="528" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A528" s="2" t="s">
         <v>4214</v>
       </c>
-      <c r="B527" s="2" t="s">
+      <c r="B528" s="2" t="s">
         <v>4215</v>
       </c>
-      <c r="C527" s="2" t="s">
+      <c r="C528" s="2" t="s">
         <v>4216</v>
       </c>
-      <c r="D527" s="2" t="s">
+      <c r="D528" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E527" s="2" t="s">
+      <c r="E528" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F527" s="2" t="s">
+      <c r="F528" s="2" t="s">
         <v>4189</v>
       </c>
-      <c r="G527" s="2" t="s">
+      <c r="G528" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H527" s="2" t="s">
+      <c r="H528" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I527" s="2" t="s">
+      <c r="I528" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J527" s="2" t="s">
+      <c r="J528" s="2" t="s">
         <v>4217</v>
       </c>
-      <c r="K527" s="2" t="s">
+      <c r="K528" s="2" t="s">
         <v>1902</v>
       </c>
-      <c r="L527" s="3">
+      <c r="L528" s="3">
         <v>29.03</v>
       </c>
-      <c r="M527" s="3">
+      <c r="M528" s="3">
         <v>4.0599999999999996</v>
       </c>
-      <c r="N527" s="2" t="s">
+      <c r="N528" s="2" t="s">
         <v>4218</v>
       </c>
-      <c r="O527" s="2"/>
-      <c r="P527" s="2"/>
-      <c r="Q527" s="2"/>
-      <c r="R527" s="2"/>
-      <c r="S527" s="2"/>
-      <c r="T527" s="2"/>
-      <c r="U527" s="2" t="s">
+      <c r="O528" s="2"/>
+      <c r="P528" s="2"/>
+      <c r="Q528" s="2"/>
+      <c r="R528" s="2"/>
+      <c r="S528" s="2"/>
+      <c r="T528" s="2"/>
+      <c r="U528" s="2" t="s">
         <v>1889</v>
       </c>
-      <c r="V527" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W527" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X527" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y527" s="2"/>
-    </row>
-    <row r="528" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A528" s="4" t="s">
+      <c r="V528" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W528" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X528" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y528" s="2"/>
+    </row>
+    <row r="529" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A529" s="4" t="s">
         <v>4219</v>
       </c>
-      <c r="B528" s="4" t="s">
+      <c r="B529" s="4" t="s">
         <v>4220</v>
       </c>
-      <c r="C528" s="4" t="s">
+      <c r="C529" s="4" t="s">
         <v>4221</v>
       </c>
-      <c r="D528" s="4" t="s">
+      <c r="D529" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="E528" s="4" t="s">
+      <c r="E529" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="F528" s="4" t="s">
+      <c r="F529" s="4" t="s">
         <v>4222</v>
       </c>
-      <c r="G528" s="4" t="s">
+      <c r="G529" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H528" s="4" t="s">
+      <c r="H529" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I528" s="4" t="s">
+      <c r="I529" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J528" s="4" t="s">
+      <c r="J529" s="4" t="s">
         <v>4223</v>
       </c>
-      <c r="K528" s="4" t="s">
+      <c r="K529" s="4" t="s">
         <v>2674</v>
       </c>
-      <c r="L528" s="5">
+      <c r="L529" s="5">
         <v>31.35</v>
       </c>
-      <c r="M528" s="5">
+      <c r="M529" s="5">
         <v>3.47</v>
       </c>
-      <c r="N528" s="4" t="s">
+      <c r="N529" s="4" t="s">
         <v>4224</v>
       </c>
-      <c r="O528" s="4" t="s">
+      <c r="O529" s="4" t="s">
         <v>4225</v>
       </c>
-      <c r="P528" s="4"/>
-      <c r="Q528" s="4"/>
-      <c r="R528" s="4"/>
-      <c r="S528" s="4"/>
-      <c r="T528" s="4"/>
-      <c r="U528" s="4" t="s">
+      <c r="P529" s="4"/>
+      <c r="Q529" s="4"/>
+      <c r="R529" s="4"/>
+      <c r="S529" s="4"/>
+      <c r="T529" s="4"/>
+      <c r="U529" s="4" t="s">
         <v>3927</v>
       </c>
-      <c r="V528" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W528" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X528" s="4" t="s">
+      <c r="V529" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W529" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X529" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y528" s="4"/>
-    </row>
-    <row r="529" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A529" s="2" t="s">
+      <c r="Y529" s="4"/>
+    </row>
+    <row r="530" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A530" s="2" t="s">
         <v>4226</v>
       </c>
-      <c r="B529" s="2" t="s">
+      <c r="B530" s="2" t="s">
         <v>4227</v>
       </c>
-      <c r="C529" s="2" t="s">
+      <c r="C530" s="2" t="s">
         <v>4228</v>
       </c>
-      <c r="D529" s="2" t="s">
+      <c r="D530" s="2" t="s">
         <v>4229</v>
       </c>
-      <c r="E529" s="2" t="s">
+      <c r="E530" s="2" t="s">
         <v>4229</v>
       </c>
-      <c r="F529" s="2" t="s">
+      <c r="F530" s="2" t="s">
         <v>4222</v>
       </c>
-      <c r="G529" s="2" t="s">
+      <c r="G530" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H529" s="2" t="s">
+      <c r="H530" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I529" s="2" t="s">
+      <c r="I530" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J529" s="2" t="s">
+      <c r="J530" s="2" t="s">
         <v>4230</v>
       </c>
-      <c r="K529" s="2" t="s">
+      <c r="K530" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L529" s="3">
+      <c r="L530" s="3">
         <v>43.99</v>
       </c>
-      <c r="M529" s="3">
+      <c r="M530" s="3">
         <v>3.26</v>
       </c>
-      <c r="N529" s="2" t="s">
+      <c r="N530" s="2" t="s">
         <v>4231</v>
       </c>
-      <c r="O529" s="2" t="s">
+      <c r="O530" s="2" t="s">
         <v>4232</v>
       </c>
-      <c r="P529" s="2"/>
-      <c r="Q529" s="2"/>
-      <c r="R529" s="2"/>
-      <c r="S529" s="2"/>
-      <c r="T529" s="2" t="s">
+      <c r="P530" s="2"/>
+      <c r="Q530" s="2"/>
+      <c r="R530" s="2"/>
+      <c r="S530" s="2"/>
+      <c r="T530" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U529" s="2" t="s">
+      <c r="U530" s="2" t="s">
         <v>4233</v>
       </c>
-      <c r="V529" s="2" t="s">
+      <c r="V530" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W529" s="2" t="s">
+      <c r="W530" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="X529" s="2" t="s">
+      <c r="X530" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y529" s="2"/>
-    </row>
-    <row r="530" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A530" s="4" t="s">
+      <c r="Y530" s="2"/>
+    </row>
+    <row r="531" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A531" s="4" t="s">
         <v>4234</v>
       </c>
-      <c r="B530" s="4" t="s">
+      <c r="B531" s="4" t="s">
         <v>4235</v>
       </c>
-      <c r="C530" s="4" t="s">
+      <c r="C531" s="4" t="s">
         <v>4236</v>
       </c>
-      <c r="D530" s="4" t="s">
+      <c r="D531" s="4" t="s">
         <v>4237</v>
       </c>
-      <c r="E530" s="4" t="s">
+      <c r="E531" s="4" t="s">
         <v>4237</v>
       </c>
-      <c r="F530" s="4" t="s">
+      <c r="F531" s="4" t="s">
         <v>4189</v>
       </c>
-      <c r="G530" s="4" t="s">
+      <c r="G531" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H530" s="4" t="s">
+      <c r="H531" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I530" s="4" t="s">
+      <c r="I531" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J530" s="4" t="s">
+      <c r="J531" s="4" t="s">
         <v>4238</v>
       </c>
-      <c r="K530" s="4" t="s">
+      <c r="K531" s="4" t="s">
         <v>1409</v>
       </c>
-      <c r="L530" s="5">
+      <c r="L531" s="5">
         <v>25.81</v>
       </c>
-      <c r="M530" s="5">
+      <c r="M531" s="5">
         <v>2.2599999999999998</v>
       </c>
-      <c r="N530" s="4" t="s">
+      <c r="N531" s="4" t="s">
         <v>4239</v>
       </c>
-      <c r="O530" s="4" t="s">
+      <c r="O531" s="4" t="s">
         <v>4240</v>
       </c>
-      <c r="P530" s="4"/>
-      <c r="Q530" s="4"/>
-      <c r="R530" s="4"/>
-      <c r="S530" s="4"/>
-      <c r="T530" s="4"/>
-      <c r="U530" s="4" t="s">
+      <c r="P531" s="4"/>
+      <c r="Q531" s="4"/>
+      <c r="R531" s="4"/>
+      <c r="S531" s="4"/>
+      <c r="T531" s="4"/>
+      <c r="U531" s="4" t="s">
         <v>3065</v>
       </c>
-      <c r="V530" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W530" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X530" s="4" t="s">
+      <c r="V531" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W531" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X531" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y530" s="4"/>
-    </row>
-    <row r="531" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A531" s="2" t="s">
+      <c r="Y531" s="4"/>
+    </row>
+    <row r="532" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A532" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="B531" s="2" t="s">
+      <c r="B532" s="2" t="s">
         <v>4241</v>
       </c>
-      <c r="C531" s="2" t="s">
+      <c r="C532" s="2" t="s">
         <v>4242</v>
       </c>
-      <c r="D531" s="2" t="s">
+      <c r="D532" s="2" t="s">
         <v>4243</v>
       </c>
-      <c r="E531" s="2" t="s">
+      <c r="E532" s="2" t="s">
         <v>4243</v>
       </c>
-      <c r="F531" s="2" t="s">
+      <c r="F532" s="2" t="s">
         <v>4244</v>
       </c>
-      <c r="G531" s="2" t="s">
+      <c r="G532" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H531" s="2" t="s">
+      <c r="H532" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I531" s="2" t="s">
+      <c r="I532" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="J531" s="2" t="s">
+      <c r="J532" s="2" t="s">
         <v>4246</v>
       </c>
-      <c r="K531" s="2" t="s">
+      <c r="K532" s="2" t="s">
         <v>1941</v>
       </c>
-      <c r="L531" s="3">
+      <c r="L532" s="3">
         <v>47.62</v>
       </c>
-      <c r="M531" s="3">
+      <c r="M532" s="3">
         <v>1.72</v>
       </c>
-      <c r="N531" s="2" t="s">
+      <c r="N532" s="2" t="s">
         <v>4247</v>
       </c>
-      <c r="O531" s="2" t="s">
+      <c r="O532" s="2" t="s">
         <v>4248</v>
       </c>
-      <c r="P531" s="2"/>
-      <c r="Q531" s="2"/>
-      <c r="R531" s="2"/>
-      <c r="S531" s="2"/>
-      <c r="T531" s="2"/>
-      <c r="U531" s="2" t="s">
+      <c r="P532" s="2"/>
+      <c r="Q532" s="2"/>
+      <c r="R532" s="2"/>
+      <c r="S532" s="2"/>
+      <c r="T532" s="2"/>
+      <c r="U532" s="2" t="s">
         <v>4249</v>
       </c>
-      <c r="V531" s="2" t="s">
+      <c r="V532" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="W531" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X531" s="2" t="s">
+      <c r="W532" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X532" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y531" s="2"/>
-    </row>
-    <row r="532" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A532" s="4" t="s">
+      <c r="Y532" s="2"/>
+    </row>
+    <row r="533" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A533" s="4" t="s">
         <v>4250</v>
       </c>
-      <c r="B532" s="4" t="s">
+      <c r="B533" s="4" t="s">
         <v>4251</v>
       </c>
-      <c r="C532" s="4" t="s">
+      <c r="C533" s="4" t="s">
         <v>4252</v>
       </c>
-      <c r="D532" s="4" t="s">
+      <c r="D533" s="4" t="s">
         <v>4253</v>
       </c>
-      <c r="E532" s="4" t="s">
+      <c r="E533" s="4" t="s">
         <v>4253</v>
       </c>
-      <c r="F532" s="4" t="s">
+      <c r="F533" s="4" t="s">
         <v>4183</v>
       </c>
-      <c r="G532" s="4" t="s">
+      <c r="G533" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H532" s="4" t="s">
+      <c r="H533" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I532" s="4" t="s">
+      <c r="I533" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J532" s="4" t="s">
+      <c r="J533" s="4" t="s">
         <v>4254</v>
       </c>
-      <c r="K532" s="4" t="s">
+      <c r="K533" s="4" t="s">
         <v>1949</v>
       </c>
-      <c r="L532" s="5">
+      <c r="L533" s="5">
         <v>27.38</v>
       </c>
-      <c r="M532" s="5">
+      <c r="M533" s="5">
         <v>1.64</v>
       </c>
-      <c r="N532" s="4" t="s">
+      <c r="N533" s="4" t="s">
         <v>4255</v>
       </c>
-      <c r="O532" s="4" t="s">
+      <c r="O533" s="4" t="s">
         <v>4256</v>
       </c>
-      <c r="P532" s="4"/>
-      <c r="Q532" s="4"/>
-      <c r="R532" s="4"/>
-      <c r="S532" s="4"/>
-      <c r="T532" s="4"/>
-      <c r="U532" s="4" t="s">
+      <c r="P533" s="4"/>
+      <c r="Q533" s="4"/>
+      <c r="R533" s="4"/>
+      <c r="S533" s="4"/>
+      <c r="T533" s="4"/>
+      <c r="U533" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="V532" s="4" t="s">
+      <c r="V533" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="W532" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X532" s="4" t="s">
+      <c r="W533" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X533" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y532" s="4"/>
-    </row>
-    <row r="533" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A533" s="2" t="s">
+      <c r="Y533" s="4"/>
+    </row>
+    <row r="534" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A534" s="2" t="s">
         <v>4257</v>
       </c>
-      <c r="B533" s="2" t="s">
+      <c r="B534" s="2" t="s">
         <v>4258</v>
       </c>
-      <c r="C533" s="2" t="s">
+      <c r="C534" s="2" t="s">
         <v>4259</v>
       </c>
-      <c r="D533" s="2" t="s">
+      <c r="D534" s="2" t="s">
         <v>4260</v>
       </c>
-      <c r="E533" s="2" t="s">
+      <c r="E534" s="2" t="s">
         <v>4260</v>
       </c>
-      <c r="F533" s="2" t="s">
+      <c r="F534" s="2" t="s">
         <v>4222</v>
       </c>
-      <c r="G533" s="2" t="s">
+      <c r="G534" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H533" s="2" t="s">
+      <c r="H534" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I533" s="2" t="s">
+      <c r="I534" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J533" s="2" t="s">
+      <c r="J534" s="2" t="s">
         <v>4261</v>
       </c>
-      <c r="K533" s="2" t="s">
+      <c r="K534" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="L533" s="3">
+      <c r="L534" s="3">
         <v>34.200000000000003</v>
       </c>
-      <c r="M533" s="3">
+      <c r="M534" s="3">
         <v>1.59</v>
       </c>
-      <c r="N533" s="2" t="s">
+      <c r="N534" s="2" t="s">
         <v>4262</v>
       </c>
-      <c r="O533" s="2"/>
-      <c r="P533" s="2"/>
-      <c r="Q533" s="2"/>
-      <c r="R533" s="2"/>
-      <c r="S533" s="2"/>
-      <c r="T533" s="2"/>
-      <c r="U533" s="2" t="s">
+      <c r="O534" s="2"/>
+      <c r="P534" s="2"/>
+      <c r="Q534" s="2"/>
+      <c r="R534" s="2"/>
+      <c r="S534" s="2"/>
+      <c r="T534" s="2"/>
+      <c r="U534" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="V533" s="2" t="s">
+      <c r="V534" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W533" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X533" s="2" t="s">
+      <c r="W534" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X534" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y533" s="2"/>
-    </row>
-    <row r="534" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A534" s="4" t="s">
+      <c r="Y534" s="2"/>
+    </row>
+    <row r="535" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A535" s="4" t="s">
         <v>4263</v>
       </c>
-      <c r="B534" s="4" t="s">
+      <c r="B535" s="4" t="s">
         <v>4264</v>
       </c>
-      <c r="C534" s="4" t="s">
+      <c r="C535" s="4" t="s">
         <v>4265</v>
       </c>
-      <c r="D534" s="4" t="s">
+      <c r="D535" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="E534" s="4" t="s">
+      <c r="E535" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="F534" s="4" t="s">
+      <c r="F535" s="4" t="s">
         <v>4222</v>
       </c>
-      <c r="G534" s="4" t="s">
+      <c r="G535" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H534" s="4" t="s">
+      <c r="H535" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I534" s="4" t="s">
+      <c r="I535" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J534" s="4" t="s">
+      <c r="J535" s="4" t="s">
         <v>4266</v>
       </c>
-      <c r="K534" s="4" t="s">
+      <c r="K535" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="L534" s="5">
+      <c r="L535" s="5">
         <v>42.17</v>
       </c>
-      <c r="M534" s="5">
+      <c r="M535" s="5">
         <v>1.59</v>
       </c>
-      <c r="N534" s="4" t="s">
+      <c r="N535" s="4" t="s">
         <v>4267</v>
       </c>
-      <c r="O534" s="4"/>
-      <c r="P534" s="4"/>
-      <c r="Q534" s="4"/>
-      <c r="R534" s="4"/>
-      <c r="S534" s="4"/>
-      <c r="T534" s="4"/>
-      <c r="U534" s="4" t="s">
+      <c r="O535" s="4"/>
+      <c r="P535" s="4"/>
+      <c r="Q535" s="4"/>
+      <c r="R535" s="4"/>
+      <c r="S535" s="4"/>
+      <c r="T535" s="4"/>
+      <c r="U535" s="4" t="s">
         <v>3642</v>
       </c>
-      <c r="V534" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W534" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X534" s="4" t="s">
+      <c r="V535" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W535" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X535" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y534" s="4"/>
-    </row>
-    <row r="535" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A535" s="2" t="s">
+      <c r="Y535" s="4"/>
+    </row>
+    <row r="536" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A536" s="2" t="s">
         <v>4268</v>
       </c>
-      <c r="B535" s="2" t="s">
+      <c r="B536" s="2" t="s">
         <v>4269</v>
       </c>
-      <c r="C535" s="2" t="s">
+      <c r="C536" s="2" t="s">
         <v>4270</v>
       </c>
-      <c r="D535" s="2" t="s">
+      <c r="D536" s="2" t="s">
         <v>4271</v>
       </c>
-      <c r="E535" s="2" t="s">
+      <c r="E536" s="2" t="s">
         <v>4271</v>
       </c>
-      <c r="F535" s="2" t="s">
+      <c r="F536" s="2" t="s">
         <v>4222</v>
       </c>
-      <c r="G535" s="2" t="s">
+      <c r="G536" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H535" s="2" t="s">
+      <c r="H536" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I535" s="2" t="s">
+      <c r="I536" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J535" s="2" t="s">
+      <c r="J536" s="2" t="s">
         <v>4272</v>
       </c>
-      <c r="K535" s="2" t="s">
+      <c r="K536" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="L535" s="3">
+      <c r="L536" s="3">
         <v>23.26</v>
       </c>
-      <c r="M535" s="3">
+      <c r="M536" s="3">
         <v>1.22</v>
       </c>
-      <c r="N535" s="2" t="s">
+      <c r="N536" s="2" t="s">
         <v>4273</v>
       </c>
-      <c r="O535" s="2"/>
-      <c r="P535" s="2"/>
-      <c r="Q535" s="2"/>
-      <c r="R535" s="2"/>
-      <c r="S535" s="2"/>
-      <c r="T535" s="2"/>
-      <c r="U535" s="2" t="s">
+      <c r="O536" s="2"/>
+      <c r="P536" s="2"/>
+      <c r="Q536" s="2"/>
+      <c r="R536" s="2"/>
+      <c r="S536" s="2"/>
+      <c r="T536" s="2"/>
+      <c r="U536" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="V535" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W535" s="2" t="s">
+      <c r="V536" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W536" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X535" s="2" t="s">
+      <c r="X536" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y535" s="2"/>
-    </row>
-    <row r="536" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A536" s="4" t="s">
+      <c r="Y536" s="2"/>
+    </row>
+    <row r="537" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A537" s="4" t="s">
         <v>4274</v>
       </c>
-      <c r="B536" s="4" t="s">
+      <c r="B537" s="4" t="s">
         <v>4275</v>
       </c>
-      <c r="C536" s="4" t="s">
+      <c r="C537" s="4" t="s">
         <v>4276</v>
       </c>
-      <c r="D536" s="4" t="s">
+      <c r="D537" s="4" t="s">
         <v>4277</v>
       </c>
-      <c r="E536" s="4" t="s">
+      <c r="E537" s="4" t="s">
         <v>4277</v>
       </c>
-      <c r="F536" s="4" t="s">
+      <c r="F537" s="4" t="s">
         <v>4189</v>
       </c>
-      <c r="G536" s="4" t="s">
+      <c r="G537" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H536" s="4" t="s">
+      <c r="H537" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I536" s="4" t="s">
+      <c r="I537" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J536" s="4" t="s">
+      <c r="J537" s="4" t="s">
         <v>4278</v>
       </c>
-      <c r="K536" s="4" t="s">
+      <c r="K537" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="L536" s="5">
+      <c r="L537" s="5">
         <v>28.36</v>
       </c>
-      <c r="M536" s="5">
+      <c r="M537" s="5">
         <v>1.22</v>
       </c>
-      <c r="N536" s="4" t="s">
+      <c r="N537" s="4" t="s">
         <v>4279</v>
       </c>
-      <c r="O536" s="4"/>
-      <c r="P536" s="4"/>
-      <c r="Q536" s="4"/>
-      <c r="R536" s="4"/>
-      <c r="S536" s="4"/>
-      <c r="T536" s="4"/>
-      <c r="U536" s="4" t="s">
+      <c r="O537" s="4"/>
+      <c r="P537" s="4"/>
+      <c r="Q537" s="4"/>
+      <c r="R537" s="4"/>
+      <c r="S537" s="4"/>
+      <c r="T537" s="4"/>
+      <c r="U537" s="4" t="s">
         <v>4280</v>
       </c>
-      <c r="V536" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W536" s="4" t="s">
+      <c r="V537" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W537" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X536" s="4" t="s">
+      <c r="X537" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y536" s="4"/>
-    </row>
-    <row r="537" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A537" s="2" t="s">
+      <c r="Y537" s="4"/>
+    </row>
+    <row r="538" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A538" s="2" t="s">
         <v>4281</v>
       </c>
-      <c r="B537" s="2" t="s">
+      <c r="B538" s="2" t="s">
         <v>4282</v>
       </c>
-      <c r="C537" s="2" t="s">
+      <c r="C538" s="2" t="s">
         <v>4283</v>
       </c>
-      <c r="D537" s="2" t="s">
+      <c r="D538" s="2" t="s">
         <v>2324</v>
       </c>
-      <c r="E537" s="2" t="s">
+      <c r="E538" s="2" t="s">
         <v>2324</v>
       </c>
-      <c r="F537" s="2" t="s">
+      <c r="F538" s="2" t="s">
         <v>4284</v>
       </c>
-      <c r="G537" s="2" t="s">
+      <c r="G538" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H537" s="2" t="s">
+      <c r="H538" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I537" s="2" t="s">
+      <c r="I538" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J537" s="2" t="s">
+      <c r="J538" s="2" t="s">
         <v>4285</v>
       </c>
-      <c r="K537" s="2" t="s">
+      <c r="K538" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="L537" s="3">
+      <c r="L538" s="3">
         <v>23.68</v>
       </c>
-      <c r="M537" s="3">
+      <c r="M538" s="3">
         <v>0.76</v>
       </c>
-      <c r="N537" s="2" t="s">
+      <c r="N538" s="2" t="s">
         <v>4286</v>
       </c>
-      <c r="O537" s="2" t="s">
+      <c r="O538" s="2" t="s">
         <v>4287</v>
       </c>
-      <c r="P537" s="2"/>
-      <c r="Q537" s="2"/>
-      <c r="R537" s="2"/>
-      <c r="S537" s="2"/>
-      <c r="T537" s="2"/>
-      <c r="U537" s="2" t="s">
+      <c r="P538" s="2"/>
+      <c r="Q538" s="2"/>
+      <c r="R538" s="2"/>
+      <c r="S538" s="2"/>
+      <c r="T538" s="2"/>
+      <c r="U538" s="2" t="s">
         <v>1985</v>
       </c>
-      <c r="V537" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W537" s="2" t="s">
+      <c r="V538" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W538" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X537" s="2" t="s">
+      <c r="X538" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y537" s="2"/>
-    </row>
-    <row r="538" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A538" s="4" t="s">
+      <c r="Y538" s="2"/>
+    </row>
+    <row r="539" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A539" s="4" t="s">
         <v>4288</v>
       </c>
-      <c r="B538" s="4" t="s">
+      <c r="B539" s="4" t="s">
         <v>4289</v>
       </c>
-      <c r="C538" s="4" t="s">
+      <c r="C539" s="4" t="s">
         <v>4290</v>
       </c>
-      <c r="D538" s="4" t="s">
+      <c r="D539" s="4" t="s">
         <v>4291</v>
       </c>
-      <c r="E538" s="4" t="s">
+      <c r="E539" s="4" t="s">
         <v>4291</v>
       </c>
-      <c r="F538" s="4" t="s">
+      <c r="F539" s="4" t="s">
         <v>4183</v>
       </c>
-      <c r="G538" s="4" t="s">
+      <c r="G539" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H538" s="4" t="s">
+      <c r="H539" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I538" s="4" t="s">
+      <c r="I539" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J538" s="4" t="s">
+      <c r="J539" s="4" t="s">
         <v>4292</v>
       </c>
-      <c r="K538" s="4" t="s">
+      <c r="K539" s="4" t="s">
         <v>2420</v>
       </c>
-      <c r="L538" s="5">
+      <c r="L539" s="5">
         <v>26.94</v>
       </c>
-      <c r="M538" s="5">
+      <c r="M539" s="5">
         <v>0.68</v>
       </c>
-      <c r="N538" s="4" t="s">
+      <c r="N539" s="4" t="s">
         <v>4293</v>
       </c>
-      <c r="O538" s="4" t="s">
+      <c r="O539" s="4" t="s">
         <v>4294</v>
       </c>
-      <c r="P538" s="4"/>
-      <c r="Q538" s="4"/>
-      <c r="R538" s="4"/>
-      <c r="S538" s="4"/>
-      <c r="T538" s="4"/>
-      <c r="U538" s="4" t="s">
+      <c r="P539" s="4"/>
+      <c r="Q539" s="4"/>
+      <c r="R539" s="4"/>
+      <c r="S539" s="4"/>
+      <c r="T539" s="4"/>
+      <c r="U539" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="V538" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W538" s="4" t="s">
+      <c r="V539" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W539" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X538" s="4" t="s">
+      <c r="X539" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y538" s="4"/>
-    </row>
-    <row r="539" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A539" s="2" t="s">
+      <c r="Y539" s="4"/>
+    </row>
+    <row r="540" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A540" s="2" t="s">
         <v>4295</v>
       </c>
-      <c r="B539" s="2" t="s">
+      <c r="B540" s="2" t="s">
         <v>4296</v>
       </c>
-      <c r="C539" s="2" t="s">
+      <c r="C540" s="2" t="s">
         <v>4297</v>
       </c>
-      <c r="D539" s="2" t="s">
+      <c r="D540" s="2" t="s">
         <v>4298</v>
       </c>
-      <c r="E539" s="2" t="s">
+      <c r="E540" s="2" t="s">
         <v>4298</v>
       </c>
-      <c r="F539" s="2" t="s">
+      <c r="F540" s="2" t="s">
         <v>4299</v>
       </c>
-      <c r="G539" s="2" t="s">
+      <c r="G540" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H539" s="2" t="s">
+      <c r="H540" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I539" s="2" t="s">
+      <c r="I540" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J539" s="2" t="s">
+      <c r="J540" s="2" t="s">
         <v>4300</v>
       </c>
-      <c r="K539" s="2" t="s">
+      <c r="K540" s="2" t="s">
         <v>2420</v>
       </c>
-      <c r="L539" s="3">
+      <c r="L540" s="3">
         <v>42.02</v>
       </c>
-      <c r="M539" s="3">
+      <c r="M540" s="3">
         <v>0.68</v>
       </c>
-      <c r="N539" s="2" t="s">
+      <c r="N540" s="2" t="s">
         <v>4301</v>
       </c>
-      <c r="O539" s="2"/>
-      <c r="P539" s="2"/>
-      <c r="Q539" s="2"/>
-      <c r="R539" s="2"/>
-      <c r="S539" s="2"/>
-      <c r="T539" s="2"/>
-      <c r="U539" s="2" t="s">
+      <c r="O540" s="2"/>
+      <c r="P540" s="2"/>
+      <c r="Q540" s="2"/>
+      <c r="R540" s="2"/>
+      <c r="S540" s="2"/>
+      <c r="T540" s="2"/>
+      <c r="U540" s="2" t="s">
         <v>4302</v>
       </c>
-      <c r="V539" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W539" s="2" t="s">
+      <c r="V540" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W540" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X539" s="2" t="s">
+      <c r="X540" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y539" s="2"/>
-    </row>
-    <row r="540" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A540" s="4" t="s">
+      <c r="Y540" s="2"/>
+    </row>
+    <row r="541" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A541" s="4" t="s">
         <v>4303</v>
       </c>
-      <c r="B540" s="4" t="s">
+      <c r="B541" s="4" t="s">
         <v>4304</v>
       </c>
-      <c r="C540" s="4" t="s">
+      <c r="C541" s="4" t="s">
         <v>4305</v>
       </c>
-      <c r="D540" s="4" t="s">
+      <c r="D541" s="4" t="s">
         <v>4306</v>
       </c>
-      <c r="E540" s="4" t="s">
+      <c r="E541" s="4" t="s">
         <v>4306</v>
       </c>
-      <c r="F540" s="4" t="s">
+      <c r="F541" s="4" t="s">
         <v>4299</v>
       </c>
-      <c r="G540" s="4" t="s">
+      <c r="G541" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H540" s="4" t="s">
+      <c r="H541" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I540" s="4" t="s">
+      <c r="I541" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J540" s="4" t="s">
+      <c r="J541" s="4" t="s">
         <v>4307</v>
       </c>
-      <c r="K540" s="4" t="s">
+      <c r="K541" s="4" t="s">
         <v>2420</v>
       </c>
-      <c r="L540" s="5">
+      <c r="L541" s="5">
         <v>37.33</v>
       </c>
-      <c r="M540" s="5">
+      <c r="M541" s="5">
         <v>0.68</v>
       </c>
-      <c r="N540" s="4" t="s">
+      <c r="N541" s="4" t="s">
         <v>4308</v>
       </c>
-      <c r="O540" s="4"/>
-      <c r="P540" s="4"/>
-      <c r="Q540" s="4"/>
-      <c r="R540" s="4"/>
-      <c r="S540" s="4"/>
-      <c r="T540" s="4"/>
-      <c r="U540" s="4" t="s">
+      <c r="O541" s="4"/>
+      <c r="P541" s="4"/>
+      <c r="Q541" s="4"/>
+      <c r="R541" s="4"/>
+      <c r="S541" s="4"/>
+      <c r="T541" s="4"/>
+      <c r="U541" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="V540" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W540" s="4" t="s">
+      <c r="V541" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W541" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X540" s="4" t="s">
+      <c r="X541" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y540" s="4"/>
-    </row>
-    <row r="541" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A541" s="2" t="s">
+      <c r="Y541" s="4"/>
+    </row>
+    <row r="542" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A542" s="2" t="s">
         <v>4309</v>
       </c>
-      <c r="B541" s="2" t="s">
+      <c r="B542" s="2" t="s">
         <v>4310</v>
       </c>
-      <c r="C541" s="2" t="s">
+      <c r="C542" s="2" t="s">
         <v>4311</v>
       </c>
-      <c r="D541" s="2" t="s">
+      <c r="D542" s="2" t="s">
         <v>3858</v>
       </c>
-      <c r="E541" s="2" t="s">
+      <c r="E542" s="2" t="s">
         <v>3858</v>
       </c>
-      <c r="F541" s="2" t="s">
+      <c r="F542" s="2" t="s">
         <v>4299</v>
       </c>
-      <c r="G541" s="2" t="s">
+      <c r="G542" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H541" s="2" t="s">
+      <c r="H542" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I541" s="2" t="s">
+      <c r="I542" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J541" s="2" t="s">
+      <c r="J542" s="2" t="s">
         <v>4312</v>
       </c>
-      <c r="K541" s="2" t="s">
+      <c r="K542" s="2" t="s">
         <v>2420</v>
       </c>
-      <c r="L541" s="3">
+      <c r="L542" s="3">
         <v>46.1</v>
       </c>
-      <c r="M541" s="3">
+      <c r="M542" s="3">
         <v>0.68</v>
       </c>
-      <c r="N541" s="2" t="s">
+      <c r="N542" s="2" t="s">
         <v>4313</v>
       </c>
-      <c r="O541" s="2"/>
-      <c r="P541" s="2"/>
-      <c r="Q541" s="2"/>
-      <c r="R541" s="2"/>
-      <c r="S541" s="2"/>
-      <c r="T541" s="2"/>
-      <c r="U541" s="2" t="s">
+      <c r="O542" s="2"/>
+      <c r="P542" s="2"/>
+      <c r="Q542" s="2"/>
+      <c r="R542" s="2"/>
+      <c r="S542" s="2"/>
+      <c r="T542" s="2"/>
+      <c r="U542" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="V541" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W541" s="2" t="s">
+      <c r="V542" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W542" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X541" s="2" t="s">
+      <c r="X542" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y541" s="2"/>
-    </row>
-    <row r="542" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A542" s="4" t="s">
+      <c r="Y542" s="2"/>
+    </row>
+    <row r="543" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A543" s="4" t="s">
         <v>4314</v>
       </c>
-      <c r="B542" s="4" t="s">
+      <c r="B543" s="4" t="s">
         <v>4315</v>
       </c>
-      <c r="C542" s="4" t="s">
+      <c r="C543" s="4" t="s">
         <v>4316</v>
       </c>
-      <c r="D542" s="4" t="s">
+      <c r="D543" s="4" t="s">
         <v>4317</v>
       </c>
-      <c r="E542" s="4" t="s">
+      <c r="E543" s="4" t="s">
         <v>4317</v>
       </c>
-      <c r="F542" s="4" t="s">
+      <c r="F543" s="4" t="s">
         <v>4189</v>
       </c>
-      <c r="G542" s="4" t="s">
+      <c r="G543" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H542" s="4" t="s">
+      <c r="H543" s="4" t="s">
         <v>4173</v>
       </c>
-      <c r="I542" s="4" t="s">
+      <c r="I543" s="4" t="s">
         <v>4174</v>
       </c>
-      <c r="J542" s="4" t="s">
+      <c r="J543" s="4" t="s">
         <v>4318</v>
       </c>
-      <c r="K542" s="4" t="s">
+      <c r="K543" s="4" t="s">
         <v>1730</v>
       </c>
-      <c r="L542" s="5">
+      <c r="L543" s="5">
         <v>21.9</v>
       </c>
-      <c r="M542" s="5">
+      <c r="M543" s="5">
         <v>0.42</v>
       </c>
-      <c r="N542" s="4" t="s">
+      <c r="N543" s="4" t="s">
         <v>4319</v>
       </c>
-      <c r="O542" s="4"/>
-      <c r="P542" s="4"/>
-      <c r="Q542" s="4"/>
-      <c r="R542" s="4"/>
-      <c r="S542" s="4"/>
-      <c r="T542" s="4"/>
-      <c r="U542" s="4" t="s">
+      <c r="O543" s="4"/>
+      <c r="P543" s="4"/>
+      <c r="Q543" s="4"/>
+      <c r="R543" s="4"/>
+      <c r="S543" s="4"/>
+      <c r="T543" s="4"/>
+      <c r="U543" s="4" t="s">
         <v>1317</v>
       </c>
-      <c r="V542" s="4" t="s">
+      <c r="V543" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W542" s="4" t="s">
+      <c r="W543" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X542" s="4" t="s">
+      <c r="X543" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y542" s="4"/>
-    </row>
-    <row r="543" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A543" s="2" t="s">
+      <c r="Y543" s="4"/>
+    </row>
+    <row r="544" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A544" s="2" t="s">
         <v>4320</v>
       </c>
-      <c r="B543" s="2" t="s">
+      <c r="B544" s="2" t="s">
         <v>4321</v>
       </c>
-      <c r="C543" s="2" t="s">
+      <c r="C544" s="2" t="s">
         <v>4322</v>
       </c>
-      <c r="D543" s="2" t="s">
+      <c r="D544" s="2" t="s">
         <v>4323</v>
       </c>
-      <c r="E543" s="2" t="s">
+      <c r="E544" s="2" t="s">
         <v>4323</v>
       </c>
-      <c r="F543" s="2" t="s">
+      <c r="F544" s="2" t="s">
         <v>4284</v>
       </c>
-      <c r="G543" s="2" t="s">
+      <c r="G544" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H543" s="2" t="s">
+      <c r="H544" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="I543" s="2" t="s">
+      <c r="I544" s="2" t="s">
         <v>4174</v>
       </c>
-      <c r="J543" s="2" t="s">
+      <c r="J544" s="2" t="s">
         <v>4285</v>
       </c>
-      <c r="K543" s="2" t="s">
+      <c r="K544" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="L543" s="3">
+      <c r="L544" s="3">
         <v>23.68</v>
       </c>
-      <c r="M543" s="3">
+      <c r="M544" s="3">
         <v>0.01</v>
       </c>
-      <c r="N543" s="2" t="s">
+      <c r="N544" s="2" t="s">
         <v>4324</v>
       </c>
-      <c r="O543" s="2" t="s">
+      <c r="O544" s="2" t="s">
         <v>4325</v>
       </c>
-      <c r="P543" s="2"/>
-      <c r="Q543" s="2"/>
-      <c r="R543" s="2"/>
-      <c r="S543" s="2"/>
-      <c r="T543" s="2"/>
-      <c r="U543" s="2" t="s">
+      <c r="P544" s="2"/>
+      <c r="Q544" s="2"/>
+      <c r="R544" s="2"/>
+      <c r="S544" s="2"/>
+      <c r="T544" s="2"/>
+      <c r="U544" s="2" t="s">
         <v>1985</v>
       </c>
-      <c r="V543" s="2" t="s">
+      <c r="V544" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="W543" s="2" t="s">
+      <c r="W544" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X543" s="2" t="s">
+      <c r="X544" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y543" s="2"/>
-    </row>
-    <row r="544" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A544" s="4" t="s">
+      <c r="Y544" s="2"/>
+    </row>
+    <row r="545" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A545" s="4" t="s">
         <v>4326</v>
       </c>
-      <c r="B544" s="4" t="s">
+      <c r="B545" s="4" t="s">
         <v>4327</v>
       </c>
-      <c r="C544" s="4" t="s">
+      <c r="C545" s="4" t="s">
         <v>4328</v>
       </c>
-      <c r="D544" s="4" t="s">
+      <c r="D545" s="4" t="s">
         <v>3869</v>
       </c>
-      <c r="E544" s="4" t="s">
+      <c r="E545" s="4" t="s">
         <v>3869</v>
       </c>
-      <c r="F544" s="4" t="s">
+      <c r="F545" s="4" t="s">
         <v>4329</v>
       </c>
-      <c r="G544" s="4" t="s">
+      <c r="G545" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H544" s="4" t="s">
+      <c r="H545" s="4" t="s">
         <v>4330</v>
       </c>
-      <c r="I544" s="4" t="s">
+      <c r="I545" s="4" t="s">
         <v>4245</v>
       </c>
-      <c r="J544" s="4" t="s">
+      <c r="J545" s="4" t="s">
         <v>4331</v>
       </c>
-      <c r="K544" s="4" t="s">
+      <c r="K545" s="4" t="s">
         <v>4332</v>
       </c>
-      <c r="L544" s="5">
+      <c r="L545" s="5">
         <v>53.51</v>
       </c>
-      <c r="M544" s="5">
+      <c r="M545" s="5">
         <v>34.090000000000003</v>
       </c>
-      <c r="N544" s="4" t="s">
+      <c r="N545" s="4" t="s">
         <v>4333</v>
       </c>
-      <c r="O544" s="4" t="s">
+      <c r="O545" s="4" t="s">
         <v>4334</v>
       </c>
-      <c r="P544" s="4"/>
-      <c r="Q544" s="4"/>
-      <c r="R544" s="4"/>
-      <c r="S544" s="4" t="s">
+      <c r="P545" s="4"/>
+      <c r="Q545" s="4"/>
+      <c r="R545" s="4"/>
+      <c r="S545" s="4" t="s">
         <v>2504</v>
       </c>
-      <c r="T544" s="4"/>
-      <c r="U544" s="4" t="s">
+      <c r="T545" s="4"/>
+      <c r="U545" s="4" t="s">
         <v>4335</v>
       </c>
-      <c r="V544" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W544" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X544" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y544" s="4"/>
-    </row>
-    <row r="545" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A545" s="2" t="s">
+      <c r="V545" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W545" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X545" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y545" s="4"/>
+    </row>
+    <row r="546" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A546" s="2" t="s">
         <v>4336</v>
       </c>
-      <c r="B545" s="2" t="s">
+      <c r="B546" s="2" t="s">
         <v>4337</v>
       </c>
-      <c r="C545" s="2" t="s">
+      <c r="C546" s="2" t="s">
         <v>4338</v>
       </c>
-      <c r="D545" s="2" t="s">
+      <c r="D546" s="2" t="s">
         <v>4339</v>
       </c>
-      <c r="E545" s="2" t="s">
+      <c r="E546" s="2" t="s">
         <v>4339</v>
       </c>
-      <c r="F545" s="2" t="s">
+      <c r="F546" s="2" t="s">
         <v>4329</v>
       </c>
-      <c r="G545" s="2" t="s">
+      <c r="G546" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H545" s="2" t="s">
+      <c r="H546" s="2" t="s">
         <v>4330</v>
       </c>
-      <c r="I545" s="2" t="s">
+      <c r="I546" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="J545" s="2" t="s">
+      <c r="J546" s="2" t="s">
         <v>4340</v>
       </c>
-      <c r="K545" s="2" t="s">
+      <c r="K546" s="2" t="s">
         <v>4341</v>
       </c>
-      <c r="L545" s="3">
+      <c r="L546" s="3">
         <v>41.25</v>
       </c>
-      <c r="M545" s="3">
+      <c r="M546" s="3">
         <v>15.83</v>
       </c>
-      <c r="N545" s="2" t="s">
+      <c r="N546" s="2" t="s">
         <v>4342</v>
       </c>
-      <c r="O545" s="2" t="s">
+      <c r="O546" s="2" t="s">
         <v>4343</v>
       </c>
-      <c r="P545" s="2"/>
-      <c r="Q545" s="2"/>
-      <c r="R545" s="2"/>
-      <c r="S545" s="2"/>
-      <c r="T545" s="2"/>
-      <c r="U545" s="2" t="s">
+      <c r="P546" s="2"/>
+      <c r="Q546" s="2"/>
+      <c r="R546" s="2"/>
+      <c r="S546" s="2"/>
+      <c r="T546" s="2"/>
+      <c r="U546" s="2" t="s">
         <v>4344</v>
       </c>
-      <c r="V545" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W545" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X545" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y545" s="2"/>
-    </row>
-    <row r="546" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A546" s="4" t="s">
+      <c r="V546" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W546" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X546" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y546" s="2"/>
+    </row>
+    <row r="547" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A547" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="B546" s="4" t="s">
+      <c r="B547" s="4" t="s">
         <v>4346</v>
       </c>
-      <c r="C546" s="4" t="s">
+      <c r="C547" s="4" t="s">
         <v>4347</v>
       </c>
-      <c r="D546" s="4" t="s">
+      <c r="D547" s="4" t="s">
         <v>4348</v>
       </c>
-      <c r="E546" s="4" t="s">
+      <c r="E547" s="4" t="s">
         <v>4348</v>
       </c>
-      <c r="F546" s="4" t="s">
+      <c r="F547" s="4" t="s">
         <v>4349</v>
       </c>
-      <c r="G546" s="4" t="s">
+      <c r="G547" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H546" s="4" t="s">
+      <c r="H547" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I546" s="4" t="s">
+      <c r="I547" s="4" t="s">
         <v>4245</v>
       </c>
-      <c r="J546" s="4" t="s">
+      <c r="J547" s="4" t="s">
         <v>4351</v>
       </c>
-      <c r="K546" s="4" t="s">
+      <c r="K547" s="4" t="s">
         <v>1453</v>
       </c>
-      <c r="L546" s="5">
+      <c r="L547" s="5">
         <v>44.5</v>
       </c>
-      <c r="M546" s="5">
+      <c r="M547" s="5">
         <v>18.600000000000001</v>
       </c>
-      <c r="N546" s="4" t="s">
+      <c r="N547" s="4" t="s">
         <v>4352</v>
       </c>
-      <c r="O546" s="4" t="s">
+      <c r="O547" s="4" t="s">
         <v>4353</v>
       </c>
-      <c r="P546" s="4"/>
-      <c r="Q546" s="4"/>
-      <c r="R546" s="4"/>
-      <c r="S546" s="4" t="s">
+      <c r="P547" s="4"/>
+      <c r="Q547" s="4"/>
+      <c r="R547" s="4"/>
+      <c r="S547" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="T546" s="4" t="s">
+      <c r="T547" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="U546" s="4" t="s">
+      <c r="U547" s="4" t="s">
         <v>4354</v>
       </c>
-      <c r="V546" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W546" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X546" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y546" s="4"/>
-    </row>
-    <row r="547" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A547" s="2" t="s">
+      <c r="V547" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W547" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X547" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y547" s="4"/>
+    </row>
+    <row r="548" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A548" s="2" t="s">
         <v>4355</v>
       </c>
-      <c r="B547" s="2" t="s">
+      <c r="B548" s="2" t="s">
         <v>4356</v>
       </c>
-      <c r="C547" s="2" t="s">
+      <c r="C548" s="2" t="s">
         <v>4357</v>
       </c>
-      <c r="D547" s="2" t="s">
+      <c r="D548" s="2" t="s">
         <v>3249</v>
       </c>
-      <c r="E547" s="2" t="s">
+      <c r="E548" s="2" t="s">
         <v>3249</v>
       </c>
-      <c r="F547" s="2" t="s">
+      <c r="F548" s="2" t="s">
         <v>4358</v>
       </c>
-      <c r="G547" s="2" t="s">
+      <c r="G548" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H547" s="2" t="s">
+      <c r="H548" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I547" s="2" t="s">
+      <c r="I548" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J547" s="2" t="s">
+      <c r="J548" s="2" t="s">
         <v>4359</v>
       </c>
-      <c r="K547" s="2" t="s">
+      <c r="K548" s="2" t="s">
         <v>4360</v>
       </c>
-      <c r="L547" s="3">
+      <c r="L548" s="3">
         <v>45.04</v>
       </c>
-      <c r="M547" s="3">
+      <c r="M548" s="3">
         <v>15.18</v>
       </c>
-      <c r="N547" s="2" t="s">
+      <c r="N548" s="2" t="s">
         <v>4361</v>
       </c>
-      <c r="O547" s="2"/>
-      <c r="P547" s="2"/>
-      <c r="Q547" s="2"/>
-      <c r="R547" s="2"/>
-      <c r="S547" s="2"/>
-      <c r="T547" s="2"/>
-      <c r="U547" s="2" t="s">
+      <c r="O548" s="2"/>
+      <c r="P548" s="2"/>
+      <c r="Q548" s="2"/>
+      <c r="R548" s="2"/>
+      <c r="S548" s="2"/>
+      <c r="T548" s="2"/>
+      <c r="U548" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="V547" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W547" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X547" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y547" s="2"/>
-    </row>
-    <row r="548" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A548" s="4" t="s">
+      <c r="V548" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W548" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X548" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y548" s="2"/>
+    </row>
+    <row r="549" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A549" s="4" t="s">
         <v>4362</v>
       </c>
-      <c r="B548" s="4" t="s">
+      <c r="B549" s="4" t="s">
         <v>4363</v>
       </c>
-      <c r="C548" s="4" t="s">
+      <c r="C549" s="4" t="s">
         <v>4364</v>
       </c>
-      <c r="D548" s="4" t="s">
+      <c r="D549" s="4" t="s">
         <v>4365</v>
       </c>
-      <c r="E548" s="4" t="s">
+      <c r="E549" s="4" t="s">
         <v>4365</v>
       </c>
-      <c r="F548" s="4" t="s">
+      <c r="F549" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G548" s="4" t="s">
+      <c r="G549" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H548" s="4" t="s">
+      <c r="H549" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I548" s="4" t="s">
+      <c r="I549" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J548" s="4" t="s">
+      <c r="J549" s="4" t="s">
         <v>4367</v>
       </c>
-      <c r="K548" s="4" t="s">
+      <c r="K549" s="4" t="s">
         <v>1597</v>
       </c>
-      <c r="L548" s="5">
+      <c r="L549" s="5">
         <v>47.06</v>
       </c>
-      <c r="M548" s="5">
+      <c r="M549" s="5">
         <v>14.81</v>
       </c>
-      <c r="N548" s="4" t="s">
+      <c r="N549" s="4" t="s">
         <v>4368</v>
       </c>
-      <c r="O548" s="4"/>
-      <c r="P548" s="4"/>
-      <c r="Q548" s="4"/>
-      <c r="R548" s="4"/>
-      <c r="S548" s="4"/>
-      <c r="T548" s="4"/>
-      <c r="U548" s="4" t="s">
+      <c r="O549" s="4"/>
+      <c r="P549" s="4"/>
+      <c r="Q549" s="4"/>
+      <c r="R549" s="4"/>
+      <c r="S549" s="4"/>
+      <c r="T549" s="4"/>
+      <c r="U549" s="4" t="s">
         <v>2074</v>
       </c>
-      <c r="V548" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W548" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X548" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y548" s="4"/>
-    </row>
-    <row r="549" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A549" s="2" t="s">
+      <c r="V549" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W549" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X549" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y549" s="4"/>
+    </row>
+    <row r="550" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A550" s="2" t="s">
         <v>4369</v>
       </c>
-      <c r="B549" s="2" t="s">
+      <c r="B550" s="2" t="s">
         <v>4370</v>
       </c>
-      <c r="C549" s="2" t="s">
+      <c r="C550" s="2" t="s">
         <v>4371</v>
       </c>
-      <c r="D549" s="2"/>
-      <c r="E549" s="2"/>
-      <c r="F549" s="2" t="s">
+      <c r="D550" s="2"/>
+      <c r="E550" s="2"/>
+      <c r="F550" s="2" t="s">
         <v>4358</v>
       </c>
-      <c r="G549" s="2" t="s">
+      <c r="G550" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H549" s="2" t="s">
+      <c r="H550" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I549" s="2" t="s">
+      <c r="I550" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J549" s="2" t="s">
+      <c r="J550" s="2" t="s">
         <v>4372</v>
       </c>
-      <c r="K549" s="2" t="s">
+      <c r="K550" s="2" t="s">
         <v>2262</v>
       </c>
-      <c r="L549" s="3">
+      <c r="L550" s="3">
         <v>50.9</v>
       </c>
-      <c r="M549" s="3">
+      <c r="M550" s="3">
         <v>14.26</v>
       </c>
-      <c r="N549" s="2" t="s">
+      <c r="N550" s="2" t="s">
         <v>4373</v>
       </c>
-      <c r="O549" s="2"/>
-      <c r="P549" s="2"/>
-      <c r="Q549" s="2"/>
-      <c r="R549" s="2"/>
-      <c r="S549" s="2" t="s">
+      <c r="O550" s="2"/>
+      <c r="P550" s="2"/>
+      <c r="Q550" s="2"/>
+      <c r="R550" s="2"/>
+      <c r="S550" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="T549" s="2" t="s">
+      <c r="T550" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="U549" s="2" t="s">
+      <c r="U550" s="2" t="s">
         <v>4374</v>
       </c>
-      <c r="V549" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W549" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X549" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y549" s="2"/>
-    </row>
-    <row r="550" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A550" s="4" t="s">
+      <c r="V550" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W550" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X550" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y550" s="2"/>
+    </row>
+    <row r="551" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A551" s="4" t="s">
         <v>4375</v>
       </c>
-      <c r="B550" s="4" t="s">
+      <c r="B551" s="4" t="s">
         <v>4376</v>
       </c>
-      <c r="C550" s="4" t="s">
+      <c r="C551" s="4" t="s">
         <v>4377</v>
       </c>
-      <c r="D550" s="4" t="s">
+      <c r="D551" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E550" s="4" t="s">
+      <c r="E551" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F550" s="4" t="s">
+      <c r="F551" s="4" t="s">
         <v>4378</v>
       </c>
-      <c r="G550" s="4" t="s">
+      <c r="G551" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H550" s="4" t="s">
+      <c r="H551" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I550" s="4" t="s">
+      <c r="I551" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J550" s="4" t="s">
+      <c r="J551" s="4" t="s">
         <v>4379</v>
       </c>
-      <c r="K550" s="4" t="s">
+      <c r="K551" s="4" t="s">
         <v>4380</v>
       </c>
-      <c r="L550" s="5">
+      <c r="L551" s="5">
         <v>44.94</v>
       </c>
-      <c r="M550" s="5">
+      <c r="M551" s="5">
         <v>13.59</v>
       </c>
-      <c r="N550" s="4" t="s">
+      <c r="N551" s="4" t="s">
         <v>4381</v>
       </c>
-      <c r="O550" s="4" t="s">
+      <c r="O551" s="4" t="s">
         <v>4382</v>
       </c>
-      <c r="P550" s="4"/>
-      <c r="Q550" s="4"/>
-      <c r="R550" s="4"/>
-      <c r="S550" s="4" t="s">
+      <c r="P551" s="4"/>
+      <c r="Q551" s="4"/>
+      <c r="R551" s="4"/>
+      <c r="S551" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="T550" s="4"/>
-      <c r="U550" s="4" t="s">
+      <c r="T551" s="4"/>
+      <c r="U551" s="4" t="s">
         <v>4383</v>
       </c>
-      <c r="V550" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W550" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X550" s="4" t="s">
+      <c r="V551" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W551" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X551" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y550" s="4"/>
-    </row>
-    <row r="551" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A551" s="2" t="s">
+      <c r="Y551" s="4"/>
+    </row>
+    <row r="552" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A552" s="2" t="s">
         <v>4384</v>
       </c>
-      <c r="B551" s="2" t="s">
+      <c r="B552" s="2" t="s">
         <v>4385</v>
       </c>
-      <c r="C551" s="2" t="s">
+      <c r="C552" s="2" t="s">
         <v>4386</v>
       </c>
-      <c r="D551" s="2" t="s">
+      <c r="D552" s="2" t="s">
         <v>2094</v>
       </c>
-      <c r="E551" s="2" t="s">
+      <c r="E552" s="2" t="s">
         <v>2094</v>
       </c>
-      <c r="F551" s="2" t="s">
+      <c r="F552" s="2" t="s">
         <v>4358</v>
       </c>
-      <c r="G551" s="2" t="s">
+      <c r="G552" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H551" s="2" t="s">
+      <c r="H552" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I551" s="2" t="s">
+      <c r="I552" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J551" s="2" t="s">
+      <c r="J552" s="2" t="s">
         <v>4387</v>
       </c>
-      <c r="K551" s="2" t="s">
+      <c r="K552" s="2" t="s">
         <v>4388</v>
       </c>
-      <c r="L551" s="3">
+      <c r="L552" s="3">
         <v>37.82</v>
       </c>
-      <c r="M551" s="3">
+      <c r="M552" s="3">
         <v>12.05</v>
       </c>
-      <c r="N551" s="2" t="s">
+      <c r="N552" s="2" t="s">
         <v>4389</v>
       </c>
-      <c r="O551" s="2" t="s">
+      <c r="O552" s="2" t="s">
         <v>4390</v>
       </c>
-      <c r="P551" s="2"/>
-      <c r="Q551" s="2"/>
-      <c r="R551" s="2"/>
-      <c r="S551" s="2" t="s">
+      <c r="P552" s="2"/>
+      <c r="Q552" s="2"/>
+      <c r="R552" s="2"/>
+      <c r="S552" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T551" s="2"/>
-      <c r="U551" s="2" t="s">
+      <c r="T552" s="2"/>
+      <c r="U552" s="2" t="s">
         <v>2519</v>
       </c>
-      <c r="V551" s="2" t="s">
+      <c r="V552" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W551" s="2" t="s">
+      <c r="W552" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="X551" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y551" s="2"/>
-    </row>
-    <row r="552" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A552" s="4" t="s">
+      <c r="X552" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y552" s="2"/>
+    </row>
+    <row r="553" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A553" s="4" t="s">
         <v>4391</v>
       </c>
-      <c r="B552" s="4" t="s">
+      <c r="B553" s="4" t="s">
         <v>4392</v>
       </c>
-      <c r="C552" s="4" t="s">
+      <c r="C553" s="4" t="s">
         <v>4393</v>
       </c>
-      <c r="D552" s="4" t="s">
+      <c r="D553" s="4" t="s">
         <v>2823</v>
       </c>
-      <c r="E552" s="4" t="s">
+      <c r="E553" s="4" t="s">
         <v>2823</v>
       </c>
-      <c r="F552" s="4" t="s">
+      <c r="F553" s="4" t="s">
         <v>4358</v>
       </c>
-      <c r="G552" s="4" t="s">
+      <c r="G553" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H552" s="4" t="s">
+      <c r="H553" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I552" s="4" t="s">
+      <c r="I553" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J552" s="4" t="s">
+      <c r="J553" s="4" t="s">
         <v>4394</v>
       </c>
-      <c r="K552" s="4" t="s">
+      <c r="K553" s="4" t="s">
         <v>4395</v>
       </c>
-      <c r="L552" s="5">
+      <c r="L553" s="5">
         <v>34.69</v>
       </c>
-      <c r="M552" s="5">
+      <c r="M553" s="5">
         <v>11.81</v>
       </c>
-      <c r="N552" s="4" t="s">
+      <c r="N553" s="4" t="s">
         <v>4396</v>
       </c>
-      <c r="O552" s="4"/>
-      <c r="P552" s="4"/>
-      <c r="Q552" s="4"/>
-      <c r="R552" s="4"/>
-      <c r="S552" s="4" t="s">
+      <c r="O553" s="4"/>
+      <c r="P553" s="4"/>
+      <c r="Q553" s="4"/>
+      <c r="R553" s="4"/>
+      <c r="S553" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="T552" s="4"/>
-      <c r="U552" s="4" t="s">
+      <c r="T553" s="4"/>
+      <c r="U553" s="4" t="s">
         <v>999</v>
       </c>
-      <c r="V552" s="4" t="s">
+      <c r="V553" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="W552" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X552" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y552" s="4"/>
-    </row>
-    <row r="553" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A553" s="2" t="s">
+      <c r="W553" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X553" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y553" s="4"/>
+    </row>
+    <row r="554" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A554" s="2" t="s">
         <v>4397</v>
       </c>
-      <c r="B553" s="2" t="s">
+      <c r="B554" s="2" t="s">
         <v>4398</v>
       </c>
-      <c r="C553" s="2" t="s">
+      <c r="C554" s="2" t="s">
         <v>4399</v>
       </c>
-      <c r="D553" s="2" t="s">
+      <c r="D554" s="2" t="s">
         <v>2060</v>
       </c>
-      <c r="E553" s="2" t="s">
+      <c r="E554" s="2" t="s">
         <v>2060</v>
       </c>
-      <c r="F553" s="2" t="s">
+      <c r="F554" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G553" s="2" t="s">
+      <c r="G554" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H553" s="2" t="s">
+      <c r="H554" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I553" s="2" t="s">
+      <c r="I554" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J553" s="2" t="s">
+      <c r="J554" s="2" t="s">
         <v>4400</v>
       </c>
-      <c r="K553" s="2" t="s">
+      <c r="K554" s="2" t="s">
         <v>4401</v>
       </c>
-      <c r="L553" s="3">
+      <c r="L554" s="3">
         <v>32.21</v>
       </c>
-      <c r="M553" s="3">
+      <c r="M554" s="3">
         <v>7.85</v>
       </c>
-      <c r="N553" s="2" t="s">
+      <c r="N554" s="2" t="s">
         <v>4402</v>
       </c>
-      <c r="O553" s="2"/>
-      <c r="P553" s="2"/>
-      <c r="Q553" s="2"/>
-      <c r="R553" s="2"/>
-      <c r="S553" s="2" t="s">
+      <c r="O554" s="2"/>
+      <c r="P554" s="2"/>
+      <c r="Q554" s="2"/>
+      <c r="R554" s="2"/>
+      <c r="S554" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="T553" s="2"/>
-      <c r="U553" s="2" t="s">
+      <c r="T554" s="2"/>
+      <c r="U554" s="2" t="s">
         <v>4403</v>
       </c>
-      <c r="V553" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W553" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X553" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y553" s="2"/>
-    </row>
-    <row r="554" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A554" s="4" t="s">
+      <c r="V554" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W554" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X554" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y554" s="2"/>
+    </row>
+    <row r="555" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A555" s="4" t="s">
         <v>4404</v>
       </c>
-      <c r="B554" s="4" t="s">
+      <c r="B555" s="4" t="s">
         <v>4405</v>
       </c>
-      <c r="C554" s="4" t="s">
+      <c r="C555" s="4" t="s">
         <v>4406</v>
       </c>
-      <c r="D554" s="4" t="s">
+      <c r="D555" s="4" t="s">
         <v>4407</v>
       </c>
-      <c r="E554" s="4" t="s">
+      <c r="E555" s="4" t="s">
         <v>4407</v>
       </c>
-      <c r="F554" s="4" t="s">
+      <c r="F555" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G554" s="4" t="s">
+      <c r="G555" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H554" s="4" t="s">
+      <c r="H555" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I554" s="4" t="s">
+      <c r="I555" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J554" s="4" t="s">
+      <c r="J555" s="4" t="s">
         <v>4408</v>
       </c>
-      <c r="K554" s="4" t="s">
+      <c r="K555" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="L554" s="5">
+      <c r="L555" s="5">
         <v>22.61</v>
       </c>
-      <c r="M554" s="5">
+      <c r="M555" s="5">
         <v>2.1800000000000002</v>
       </c>
-      <c r="N554" s="4" t="s">
+      <c r="N555" s="4" t="s">
         <v>4409</v>
       </c>
-      <c r="O554" s="4"/>
-      <c r="P554" s="4"/>
-      <c r="Q554" s="4"/>
-      <c r="R554" s="4"/>
-      <c r="S554" s="4"/>
-      <c r="T554" s="4"/>
-      <c r="U554" s="4" t="s">
+      <c r="O555" s="4"/>
+      <c r="P555" s="4"/>
+      <c r="Q555" s="4"/>
+      <c r="R555" s="4"/>
+      <c r="S555" s="4"/>
+      <c r="T555" s="4"/>
+      <c r="U555" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="V554" s="4" t="s">
+      <c r="V555" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="W554" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X554" s="4" t="s">
+      <c r="W555" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X555" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y554" s="4"/>
-    </row>
-    <row r="555" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A555" s="2" t="s">
+      <c r="Y555" s="4"/>
+    </row>
+    <row r="556" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A556" s="2" t="s">
         <v>4410</v>
       </c>
-      <c r="B555" s="2" t="s">
+      <c r="B556" s="2" t="s">
         <v>4411</v>
       </c>
-      <c r="C555" s="2" t="s">
+      <c r="C556" s="2" t="s">
         <v>4412</v>
       </c>
-      <c r="D555" s="2" t="s">
+      <c r="D556" s="2" t="s">
         <v>4413</v>
       </c>
-      <c r="E555" s="2" t="s">
+      <c r="E556" s="2" t="s">
         <v>4413</v>
       </c>
-      <c r="F555" s="2" t="s">
+      <c r="F556" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G555" s="2" t="s">
+      <c r="G556" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H555" s="2" t="s">
+      <c r="H556" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I555" s="2" t="s">
+      <c r="I556" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J555" s="2" t="s">
+      <c r="J556" s="2" t="s">
         <v>4414</v>
       </c>
-      <c r="K555" s="2" t="s">
+      <c r="K556" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L555" s="3">
+      <c r="L556" s="3">
         <v>21.74</v>
       </c>
-      <c r="M555" s="3">
+      <c r="M556" s="3">
         <v>2.1800000000000002</v>
       </c>
-      <c r="N555" s="2" t="s">
+      <c r="N556" s="2" t="s">
         <v>4415</v>
       </c>
-      <c r="O555" s="2"/>
-      <c r="P555" s="2"/>
-      <c r="Q555" s="2"/>
-      <c r="R555" s="2"/>
-      <c r="S555" s="2"/>
-      <c r="T555" s="2"/>
-      <c r="U555" s="2" t="s">
+      <c r="O556" s="2"/>
+      <c r="P556" s="2"/>
+      <c r="Q556" s="2"/>
+      <c r="R556" s="2"/>
+      <c r="S556" s="2"/>
+      <c r="T556" s="2"/>
+      <c r="U556" s="2" t="s">
         <v>4416</v>
       </c>
-      <c r="V555" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W555" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X555" s="2" t="s">
+      <c r="V556" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W556" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X556" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y555" s="2"/>
-    </row>
-    <row r="556" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A556" s="4" t="s">
+      <c r="Y556" s="2"/>
+    </row>
+    <row r="557" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A557" s="4" t="s">
         <v>4417</v>
       </c>
-      <c r="B556" s="4" t="s">
+      <c r="B557" s="4" t="s">
         <v>4418</v>
       </c>
-      <c r="C556" s="4" t="s">
+      <c r="C557" s="4" t="s">
         <v>4419</v>
       </c>
-      <c r="D556" s="4" t="s">
+      <c r="D557" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="E556" s="4" t="s">
+      <c r="E557" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="F556" s="4" t="s">
+      <c r="F557" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G556" s="4" t="s">
+      <c r="G557" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H556" s="4" t="s">
+      <c r="H557" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I556" s="4" t="s">
+      <c r="I557" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J556" s="4" t="s">
+      <c r="J557" s="4" t="s">
         <v>4420</v>
       </c>
-      <c r="K556" s="4" t="s">
+      <c r="K557" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="L556" s="5">
+      <c r="L557" s="5">
         <v>30.94</v>
       </c>
-      <c r="M556" s="5">
+      <c r="M557" s="5">
         <v>2.1800000000000002</v>
       </c>
-      <c r="N556" s="4" t="s">
+      <c r="N557" s="4" t="s">
         <v>4421</v>
       </c>
-      <c r="O556" s="4"/>
-      <c r="P556" s="4"/>
-      <c r="Q556" s="4"/>
-      <c r="R556" s="4"/>
-      <c r="S556" s="4"/>
-      <c r="T556" s="4"/>
-      <c r="U556" s="4" t="s">
+      <c r="O557" s="4"/>
+      <c r="P557" s="4"/>
+      <c r="Q557" s="4"/>
+      <c r="R557" s="4"/>
+      <c r="S557" s="4"/>
+      <c r="T557" s="4"/>
+      <c r="U557" s="4" t="s">
         <v>4416</v>
       </c>
-      <c r="V556" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W556" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X556" s="4" t="s">
+      <c r="V557" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W557" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X557" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y556" s="4"/>
-    </row>
-    <row r="557" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A557" s="2" t="s">
+      <c r="Y557" s="4"/>
+    </row>
+    <row r="558" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A558" s="2" t="s">
         <v>4422</v>
       </c>
-      <c r="B557" s="2" t="s">
+      <c r="B558" s="2" t="s">
         <v>4423</v>
       </c>
-      <c r="C557" s="2" t="s">
+      <c r="C558" s="2" t="s">
         <v>4424</v>
       </c>
-      <c r="D557" s="2" t="s">
+      <c r="D558" s="2" t="s">
         <v>2728</v>
       </c>
-      <c r="E557" s="2" t="s">
+      <c r="E558" s="2" t="s">
         <v>2728</v>
       </c>
-      <c r="F557" s="2" t="s">
+      <c r="F558" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G557" s="2" t="s">
+      <c r="G558" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H557" s="2" t="s">
+      <c r="H558" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I557" s="2" t="s">
+      <c r="I558" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J557" s="2" t="s">
+      <c r="J558" s="2" t="s">
         <v>4425</v>
       </c>
-      <c r="K557" s="2" t="s">
+      <c r="K558" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="L557" s="3">
+      <c r="L558" s="3">
         <v>22.52</v>
       </c>
-      <c r="M557" s="3">
+      <c r="M558" s="3">
         <v>1.68</v>
       </c>
-      <c r="N557" s="2" t="s">
+      <c r="N558" s="2" t="s">
         <v>4426</v>
       </c>
-      <c r="O557" s="2"/>
-      <c r="P557" s="2"/>
-      <c r="Q557" s="2"/>
-      <c r="R557" s="2"/>
-      <c r="S557" s="2"/>
-      <c r="T557" s="2"/>
-      <c r="U557" s="2" t="s">
+      <c r="O558" s="2"/>
+      <c r="P558" s="2"/>
+      <c r="Q558" s="2"/>
+      <c r="R558" s="2"/>
+      <c r="S558" s="2"/>
+      <c r="T558" s="2"/>
+      <c r="U558" s="2" t="s">
         <v>4427</v>
       </c>
-      <c r="V557" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W557" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X557" s="2" t="s">
+      <c r="V558" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W558" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X558" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y557" s="2"/>
-    </row>
-    <row r="558" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A558" s="4" t="s">
+      <c r="Y558" s="2"/>
+    </row>
+    <row r="559" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A559" s="4" t="s">
         <v>4428</v>
       </c>
-      <c r="B558" s="4" t="s">
+      <c r="B559" s="4" t="s">
         <v>4429</v>
       </c>
-      <c r="C558" s="4" t="s">
+      <c r="C559" s="4" t="s">
         <v>4430</v>
       </c>
-      <c r="D558" s="4"/>
-      <c r="E558" s="4"/>
-      <c r="F558" s="4" t="s">
+      <c r="D559" s="4"/>
+      <c r="E559" s="4"/>
+      <c r="F559" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G558" s="4" t="s">
+      <c r="G559" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H558" s="4" t="s">
+      <c r="H559" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I558" s="4" t="s">
+      <c r="I559" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J558" s="4" t="s">
+      <c r="J559" s="4" t="s">
         <v>4431</v>
       </c>
-      <c r="K558" s="4" t="s">
+      <c r="K559" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="L558" s="5">
+      <c r="L559" s="5">
         <v>24.56</v>
       </c>
-      <c r="M558" s="5">
+      <c r="M559" s="5">
         <v>1.43</v>
       </c>
-      <c r="N558" s="4" t="s">
+      <c r="N559" s="4" t="s">
         <v>4432</v>
       </c>
-      <c r="O558" s="4"/>
-      <c r="P558" s="4"/>
-      <c r="Q558" s="4"/>
-      <c r="R558" s="4"/>
-      <c r="S558" s="4"/>
-      <c r="T558" s="4"/>
-      <c r="U558" s="4" t="s">
+      <c r="O559" s="4"/>
+      <c r="P559" s="4"/>
+      <c r="Q559" s="4"/>
+      <c r="R559" s="4"/>
+      <c r="S559" s="4"/>
+      <c r="T559" s="4"/>
+      <c r="U559" s="4" t="s">
         <v>4433</v>
       </c>
-      <c r="V558" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W558" s="4" t="s">
+      <c r="V559" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W559" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X558" s="4" t="s">
+      <c r="X559" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y558" s="4"/>
-    </row>
-    <row r="559" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A559" s="2" t="s">
+      <c r="Y559" s="4"/>
+    </row>
+    <row r="560" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A560" s="2" t="s">
         <v>4434</v>
       </c>
-      <c r="B559" s="2" t="s">
+      <c r="B560" s="2" t="s">
         <v>4435</v>
       </c>
-      <c r="C559" s="2" t="s">
+      <c r="C560" s="2" t="s">
         <v>4436</v>
       </c>
-      <c r="D559" s="2"/>
-      <c r="E559" s="2"/>
-      <c r="F559" s="2" t="s">
+      <c r="D560" s="2"/>
+      <c r="E560" s="2"/>
+      <c r="F560" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G559" s="2" t="s">
+      <c r="G560" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H559" s="2" t="s">
+      <c r="H560" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I559" s="2" t="s">
+      <c r="I560" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J559" s="2" t="s">
+      <c r="J560" s="2" t="s">
         <v>2875</v>
       </c>
-      <c r="K559" s="2" t="s">
+      <c r="K560" s="2" t="s">
         <v>4437</v>
       </c>
-      <c r="L559" s="3">
+      <c r="L560" s="3">
         <v>24.58</v>
       </c>
-      <c r="M559" s="3">
+      <c r="M560" s="3">
         <v>1.38</v>
       </c>
-      <c r="N559" s="2" t="s">
+      <c r="N560" s="2" t="s">
         <v>4438</v>
       </c>
-      <c r="O559" s="2"/>
-      <c r="P559" s="2"/>
-      <c r="Q559" s="2"/>
-      <c r="R559" s="2"/>
-      <c r="S559" s="2"/>
-      <c r="T559" s="2"/>
-      <c r="U559" s="2" t="s">
+      <c r="O560" s="2"/>
+      <c r="P560" s="2"/>
+      <c r="Q560" s="2"/>
+      <c r="R560" s="2"/>
+      <c r="S560" s="2"/>
+      <c r="T560" s="2"/>
+      <c r="U560" s="2" t="s">
         <v>2127</v>
       </c>
-      <c r="V559" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W559" s="2" t="s">
+      <c r="V560" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W560" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X559" s="2" t="s">
+      <c r="X560" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y559" s="2"/>
-    </row>
-    <row r="560" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A560" s="4" t="s">
+      <c r="Y560" s="2"/>
+    </row>
+    <row r="561" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A561" s="4" t="s">
         <v>4439</v>
       </c>
-      <c r="B560" s="4" t="s">
+      <c r="B561" s="4" t="s">
         <v>4440</v>
       </c>
-      <c r="C560" s="4" t="s">
+      <c r="C561" s="4" t="s">
         <v>4441</v>
       </c>
-      <c r="D560" s="4"/>
-      <c r="E560" s="4"/>
-      <c r="F560" s="4" t="s">
+      <c r="D561" s="4"/>
+      <c r="E561" s="4"/>
+      <c r="F561" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G560" s="4" t="s">
+      <c r="G561" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="H560" s="4" t="s">
+      <c r="H561" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I560" s="4" t="s">
+      <c r="I561" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J560" s="4" t="s">
+      <c r="J561" s="4" t="s">
         <v>4442</v>
       </c>
-      <c r="K560" s="4" t="s">
+      <c r="K561" s="4" t="s">
         <v>3126</v>
       </c>
-      <c r="L560" s="5">
+      <c r="L561" s="5">
         <v>23.32</v>
       </c>
-      <c r="M560" s="5">
+      <c r="M561" s="5">
         <v>1.34</v>
       </c>
-      <c r="N560" s="4" t="s">
+      <c r="N561" s="4" t="s">
         <v>4443</v>
       </c>
-      <c r="O560" s="4"/>
-      <c r="P560" s="4"/>
-      <c r="Q560" s="4"/>
-      <c r="R560" s="4"/>
-      <c r="S560" s="4"/>
-      <c r="T560" s="4"/>
-      <c r="U560" s="4" t="s">
+      <c r="O561" s="4"/>
+      <c r="P561" s="4"/>
+      <c r="Q561" s="4"/>
+      <c r="R561" s="4"/>
+      <c r="S561" s="4"/>
+      <c r="T561" s="4"/>
+      <c r="U561" s="4" t="s">
         <v>2127</v>
       </c>
-      <c r="V560" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W560" s="4" t="s">
+      <c r="V561" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W561" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X560" s="4" t="s">
+      <c r="X561" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y560" s="4"/>
-    </row>
-    <row r="561" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A561" s="2" t="s">
+      <c r="Y561" s="4"/>
+    </row>
+    <row r="562" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A562" s="2" t="s">
         <v>4444</v>
       </c>
-      <c r="B561" s="2" t="s">
+      <c r="B562" s="2" t="s">
         <v>4445</v>
       </c>
-      <c r="C561" s="2" t="s">
+      <c r="C562" s="2" t="s">
         <v>4446</v>
       </c>
-      <c r="D561" s="2" t="s">
+      <c r="D562" s="2" t="s">
         <v>1677</v>
       </c>
-      <c r="E561" s="2" t="s">
+      <c r="E562" s="2" t="s">
         <v>1677</v>
       </c>
-      <c r="F561" s="2" t="s">
+      <c r="F562" s="2" t="s">
         <v>4447</v>
       </c>
-      <c r="G561" s="2" t="s">
+      <c r="G562" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H561" s="2" t="s">
+      <c r="H562" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I561" s="2" t="s">
+      <c r="I562" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J561" s="2" t="s">
+      <c r="J562" s="2" t="s">
         <v>4448</v>
       </c>
-      <c r="K561" s="2" t="s">
+      <c r="K562" s="2" t="s">
         <v>4449</v>
       </c>
-      <c r="L561" s="3">
+      <c r="L562" s="3">
         <v>29.71</v>
       </c>
-      <c r="M561" s="3">
+      <c r="M562" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="N561" s="2" t="s">
+      <c r="N562" s="2" t="s">
         <v>4450</v>
       </c>
-      <c r="O561" s="2" t="s">
+      <c r="O562" s="2" t="s">
         <v>4451</v>
       </c>
-      <c r="P561" s="2"/>
-      <c r="Q561" s="2"/>
-      <c r="R561" s="2"/>
-      <c r="S561" s="2"/>
-      <c r="T561" s="2"/>
-      <c r="U561" s="2" t="s">
+      <c r="P562" s="2"/>
+      <c r="Q562" s="2"/>
+      <c r="R562" s="2"/>
+      <c r="S562" s="2"/>
+      <c r="T562" s="2"/>
+      <c r="U562" s="2" t="s">
         <v>4233</v>
       </c>
-      <c r="V561" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W561" s="2" t="s">
+      <c r="V562" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W562" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X561" s="2" t="s">
+      <c r="X562" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y561" s="2"/>
-    </row>
-    <row r="562" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A562" s="4" t="s">
+      <c r="Y562" s="2"/>
+    </row>
+    <row r="563" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A563" s="4" t="s">
         <v>4452</v>
       </c>
-      <c r="B562" s="4" t="s">
+      <c r="B563" s="4" t="s">
         <v>4453</v>
       </c>
-      <c r="C562" s="4" t="s">
+      <c r="C563" s="4" t="s">
         <v>4454</v>
       </c>
-      <c r="D562" s="4" t="s">
+      <c r="D563" s="4" t="s">
         <v>2324</v>
       </c>
-      <c r="E562" s="4" t="s">
+      <c r="E563" s="4" t="s">
         <v>2324</v>
       </c>
-      <c r="F562" s="4" t="s">
+      <c r="F563" s="4" t="s">
         <v>4447</v>
       </c>
-      <c r="G562" s="4" t="s">
+      <c r="G563" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H562" s="4" t="s">
+      <c r="H563" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I562" s="4" t="s">
+      <c r="I563" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J562" s="4" t="s">
+      <c r="J563" s="4" t="s">
         <v>4455</v>
       </c>
-      <c r="K562" s="4" t="s">
+      <c r="K563" s="4" t="s">
         <v>2420</v>
       </c>
-      <c r="L562" s="5">
+      <c r="L563" s="5">
         <v>28.07</v>
       </c>
-      <c r="M562" s="5">
+      <c r="M563" s="5">
         <v>0.68</v>
       </c>
-      <c r="N562" s="4" t="s">
+      <c r="N563" s="4" t="s">
         <v>4456</v>
       </c>
-      <c r="O562" s="4" t="s">
+      <c r="O563" s="4" t="s">
         <v>4457</v>
       </c>
-      <c r="P562" s="4"/>
-      <c r="Q562" s="4"/>
-      <c r="R562" s="4"/>
-      <c r="S562" s="4"/>
-      <c r="T562" s="4"/>
-      <c r="U562" s="4" t="s">
+      <c r="P563" s="4"/>
+      <c r="Q563" s="4"/>
+      <c r="R563" s="4"/>
+      <c r="S563" s="4"/>
+      <c r="T563" s="4"/>
+      <c r="U563" s="4" t="s">
         <v>4458</v>
       </c>
-      <c r="V562" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W562" s="4" t="s">
+      <c r="V563" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W563" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X562" s="4" t="s">
+      <c r="X563" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y562" s="4"/>
-    </row>
-    <row r="563" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A563" s="2" t="s">
+      <c r="Y563" s="4"/>
+    </row>
+    <row r="564" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A564" s="2" t="s">
         <v>4459</v>
       </c>
-      <c r="B563" s="2" t="s">
+      <c r="B564" s="2" t="s">
         <v>4460</v>
       </c>
-      <c r="C563" s="2" t="s">
+      <c r="C564" s="2" t="s">
         <v>4461</v>
       </c>
-      <c r="D563" s="2" t="s">
+      <c r="D564" s="2" t="s">
         <v>4462</v>
       </c>
-      <c r="E563" s="2" t="s">
+      <c r="E564" s="2" t="s">
         <v>4462</v>
       </c>
-      <c r="F563" s="2" t="s">
+      <c r="F564" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G563" s="2" t="s">
+      <c r="G564" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H563" s="2" t="s">
+      <c r="H564" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I563" s="2" t="s">
+      <c r="I564" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J563" s="2" t="s">
+      <c r="J564" s="2" t="s">
         <v>4463</v>
       </c>
-      <c r="K563" s="2" t="s">
+      <c r="K564" s="2" t="s">
         <v>2420</v>
       </c>
-      <c r="L563" s="3">
+      <c r="L564" s="3">
         <v>23.29</v>
       </c>
-      <c r="M563" s="3">
+      <c r="M564" s="3">
         <v>0.68</v>
       </c>
-      <c r="N563" s="2" t="s">
+      <c r="N564" s="2" t="s">
         <v>4464</v>
       </c>
-      <c r="O563" s="2"/>
-      <c r="P563" s="2"/>
-      <c r="Q563" s="2"/>
-      <c r="R563" s="2"/>
-      <c r="S563" s="2"/>
-      <c r="T563" s="2"/>
-      <c r="U563" s="2" t="s">
+      <c r="O564" s="2"/>
+      <c r="P564" s="2"/>
+      <c r="Q564" s="2"/>
+      <c r="R564" s="2"/>
+      <c r="S564" s="2"/>
+      <c r="T564" s="2"/>
+      <c r="U564" s="2" t="s">
         <v>4433</v>
       </c>
-      <c r="V563" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W563" s="2" t="s">
+      <c r="V564" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W564" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X563" s="2" t="s">
+      <c r="X564" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y563" s="2"/>
-    </row>
-    <row r="564" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A564" s="4" t="s">
+      <c r="Y564" s="2"/>
+    </row>
+    <row r="565" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A565" s="4" t="s">
         <v>4465</v>
       </c>
-      <c r="B564" s="4" t="s">
+      <c r="B565" s="4" t="s">
         <v>4466</v>
       </c>
-      <c r="C564" s="4" t="s">
+      <c r="C565" s="4" t="s">
         <v>4467</v>
       </c>
-      <c r="D564" s="4" t="s">
+      <c r="D565" s="4" t="s">
         <v>4468</v>
       </c>
-      <c r="E564" s="4" t="s">
+      <c r="E565" s="4" t="s">
         <v>4468</v>
       </c>
-      <c r="F564" s="4" t="s">
+      <c r="F565" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G564" s="4" t="s">
+      <c r="G565" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H564" s="4" t="s">
+      <c r="H565" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I564" s="4" t="s">
+      <c r="I565" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J564" s="4" t="s">
+      <c r="J565" s="4" t="s">
         <v>4469</v>
       </c>
-      <c r="K564" s="4" t="s">
+      <c r="K565" s="4" t="s">
         <v>3537</v>
       </c>
-      <c r="L564" s="5">
+      <c r="L565" s="5">
         <v>38.619999999999997</v>
       </c>
-      <c r="M564" s="5">
+      <c r="M565" s="5">
         <v>0.51</v>
       </c>
-      <c r="N564" s="4" t="s">
+      <c r="N565" s="4" t="s">
         <v>4470</v>
       </c>
-      <c r="O564" s="4"/>
-      <c r="P564" s="4"/>
-      <c r="Q564" s="4"/>
-      <c r="R564" s="4"/>
-      <c r="S564" s="4"/>
-      <c r="T564" s="4"/>
-      <c r="U564" s="4" t="s">
+      <c r="O565" s="4"/>
+      <c r="P565" s="4"/>
+      <c r="Q565" s="4"/>
+      <c r="R565" s="4"/>
+      <c r="S565" s="4"/>
+      <c r="T565" s="4"/>
+      <c r="U565" s="4" t="s">
         <v>2364</v>
       </c>
-      <c r="V564" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W564" s="4" t="s">
+      <c r="V565" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W565" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X564" s="4" t="s">
+      <c r="X565" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y564" s="4"/>
-    </row>
-    <row r="565" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A565" s="2" t="s">
+      <c r="Y565" s="4"/>
+    </row>
+    <row r="566" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A566" s="2" t="s">
         <v>4471</v>
       </c>
-      <c r="B565" s="2" t="s">
+      <c r="B566" s="2" t="s">
         <v>4472</v>
       </c>
-      <c r="C565" s="2" t="s">
+      <c r="C566" s="2" t="s">
         <v>4473</v>
       </c>
-      <c r="D565" s="2" t="s">
+      <c r="D566" s="2" t="s">
         <v>3815</v>
       </c>
-      <c r="E565" s="2" t="s">
+      <c r="E566" s="2" t="s">
         <v>3815</v>
       </c>
-      <c r="F565" s="2" t="s">
+      <c r="F566" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G565" s="2" t="s">
+      <c r="G566" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H565" s="2" t="s">
+      <c r="H566" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I565" s="2" t="s">
+      <c r="I566" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J565" s="2" t="s">
+      <c r="J566" s="2" t="s">
         <v>4474</v>
       </c>
-      <c r="K565" s="2" t="s">
+      <c r="K566" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="L565" s="3">
+      <c r="L566" s="3">
         <v>23.9</v>
       </c>
-      <c r="M565" s="3">
+      <c r="M566" s="3">
         <v>0.47</v>
       </c>
-      <c r="N565" s="2" t="s">
+      <c r="N566" s="2" t="s">
         <v>4475</v>
       </c>
-      <c r="O565" s="2"/>
-      <c r="P565" s="2"/>
-      <c r="Q565" s="2"/>
-      <c r="R565" s="2"/>
-      <c r="S565" s="2"/>
-      <c r="T565" s="2"/>
-      <c r="U565" s="2" t="s">
+      <c r="O566" s="2"/>
+      <c r="P566" s="2"/>
+      <c r="Q566" s="2"/>
+      <c r="R566" s="2"/>
+      <c r="S566" s="2"/>
+      <c r="T566" s="2"/>
+      <c r="U566" s="2" t="s">
         <v>4433</v>
       </c>
-      <c r="V565" s="2" t="s">
+      <c r="V566" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="W565" s="2" t="s">
+      <c r="W566" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X565" s="2" t="s">
+      <c r="X566" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y565" s="2"/>
-    </row>
-    <row r="566" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A566" s="4" t="s">
+      <c r="Y566" s="2"/>
+    </row>
+    <row r="567" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A567" s="4" t="s">
         <v>4476</v>
       </c>
-      <c r="B566" s="4" t="s">
+      <c r="B567" s="4" t="s">
         <v>4477</v>
       </c>
-      <c r="C566" s="4" t="s">
+      <c r="C567" s="4" t="s">
         <v>4478</v>
       </c>
-      <c r="D566" s="4" t="s">
+      <c r="D567" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="E566" s="4" t="s">
+      <c r="E567" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="F566" s="4" t="s">
+      <c r="F567" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G566" s="4" t="s">
+      <c r="G567" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H566" s="4" t="s">
+      <c r="H567" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I566" s="4" t="s">
+      <c r="I567" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J566" s="4" t="s">
+      <c r="J567" s="4" t="s">
         <v>4479</v>
       </c>
-      <c r="K566" s="4" t="s">
+      <c r="K567" s="4" t="s">
         <v>1738</v>
       </c>
-      <c r="L566" s="5">
+      <c r="L567" s="5">
         <v>32.380000000000003</v>
       </c>
-      <c r="M566" s="5">
+      <c r="M567" s="5">
         <v>0.06</v>
       </c>
-      <c r="N566" s="4" t="s">
+      <c r="N567" s="4" t="s">
         <v>4480</v>
       </c>
-      <c r="O566" s="4"/>
-      <c r="P566" s="4"/>
-      <c r="Q566" s="4"/>
-      <c r="R566" s="4"/>
-      <c r="S566" s="4"/>
-      <c r="T566" s="4"/>
-      <c r="U566" s="4" t="s">
+      <c r="O567" s="4"/>
+      <c r="P567" s="4"/>
+      <c r="Q567" s="4"/>
+      <c r="R567" s="4"/>
+      <c r="S567" s="4"/>
+      <c r="T567" s="4"/>
+      <c r="U567" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="V566" s="4" t="s">
+      <c r="V567" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W566" s="4" t="s">
+      <c r="W567" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X566" s="4" t="s">
+      <c r="X567" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y566" s="4"/>
-    </row>
-    <row r="567" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A567" s="2" t="s">
+      <c r="Y567" s="4"/>
+    </row>
+    <row r="568" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A568" s="2" t="s">
         <v>4481</v>
       </c>
-      <c r="B567" s="2" t="s">
+      <c r="B568" s="2" t="s">
         <v>4482</v>
       </c>
-      <c r="C567" s="2" t="s">
+      <c r="C568" s="2" t="s">
         <v>4483</v>
       </c>
-      <c r="D567" s="2" t="s">
+      <c r="D568" s="2" t="s">
         <v>4484</v>
       </c>
-      <c r="E567" s="2" t="s">
+      <c r="E568" s="2" t="s">
         <v>4484</v>
       </c>
-      <c r="F567" s="2" t="s">
+      <c r="F568" s="2" t="s">
         <v>4358</v>
       </c>
-      <c r="G567" s="2" t="s">
+      <c r="G568" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="H567" s="2" t="s">
+      <c r="H568" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I567" s="2" t="s">
+      <c r="I568" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J567" s="2" t="s">
+      <c r="J568" s="2" t="s">
         <v>4485</v>
       </c>
-      <c r="K567" s="2" t="s">
+      <c r="K568" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="L567" s="3">
+      <c r="L568" s="3">
         <v>23.28</v>
       </c>
-      <c r="M567" s="3">
+      <c r="M568" s="3">
         <v>0.01</v>
       </c>
-      <c r="N567" s="2" t="s">
+      <c r="N568" s="2" t="s">
         <v>4486</v>
       </c>
-      <c r="O567" s="2"/>
-      <c r="P567" s="2"/>
-      <c r="Q567" s="2"/>
-      <c r="R567" s="2"/>
-      <c r="S567" s="2"/>
-      <c r="T567" s="2"/>
-      <c r="U567" s="2" t="s">
+      <c r="O568" s="2"/>
+      <c r="P568" s="2"/>
+      <c r="Q568" s="2"/>
+      <c r="R568" s="2"/>
+      <c r="S568" s="2"/>
+      <c r="T568" s="2"/>
+      <c r="U568" s="2" t="s">
         <v>3513</v>
       </c>
-      <c r="V567" s="2" t="s">
+      <c r="V568" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="W567" s="2" t="s">
+      <c r="W568" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X567" s="2" t="s">
+      <c r="X568" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y567" s="2"/>
-    </row>
-    <row r="568" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A568" s="4" t="s">
+      <c r="Y568" s="2"/>
+    </row>
+    <row r="569" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A569" s="4" t="s">
         <v>4487</v>
       </c>
-      <c r="B568" s="4" t="s">
+      <c r="B569" s="4" t="s">
         <v>4488</v>
       </c>
-      <c r="C568" s="4" t="s">
+      <c r="C569" s="4" t="s">
         <v>4489</v>
       </c>
-      <c r="D568" s="4" t="s">
+      <c r="D569" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="E568" s="4" t="s">
+      <c r="E569" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="F568" s="4" t="s">
+      <c r="F569" s="4" t="s">
         <v>4366</v>
       </c>
-      <c r="G568" s="4" t="s">
+      <c r="G569" s="4" t="s">
         <v>2735</v>
       </c>
-      <c r="H568" s="4" t="s">
+      <c r="H569" s="4" t="s">
         <v>4350</v>
       </c>
-      <c r="I568" s="4" t="s">
+      <c r="I569" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="J568" s="4" t="s">
+      <c r="J569" s="4" t="s">
         <v>4490</v>
       </c>
-      <c r="K568" s="4" t="s">
+      <c r="K569" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L568" s="5">
+      <c r="L569" s="5">
         <v>29.59</v>
       </c>
-      <c r="M568" s="5">
+      <c r="M569" s="5">
         <v>0.01</v>
       </c>
-      <c r="N568" s="4" t="s">
+      <c r="N569" s="4" t="s">
         <v>4491</v>
       </c>
-      <c r="O568" s="4"/>
-      <c r="P568" s="4"/>
-      <c r="Q568" s="4"/>
-      <c r="R568" s="4"/>
-      <c r="S568" s="4"/>
-      <c r="T568" s="4"/>
-      <c r="U568" s="4" t="s">
+      <c r="O569" s="4"/>
+      <c r="P569" s="4"/>
+      <c r="Q569" s="4"/>
+      <c r="R569" s="4"/>
+      <c r="S569" s="4"/>
+      <c r="T569" s="4"/>
+      <c r="U569" s="4" t="s">
         <v>4492</v>
       </c>
-      <c r="V568" s="4" t="s">
+      <c r="V569" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W568" s="4" t="s">
+      <c r="W569" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X568" s="4" t="s">
+      <c r="X569" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y568" s="4"/>
-    </row>
-    <row r="569" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A569" s="2" t="s">
+      <c r="Y569" s="4"/>
+    </row>
+    <row r="570" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A570" s="2" t="s">
         <v>4493</v>
       </c>
-      <c r="B569" s="2" t="s">
+      <c r="B570" s="2" t="s">
         <v>4494</v>
       </c>
-      <c r="C569" s="2" t="s">
+      <c r="C570" s="2" t="s">
         <v>4495</v>
       </c>
-      <c r="D569" s="2" t="s">
+      <c r="D570" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="E569" s="2" t="s">
+      <c r="E570" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="F569" s="2" t="s">
+      <c r="F570" s="2" t="s">
         <v>4366</v>
       </c>
-      <c r="G569" s="2" t="s">
+      <c r="G570" s="2" t="s">
         <v>2735</v>
       </c>
-      <c r="H569" s="2" t="s">
+      <c r="H570" s="2" t="s">
         <v>4350</v>
       </c>
-      <c r="I569" s="2" t="s">
+      <c r="I570" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="J569" s="2" t="s">
+      <c r="J570" s="2" t="s">
         <v>4496</v>
       </c>
-      <c r="K569" s="2" t="s">
+      <c r="K570" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="L569" s="3">
+      <c r="L570" s="3">
         <v>23.96</v>
       </c>
-      <c r="M569" s="3">
+      <c r="M570" s="3">
         <v>0.01</v>
       </c>
-      <c r="N569" s="2" t="s">
+      <c r="N570" s="2" t="s">
         <v>4497</v>
       </c>
-      <c r="O569" s="2"/>
-      <c r="P569" s="2"/>
-      <c r="Q569" s="2"/>
-      <c r="R569" s="2"/>
-      <c r="S569" s="2"/>
-      <c r="T569" s="2"/>
-      <c r="U569" s="2" t="s">
+      <c r="O570" s="2"/>
+      <c r="P570" s="2"/>
+      <c r="Q570" s="2"/>
+      <c r="R570" s="2"/>
+      <c r="S570" s="2"/>
+      <c r="T570" s="2"/>
+      <c r="U570" s="2" t="s">
         <v>4433</v>
       </c>
-      <c r="V569" s="2" t="s">
+      <c r="V570" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="W569" s="2" t="s">
+      <c r="W570" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X569" s="2" t="s">
+      <c r="X570" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y569" s="2"/>
-    </row>
-    <row r="570" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A570" s="4" t="s">
+      <c r="Y570" s="2"/>
+    </row>
+    <row r="571" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A571" s="4" t="s">
         <v>4498</v>
       </c>
-      <c r="B570" s="4" t="s">
+      <c r="B571" s="4" t="s">
         <v>4499</v>
       </c>
-      <c r="C570" s="4" t="s">
+      <c r="C571" s="4" t="s">
         <v>4500</v>
       </c>
-      <c r="D570" s="4"/>
-      <c r="E570" s="4"/>
-      <c r="F570" s="4" t="s">
+      <c r="D571" s="4"/>
+      <c r="E571" s="4"/>
+      <c r="F571" s="4" t="s">
         <v>4501</v>
       </c>
-      <c r="G570" s="4" t="s">
+      <c r="G571" s="4" t="s">
         <v>1234</v>
       </c>
-      <c r="H570" s="4" t="s">
+      <c r="H571" s="4" t="s">
         <v>4502</v>
       </c>
-      <c r="I570" s="4" t="s">
+      <c r="I571" s="4" t="s">
         <v>4503</v>
       </c>
-      <c r="J570" s="4" t="s">
+      <c r="J571" s="4" t="s">
         <v>4504</v>
       </c>
-      <c r="K570" s="4" t="s">
+      <c r="K571" s="4" t="s">
         <v>4505</v>
       </c>
-      <c r="L570" s="5">
+      <c r="L571" s="5">
         <v>48.62</v>
       </c>
-      <c r="M570" s="5">
+      <c r="M571" s="5">
         <v>14.1</v>
       </c>
-      <c r="N570" s="4" t="s">
+      <c r="N571" s="4" t="s">
         <v>4506</v>
       </c>
-      <c r="O570" s="4" t="s">
+      <c r="O571" s="4" t="s">
         <v>4507</v>
       </c>
-      <c r="P570" s="4"/>
-      <c r="Q570" s="4"/>
-      <c r="R570" s="4"/>
-      <c r="S570" s="4" t="s">
+      <c r="P571" s="4"/>
+      <c r="Q571" s="4"/>
+      <c r="R571" s="4"/>
+      <c r="S571" s="4" t="s">
         <v>1787</v>
       </c>
-      <c r="T570" s="4" t="s">
+      <c r="T571" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="U570" s="4" t="s">
+      <c r="U571" s="4" t="s">
         <v>4508</v>
       </c>
-      <c r="V570" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W570" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X570" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y570" s="4"/>
-    </row>
-    <row r="571" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A571" s="2" t="s">
+      <c r="V571" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W571" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X571" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y571" s="4"/>
+    </row>
+    <row r="572" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A572" s="2" t="s">
         <v>4503</v>
       </c>
-      <c r="B571" s="2" t="s">
+      <c r="B572" s="2" t="s">
         <v>4509</v>
       </c>
-      <c r="C571" s="2" t="s">
+      <c r="C572" s="2" t="s">
         <v>4510</v>
       </c>
-      <c r="D571" s="2" t="s">
+      <c r="D572" s="2" t="s">
         <v>4511</v>
       </c>
-      <c r="E571" s="2" t="s">
+      <c r="E572" s="2" t="s">
         <v>4511</v>
       </c>
-      <c r="F571" s="2" t="s">
+      <c r="F572" s="2" t="s">
         <v>4512</v>
       </c>
-      <c r="G571" s="2" t="s">
+      <c r="G572" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H571" s="2" t="s">
+      <c r="H572" s="2" t="s">
         <v>4502</v>
       </c>
-      <c r="I571" s="2" t="s">
+      <c r="I572" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="J571" s="2" t="s">
+      <c r="J572" s="2" t="s">
         <v>4513</v>
       </c>
-      <c r="K571" s="2" t="s">
+      <c r="K572" s="2" t="s">
         <v>4514</v>
       </c>
-      <c r="L571" s="3">
+      <c r="L572" s="3">
         <v>38.26</v>
       </c>
-      <c r="M571" s="3">
+      <c r="M572" s="3">
         <v>9.7100000000000009</v>
       </c>
-      <c r="N571" s="2" t="s">
+      <c r="N572" s="2" t="s">
         <v>4515</v>
       </c>
-      <c r="O571" s="2" t="s">
+      <c r="O572" s="2" t="s">
         <v>4516</v>
       </c>
-      <c r="P571" s="2"/>
-      <c r="Q571" s="2"/>
-      <c r="R571" s="2"/>
-      <c r="S571" s="2" t="s">
+      <c r="P572" s="2"/>
+      <c r="Q572" s="2"/>
+      <c r="R572" s="2"/>
+      <c r="S572" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T571" s="2" t="s">
+      <c r="T572" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="U571" s="2" t="s">
+      <c r="U572" s="2" t="s">
         <v>4517</v>
       </c>
-      <c r="V571" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W571" s="2" t="s">
+      <c r="V572" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W572" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="X571" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y571" s="2"/>
-    </row>
-    <row r="572" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A572" s="4" t="s">
+      <c r="X572" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y572" s="2"/>
+    </row>
+    <row r="573" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A573" s="4" t="s">
         <v>4245</v>
       </c>
-      <c r="B572" s="4" t="s">
+      <c r="B573" s="4" t="s">
         <v>4518</v>
       </c>
-      <c r="C572" s="4" t="s">
+      <c r="C573" s="4" t="s">
         <v>4519</v>
       </c>
-      <c r="D572" s="4" t="s">
+      <c r="D573" s="4" t="s">
         <v>4520</v>
       </c>
-      <c r="E572" s="4" t="s">
+      <c r="E573" s="4" t="s">
         <v>4520</v>
       </c>
-      <c r="F572" s="4" t="s">
+      <c r="F573" s="4" t="s">
         <v>4521</v>
       </c>
-      <c r="G572" s="4" t="s">
+      <c r="G573" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H572" s="4" t="s">
+      <c r="H573" s="4" t="s">
         <v>4522</v>
       </c>
-      <c r="I572" s="4" t="s">
+      <c r="I573" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="J572" s="4" t="s">
+      <c r="J573" s="4" t="s">
         <v>4523</v>
       </c>
-      <c r="K572" s="4" t="s">
+      <c r="K573" s="4" t="s">
         <v>4524</v>
       </c>
-      <c r="L572" s="5">
+      <c r="L573" s="5">
         <v>41.32</v>
       </c>
-      <c r="M572" s="5">
+      <c r="M573" s="5">
         <v>10.85</v>
       </c>
-      <c r="N572" s="4" t="s">
+      <c r="N573" s="4" t="s">
         <v>4525</v>
       </c>
-      <c r="O572" s="4" t="s">
+      <c r="O573" s="4" t="s">
         <v>4526</v>
       </c>
-      <c r="P572" s="4"/>
-      <c r="Q572" s="4"/>
-      <c r="R572" s="4"/>
-      <c r="S572" s="4" t="s">
+      <c r="P573" s="4"/>
+      <c r="Q573" s="4"/>
+      <c r="R573" s="4"/>
+      <c r="S573" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="T572" s="4" t="s">
+      <c r="T573" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U572" s="4" t="s">
+      <c r="U573" s="4" t="s">
         <v>1951</v>
       </c>
-      <c r="V572" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W572" s="4" t="s">
+      <c r="V573" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W573" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="X572" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y572" s="4"/>
-    </row>
-    <row r="573" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A573" s="2" t="s">
+      <c r="X573" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y573" s="4"/>
+    </row>
+    <row r="574" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A574" s="2" t="s">
         <v>4527</v>
       </c>
-      <c r="B573" s="2" t="s">
+      <c r="B574" s="2" t="s">
         <v>4528</v>
       </c>
-      <c r="C573" s="2" t="s">
+      <c r="C574" s="2" t="s">
         <v>4529</v>
       </c>
-      <c r="D573" s="2" t="s">
+      <c r="D574" s="2" t="s">
         <v>4530</v>
       </c>
-      <c r="E573" s="2" t="s">
+      <c r="E574" s="2" t="s">
         <v>4530</v>
       </c>
-      <c r="F573" s="2" t="s">
+      <c r="F574" s="2" t="s">
         <v>4531</v>
       </c>
-      <c r="G573" s="2" t="s">
+      <c r="G574" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H573" s="2" t="s">
+      <c r="H574" s="2" t="s">
         <v>4532</v>
       </c>
-      <c r="I573" s="2" t="s">
+      <c r="I574" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="J573" s="2" t="s">
+      <c r="J574" s="2" t="s">
         <v>4533</v>
       </c>
-      <c r="K573" s="2" t="s">
+      <c r="K574" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="L573" s="3">
+      <c r="L574" s="3">
         <v>34.869999999999997</v>
       </c>
-      <c r="M573" s="3">
+      <c r="M574" s="3">
         <v>0.93</v>
       </c>
-      <c r="N573" s="2" t="s">
+      <c r="N574" s="2" t="s">
         <v>4534</v>
       </c>
-      <c r="O573" s="2" t="s">
+      <c r="O574" s="2" t="s">
         <v>4535</v>
       </c>
-      <c r="P573" s="2"/>
-      <c r="Q573" s="2"/>
-      <c r="R573" s="2"/>
-      <c r="S573" s="2"/>
-      <c r="T573" s="2"/>
-      <c r="U573" s="2" t="s">
+      <c r="P574" s="2"/>
+      <c r="Q574" s="2"/>
+      <c r="R574" s="2"/>
+      <c r="S574" s="2"/>
+      <c r="T574" s="2"/>
+      <c r="U574" s="2" t="s">
         <v>4536</v>
       </c>
-      <c r="V573" s="2" t="s">
+      <c r="V574" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W573" s="2" t="s">
+      <c r="W574" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X573" s="2" t="s">
+      <c r="X574" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y573" s="2"/>
-    </row>
-    <row r="574" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A574" s="4" t="s">
+      <c r="Y574" s="2"/>
+    </row>
+    <row r="575" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B574" s="4" t="s">
+      <c r="B575" s="4" t="s">
         <v>4537</v>
       </c>
-      <c r="C574" s="4" t="s">
+      <c r="C575" s="4" t="s">
         <v>4538</v>
       </c>
-      <c r="D574" s="4" t="s">
+      <c r="D575" s="4" t="s">
         <v>4539</v>
       </c>
-      <c r="E574" s="4" t="s">
+      <c r="E575" s="4" t="s">
         <v>4539</v>
       </c>
-      <c r="F574" s="4" t="s">
+      <c r="F575" s="4" t="s">
         <v>4540</v>
       </c>
-      <c r="G574" s="4" t="s">
+      <c r="G575" s="4" t="s">
         <v>4541</v>
       </c>
-      <c r="H574" s="4" t="s">
+      <c r="H575" s="4" t="s">
         <v>4542</v>
       </c>
-      <c r="I574" s="4"/>
-      <c r="J574" s="4" t="s">
+      <c r="I575" s="4"/>
+      <c r="J575" s="4" t="s">
         <v>4543</v>
       </c>
-      <c r="K574" s="4" t="s">
+      <c r="K575" s="4" t="s">
         <v>4544</v>
       </c>
-      <c r="L574" s="5">
+      <c r="L575" s="5">
         <v>46.21</v>
       </c>
-      <c r="M574" s="5">
+      <c r="M575" s="5">
         <v>1.25</v>
       </c>
-      <c r="N574" s="4" t="s">
+      <c r="N575" s="4" t="s">
         <v>4545</v>
       </c>
-      <c r="O574" s="4" t="s">
+      <c r="O575" s="4" t="s">
         <v>4546</v>
       </c>
-      <c r="P574" s="4"/>
-      <c r="Q574" s="4"/>
-      <c r="R574" s="4"/>
-      <c r="S574" s="4"/>
-      <c r="T574" s="4"/>
-      <c r="U574" s="4" t="s">
+      <c r="P575" s="4"/>
+      <c r="Q575" s="4"/>
+      <c r="R575" s="4"/>
+      <c r="S575" s="4"/>
+      <c r="T575" s="4"/>
+      <c r="U575" s="4" t="s">
         <v>4547</v>
       </c>
-      <c r="V574" s="4" t="s">
+      <c r="V575" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W574" s="4" t="s">
+      <c r="W575" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X574" s="4" t="s">
+      <c r="X575" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y574" s="7" t="s">
+      <c r="Y575" s="7" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="575" spans="1:25" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="8" t="s">
+    <row r="576" spans="1:25" s="11" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A576" s="8" t="s">
         <v>4692</v>
       </c>
-      <c r="B575" s="8" t="s">
+      <c r="B576" s="8" t="s">
         <v>4537</v>
       </c>
-      <c r="C575" s="8" t="s">
+      <c r="C576" s="8" t="s">
         <v>4538</v>
       </c>
-      <c r="D575" s="8" t="s">
+      <c r="D576" s="8" t="s">
         <v>4539</v>
       </c>
-      <c r="E575" s="8" t="s">
+      <c r="E576" s="8" t="s">
         <v>4539</v>
       </c>
-      <c r="F575" s="8" t="s">
+      <c r="F576" s="8" t="s">
         <v>4693</v>
       </c>
-      <c r="G575" s="2" t="s">
+      <c r="G576" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="H575" s="8" t="s">
+      <c r="H576" s="8" t="s">
         <v>4563</v>
       </c>
-      <c r="I575" s="2" t="s">
+      <c r="I576" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="J575" s="8" t="s">
+      <c r="J576" s="8" t="s">
         <v>4543</v>
       </c>
-      <c r="K575" s="8" t="s">
+      <c r="K576" s="8" t="s">
         <v>4544</v>
       </c>
-      <c r="L575" s="9">
+      <c r="L576" s="9">
         <v>46.21</v>
       </c>
-      <c r="M575" s="9">
+      <c r="M576" s="9">
         <v>1.25</v>
       </c>
-      <c r="N575" s="8" t="s">
+      <c r="N576" s="8" t="s">
         <v>4545</v>
       </c>
-      <c r="O575" s="8" t="s">
+      <c r="O576" s="8" t="s">
         <v>4546</v>
       </c>
-      <c r="P575" s="8"/>
-      <c r="Q575" s="8"/>
-      <c r="R575" s="8"/>
-      <c r="S575" s="8"/>
-      <c r="T575" s="8"/>
-      <c r="U575" s="8" t="s">
+      <c r="P576" s="8"/>
+      <c r="Q576" s="8"/>
+      <c r="R576" s="8"/>
+      <c r="S576" s="8"/>
+      <c r="T576" s="8"/>
+      <c r="U576" s="8" t="s">
         <v>4547</v>
       </c>
-      <c r="V575" s="8" t="s">
+      <c r="V576" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="W575" s="8" t="s">
+      <c r="W576" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="X575" s="8" t="s">
+      <c r="X576" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="Y575" s="10" t="s">
+      <c r="Y576" s="10" t="s">
         <v>272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Y575" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{4E491AA4-E984-4D63-AFB9-2179103AC520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D8673D9-9A56-4418-B7E5-C0BAFA7FFF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7585" uniqueCount="3447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="3443">
   <si>
     <t>emp_id</t>
   </si>
@@ -9102,9 +9102,6 @@
     <t>79.48%</t>
   </si>
   <si>
-    <t>110.76%</t>
-  </si>
-  <si>
     <t>135.42%</t>
   </si>
   <si>
@@ -9417,9 +9414,6 @@
     <t>104.71%</t>
   </si>
   <si>
-    <t>107.57%</t>
-  </si>
-  <si>
     <t>105.96%</t>
   </si>
   <si>
@@ -10308,9 +10302,6 @@
     <t>80.35%</t>
   </si>
   <si>
-    <t>139.30%</t>
-  </si>
-  <si>
     <t>88.19%</t>
   </si>
   <si>
@@ -10375,9 +10366,6 @@
   </si>
   <si>
     <t>86.31%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
   </si>
 </sst>
 </file>
@@ -10501,10 +10489,6 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10513,6 +10497,10 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10529,10 +10517,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10839,38 +10823,38 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="18" width="18" customWidth="1"/>
     <col min="19" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="14" style="12" customWidth="1"/>
+    <col min="21" max="21" width="14" style="10" customWidth="1"/>
     <col min="22" max="24" width="11" customWidth="1"/>
     <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>2915</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -10933,7 +10917,7 @@
       <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="9" t="s">
         <v>20</v>
       </c>
       <c r="V2" s="1" t="s">
@@ -11055,7 +11039,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="11" t="s">
         <v>2952</v>
       </c>
       <c r="V4" s="3">
@@ -11068,7 +11052,7 @@
         <v>44</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="10"/>
+      <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
@@ -11121,7 +11105,7 @@
       <c r="T5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" s="11" t="s">
         <v>2951</v>
       </c>
       <c r="V5" s="3">
@@ -11134,7 +11118,7 @@
         <v>35</v>
       </c>
       <c r="Y5" s="3"/>
-      <c r="Z5" s="10"/>
+      <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
@@ -11198,7 +11182,7 @@
         <v>35</v>
       </c>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="10"/>
+      <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
@@ -11260,7 +11244,7 @@
         <v>35</v>
       </c>
       <c r="Y7" s="3"/>
-      <c r="Z7" s="10"/>
+      <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
@@ -11322,7 +11306,7 @@
         <v>35</v>
       </c>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="10"/>
+      <c r="Z8" s="8"/>
     </row>
     <row r="9" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
@@ -11382,7 +11366,7 @@
         <v>35</v>
       </c>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="10"/>
+      <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
@@ -11444,7 +11428,7 @@
         <v>35</v>
       </c>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="10"/>
+      <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
@@ -11504,7 +11488,7 @@
         <v>35</v>
       </c>
       <c r="Y11" s="3"/>
-      <c r="Z11" s="10"/>
+      <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
@@ -11564,7 +11548,7 @@
         <v>35</v>
       </c>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="10"/>
+      <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
@@ -11624,7 +11608,7 @@
         <v>35</v>
       </c>
       <c r="Y13" s="3"/>
-      <c r="Z13" s="10"/>
+      <c r="Z13" s="8"/>
     </row>
     <row r="14" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
@@ -11686,7 +11670,7 @@
         <v>34</v>
       </c>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="10"/>
+      <c r="Z14" s="8"/>
     </row>
     <row r="15" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
@@ -11752,7 +11736,7 @@
         <v>34</v>
       </c>
       <c r="Y15" s="3"/>
-      <c r="Z15" s="10"/>
+      <c r="Z15" s="8"/>
     </row>
     <row r="16" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
@@ -11814,7 +11798,7 @@
         <v>44</v>
       </c>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="10"/>
+      <c r="Z16" s="8"/>
     </row>
     <row r="17" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
@@ -11876,7 +11860,7 @@
         <v>44</v>
       </c>
       <c r="Y17" s="3"/>
-      <c r="Z17" s="10"/>
+      <c r="Z17" s="8"/>
     </row>
     <row r="18" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
@@ -11938,7 +11922,7 @@
         <v>44</v>
       </c>
       <c r="Y18" s="3"/>
-      <c r="Z18" s="10"/>
+      <c r="Z18" s="8"/>
     </row>
     <row r="19" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
@@ -11998,7 +11982,7 @@
         <v>44</v>
       </c>
       <c r="Y19" s="3"/>
-      <c r="Z19" s="10"/>
+      <c r="Z19" s="8"/>
     </row>
     <row r="20" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
@@ -12058,7 +12042,7 @@
         <v>44</v>
       </c>
       <c r="Y20" s="3"/>
-      <c r="Z20" s="10"/>
+      <c r="Z20" s="8"/>
     </row>
     <row r="21" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
@@ -12118,7 +12102,7 @@
         <v>44</v>
       </c>
       <c r="Y21" s="3"/>
-      <c r="Z21" s="10"/>
+      <c r="Z21" s="8"/>
     </row>
     <row r="22" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
@@ -12178,7 +12162,7 @@
         <v>44</v>
       </c>
       <c r="Y22" s="3"/>
-      <c r="Z22" s="10"/>
+      <c r="Z22" s="8"/>
     </row>
     <row r="23" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
@@ -12240,7 +12224,7 @@
         <v>44</v>
       </c>
       <c r="Y23" s="3"/>
-      <c r="Z23" s="10"/>
+      <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
@@ -12302,7 +12286,7 @@
         <v>44</v>
       </c>
       <c r="Y24" s="3"/>
-      <c r="Z24" s="10"/>
+      <c r="Z24" s="8"/>
     </row>
     <row r="25" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
@@ -12362,7 +12346,7 @@
         <v>44</v>
       </c>
       <c r="Y25" s="3"/>
-      <c r="Z25" s="10"/>
+      <c r="Z25" s="8"/>
     </row>
     <row r="26" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
@@ -12422,7 +12406,7 @@
         <v>44</v>
       </c>
       <c r="Y26" s="3"/>
-      <c r="Z26" s="10"/>
+      <c r="Z26" s="8"/>
     </row>
     <row r="27" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
@@ -12482,7 +12466,7 @@
         <v>44</v>
       </c>
       <c r="Y27" s="3"/>
-      <c r="Z27" s="10"/>
+      <c r="Z27" s="8"/>
     </row>
     <row r="28" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
@@ -12542,7 +12526,7 @@
         <v>44</v>
       </c>
       <c r="Y28" s="3"/>
-      <c r="Z28" s="10"/>
+      <c r="Z28" s="8"/>
     </row>
     <row r="29" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
@@ -12604,7 +12588,7 @@
         <v>44</v>
       </c>
       <c r="Y29" s="3"/>
-      <c r="Z29" s="10"/>
+      <c r="Z29" s="8"/>
     </row>
     <row r="30" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
@@ -12668,7 +12652,7 @@
         <v>35</v>
       </c>
       <c r="Y30" s="3"/>
-      <c r="Z30" s="10"/>
+      <c r="Z30" s="8"/>
     </row>
     <row r="31" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
@@ -12730,7 +12714,7 @@
         <v>35</v>
       </c>
       <c r="Y31" s="3"/>
-      <c r="Z31" s="10"/>
+      <c r="Z31" s="8"/>
     </row>
     <row r="32" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
@@ -12796,7 +12780,7 @@
         <v>35</v>
       </c>
       <c r="Y32" s="3"/>
-      <c r="Z32" s="10"/>
+      <c r="Z32" s="8"/>
     </row>
     <row r="33" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
@@ -12856,7 +12840,7 @@
         <v>35</v>
       </c>
       <c r="Y33" s="3"/>
-      <c r="Z33" s="10"/>
+      <c r="Z33" s="8"/>
     </row>
     <row r="34" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
@@ -12916,7 +12900,7 @@
         <v>35</v>
       </c>
       <c r="Y34" s="3"/>
-      <c r="Z34" s="10"/>
+      <c r="Z34" s="8"/>
     </row>
     <row r="35" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
@@ -12976,7 +12960,7 @@
         <v>35</v>
       </c>
       <c r="Y35" s="3"/>
-      <c r="Z35" s="10"/>
+      <c r="Z35" s="8"/>
     </row>
     <row r="36" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
@@ -13040,7 +13024,7 @@
         <v>34</v>
       </c>
       <c r="Y36" s="3"/>
-      <c r="Z36" s="10"/>
+      <c r="Z36" s="8"/>
     </row>
     <row r="37" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
@@ -13104,7 +13088,7 @@
         <v>35</v>
       </c>
       <c r="Y37" s="3"/>
-      <c r="Z37" s="10"/>
+      <c r="Z37" s="8"/>
     </row>
     <row r="38" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
@@ -13166,7 +13150,7 @@
         <v>35</v>
       </c>
       <c r="Y38" s="3"/>
-      <c r="Z38" s="10"/>
+      <c r="Z38" s="8"/>
     </row>
     <row r="39" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
@@ -13228,7 +13212,7 @@
         <v>35</v>
       </c>
       <c r="Y39" s="3"/>
-      <c r="Z39" s="10"/>
+      <c r="Z39" s="8"/>
     </row>
     <row r="40" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
@@ -13288,7 +13272,7 @@
         <v>44</v>
       </c>
       <c r="Y40" s="3"/>
-      <c r="Z40" s="10"/>
+      <c r="Z40" s="8"/>
     </row>
     <row r="41" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
@@ -13348,7 +13332,7 @@
         <v>44</v>
       </c>
       <c r="Y41" s="3"/>
-      <c r="Z41" s="10"/>
+      <c r="Z41" s="8"/>
     </row>
     <row r="42" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
@@ -13410,7 +13394,7 @@
         <v>44</v>
       </c>
       <c r="Y42" s="3"/>
-      <c r="Z42" s="10"/>
+      <c r="Z42" s="8"/>
     </row>
     <row r="43" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
@@ -13470,7 +13454,7 @@
         <v>44</v>
       </c>
       <c r="Y43" s="3"/>
-      <c r="Z43" s="10"/>
+      <c r="Z43" s="8"/>
     </row>
     <row r="44" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
@@ -13526,7 +13510,7 @@
         <v>44</v>
       </c>
       <c r="Y44" s="3"/>
-      <c r="Z44" s="10"/>
+      <c r="Z44" s="8"/>
     </row>
     <row r="45" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
@@ -13582,7 +13566,7 @@
         <v>44</v>
       </c>
       <c r="Y45" s="3"/>
-      <c r="Z45" s="10"/>
+      <c r="Z45" s="8"/>
     </row>
     <row r="46" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
@@ -13638,7 +13622,7 @@
         <v>44</v>
       </c>
       <c r="Y46" s="3"/>
-      <c r="Z46" s="10"/>
+      <c r="Z46" s="8"/>
     </row>
     <row r="47" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
@@ -13700,7 +13684,7 @@
         <v>44</v>
       </c>
       <c r="Y47" s="3"/>
-      <c r="Z47" s="10"/>
+      <c r="Z47" s="8"/>
     </row>
     <row r="48" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
@@ -13762,7 +13746,7 @@
         <v>44</v>
       </c>
       <c r="Y48" s="3"/>
-      <c r="Z48" s="10"/>
+      <c r="Z48" s="8"/>
     </row>
     <row r="49" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
@@ -13822,7 +13806,7 @@
         <v>44</v>
       </c>
       <c r="Y49" s="3"/>
-      <c r="Z49" s="10"/>
+      <c r="Z49" s="8"/>
     </row>
     <row r="50" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
@@ -13882,7 +13866,7 @@
         <v>44</v>
       </c>
       <c r="Y50" s="3"/>
-      <c r="Z50" s="10"/>
+      <c r="Z50" s="8"/>
     </row>
     <row r="51" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
@@ -13942,7 +13926,7 @@
         <v>44</v>
       </c>
       <c r="Y51" s="3"/>
-      <c r="Z51" s="10"/>
+      <c r="Z51" s="8"/>
     </row>
     <row r="52" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
@@ -14002,7 +13986,7 @@
         <v>44</v>
       </c>
       <c r="Y52" s="3"/>
-      <c r="Z52" s="10"/>
+      <c r="Z52" s="8"/>
     </row>
     <row r="53" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
@@ -14062,7 +14046,7 @@
         <v>44</v>
       </c>
       <c r="Y53" s="3"/>
-      <c r="Z53" s="10"/>
+      <c r="Z53" s="8"/>
     </row>
     <row r="54" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
@@ -14122,7 +14106,7 @@
         <v>44</v>
       </c>
       <c r="Y54" s="3"/>
-      <c r="Z54" s="10"/>
+      <c r="Z54" s="8"/>
     </row>
     <row r="55" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
@@ -14182,7 +14166,7 @@
         <v>44</v>
       </c>
       <c r="Y55" s="3"/>
-      <c r="Z55" s="10"/>
+      <c r="Z55" s="8"/>
     </row>
     <row r="56" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
@@ -14244,7 +14228,7 @@
         <v>35</v>
       </c>
       <c r="Y56" s="3"/>
-      <c r="Z56" s="10"/>
+      <c r="Z56" s="8"/>
     </row>
     <row r="57" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
@@ -14310,7 +14294,7 @@
         <v>35</v>
       </c>
       <c r="Y57" s="3"/>
-      <c r="Z57" s="10"/>
+      <c r="Z57" s="8"/>
     </row>
     <row r="58" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
@@ -14376,7 +14360,7 @@
       <c r="Y58" s="3" t="s">
         <v>2910</v>
       </c>
-      <c r="Z58" s="10"/>
+      <c r="Z58" s="8"/>
     </row>
     <row r="59" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
@@ -14442,7 +14426,7 @@
         <v>35</v>
       </c>
       <c r="Y59" s="3"/>
-      <c r="Z59" s="10"/>
+      <c r="Z59" s="8"/>
     </row>
     <row r="60" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
@@ -14506,7 +14490,7 @@
         <v>35</v>
       </c>
       <c r="Y60" s="3"/>
-      <c r="Z60" s="10"/>
+      <c r="Z60" s="8"/>
     </row>
     <row r="61" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
@@ -14568,7 +14552,7 @@
         <v>44</v>
       </c>
       <c r="Y61" s="3"/>
-      <c r="Z61" s="10"/>
+      <c r="Z61" s="8"/>
     </row>
     <row r="62" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
@@ -14630,7 +14614,7 @@
         <v>44</v>
       </c>
       <c r="Y62" s="3"/>
-      <c r="Z62" s="10"/>
+      <c r="Z62" s="8"/>
     </row>
     <row r="63" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
@@ -14692,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="Y63" s="3"/>
-      <c r="Z63" s="10"/>
+      <c r="Z63" s="8"/>
     </row>
     <row r="64" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
@@ -14758,7 +14742,7 @@
       <c r="Y64" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Z64" s="10"/>
+      <c r="Z64" s="8"/>
     </row>
     <row r="65" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
@@ -14820,7 +14804,7 @@
         <v>44</v>
       </c>
       <c r="Y65" s="3"/>
-      <c r="Z65" s="10"/>
+      <c r="Z65" s="8"/>
     </row>
     <row r="66" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
@@ -14882,7 +14866,7 @@
         <v>44</v>
       </c>
       <c r="Y66" s="3"/>
-      <c r="Z66" s="10"/>
+      <c r="Z66" s="8"/>
     </row>
     <row r="67" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
@@ -14944,7 +14928,7 @@
         <v>44</v>
       </c>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="10"/>
+      <c r="Z67" s="8"/>
     </row>
     <row r="68" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
@@ -15006,7 +14990,7 @@
         <v>35</v>
       </c>
       <c r="Y68" s="3"/>
-      <c r="Z68" s="10"/>
+      <c r="Z68" s="8"/>
     </row>
     <row r="69" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
@@ -15070,7 +15054,7 @@
         <v>35</v>
       </c>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="10"/>
+      <c r="Z69" s="8"/>
     </row>
     <row r="70" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
@@ -15132,7 +15116,7 @@
         <v>35</v>
       </c>
       <c r="Y70" s="3"/>
-      <c r="Z70" s="10"/>
+      <c r="Z70" s="8"/>
     </row>
     <row r="71" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
@@ -15194,7 +15178,7 @@
         <v>44</v>
       </c>
       <c r="Y71" s="3"/>
-      <c r="Z71" s="10"/>
+      <c r="Z71" s="8"/>
     </row>
     <row r="72" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
@@ -15258,7 +15242,7 @@
         <v>35</v>
       </c>
       <c r="Y72" s="3"/>
-      <c r="Z72" s="10"/>
+      <c r="Z72" s="8"/>
     </row>
     <row r="73" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
@@ -15320,7 +15304,7 @@
         <v>44</v>
       </c>
       <c r="Y73" s="3"/>
-      <c r="Z73" s="10"/>
+      <c r="Z73" s="8"/>
     </row>
     <row r="74" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
@@ -15382,7 +15366,7 @@
         <v>44</v>
       </c>
       <c r="Y74" s="3"/>
-      <c r="Z74" s="10"/>
+      <c r="Z74" s="8"/>
     </row>
     <row r="75" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
@@ -15444,7 +15428,7 @@
         <v>44</v>
       </c>
       <c r="Y75" s="3"/>
-      <c r="Z75" s="10"/>
+      <c r="Z75" s="8"/>
     </row>
     <row r="76" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
@@ -15506,7 +15490,7 @@
         <v>35</v>
       </c>
       <c r="Y76" s="3"/>
-      <c r="Z76" s="10"/>
+      <c r="Z76" s="8"/>
     </row>
     <row r="77" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
@@ -15568,7 +15552,7 @@
         <v>44</v>
       </c>
       <c r="Y77" s="3"/>
-      <c r="Z77" s="10"/>
+      <c r="Z77" s="8"/>
     </row>
     <row r="78" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
@@ -15634,7 +15618,7 @@
         <v>35</v>
       </c>
       <c r="Y78" s="3"/>
-      <c r="Z78" s="10"/>
+      <c r="Z78" s="8"/>
     </row>
     <row r="79" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
@@ -15683,9 +15667,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
-      <c r="U79" s="7" t="s">
-        <v>3021</v>
-      </c>
+      <c r="U79" s="7"/>
       <c r="V79" s="3">
         <v>3</v>
       </c>
@@ -15698,7 +15680,7 @@
       <c r="Y79" s="3">
         <v>21062524</v>
       </c>
-      <c r="Z79" s="10"/>
+      <c r="Z79" s="8"/>
     </row>
     <row r="80" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
@@ -15748,7 +15730,7 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="7" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="V80" s="3">
         <v>2</v>
@@ -15760,7 +15742,7 @@
         <v>44</v>
       </c>
       <c r="Y80" s="3"/>
-      <c r="Z80" s="10"/>
+      <c r="Z80" s="8"/>
     </row>
     <row r="81" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
@@ -15810,7 +15792,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="7" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="V81" s="3">
         <v>2</v>
@@ -15822,7 +15804,7 @@
         <v>44</v>
       </c>
       <c r="Y81" s="3"/>
-      <c r="Z81" s="10"/>
+      <c r="Z81" s="8"/>
     </row>
     <row r="82" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
@@ -15876,7 +15858,7 @@
         <v>53</v>
       </c>
       <c r="U82" s="7" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="V82" s="3">
         <v>3</v>
@@ -15888,7 +15870,7 @@
         <v>35</v>
       </c>
       <c r="Y82" s="3"/>
-      <c r="Z82" s="10"/>
+      <c r="Z82" s="8"/>
     </row>
     <row r="83" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
@@ -15942,7 +15924,7 @@
         <v>74</v>
       </c>
       <c r="U83" s="7" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="V83" s="3">
         <v>3</v>
@@ -15954,7 +15936,7 @@
         <v>35</v>
       </c>
       <c r="Y83" s="3"/>
-      <c r="Z83" s="10"/>
+      <c r="Z83" s="8"/>
     </row>
     <row r="84" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
@@ -16008,7 +15990,7 @@
         <v>74</v>
       </c>
       <c r="U84" s="7" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="V84" s="3">
         <v>3</v>
@@ -16020,7 +16002,7 @@
         <v>35</v>
       </c>
       <c r="Y84" s="3"/>
-      <c r="Z84" s="10"/>
+      <c r="Z84" s="8"/>
     </row>
     <row r="85" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
@@ -16070,7 +16052,7 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
       <c r="U85" s="7" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="V85" s="3">
         <v>3</v>
@@ -16082,7 +16064,7 @@
         <v>44</v>
       </c>
       <c r="Y85" s="3"/>
-      <c r="Z85" s="10"/>
+      <c r="Z85" s="8"/>
     </row>
     <row r="86" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
@@ -16136,7 +16118,7 @@
         <v>53</v>
       </c>
       <c r="U86" s="7" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="V86" s="3">
         <v>3</v>
@@ -16148,7 +16130,7 @@
         <v>35</v>
       </c>
       <c r="Y86" s="3"/>
-      <c r="Z86" s="10"/>
+      <c r="Z86" s="8"/>
     </row>
     <row r="87" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
@@ -16194,7 +16176,7 @@
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
       <c r="U87" s="7" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="V87" s="3">
         <v>3</v>
@@ -16206,7 +16188,7 @@
         <v>35</v>
       </c>
       <c r="Y87" s="3"/>
-      <c r="Z87" s="10"/>
+      <c r="Z87" s="8"/>
     </row>
     <row r="88" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
@@ -16258,7 +16240,7 @@
         <v>74</v>
       </c>
       <c r="U88" s="7" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="V88" s="3">
         <v>3</v>
@@ -16270,7 +16252,7 @@
         <v>35</v>
       </c>
       <c r="Y88" s="3"/>
-      <c r="Z88" s="10"/>
+      <c r="Z88" s="8"/>
     </row>
     <row r="89" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
@@ -16320,7 +16302,7 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
       <c r="U89" s="7" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="V89" s="3">
         <v>3</v>
@@ -16332,7 +16314,7 @@
         <v>203</v>
       </c>
       <c r="Y89" s="3"/>
-      <c r="Z89" s="10"/>
+      <c r="Z89" s="8"/>
     </row>
     <row r="90" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
@@ -16382,7 +16364,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="7" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="V90" s="3">
         <v>3</v>
@@ -16394,7 +16376,7 @@
         <v>35</v>
       </c>
       <c r="Y90" s="3"/>
-      <c r="Z90" s="10"/>
+      <c r="Z90" s="8"/>
     </row>
     <row r="91" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
@@ -16444,7 +16426,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
       <c r="U91" s="7" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>44</v>
@@ -16456,7 +16438,7 @@
         <v>44</v>
       </c>
       <c r="Y91" s="3"/>
-      <c r="Z91" s="10"/>
+      <c r="Z91" s="8"/>
     </row>
     <row r="92" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
@@ -16506,7 +16488,7 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
       <c r="U92" s="7" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="V92" s="3" t="s">
         <v>44</v>
@@ -16518,7 +16500,7 @@
         <v>44</v>
       </c>
       <c r="Y92" s="3"/>
-      <c r="Z92" s="10"/>
+      <c r="Z92" s="8"/>
     </row>
     <row r="93" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
@@ -16568,7 +16550,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
       <c r="U93" s="7" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="V93" s="3" t="s">
         <v>44</v>
@@ -16580,7 +16562,7 @@
         <v>44</v>
       </c>
       <c r="Y93" s="3"/>
-      <c r="Z93" s="10"/>
+      <c r="Z93" s="8"/>
     </row>
     <row r="94" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
@@ -16630,7 +16612,7 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
       <c r="U94" s="7" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>44</v>
@@ -16642,7 +16624,7 @@
         <v>44</v>
       </c>
       <c r="Y94" s="3"/>
-      <c r="Z94" s="10"/>
+      <c r="Z94" s="8"/>
     </row>
     <row r="95" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
@@ -16692,7 +16674,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="7" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="V95" s="3" t="s">
         <v>44</v>
@@ -16704,7 +16686,7 @@
         <v>44</v>
       </c>
       <c r="Y95" s="3"/>
-      <c r="Z95" s="10"/>
+      <c r="Z95" s="8"/>
     </row>
     <row r="96" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
@@ -16758,7 +16740,7 @@
         <v>520</v>
       </c>
       <c r="U96" s="7" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="V96" s="3">
         <v>3</v>
@@ -16770,7 +16752,7 @@
         <v>35</v>
       </c>
       <c r="Y96" s="3"/>
-      <c r="Z96" s="10"/>
+      <c r="Z96" s="8"/>
     </row>
     <row r="97" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
@@ -16820,7 +16802,7 @@
         <v>74</v>
       </c>
       <c r="U97" s="7" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="V97" s="3">
         <v>3</v>
@@ -16832,7 +16814,7 @@
         <v>35</v>
       </c>
       <c r="Y97" s="3"/>
-      <c r="Z97" s="10"/>
+      <c r="Z97" s="8"/>
     </row>
     <row r="98" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
@@ -16886,7 +16868,7 @@
         <v>74</v>
       </c>
       <c r="U98" s="7" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="V98" s="3">
         <v>3</v>
@@ -16898,7 +16880,7 @@
         <v>35</v>
       </c>
       <c r="Y98" s="3"/>
-      <c r="Z98" s="10"/>
+      <c r="Z98" s="8"/>
     </row>
     <row r="99" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
@@ -16950,7 +16932,7 @@
       </c>
       <c r="T99" s="3"/>
       <c r="U99" s="7" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="V99" s="3">
         <v>3</v>
@@ -16962,7 +16944,7 @@
         <v>35</v>
       </c>
       <c r="Y99" s="3"/>
-      <c r="Z99" s="10"/>
+      <c r="Z99" s="8"/>
     </row>
     <row r="100" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
@@ -17012,7 +16994,7 @@
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
       <c r="U100" s="7" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="V100" s="3">
         <v>3</v>
@@ -17024,7 +17006,7 @@
         <v>44</v>
       </c>
       <c r="Y100" s="3"/>
-      <c r="Z100" s="10"/>
+      <c r="Z100" s="8"/>
     </row>
     <row r="101" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
@@ -17074,7 +17056,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="7" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="V101" s="3">
         <v>3</v>
@@ -17086,7 +17068,7 @@
         <v>44</v>
       </c>
       <c r="Y101" s="3"/>
-      <c r="Z101" s="10"/>
+      <c r="Z101" s="8"/>
     </row>
     <row r="102" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
@@ -17136,7 +17118,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="7" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>44</v>
@@ -17148,7 +17130,7 @@
         <v>44</v>
       </c>
       <c r="Y102" s="3"/>
-      <c r="Z102" s="10"/>
+      <c r="Z102" s="8"/>
     </row>
     <row r="103" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
@@ -17202,7 +17184,7 @@
         <v>33</v>
       </c>
       <c r="U103" s="7" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="V103" s="3">
         <v>3</v>
@@ -17214,7 +17196,7 @@
         <v>35</v>
       </c>
       <c r="Y103" s="3"/>
-      <c r="Z103" s="10"/>
+      <c r="Z103" s="8"/>
     </row>
     <row r="104" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
@@ -17264,7 +17246,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
       <c r="U104" s="7" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="V104" s="3">
         <v>3</v>
@@ -17276,7 +17258,7 @@
         <v>203</v>
       </c>
       <c r="Y104" s="3"/>
-      <c r="Z104" s="10"/>
+      <c r="Z104" s="8"/>
     </row>
     <row r="105" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
@@ -17328,7 +17310,7 @@
       </c>
       <c r="T105" s="3"/>
       <c r="U105" s="7" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="V105" s="3">
         <v>3</v>
@@ -17340,7 +17322,7 @@
         <v>203</v>
       </c>
       <c r="Y105" s="3"/>
-      <c r="Z105" s="10"/>
+      <c r="Z105" s="8"/>
     </row>
     <row r="106" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
@@ -17390,7 +17372,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
       <c r="U106" s="7" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="V106" s="3">
         <v>3</v>
@@ -17402,7 +17384,7 @@
         <v>44</v>
       </c>
       <c r="Y106" s="3"/>
-      <c r="Z106" s="10"/>
+      <c r="Z106" s="8"/>
     </row>
     <row r="107" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
@@ -17448,7 +17430,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="7" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="V107" s="3">
         <v>2</v>
@@ -17460,7 +17442,7 @@
         <v>44</v>
       </c>
       <c r="Y107" s="3"/>
-      <c r="Z107" s="10"/>
+      <c r="Z107" s="8"/>
     </row>
     <row r="108" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
@@ -17510,7 +17492,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="7" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="V108" s="3">
         <v>3</v>
@@ -17522,7 +17504,7 @@
         <v>44</v>
       </c>
       <c r="Y108" s="3"/>
-      <c r="Z108" s="10"/>
+      <c r="Z108" s="8"/>
     </row>
     <row r="109" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
@@ -17574,7 +17556,7 @@
         <v>2950</v>
       </c>
       <c r="U109" s="7" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="V109" s="3">
         <v>3</v>
@@ -17586,7 +17568,7 @@
         <v>44</v>
       </c>
       <c r="Y109" s="3"/>
-      <c r="Z109" s="10"/>
+      <c r="Z109" s="8"/>
     </row>
     <row r="110" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
@@ -17636,7 +17618,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="7" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="V110" s="3">
         <v>3</v>
@@ -17648,7 +17630,7 @@
         <v>44</v>
       </c>
       <c r="Y110" s="3"/>
-      <c r="Z110" s="10"/>
+      <c r="Z110" s="8"/>
     </row>
     <row r="111" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
@@ -17694,7 +17676,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="7" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="V111" s="3">
         <v>3</v>
@@ -17706,7 +17688,7 @@
         <v>35</v>
       </c>
       <c r="Y111" s="3"/>
-      <c r="Z111" s="10"/>
+      <c r="Z111" s="8"/>
     </row>
     <row r="112" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
@@ -17756,7 +17738,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="7" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="V112" s="3">
         <v>3</v>
@@ -17768,7 +17750,7 @@
         <v>44</v>
       </c>
       <c r="Y112" s="3"/>
-      <c r="Z112" s="10"/>
+      <c r="Z112" s="8"/>
     </row>
     <row r="113" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
@@ -17822,7 +17804,7 @@
         <v>240</v>
       </c>
       <c r="U113" s="7" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="V113" s="3">
         <v>3</v>
@@ -17834,7 +17816,7 @@
         <v>35</v>
       </c>
       <c r="Y113" s="3"/>
-      <c r="Z113" s="10"/>
+      <c r="Z113" s="8"/>
     </row>
     <row r="114" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
@@ -17884,7 +17866,7 @@
         <v>397</v>
       </c>
       <c r="U114" s="7" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="V114" s="3">
         <v>3</v>
@@ -17896,7 +17878,7 @@
         <v>35</v>
       </c>
       <c r="Y114" s="3"/>
-      <c r="Z114" s="10"/>
+      <c r="Z114" s="8"/>
     </row>
     <row r="115" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
@@ -17946,7 +17928,7 @@
         <v>397</v>
       </c>
       <c r="U115" s="7" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="V115" s="3">
         <v>3</v>
@@ -17958,7 +17940,7 @@
         <v>35</v>
       </c>
       <c r="Y115" s="3"/>
-      <c r="Z115" s="10"/>
+      <c r="Z115" s="8"/>
     </row>
     <row r="116" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
@@ -18010,7 +17992,7 @@
         <v>33</v>
       </c>
       <c r="U116" s="7" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="V116" s="3">
         <v>3</v>
@@ -18022,7 +18004,7 @@
         <v>35</v>
       </c>
       <c r="Y116" s="3"/>
-      <c r="Z116" s="10"/>
+      <c r="Z116" s="8"/>
     </row>
     <row r="117" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
@@ -18072,7 +18054,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="7" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="V117" s="3" t="s">
         <v>44</v>
@@ -18084,7 +18066,7 @@
         <v>44</v>
       </c>
       <c r="Y117" s="3"/>
-      <c r="Z117" s="10"/>
+      <c r="Z117" s="8"/>
     </row>
     <row r="118" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
@@ -18138,7 +18120,7 @@
         <v>74</v>
       </c>
       <c r="U118" s="7" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="V118" s="3">
         <v>3</v>
@@ -18150,7 +18132,7 @@
         <v>35</v>
       </c>
       <c r="Y118" s="3"/>
-      <c r="Z118" s="10"/>
+      <c r="Z118" s="8"/>
     </row>
     <row r="119" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
@@ -18202,7 +18184,7 @@
       </c>
       <c r="T119" s="3"/>
       <c r="U119" s="7" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="V119" s="3">
         <v>3</v>
@@ -18214,7 +18196,7 @@
         <v>35</v>
       </c>
       <c r="Y119" s="3"/>
-      <c r="Z119" s="10"/>
+      <c r="Z119" s="8"/>
     </row>
     <row r="120" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
@@ -18260,7 +18242,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
       <c r="U120" s="7" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="V120" s="3">
         <v>3</v>
@@ -18272,7 +18254,7 @@
         <v>44</v>
       </c>
       <c r="Y120" s="3"/>
-      <c r="Z120" s="10"/>
+      <c r="Z120" s="8"/>
     </row>
     <row r="121" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
@@ -18318,7 +18300,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="7" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="V121" s="3">
         <v>3</v>
@@ -18330,7 +18312,7 @@
         <v>44</v>
       </c>
       <c r="Y121" s="3"/>
-      <c r="Z121" s="10"/>
+      <c r="Z121" s="8"/>
     </row>
     <row r="122" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
@@ -18376,7 +18358,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="7" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="V122" s="3" t="s">
         <v>44</v>
@@ -18388,7 +18370,7 @@
         <v>44</v>
       </c>
       <c r="Y122" s="3"/>
-      <c r="Z122" s="10"/>
+      <c r="Z122" s="8"/>
     </row>
     <row r="123" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
@@ -18434,7 +18416,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="7" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="V123" s="3">
         <v>3</v>
@@ -18446,7 +18428,7 @@
         <v>35</v>
       </c>
       <c r="Y123" s="3"/>
-      <c r="Z123" s="10"/>
+      <c r="Z123" s="8"/>
     </row>
     <row r="124" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
@@ -18500,7 +18482,7 @@
         <v>53</v>
       </c>
       <c r="U124" s="7" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="V124" s="3">
         <v>3</v>
@@ -18512,7 +18494,7 @@
         <v>35</v>
       </c>
       <c r="Y124" s="3"/>
-      <c r="Z124" s="10"/>
+      <c r="Z124" s="8"/>
     </row>
     <row r="125" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
@@ -18566,7 +18548,7 @@
         <v>240</v>
       </c>
       <c r="U125" s="7" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="V125" s="3">
         <v>4</v>
@@ -18578,7 +18560,7 @@
         <v>35</v>
       </c>
       <c r="Y125" s="3"/>
-      <c r="Z125" s="10"/>
+      <c r="Z125" s="8"/>
     </row>
     <row r="126" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
@@ -18630,7 +18612,7 @@
         <v>33</v>
       </c>
       <c r="U126" s="7" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="V126" s="3">
         <v>3</v>
@@ -18642,7 +18624,7 @@
         <v>35</v>
       </c>
       <c r="Y126" s="3"/>
-      <c r="Z126" s="10"/>
+      <c r="Z126" s="8"/>
     </row>
     <row r="127" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
@@ -18692,7 +18674,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
       <c r="U127" s="7" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="V127" s="3">
         <v>3</v>
@@ -18704,7 +18686,7 @@
         <v>44</v>
       </c>
       <c r="Y127" s="3"/>
-      <c r="Z127" s="10"/>
+      <c r="Z127" s="8"/>
     </row>
     <row r="128" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
@@ -18750,7 +18732,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="7" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="V128" s="3">
         <v>3</v>
@@ -18762,7 +18744,7 @@
         <v>44</v>
       </c>
       <c r="Y128" s="3"/>
-      <c r="Z128" s="10"/>
+      <c r="Z128" s="8"/>
     </row>
     <row r="129" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
@@ -18812,7 +18794,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="7" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="V129" s="3">
         <v>3</v>
@@ -18824,7 +18806,7 @@
         <v>44</v>
       </c>
       <c r="Y129" s="3"/>
-      <c r="Z129" s="10"/>
+      <c r="Z129" s="8"/>
     </row>
     <row r="130" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
@@ -18870,7 +18852,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="7" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="V130" s="3">
         <v>3</v>
@@ -18882,7 +18864,7 @@
         <v>44</v>
       </c>
       <c r="Y130" s="3"/>
-      <c r="Z130" s="10"/>
+      <c r="Z130" s="8"/>
     </row>
     <row r="131" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
@@ -18932,7 +18914,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
       <c r="U131" s="7" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="V131" s="3">
         <v>3</v>
@@ -18944,7 +18926,7 @@
         <v>44</v>
       </c>
       <c r="Y131" s="3"/>
-      <c r="Z131" s="10"/>
+      <c r="Z131" s="8"/>
     </row>
     <row r="132" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
@@ -18994,7 +18976,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
       <c r="U132" s="7" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="V132" s="3" t="s">
         <v>44</v>
@@ -19006,7 +18988,7 @@
         <v>44</v>
       </c>
       <c r="Y132" s="3"/>
-      <c r="Z132" s="10"/>
+      <c r="Z132" s="8"/>
     </row>
     <row r="133" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
@@ -19060,7 +19042,7 @@
         <v>240</v>
       </c>
       <c r="U133" s="7" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="V133" s="3">
         <v>3</v>
@@ -19072,7 +19054,7 @@
         <v>35</v>
       </c>
       <c r="Y133" s="3"/>
-      <c r="Z133" s="10"/>
+      <c r="Z133" s="8"/>
     </row>
     <row r="134" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
@@ -19124,7 +19106,7 @@
         <v>33</v>
       </c>
       <c r="U134" s="7" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="V134" s="3">
         <v>3</v>
@@ -19136,7 +19118,7 @@
         <v>35</v>
       </c>
       <c r="Y134" s="3"/>
-      <c r="Z134" s="10"/>
+      <c r="Z134" s="8"/>
     </row>
     <row r="135" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
@@ -19188,7 +19170,7 @@
         <v>33</v>
       </c>
       <c r="U135" s="7" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="V135" s="3">
         <v>3</v>
@@ -19200,7 +19182,7 @@
         <v>44</v>
       </c>
       <c r="Y135" s="3"/>
-      <c r="Z135" s="10"/>
+      <c r="Z135" s="8"/>
     </row>
     <row r="136" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
@@ -19250,7 +19232,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="7" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="V136" s="3">
         <v>3</v>
@@ -19262,7 +19244,7 @@
         <v>44</v>
       </c>
       <c r="Y136" s="3"/>
-      <c r="Z136" s="10"/>
+      <c r="Z136" s="8"/>
     </row>
     <row r="137" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
@@ -19308,7 +19290,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="7" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="V137" s="3">
         <v>3</v>
@@ -19320,7 +19302,7 @@
         <v>44</v>
       </c>
       <c r="Y137" s="3"/>
-      <c r="Z137" s="10"/>
+      <c r="Z137" s="8"/>
     </row>
     <row r="138" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
@@ -19370,7 +19352,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="V138" s="3" t="s">
         <v>44</v>
@@ -19382,7 +19364,7 @@
         <v>44</v>
       </c>
       <c r="Y138" s="3"/>
-      <c r="Z138" s="10"/>
+      <c r="Z138" s="8"/>
     </row>
     <row r="139" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
@@ -19432,7 +19414,7 @@
         <v>314</v>
       </c>
       <c r="U139" s="7" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="V139" s="3">
         <v>3</v>
@@ -19444,7 +19426,7 @@
         <v>35</v>
       </c>
       <c r="Y139" s="3"/>
-      <c r="Z139" s="10"/>
+      <c r="Z139" s="8"/>
     </row>
     <row r="140" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
@@ -19494,7 +19476,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="7" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="V140" s="3">
         <v>3</v>
@@ -19506,7 +19488,7 @@
         <v>203</v>
       </c>
       <c r="Y140" s="3"/>
-      <c r="Z140" s="10"/>
+      <c r="Z140" s="8"/>
     </row>
     <row r="141" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
@@ -19556,7 +19538,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="7" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="V141" s="3">
         <v>3</v>
@@ -19568,7 +19550,7 @@
         <v>35</v>
       </c>
       <c r="Y141" s="3"/>
-      <c r="Z141" s="10"/>
+      <c r="Z141" s="8"/>
     </row>
     <row r="142" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
@@ -19614,7 +19596,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="7" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="V142" s="3">
         <v>3</v>
@@ -19626,7 +19608,7 @@
         <v>44</v>
       </c>
       <c r="Y142" s="3"/>
-      <c r="Z142" s="10"/>
+      <c r="Z142" s="8"/>
     </row>
     <row r="143" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
@@ -19676,7 +19658,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="7" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="V143" s="3">
         <v>3</v>
@@ -19688,7 +19670,7 @@
         <v>44</v>
       </c>
       <c r="Y143" s="3"/>
-      <c r="Z143" s="10"/>
+      <c r="Z143" s="8"/>
     </row>
     <row r="144" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
@@ -19738,7 +19720,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="7" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="V144" s="3" t="s">
         <v>44</v>
@@ -19750,7 +19732,7 @@
         <v>44</v>
       </c>
       <c r="Y144" s="3"/>
-      <c r="Z144" s="10"/>
+      <c r="Z144" s="8"/>
     </row>
     <row r="145" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
@@ -19800,7 +19782,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="7" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="V145" s="3" t="s">
         <v>44</v>
@@ -19812,7 +19794,7 @@
         <v>44</v>
       </c>
       <c r="Y145" s="3"/>
-      <c r="Z145" s="10"/>
+      <c r="Z145" s="8"/>
     </row>
     <row r="146" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
@@ -19862,7 +19844,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="7" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="V146" s="3" t="s">
         <v>44</v>
@@ -19874,7 +19856,7 @@
         <v>44</v>
       </c>
       <c r="Y146" s="3"/>
-      <c r="Z146" s="10"/>
+      <c r="Z146" s="8"/>
     </row>
     <row r="147" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
@@ -19928,7 +19910,7 @@
         <v>52</v>
       </c>
       <c r="U147" s="7" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="V147" s="3">
         <v>2</v>
@@ -19940,7 +19922,7 @@
         <v>35</v>
       </c>
       <c r="Y147" s="3"/>
-      <c r="Z147" s="10"/>
+      <c r="Z147" s="8"/>
     </row>
     <row r="148" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
@@ -19992,7 +19974,7 @@
         <v>239</v>
       </c>
       <c r="U148" s="7" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="V148" s="3">
         <v>2</v>
@@ -20004,7 +19986,7 @@
         <v>35</v>
       </c>
       <c r="Y148" s="3"/>
-      <c r="Z148" s="10"/>
+      <c r="Z148" s="8"/>
     </row>
     <row r="149" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
@@ -20052,7 +20034,7 @@
       </c>
       <c r="T149" s="3"/>
       <c r="U149" s="7" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="V149" s="3">
         <v>3</v>
@@ -20064,7 +20046,7 @@
         <v>35</v>
       </c>
       <c r="Y149" s="3"/>
-      <c r="Z149" s="10"/>
+      <c r="Z149" s="8"/>
     </row>
     <row r="150" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
@@ -20116,7 +20098,7 @@
       </c>
       <c r="T150" s="3"/>
       <c r="U150" s="7" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="V150" s="3">
         <v>2</v>
@@ -20128,7 +20110,7 @@
         <v>35</v>
       </c>
       <c r="Y150" s="3"/>
-      <c r="Z150" s="10"/>
+      <c r="Z150" s="8"/>
     </row>
     <row r="151" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
@@ -20182,7 +20164,7 @@
         <v>74</v>
       </c>
       <c r="U151" s="7" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="V151" s="3">
         <v>2</v>
@@ -20194,7 +20176,7 @@
         <v>35</v>
       </c>
       <c r="Y151" s="3"/>
-      <c r="Z151" s="10"/>
+      <c r="Z151" s="8"/>
     </row>
     <row r="152" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
@@ -20248,7 +20230,7 @@
         <v>33</v>
       </c>
       <c r="U152" s="7" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="V152" s="3">
         <v>3</v>
@@ -20260,7 +20242,7 @@
         <v>35</v>
       </c>
       <c r="Y152" s="3"/>
-      <c r="Z152" s="10"/>
+      <c r="Z152" s="8"/>
     </row>
     <row r="153" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
@@ -20310,7 +20292,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="7" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="V153" s="3">
         <v>3</v>
@@ -20322,7 +20304,7 @@
         <v>44</v>
       </c>
       <c r="Y153" s="3"/>
-      <c r="Z153" s="10"/>
+      <c r="Z153" s="8"/>
     </row>
     <row r="154" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
@@ -20372,7 +20354,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="7" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="V154" s="3">
         <v>3</v>
@@ -20384,7 +20366,7 @@
         <v>35</v>
       </c>
       <c r="Y154" s="3"/>
-      <c r="Z154" s="10"/>
+      <c r="Z154" s="8"/>
     </row>
     <row r="155" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
@@ -20436,7 +20418,7 @@
       </c>
       <c r="T155" s="3"/>
       <c r="U155" s="7" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="V155" s="3">
         <v>3</v>
@@ -20448,7 +20430,7 @@
         <v>35</v>
       </c>
       <c r="Y155" s="3"/>
-      <c r="Z155" s="10"/>
+      <c r="Z155" s="8"/>
     </row>
     <row r="156" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
@@ -20502,7 +20484,7 @@
         <v>33</v>
       </c>
       <c r="U156" s="7" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="V156" s="3">
         <v>3</v>
@@ -20514,7 +20496,7 @@
         <v>35</v>
       </c>
       <c r="Y156" s="3"/>
-      <c r="Z156" s="10"/>
+      <c r="Z156" s="8"/>
     </row>
     <row r="157" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
@@ -20566,7 +20548,7 @@
       </c>
       <c r="T157" s="3"/>
       <c r="U157" s="7" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="V157" s="3">
         <v>2</v>
@@ -20578,7 +20560,7 @@
         <v>35</v>
       </c>
       <c r="Y157" s="3"/>
-      <c r="Z157" s="10"/>
+      <c r="Z157" s="8"/>
     </row>
     <row r="158" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
@@ -20632,7 +20614,7 @@
         <v>33</v>
       </c>
       <c r="U158" s="7" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="V158" s="3">
         <v>3</v>
@@ -20644,7 +20626,7 @@
         <v>35</v>
       </c>
       <c r="Y158" s="3"/>
-      <c r="Z158" s="10"/>
+      <c r="Z158" s="8"/>
     </row>
     <row r="159" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
@@ -20696,7 +20678,7 @@
       </c>
       <c r="T159" s="3"/>
       <c r="U159" s="7" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="V159" s="3">
         <v>3</v>
@@ -20708,7 +20690,7 @@
         <v>35</v>
       </c>
       <c r="Y159" s="3"/>
-      <c r="Z159" s="10"/>
+      <c r="Z159" s="8"/>
     </row>
     <row r="160" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
@@ -20760,7 +20742,7 @@
       </c>
       <c r="T160" s="3"/>
       <c r="U160" s="7" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="V160" s="3">
         <v>3</v>
@@ -20772,7 +20754,7 @@
         <v>35</v>
       </c>
       <c r="Y160" s="3"/>
-      <c r="Z160" s="10"/>
+      <c r="Z160" s="8"/>
     </row>
     <row r="161" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3">
@@ -20818,7 +20800,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="7" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="V161" s="3">
         <v>3</v>
@@ -20830,7 +20812,7 @@
         <v>44</v>
       </c>
       <c r="Y161" s="3"/>
-      <c r="Z161" s="10"/>
+      <c r="Z161" s="8"/>
     </row>
     <row r="162" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3">
@@ -20884,7 +20866,7 @@
         <v>314</v>
       </c>
       <c r="U162" s="7" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="V162" s="3">
         <v>3</v>
@@ -20896,7 +20878,7 @@
         <v>35</v>
       </c>
       <c r="Y162" s="3"/>
-      <c r="Z162" s="10"/>
+      <c r="Z162" s="8"/>
     </row>
     <row r="163" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
@@ -20948,7 +20930,7 @@
       </c>
       <c r="T163" s="3"/>
       <c r="U163" s="7" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="V163" s="3">
         <v>3</v>
@@ -20960,7 +20942,7 @@
         <v>35</v>
       </c>
       <c r="Y163" s="3"/>
-      <c r="Z163" s="10"/>
+      <c r="Z163" s="8"/>
     </row>
     <row r="164" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
@@ -21014,7 +20996,7 @@
         <v>74</v>
       </c>
       <c r="U164" s="7" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="V164" s="3">
         <v>3</v>
@@ -21026,7 +21008,7 @@
         <v>35</v>
       </c>
       <c r="Y164" s="3"/>
-      <c r="Z164" s="10"/>
+      <c r="Z164" s="8"/>
     </row>
     <row r="165" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
@@ -21076,7 +21058,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="7" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="V165" s="3">
         <v>3</v>
@@ -21088,7 +21070,7 @@
         <v>35</v>
       </c>
       <c r="Y165" s="3"/>
-      <c r="Z165" s="10"/>
+      <c r="Z165" s="8"/>
     </row>
     <row r="166" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3">
@@ -21138,7 +21120,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="7" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="V166" s="3">
         <v>2</v>
@@ -21150,7 +21132,7 @@
         <v>35</v>
       </c>
       <c r="Y166" s="3"/>
-      <c r="Z166" s="10"/>
+      <c r="Z166" s="8"/>
     </row>
     <row r="167" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
@@ -21204,7 +21186,7 @@
         <v>314</v>
       </c>
       <c r="U167" s="7" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="V167" s="3">
         <v>2</v>
@@ -21216,7 +21198,7 @@
         <v>35</v>
       </c>
       <c r="Y167" s="3"/>
-      <c r="Z167" s="10"/>
+      <c r="Z167" s="8"/>
     </row>
     <row r="168" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
@@ -21270,7 +21252,7 @@
         <v>74</v>
       </c>
       <c r="U168" s="7" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="V168" s="3">
         <v>3</v>
@@ -21282,7 +21264,7 @@
         <v>35</v>
       </c>
       <c r="Y168" s="3"/>
-      <c r="Z168" s="10"/>
+      <c r="Z168" s="8"/>
     </row>
     <row r="169" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
@@ -21334,7 +21316,7 @@
       </c>
       <c r="T169" s="3"/>
       <c r="U169" s="7" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="V169" s="3">
         <v>3</v>
@@ -21346,7 +21328,7 @@
         <v>34</v>
       </c>
       <c r="Y169" s="3"/>
-      <c r="Z169" s="10"/>
+      <c r="Z169" s="8"/>
     </row>
     <row r="170" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3">
@@ -21398,7 +21380,7 @@
         <v>2950</v>
       </c>
       <c r="U170" s="7" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="V170" s="3">
         <v>3</v>
@@ -21410,7 +21392,7 @@
         <v>44</v>
       </c>
       <c r="Y170" s="3"/>
-      <c r="Z170" s="10"/>
+      <c r="Z170" s="8"/>
     </row>
     <row r="171" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
@@ -21460,7 +21442,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="7" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="V171" s="3">
         <v>3</v>
@@ -21472,7 +21454,7 @@
         <v>44</v>
       </c>
       <c r="Y171" s="3"/>
-      <c r="Z171" s="10"/>
+      <c r="Z171" s="8"/>
     </row>
     <row r="172" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
@@ -21522,7 +21504,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="7" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="V172" s="3">
         <v>3</v>
@@ -21534,7 +21516,7 @@
         <v>44</v>
       </c>
       <c r="Y172" s="3"/>
-      <c r="Z172" s="10"/>
+      <c r="Z172" s="8"/>
     </row>
     <row r="173" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
@@ -21584,7 +21566,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="7" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="V173" s="3">
         <v>3</v>
@@ -21596,7 +21578,7 @@
         <v>44</v>
       </c>
       <c r="Y173" s="3"/>
-      <c r="Z173" s="10"/>
+      <c r="Z173" s="8"/>
     </row>
     <row r="174" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
@@ -21646,7 +21628,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="7" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="V174" s="3">
         <v>3</v>
@@ -21658,7 +21640,7 @@
         <v>44</v>
       </c>
       <c r="Y174" s="3"/>
-      <c r="Z174" s="10"/>
+      <c r="Z174" s="8"/>
     </row>
     <row r="175" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
@@ -21708,7 +21690,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="7" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="V175" s="3">
         <v>3</v>
@@ -21720,7 +21702,7 @@
         <v>44</v>
       </c>
       <c r="Y175" s="3"/>
-      <c r="Z175" s="10"/>
+      <c r="Z175" s="8"/>
     </row>
     <row r="176" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
@@ -21770,7 +21752,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="7" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="V176" s="3">
         <v>3</v>
@@ -21782,7 +21764,7 @@
         <v>44</v>
       </c>
       <c r="Y176" s="3"/>
-      <c r="Z176" s="10"/>
+      <c r="Z176" s="8"/>
     </row>
     <row r="177" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3">
@@ -21832,7 +21814,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="7" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="V177" s="3">
         <v>3</v>
@@ -21844,7 +21826,7 @@
         <v>44</v>
       </c>
       <c r="Y177" s="3"/>
-      <c r="Z177" s="10"/>
+      <c r="Z177" s="8"/>
     </row>
     <row r="178" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
@@ -21894,7 +21876,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="7" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="V178" s="3">
         <v>2</v>
@@ -21906,7 +21888,7 @@
         <v>44</v>
       </c>
       <c r="Y178" s="3"/>
-      <c r="Z178" s="10"/>
+      <c r="Z178" s="8"/>
     </row>
     <row r="179" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
@@ -21956,7 +21938,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="7" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="V179" s="3" t="s">
         <v>44</v>
@@ -21968,7 +21950,7 @@
         <v>44</v>
       </c>
       <c r="Y179" s="3"/>
-      <c r="Z179" s="10"/>
+      <c r="Z179" s="8"/>
     </row>
     <row r="180" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
@@ -22020,7 +22002,7 @@
         <v>33</v>
       </c>
       <c r="U180" s="7" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="V180" s="3">
         <v>3</v>
@@ -22032,7 +22014,7 @@
         <v>35</v>
       </c>
       <c r="Y180" s="3"/>
-      <c r="Z180" s="10"/>
+      <c r="Z180" s="8"/>
     </row>
     <row r="181" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
@@ -22094,7 +22076,7 @@
         <v>44</v>
       </c>
       <c r="Y181" s="3"/>
-      <c r="Z181" s="10"/>
+      <c r="Z181" s="8"/>
     </row>
     <row r="182" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3">
@@ -22144,7 +22126,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="7" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="V182" s="3">
         <v>3</v>
@@ -22156,7 +22138,7 @@
         <v>44</v>
       </c>
       <c r="Y182" s="3"/>
-      <c r="Z182" s="10"/>
+      <c r="Z182" s="8"/>
     </row>
     <row r="183" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3">
@@ -22210,7 +22192,7 @@
         <v>240</v>
       </c>
       <c r="U183" s="7" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="V183" s="3">
         <v>4</v>
@@ -22222,7 +22204,7 @@
         <v>35</v>
       </c>
       <c r="Y183" s="3"/>
-      <c r="Z183" s="10"/>
+      <c r="Z183" s="8"/>
     </row>
     <row r="184" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3">
@@ -22272,7 +22254,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="7" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="V184" s="3">
         <v>3</v>
@@ -22284,7 +22266,7 @@
         <v>44</v>
       </c>
       <c r="Y184" s="3"/>
-      <c r="Z184" s="10"/>
+      <c r="Z184" s="8"/>
     </row>
     <row r="185" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3">
@@ -22334,7 +22316,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="7" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="V185" s="3">
         <v>3</v>
@@ -22346,7 +22328,7 @@
         <v>44</v>
       </c>
       <c r="Y185" s="3"/>
-      <c r="Z185" s="10"/>
+      <c r="Z185" s="8"/>
     </row>
     <row r="186" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
@@ -22396,7 +22378,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="7" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="V186" s="3">
         <v>3</v>
@@ -22408,7 +22390,7 @@
         <v>44</v>
       </c>
       <c r="Y186" s="3"/>
-      <c r="Z186" s="10"/>
+      <c r="Z186" s="8"/>
     </row>
     <row r="187" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3">
@@ -22458,7 +22440,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="7" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="V187" s="3">
         <v>3</v>
@@ -22470,7 +22452,7 @@
         <v>44</v>
       </c>
       <c r="Y187" s="3"/>
-      <c r="Z187" s="10"/>
+      <c r="Z187" s="8"/>
     </row>
     <row r="188" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3">
@@ -22520,7 +22502,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="7" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="V188" s="3" t="s">
         <v>44</v>
@@ -22532,7 +22514,7 @@
         <v>44</v>
       </c>
       <c r="Y188" s="3"/>
-      <c r="Z188" s="10"/>
+      <c r="Z188" s="8"/>
     </row>
     <row r="189" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3">
@@ -22594,7 +22576,7 @@
         <v>44</v>
       </c>
       <c r="Y189" s="3"/>
-      <c r="Z189" s="10"/>
+      <c r="Z189" s="8"/>
     </row>
     <row r="190" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
@@ -22643,9 +22625,7 @@
       <c r="R190" s="3"/>
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
-      <c r="U190" s="7" t="s">
-        <v>3126</v>
-      </c>
+      <c r="U190" s="7"/>
       <c r="V190" s="3">
         <v>3</v>
       </c>
@@ -22658,7 +22638,7 @@
       <c r="Y190" s="3" t="s">
         <v>2931</v>
       </c>
-      <c r="Z190" s="10"/>
+      <c r="Z190" s="8"/>
     </row>
     <row r="191" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3">
@@ -22710,7 +22690,7 @@
         <v>448</v>
       </c>
       <c r="U191" s="7" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="V191" s="3">
         <v>3</v>
@@ -22722,7 +22702,7 @@
         <v>35</v>
       </c>
       <c r="Y191" s="3"/>
-      <c r="Z191" s="10"/>
+      <c r="Z191" s="8"/>
     </row>
     <row r="192" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
@@ -22776,7 +22756,7 @@
         <v>445</v>
       </c>
       <c r="U192" s="7" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="V192" s="3">
         <v>3</v>
@@ -22788,7 +22768,7 @@
         <v>35</v>
       </c>
       <c r="Y192" s="3"/>
-      <c r="Z192" s="10"/>
+      <c r="Z192" s="8"/>
     </row>
     <row r="193" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
@@ -22842,7 +22822,7 @@
         <v>448</v>
       </c>
       <c r="U193" s="7" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="V193" s="3">
         <v>3</v>
@@ -22854,7 +22834,7 @@
         <v>35</v>
       </c>
       <c r="Y193" s="3"/>
-      <c r="Z193" s="10"/>
+      <c r="Z193" s="8"/>
     </row>
     <row r="194" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3">
@@ -22908,7 +22888,7 @@
         <v>240</v>
       </c>
       <c r="U194" s="7" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="V194" s="3">
         <v>3</v>
@@ -22920,7 +22900,7 @@
         <v>35</v>
       </c>
       <c r="Y194" s="3"/>
-      <c r="Z194" s="10"/>
+      <c r="Z194" s="8"/>
     </row>
     <row r="195" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
@@ -22974,7 +22954,7 @@
         <v>448</v>
       </c>
       <c r="U195" s="7" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="V195" s="3">
         <v>3</v>
@@ -22986,7 +22966,7 @@
         <v>35</v>
       </c>
       <c r="Y195" s="3"/>
-      <c r="Z195" s="10"/>
+      <c r="Z195" s="8"/>
     </row>
     <row r="196" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3">
@@ -23040,7 +23020,7 @@
         <v>448</v>
       </c>
       <c r="U196" s="7" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="V196" s="3">
         <v>3</v>
@@ -23052,7 +23032,7 @@
         <v>35</v>
       </c>
       <c r="Y196" s="3"/>
-      <c r="Z196" s="10"/>
+      <c r="Z196" s="8"/>
     </row>
     <row r="197" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3">
@@ -23106,7 +23086,7 @@
         <v>1237</v>
       </c>
       <c r="U197" s="7" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="V197" s="3">
         <v>3</v>
@@ -23118,7 +23098,7 @@
         <v>35</v>
       </c>
       <c r="Y197" s="3"/>
-      <c r="Z197" s="10"/>
+      <c r="Z197" s="8"/>
     </row>
     <row r="198" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3">
@@ -23172,7 +23152,7 @@
         <v>281</v>
       </c>
       <c r="U198" s="7" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="V198" s="3">
         <v>3</v>
@@ -23184,7 +23164,7 @@
         <v>35</v>
       </c>
       <c r="Y198" s="3"/>
-      <c r="Z198" s="10"/>
+      <c r="Z198" s="8"/>
     </row>
     <row r="199" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3">
@@ -23236,7 +23216,7 @@
       </c>
       <c r="T199" s="3"/>
       <c r="U199" s="7" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="V199" s="3">
         <v>3</v>
@@ -23248,7 +23228,7 @@
         <v>35</v>
       </c>
       <c r="Y199" s="3"/>
-      <c r="Z199" s="10"/>
+      <c r="Z199" s="8"/>
     </row>
     <row r="200" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3">
@@ -23298,7 +23278,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="7" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="V200" s="3" t="s">
         <v>44</v>
@@ -23310,7 +23290,7 @@
         <v>44</v>
       </c>
       <c r="Y200" s="3"/>
-      <c r="Z200" s="10"/>
+      <c r="Z200" s="8"/>
     </row>
     <row r="201" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
@@ -23362,7 +23342,7 @@
         <v>397</v>
       </c>
       <c r="U201" s="7" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="V201" s="3">
         <v>3</v>
@@ -23374,7 +23354,7 @@
         <v>203</v>
       </c>
       <c r="Y201" s="3"/>
-      <c r="Z201" s="10"/>
+      <c r="Z201" s="8"/>
     </row>
     <row r="202" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
@@ -23428,7 +23408,7 @@
         <v>397</v>
       </c>
       <c r="U202" s="7" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="V202" s="3">
         <v>4</v>
@@ -23440,7 +23420,7 @@
         <v>34</v>
       </c>
       <c r="Y202" s="3"/>
-      <c r="Z202" s="10"/>
+      <c r="Z202" s="8"/>
     </row>
     <row r="203" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3">
@@ -23494,7 +23474,7 @@
         <v>314</v>
       </c>
       <c r="U203" s="7" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="V203" s="3">
         <v>4</v>
@@ -23506,7 +23486,7 @@
         <v>35</v>
       </c>
       <c r="Y203" s="3"/>
-      <c r="Z203" s="10"/>
+      <c r="Z203" s="8"/>
     </row>
     <row r="204" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
@@ -23558,7 +23538,7 @@
         <v>240</v>
       </c>
       <c r="U204" s="7" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="V204" s="3">
         <v>4</v>
@@ -23570,7 +23550,7 @@
         <v>35</v>
       </c>
       <c r="Y204" s="3"/>
-      <c r="Z204" s="10"/>
+      <c r="Z204" s="8"/>
     </row>
     <row r="205" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3">
@@ -23624,7 +23604,7 @@
         <v>74</v>
       </c>
       <c r="U205" s="7" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="V205" s="3">
         <v>4</v>
@@ -23636,7 +23616,7 @@
         <v>34</v>
       </c>
       <c r="Y205" s="3"/>
-      <c r="Z205" s="10"/>
+      <c r="Z205" s="8"/>
     </row>
     <row r="206" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3">
@@ -23688,7 +23668,7 @@
       </c>
       <c r="T206" s="3"/>
       <c r="U206" s="7" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="V206" s="3">
         <v>3</v>
@@ -23700,7 +23680,7 @@
         <v>35</v>
       </c>
       <c r="Y206" s="3"/>
-      <c r="Z206" s="10"/>
+      <c r="Z206" s="8"/>
     </row>
     <row r="207" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3">
@@ -23750,7 +23730,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="7" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="V207" s="3">
         <v>3</v>
@@ -23762,7 +23742,7 @@
         <v>35</v>
       </c>
       <c r="Y207" s="3"/>
-      <c r="Z207" s="10"/>
+      <c r="Z207" s="8"/>
     </row>
     <row r="208" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3">
@@ -23822,7 +23802,7 @@
         <v>44</v>
       </c>
       <c r="Y208" s="3"/>
-      <c r="Z208" s="10"/>
+      <c r="Z208" s="8"/>
     </row>
     <row r="209" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3">
@@ -23868,7 +23848,7 @@
         <v>281</v>
       </c>
       <c r="U209" s="7" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="V209" s="3">
         <v>3</v>
@@ -23880,7 +23860,7 @@
         <v>35</v>
       </c>
       <c r="Y209" s="3"/>
-      <c r="Z209" s="10"/>
+      <c r="Z209" s="8"/>
     </row>
     <row r="210" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3">
@@ -23926,7 +23906,7 @@
       </c>
       <c r="T210" s="3"/>
       <c r="U210" s="7" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="V210" s="3">
         <v>3</v>
@@ -23938,7 +23918,7 @@
         <v>35</v>
       </c>
       <c r="Y210" s="3"/>
-      <c r="Z210" s="10"/>
+      <c r="Z210" s="8"/>
     </row>
     <row r="211" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3">
@@ -23984,7 +23964,7 @@
       </c>
       <c r="T211" s="3"/>
       <c r="U211" s="7" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="V211" s="3">
         <v>3</v>
@@ -23996,7 +23976,7 @@
         <v>35</v>
       </c>
       <c r="Y211" s="3"/>
-      <c r="Z211" s="10"/>
+      <c r="Z211" s="8"/>
     </row>
     <row r="212" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3">
@@ -24042,7 +24022,7 @@
       </c>
       <c r="T212" s="3"/>
       <c r="U212" s="7" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="V212" s="3">
         <v>3</v>
@@ -24054,7 +24034,7 @@
         <v>35</v>
       </c>
       <c r="Y212" s="3"/>
-      <c r="Z212" s="10"/>
+      <c r="Z212" s="8"/>
     </row>
     <row r="213" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3">
@@ -24100,7 +24080,7 @@
       </c>
       <c r="T213" s="3"/>
       <c r="U213" s="7" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="V213" s="3">
         <v>3</v>
@@ -24112,7 +24092,7 @@
         <v>35</v>
       </c>
       <c r="Y213" s="3"/>
-      <c r="Z213" s="10"/>
+      <c r="Z213" s="8"/>
     </row>
     <row r="214" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3">
@@ -24156,7 +24136,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="7" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="V214" s="3">
         <v>3</v>
@@ -24168,7 +24148,7 @@
         <v>203</v>
       </c>
       <c r="Y214" s="3"/>
-      <c r="Z214" s="10"/>
+      <c r="Z214" s="8"/>
     </row>
     <row r="215" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3">
@@ -24212,7 +24192,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="7" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="V215" s="3">
         <v>3</v>
@@ -24224,7 +24204,7 @@
         <v>203</v>
       </c>
       <c r="Y215" s="3"/>
-      <c r="Z215" s="10"/>
+      <c r="Z215" s="8"/>
     </row>
     <row r="216" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3">
@@ -24274,7 +24254,7 @@
         <v>240</v>
       </c>
       <c r="U216" s="7" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="V216" s="3">
         <v>3</v>
@@ -24286,7 +24266,7 @@
         <v>35</v>
       </c>
       <c r="Y216" s="3"/>
-      <c r="Z216" s="10"/>
+      <c r="Z216" s="8"/>
     </row>
     <row r="217" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3">
@@ -24336,7 +24316,7 @@
         <v>74</v>
       </c>
       <c r="U217" s="7" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="V217" s="3">
         <v>3</v>
@@ -24348,7 +24328,7 @@
         <v>35</v>
       </c>
       <c r="Y217" s="3"/>
-      <c r="Z217" s="10"/>
+      <c r="Z217" s="8"/>
     </row>
     <row r="218" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3">
@@ -24396,7 +24376,7 @@
         <v>445</v>
       </c>
       <c r="U218" s="7" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="V218" s="3">
         <v>3</v>
@@ -24408,7 +24388,7 @@
         <v>34</v>
       </c>
       <c r="Y218" s="3"/>
-      <c r="Z218" s="10"/>
+      <c r="Z218" s="8"/>
     </row>
     <row r="219" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3">
@@ -24452,7 +24432,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="7" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="V219" s="3">
         <v>3</v>
@@ -24464,7 +24444,7 @@
         <v>35</v>
       </c>
       <c r="Y219" s="3"/>
-      <c r="Z219" s="10"/>
+      <c r="Z219" s="8"/>
     </row>
     <row r="220" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3">
@@ -24510,7 +24490,7 @@
         <v>33</v>
       </c>
       <c r="U220" s="7" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="V220" s="3">
         <v>2</v>
@@ -24522,7 +24502,7 @@
         <v>35</v>
       </c>
       <c r="Y220" s="3"/>
-      <c r="Z220" s="10"/>
+      <c r="Z220" s="8"/>
     </row>
     <row r="221" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3">
@@ -24566,7 +24546,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="7" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="V221" s="3">
         <v>3</v>
@@ -24578,7 +24558,7 @@
         <v>44</v>
       </c>
       <c r="Y221" s="3"/>
-      <c r="Z221" s="10"/>
+      <c r="Z221" s="8"/>
     </row>
     <row r="222" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3">
@@ -24642,7 +24622,7 @@
         <v>34</v>
       </c>
       <c r="Y222" s="3"/>
-      <c r="Z222" s="10"/>
+      <c r="Z222" s="8"/>
     </row>
     <row r="223" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3">
@@ -24690,7 +24670,7 @@
         <v>281</v>
       </c>
       <c r="U223" s="7" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="V223" s="3">
         <v>3</v>
@@ -24702,7 +24682,7 @@
         <v>35</v>
       </c>
       <c r="Y223" s="3"/>
-      <c r="Z223" s="10"/>
+      <c r="Z223" s="8"/>
     </row>
     <row r="224" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3">
@@ -24748,7 +24728,7 @@
         <v>281</v>
       </c>
       <c r="U224" s="7" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="V224" s="3">
         <v>3</v>
@@ -24760,7 +24740,7 @@
         <v>35</v>
       </c>
       <c r="Y224" s="3"/>
-      <c r="Z224" s="10"/>
+      <c r="Z224" s="8"/>
     </row>
     <row r="225" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3">
@@ -24804,7 +24784,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="7" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="V225" s="3">
         <v>2</v>
@@ -24816,7 +24796,7 @@
         <v>35</v>
       </c>
       <c r="Y225" s="3"/>
-      <c r="Z225" s="10"/>
+      <c r="Z225" s="8"/>
     </row>
     <row r="226" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3">
@@ -24864,7 +24844,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="7" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="V226" s="3" t="s">
         <v>44</v>
@@ -24876,7 +24856,7 @@
         <v>44</v>
       </c>
       <c r="Y226" s="3"/>
-      <c r="Z226" s="10"/>
+      <c r="Z226" s="8"/>
     </row>
     <row r="227" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
@@ -24924,7 +24904,7 @@
       </c>
       <c r="T227" s="3"/>
       <c r="U227" s="7" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="V227" s="3">
         <v>3</v>
@@ -24936,7 +24916,7 @@
         <v>35</v>
       </c>
       <c r="Y227" s="3"/>
-      <c r="Z227" s="10"/>
+      <c r="Z227" s="8"/>
     </row>
     <row r="228" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3">
@@ -24986,7 +24966,7 @@
         <v>74</v>
       </c>
       <c r="U228" s="7" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="V228" s="3">
         <v>3</v>
@@ -24998,7 +24978,7 @@
         <v>35</v>
       </c>
       <c r="Y228" s="3"/>
-      <c r="Z228" s="10"/>
+      <c r="Z228" s="8"/>
     </row>
     <row r="229" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3">
@@ -25046,7 +25026,7 @@
         <v>281</v>
       </c>
       <c r="U229" s="7" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="V229" s="3">
         <v>3</v>
@@ -25058,7 +25038,7 @@
         <v>35</v>
       </c>
       <c r="Y229" s="3"/>
-      <c r="Z229" s="10"/>
+      <c r="Z229" s="8"/>
     </row>
     <row r="230" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3">
@@ -25102,7 +25082,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="7" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="V230" s="3">
         <v>3</v>
@@ -25114,7 +25094,7 @@
         <v>203</v>
       </c>
       <c r="Y230" s="3"/>
-      <c r="Z230" s="10"/>
+      <c r="Z230" s="8"/>
     </row>
     <row r="231" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3">
@@ -25158,7 +25138,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="7" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="V231" s="3">
         <v>3</v>
@@ -25170,7 +25150,7 @@
         <v>44</v>
       </c>
       <c r="Y231" s="3"/>
-      <c r="Z231" s="10"/>
+      <c r="Z231" s="8"/>
     </row>
     <row r="232" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3">
@@ -25220,7 +25200,7 @@
         <v>33</v>
       </c>
       <c r="U232" s="7" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="V232" s="3">
         <v>3</v>
@@ -25232,7 +25212,7 @@
         <v>35</v>
       </c>
       <c r="Y232" s="3"/>
-      <c r="Z232" s="10"/>
+      <c r="Z232" s="8"/>
     </row>
     <row r="233" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3">
@@ -25286,7 +25266,7 @@
         <v>445</v>
       </c>
       <c r="U233" s="7" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="V233" s="3">
         <v>3</v>
@@ -25298,7 +25278,7 @@
         <v>35</v>
       </c>
       <c r="Y233" s="3"/>
-      <c r="Z233" s="10"/>
+      <c r="Z233" s="8"/>
     </row>
     <row r="234" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3">
@@ -25348,7 +25328,7 @@
         <v>111</v>
       </c>
       <c r="U234" s="7" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="V234" s="3">
         <v>3</v>
@@ -25360,7 +25340,7 @@
         <v>35</v>
       </c>
       <c r="Y234" s="3"/>
-      <c r="Z234" s="10"/>
+      <c r="Z234" s="8"/>
     </row>
     <row r="235" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3">
@@ -25414,7 +25394,7 @@
         <v>958</v>
       </c>
       <c r="U235" s="7" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="V235" s="3">
         <v>3</v>
@@ -25426,7 +25406,7 @@
         <v>35</v>
       </c>
       <c r="Y235" s="3"/>
-      <c r="Z235" s="10"/>
+      <c r="Z235" s="8"/>
     </row>
     <row r="236" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3">
@@ -25480,7 +25460,7 @@
         <v>74</v>
       </c>
       <c r="U236" s="7" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="V236" s="3">
         <v>3</v>
@@ -25492,7 +25472,7 @@
         <v>35</v>
       </c>
       <c r="Y236" s="3"/>
-      <c r="Z236" s="10"/>
+      <c r="Z236" s="8"/>
     </row>
     <row r="237" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3">
@@ -25546,7 +25526,7 @@
         <v>53</v>
       </c>
       <c r="U237" s="7" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="V237" s="3">
         <v>4</v>
@@ -25558,7 +25538,7 @@
         <v>34</v>
       </c>
       <c r="Y237" s="3"/>
-      <c r="Z237" s="10"/>
+      <c r="Z237" s="8"/>
     </row>
     <row r="238" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3">
@@ -25612,7 +25592,7 @@
         <v>33</v>
       </c>
       <c r="U238" s="7" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="V238" s="3">
         <v>4</v>
@@ -25624,7 +25604,7 @@
         <v>34</v>
       </c>
       <c r="Y238" s="3"/>
-      <c r="Z238" s="10"/>
+      <c r="Z238" s="8"/>
     </row>
     <row r="239" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3">
@@ -25674,7 +25654,7 @@
       </c>
       <c r="T239" s="3"/>
       <c r="U239" s="7" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="V239" s="3">
         <v>3</v>
@@ -25686,7 +25666,7 @@
         <v>35</v>
       </c>
       <c r="Y239" s="3"/>
-      <c r="Z239" s="10"/>
+      <c r="Z239" s="8"/>
     </row>
     <row r="240" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3">
@@ -25736,7 +25716,7 @@
       </c>
       <c r="T240" s="3"/>
       <c r="U240" s="7" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="V240" s="3">
         <v>3</v>
@@ -25748,7 +25728,7 @@
         <v>35</v>
       </c>
       <c r="Y240" s="3"/>
-      <c r="Z240" s="10"/>
+      <c r="Z240" s="8"/>
     </row>
     <row r="241" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3">
@@ -25800,7 +25780,7 @@
         <v>445</v>
       </c>
       <c r="U241" s="7" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="V241" s="3">
         <v>4</v>
@@ -25812,7 +25792,7 @@
         <v>35</v>
       </c>
       <c r="Y241" s="3"/>
-      <c r="Z241" s="10"/>
+      <c r="Z241" s="8"/>
     </row>
     <row r="242" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3">
@@ -25862,7 +25842,7 @@
       </c>
       <c r="T242" s="3"/>
       <c r="U242" s="7" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="V242" s="3">
         <v>3</v>
@@ -25874,7 +25854,7 @@
         <v>35</v>
       </c>
       <c r="Y242" s="3"/>
-      <c r="Z242" s="10"/>
+      <c r="Z242" s="8"/>
     </row>
     <row r="243" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3">
@@ -25918,7 +25898,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="7" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="V243" s="3">
         <v>2</v>
@@ -25930,7 +25910,7 @@
         <v>203</v>
       </c>
       <c r="Y243" s="3"/>
-      <c r="Z243" s="10"/>
+      <c r="Z243" s="8"/>
     </row>
     <row r="244" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3">
@@ -25982,7 +25962,7 @@
         <v>240</v>
       </c>
       <c r="U244" s="7" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="V244" s="3">
         <v>3</v>
@@ -25994,7 +25974,7 @@
         <v>35</v>
       </c>
       <c r="Y244" s="3"/>
-      <c r="Z244" s="10"/>
+      <c r="Z244" s="8"/>
     </row>
     <row r="245" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3">
@@ -26046,7 +26026,7 @@
         <v>74</v>
       </c>
       <c r="U245" s="7" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="V245" s="3">
         <v>3</v>
@@ -26058,7 +26038,7 @@
         <v>35</v>
       </c>
       <c r="Y245" s="3"/>
-      <c r="Z245" s="10"/>
+      <c r="Z245" s="8"/>
     </row>
     <row r="246" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3">
@@ -26110,7 +26090,7 @@
         <v>74</v>
       </c>
       <c r="U246" s="7" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="V246" s="3">
         <v>4</v>
@@ -26122,7 +26102,7 @@
         <v>35</v>
       </c>
       <c r="Y246" s="3"/>
-      <c r="Z246" s="10"/>
+      <c r="Z246" s="8"/>
     </row>
     <row r="247" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3">
@@ -26176,7 +26156,7 @@
         <v>240</v>
       </c>
       <c r="U247" s="7" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="V247" s="3">
         <v>3</v>
@@ -26188,7 +26168,7 @@
         <v>34</v>
       </c>
       <c r="Y247" s="3"/>
-      <c r="Z247" s="10"/>
+      <c r="Z247" s="8"/>
     </row>
     <row r="248" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3">
@@ -26240,7 +26220,7 @@
       </c>
       <c r="T248" s="3"/>
       <c r="U248" s="7" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="V248" s="3">
         <v>3</v>
@@ -26252,7 +26232,7 @@
         <v>35</v>
       </c>
       <c r="Y248" s="3"/>
-      <c r="Z248" s="10"/>
+      <c r="Z248" s="8"/>
     </row>
     <row r="249" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3">
@@ -26300,7 +26280,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="7" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="V249" s="3">
         <v>3</v>
@@ -26312,7 +26292,7 @@
         <v>35</v>
       </c>
       <c r="Y249" s="3"/>
-      <c r="Z249" s="10"/>
+      <c r="Z249" s="8"/>
     </row>
     <row r="250" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3">
@@ -26360,7 +26340,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="7" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="V250" s="3">
         <v>3</v>
@@ -26372,7 +26352,7 @@
         <v>35</v>
       </c>
       <c r="Y250" s="3"/>
-      <c r="Z250" s="10"/>
+      <c r="Z250" s="8"/>
     </row>
     <row r="251" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3">
@@ -26420,7 +26400,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="7" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="V251" s="3">
         <v>3</v>
@@ -26432,7 +26412,7 @@
         <v>35</v>
       </c>
       <c r="Y251" s="3"/>
-      <c r="Z251" s="10"/>
+      <c r="Z251" s="8"/>
     </row>
     <row r="252" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3">
@@ -26480,7 +26460,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="7" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="V252" s="3">
         <v>3</v>
@@ -26492,7 +26472,7 @@
         <v>35</v>
       </c>
       <c r="Y252" s="3"/>
-      <c r="Z252" s="10"/>
+      <c r="Z252" s="8"/>
     </row>
     <row r="253" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3">
@@ -26540,7 +26520,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="7" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="V253" s="3">
         <v>3</v>
@@ -26552,7 +26532,7 @@
         <v>44</v>
       </c>
       <c r="Y253" s="3"/>
-      <c r="Z253" s="10"/>
+      <c r="Z253" s="8"/>
     </row>
     <row r="254" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3">
@@ -26600,7 +26580,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="7" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="V254" s="3">
         <v>3</v>
@@ -26612,7 +26592,7 @@
         <v>44</v>
       </c>
       <c r="Y254" s="3"/>
-      <c r="Z254" s="10"/>
+      <c r="Z254" s="8"/>
     </row>
     <row r="255" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3">
@@ -26662,7 +26642,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="7" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="V255" s="3">
         <v>3</v>
@@ -26674,7 +26654,7 @@
         <v>44</v>
       </c>
       <c r="Y255" s="3"/>
-      <c r="Z255" s="10"/>
+      <c r="Z255" s="8"/>
     </row>
     <row r="256" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3">
@@ -26722,7 +26702,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="7" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="V256" s="3">
         <v>2</v>
@@ -26734,7 +26714,7 @@
         <v>44</v>
       </c>
       <c r="Y256" s="3"/>
-      <c r="Z256" s="10"/>
+      <c r="Z256" s="8"/>
     </row>
     <row r="257" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3">
@@ -26784,7 +26764,7 @@
         <v>965</v>
       </c>
       <c r="U257" s="7" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="V257" s="3">
         <v>4</v>
@@ -26796,7 +26776,7 @@
         <v>35</v>
       </c>
       <c r="Y257" s="3"/>
-      <c r="Z257" s="10"/>
+      <c r="Z257" s="8"/>
     </row>
     <row r="258" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3">
@@ -26846,7 +26826,7 @@
         <v>1062</v>
       </c>
       <c r="U258" s="7" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="V258" s="3">
         <v>4</v>
@@ -26858,7 +26838,7 @@
         <v>35</v>
       </c>
       <c r="Y258" s="3"/>
-      <c r="Z258" s="10"/>
+      <c r="Z258" s="8"/>
     </row>
     <row r="259" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3">
@@ -26906,7 +26886,7 @@
       </c>
       <c r="T259" s="3"/>
       <c r="U259" s="7" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="V259" s="3">
         <v>4</v>
@@ -26918,7 +26898,7 @@
         <v>35</v>
       </c>
       <c r="Y259" s="3"/>
-      <c r="Z259" s="10"/>
+      <c r="Z259" s="8"/>
     </row>
     <row r="260" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3">
@@ -26964,7 +26944,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="7" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="V260" s="3">
         <v>4</v>
@@ -26976,7 +26956,7 @@
         <v>44</v>
       </c>
       <c r="Y260" s="3"/>
-      <c r="Z260" s="10"/>
+      <c r="Z260" s="8"/>
     </row>
     <row r="261" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3">
@@ -27026,7 +27006,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="7" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="V261" s="3" t="s">
         <v>44</v>
@@ -27038,7 +27018,7 @@
         <v>44</v>
       </c>
       <c r="Y261" s="3"/>
-      <c r="Z261" s="10"/>
+      <c r="Z261" s="8"/>
     </row>
     <row r="262" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3">
@@ -27088,7 +27068,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="7" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="V262" s="3" t="s">
         <v>44</v>
@@ -27100,7 +27080,7 @@
         <v>44</v>
       </c>
       <c r="Y262" s="3"/>
-      <c r="Z262" s="10"/>
+      <c r="Z262" s="8"/>
     </row>
     <row r="263" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3">
@@ -27152,7 +27132,7 @@
       </c>
       <c r="T263" s="3"/>
       <c r="U263" s="7" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="V263" s="3">
         <v>3</v>
@@ -27164,7 +27144,7 @@
         <v>35</v>
       </c>
       <c r="Y263" s="3"/>
-      <c r="Z263" s="10"/>
+      <c r="Z263" s="8"/>
     </row>
     <row r="264" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3">
@@ -27216,7 +27196,7 @@
       </c>
       <c r="T264" s="3"/>
       <c r="U264" s="7" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="V264" s="3">
         <v>4</v>
@@ -27228,7 +27208,7 @@
         <v>35</v>
       </c>
       <c r="Y264" s="3"/>
-      <c r="Z264" s="10"/>
+      <c r="Z264" s="8"/>
     </row>
     <row r="265" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3">
@@ -27288,7 +27268,7 @@
         <v>44</v>
       </c>
       <c r="Y265" s="3"/>
-      <c r="Z265" s="10"/>
+      <c r="Z265" s="8"/>
     </row>
     <row r="266" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3">
@@ -27342,7 +27322,7 @@
         <v>314</v>
       </c>
       <c r="U266" s="7" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="V266" s="3">
         <v>4</v>
@@ -27354,7 +27334,7 @@
         <v>35</v>
       </c>
       <c r="Y266" s="3"/>
-      <c r="Z266" s="10"/>
+      <c r="Z266" s="8"/>
     </row>
     <row r="267" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3">
@@ -27408,7 +27388,7 @@
         <v>74</v>
       </c>
       <c r="U267" s="7" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="V267" s="3">
         <v>3</v>
@@ -27420,7 +27400,7 @@
         <v>35</v>
       </c>
       <c r="Y267" s="3"/>
-      <c r="Z267" s="10"/>
+      <c r="Z267" s="8"/>
     </row>
     <row r="268" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3">
@@ -27474,7 +27454,7 @@
         <v>314</v>
       </c>
       <c r="U268" s="7" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="V268" s="3">
         <v>4</v>
@@ -27486,7 +27466,7 @@
         <v>34</v>
       </c>
       <c r="Y268" s="3"/>
-      <c r="Z268" s="10"/>
+      <c r="Z268" s="8"/>
     </row>
     <row r="269" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3">
@@ -27538,7 +27518,7 @@
         <v>281</v>
       </c>
       <c r="U269" s="7" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="V269" s="3">
         <v>3</v>
@@ -27550,7 +27530,7 @@
         <v>35</v>
       </c>
       <c r="Y269" s="3"/>
-      <c r="Z269" s="10"/>
+      <c r="Z269" s="8"/>
     </row>
     <row r="270" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3">
@@ -27604,7 +27584,7 @@
         <v>314</v>
       </c>
       <c r="U270" s="7" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="V270" s="3">
         <v>4</v>
@@ -27616,7 +27596,7 @@
         <v>35</v>
       </c>
       <c r="Y270" s="3"/>
-      <c r="Z270" s="10"/>
+      <c r="Z270" s="8"/>
     </row>
     <row r="271" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3">
@@ -27666,7 +27646,7 @@
       </c>
       <c r="T271" s="3"/>
       <c r="U271" s="7" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="V271" s="3">
         <v>3</v>
@@ -27678,7 +27658,7 @@
         <v>35</v>
       </c>
       <c r="Y271" s="3"/>
-      <c r="Z271" s="10"/>
+      <c r="Z271" s="8"/>
     </row>
     <row r="272" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3">
@@ -27728,7 +27708,7 @@
       </c>
       <c r="T272" s="3"/>
       <c r="U272" s="7" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="V272" s="3">
         <v>3</v>
@@ -27740,7 +27720,7 @@
         <v>35</v>
       </c>
       <c r="Y272" s="3"/>
-      <c r="Z272" s="10"/>
+      <c r="Z272" s="8"/>
     </row>
     <row r="273" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3">
@@ -27788,7 +27768,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="7" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="V273" s="3">
         <v>2</v>
@@ -27800,7 +27780,7 @@
         <v>35</v>
       </c>
       <c r="Y273" s="3"/>
-      <c r="Z273" s="10"/>
+      <c r="Z273" s="8"/>
     </row>
     <row r="274" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3">
@@ -27852,7 +27832,7 @@
         <v>240</v>
       </c>
       <c r="U274" s="7" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="V274" s="3">
         <v>3</v>
@@ -27864,7 +27844,7 @@
         <v>35</v>
       </c>
       <c r="Y274" s="3"/>
-      <c r="Z274" s="10"/>
+      <c r="Z274" s="8"/>
     </row>
     <row r="275" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3">
@@ -27914,7 +27894,7 @@
       </c>
       <c r="T275" s="3"/>
       <c r="U275" s="7" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="V275" s="3">
         <v>3</v>
@@ -27926,7 +27906,7 @@
         <v>35</v>
       </c>
       <c r="Y275" s="3"/>
-      <c r="Z275" s="10"/>
+      <c r="Z275" s="8"/>
     </row>
     <row r="276" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3">
@@ -27990,7 +27970,7 @@
         <v>35</v>
       </c>
       <c r="Y276" s="3"/>
-      <c r="Z276" s="10"/>
+      <c r="Z276" s="8"/>
     </row>
     <row r="277" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3">
@@ -28040,7 +28020,7 @@
       </c>
       <c r="T277" s="3"/>
       <c r="U277" s="7" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="V277" s="3">
         <v>3</v>
@@ -28052,7 +28032,7 @@
         <v>35</v>
       </c>
       <c r="Y277" s="3"/>
-      <c r="Z277" s="10"/>
+      <c r="Z277" s="8"/>
     </row>
     <row r="278" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3">
@@ -28102,7 +28082,7 @@
       </c>
       <c r="T278" s="3"/>
       <c r="U278" s="7" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="V278" s="3">
         <v>3</v>
@@ -28114,7 +28094,7 @@
         <v>35</v>
       </c>
       <c r="Y278" s="3"/>
-      <c r="Z278" s="10"/>
+      <c r="Z278" s="8"/>
     </row>
     <row r="279" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3">
@@ -28164,7 +28144,7 @@
       </c>
       <c r="T279" s="3"/>
       <c r="U279" s="7" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="V279" s="3">
         <v>3</v>
@@ -28176,7 +28156,7 @@
         <v>35</v>
       </c>
       <c r="Y279" s="3"/>
-      <c r="Z279" s="10"/>
+      <c r="Z279" s="8"/>
     </row>
     <row r="280" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3">
@@ -28226,7 +28206,7 @@
         <v>2950</v>
       </c>
       <c r="U280" s="7" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="V280" s="3">
         <v>3</v>
@@ -28238,7 +28218,7 @@
         <v>35</v>
       </c>
       <c r="Y280" s="3"/>
-      <c r="Z280" s="10"/>
+      <c r="Z280" s="8"/>
     </row>
     <row r="281" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3">
@@ -28286,7 +28266,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="7" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="V281" s="3">
         <v>2</v>
@@ -28298,7 +28278,7 @@
         <v>35</v>
       </c>
       <c r="Y281" s="3"/>
-      <c r="Z281" s="10"/>
+      <c r="Z281" s="8"/>
     </row>
     <row r="282" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3">
@@ -28346,7 +28326,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="7" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="V282" s="3">
         <v>3</v>
@@ -28358,7 +28338,7 @@
         <v>35</v>
       </c>
       <c r="Y282" s="3"/>
-      <c r="Z282" s="10"/>
+      <c r="Z282" s="8"/>
     </row>
     <row r="283" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3">
@@ -28410,7 +28390,7 @@
       </c>
       <c r="T283" s="3"/>
       <c r="U283" s="7" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="V283" s="3">
         <v>4</v>
@@ -28422,7 +28402,7 @@
         <v>35</v>
       </c>
       <c r="Y283" s="3"/>
-      <c r="Z283" s="10"/>
+      <c r="Z283" s="8"/>
     </row>
     <row r="284" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3">
@@ -28470,7 +28450,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="7" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="V284" s="3">
         <v>3</v>
@@ -28482,7 +28462,7 @@
         <v>35</v>
       </c>
       <c r="Y284" s="3"/>
-      <c r="Z284" s="10"/>
+      <c r="Z284" s="8"/>
     </row>
     <row r="285" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3">
@@ -28530,7 +28510,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="7" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="V285" s="3">
         <v>3</v>
@@ -28542,7 +28522,7 @@
         <v>44</v>
       </c>
       <c r="Y285" s="3"/>
-      <c r="Z285" s="10"/>
+      <c r="Z285" s="8"/>
     </row>
     <row r="286" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3">
@@ -28592,7 +28572,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="7" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="V286" s="3">
         <v>3</v>
@@ -28604,7 +28584,7 @@
         <v>44</v>
       </c>
       <c r="Y286" s="3"/>
-      <c r="Z286" s="10"/>
+      <c r="Z286" s="8"/>
     </row>
     <row r="287" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3">
@@ -28654,7 +28634,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="7" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="V287" s="3">
         <v>3</v>
@@ -28666,7 +28646,7 @@
         <v>44</v>
       </c>
       <c r="Y287" s="3"/>
-      <c r="Z287" s="10"/>
+      <c r="Z287" s="8"/>
     </row>
     <row r="288" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3">
@@ -28714,7 +28694,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="7" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="V288" s="3">
         <v>3</v>
@@ -28726,7 +28706,7 @@
         <v>44</v>
       </c>
       <c r="Y288" s="3"/>
-      <c r="Z288" s="10"/>
+      <c r="Z288" s="8"/>
     </row>
     <row r="289" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3">
@@ -28774,7 +28754,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="V289" s="3">
         <v>2</v>
@@ -28786,7 +28766,7 @@
         <v>44</v>
       </c>
       <c r="Y289" s="3"/>
-      <c r="Z289" s="10"/>
+      <c r="Z289" s="8"/>
     </row>
     <row r="290" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3">
@@ -28836,7 +28816,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="7" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="V290" s="3">
         <v>3</v>
@@ -28848,7 +28828,7 @@
         <v>44</v>
       </c>
       <c r="Y290" s="3"/>
-      <c r="Z290" s="10"/>
+      <c r="Z290" s="8"/>
     </row>
     <row r="291" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3">
@@ -28896,7 +28876,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="7" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="V291" s="3">
         <v>1</v>
@@ -28908,7 +28888,7 @@
         <v>44</v>
       </c>
       <c r="Y291" s="3"/>
-      <c r="Z291" s="10"/>
+      <c r="Z291" s="8"/>
     </row>
     <row r="292" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3">
@@ -28956,7 +28936,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="7" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="V292" s="3">
         <v>1</v>
@@ -28968,7 +28948,7 @@
         <v>44</v>
       </c>
       <c r="Y292" s="3"/>
-      <c r="Z292" s="10"/>
+      <c r="Z292" s="8"/>
     </row>
     <row r="293" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3">
@@ -29030,7 +29010,7 @@
         <v>44</v>
       </c>
       <c r="Y293" s="3"/>
-      <c r="Z293" s="10"/>
+      <c r="Z293" s="8"/>
     </row>
     <row r="294" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3">
@@ -29090,7 +29070,7 @@
         <v>44</v>
       </c>
       <c r="Y294" s="3"/>
-      <c r="Z294" s="10"/>
+      <c r="Z294" s="8"/>
     </row>
     <row r="295" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3">
@@ -29144,7 +29124,7 @@
         <v>1237</v>
       </c>
       <c r="U295" s="7" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="V295" s="3">
         <v>3</v>
@@ -29156,7 +29136,7 @@
         <v>35</v>
       </c>
       <c r="Y295" s="3"/>
-      <c r="Z295" s="10"/>
+      <c r="Z295" s="8"/>
     </row>
     <row r="296" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3">
@@ -29208,7 +29188,7 @@
       </c>
       <c r="T296" s="3"/>
       <c r="U296" s="7" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="V296" s="3">
         <v>3</v>
@@ -29220,7 +29200,7 @@
         <v>35</v>
       </c>
       <c r="Y296" s="3"/>
-      <c r="Z296" s="10"/>
+      <c r="Z296" s="8"/>
     </row>
     <row r="297" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3">
@@ -29274,7 +29254,7 @@
         <v>314</v>
       </c>
       <c r="U297" s="7" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="V297" s="3">
         <v>3</v>
@@ -29286,7 +29266,7 @@
         <v>35</v>
       </c>
       <c r="Y297" s="3"/>
-      <c r="Z297" s="10"/>
+      <c r="Z297" s="8"/>
     </row>
     <row r="298" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3">
@@ -29338,7 +29318,7 @@
       </c>
       <c r="T298" s="3"/>
       <c r="U298" s="7" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="V298" s="3">
         <v>3</v>
@@ -29350,7 +29330,7 @@
         <v>35</v>
       </c>
       <c r="Y298" s="3"/>
-      <c r="Z298" s="10"/>
+      <c r="Z298" s="8"/>
     </row>
     <row r="299" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3">
@@ -29404,7 +29384,7 @@
         <v>445</v>
       </c>
       <c r="U299" s="7" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="V299" s="3">
         <v>3</v>
@@ -29416,7 +29396,7 @@
         <v>35</v>
       </c>
       <c r="Y299" s="3"/>
-      <c r="Z299" s="10"/>
+      <c r="Z299" s="8"/>
     </row>
     <row r="300" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3">
@@ -29468,7 +29448,7 @@
         <v>397</v>
       </c>
       <c r="U300" s="7" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="V300" s="3">
         <v>3</v>
@@ -29480,7 +29460,7 @@
         <v>35</v>
       </c>
       <c r="Y300" s="3"/>
-      <c r="Z300" s="10"/>
+      <c r="Z300" s="8"/>
     </row>
     <row r="301" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3">
@@ -29530,7 +29510,7 @@
       </c>
       <c r="T301" s="3"/>
       <c r="U301" s="7" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="V301" s="3">
         <v>3</v>
@@ -29542,7 +29522,7 @@
         <v>203</v>
       </c>
       <c r="Y301" s="3"/>
-      <c r="Z301" s="10"/>
+      <c r="Z301" s="8"/>
     </row>
     <row r="302" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3">
@@ -29592,7 +29572,7 @@
       </c>
       <c r="T302" s="3"/>
       <c r="U302" s="7" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="V302" s="3">
         <v>3</v>
@@ -29604,7 +29584,7 @@
         <v>35</v>
       </c>
       <c r="Y302" s="3"/>
-      <c r="Z302" s="10"/>
+      <c r="Z302" s="8"/>
     </row>
     <row r="303" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3">
@@ -29656,7 +29636,7 @@
       </c>
       <c r="T303" s="3"/>
       <c r="U303" s="7" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="V303" s="3">
         <v>4</v>
@@ -29668,7 +29648,7 @@
         <v>35</v>
       </c>
       <c r="Y303" s="3"/>
-      <c r="Z303" s="10"/>
+      <c r="Z303" s="8"/>
     </row>
     <row r="304" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3">
@@ -29716,7 +29696,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="7" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="V304" s="3">
         <v>3</v>
@@ -29728,7 +29708,7 @@
         <v>35</v>
       </c>
       <c r="Y304" s="3"/>
-      <c r="Z304" s="10"/>
+      <c r="Z304" s="8"/>
     </row>
     <row r="305" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3">
@@ -29782,7 +29762,7 @@
         <v>74</v>
       </c>
       <c r="U305" s="7" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="V305" s="3">
         <v>3</v>
@@ -29794,7 +29774,7 @@
         <v>35</v>
       </c>
       <c r="Y305" s="3"/>
-      <c r="Z305" s="10"/>
+      <c r="Z305" s="8"/>
     </row>
     <row r="306" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3">
@@ -29848,7 +29828,7 @@
         <v>281</v>
       </c>
       <c r="U306" s="7" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="V306" s="3">
         <v>3</v>
@@ -29860,7 +29840,7 @@
         <v>35</v>
       </c>
       <c r="Y306" s="3"/>
-      <c r="Z306" s="10"/>
+      <c r="Z306" s="8"/>
     </row>
     <row r="307" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3">
@@ -29912,7 +29892,7 @@
         <v>314</v>
       </c>
       <c r="U307" s="7" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="V307" s="3">
         <v>3</v>
@@ -29924,7 +29904,7 @@
         <v>34</v>
       </c>
       <c r="Y307" s="3"/>
-      <c r="Z307" s="10"/>
+      <c r="Z307" s="8"/>
     </row>
     <row r="308" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3">
@@ -29976,7 +29956,7 @@
       </c>
       <c r="T308" s="3"/>
       <c r="U308" s="7" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="V308" s="3">
         <v>4</v>
@@ -29988,7 +29968,7 @@
         <v>35</v>
       </c>
       <c r="Y308" s="3"/>
-      <c r="Z308" s="10"/>
+      <c r="Z308" s="8"/>
     </row>
     <row r="309" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3">
@@ -30038,7 +30018,7 @@
       </c>
       <c r="T309" s="3"/>
       <c r="U309" s="7" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="V309" s="3">
         <v>3</v>
@@ -30050,7 +30030,7 @@
         <v>203</v>
       </c>
       <c r="Y309" s="3"/>
-      <c r="Z309" s="10"/>
+      <c r="Z309" s="8"/>
     </row>
     <row r="310" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3">
@@ -30102,7 +30082,7 @@
         <v>445</v>
       </c>
       <c r="U310" s="7" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="V310" s="3">
         <v>3</v>
@@ -30114,7 +30094,7 @@
         <v>35</v>
       </c>
       <c r="Y310" s="3"/>
-      <c r="Z310" s="10"/>
+      <c r="Z310" s="8"/>
     </row>
     <row r="311" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3">
@@ -30164,7 +30144,7 @@
       </c>
       <c r="T311" s="3"/>
       <c r="U311" s="7" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="V311" s="3">
         <v>4</v>
@@ -30176,7 +30156,7 @@
         <v>35</v>
       </c>
       <c r="Y311" s="3"/>
-      <c r="Z311" s="10"/>
+      <c r="Z311" s="8"/>
     </row>
     <row r="312" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3">
@@ -30224,7 +30204,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="7" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="V312" s="3">
         <v>3</v>
@@ -30236,7 +30216,7 @@
         <v>35</v>
       </c>
       <c r="Y312" s="3"/>
-      <c r="Z312" s="10"/>
+      <c r="Z312" s="8"/>
     </row>
     <row r="313" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3">
@@ -30284,7 +30264,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="7" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="V313" s="3">
         <v>3</v>
@@ -30296,7 +30276,7 @@
         <v>35</v>
       </c>
       <c r="Y313" s="3"/>
-      <c r="Z313" s="10"/>
+      <c r="Z313" s="8"/>
     </row>
     <row r="314" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3">
@@ -30346,7 +30326,7 @@
         <v>2950</v>
       </c>
       <c r="U314" s="7" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="V314" s="3">
         <v>4</v>
@@ -30358,7 +30338,7 @@
         <v>35</v>
       </c>
       <c r="Y314" s="3"/>
-      <c r="Z314" s="10"/>
+      <c r="Z314" s="8"/>
     </row>
     <row r="315" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3">
@@ -30402,7 +30382,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="7" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="V315" s="3">
         <v>3</v>
@@ -30414,7 +30394,7 @@
         <v>35</v>
       </c>
       <c r="Y315" s="3"/>
-      <c r="Z315" s="10"/>
+      <c r="Z315" s="8"/>
     </row>
     <row r="316" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3">
@@ -30470,7 +30450,7 @@
         <v>35</v>
       </c>
       <c r="Y316" s="3"/>
-      <c r="Z316" s="10"/>
+      <c r="Z316" s="8"/>
     </row>
     <row r="317" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3">
@@ -30514,7 +30494,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="7" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="V317" s="3">
         <v>3</v>
@@ -30526,7 +30506,7 @@
         <v>44</v>
       </c>
       <c r="Y317" s="3"/>
-      <c r="Z317" s="10"/>
+      <c r="Z317" s="8"/>
     </row>
     <row r="318" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3">
@@ -30570,7 +30550,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="7" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="V318" s="3">
         <v>2</v>
@@ -30582,7 +30562,7 @@
         <v>44</v>
       </c>
       <c r="Y318" s="3"/>
-      <c r="Z318" s="10"/>
+      <c r="Z318" s="8"/>
     </row>
     <row r="319" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3">
@@ -30632,7 +30612,7 @@
       </c>
       <c r="T319" s="3"/>
       <c r="U319" s="7" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="V319" s="3">
         <v>3</v>
@@ -30644,7 +30624,7 @@
         <v>34</v>
       </c>
       <c r="Y319" s="3"/>
-      <c r="Z319" s="10"/>
+      <c r="Z319" s="8"/>
     </row>
     <row r="320" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3">
@@ -30694,7 +30674,7 @@
       </c>
       <c r="T320" s="3"/>
       <c r="U320" s="7" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="V320" s="3">
         <v>3</v>
@@ -30706,7 +30686,7 @@
         <v>35</v>
       </c>
       <c r="Y320" s="3"/>
-      <c r="Z320" s="10"/>
+      <c r="Z320" s="8"/>
     </row>
     <row r="321" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3">
@@ -30756,7 +30736,7 @@
       </c>
       <c r="T321" s="3"/>
       <c r="U321" s="7" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="V321" s="3">
         <v>4</v>
@@ -30768,7 +30748,7 @@
         <v>35</v>
       </c>
       <c r="Y321" s="3"/>
-      <c r="Z321" s="10"/>
+      <c r="Z321" s="8"/>
     </row>
     <row r="322" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3">
@@ -30812,7 +30792,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="7" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="V322" s="3">
         <v>3</v>
@@ -30824,7 +30804,7 @@
         <v>35</v>
       </c>
       <c r="Y322" s="3"/>
-      <c r="Z322" s="10"/>
+      <c r="Z322" s="8"/>
     </row>
     <row r="323" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3">
@@ -30868,7 +30848,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="7" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="V323" s="3">
         <v>3</v>
@@ -30880,7 +30860,7 @@
         <v>44</v>
       </c>
       <c r="Y323" s="3"/>
-      <c r="Z323" s="10"/>
+      <c r="Z323" s="8"/>
     </row>
     <row r="324" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3">
@@ -30928,7 +30908,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="7" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="V324" s="3">
         <v>3</v>
@@ -30940,7 +30920,7 @@
         <v>44</v>
       </c>
       <c r="Y324" s="3"/>
-      <c r="Z324" s="10"/>
+      <c r="Z324" s="8"/>
     </row>
     <row r="325" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3">
@@ -30990,7 +30970,7 @@
       </c>
       <c r="T325" s="3"/>
       <c r="U325" s="7" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="V325" s="3">
         <v>3</v>
@@ -31002,7 +30982,7 @@
         <v>34</v>
       </c>
       <c r="Y325" s="3"/>
-      <c r="Z325" s="10"/>
+      <c r="Z325" s="8"/>
     </row>
     <row r="326" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3">
@@ -31052,7 +31032,7 @@
       </c>
       <c r="T326" s="3"/>
       <c r="U326" s="7" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="V326" s="3">
         <v>3</v>
@@ -31064,7 +31044,7 @@
         <v>35</v>
       </c>
       <c r="Y326" s="3"/>
-      <c r="Z326" s="10"/>
+      <c r="Z326" s="8"/>
     </row>
     <row r="327" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3">
@@ -31116,7 +31096,7 @@
         <v>1237</v>
       </c>
       <c r="U327" s="7" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="V327" s="3">
         <v>3</v>
@@ -31128,7 +31108,7 @@
         <v>35</v>
       </c>
       <c r="Y327" s="3"/>
-      <c r="Z327" s="10"/>
+      <c r="Z327" s="8"/>
     </row>
     <row r="328" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3">
@@ -31180,7 +31160,7 @@
         <v>314</v>
       </c>
       <c r="U328" s="7" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="V328" s="3">
         <v>3</v>
@@ -31192,7 +31172,7 @@
         <v>35</v>
       </c>
       <c r="Y328" s="3"/>
-      <c r="Z328" s="10"/>
+      <c r="Z328" s="8"/>
     </row>
     <row r="329" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3">
@@ -31242,7 +31222,7 @@
         <v>74</v>
       </c>
       <c r="U329" s="7" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="V329" s="3">
         <v>3</v>
@@ -31254,7 +31234,7 @@
         <v>34</v>
       </c>
       <c r="Y329" s="3"/>
-      <c r="Z329" s="10"/>
+      <c r="Z329" s="8"/>
     </row>
     <row r="330" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3">
@@ -31304,7 +31284,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="7" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="V330" s="3">
         <v>3</v>
@@ -31316,7 +31296,7 @@
         <v>35</v>
       </c>
       <c r="Y330" s="3"/>
-      <c r="Z330" s="10"/>
+      <c r="Z330" s="8"/>
     </row>
     <row r="331" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3">
@@ -31362,7 +31342,7 @@
         <v>240</v>
       </c>
       <c r="U331" s="7" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="V331" s="3">
         <v>3</v>
@@ -31374,7 +31354,7 @@
         <v>35</v>
       </c>
       <c r="Y331" s="3"/>
-      <c r="Z331" s="10"/>
+      <c r="Z331" s="8"/>
     </row>
     <row r="332" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3">
@@ -31420,7 +31400,7 @@
         <v>33</v>
       </c>
       <c r="U332" s="7" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="V332" s="3">
         <v>3</v>
@@ -31432,7 +31412,7 @@
         <v>35</v>
       </c>
       <c r="Y332" s="3"/>
-      <c r="Z332" s="10"/>
+      <c r="Z332" s="8"/>
     </row>
     <row r="333" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3">
@@ -31476,7 +31456,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="7" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="V333" s="3">
         <v>4</v>
@@ -31488,7 +31468,7 @@
         <v>35</v>
       </c>
       <c r="Y333" s="3"/>
-      <c r="Z333" s="10"/>
+      <c r="Z333" s="8"/>
     </row>
     <row r="334" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3">
@@ -31532,7 +31512,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="7" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="V334" s="3">
         <v>3</v>
@@ -31544,7 +31524,7 @@
         <v>203</v>
       </c>
       <c r="Y334" s="3"/>
-      <c r="Z334" s="10"/>
+      <c r="Z334" s="8"/>
     </row>
     <row r="335" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3">
@@ -31588,7 +31568,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="7" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="V335" s="3">
         <v>2</v>
@@ -31600,7 +31580,7 @@
         <v>44</v>
       </c>
       <c r="Y335" s="3"/>
-      <c r="Z335" s="10"/>
+      <c r="Z335" s="8"/>
     </row>
     <row r="336" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3">
@@ -31644,7 +31624,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="7" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="V336" s="3">
         <v>3</v>
@@ -31656,7 +31636,7 @@
         <v>44</v>
       </c>
       <c r="Y336" s="3"/>
-      <c r="Z336" s="10"/>
+      <c r="Z336" s="8"/>
     </row>
     <row r="337" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3">
@@ -31704,7 +31684,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="7" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="V337" s="3">
         <v>3</v>
@@ -31716,7 +31696,7 @@
         <v>44</v>
       </c>
       <c r="Y337" s="3"/>
-      <c r="Z337" s="10"/>
+      <c r="Z337" s="8"/>
     </row>
     <row r="338" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3">
@@ -31764,7 +31744,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="V338" s="3">
         <v>2</v>
@@ -31776,7 +31756,7 @@
         <v>44</v>
       </c>
       <c r="Y338" s="3"/>
-      <c r="Z338" s="10"/>
+      <c r="Z338" s="8"/>
     </row>
     <row r="339" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3">
@@ -31824,7 +31804,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="V339" s="3">
         <v>2</v>
@@ -31836,7 +31816,7 @@
         <v>44</v>
       </c>
       <c r="Y339" s="3"/>
-      <c r="Z339" s="10"/>
+      <c r="Z339" s="8"/>
     </row>
     <row r="340" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3">
@@ -31884,7 +31864,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="7" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="V340" s="3">
         <v>2</v>
@@ -31896,7 +31876,7 @@
         <v>44</v>
       </c>
       <c r="Y340" s="3"/>
-      <c r="Z340" s="10"/>
+      <c r="Z340" s="8"/>
     </row>
     <row r="341" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3">
@@ -31958,7 +31938,7 @@
         <v>35</v>
       </c>
       <c r="Y341" s="3"/>
-      <c r="Z341" s="10"/>
+      <c r="Z341" s="8"/>
     </row>
     <row r="342" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3">
@@ -32012,7 +31992,7 @@
         <v>397</v>
       </c>
       <c r="U342" s="7" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="V342" s="3">
         <v>3</v>
@@ -32024,7 +32004,7 @@
         <v>34</v>
       </c>
       <c r="Y342" s="3"/>
-      <c r="Z342" s="10"/>
+      <c r="Z342" s="8"/>
     </row>
     <row r="343" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3">
@@ -32078,7 +32058,7 @@
         <v>2950</v>
       </c>
       <c r="U343" s="7" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="V343" s="3">
         <v>4</v>
@@ -32090,7 +32070,7 @@
         <v>35</v>
       </c>
       <c r="Y343" s="3"/>
-      <c r="Z343" s="10"/>
+      <c r="Z343" s="8"/>
     </row>
     <row r="344" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3">
@@ -32140,7 +32120,7 @@
       </c>
       <c r="T344" s="3"/>
       <c r="U344" s="7" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="V344" s="3">
         <v>3</v>
@@ -32152,7 +32132,7 @@
         <v>35</v>
       </c>
       <c r="Y344" s="3"/>
-      <c r="Z344" s="10"/>
+      <c r="Z344" s="8"/>
     </row>
     <row r="345" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3">
@@ -32204,7 +32184,7 @@
         <v>314</v>
       </c>
       <c r="U345" s="7" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="V345" s="3">
         <v>4</v>
@@ -32216,7 +32196,7 @@
         <v>35</v>
       </c>
       <c r="Y345" s="3"/>
-      <c r="Z345" s="10"/>
+      <c r="Z345" s="8"/>
     </row>
     <row r="346" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3">
@@ -32268,7 +32248,7 @@
         <v>397</v>
       </c>
       <c r="U346" s="7" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="V346" s="3">
         <v>3</v>
@@ -32280,7 +32260,7 @@
         <v>35</v>
       </c>
       <c r="Y346" s="3"/>
-      <c r="Z346" s="10"/>
+      <c r="Z346" s="8"/>
     </row>
     <row r="347" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3">
@@ -32330,7 +32310,7 @@
       </c>
       <c r="T347" s="3"/>
       <c r="U347" s="7" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="V347" s="3">
         <v>4</v>
@@ -32342,7 +32322,7 @@
         <v>34</v>
       </c>
       <c r="Y347" s="3"/>
-      <c r="Z347" s="10"/>
+      <c r="Z347" s="8"/>
     </row>
     <row r="348" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3">
@@ -32396,7 +32376,7 @@
         <v>53</v>
       </c>
       <c r="U348" s="7" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="V348" s="3">
         <v>3</v>
@@ -32408,7 +32388,7 @@
         <v>34</v>
       </c>
       <c r="Y348" s="3"/>
-      <c r="Z348" s="10"/>
+      <c r="Z348" s="8"/>
     </row>
     <row r="349" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3">
@@ -32464,7 +32444,7 @@
         <v>44</v>
       </c>
       <c r="Y349" s="3"/>
-      <c r="Z349" s="10"/>
+      <c r="Z349" s="8"/>
     </row>
     <row r="350" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3">
@@ -32520,7 +32500,7 @@
         <v>44</v>
       </c>
       <c r="Y350" s="3"/>
-      <c r="Z350" s="10"/>
+      <c r="Z350" s="8"/>
     </row>
     <row r="351" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3">
@@ -32574,7 +32554,7 @@
         <v>281</v>
       </c>
       <c r="U351" s="7" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="V351" s="3">
         <v>3</v>
@@ -32586,7 +32566,7 @@
         <v>35</v>
       </c>
       <c r="Y351" s="3"/>
-      <c r="Z351" s="10"/>
+      <c r="Z351" s="8"/>
     </row>
     <row r="352" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3">
@@ -32640,7 +32620,7 @@
         <v>74</v>
       </c>
       <c r="U352" s="7" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
       <c r="V352" s="3">
         <v>3</v>
@@ -32652,7 +32632,7 @@
         <v>35</v>
       </c>
       <c r="Y352" s="3"/>
-      <c r="Z352" s="10"/>
+      <c r="Z352" s="8"/>
     </row>
     <row r="353" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3">
@@ -32702,7 +32682,7 @@
       </c>
       <c r="T353" s="3"/>
       <c r="U353" s="7" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="V353" s="3">
         <v>2</v>
@@ -32714,7 +32694,7 @@
         <v>35</v>
       </c>
       <c r="Y353" s="3"/>
-      <c r="Z353" s="10"/>
+      <c r="Z353" s="8"/>
     </row>
     <row r="354" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3">
@@ -32764,7 +32744,7 @@
       </c>
       <c r="T354" s="3"/>
       <c r="U354" s="7" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="V354" s="3">
         <v>3</v>
@@ -32776,7 +32756,7 @@
         <v>34</v>
       </c>
       <c r="Y354" s="3"/>
-      <c r="Z354" s="10"/>
+      <c r="Z354" s="8"/>
     </row>
     <row r="355" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3">
@@ -32824,7 +32804,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="7" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="V355" s="3">
         <v>3</v>
@@ -32836,7 +32816,7 @@
         <v>35</v>
       </c>
       <c r="Y355" s="3"/>
-      <c r="Z355" s="10"/>
+      <c r="Z355" s="8"/>
     </row>
     <row r="356" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3">
@@ -32884,7 +32864,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="7" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="V356" s="3">
         <v>3</v>
@@ -32896,7 +32876,7 @@
         <v>34</v>
       </c>
       <c r="Y356" s="3"/>
-      <c r="Z356" s="10"/>
+      <c r="Z356" s="8"/>
     </row>
     <row r="357" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3">
@@ -32944,7 +32924,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="7" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="V357" s="3">
         <v>3</v>
@@ -32956,7 +32936,7 @@
         <v>35</v>
       </c>
       <c r="Y357" s="3"/>
-      <c r="Z357" s="10"/>
+      <c r="Z357" s="8"/>
     </row>
     <row r="358" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3">
@@ -33016,7 +32996,7 @@
         <v>44</v>
       </c>
       <c r="Y358" s="3"/>
-      <c r="Z358" s="10"/>
+      <c r="Z358" s="8"/>
     </row>
     <row r="359" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3">
@@ -33068,7 +33048,7 @@
         <v>1515</v>
       </c>
       <c r="U359" s="7" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
       <c r="V359" s="3">
         <v>3</v>
@@ -33080,7 +33060,7 @@
         <v>35</v>
       </c>
       <c r="Y359" s="3"/>
-      <c r="Z359" s="10"/>
+      <c r="Z359" s="8"/>
     </row>
     <row r="360" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3">
@@ -33130,7 +33110,7 @@
       </c>
       <c r="T360" s="3"/>
       <c r="U360" s="7" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="V360" s="3">
         <v>4</v>
@@ -33142,7 +33122,7 @@
         <v>35</v>
       </c>
       <c r="Y360" s="3"/>
-      <c r="Z360" s="10"/>
+      <c r="Z360" s="8"/>
     </row>
     <row r="361" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3">
@@ -33194,7 +33174,7 @@
         <v>1244</v>
       </c>
       <c r="U361" s="7" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="V361" s="3">
         <v>4</v>
@@ -33206,7 +33186,7 @@
         <v>35</v>
       </c>
       <c r="Y361" s="3"/>
-      <c r="Z361" s="10"/>
+      <c r="Z361" s="8"/>
     </row>
     <row r="362" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3">
@@ -33256,7 +33236,7 @@
       </c>
       <c r="T362" s="3"/>
       <c r="U362" s="7" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="V362" s="3">
         <v>3</v>
@@ -33268,7 +33248,7 @@
         <v>35</v>
       </c>
       <c r="Y362" s="3"/>
-      <c r="Z362" s="10"/>
+      <c r="Z362" s="8"/>
     </row>
     <row r="363" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3">
@@ -33318,7 +33298,7 @@
       </c>
       <c r="T363" s="3"/>
       <c r="U363" s="7" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
       <c r="V363" s="3">
         <v>3</v>
@@ -33330,7 +33310,7 @@
         <v>35</v>
       </c>
       <c r="Y363" s="3"/>
-      <c r="Z363" s="10"/>
+      <c r="Z363" s="8"/>
     </row>
     <row r="364" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3">
@@ -33380,7 +33360,7 @@
       </c>
       <c r="T364" s="3"/>
       <c r="U364" s="7" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="V364" s="3">
         <v>3</v>
@@ -33392,7 +33372,7 @@
         <v>35</v>
       </c>
       <c r="Y364" s="3"/>
-      <c r="Z364" s="10"/>
+      <c r="Z364" s="8"/>
     </row>
     <row r="365" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3">
@@ -33444,7 +33424,7 @@
         <v>314</v>
       </c>
       <c r="U365" s="7" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="V365" s="3">
         <v>3</v>
@@ -33456,7 +33436,7 @@
         <v>34</v>
       </c>
       <c r="Y365" s="3"/>
-      <c r="Z365" s="10"/>
+      <c r="Z365" s="8"/>
     </row>
     <row r="366" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3">
@@ -33504,7 +33484,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="7" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="V366" s="3">
         <v>2</v>
@@ -33516,7 +33496,7 @@
         <v>35</v>
       </c>
       <c r="Y366" s="3"/>
-      <c r="Z366" s="10"/>
+      <c r="Z366" s="8"/>
     </row>
     <row r="367" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3">
@@ -33566,7 +33546,7 @@
       </c>
       <c r="T367" s="3"/>
       <c r="U367" s="7" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
       <c r="V367" s="3">
         <v>4</v>
@@ -33578,7 +33558,7 @@
         <v>35</v>
       </c>
       <c r="Y367" s="3"/>
-      <c r="Z367" s="10"/>
+      <c r="Z367" s="8"/>
     </row>
     <row r="368" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3">
@@ -33628,7 +33608,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="7" t="s">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="V368" s="3">
         <v>3</v>
@@ -33640,7 +33620,7 @@
         <v>44</v>
       </c>
       <c r="Y368" s="3"/>
-      <c r="Z368" s="10"/>
+      <c r="Z368" s="8"/>
     </row>
     <row r="369" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3">
@@ -33688,7 +33668,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="7" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="V369" s="3">
         <v>3</v>
@@ -33700,7 +33680,7 @@
         <v>35</v>
       </c>
       <c r="Y369" s="3"/>
-      <c r="Z369" s="10"/>
+      <c r="Z369" s="8"/>
     </row>
     <row r="370" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3">
@@ -33744,7 +33724,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="7" t="s">
-        <v>3281</v>
+        <v>3279</v>
       </c>
       <c r="V370" s="3">
         <v>3</v>
@@ -33756,7 +33736,7 @@
         <v>35</v>
       </c>
       <c r="Y370" s="3"/>
-      <c r="Z370" s="10"/>
+      <c r="Z370" s="8"/>
     </row>
     <row r="371" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3">
@@ -33800,7 +33780,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="7" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="V371" s="3">
         <v>3</v>
@@ -33812,7 +33792,7 @@
         <v>44</v>
       </c>
       <c r="Y371" s="3"/>
-      <c r="Z371" s="10"/>
+      <c r="Z371" s="8"/>
     </row>
     <row r="372" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3">
@@ -33860,7 +33840,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="7" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="V372" s="3">
         <v>2</v>
@@ -33872,7 +33852,7 @@
         <v>44</v>
       </c>
       <c r="Y372" s="3"/>
-      <c r="Z372" s="10"/>
+      <c r="Z372" s="8"/>
     </row>
     <row r="373" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3">
@@ -33920,7 +33900,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="7" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="V373" s="3">
         <v>3</v>
@@ -33932,7 +33912,7 @@
         <v>44</v>
       </c>
       <c r="Y373" s="3"/>
-      <c r="Z373" s="10"/>
+      <c r="Z373" s="8"/>
     </row>
     <row r="374" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3">
@@ -33980,7 +33960,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="7" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="V374" s="3">
         <v>2</v>
@@ -33992,7 +33972,7 @@
         <v>44</v>
       </c>
       <c r="Y374" s="3"/>
-      <c r="Z374" s="10"/>
+      <c r="Z374" s="8"/>
     </row>
     <row r="375" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3">
@@ -34040,7 +34020,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="7" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="V375" s="3">
         <v>3</v>
@@ -34052,7 +34032,7 @@
         <v>44</v>
       </c>
       <c r="Y375" s="3"/>
-      <c r="Z375" s="10"/>
+      <c r="Z375" s="8"/>
     </row>
     <row r="376" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3">
@@ -34100,7 +34080,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="7" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="V376" s="3" t="s">
         <v>44</v>
@@ -34112,7 +34092,7 @@
         <v>44</v>
       </c>
       <c r="Y376" s="3"/>
-      <c r="Z376" s="10"/>
+      <c r="Z376" s="8"/>
     </row>
     <row r="377" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3">
@@ -34172,7 +34152,7 @@
         <v>44</v>
       </c>
       <c r="Y377" s="3"/>
-      <c r="Z377" s="10"/>
+      <c r="Z377" s="8"/>
     </row>
     <row r="378" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3">
@@ -34232,7 +34212,7 @@
         <v>44</v>
       </c>
       <c r="Y378" s="3"/>
-      <c r="Z378" s="10"/>
+      <c r="Z378" s="8"/>
     </row>
     <row r="379" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3">
@@ -34292,7 +34272,7 @@
         <v>44</v>
       </c>
       <c r="Y379" s="3"/>
-      <c r="Z379" s="10"/>
+      <c r="Z379" s="8"/>
     </row>
     <row r="380" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3">
@@ -34352,7 +34332,7 @@
         <v>44</v>
       </c>
       <c r="Y380" s="3"/>
-      <c r="Z380" s="10"/>
+      <c r="Z380" s="8"/>
     </row>
     <row r="381" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3">
@@ -34402,7 +34382,7 @@
       </c>
       <c r="T381" s="3"/>
       <c r="U381" s="7" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="V381" s="3">
         <v>3</v>
@@ -34414,7 +34394,7 @@
         <v>35</v>
       </c>
       <c r="Y381" s="3"/>
-      <c r="Z381" s="10"/>
+      <c r="Z381" s="8"/>
     </row>
     <row r="382" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3">
@@ -34464,7 +34444,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="7" t="s">
-        <v>3287</v>
+        <v>3285</v>
       </c>
       <c r="V382" s="3">
         <v>3</v>
@@ -34476,7 +34456,7 @@
         <v>44</v>
       </c>
       <c r="Y382" s="3"/>
-      <c r="Z382" s="10"/>
+      <c r="Z382" s="8"/>
     </row>
     <row r="383" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3">
@@ -34530,7 +34510,7 @@
         <v>53</v>
       </c>
       <c r="U383" s="7" t="s">
-        <v>3288</v>
+        <v>3286</v>
       </c>
       <c r="V383" s="3">
         <v>3</v>
@@ -34542,7 +34522,7 @@
         <v>35</v>
       </c>
       <c r="Y383" s="3"/>
-      <c r="Z383" s="10"/>
+      <c r="Z383" s="8"/>
     </row>
     <row r="384" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3">
@@ -34592,7 +34572,7 @@
       </c>
       <c r="T384" s="3"/>
       <c r="U384" s="7" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
       <c r="V384" s="3">
         <v>4</v>
@@ -34604,7 +34584,7 @@
         <v>35</v>
       </c>
       <c r="Y384" s="3"/>
-      <c r="Z384" s="10"/>
+      <c r="Z384" s="8"/>
     </row>
     <row r="385" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3">
@@ -34656,7 +34636,7 @@
       </c>
       <c r="T385" s="3"/>
       <c r="U385" s="7" t="s">
-        <v>3290</v>
+        <v>3288</v>
       </c>
       <c r="V385" s="3">
         <v>3</v>
@@ -34668,7 +34648,7 @@
         <v>34</v>
       </c>
       <c r="Y385" s="3"/>
-      <c r="Z385" s="10"/>
+      <c r="Z385" s="8"/>
     </row>
     <row r="386" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3">
@@ -34720,7 +34700,7 @@
         <v>1326</v>
       </c>
       <c r="U386" s="7" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
       <c r="V386" s="3">
         <v>4</v>
@@ -34732,7 +34712,7 @@
         <v>35</v>
       </c>
       <c r="Y386" s="3"/>
-      <c r="Z386" s="10"/>
+      <c r="Z386" s="8"/>
     </row>
     <row r="387" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3">
@@ -34780,7 +34760,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="7" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="V387" s="3">
         <v>3</v>
@@ -34792,7 +34772,7 @@
         <v>35</v>
       </c>
       <c r="Y387" s="3"/>
-      <c r="Z387" s="10"/>
+      <c r="Z387" s="8"/>
     </row>
     <row r="388" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3">
@@ -34840,7 +34820,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="7" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="V388" s="3">
         <v>3</v>
@@ -34852,7 +34832,7 @@
         <v>203</v>
       </c>
       <c r="Y388" s="3"/>
-      <c r="Z388" s="10"/>
+      <c r="Z388" s="8"/>
     </row>
     <row r="389" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3">
@@ -34900,7 +34880,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="7" t="s">
-        <v>3294</v>
+        <v>3292</v>
       </c>
       <c r="V389" s="3">
         <v>3</v>
@@ -34912,7 +34892,7 @@
         <v>35</v>
       </c>
       <c r="Y389" s="3"/>
-      <c r="Z389" s="10"/>
+      <c r="Z389" s="8"/>
     </row>
     <row r="390" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3">
@@ -34960,7 +34940,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="7" t="s">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="V390" s="3">
         <v>4</v>
@@ -34972,7 +34952,7 @@
         <v>35</v>
       </c>
       <c r="Y390" s="3"/>
-      <c r="Z390" s="10"/>
+      <c r="Z390" s="8"/>
     </row>
     <row r="391" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3">
@@ -35022,7 +35002,7 @@
       </c>
       <c r="T391" s="3"/>
       <c r="U391" s="7" t="s">
-        <v>3296</v>
+        <v>3294</v>
       </c>
       <c r="V391" s="3">
         <v>3</v>
@@ -35034,7 +35014,7 @@
         <v>35</v>
       </c>
       <c r="Y391" s="3"/>
-      <c r="Z391" s="10"/>
+      <c r="Z391" s="8"/>
     </row>
     <row r="392" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3">
@@ -35084,7 +35064,7 @@
       </c>
       <c r="T392" s="3"/>
       <c r="U392" s="7" t="s">
-        <v>3297</v>
+        <v>3295</v>
       </c>
       <c r="V392" s="3">
         <v>3</v>
@@ -35096,7 +35076,7 @@
         <v>35</v>
       </c>
       <c r="Y392" s="3"/>
-      <c r="Z392" s="10"/>
+      <c r="Z392" s="8"/>
     </row>
     <row r="393" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3">
@@ -35144,7 +35124,7 @@
       <c r="S393" s="3"/>
       <c r="T393" s="3"/>
       <c r="U393" s="7" t="s">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="V393" s="3">
         <v>3</v>
@@ -35156,7 +35136,7 @@
         <v>35</v>
       </c>
       <c r="Y393" s="3"/>
-      <c r="Z393" s="10"/>
+      <c r="Z393" s="8"/>
     </row>
     <row r="394" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3">
@@ -35204,7 +35184,7 @@
       <c r="S394" s="3"/>
       <c r="T394" s="3"/>
       <c r="U394" s="7" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="V394" s="3">
         <v>3</v>
@@ -35216,7 +35196,7 @@
         <v>35</v>
       </c>
       <c r="Y394" s="3"/>
-      <c r="Z394" s="10"/>
+      <c r="Z394" s="8"/>
     </row>
     <row r="395" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3">
@@ -35268,7 +35248,7 @@
         <v>33</v>
       </c>
       <c r="U395" s="7" t="s">
-        <v>3299</v>
+        <v>3297</v>
       </c>
       <c r="V395" s="3">
         <v>3</v>
@@ -35280,7 +35260,7 @@
         <v>35</v>
       </c>
       <c r="Y395" s="3"/>
-      <c r="Z395" s="10"/>
+      <c r="Z395" s="8"/>
     </row>
     <row r="396" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3">
@@ -35328,7 +35308,7 @@
       <c r="S396" s="3"/>
       <c r="T396" s="3"/>
       <c r="U396" s="7" t="s">
-        <v>3300</v>
+        <v>3298</v>
       </c>
       <c r="V396" s="3">
         <v>2</v>
@@ -35340,7 +35320,7 @@
         <v>35</v>
       </c>
       <c r="Y396" s="3"/>
-      <c r="Z396" s="10"/>
+      <c r="Z396" s="8"/>
     </row>
     <row r="397" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3">
@@ -35390,7 +35370,7 @@
       </c>
       <c r="T397" s="3"/>
       <c r="U397" s="7" t="s">
-        <v>3301</v>
+        <v>3299</v>
       </c>
       <c r="V397" s="3">
         <v>3</v>
@@ -35402,7 +35382,7 @@
         <v>35</v>
       </c>
       <c r="Y397" s="3"/>
-      <c r="Z397" s="10"/>
+      <c r="Z397" s="8"/>
     </row>
     <row r="398" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3">
@@ -35450,7 +35430,7 @@
       <c r="S398" s="3"/>
       <c r="T398" s="3"/>
       <c r="U398" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="V398" s="3">
         <v>3</v>
@@ -35462,7 +35442,7 @@
         <v>44</v>
       </c>
       <c r="Y398" s="3"/>
-      <c r="Z398" s="10"/>
+      <c r="Z398" s="8"/>
     </row>
     <row r="399" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3">
@@ -35514,7 +35494,7 @@
       </c>
       <c r="T399" s="3"/>
       <c r="U399" s="7" t="s">
-        <v>3302</v>
+        <v>3300</v>
       </c>
       <c r="V399" s="3">
         <v>3</v>
@@ -35526,7 +35506,7 @@
         <v>35</v>
       </c>
       <c r="Y399" s="3"/>
-      <c r="Z399" s="10"/>
+      <c r="Z399" s="8"/>
     </row>
     <row r="400" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3">
@@ -35576,7 +35556,7 @@
       </c>
       <c r="T400" s="3"/>
       <c r="U400" s="7" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="V400" s="3">
         <v>3</v>
@@ -35588,7 +35568,7 @@
         <v>35</v>
       </c>
       <c r="Y400" s="3"/>
-      <c r="Z400" s="10"/>
+      <c r="Z400" s="8"/>
     </row>
     <row r="401" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3">
@@ -35638,7 +35618,7 @@
       </c>
       <c r="T401" s="3"/>
       <c r="U401" s="7" t="s">
-        <v>3303</v>
+        <v>3301</v>
       </c>
       <c r="V401" s="3">
         <v>3</v>
@@ -35650,7 +35630,7 @@
         <v>35</v>
       </c>
       <c r="Y401" s="3"/>
-      <c r="Z401" s="10"/>
+      <c r="Z401" s="8"/>
     </row>
     <row r="402" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3">
@@ -35702,7 +35682,7 @@
         <v>33</v>
       </c>
       <c r="U402" s="7" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="V402" s="3">
         <v>3</v>
@@ -35714,7 +35694,7 @@
         <v>35</v>
       </c>
       <c r="Y402" s="3"/>
-      <c r="Z402" s="10"/>
+      <c r="Z402" s="8"/>
     </row>
     <row r="403" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3">
@@ -35764,7 +35744,7 @@
         <v>1326</v>
       </c>
       <c r="U403" s="7" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="V403" s="3">
         <v>3</v>
@@ -35776,7 +35756,7 @@
         <v>35</v>
       </c>
       <c r="Y403" s="3"/>
-      <c r="Z403" s="10"/>
+      <c r="Z403" s="8"/>
     </row>
     <row r="404" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3">
@@ -35824,7 +35804,7 @@
       <c r="S404" s="3"/>
       <c r="T404" s="3"/>
       <c r="U404" s="7" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="V404" s="3">
         <v>3</v>
@@ -35836,7 +35816,7 @@
         <v>35</v>
       </c>
       <c r="Y404" s="3"/>
-      <c r="Z404" s="10"/>
+      <c r="Z404" s="8"/>
     </row>
     <row r="405" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3">
@@ -35884,7 +35864,7 @@
       <c r="S405" s="3"/>
       <c r="T405" s="3"/>
       <c r="U405" s="7" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="V405" s="3">
         <v>3</v>
@@ -35896,7 +35876,7 @@
         <v>35</v>
       </c>
       <c r="Y405" s="3"/>
-      <c r="Z405" s="10"/>
+      <c r="Z405" s="8"/>
     </row>
     <row r="406" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3">
@@ -35944,7 +35924,7 @@
       <c r="S406" s="3"/>
       <c r="T406" s="3"/>
       <c r="U406" s="7" t="s">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="V406" s="3">
         <v>3</v>
@@ -35956,7 +35936,7 @@
         <v>35</v>
       </c>
       <c r="Y406" s="3"/>
-      <c r="Z406" s="10"/>
+      <c r="Z406" s="8"/>
     </row>
     <row r="407" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3">
@@ -36004,7 +35984,7 @@
       <c r="S407" s="3"/>
       <c r="T407" s="3"/>
       <c r="U407" s="7" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="V407" s="3">
         <v>3</v>
@@ -36016,7 +35996,7 @@
         <v>35</v>
       </c>
       <c r="Y407" s="3"/>
-      <c r="Z407" s="10"/>
+      <c r="Z407" s="8"/>
     </row>
     <row r="408" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3">
@@ -36064,7 +36044,7 @@
       <c r="S408" s="3"/>
       <c r="T408" s="3"/>
       <c r="U408" s="7" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="V408" s="3">
         <v>3</v>
@@ -36076,7 +36056,7 @@
         <v>35</v>
       </c>
       <c r="Y408" s="3"/>
-      <c r="Z408" s="10"/>
+      <c r="Z408" s="8"/>
     </row>
     <row r="409" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3">
@@ -36124,7 +36104,7 @@
       <c r="S409" s="3"/>
       <c r="T409" s="3"/>
       <c r="U409" s="7" t="s">
-        <v>3309</v>
+        <v>3307</v>
       </c>
       <c r="V409" s="3">
         <v>3</v>
@@ -36136,7 +36116,7 @@
         <v>35</v>
       </c>
       <c r="Y409" s="3"/>
-      <c r="Z409" s="10"/>
+      <c r="Z409" s="8"/>
     </row>
     <row r="410" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3">
@@ -36184,7 +36164,7 @@
       <c r="S410" s="3"/>
       <c r="T410" s="3"/>
       <c r="U410" s="7" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="V410" s="3">
         <v>3</v>
@@ -36196,7 +36176,7 @@
         <v>35</v>
       </c>
       <c r="Y410" s="3"/>
-      <c r="Z410" s="10"/>
+      <c r="Z410" s="8"/>
     </row>
     <row r="411" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3">
@@ -36250,7 +36230,7 @@
         <v>240</v>
       </c>
       <c r="U411" s="7" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
       <c r="V411" s="3">
         <v>3</v>
@@ -36262,7 +36242,7 @@
         <v>35</v>
       </c>
       <c r="Y411" s="3"/>
-      <c r="Z411" s="10"/>
+      <c r="Z411" s="8"/>
     </row>
     <row r="412" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3">
@@ -36310,7 +36290,7 @@
       <c r="S412" s="3"/>
       <c r="T412" s="3"/>
       <c r="U412" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="V412" s="3">
         <v>3</v>
@@ -36322,7 +36302,7 @@
         <v>44</v>
       </c>
       <c r="Y412" s="3"/>
-      <c r="Z412" s="10"/>
+      <c r="Z412" s="8"/>
     </row>
     <row r="413" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3">
@@ -36382,7 +36362,7 @@
         <v>44</v>
       </c>
       <c r="Y413" s="3"/>
-      <c r="Z413" s="10"/>
+      <c r="Z413" s="8"/>
     </row>
     <row r="414" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3">
@@ -36434,7 +36414,7 @@
         <v>2950</v>
       </c>
       <c r="U414" s="7" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="V414" s="3">
         <v>3</v>
@@ -36446,7 +36426,7 @@
         <v>35</v>
       </c>
       <c r="Y414" s="3"/>
-      <c r="Z414" s="10"/>
+      <c r="Z414" s="8"/>
     </row>
     <row r="415" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3">
@@ -36496,7 +36476,7 @@
       </c>
       <c r="T415" s="3"/>
       <c r="U415" s="7" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="V415" s="3">
         <v>3</v>
@@ -36508,7 +36488,7 @@
         <v>35</v>
       </c>
       <c r="Y415" s="3"/>
-      <c r="Z415" s="10"/>
+      <c r="Z415" s="8"/>
     </row>
     <row r="416" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3">
@@ -36558,7 +36538,7 @@
       </c>
       <c r="T416" s="3"/>
       <c r="U416" s="7" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="V416" s="3">
         <v>3</v>
@@ -36570,7 +36550,7 @@
         <v>34</v>
       </c>
       <c r="Y416" s="3"/>
-      <c r="Z416" s="10"/>
+      <c r="Z416" s="8"/>
     </row>
     <row r="417" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3">
@@ -36620,7 +36600,7 @@
       <c r="S417" s="3"/>
       <c r="T417" s="3"/>
       <c r="U417" s="7" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="V417" s="3">
         <v>3</v>
@@ -36632,7 +36612,7 @@
         <v>35</v>
       </c>
       <c r="Y417" s="3"/>
-      <c r="Z417" s="10"/>
+      <c r="Z417" s="8"/>
     </row>
     <row r="418" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3">
@@ -36680,7 +36660,7 @@
       <c r="S418" s="3"/>
       <c r="T418" s="3"/>
       <c r="U418" s="7" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="V418" s="3">
         <v>3</v>
@@ -36692,7 +36672,7 @@
         <v>203</v>
       </c>
       <c r="Y418" s="3"/>
-      <c r="Z418" s="10"/>
+      <c r="Z418" s="8"/>
     </row>
     <row r="419" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3">
@@ -36740,7 +36720,7 @@
       <c r="S419" s="3"/>
       <c r="T419" s="3"/>
       <c r="U419" s="7" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
       <c r="V419" s="3">
         <v>2</v>
@@ -36752,7 +36732,7 @@
         <v>35</v>
       </c>
       <c r="Y419" s="3"/>
-      <c r="Z419" s="10"/>
+      <c r="Z419" s="8"/>
     </row>
     <row r="420" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3">
@@ -36802,7 +36782,7 @@
       </c>
       <c r="T420" s="3"/>
       <c r="U420" s="7" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="V420" s="3">
         <v>3</v>
@@ -36814,7 +36794,7 @@
         <v>34</v>
       </c>
       <c r="Y420" s="3"/>
-      <c r="Z420" s="10"/>
+      <c r="Z420" s="8"/>
     </row>
     <row r="421" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3">
@@ -36866,7 +36846,7 @@
         <v>314</v>
       </c>
       <c r="U421" s="7" t="s">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="V421" s="3">
         <v>3</v>
@@ -36878,7 +36858,7 @@
         <v>34</v>
       </c>
       <c r="Y421" s="3"/>
-      <c r="Z421" s="10"/>
+      <c r="Z421" s="8"/>
     </row>
     <row r="422" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3">
@@ -36928,7 +36908,7 @@
       </c>
       <c r="T422" s="3"/>
       <c r="U422" s="7" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
       <c r="V422" s="3">
         <v>3</v>
@@ -36940,7 +36920,7 @@
         <v>35</v>
       </c>
       <c r="Y422" s="3"/>
-      <c r="Z422" s="10"/>
+      <c r="Z422" s="8"/>
     </row>
     <row r="423" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3">
@@ -36990,7 +36970,7 @@
       </c>
       <c r="T423" s="3"/>
       <c r="U423" s="7" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
       <c r="V423" s="3">
         <v>3</v>
@@ -37002,7 +36982,7 @@
         <v>35</v>
       </c>
       <c r="Y423" s="3"/>
-      <c r="Z423" s="10"/>
+      <c r="Z423" s="8"/>
     </row>
     <row r="424" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3">
@@ -37050,7 +37030,7 @@
       <c r="S424" s="3"/>
       <c r="T424" s="3"/>
       <c r="U424" s="7" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
       <c r="V424" s="3">
         <v>3</v>
@@ -37062,7 +37042,7 @@
         <v>203</v>
       </c>
       <c r="Y424" s="3"/>
-      <c r="Z424" s="10"/>
+      <c r="Z424" s="8"/>
     </row>
     <row r="425" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3">
@@ -37110,7 +37090,7 @@
       <c r="S425" s="3"/>
       <c r="T425" s="3"/>
       <c r="U425" s="7" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="V425" s="3">
         <v>3</v>
@@ -37122,7 +37102,7 @@
         <v>203</v>
       </c>
       <c r="Y425" s="3"/>
-      <c r="Z425" s="10"/>
+      <c r="Z425" s="8"/>
     </row>
     <row r="426" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3">
@@ -37172,7 +37152,7 @@
       </c>
       <c r="T426" s="3"/>
       <c r="U426" s="7" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="V426" s="3">
         <v>3</v>
@@ -37184,7 +37164,7 @@
         <v>35</v>
       </c>
       <c r="Y426" s="3"/>
-      <c r="Z426" s="10"/>
+      <c r="Z426" s="8"/>
     </row>
     <row r="427" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3">
@@ -37238,7 +37218,7 @@
         <v>53</v>
       </c>
       <c r="U427" s="7" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="V427" s="3">
         <v>3</v>
@@ -37250,7 +37230,7 @@
         <v>35</v>
       </c>
       <c r="Y427" s="3"/>
-      <c r="Z427" s="10"/>
+      <c r="Z427" s="8"/>
     </row>
     <row r="428" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3">
@@ -37300,7 +37280,7 @@
       </c>
       <c r="T428" s="3"/>
       <c r="U428" s="7" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="V428" s="3">
         <v>3</v>
@@ -37312,7 +37292,7 @@
         <v>35</v>
       </c>
       <c r="Y428" s="3"/>
-      <c r="Z428" s="10"/>
+      <c r="Z428" s="8"/>
     </row>
     <row r="429" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3">
@@ -37362,7 +37342,7 @@
         <v>53</v>
       </c>
       <c r="U429" s="7" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
       <c r="V429" s="3">
         <v>3</v>
@@ -37374,7 +37354,7 @@
         <v>35</v>
       </c>
       <c r="Y429" s="3"/>
-      <c r="Z429" s="10"/>
+      <c r="Z429" s="8"/>
     </row>
     <row r="430" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3">
@@ -37426,7 +37406,7 @@
       </c>
       <c r="T430" s="3"/>
       <c r="U430" s="7" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="V430" s="3">
         <v>4</v>
@@ -37438,7 +37418,7 @@
         <v>34</v>
       </c>
       <c r="Y430" s="3"/>
-      <c r="Z430" s="10"/>
+      <c r="Z430" s="8"/>
     </row>
     <row r="431" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3">
@@ -37486,7 +37466,7 @@
       <c r="S431" s="3"/>
       <c r="T431" s="3"/>
       <c r="U431" s="7" t="s">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="V431" s="3">
         <v>3</v>
@@ -37498,7 +37478,7 @@
         <v>44</v>
       </c>
       <c r="Y431" s="3"/>
-      <c r="Z431" s="10"/>
+      <c r="Z431" s="8"/>
     </row>
     <row r="432" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3">
@@ -37548,7 +37528,7 @@
       <c r="S432" s="3"/>
       <c r="T432" s="3"/>
       <c r="U432" s="7" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
       <c r="V432" s="3">
         <v>3</v>
@@ -37560,7 +37540,7 @@
         <v>44</v>
       </c>
       <c r="Y432" s="3"/>
-      <c r="Z432" s="10"/>
+      <c r="Z432" s="8"/>
     </row>
     <row r="433" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3">
@@ -37620,7 +37600,7 @@
         <v>44</v>
       </c>
       <c r="Y433" s="3"/>
-      <c r="Z433" s="10"/>
+      <c r="Z433" s="8"/>
     </row>
     <row r="434" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3">
@@ -37680,7 +37660,7 @@
         <v>44</v>
       </c>
       <c r="Y434" s="3"/>
-      <c r="Z434" s="10"/>
+      <c r="Z434" s="8"/>
     </row>
     <row r="435" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3">
@@ -37734,7 +37714,7 @@
         <v>2071</v>
       </c>
       <c r="U435" s="7" t="s">
-        <v>3325</v>
+        <v>3323</v>
       </c>
       <c r="V435" s="3">
         <v>3</v>
@@ -37746,7 +37726,7 @@
         <v>35</v>
       </c>
       <c r="Y435" s="3"/>
-      <c r="Z435" s="10"/>
+      <c r="Z435" s="8"/>
     </row>
     <row r="436" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3">
@@ -37798,7 +37778,7 @@
       </c>
       <c r="T436" s="3"/>
       <c r="U436" s="7" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="V436" s="3">
         <v>3</v>
@@ -37810,7 +37790,7 @@
         <v>35</v>
       </c>
       <c r="Y436" s="3"/>
-      <c r="Z436" s="10"/>
+      <c r="Z436" s="8"/>
     </row>
     <row r="437" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3">
@@ -37860,7 +37840,7 @@
       <c r="S437" s="3"/>
       <c r="T437" s="3"/>
       <c r="U437" s="7" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="V437" s="3">
         <v>3</v>
@@ -37872,7 +37852,7 @@
         <v>44</v>
       </c>
       <c r="Y437" s="3"/>
-      <c r="Z437" s="10"/>
+      <c r="Z437" s="8"/>
     </row>
     <row r="438" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3">
@@ -37926,7 +37906,7 @@
         <v>74</v>
       </c>
       <c r="U438" s="7" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
       <c r="V438" s="3">
         <v>3</v>
@@ -37938,7 +37918,7 @@
         <v>35</v>
       </c>
       <c r="Y438" s="3"/>
-      <c r="Z438" s="10"/>
+      <c r="Z438" s="8"/>
     </row>
     <row r="439" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3">
@@ -37988,7 +37968,7 @@
       <c r="S439" s="3"/>
       <c r="T439" s="3"/>
       <c r="U439" s="7" t="s">
-        <v>3329</v>
+        <v>3327</v>
       </c>
       <c r="V439" s="3" t="s">
         <v>44</v>
@@ -38000,7 +37980,7 @@
         <v>44</v>
       </c>
       <c r="Y439" s="3"/>
-      <c r="Z439" s="10"/>
+      <c r="Z439" s="8"/>
     </row>
     <row r="440" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3">
@@ -38052,7 +38032,7 @@
       </c>
       <c r="T440" s="3"/>
       <c r="U440" s="7" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="V440" s="3">
         <v>4</v>
@@ -38064,7 +38044,7 @@
         <v>35</v>
       </c>
       <c r="Y440" s="3"/>
-      <c r="Z440" s="10"/>
+      <c r="Z440" s="8"/>
     </row>
     <row r="441" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3">
@@ -38110,7 +38090,7 @@
       </c>
       <c r="T441" s="3"/>
       <c r="U441" s="7" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="V441" s="3">
         <v>3</v>
@@ -38122,7 +38102,7 @@
         <v>35</v>
       </c>
       <c r="Y441" s="3"/>
-      <c r="Z441" s="10"/>
+      <c r="Z441" s="8"/>
     </row>
     <row r="442" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3">
@@ -38174,7 +38154,7 @@
       </c>
       <c r="T442" s="3"/>
       <c r="U442" s="7" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
       <c r="V442" s="3">
         <v>4</v>
@@ -38186,7 +38166,7 @@
         <v>34</v>
       </c>
       <c r="Y442" s="3"/>
-      <c r="Z442" s="10"/>
+      <c r="Z442" s="8"/>
     </row>
     <row r="443" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3">
@@ -38230,7 +38210,7 @@
       <c r="S443" s="3"/>
       <c r="T443" s="3"/>
       <c r="U443" s="7" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="V443" s="3">
         <v>3</v>
@@ -38242,7 +38222,7 @@
         <v>35</v>
       </c>
       <c r="Y443" s="3"/>
-      <c r="Z443" s="10"/>
+      <c r="Z443" s="8"/>
     </row>
     <row r="444" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3">
@@ -38288,7 +38268,7 @@
       </c>
       <c r="T444" s="3"/>
       <c r="U444" s="7" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
       <c r="V444" s="3">
         <v>3</v>
@@ -38300,7 +38280,7 @@
         <v>35</v>
       </c>
       <c r="Y444" s="3"/>
-      <c r="Z444" s="10"/>
+      <c r="Z444" s="8"/>
     </row>
     <row r="445" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3">
@@ -38346,7 +38326,7 @@
         <v>240</v>
       </c>
       <c r="U445" s="7" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
       <c r="V445" s="3">
         <v>4</v>
@@ -38358,7 +38338,7 @@
         <v>35</v>
       </c>
       <c r="Y445" s="3"/>
-      <c r="Z445" s="10"/>
+      <c r="Z445" s="8"/>
     </row>
     <row r="446" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3">
@@ -38404,7 +38384,7 @@
         <v>281</v>
       </c>
       <c r="U446" s="7" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
       <c r="V446" s="3">
         <v>3</v>
@@ -38416,7 +38396,7 @@
         <v>35</v>
       </c>
       <c r="Y446" s="3"/>
-      <c r="Z446" s="10"/>
+      <c r="Z446" s="8"/>
     </row>
     <row r="447" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3">
@@ -38460,7 +38440,7 @@
       <c r="S447" s="3"/>
       <c r="T447" s="3"/>
       <c r="U447" s="7" t="s">
-        <v>3337</v>
+        <v>3335</v>
       </c>
       <c r="V447" s="3">
         <v>2</v>
@@ -38472,7 +38452,7 @@
         <v>203</v>
       </c>
       <c r="Y447" s="3"/>
-      <c r="Z447" s="10"/>
+      <c r="Z447" s="8"/>
     </row>
     <row r="448" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3">
@@ -38518,7 +38498,7 @@
         <v>281</v>
       </c>
       <c r="U448" s="7" t="s">
-        <v>3338</v>
+        <v>3336</v>
       </c>
       <c r="V448" s="3">
         <v>3</v>
@@ -38530,7 +38510,7 @@
         <v>34</v>
       </c>
       <c r="Y448" s="3"/>
-      <c r="Z448" s="10"/>
+      <c r="Z448" s="8"/>
     </row>
     <row r="449" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3">
@@ -38574,7 +38554,7 @@
       <c r="S449" s="3"/>
       <c r="T449" s="3"/>
       <c r="U449" s="7" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="V449" s="3">
         <v>3</v>
@@ -38586,7 +38566,7 @@
         <v>35</v>
       </c>
       <c r="Y449" s="3"/>
-      <c r="Z449" s="10"/>
+      <c r="Z449" s="8"/>
     </row>
     <row r="450" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3">
@@ -38632,7 +38612,7 @@
         <v>33</v>
       </c>
       <c r="U450" s="7" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="V450" s="3">
         <v>3</v>
@@ -38644,7 +38624,7 @@
         <v>34</v>
       </c>
       <c r="Y450" s="3"/>
-      <c r="Z450" s="10"/>
+      <c r="Z450" s="8"/>
     </row>
     <row r="451" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3">
@@ -38690,7 +38670,7 @@
         <v>281</v>
       </c>
       <c r="U451" s="7" t="s">
-        <v>3341</v>
+        <v>3339</v>
       </c>
       <c r="V451" s="3">
         <v>3</v>
@@ -38702,7 +38682,7 @@
         <v>34</v>
       </c>
       <c r="Y451" s="3"/>
-      <c r="Z451" s="10"/>
+      <c r="Z451" s="8"/>
     </row>
     <row r="452" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3">
@@ -38746,7 +38726,7 @@
       <c r="S452" s="3"/>
       <c r="T452" s="3"/>
       <c r="U452" s="7" t="s">
-        <v>3342</v>
+        <v>3340</v>
       </c>
       <c r="V452" s="3">
         <v>2</v>
@@ -38758,7 +38738,7 @@
         <v>203</v>
       </c>
       <c r="Y452" s="3"/>
-      <c r="Z452" s="10"/>
+      <c r="Z452" s="8"/>
     </row>
     <row r="453" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3">
@@ -38802,7 +38782,7 @@
       <c r="S453" s="3"/>
       <c r="T453" s="3"/>
       <c r="U453" s="7" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="V453" s="3">
         <v>3</v>
@@ -38814,7 +38794,7 @@
         <v>35</v>
       </c>
       <c r="Y453" s="3"/>
-      <c r="Z453" s="10"/>
+      <c r="Z453" s="8"/>
     </row>
     <row r="454" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3">
@@ -38858,7 +38838,7 @@
       <c r="S454" s="3"/>
       <c r="T454" s="3"/>
       <c r="U454" s="7" t="s">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="V454" s="3">
         <v>3</v>
@@ -38870,7 +38850,7 @@
         <v>44</v>
       </c>
       <c r="Y454" s="3"/>
-      <c r="Z454" s="10"/>
+      <c r="Z454" s="8"/>
     </row>
     <row r="455" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3">
@@ -38914,7 +38894,7 @@
       <c r="S455" s="3"/>
       <c r="T455" s="3"/>
       <c r="U455" s="7" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="V455" s="3">
         <v>3</v>
@@ -38926,7 +38906,7 @@
         <v>44</v>
       </c>
       <c r="Y455" s="3"/>
-      <c r="Z455" s="10"/>
+      <c r="Z455" s="8"/>
     </row>
     <row r="456" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3">
@@ -38970,7 +38950,7 @@
       <c r="S456" s="3"/>
       <c r="T456" s="3"/>
       <c r="U456" s="7" t="s">
-        <v>3344</v>
+        <v>3342</v>
       </c>
       <c r="V456" s="3">
         <v>3</v>
@@ -38982,7 +38962,7 @@
         <v>44</v>
       </c>
       <c r="Y456" s="3"/>
-      <c r="Z456" s="10"/>
+      <c r="Z456" s="8"/>
     </row>
     <row r="457" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3">
@@ -39030,7 +39010,7 @@
       <c r="S457" s="3"/>
       <c r="T457" s="3"/>
       <c r="U457" s="7" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="V457" s="3">
         <v>3</v>
@@ -39042,7 +39022,7 @@
         <v>44</v>
       </c>
       <c r="Y457" s="3"/>
-      <c r="Z457" s="10"/>
+      <c r="Z457" s="8"/>
     </row>
     <row r="458" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3">
@@ -39102,7 +39082,7 @@
         <v>44</v>
       </c>
       <c r="Y458" s="3"/>
-      <c r="Z458" s="10"/>
+      <c r="Z458" s="8"/>
     </row>
     <row r="459" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3">
@@ -39146,7 +39126,7 @@
       <c r="S459" s="3"/>
       <c r="T459" s="3"/>
       <c r="U459" s="7" t="s">
-        <v>3345</v>
+        <v>3343</v>
       </c>
       <c r="V459" s="3">
         <v>3</v>
@@ -39158,7 +39138,7 @@
         <v>35</v>
       </c>
       <c r="Y459" s="3"/>
-      <c r="Z459" s="10"/>
+      <c r="Z459" s="8"/>
     </row>
     <row r="460" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3">
@@ -39202,7 +39182,7 @@
       <c r="S460" s="3"/>
       <c r="T460" s="3"/>
       <c r="U460" s="7" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="V460" s="3">
         <v>3</v>
@@ -39214,7 +39194,7 @@
         <v>35</v>
       </c>
       <c r="Y460" s="3"/>
-      <c r="Z460" s="10"/>
+      <c r="Z460" s="8"/>
     </row>
     <row r="461" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3">
@@ -39266,7 +39246,7 @@
         <v>397</v>
       </c>
       <c r="U461" s="7" t="s">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="V461" s="3">
         <v>3</v>
@@ -39278,7 +39258,7 @@
         <v>203</v>
       </c>
       <c r="Y461" s="3"/>
-      <c r="Z461" s="10"/>
+      <c r="Z461" s="8"/>
     </row>
     <row r="462" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3">
@@ -39324,7 +39304,7 @@
       </c>
       <c r="T462" s="3"/>
       <c r="U462" s="7" t="s">
-        <v>3348</v>
+        <v>3346</v>
       </c>
       <c r="V462" s="3">
         <v>4</v>
@@ -39336,7 +39316,7 @@
         <v>35</v>
       </c>
       <c r="Y462" s="3"/>
-      <c r="Z462" s="10"/>
+      <c r="Z462" s="8"/>
     </row>
     <row r="463" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3">
@@ -39384,7 +39364,7 @@
       <c r="S463" s="3"/>
       <c r="T463" s="3"/>
       <c r="U463" s="7" t="s">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="V463" s="3">
         <v>2</v>
@@ -39396,7 +39376,7 @@
         <v>44</v>
       </c>
       <c r="Y463" s="3"/>
-      <c r="Z463" s="10"/>
+      <c r="Z463" s="8"/>
     </row>
     <row r="464" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3">
@@ -39442,7 +39422,7 @@
       <c r="S464" s="3"/>
       <c r="T464" s="3"/>
       <c r="U464" s="7" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="V464" s="3">
         <v>3</v>
@@ -39454,7 +39434,7 @@
         <v>34</v>
       </c>
       <c r="Y464" s="3"/>
-      <c r="Z464" s="10"/>
+      <c r="Z464" s="8"/>
     </row>
     <row r="465" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3">
@@ -39518,7 +39498,7 @@
         <v>35</v>
       </c>
       <c r="Y465" s="3"/>
-      <c r="Z465" s="10"/>
+      <c r="Z465" s="8"/>
     </row>
     <row r="466" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3">
@@ -39564,7 +39544,7 @@
       </c>
       <c r="T466" s="3"/>
       <c r="U466" s="7" t="s">
-        <v>3351</v>
+        <v>3349</v>
       </c>
       <c r="V466" s="3">
         <v>3</v>
@@ -39576,7 +39556,7 @@
         <v>35</v>
       </c>
       <c r="Y466" s="3"/>
-      <c r="Z466" s="10"/>
+      <c r="Z466" s="8"/>
     </row>
     <row r="467" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3">
@@ -39622,7 +39602,7 @@
       </c>
       <c r="T467" s="3"/>
       <c r="U467" s="7" t="s">
-        <v>3352</v>
+        <v>3350</v>
       </c>
       <c r="V467" s="3">
         <v>3</v>
@@ -39634,7 +39614,7 @@
         <v>35</v>
       </c>
       <c r="Y467" s="3"/>
-      <c r="Z467" s="10"/>
+      <c r="Z467" s="8"/>
     </row>
     <row r="468" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3">
@@ -39680,7 +39660,7 @@
       </c>
       <c r="T468" s="3"/>
       <c r="U468" s="7" t="s">
-        <v>3353</v>
+        <v>3351</v>
       </c>
       <c r="V468" s="3">
         <v>3</v>
@@ -39692,7 +39672,7 @@
         <v>35</v>
       </c>
       <c r="Y468" s="3"/>
-      <c r="Z468" s="10"/>
+      <c r="Z468" s="8"/>
     </row>
     <row r="469" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3">
@@ -39738,7 +39718,7 @@
       </c>
       <c r="T469" s="3"/>
       <c r="U469" s="7" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
       <c r="V469" s="3">
         <v>3</v>
@@ -39750,7 +39730,7 @@
         <v>35</v>
       </c>
       <c r="Y469" s="3"/>
-      <c r="Z469" s="10"/>
+      <c r="Z469" s="8"/>
     </row>
     <row r="470" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3">
@@ -39798,7 +39778,7 @@
         <v>314</v>
       </c>
       <c r="U470" s="7" t="s">
-        <v>3355</v>
+        <v>3353</v>
       </c>
       <c r="V470" s="3">
         <v>4</v>
@@ -39810,7 +39790,7 @@
         <v>35</v>
       </c>
       <c r="Y470" s="3"/>
-      <c r="Z470" s="10"/>
+      <c r="Z470" s="8"/>
     </row>
     <row r="471" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3">
@@ -39858,7 +39838,7 @@
         <v>314</v>
       </c>
       <c r="U471" s="7" t="s">
-        <v>3356</v>
+        <v>3354</v>
       </c>
       <c r="V471" s="3">
         <v>3</v>
@@ -39870,7 +39850,7 @@
         <v>35</v>
       </c>
       <c r="Y471" s="3"/>
-      <c r="Z471" s="10"/>
+      <c r="Z471" s="8"/>
     </row>
     <row r="472" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3">
@@ -39916,7 +39896,7 @@
       </c>
       <c r="T472" s="3"/>
       <c r="U472" s="7" t="s">
-        <v>3357</v>
+        <v>3355</v>
       </c>
       <c r="V472" s="3">
         <v>3</v>
@@ -39928,7 +39908,7 @@
         <v>34</v>
       </c>
       <c r="Y472" s="3"/>
-      <c r="Z472" s="10"/>
+      <c r="Z472" s="8"/>
     </row>
     <row r="473" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3">
@@ -39972,7 +39952,7 @@
       <c r="S473" s="3"/>
       <c r="T473" s="3"/>
       <c r="U473" s="7" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="V473" s="3">
         <v>3</v>
@@ -39984,7 +39964,7 @@
         <v>203</v>
       </c>
       <c r="Y473" s="3"/>
-      <c r="Z473" s="10"/>
+      <c r="Z473" s="8"/>
     </row>
     <row r="474" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3">
@@ -40034,7 +40014,7 @@
       </c>
       <c r="T474" s="3"/>
       <c r="U474" s="7" t="s">
-        <v>3358</v>
+        <v>3356</v>
       </c>
       <c r="V474" s="3">
         <v>3</v>
@@ -40046,7 +40026,7 @@
         <v>35</v>
       </c>
       <c r="Y474" s="3"/>
-      <c r="Z474" s="10"/>
+      <c r="Z474" s="8"/>
     </row>
     <row r="475" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3">
@@ -40090,7 +40070,7 @@
       <c r="S475" s="3"/>
       <c r="T475" s="3"/>
       <c r="U475" s="7" t="s">
-        <v>3359</v>
+        <v>3357</v>
       </c>
       <c r="V475" s="3">
         <v>3</v>
@@ -40102,7 +40082,7 @@
         <v>203</v>
       </c>
       <c r="Y475" s="3"/>
-      <c r="Z475" s="10"/>
+      <c r="Z475" s="8"/>
     </row>
     <row r="476" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3">
@@ -40148,7 +40128,7 @@
       </c>
       <c r="T476" s="3"/>
       <c r="U476" s="7" t="s">
-        <v>3360</v>
+        <v>3358</v>
       </c>
       <c r="V476" s="3">
         <v>3</v>
@@ -40160,7 +40140,7 @@
         <v>35</v>
       </c>
       <c r="Y476" s="3"/>
-      <c r="Z476" s="10"/>
+      <c r="Z476" s="8"/>
     </row>
     <row r="477" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3">
@@ -40210,7 +40190,7 @@
       </c>
       <c r="T477" s="3"/>
       <c r="U477" s="7" t="s">
-        <v>3361</v>
+        <v>3359</v>
       </c>
       <c r="V477" s="3">
         <v>3</v>
@@ -40222,7 +40202,7 @@
         <v>35</v>
       </c>
       <c r="Y477" s="3"/>
-      <c r="Z477" s="10"/>
+      <c r="Z477" s="8"/>
     </row>
     <row r="478" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3">
@@ -40266,7 +40246,7 @@
       <c r="S478" s="3"/>
       <c r="T478" s="3"/>
       <c r="U478" s="7" t="s">
-        <v>3362</v>
+        <v>3360</v>
       </c>
       <c r="V478" s="3">
         <v>3</v>
@@ -40278,7 +40258,7 @@
         <v>35</v>
       </c>
       <c r="Y478" s="3"/>
-      <c r="Z478" s="10"/>
+      <c r="Z478" s="8"/>
     </row>
     <row r="479" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3">
@@ -40326,7 +40306,7 @@
       <c r="S479" s="3"/>
       <c r="T479" s="3"/>
       <c r="U479" s="7" t="s">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="V479" s="3">
         <v>2</v>
@@ -40338,7 +40318,7 @@
         <v>35</v>
       </c>
       <c r="Y479" s="3"/>
-      <c r="Z479" s="10"/>
+      <c r="Z479" s="8"/>
     </row>
     <row r="480" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3">
@@ -40382,7 +40362,7 @@
       <c r="S480" s="3"/>
       <c r="T480" s="3"/>
       <c r="U480" s="7" t="s">
-        <v>3364</v>
+        <v>3362</v>
       </c>
       <c r="V480" s="3">
         <v>3</v>
@@ -40394,7 +40374,7 @@
         <v>35</v>
       </c>
       <c r="Y480" s="3"/>
-      <c r="Z480" s="10"/>
+      <c r="Z480" s="8"/>
     </row>
     <row r="481" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3">
@@ -40438,7 +40418,7 @@
       <c r="S481" s="3"/>
       <c r="T481" s="3"/>
       <c r="U481" s="7" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="V481" s="3">
         <v>3</v>
@@ -40450,7 +40430,7 @@
         <v>35</v>
       </c>
       <c r="Y481" s="3"/>
-      <c r="Z481" s="10"/>
+      <c r="Z481" s="8"/>
     </row>
     <row r="482" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3">
@@ -40498,7 +40478,7 @@
       <c r="S482" s="3"/>
       <c r="T482" s="3"/>
       <c r="U482" s="7" t="s">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="V482" s="3" t="s">
         <v>44</v>
@@ -40510,7 +40490,7 @@
         <v>44</v>
       </c>
       <c r="Y482" s="3"/>
-      <c r="Z482" s="10"/>
+      <c r="Z482" s="8"/>
     </row>
     <row r="483" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3">
@@ -40564,7 +40544,7 @@
         <v>445</v>
       </c>
       <c r="U483" s="7" t="s">
-        <v>3366</v>
+        <v>3364</v>
       </c>
       <c r="V483" s="3">
         <v>2</v>
@@ -40576,7 +40556,7 @@
         <v>35</v>
       </c>
       <c r="Y483" s="3"/>
-      <c r="Z483" s="10"/>
+      <c r="Z483" s="8"/>
     </row>
     <row r="484" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3">
@@ -40628,7 +40608,7 @@
       </c>
       <c r="T484" s="3"/>
       <c r="U484" s="7" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
       <c r="V484" s="3">
         <v>3</v>
@@ -40640,7 +40620,7 @@
         <v>35</v>
       </c>
       <c r="Y484" s="3"/>
-      <c r="Z484" s="10"/>
+      <c r="Z484" s="8"/>
     </row>
     <row r="485" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3">
@@ -40692,7 +40672,7 @@
       </c>
       <c r="T485" s="3"/>
       <c r="U485" s="7" t="s">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="V485" s="3">
         <v>3</v>
@@ -40704,7 +40684,7 @@
         <v>35</v>
       </c>
       <c r="Y485" s="3"/>
-      <c r="Z485" s="10"/>
+      <c r="Z485" s="8"/>
     </row>
     <row r="486" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3">
@@ -40756,7 +40736,7 @@
       </c>
       <c r="T486" s="3"/>
       <c r="U486" s="7" t="s">
-        <v>3369</v>
+        <v>3367</v>
       </c>
       <c r="V486" s="3">
         <v>3</v>
@@ -40768,7 +40748,7 @@
         <v>35</v>
       </c>
       <c r="Y486" s="3"/>
-      <c r="Z486" s="10"/>
+      <c r="Z486" s="8"/>
     </row>
     <row r="487" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3">
@@ -40816,7 +40796,7 @@
       <c r="S487" s="3"/>
       <c r="T487" s="3"/>
       <c r="U487" s="7" t="s">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="V487" s="3">
         <v>3</v>
@@ -40828,7 +40808,7 @@
         <v>35</v>
       </c>
       <c r="Y487" s="3"/>
-      <c r="Z487" s="10"/>
+      <c r="Z487" s="8"/>
     </row>
     <row r="488" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3">
@@ -40880,7 +40860,7 @@
         <v>2950</v>
       </c>
       <c r="U488" s="7" t="s">
-        <v>3371</v>
+        <v>3369</v>
       </c>
       <c r="V488" s="3">
         <v>3</v>
@@ -40892,7 +40872,7 @@
         <v>35</v>
       </c>
       <c r="Y488" s="3"/>
-      <c r="Z488" s="10"/>
+      <c r="Z488" s="8"/>
     </row>
     <row r="489" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3">
@@ -40940,7 +40920,7 @@
       <c r="S489" s="3"/>
       <c r="T489" s="3"/>
       <c r="U489" s="7" t="s">
-        <v>3372</v>
+        <v>3370</v>
       </c>
       <c r="V489" s="3">
         <v>3</v>
@@ -40952,7 +40932,7 @@
         <v>35</v>
       </c>
       <c r="Y489" s="3"/>
-      <c r="Z489" s="10"/>
+      <c r="Z489" s="8"/>
     </row>
     <row r="490" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3">
@@ -41004,7 +40984,7 @@
       </c>
       <c r="T490" s="3"/>
       <c r="U490" s="7" t="s">
-        <v>3373</v>
+        <v>3371</v>
       </c>
       <c r="V490" s="3">
         <v>3</v>
@@ -41016,7 +40996,7 @@
         <v>34</v>
       </c>
       <c r="Y490" s="3"/>
-      <c r="Z490" s="10"/>
+      <c r="Z490" s="8"/>
     </row>
     <row r="491" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3">
@@ -41068,7 +41048,7 @@
       </c>
       <c r="T491" s="3"/>
       <c r="U491" s="7" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
       <c r="V491" s="3">
         <v>3</v>
@@ -41080,7 +41060,7 @@
         <v>35</v>
       </c>
       <c r="Y491" s="3"/>
-      <c r="Z491" s="10"/>
+      <c r="Z491" s="8"/>
     </row>
     <row r="492" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3">
@@ -41132,7 +41112,7 @@
       </c>
       <c r="T492" s="3"/>
       <c r="U492" s="7" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="V492" s="3">
         <v>3</v>
@@ -41144,7 +41124,7 @@
         <v>35</v>
       </c>
       <c r="Y492" s="3"/>
-      <c r="Z492" s="10"/>
+      <c r="Z492" s="8"/>
     </row>
     <row r="493" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3">
@@ -41192,7 +41172,7 @@
         <v>240</v>
       </c>
       <c r="U493" s="7" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="V493" s="3">
         <v>3</v>
@@ -41204,7 +41184,7 @@
         <v>35</v>
       </c>
       <c r="Y493" s="3"/>
-      <c r="Z493" s="10"/>
+      <c r="Z493" s="8"/>
     </row>
     <row r="494" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3">
@@ -41256,7 +41236,7 @@
         <v>2950</v>
       </c>
       <c r="U494" s="7" t="s">
-        <v>3376</v>
+        <v>3374</v>
       </c>
       <c r="V494" s="3">
         <v>3</v>
@@ -41268,7 +41248,7 @@
         <v>35</v>
       </c>
       <c r="Y494" s="3"/>
-      <c r="Z494" s="10"/>
+      <c r="Z494" s="8"/>
     </row>
     <row r="495" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3">
@@ -41318,7 +41298,7 @@
         <v>240</v>
       </c>
       <c r="U495" s="7" t="s">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="V495" s="3">
         <v>3</v>
@@ -41330,7 +41310,7 @@
         <v>35</v>
       </c>
       <c r="Y495" s="3"/>
-      <c r="Z495" s="10"/>
+      <c r="Z495" s="8"/>
     </row>
     <row r="496" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3">
@@ -41380,7 +41360,7 @@
         <v>74</v>
       </c>
       <c r="U496" s="7" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="V496" s="3">
         <v>3</v>
@@ -41392,7 +41372,7 @@
         <v>35</v>
       </c>
       <c r="Y496" s="3"/>
-      <c r="Z496" s="10"/>
+      <c r="Z496" s="8"/>
     </row>
     <row r="497" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3">
@@ -41446,7 +41426,7 @@
         <v>53</v>
       </c>
       <c r="U497" s="7" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="V497" s="3">
         <v>3</v>
@@ -41458,7 +41438,7 @@
         <v>35</v>
       </c>
       <c r="Y497" s="3"/>
-      <c r="Z497" s="10"/>
+      <c r="Z497" s="8"/>
     </row>
     <row r="498" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3">
@@ -41506,7 +41486,7 @@
       <c r="S498" s="3"/>
       <c r="T498" s="3"/>
       <c r="U498" s="7" t="s">
-        <v>3379</v>
+        <v>3377</v>
       </c>
       <c r="V498" s="3">
         <v>3</v>
@@ -41518,7 +41498,7 @@
         <v>44</v>
       </c>
       <c r="Y498" s="3"/>
-      <c r="Z498" s="10"/>
+      <c r="Z498" s="8"/>
     </row>
     <row r="499" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3">
@@ -41566,7 +41546,7 @@
       <c r="S499" s="3"/>
       <c r="T499" s="3"/>
       <c r="U499" s="7" t="s">
-        <v>3380</v>
+        <v>3378</v>
       </c>
       <c r="V499" s="3">
         <v>3</v>
@@ -41578,7 +41558,7 @@
         <v>44</v>
       </c>
       <c r="Y499" s="3"/>
-      <c r="Z499" s="10"/>
+      <c r="Z499" s="8"/>
     </row>
     <row r="500" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3">
@@ -41632,7 +41612,7 @@
         <v>281</v>
       </c>
       <c r="U500" s="7" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="V500" s="3">
         <v>3</v>
@@ -41644,7 +41624,7 @@
         <v>35</v>
       </c>
       <c r="Y500" s="3"/>
-      <c r="Z500" s="10"/>
+      <c r="Z500" s="8"/>
     </row>
     <row r="501" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3">
@@ -41694,7 +41674,7 @@
       <c r="S501" s="3"/>
       <c r="T501" s="3"/>
       <c r="U501" s="7" t="s">
-        <v>3382</v>
+        <v>3380</v>
       </c>
       <c r="V501" s="3">
         <v>3</v>
@@ -41706,7 +41686,7 @@
         <v>44</v>
       </c>
       <c r="Y501" s="3"/>
-      <c r="Z501" s="10"/>
+      <c r="Z501" s="8"/>
     </row>
     <row r="502" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3">
@@ -41756,7 +41736,7 @@
       <c r="S502" s="3"/>
       <c r="T502" s="3"/>
       <c r="U502" s="7" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
       <c r="V502" s="3">
         <v>3</v>
@@ -41768,7 +41748,7 @@
         <v>44</v>
       </c>
       <c r="Y502" s="3"/>
-      <c r="Z502" s="10"/>
+      <c r="Z502" s="8"/>
     </row>
     <row r="503" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3">
@@ -41820,7 +41800,7 @@
       </c>
       <c r="T503" s="3"/>
       <c r="U503" s="7" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
       <c r="V503" s="3">
         <v>3</v>
@@ -41832,7 +41812,7 @@
         <v>34</v>
       </c>
       <c r="Y503" s="3"/>
-      <c r="Z503" s="10"/>
+      <c r="Z503" s="8"/>
     </row>
     <row r="504" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3">
@@ -41884,7 +41864,7 @@
         <v>33</v>
       </c>
       <c r="U504" s="7" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="V504" s="3">
         <v>3</v>
@@ -41896,7 +41876,7 @@
         <v>35</v>
       </c>
       <c r="Y504" s="3"/>
-      <c r="Z504" s="10"/>
+      <c r="Z504" s="8"/>
     </row>
     <row r="505" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3">
@@ -41946,7 +41926,7 @@
       <c r="S505" s="3"/>
       <c r="T505" s="3"/>
       <c r="U505" s="7" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
       <c r="V505" s="3">
         <v>3</v>
@@ -41958,7 +41938,7 @@
         <v>35</v>
       </c>
       <c r="Y505" s="3"/>
-      <c r="Z505" s="10"/>
+      <c r="Z505" s="8"/>
     </row>
     <row r="506" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3">
@@ -42004,7 +41984,7 @@
       <c r="S506" s="3"/>
       <c r="T506" s="3"/>
       <c r="U506" s="7" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="V506" s="3">
         <v>3</v>
@@ -42016,7 +41996,7 @@
         <v>35</v>
       </c>
       <c r="Y506" s="3"/>
-      <c r="Z506" s="10"/>
+      <c r="Z506" s="8"/>
     </row>
     <row r="507" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3">
@@ -42078,7 +42058,7 @@
         <v>44</v>
       </c>
       <c r="Y507" s="3"/>
-      <c r="Z507" s="10"/>
+      <c r="Z507" s="8"/>
     </row>
     <row r="508" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3">
@@ -42126,7 +42106,7 @@
       <c r="S508" s="3"/>
       <c r="T508" s="3"/>
       <c r="U508" s="7" t="s">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="V508" s="3">
         <v>3</v>
@@ -42138,7 +42118,7 @@
         <v>44</v>
       </c>
       <c r="Y508" s="3"/>
-      <c r="Z508" s="10"/>
+      <c r="Z508" s="8"/>
     </row>
     <row r="509" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3">
@@ -42192,7 +42172,7 @@
         <v>1237</v>
       </c>
       <c r="U509" s="7" t="s">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="V509" s="3">
         <v>3</v>
@@ -42204,7 +42184,7 @@
         <v>35</v>
       </c>
       <c r="Y509" s="3"/>
-      <c r="Z509" s="10"/>
+      <c r="Z509" s="8"/>
     </row>
     <row r="510" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3">
@@ -42254,7 +42234,7 @@
       <c r="S510" s="3"/>
       <c r="T510" s="3"/>
       <c r="U510" s="7" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="V510" s="3">
         <v>3</v>
@@ -42266,7 +42246,7 @@
         <v>44</v>
       </c>
       <c r="Y510" s="3"/>
-      <c r="Z510" s="10"/>
+      <c r="Z510" s="8"/>
     </row>
     <row r="511" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3">
@@ -42320,7 +42300,7 @@
         <v>240</v>
       </c>
       <c r="U511" s="7" t="s">
-        <v>3390</v>
+        <v>3388</v>
       </c>
       <c r="V511" s="3">
         <v>3</v>
@@ -42332,7 +42312,7 @@
         <v>35</v>
       </c>
       <c r="Y511" s="3"/>
-      <c r="Z511" s="10"/>
+      <c r="Z511" s="8"/>
     </row>
     <row r="512" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3">
@@ -42378,7 +42358,7 @@
         <v>281</v>
       </c>
       <c r="U512" s="7" t="s">
-        <v>3391</v>
+        <v>3389</v>
       </c>
       <c r="V512" s="3">
         <v>3</v>
@@ -42390,7 +42370,7 @@
         <v>35</v>
       </c>
       <c r="Y512" s="3"/>
-      <c r="Z512" s="10"/>
+      <c r="Z512" s="8"/>
     </row>
     <row r="513" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3">
@@ -42440,7 +42420,7 @@
       </c>
       <c r="T513" s="3"/>
       <c r="U513" s="7" t="s">
-        <v>3392</v>
+        <v>3390</v>
       </c>
       <c r="V513" s="3">
         <v>4</v>
@@ -42452,7 +42432,7 @@
         <v>34</v>
       </c>
       <c r="Y513" s="3"/>
-      <c r="Z513" s="10"/>
+      <c r="Z513" s="8"/>
     </row>
     <row r="514" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3">
@@ -42502,7 +42482,7 @@
       <c r="S514" s="3"/>
       <c r="T514" s="3"/>
       <c r="U514" s="7" t="s">
-        <v>3393</v>
+        <v>3391</v>
       </c>
       <c r="V514" s="3">
         <v>3</v>
@@ -42514,7 +42494,7 @@
         <v>44</v>
       </c>
       <c r="Y514" s="3"/>
-      <c r="Z514" s="10"/>
+      <c r="Z514" s="8"/>
     </row>
     <row r="515" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3">
@@ -42560,7 +42540,7 @@
       </c>
       <c r="T515" s="3"/>
       <c r="U515" s="7" t="s">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="V515" s="3">
         <v>3</v>
@@ -42572,7 +42552,7 @@
         <v>35</v>
       </c>
       <c r="Y515" s="3"/>
-      <c r="Z515" s="10"/>
+      <c r="Z515" s="8"/>
     </row>
     <row r="516" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3">
@@ -42620,7 +42600,7 @@
       </c>
       <c r="T516" s="3"/>
       <c r="U516" s="7" t="s">
-        <v>3395</v>
+        <v>3393</v>
       </c>
       <c r="V516" s="3">
         <v>3</v>
@@ -42632,7 +42612,7 @@
         <v>35</v>
       </c>
       <c r="Y516" s="3"/>
-      <c r="Z516" s="10"/>
+      <c r="Z516" s="8"/>
     </row>
     <row r="517" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3">
@@ -42686,7 +42666,7 @@
         <v>2950</v>
       </c>
       <c r="U517" s="7" t="s">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="V517" s="3">
         <v>3</v>
@@ -42698,7 +42678,7 @@
         <v>35</v>
       </c>
       <c r="Y517" s="3"/>
-      <c r="Z517" s="10"/>
+      <c r="Z517" s="8"/>
     </row>
     <row r="518" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3">
@@ -42744,7 +42724,7 @@
       </c>
       <c r="T518" s="3"/>
       <c r="U518" s="7" t="s">
-        <v>3397</v>
+        <v>3395</v>
       </c>
       <c r="V518" s="3">
         <v>3</v>
@@ -42756,7 +42736,7 @@
         <v>35</v>
       </c>
       <c r="Y518" s="3"/>
-      <c r="Z518" s="10"/>
+      <c r="Z518" s="8"/>
     </row>
     <row r="519" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3">
@@ -42802,7 +42782,7 @@
       </c>
       <c r="T519" s="3"/>
       <c r="U519" s="7" t="s">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="V519" s="3">
         <v>3</v>
@@ -42814,7 +42794,7 @@
         <v>35</v>
       </c>
       <c r="Y519" s="3"/>
-      <c r="Z519" s="10"/>
+      <c r="Z519" s="8"/>
     </row>
     <row r="520" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3">
@@ -42862,7 +42842,7 @@
         <v>74</v>
       </c>
       <c r="U520" s="7" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
       <c r="V520" s="3">
         <v>3</v>
@@ -42874,7 +42854,7 @@
         <v>35</v>
       </c>
       <c r="Y520" s="3"/>
-      <c r="Z520" s="10"/>
+      <c r="Z520" s="8"/>
     </row>
     <row r="521" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3">
@@ -42922,7 +42902,7 @@
         <v>314</v>
       </c>
       <c r="U521" s="7" t="s">
-        <v>3400</v>
+        <v>3398</v>
       </c>
       <c r="V521" s="3">
         <v>3</v>
@@ -42934,7 +42914,7 @@
         <v>35</v>
       </c>
       <c r="Y521" s="3"/>
-      <c r="Z521" s="10"/>
+      <c r="Z521" s="8"/>
     </row>
     <row r="522" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3">
@@ -42982,7 +42962,7 @@
         <v>1326</v>
       </c>
       <c r="U522" s="7" t="s">
-        <v>3401</v>
+        <v>3399</v>
       </c>
       <c r="V522" s="3">
         <v>3</v>
@@ -42994,7 +42974,7 @@
         <v>35</v>
       </c>
       <c r="Y522" s="3"/>
-      <c r="Z522" s="10"/>
+      <c r="Z522" s="8"/>
     </row>
     <row r="523" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3">
@@ -43046,7 +43026,7 @@
         <v>2950</v>
       </c>
       <c r="U523" s="7" t="s">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="V523" s="3">
         <v>3</v>
@@ -43058,7 +43038,7 @@
         <v>35</v>
       </c>
       <c r="Y523" s="3"/>
-      <c r="Z523" s="10"/>
+      <c r="Z523" s="8"/>
     </row>
     <row r="524" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3">
@@ -43114,7 +43094,7 @@
         <v>35</v>
       </c>
       <c r="Y524" s="3"/>
-      <c r="Z524" s="10"/>
+      <c r="Z524" s="8"/>
     </row>
     <row r="525" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3">
@@ -43158,7 +43138,7 @@
       <c r="S525" s="3"/>
       <c r="T525" s="3"/>
       <c r="U525" s="7" t="s">
-        <v>3403</v>
+        <v>3401</v>
       </c>
       <c r="V525" s="3">
         <v>3</v>
@@ -43170,7 +43150,7 @@
         <v>35</v>
       </c>
       <c r="Y525" s="3"/>
-      <c r="Z525" s="10"/>
+      <c r="Z525" s="8"/>
     </row>
     <row r="526" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3">
@@ -43220,7 +43200,7 @@
       <c r="S526" s="3"/>
       <c r="T526" s="3"/>
       <c r="U526" s="7" t="s">
-        <v>3404</v>
+        <v>3402</v>
       </c>
       <c r="V526" s="3">
         <v>3</v>
@@ -43232,7 +43212,7 @@
         <v>35</v>
       </c>
       <c r="Y526" s="3"/>
-      <c r="Z526" s="10"/>
+      <c r="Z526" s="8"/>
     </row>
     <row r="527" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3">
@@ -43280,7 +43260,7 @@
       <c r="S527" s="3"/>
       <c r="T527" s="3"/>
       <c r="U527" s="7" t="s">
-        <v>3405</v>
+        <v>3403</v>
       </c>
       <c r="V527" s="3" t="s">
         <v>44</v>
@@ -43292,7 +43272,7 @@
         <v>44</v>
       </c>
       <c r="Y527" s="3"/>
-      <c r="Z527" s="10"/>
+      <c r="Z527" s="8"/>
     </row>
     <row r="528" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3">
@@ -43338,7 +43318,7 @@
       </c>
       <c r="T528" s="3"/>
       <c r="U528" s="7" t="s">
-        <v>3406</v>
+        <v>3404</v>
       </c>
       <c r="V528" s="3">
         <v>3</v>
@@ -43350,7 +43330,7 @@
         <v>35</v>
       </c>
       <c r="Y528" s="3"/>
-      <c r="Z528" s="10"/>
+      <c r="Z528" s="8"/>
     </row>
     <row r="529" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3">
@@ -43398,7 +43378,7 @@
       <c r="S529" s="3"/>
       <c r="T529" s="3"/>
       <c r="U529" s="7" t="s">
-        <v>3407</v>
+        <v>3405</v>
       </c>
       <c r="V529" s="3">
         <v>3</v>
@@ -43410,7 +43390,7 @@
         <v>44</v>
       </c>
       <c r="Y529" s="3"/>
-      <c r="Z529" s="10"/>
+      <c r="Z529" s="8"/>
     </row>
     <row r="530" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3">
@@ -43460,7 +43440,7 @@
       <c r="S530" s="3"/>
       <c r="T530" s="3"/>
       <c r="U530" s="7" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="V530" s="3" t="s">
         <v>44</v>
@@ -43472,7 +43452,7 @@
         <v>44</v>
       </c>
       <c r="Y530" s="3"/>
-      <c r="Z530" s="10"/>
+      <c r="Z530" s="8"/>
     </row>
     <row r="531" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3">
@@ -43530,7 +43510,7 @@
         <v>44</v>
       </c>
       <c r="Y531" s="3"/>
-      <c r="Z531" s="10"/>
+      <c r="Z531" s="8"/>
     </row>
     <row r="532" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3">
@@ -43580,7 +43560,7 @@
         <v>1977</v>
       </c>
       <c r="U532" s="7" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="V532" s="3">
         <v>3</v>
@@ -43592,7 +43572,7 @@
         <v>35</v>
       </c>
       <c r="Y532" s="3"/>
-      <c r="Z532" s="10"/>
+      <c r="Z532" s="8"/>
     </row>
     <row r="533" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3">
@@ -43646,7 +43626,7 @@
         <v>397</v>
       </c>
       <c r="U533" s="7" t="s">
-        <v>3409</v>
+        <v>3407</v>
       </c>
       <c r="V533" s="3">
         <v>3</v>
@@ -43658,7 +43638,7 @@
         <v>35</v>
       </c>
       <c r="Y533" s="3"/>
-      <c r="Z533" s="10"/>
+      <c r="Z533" s="8"/>
     </row>
     <row r="534" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3">
@@ -43710,7 +43690,7 @@
       </c>
       <c r="T534" s="3"/>
       <c r="U534" s="7" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
       <c r="V534" s="3">
         <v>3</v>
@@ -43722,7 +43702,7 @@
         <v>35</v>
       </c>
       <c r="Y534" s="3"/>
-      <c r="Z534" s="10"/>
+      <c r="Z534" s="8"/>
     </row>
     <row r="535" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3">
@@ -43772,7 +43752,7 @@
       <c r="S535" s="3"/>
       <c r="T535" s="3"/>
       <c r="U535" s="7" t="s">
-        <v>3411</v>
+        <v>3409</v>
       </c>
       <c r="V535" s="3">
         <v>3</v>
@@ -43784,7 +43764,7 @@
         <v>35</v>
       </c>
       <c r="Y535" s="3"/>
-      <c r="Z535" s="10"/>
+      <c r="Z535" s="8"/>
     </row>
     <row r="536" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3">
@@ -43838,7 +43818,7 @@
         <v>74</v>
       </c>
       <c r="U536" s="7" t="s">
-        <v>3412</v>
+        <v>3410</v>
       </c>
       <c r="V536" s="3">
         <v>3</v>
@@ -43850,7 +43830,7 @@
         <v>35</v>
       </c>
       <c r="Y536" s="3"/>
-      <c r="Z536" s="10"/>
+      <c r="Z536" s="8"/>
     </row>
     <row r="537" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3">
@@ -43902,7 +43882,7 @@
       </c>
       <c r="T537" s="3"/>
       <c r="U537" s="7" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="V537" s="3">
         <v>3</v>
@@ -43914,7 +43894,7 @@
         <v>35</v>
       </c>
       <c r="Y537" s="3"/>
-      <c r="Z537" s="10"/>
+      <c r="Z537" s="8"/>
     </row>
     <row r="538" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3">
@@ -43966,7 +43946,7 @@
       </c>
       <c r="T538" s="3"/>
       <c r="U538" s="7" t="s">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="V538" s="3">
         <v>3</v>
@@ -43978,7 +43958,7 @@
         <v>35</v>
       </c>
       <c r="Y538" s="3"/>
-      <c r="Z538" s="10"/>
+      <c r="Z538" s="8"/>
     </row>
     <row r="539" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3">
@@ -44028,7 +44008,7 @@
       <c r="S539" s="3"/>
       <c r="T539" s="3"/>
       <c r="U539" s="7" t="s">
-        <v>3414</v>
+        <v>3412</v>
       </c>
       <c r="V539" s="3">
         <v>2</v>
@@ -44040,7 +44020,7 @@
         <v>44</v>
       </c>
       <c r="Y539" s="3"/>
-      <c r="Z539" s="10"/>
+      <c r="Z539" s="8"/>
     </row>
     <row r="540" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3">
@@ -44090,7 +44070,7 @@
       <c r="S540" s="3"/>
       <c r="T540" s="3"/>
       <c r="U540" s="7" t="s">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="V540" s="3">
         <v>4</v>
@@ -44102,7 +44082,7 @@
         <v>44</v>
       </c>
       <c r="Y540" s="3"/>
-      <c r="Z540" s="10"/>
+      <c r="Z540" s="8"/>
     </row>
     <row r="541" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3">
@@ -44152,7 +44132,7 @@
       <c r="S541" s="3"/>
       <c r="T541" s="3"/>
       <c r="U541" s="7" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="V541" s="3" t="s">
         <v>44</v>
@@ -44164,7 +44144,7 @@
         <v>44</v>
       </c>
       <c r="Y541" s="3"/>
-      <c r="Z541" s="10"/>
+      <c r="Z541" s="8"/>
     </row>
     <row r="542" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3">
@@ -44210,7 +44190,7 @@
       <c r="S542" s="3"/>
       <c r="T542" s="3"/>
       <c r="U542" s="7" t="s">
-        <v>3417</v>
+        <v>3415</v>
       </c>
       <c r="V542" s="3">
         <v>3</v>
@@ -44222,7 +44202,7 @@
         <v>35</v>
       </c>
       <c r="Y542" s="3"/>
-      <c r="Z542" s="10"/>
+      <c r="Z542" s="8"/>
     </row>
     <row r="543" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3">
@@ -44276,7 +44256,7 @@
         <v>74</v>
       </c>
       <c r="U543" s="7" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="V543" s="3">
         <v>3</v>
@@ -44288,7 +44268,7 @@
         <v>35</v>
       </c>
       <c r="Y543" s="3"/>
-      <c r="Z543" s="10"/>
+      <c r="Z543" s="8"/>
     </row>
     <row r="544" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3">
@@ -44336,7 +44316,7 @@
       </c>
       <c r="T544" s="3"/>
       <c r="U544" s="7" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="V544" s="3">
         <v>3</v>
@@ -44348,7 +44328,7 @@
         <v>35</v>
       </c>
       <c r="Y544" s="3"/>
-      <c r="Z544" s="10"/>
+      <c r="Z544" s="8"/>
     </row>
     <row r="545" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3">
@@ -44400,7 +44380,7 @@
       </c>
       <c r="T545" s="3"/>
       <c r="U545" s="7" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="V545" s="3">
         <v>3</v>
@@ -44412,7 +44392,7 @@
         <v>35</v>
       </c>
       <c r="Y545" s="3"/>
-      <c r="Z545" s="10"/>
+      <c r="Z545" s="8"/>
     </row>
     <row r="546" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3">
@@ -44464,7 +44444,7 @@
         <v>33</v>
       </c>
       <c r="U546" s="7" t="s">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="V546" s="3">
         <v>3</v>
@@ -44476,7 +44456,7 @@
         <v>35</v>
       </c>
       <c r="Y546" s="3"/>
-      <c r="Z546" s="10"/>
+      <c r="Z546" s="8"/>
     </row>
     <row r="547" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3">
@@ -44528,7 +44508,7 @@
       </c>
       <c r="T547" s="3"/>
       <c r="U547" s="7" t="s">
-        <v>3422</v>
+        <v>3420</v>
       </c>
       <c r="V547" s="3">
         <v>4</v>
@@ -44540,7 +44520,7 @@
         <v>35</v>
       </c>
       <c r="Y547" s="3"/>
-      <c r="Z547" s="10"/>
+      <c r="Z547" s="8"/>
     </row>
     <row r="548" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3">
@@ -44585,9 +44565,7 @@
       <c r="R548" s="3"/>
       <c r="S548" s="3"/>
       <c r="T548" s="3"/>
-      <c r="U548" s="7" t="s">
-        <v>3423</v>
-      </c>
+      <c r="U548" s="7"/>
       <c r="V548" s="3">
         <v>3</v>
       </c>
@@ -44600,7 +44578,7 @@
       <c r="Y548" s="3" t="s">
         <v>2937</v>
       </c>
-      <c r="Z548" s="10"/>
+      <c r="Z548" s="8"/>
     </row>
     <row r="549" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3">
@@ -44646,7 +44624,7 @@
       <c r="S549" s="3"/>
       <c r="T549" s="3"/>
       <c r="U549" s="7" t="s">
-        <v>3424</v>
+        <v>3421</v>
       </c>
       <c r="V549" s="3" t="s">
         <v>44</v>
@@ -44658,7 +44636,7 @@
         <v>44</v>
       </c>
       <c r="Y549" s="3"/>
-      <c r="Z549" s="10"/>
+      <c r="Z549" s="8"/>
     </row>
     <row r="550" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3">
@@ -44706,7 +44684,7 @@
       </c>
       <c r="T550" s="3"/>
       <c r="U550" s="7" t="s">
-        <v>3425</v>
+        <v>3422</v>
       </c>
       <c r="V550" s="3">
         <v>3</v>
@@ -44718,7 +44696,7 @@
         <v>35</v>
       </c>
       <c r="Y550" s="3"/>
-      <c r="Z550" s="10"/>
+      <c r="Z550" s="8"/>
     </row>
     <row r="551" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3">
@@ -44766,7 +44744,7 @@
         <v>33</v>
       </c>
       <c r="U551" s="7" t="s">
-        <v>3426</v>
+        <v>3423</v>
       </c>
       <c r="V551" s="3">
         <v>3</v>
@@ -44778,7 +44756,7 @@
         <v>35</v>
       </c>
       <c r="Y551" s="3"/>
-      <c r="Z551" s="10"/>
+      <c r="Z551" s="8"/>
     </row>
     <row r="552" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3">
@@ -44828,7 +44806,7 @@
         <v>445</v>
       </c>
       <c r="U552" s="7" t="s">
-        <v>3427</v>
+        <v>3424</v>
       </c>
       <c r="V552" s="3">
         <v>3</v>
@@ -44840,7 +44818,7 @@
         <v>35</v>
       </c>
       <c r="Y552" s="3"/>
-      <c r="Z552" s="10"/>
+      <c r="Z552" s="8"/>
     </row>
     <row r="553" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3">
@@ -44894,7 +44872,7 @@
         <v>53</v>
       </c>
       <c r="U553" s="7" t="s">
-        <v>3428</v>
+        <v>3425</v>
       </c>
       <c r="V553" s="3">
         <v>3</v>
@@ -44906,7 +44884,7 @@
         <v>35</v>
       </c>
       <c r="Y553" s="3"/>
-      <c r="Z553" s="10"/>
+      <c r="Z553" s="8"/>
     </row>
     <row r="554" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3">
@@ -44956,7 +44934,7 @@
         <v>1112</v>
       </c>
       <c r="U554" s="7" t="s">
-        <v>3429</v>
+        <v>3426</v>
       </c>
       <c r="V554" s="3">
         <v>3</v>
@@ -44968,7 +44946,7 @@
         <v>35</v>
       </c>
       <c r="Y554" s="3"/>
-      <c r="Z554" s="10"/>
+      <c r="Z554" s="8"/>
     </row>
     <row r="555" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3">
@@ -45018,7 +44996,7 @@
         <v>53</v>
       </c>
       <c r="U555" s="7" t="s">
-        <v>3430</v>
+        <v>3427</v>
       </c>
       <c r="V555" s="3">
         <v>3</v>
@@ -45030,7 +45008,7 @@
         <v>35</v>
       </c>
       <c r="Y555" s="3"/>
-      <c r="Z555" s="10"/>
+      <c r="Z555" s="8"/>
     </row>
     <row r="556" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3">
@@ -45078,7 +45056,7 @@
         <v>33</v>
       </c>
       <c r="U556" s="7" t="s">
-        <v>3431</v>
+        <v>3428</v>
       </c>
       <c r="V556" s="3">
         <v>3</v>
@@ -45090,7 +45068,7 @@
         <v>35</v>
       </c>
       <c r="Y556" s="3"/>
-      <c r="Z556" s="10"/>
+      <c r="Z556" s="8"/>
     </row>
     <row r="557" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3">
@@ -45136,7 +45114,7 @@
       <c r="S557" s="3"/>
       <c r="T557" s="3"/>
       <c r="U557" s="7" t="s">
-        <v>3432</v>
+        <v>3429</v>
       </c>
       <c r="V557" s="3">
         <v>3</v>
@@ -45148,7 +45126,7 @@
         <v>44</v>
       </c>
       <c r="Y557" s="3"/>
-      <c r="Z557" s="10"/>
+      <c r="Z557" s="8"/>
     </row>
     <row r="558" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3">
@@ -45194,7 +45172,7 @@
       <c r="S558" s="3"/>
       <c r="T558" s="3"/>
       <c r="U558" s="7" t="s">
-        <v>3433</v>
+        <v>3430</v>
       </c>
       <c r="V558" s="3">
         <v>3</v>
@@ -45206,7 +45184,7 @@
         <v>44</v>
       </c>
       <c r="Y558" s="3"/>
-      <c r="Z558" s="10"/>
+      <c r="Z558" s="8"/>
     </row>
     <row r="559" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3">
@@ -45254,7 +45232,7 @@
         <v>240</v>
       </c>
       <c r="U559" s="7" t="s">
-        <v>3434</v>
+        <v>3431</v>
       </c>
       <c r="V559" s="3">
         <v>3</v>
@@ -45266,7 +45244,7 @@
         <v>35</v>
       </c>
       <c r="Y559" s="3"/>
-      <c r="Z559" s="10"/>
+      <c r="Z559" s="8"/>
     </row>
     <row r="560" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3">
@@ -45316,7 +45294,7 @@
         <v>102</v>
       </c>
       <c r="U560" s="7" t="s">
-        <v>3435</v>
+        <v>3432</v>
       </c>
       <c r="V560" s="3">
         <v>3</v>
@@ -45328,7 +45306,7 @@
         <v>35</v>
       </c>
       <c r="Y560" s="3"/>
-      <c r="Z560" s="10"/>
+      <c r="Z560" s="8"/>
     </row>
     <row r="561" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3">
@@ -45382,7 +45360,7 @@
         <v>2438</v>
       </c>
       <c r="U561" s="7" t="s">
-        <v>3436</v>
+        <v>3433</v>
       </c>
       <c r="V561" s="3">
         <v>3</v>
@@ -45394,7 +45372,7 @@
         <v>35</v>
       </c>
       <c r="Y561" s="3"/>
-      <c r="Z561" s="10"/>
+      <c r="Z561" s="8"/>
     </row>
     <row r="562" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3">
@@ -45456,7 +45434,7 @@
         <v>44</v>
       </c>
       <c r="Y562" s="3"/>
-      <c r="Z562" s="10"/>
+      <c r="Z562" s="8"/>
     </row>
     <row r="563" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3">
@@ -45510,7 +45488,7 @@
         <v>74</v>
       </c>
       <c r="U563" s="7" t="s">
-        <v>3437</v>
+        <v>3434</v>
       </c>
       <c r="V563" s="3">
         <v>3</v>
@@ -45522,7 +45500,7 @@
         <v>35</v>
       </c>
       <c r="Y563" s="3"/>
-      <c r="Z563" s="10"/>
+      <c r="Z563" s="8"/>
     </row>
     <row r="564" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3">
@@ -45572,7 +45550,7 @@
       <c r="S564" s="3"/>
       <c r="T564" s="3"/>
       <c r="U564" s="7" t="s">
-        <v>3438</v>
+        <v>3435</v>
       </c>
       <c r="V564" s="3">
         <v>3</v>
@@ -45584,7 +45562,7 @@
         <v>44</v>
       </c>
       <c r="Y564" s="3"/>
-      <c r="Z564" s="10"/>
+      <c r="Z564" s="8"/>
     </row>
     <row r="565" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3">
@@ -45634,7 +45612,7 @@
       <c r="S565" s="3"/>
       <c r="T565" s="3"/>
       <c r="U565" s="7" t="s">
-        <v>3439</v>
+        <v>3436</v>
       </c>
       <c r="V565" s="3" t="s">
         <v>44</v>
@@ -45646,7 +45624,7 @@
         <v>44</v>
       </c>
       <c r="Y565" s="3"/>
-      <c r="Z565" s="10"/>
+      <c r="Z565" s="8"/>
     </row>
     <row r="566" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3">
@@ -45700,7 +45678,7 @@
         <v>33</v>
       </c>
       <c r="U566" s="7" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="V566" s="3">
         <v>3</v>
@@ -45712,7 +45690,7 @@
         <v>35</v>
       </c>
       <c r="Y566" s="3"/>
-      <c r="Z566" s="10"/>
+      <c r="Z566" s="8"/>
     </row>
     <row r="567" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3">
@@ -45758,7 +45736,7 @@
       <c r="S567" s="3"/>
       <c r="T567" s="3"/>
       <c r="U567" s="7" t="s">
-        <v>3440</v>
+        <v>3437</v>
       </c>
       <c r="V567" s="3">
         <v>3</v>
@@ -45770,7 +45748,7 @@
         <v>35</v>
       </c>
       <c r="Y567" s="3"/>
-      <c r="Z567" s="10"/>
+      <c r="Z567" s="8"/>
     </row>
     <row r="568" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3">
@@ -45820,7 +45798,7 @@
       <c r="S568" s="3"/>
       <c r="T568" s="3"/>
       <c r="U568" s="7" t="s">
-        <v>3441</v>
+        <v>3438</v>
       </c>
       <c r="V568" s="3">
         <v>3</v>
@@ -45832,7 +45810,7 @@
         <v>44</v>
       </c>
       <c r="Y568" s="3"/>
-      <c r="Z568" s="10"/>
+      <c r="Z568" s="8"/>
     </row>
     <row r="569" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3">
@@ -45882,7 +45860,7 @@
       <c r="S569" s="3"/>
       <c r="T569" s="3"/>
       <c r="U569" s="7" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="V569" s="3" t="s">
         <v>44</v>
@@ -45894,7 +45872,7 @@
         <v>44</v>
       </c>
       <c r="Y569" s="3"/>
-      <c r="Z569" s="10"/>
+      <c r="Z569" s="8"/>
     </row>
     <row r="570" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3">
@@ -45946,7 +45924,7 @@
         <v>2950</v>
       </c>
       <c r="U570" s="7" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="V570" s="3">
         <v>4</v>
@@ -45958,7 +45936,7 @@
         <v>44</v>
       </c>
       <c r="Y570" s="3"/>
-      <c r="Z570" s="10"/>
+      <c r="Z570" s="8"/>
     </row>
     <row r="571" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3">
@@ -46008,7 +45986,7 @@
       <c r="S571" s="3"/>
       <c r="T571" s="3"/>
       <c r="U571" s="7" t="s">
-        <v>3442</v>
+        <v>3439</v>
       </c>
       <c r="V571" s="3" t="s">
         <v>44</v>
@@ -46020,7 +45998,7 @@
         <v>44</v>
       </c>
       <c r="Y571" s="3"/>
-      <c r="Z571" s="10"/>
+      <c r="Z571" s="8"/>
     </row>
     <row r="572" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3">
@@ -46072,7 +46050,7 @@
       </c>
       <c r="T572" s="3"/>
       <c r="U572" s="7" t="s">
-        <v>3443</v>
+        <v>3440</v>
       </c>
       <c r="V572" s="3">
         <v>4</v>
@@ -46084,7 +46062,7 @@
         <v>35</v>
       </c>
       <c r="Y572" s="3"/>
-      <c r="Z572" s="10"/>
+      <c r="Z572" s="8"/>
     </row>
     <row r="573" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3">
@@ -46134,7 +46112,7 @@
       <c r="S573" s="3"/>
       <c r="T573" s="3"/>
       <c r="U573" s="7" t="s">
-        <v>3444</v>
+        <v>3441</v>
       </c>
       <c r="V573" s="3" t="s">
         <v>44</v>
@@ -46146,7 +46124,7 @@
         <v>44</v>
       </c>
       <c r="Y573" s="3"/>
-      <c r="Z573" s="10"/>
+      <c r="Z573" s="8"/>
     </row>
     <row r="574" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3">
@@ -46194,7 +46172,7 @@
         <v>33</v>
       </c>
       <c r="U574" s="7" t="s">
-        <v>3445</v>
+        <v>3442</v>
       </c>
       <c r="V574" s="3">
         <v>4</v>
@@ -46206,7 +46184,7 @@
         <v>44</v>
       </c>
       <c r="Y574" s="3"/>
-      <c r="Z574" s="10"/>
+      <c r="Z574" s="8"/>
     </row>
     <row r="575" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
@@ -46255,9 +46233,7 @@
       <c r="R575" s="3"/>
       <c r="S575" s="3"/>
       <c r="T575" s="3"/>
-      <c r="U575" s="7" t="s">
-        <v>3126</v>
-      </c>
+      <c r="U575" s="7"/>
       <c r="V575" s="3" t="s">
         <v>44</v>
       </c>
@@ -46270,7 +46246,7 @@
       <c r="Y575" s="3" t="s">
         <v>2931</v>
       </c>
-      <c r="Z575" s="10"/>
+      <c r="Z575" s="8"/>
     </row>
     <row r="576" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
@@ -46319,9 +46295,7 @@
       <c r="R576" s="3"/>
       <c r="S576" s="3"/>
       <c r="T576" s="3"/>
-      <c r="U576" s="7" t="s">
-        <v>3446</v>
-      </c>
+      <c r="U576" s="7"/>
       <c r="V576" s="3" t="s">
         <v>44</v>
       </c>
@@ -46334,7 +46308,7 @@
       <c r="Y576" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="Z576" s="10"/>
+      <c r="Z576" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D8673D9-9A56-4418-B7E5-C0BAFA7FFF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{1CC400DF-E6DE-4F72-9D5D-E4EBEDAF0708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="3443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7584" uniqueCount="3444">
   <si>
     <t>emp_id</t>
   </si>
@@ -10366,6 +10366,9 @@
   </si>
   <si>
     <t>86.31%</t>
+  </si>
+  <si>
+    <t>Critical Position</t>
   </si>
 </sst>
 </file>
@@ -17795,7 +17798,9 @@
         <v>420</v>
       </c>
       <c r="P113" s="3"/>
-      <c r="Q113" s="3"/>
+      <c r="Q113" s="3" t="s">
+        <v>3443</v>
+      </c>
       <c r="R113" s="3"/>
       <c r="S113" s="3" t="s">
         <v>421</v>
@@ -20987,7 +20992,9 @@
         <v>776</v>
       </c>
       <c r="P164" s="3"/>
-      <c r="Q164" s="3"/>
+      <c r="Q164" s="3" t="s">
+        <v>3443</v>
+      </c>
       <c r="R164" s="3"/>
       <c r="S164" s="3" t="s">
         <v>33</v>
@@ -23531,7 +23538,9 @@
         <v>945</v>
       </c>
       <c r="P204" s="3"/>
-      <c r="Q204" s="3"/>
+      <c r="Q204" s="3" t="s">
+        <v>3443</v>
+      </c>
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
       <c r="T204" s="3" t="s">
@@ -44677,7 +44686,9 @@
         <v>2453</v>
       </c>
       <c r="P550" s="3"/>
-      <c r="Q550" s="3"/>
+      <c r="Q550" s="3" t="s">
+        <v>3443</v>
+      </c>
       <c r="R550" s="3"/>
       <c r="S550" s="3" t="s">
         <v>2454</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{E44FDED3-A441-450F-AEE8-9F34D66C61FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{91B7BEA2-D093-4B1F-8F28-78C84DEF5764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46217,7 +46217,7 @@
         <v>2913</v>
       </c>
       <c r="G575" s="3" t="s">
-        <v>2948</v>
+        <v>107</v>
       </c>
       <c r="H575" s="3" t="s">
         <v>2794</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{91B7BEA2-D093-4B1F-8F28-78C84DEF5764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{0A22B05D-E096-495C-83B0-60FDE4DEFC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7584" uniqueCount="3444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="3444">
   <si>
     <t>emp_id</t>
   </si>
@@ -10520,6 +10520,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20336,8 +20340,8 @@
       <c r="H154" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="I154" s="3">
-        <v>168001</v>
+      <c r="I154" s="3" t="s">
+        <v>2910</v>
       </c>
       <c r="J154" s="5">
         <v>24215</v>
@@ -20974,8 +20978,8 @@
       <c r="H164" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I164" s="3">
-        <v>168001</v>
+      <c r="I164" s="3" t="s">
+        <v>2910</v>
       </c>
       <c r="J164" s="5">
         <v>29389</v>
@@ -21736,8 +21740,8 @@
       <c r="H176" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I176" s="3">
-        <v>168001</v>
+      <c r="I176" s="3" t="s">
+        <v>2910</v>
       </c>
       <c r="J176" s="5">
         <v>29553</v>
@@ -21860,8 +21864,8 @@
       <c r="H178" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I178" s="3">
-        <v>168001</v>
+      <c r="I178" s="3" t="s">
+        <v>2910</v>
       </c>
       <c r="J178" s="5">
         <v>32000</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0A22B05D-E096-495C-83B0-60FDE4DEFC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D56CDC30-2E20-4EC8-A892-43688360C41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="3444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="3445">
   <si>
     <t>emp_id</t>
   </si>
@@ -10369,6 +10369,9 @@
   </si>
   <si>
     <t>Acting Department Manager - Batch and Furnace</t>
+  </si>
+  <si>
+    <t>168001A.jpg</t>
   </si>
 </sst>
 </file>
@@ -10520,10 +10523,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46300,7 +46299,7 @@
       <c r="L576" s="4"/>
       <c r="M576" s="4"/>
       <c r="N576" s="3" t="s">
-        <v>2764</v>
+        <v>3444</v>
       </c>
       <c r="O576" s="3" t="s">
         <v>2765</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{D56CDC30-2E20-4EC8-A892-43688360C41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{015EE132-8702-492C-BC59-E6AE9B62D6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -10810,6 +10811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z576"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10939,7 +10941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>168001</v>
       </c>
@@ -10998,7 +11000,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>168016</v>
       </c>
@@ -11060,7 +11062,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="8"/>
     </row>
-    <row r="5" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>258026</v>
       </c>
@@ -11126,7 +11128,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>234064</v>
       </c>
@@ -11190,7 +11192,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>254019</v>
       </c>
@@ -11252,7 +11254,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>264004</v>
       </c>
@@ -11314,7 +11316,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="8"/>
     </row>
-    <row r="9" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>264018</v>
       </c>
@@ -11374,7 +11376,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="8"/>
     </row>
-    <row r="10" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>264024</v>
       </c>
@@ -11436,7 +11438,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="8"/>
     </row>
-    <row r="11" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>264034</v>
       </c>
@@ -11496,7 +11498,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="8"/>
     </row>
-    <row r="12" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>264050</v>
       </c>
@@ -11556,7 +11558,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="8"/>
     </row>
-    <row r="13" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>265038</v>
       </c>
@@ -11616,7 +11618,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>265122</v>
       </c>
@@ -11678,7 +11680,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="8"/>
     </row>
-    <row r="15" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>266005</v>
       </c>
@@ -11744,7 +11746,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="8"/>
     </row>
-    <row r="16" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>267010</v>
       </c>
@@ -11806,7 +11808,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>267071</v>
       </c>
@@ -11868,7 +11870,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>267082</v>
       </c>
@@ -11930,7 +11932,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="8"/>
     </row>
-    <row r="19" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>267089</v>
       </c>
@@ -11990,7 +11992,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="8"/>
     </row>
-    <row r="20" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>267090</v>
       </c>
@@ -12050,7 +12052,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>268010</v>
       </c>
@@ -12110,7 +12112,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>268011</v>
       </c>
@@ -12170,7 +12172,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>268051</v>
       </c>
@@ -12232,7 +12234,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>268060</v>
       </c>
@@ -12294,7 +12296,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>268065</v>
       </c>
@@ -12354,7 +12356,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>268066</v>
       </c>
@@ -12414,7 +12416,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>268067</v>
       </c>
@@ -12474,7 +12476,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>268085</v>
       </c>
@@ -12534,7 +12536,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>269023</v>
       </c>
@@ -12596,7 +12598,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>235035</v>
       </c>
@@ -12660,7 +12662,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="8"/>
     </row>
-    <row r="31" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>253020</v>
       </c>
@@ -12722,7 +12724,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="8"/>
     </row>
-    <row r="32" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>250051</v>
       </c>
@@ -12788,7 +12790,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="8"/>
     </row>
-    <row r="33" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>254009</v>
       </c>
@@ -12848,7 +12850,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="8"/>
     </row>
-    <row r="34" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>254054</v>
       </c>
@@ -12908,7 +12910,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="8"/>
     </row>
-    <row r="35" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>255001</v>
       </c>
@@ -12968,7 +12970,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="8"/>
     </row>
-    <row r="36" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>255023</v>
       </c>
@@ -13032,7 +13034,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="8"/>
     </row>
-    <row r="37" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>257010</v>
       </c>
@@ -13096,7 +13098,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="8"/>
     </row>
-    <row r="38" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>257029</v>
       </c>
@@ -13158,7 +13160,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="8"/>
     </row>
-    <row r="39" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>261023</v>
       </c>
@@ -13220,7 +13222,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="8"/>
     </row>
-    <row r="40" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>267025</v>
       </c>
@@ -13280,7 +13282,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="8"/>
     </row>
-    <row r="41" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>267026</v>
       </c>
@@ -13340,7 +13342,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="8"/>
     </row>
-    <row r="42" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>267028</v>
       </c>
@@ -13402,7 +13404,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="8"/>
     </row>
-    <row r="43" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>267079</v>
       </c>
@@ -13462,7 +13464,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="8"/>
     </row>
-    <row r="44" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>267100</v>
       </c>
@@ -13518,7 +13520,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="8"/>
     </row>
-    <row r="45" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>267101</v>
       </c>
@@ -13574,7 +13576,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="8"/>
     </row>
-    <row r="46" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>267105</v>
       </c>
@@ -13630,7 +13632,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="8"/>
     </row>
-    <row r="47" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>268016</v>
       </c>
@@ -13692,7 +13694,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="8"/>
     </row>
-    <row r="48" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>268059</v>
       </c>
@@ -13754,7 +13756,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="8"/>
     </row>
-    <row r="49" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>268061</v>
       </c>
@@ -13814,7 +13816,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>268079</v>
       </c>
@@ -13874,7 +13876,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="8"/>
     </row>
-    <row r="51" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>268082</v>
       </c>
@@ -13934,7 +13936,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="8"/>
     </row>
-    <row r="52" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>269020</v>
       </c>
@@ -13994,7 +13996,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="8"/>
     </row>
-    <row r="53" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>269025</v>
       </c>
@@ -14054,7 +14056,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="8"/>
     </row>
-    <row r="54" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>269026</v>
       </c>
@@ -14114,7 +14116,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="8"/>
     </row>
-    <row r="55" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>269027</v>
       </c>
@@ -14174,7 +14176,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="8"/>
     </row>
-    <row r="56" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>255012</v>
       </c>
@@ -14236,7 +14238,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="8"/>
     </row>
-    <row r="57" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>259025</v>
       </c>
@@ -14302,7 +14304,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="8"/>
     </row>
-    <row r="58" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>159029</v>
       </c>
@@ -14368,7 +14370,7 @@
       </c>
       <c r="Z58" s="8"/>
     </row>
-    <row r="59" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>164005</v>
       </c>
@@ -14434,7 +14436,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="8"/>
     </row>
-    <row r="60" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>152008</v>
       </c>
@@ -14498,7 +14500,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="8"/>
     </row>
-    <row r="61" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>267063</v>
       </c>
@@ -14560,7 +14562,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="8"/>
     </row>
-    <row r="62" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>168017</v>
       </c>
@@ -14622,7 +14624,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="8"/>
     </row>
-    <row r="63" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>167034</v>
       </c>
@@ -14684,7 +14686,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="8"/>
     </row>
-    <row r="64" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>266049</v>
       </c>
@@ -14750,7 +14752,7 @@
       </c>
       <c r="Z64" s="8"/>
     </row>
-    <row r="65" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>466004</v>
       </c>
@@ -14812,7 +14814,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="8"/>
     </row>
-    <row r="66" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>269013</v>
       </c>
@@ -14874,7 +14876,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="8"/>
     </row>
-    <row r="67" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>269001</v>
       </c>
@@ -14936,7 +14938,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="8"/>
     </row>
-    <row r="68" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>265088</v>
       </c>
@@ -14998,7 +15000,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="8"/>
     </row>
-    <row r="69" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>239005</v>
       </c>
@@ -15062,7 +15064,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="8"/>
     </row>
-    <row r="70" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>166027</v>
       </c>
@@ -15124,7 +15126,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="8"/>
     </row>
-    <row r="71" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>168018</v>
       </c>
@@ -15186,7 +15188,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="8"/>
     </row>
-    <row r="72" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>157033</v>
       </c>
@@ -15250,7 +15252,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="8"/>
     </row>
-    <row r="73" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>169001</v>
       </c>
@@ -15312,7 +15314,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="8"/>
     </row>
-    <row r="74" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>166035</v>
       </c>
@@ -15374,7 +15376,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="8"/>
     </row>
-    <row r="75" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>269014</v>
       </c>
@@ -15436,7 +15438,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="8"/>
     </row>
-    <row r="76" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>166032</v>
       </c>
@@ -15498,7 +15500,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="8"/>
     </row>
-    <row r="77" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>169017</v>
       </c>
@@ -15560,7 +15562,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="8"/>
     </row>
-    <row r="78" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>265011</v>
       </c>
@@ -15626,7 +15628,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="8"/>
     </row>
-    <row r="79" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>168015</v>
       </c>
@@ -15688,7 +15690,7 @@
       </c>
       <c r="Z79" s="8"/>
     </row>
-    <row r="80" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>168004</v>
       </c>
@@ -15750,7 +15752,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="8"/>
     </row>
-    <row r="81" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>168028</v>
       </c>
@@ -15812,7 +15814,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="8"/>
     </row>
-    <row r="82" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>160023</v>
       </c>
@@ -15878,7 +15880,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="8"/>
     </row>
-    <row r="83" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>150026</v>
       </c>
@@ -15944,7 +15946,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="8"/>
     </row>
-    <row r="84" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <v>161016</v>
       </c>
@@ -16010,7 +16012,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="8"/>
     </row>
-    <row r="85" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>167040</v>
       </c>
@@ -16072,7 +16074,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="8"/>
     </row>
-    <row r="86" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>161006</v>
       </c>
@@ -16138,7 +16140,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="8"/>
     </row>
-    <row r="87" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <v>164014</v>
       </c>
@@ -16196,7 +16198,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="8"/>
     </row>
-    <row r="88" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>165026</v>
       </c>
@@ -16260,7 +16262,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="8"/>
     </row>
-    <row r="89" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>166009</v>
       </c>
@@ -16322,7 +16324,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="8"/>
     </row>
-    <row r="90" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <v>166010</v>
       </c>
@@ -16384,7 +16386,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>168038</v>
       </c>
@@ -16446,7 +16448,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <v>168041</v>
       </c>
@@ -16508,7 +16510,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <v>169015</v>
       </c>
@@ -16570,7 +16572,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>169020</v>
       </c>
@@ -16632,7 +16634,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>169021</v>
       </c>
@@ -16694,7 +16696,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <v>147016</v>
       </c>
@@ -16760,7 +16762,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <v>148017</v>
       </c>
@@ -16822,7 +16824,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>150010</v>
       </c>
@@ -16888,7 +16890,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="8"/>
     </row>
-    <row r="99" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>166021</v>
       </c>
@@ -16952,7 +16954,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>167004</v>
       </c>
@@ -17014,7 +17016,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="8"/>
     </row>
-    <row r="101" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>167023</v>
       </c>
@@ -17076,7 +17078,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="8"/>
     </row>
-    <row r="102" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>169003</v>
       </c>
@@ -17138,7 +17140,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="8"/>
     </row>
-    <row r="103" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>147022</v>
       </c>
@@ -17204,7 +17206,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="8"/>
     </row>
-    <row r="104" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>165014</v>
       </c>
@@ -17266,7 +17268,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="8"/>
     </row>
-    <row r="105" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
         <v>166028</v>
       </c>
@@ -17330,7 +17332,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="8"/>
     </row>
-    <row r="106" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>167015</v>
       </c>
@@ -17392,7 +17394,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="8"/>
     </row>
-    <row r="107" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>168002</v>
       </c>
@@ -17450,7 +17452,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="8"/>
     </row>
-    <row r="108" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>168014</v>
       </c>
@@ -17512,7 +17514,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="8"/>
     </row>
-    <row r="109" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
         <v>168022</v>
       </c>
@@ -17576,7 +17578,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="8"/>
     </row>
-    <row r="110" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>168037</v>
       </c>
@@ -17638,7 +17640,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="8"/>
     </row>
-    <row r="111" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>333003</v>
       </c>
@@ -17696,7 +17698,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="8"/>
     </row>
-    <row r="112" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>168010</v>
       </c>
@@ -17758,7 +17760,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="8"/>
     </row>
-    <row r="113" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>136049</v>
       </c>
@@ -17826,7 +17828,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="8"/>
     </row>
-    <row r="114" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>135071</v>
       </c>
@@ -17888,7 +17890,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="8"/>
     </row>
-    <row r="115" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>156025</v>
       </c>
@@ -17950,7 +17952,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="8"/>
     </row>
-    <row r="116" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>165027</v>
       </c>
@@ -18014,7 +18016,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="8"/>
     </row>
-    <row r="117" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
         <v>169005</v>
       </c>
@@ -18076,7 +18078,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="8"/>
     </row>
-    <row r="118" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>155015</v>
       </c>
@@ -18142,7 +18144,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="8"/>
     </row>
-    <row r="119" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
         <v>166025</v>
       </c>
@@ -18206,7 +18208,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="8"/>
     </row>
-    <row r="120" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
         <v>167027</v>
       </c>
@@ -18264,7 +18266,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="8"/>
     </row>
-    <row r="121" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>168019</v>
       </c>
@@ -18322,7 +18324,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="8"/>
     </row>
-    <row r="122" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>169011</v>
       </c>
@@ -18380,7 +18382,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="8"/>
     </row>
-    <row r="123" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>139011</v>
       </c>
@@ -18438,7 +18440,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="8"/>
     </row>
-    <row r="124" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
         <v>159042</v>
       </c>
@@ -18504,7 +18506,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="8"/>
     </row>
-    <row r="125" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
         <v>164024</v>
       </c>
@@ -18570,7 +18572,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="8"/>
     </row>
-    <row r="126" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>166002</v>
       </c>
@@ -18634,7 +18636,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="8"/>
     </row>
-    <row r="127" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>167005</v>
       </c>
@@ -18696,7 +18698,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="8"/>
     </row>
-    <row r="128" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
         <v>167030</v>
       </c>
@@ -18754,7 +18756,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="8"/>
     </row>
-    <row r="129" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
         <v>168021</v>
       </c>
@@ -18816,7 +18818,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="8"/>
     </row>
-    <row r="130" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
         <v>168033</v>
       </c>
@@ -18874,7 +18876,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="8"/>
     </row>
-    <row r="131" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
         <v>168036</v>
       </c>
@@ -18936,7 +18938,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="8"/>
     </row>
-    <row r="132" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>169018</v>
       </c>
@@ -18998,7 +19000,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="8"/>
     </row>
-    <row r="133" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
         <v>161001</v>
       </c>
@@ -19064,7 +19066,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="8"/>
     </row>
-    <row r="134" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
         <v>166020</v>
       </c>
@@ -19128,7 +19130,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="8"/>
     </row>
-    <row r="135" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
         <v>167017</v>
       </c>
@@ -19192,7 +19194,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="8"/>
     </row>
-    <row r="136" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
         <v>168020</v>
       </c>
@@ -19254,7 +19256,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="8"/>
     </row>
-    <row r="137" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>168025</v>
       </c>
@@ -19312,7 +19314,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="8"/>
     </row>
-    <row r="138" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
         <v>169010</v>
       </c>
@@ -19374,7 +19376,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="8"/>
     </row>
-    <row r="139" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
         <v>154012</v>
       </c>
@@ -19436,7 +19438,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="8"/>
     </row>
-    <row r="140" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
         <v>165005</v>
       </c>
@@ -19498,7 +19500,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="8"/>
     </row>
-    <row r="141" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>166019</v>
       </c>
@@ -19560,7 +19562,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="8"/>
     </row>
-    <row r="142" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>168005</v>
       </c>
@@ -19618,7 +19620,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="8"/>
     </row>
-    <row r="143" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
         <v>168023</v>
       </c>
@@ -19680,7 +19682,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="8"/>
     </row>
-    <row r="144" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
         <v>168039</v>
       </c>
@@ -19742,7 +19744,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="8"/>
     </row>
-    <row r="145" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
         <v>168040</v>
       </c>
@@ -19804,7 +19806,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="8"/>
     </row>
-    <row r="146" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>169004</v>
       </c>
@@ -19866,7 +19868,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="8"/>
     </row>
-    <row r="147" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
         <v>156026</v>
       </c>
@@ -19932,7 +19934,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="8"/>
     </row>
-    <row r="148" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
         <v>166014</v>
       </c>
@@ -19996,7 +19998,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="8"/>
     </row>
-    <row r="149" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>166022</v>
       </c>
@@ -20056,7 +20058,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="8"/>
     </row>
-    <row r="150" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>156031</v>
       </c>
@@ -20120,7 +20122,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="8"/>
     </row>
-    <row r="151" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
         <v>161027</v>
       </c>
@@ -20186,7 +20188,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="8"/>
     </row>
-    <row r="152" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
         <v>164032</v>
       </c>
@@ -20252,7 +20254,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="8"/>
     </row>
-    <row r="153" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
         <v>168008</v>
       </c>
@@ -20314,7 +20316,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="8"/>
     </row>
-    <row r="154" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>146037</v>
       </c>
@@ -20376,7 +20378,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="8"/>
     </row>
-    <row r="155" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
         <v>139013</v>
       </c>
@@ -20440,7 +20442,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="8"/>
     </row>
-    <row r="156" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
         <v>145015</v>
       </c>
@@ -20506,7 +20508,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="8"/>
     </row>
-    <row r="157" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
         <v>161005</v>
       </c>
@@ -20570,7 +20572,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="8"/>
     </row>
-    <row r="158" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>163003</v>
       </c>
@@ -20636,7 +20638,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="8"/>
     </row>
-    <row r="159" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
         <v>166024</v>
       </c>
@@ -20700,7 +20702,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="8"/>
     </row>
-    <row r="160" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
         <v>167001</v>
       </c>
@@ -20764,7 +20766,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="8"/>
     </row>
-    <row r="161" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3">
         <v>167012</v>
       </c>
@@ -20822,7 +20824,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="8"/>
     </row>
-    <row r="162" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3">
         <v>260001</v>
       </c>
@@ -20888,7 +20890,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="8"/>
     </row>
-    <row r="163" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
         <v>267001</v>
       </c>
@@ -20952,7 +20954,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="8"/>
     </row>
-    <row r="164" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
         <v>160001</v>
       </c>
@@ -21020,7 +21022,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="8"/>
     </row>
-    <row r="165" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
         <v>135095</v>
       </c>
@@ -21082,7 +21084,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="8"/>
     </row>
-    <row r="166" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3">
         <v>159019</v>
       </c>
@@ -21144,7 +21146,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="8"/>
     </row>
-    <row r="167" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
         <v>160013</v>
       </c>
@@ -21210,7 +21212,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="8"/>
     </row>
-    <row r="168" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
         <v>164008</v>
       </c>
@@ -21276,7 +21278,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="8"/>
     </row>
-    <row r="169" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
         <v>165004</v>
       </c>
@@ -21340,7 +21342,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="8"/>
     </row>
-    <row r="170" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3">
         <v>167013</v>
       </c>
@@ -21404,7 +21406,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="8"/>
     </row>
-    <row r="171" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
         <v>167020</v>
       </c>
@@ -21466,7 +21468,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="8"/>
     </row>
-    <row r="172" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
         <v>167029</v>
       </c>
@@ -21528,7 +21530,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="8"/>
     </row>
-    <row r="173" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
         <v>167032</v>
       </c>
@@ -21590,7 +21592,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="8"/>
     </row>
-    <row r="174" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
         <v>168006</v>
       </c>
@@ -21652,7 +21654,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="8"/>
     </row>
-    <row r="175" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
         <v>168012</v>
       </c>
@@ -21714,7 +21716,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="8"/>
     </row>
-    <row r="176" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
         <v>168024</v>
       </c>
@@ -21776,7 +21778,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="8"/>
     </row>
-    <row r="177" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3">
         <v>168029</v>
       </c>
@@ -21838,7 +21840,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="8"/>
     </row>
-    <row r="178" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>168030</v>
       </c>
@@ -21900,7 +21902,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="8"/>
     </row>
-    <row r="179" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
         <v>169006</v>
       </c>
@@ -21962,7 +21964,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="8"/>
     </row>
-    <row r="180" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
         <v>337004</v>
       </c>
@@ -22026,7 +22028,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="8"/>
     </row>
-    <row r="181" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
         <v>364002</v>
       </c>
@@ -22588,7 +22590,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="8"/>
     </row>
-    <row r="190" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
         <v>268029</v>
       </c>
@@ -22650,7 +22652,7 @@
       </c>
       <c r="Z190" s="8"/>
     </row>
-    <row r="191" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3">
         <v>232027</v>
       </c>
@@ -22714,7 +22716,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="8"/>
     </row>
-    <row r="192" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
         <v>234092</v>
       </c>
@@ -22780,7 +22782,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="8"/>
     </row>
-    <row r="193" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
         <v>240029</v>
       </c>
@@ -22846,7 +22848,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="8"/>
     </row>
-    <row r="194" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3">
         <v>247012</v>
       </c>
@@ -22912,7 +22914,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="8"/>
     </row>
-    <row r="195" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
         <v>434007</v>
       </c>
@@ -22978,7 +22980,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="8"/>
     </row>
-    <row r="196" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3">
         <v>435004</v>
       </c>
@@ -23044,7 +23046,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="8"/>
     </row>
-    <row r="197" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3">
         <v>442002</v>
       </c>
@@ -23110,7 +23112,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="8"/>
     </row>
-    <row r="198" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3">
         <v>442007</v>
       </c>
@@ -23176,7 +23178,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="8"/>
     </row>
-    <row r="199" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3">
         <v>256029</v>
       </c>
@@ -23240,7 +23242,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="8"/>
     </row>
-    <row r="200" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3">
         <v>269012</v>
       </c>
@@ -23302,7 +23304,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="8"/>
     </row>
-    <row r="201" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
         <v>236012</v>
       </c>
@@ -23366,7 +23368,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="8"/>
     </row>
-    <row r="202" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
         <v>240005</v>
       </c>
@@ -23432,7 +23434,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="8"/>
     </row>
-    <row r="203" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3">
         <v>258001</v>
       </c>
@@ -23498,7 +23500,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="8"/>
     </row>
-    <row r="204" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
         <v>264090</v>
       </c>
@@ -23564,7 +23566,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="8"/>
     </row>
-    <row r="205" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3">
         <v>264066</v>
       </c>
@@ -23630,7 +23632,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="8"/>
     </row>
-    <row r="206" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3">
         <v>266086</v>
       </c>
@@ -23694,7 +23696,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="8"/>
     </row>
-    <row r="207" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3">
         <v>239024</v>
       </c>
@@ -23756,7 +23758,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="8"/>
     </row>
-    <row r="208" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3">
         <v>269009</v>
       </c>
@@ -23816,7 +23818,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="8"/>
     </row>
-    <row r="209" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3">
         <v>251010</v>
       </c>
@@ -23874,7 +23876,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="8"/>
     </row>
-    <row r="210" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3">
         <v>256050</v>
       </c>
@@ -23932,7 +23934,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="8"/>
     </row>
-    <row r="211" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3">
         <v>256051</v>
       </c>
@@ -23990,7 +23992,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="8"/>
     </row>
-    <row r="212" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3">
         <v>258031</v>
       </c>
@@ -24048,7 +24050,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="8"/>
     </row>
-    <row r="213" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3">
         <v>258041</v>
       </c>
@@ -24106,7 +24108,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="8"/>
     </row>
-    <row r="214" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3">
         <v>264067</v>
       </c>
@@ -24162,7 +24164,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="8"/>
     </row>
-    <row r="215" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3">
         <v>266047</v>
       </c>
@@ -24218,7 +24220,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="8"/>
     </row>
-    <row r="216" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3">
         <v>242029</v>
       </c>
@@ -24280,7 +24282,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="8"/>
     </row>
-    <row r="217" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3">
         <v>245012</v>
       </c>
@@ -24342,7 +24344,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="8"/>
     </row>
-    <row r="218" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3">
         <v>251041</v>
       </c>
@@ -24402,7 +24404,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="8"/>
     </row>
-    <row r="219" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3">
         <v>264070</v>
       </c>
@@ -24458,7 +24460,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="8"/>
     </row>
-    <row r="220" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3">
         <v>266061</v>
       </c>
@@ -24516,7 +24518,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="8"/>
     </row>
-    <row r="221" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3">
         <v>267007</v>
       </c>
@@ -24572,7 +24574,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="8"/>
     </row>
-    <row r="222" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3">
         <v>440018</v>
       </c>
@@ -24636,7 +24638,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="8"/>
     </row>
-    <row r="223" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3">
         <v>251012</v>
       </c>
@@ -24696,7 +24698,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="8"/>
     </row>
-    <row r="224" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3">
         <v>265032</v>
       </c>
@@ -24754,7 +24756,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="8"/>
     </row>
-    <row r="225" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3">
         <v>265053</v>
       </c>
@@ -24810,7 +24812,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="8"/>
     </row>
-    <row r="226" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3">
         <v>268090</v>
       </c>
@@ -24870,7 +24872,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="8"/>
     </row>
-    <row r="227" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
         <v>250042</v>
       </c>
@@ -24930,7 +24932,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="8"/>
     </row>
-    <row r="228" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3">
         <v>252013</v>
       </c>
@@ -24992,7 +24994,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="8"/>
     </row>
-    <row r="229" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3">
         <v>253045</v>
       </c>
@@ -25052,7 +25054,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="8"/>
     </row>
-    <row r="230" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3">
         <v>264063</v>
       </c>
@@ -25108,7 +25110,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="8"/>
     </row>
-    <row r="231" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3">
         <v>267008</v>
       </c>
@@ -25164,7 +25166,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="8"/>
     </row>
-    <row r="232" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3">
         <v>438016</v>
       </c>
@@ -25226,7 +25228,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="8"/>
     </row>
-    <row r="233" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3">
         <v>239006</v>
       </c>
@@ -25292,7 +25294,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="8"/>
     </row>
-    <row r="234" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3">
         <v>233034</v>
       </c>
@@ -25354,7 +25356,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="8"/>
     </row>
-    <row r="235" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3">
         <v>240034</v>
       </c>
@@ -25420,7 +25422,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="8"/>
     </row>
-    <row r="236" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3">
         <v>245015</v>
       </c>
@@ -25486,7 +25488,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="8"/>
     </row>
-    <row r="237" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3">
         <v>247008</v>
       </c>
@@ -25552,7 +25554,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="8"/>
     </row>
-    <row r="238" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3">
         <v>249019</v>
       </c>
@@ -25618,7 +25620,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="8"/>
     </row>
-    <row r="239" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3">
         <v>249046</v>
       </c>
@@ -25680,7 +25682,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="8"/>
     </row>
-    <row r="240" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3">
         <v>250016</v>
       </c>
@@ -25742,7 +25744,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="8"/>
     </row>
-    <row r="241" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3">
         <v>250017</v>
       </c>
@@ -25806,7 +25808,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="8"/>
     </row>
-    <row r="242" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3">
         <v>250059</v>
       </c>
@@ -25868,7 +25870,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="8"/>
     </row>
-    <row r="243" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3">
         <v>253003</v>
       </c>
@@ -25924,7 +25926,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="8"/>
     </row>
-    <row r="244" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3">
         <v>254055</v>
       </c>
@@ -25988,7 +25990,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="8"/>
     </row>
-    <row r="245" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3">
         <v>261028</v>
       </c>
@@ -26052,7 +26054,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="8"/>
     </row>
-    <row r="246" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3">
         <v>264007</v>
       </c>
@@ -26116,7 +26118,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="8"/>
     </row>
-    <row r="247" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3">
         <v>265019</v>
       </c>
@@ -26182,7 +26184,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="8"/>
     </row>
-    <row r="248" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3">
         <v>265047</v>
       </c>
@@ -26246,7 +26248,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="8"/>
     </row>
-    <row r="249" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3">
         <v>266010</v>
       </c>
@@ -26306,7 +26308,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="8"/>
     </row>
-    <row r="250" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3">
         <v>266021</v>
       </c>
@@ -26366,7 +26368,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="8"/>
     </row>
-    <row r="251" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3">
         <v>266052</v>
       </c>
@@ -26426,7 +26428,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="8"/>
     </row>
-    <row r="252" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3">
         <v>266060</v>
       </c>
@@ -26486,7 +26488,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="8"/>
     </row>
-    <row r="253" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3">
         <v>267047</v>
       </c>
@@ -26546,7 +26548,7 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="8"/>
     </row>
-    <row r="254" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3">
         <v>267048</v>
       </c>
@@ -26606,7 +26608,7 @@
       <c r="Y254" s="3"/>
       <c r="Z254" s="8"/>
     </row>
-    <row r="255" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3">
         <v>268013</v>
       </c>
@@ -26668,7 +26670,7 @@
       <c r="Y255" s="3"/>
       <c r="Z255" s="8"/>
     </row>
-    <row r="256" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3">
         <v>268056</v>
       </c>
@@ -26728,7 +26730,7 @@
       <c r="Y256" s="3"/>
       <c r="Z256" s="8"/>
     </row>
-    <row r="257" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3">
         <v>244005</v>
       </c>
@@ -26790,7 +26792,7 @@
       <c r="Y257" s="3"/>
       <c r="Z257" s="8"/>
     </row>
-    <row r="258" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3">
         <v>259005</v>
       </c>
@@ -26852,7 +26854,7 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="8"/>
     </row>
-    <row r="259" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3">
         <v>260003</v>
       </c>
@@ -26912,7 +26914,7 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="8"/>
     </row>
-    <row r="260" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3">
         <v>267003</v>
       </c>
@@ -26970,7 +26972,7 @@
       <c r="Y260" s="3"/>
       <c r="Z260" s="8"/>
     </row>
-    <row r="261" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3">
         <v>268083</v>
       </c>
@@ -27032,7 +27034,7 @@
       <c r="Y261" s="3"/>
       <c r="Z261" s="8"/>
     </row>
-    <row r="262" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3">
         <v>269016</v>
       </c>
@@ -27094,7 +27096,7 @@
       <c r="Y262" s="3"/>
       <c r="Z262" s="8"/>
     </row>
-    <row r="263" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3">
         <v>233010</v>
       </c>
@@ -27158,7 +27160,7 @@
       <c r="Y263" s="3"/>
       <c r="Z263" s="8"/>
     </row>
-    <row r="264" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3">
         <v>259013</v>
       </c>
@@ -27222,7 +27224,7 @@
       <c r="Y264" s="3"/>
       <c r="Z264" s="8"/>
     </row>
-    <row r="265" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3">
         <v>268091</v>
       </c>
@@ -27282,7 +27284,7 @@
       <c r="Y265" s="3"/>
       <c r="Z265" s="8"/>
     </row>
-    <row r="266" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3">
         <v>248035</v>
       </c>
@@ -27348,7 +27350,7 @@
       <c r="Y266" s="3"/>
       <c r="Z266" s="8"/>
     </row>
-    <row r="267" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3">
         <v>249010</v>
       </c>
@@ -27414,7 +27416,7 @@
       <c r="Y267" s="3"/>
       <c r="Z267" s="8"/>
     </row>
-    <row r="268" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3">
         <v>249053</v>
       </c>
@@ -27480,7 +27482,7 @@
       <c r="Y268" s="3"/>
       <c r="Z268" s="8"/>
     </row>
-    <row r="269" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3">
         <v>251019</v>
       </c>
@@ -27544,7 +27546,7 @@
       <c r="Y269" s="3"/>
       <c r="Z269" s="8"/>
     </row>
-    <row r="270" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3">
         <v>252004</v>
       </c>
@@ -27610,7 +27612,7 @@
       <c r="Y270" s="3"/>
       <c r="Z270" s="8"/>
     </row>
-    <row r="271" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3">
         <v>252009</v>
       </c>
@@ -27672,7 +27674,7 @@
       <c r="Y271" s="3"/>
       <c r="Z271" s="8"/>
     </row>
-    <row r="272" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3">
         <v>253037</v>
       </c>
@@ -27734,7 +27736,7 @@
       <c r="Y272" s="3"/>
       <c r="Z272" s="8"/>
     </row>
-    <row r="273" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3">
         <v>254018</v>
       </c>
@@ -27794,7 +27796,7 @@
       <c r="Y273" s="3"/>
       <c r="Z273" s="8"/>
     </row>
-    <row r="274" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3">
         <v>254035</v>
       </c>
@@ -27858,7 +27860,7 @@
       <c r="Y274" s="3"/>
       <c r="Z274" s="8"/>
     </row>
-    <row r="275" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3">
         <v>254049</v>
       </c>
@@ -27920,7 +27922,7 @@
       <c r="Y275" s="3"/>
       <c r="Z275" s="8"/>
     </row>
-    <row r="276" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3">
         <v>256032</v>
       </c>
@@ -27984,7 +27986,7 @@
       <c r="Y276" s="3"/>
       <c r="Z276" s="8"/>
     </row>
-    <row r="277" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3">
         <v>260018</v>
       </c>
@@ -28046,7 +28048,7 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="8"/>
     </row>
-    <row r="278" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3">
         <v>260045</v>
       </c>
@@ -28108,7 +28110,7 @@
       <c r="Y278" s="3"/>
       <c r="Z278" s="8"/>
     </row>
-    <row r="279" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3">
         <v>264040</v>
       </c>
@@ -28170,7 +28172,7 @@
       <c r="Y279" s="3"/>
       <c r="Z279" s="8"/>
     </row>
-    <row r="280" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3">
         <v>264091</v>
       </c>
@@ -28232,7 +28234,7 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="8"/>
     </row>
-    <row r="281" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3">
         <v>265012</v>
       </c>
@@ -28292,7 +28294,7 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="8"/>
     </row>
-    <row r="282" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3">
         <v>265040</v>
       </c>
@@ -28352,7 +28354,7 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="8"/>
     </row>
-    <row r="283" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3">
         <v>266050</v>
       </c>
@@ -28416,7 +28418,7 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="8"/>
     </row>
-    <row r="284" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3">
         <v>266072</v>
       </c>
@@ -28476,7 +28478,7 @@
       <c r="Y284" s="3"/>
       <c r="Z284" s="8"/>
     </row>
-    <row r="285" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3">
         <v>267022</v>
       </c>
@@ -28536,7 +28538,7 @@
       <c r="Y285" s="3"/>
       <c r="Z285" s="8"/>
     </row>
-    <row r="286" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3">
         <v>267035</v>
       </c>
@@ -28598,7 +28600,7 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="8"/>
     </row>
-    <row r="287" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3">
         <v>267074</v>
       </c>
@@ -28660,7 +28662,7 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="8"/>
     </row>
-    <row r="288" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3">
         <v>267083</v>
       </c>
@@ -28720,7 +28722,7 @@
       <c r="Y288" s="3"/>
       <c r="Z288" s="8"/>
     </row>
-    <row r="289" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3">
         <v>267099</v>
       </c>
@@ -28780,7 +28782,7 @@
       <c r="Y289" s="3"/>
       <c r="Z289" s="8"/>
     </row>
-    <row r="290" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3">
         <v>268012</v>
       </c>
@@ -28842,7 +28844,7 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="8"/>
     </row>
-    <row r="291" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3">
         <v>268042</v>
       </c>
@@ -28902,7 +28904,7 @@
       <c r="Y291" s="3"/>
       <c r="Z291" s="8"/>
     </row>
-    <row r="292" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3">
         <v>268073</v>
       </c>
@@ -28962,7 +28964,7 @@
       <c r="Y292" s="3"/>
       <c r="Z292" s="8"/>
     </row>
-    <row r="293" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3">
         <v>269011</v>
       </c>
@@ -29024,7 +29026,7 @@
       <c r="Y293" s="3"/>
       <c r="Z293" s="8"/>
     </row>
-    <row r="294" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3">
         <v>269024</v>
       </c>
@@ -29084,7 +29086,7 @@
       <c r="Y294" s="3"/>
       <c r="Z294" s="8"/>
     </row>
-    <row r="295" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3">
         <v>238030</v>
       </c>
@@ -29150,7 +29152,7 @@
       <c r="Y295" s="3"/>
       <c r="Z295" s="8"/>
     </row>
-    <row r="296" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3">
         <v>240018</v>
       </c>
@@ -29214,7 +29216,7 @@
       <c r="Y296" s="3"/>
       <c r="Z296" s="8"/>
     </row>
-    <row r="297" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3">
         <v>251006</v>
       </c>
@@ -29280,7 +29282,7 @@
       <c r="Y297" s="3"/>
       <c r="Z297" s="8"/>
     </row>
-    <row r="298" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3">
         <v>251025</v>
       </c>
@@ -29344,7 +29346,7 @@
       <c r="Y298" s="3"/>
       <c r="Z298" s="8"/>
     </row>
-    <row r="299" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3">
         <v>252027</v>
       </c>
@@ -29410,7 +29412,7 @@
       <c r="Y299" s="3"/>
       <c r="Z299" s="8"/>
     </row>
-    <row r="300" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3">
         <v>253042</v>
       </c>
@@ -29474,7 +29476,7 @@
       <c r="Y300" s="3"/>
       <c r="Z300" s="8"/>
     </row>
-    <row r="301" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3">
         <v>256036</v>
       </c>
@@ -29536,7 +29538,7 @@
       <c r="Y301" s="3"/>
       <c r="Z301" s="8"/>
     </row>
-    <row r="302" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3">
         <v>256038</v>
       </c>
@@ -29598,7 +29600,7 @@
       <c r="Y302" s="3"/>
       <c r="Z302" s="8"/>
     </row>
-    <row r="303" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3">
         <v>266057</v>
       </c>
@@ -29662,7 +29664,7 @@
       <c r="Y303" s="3"/>
       <c r="Z303" s="8"/>
     </row>
-    <row r="304" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3">
         <v>266065</v>
       </c>
@@ -29722,7 +29724,7 @@
       <c r="Y304" s="3"/>
       <c r="Z304" s="8"/>
     </row>
-    <row r="305" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3">
         <v>246004</v>
       </c>
@@ -29788,7 +29790,7 @@
       <c r="Y305" s="3"/>
       <c r="Z305" s="8"/>
     </row>
-    <row r="306" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3">
         <v>256014</v>
       </c>
@@ -29854,7 +29856,7 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="8"/>
     </row>
-    <row r="307" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3">
         <v>244028</v>
       </c>
@@ -29918,7 +29920,7 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="8"/>
     </row>
-    <row r="308" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3">
         <v>251048</v>
       </c>
@@ -29982,7 +29984,7 @@
       <c r="Y308" s="3"/>
       <c r="Z308" s="8"/>
     </row>
-    <row r="309" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3">
         <v>255003</v>
       </c>
@@ -30044,7 +30046,7 @@
       <c r="Y309" s="3"/>
       <c r="Z309" s="8"/>
     </row>
-    <row r="310" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3">
         <v>257021</v>
       </c>
@@ -30108,7 +30110,7 @@
       <c r="Y310" s="3"/>
       <c r="Z310" s="8"/>
     </row>
-    <row r="311" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3">
         <v>258035</v>
       </c>
@@ -30170,7 +30172,7 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="8"/>
     </row>
-    <row r="312" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3">
         <v>260029</v>
       </c>
@@ -30230,7 +30232,7 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="8"/>
     </row>
-    <row r="313" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3">
         <v>264019</v>
       </c>
@@ -30290,7 +30292,7 @@
       <c r="Y313" s="3"/>
       <c r="Z313" s="8"/>
     </row>
-    <row r="314" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3">
         <v>264039</v>
       </c>
@@ -30352,7 +30354,7 @@
       <c r="Y314" s="3"/>
       <c r="Z314" s="8"/>
     </row>
-    <row r="315" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3">
         <v>265043</v>
       </c>
@@ -30408,7 +30410,7 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="8"/>
     </row>
-    <row r="316" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3">
         <v>265058</v>
       </c>
@@ -30464,7 +30466,7 @@
       <c r="Y316" s="3"/>
       <c r="Z316" s="8"/>
     </row>
-    <row r="317" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3">
         <v>267017</v>
       </c>
@@ -30520,7 +30522,7 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="8"/>
     </row>
-    <row r="318" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3">
         <v>267080</v>
       </c>
@@ -30576,7 +30578,7 @@
       <c r="Y318" s="3"/>
       <c r="Z318" s="8"/>
     </row>
-    <row r="319" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3">
         <v>243010</v>
       </c>
@@ -30638,7 +30640,7 @@
       <c r="Y319" s="3"/>
       <c r="Z319" s="8"/>
     </row>
-    <row r="320" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3">
         <v>255004</v>
       </c>
@@ -30700,7 +30702,7 @@
       <c r="Y320" s="3"/>
       <c r="Z320" s="8"/>
     </row>
-    <row r="321" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3">
         <v>258022</v>
       </c>
@@ -30762,7 +30764,7 @@
       <c r="Y321" s="3"/>
       <c r="Z321" s="8"/>
     </row>
-    <row r="322" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3">
         <v>265023</v>
       </c>
@@ -30818,7 +30820,7 @@
       <c r="Y322" s="3"/>
       <c r="Z322" s="8"/>
     </row>
-    <row r="323" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3">
         <v>267005</v>
       </c>
@@ -30874,7 +30876,7 @@
       <c r="Y323" s="3"/>
       <c r="Z323" s="8"/>
     </row>
-    <row r="324" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3">
         <v>267060</v>
       </c>
@@ -30934,7 +30936,7 @@
       <c r="Y324" s="3"/>
       <c r="Z324" s="8"/>
     </row>
-    <row r="325" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3">
         <v>439003</v>
       </c>
@@ -30996,7 +30998,7 @@
       <c r="Y325" s="3"/>
       <c r="Z325" s="8"/>
     </row>
-    <row r="326" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3">
         <v>244011</v>
       </c>
@@ -31058,7 +31060,7 @@
       <c r="Y326" s="3"/>
       <c r="Z326" s="8"/>
     </row>
-    <row r="327" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3">
         <v>247019</v>
       </c>
@@ -31122,7 +31124,7 @@
       <c r="Y327" s="3"/>
       <c r="Z327" s="8"/>
     </row>
-    <row r="328" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3">
         <v>252038</v>
       </c>
@@ -31186,7 +31188,7 @@
       <c r="Y328" s="3"/>
       <c r="Z328" s="8"/>
     </row>
-    <row r="329" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3">
         <v>259016</v>
       </c>
@@ -31248,7 +31250,7 @@
       <c r="Y329" s="3"/>
       <c r="Z329" s="8"/>
     </row>
-    <row r="330" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3">
         <v>264044</v>
       </c>
@@ -31310,7 +31312,7 @@
       <c r="Y330" s="3"/>
       <c r="Z330" s="8"/>
     </row>
-    <row r="331" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3">
         <v>264074</v>
       </c>
@@ -31368,7 +31370,7 @@
       <c r="Y331" s="3"/>
       <c r="Z331" s="8"/>
     </row>
-    <row r="332" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3">
         <v>264075</v>
       </c>
@@ -31426,7 +31428,7 @@
       <c r="Y332" s="3"/>
       <c r="Z332" s="8"/>
     </row>
-    <row r="333" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3">
         <v>265110</v>
       </c>
@@ -31482,7 +31484,7 @@
       <c r="Y333" s="3"/>
       <c r="Z333" s="8"/>
     </row>
-    <row r="334" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3">
         <v>266013</v>
       </c>
@@ -31538,7 +31540,7 @@
       <c r="Y334" s="3"/>
       <c r="Z334" s="8"/>
     </row>
-    <row r="335" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3">
         <v>267014</v>
       </c>
@@ -31594,7 +31596,7 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="8"/>
     </row>
-    <row r="336" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3">
         <v>267015</v>
       </c>
@@ -31650,7 +31652,7 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="8"/>
     </row>
-    <row r="337" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3">
         <v>267086</v>
       </c>
@@ -31710,7 +31712,7 @@
       <c r="Y337" s="3"/>
       <c r="Z337" s="8"/>
     </row>
-    <row r="338" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3">
         <v>268030</v>
       </c>
@@ -31770,7 +31772,7 @@
       <c r="Y338" s="3"/>
       <c r="Z338" s="8"/>
     </row>
-    <row r="339" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3">
         <v>268031</v>
       </c>
@@ -31830,7 +31832,7 @@
       <c r="Y339" s="3"/>
       <c r="Z339" s="8"/>
     </row>
-    <row r="340" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3">
         <v>268041</v>
       </c>
@@ -31890,7 +31892,7 @@
       <c r="Y340" s="3"/>
       <c r="Z340" s="8"/>
     </row>
-    <row r="341" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3">
         <v>257019</v>
       </c>
@@ -31952,7 +31954,7 @@
       <c r="Y341" s="3"/>
       <c r="Z341" s="8"/>
     </row>
-    <row r="342" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3">
         <v>242025</v>
       </c>
@@ -32018,7 +32020,7 @@
       <c r="Y342" s="3"/>
       <c r="Z342" s="8"/>
     </row>
-    <row r="343" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3">
         <v>243003</v>
       </c>
@@ -32084,7 +32086,7 @@
       <c r="Y343" s="3"/>
       <c r="Z343" s="8"/>
     </row>
-    <row r="344" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3">
         <v>247020</v>
       </c>
@@ -32146,7 +32148,7 @@
       <c r="Y344" s="3"/>
       <c r="Z344" s="8"/>
     </row>
-    <row r="345" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3">
         <v>249094</v>
       </c>
@@ -32210,7 +32212,7 @@
       <c r="Y345" s="3"/>
       <c r="Z345" s="8"/>
     </row>
-    <row r="346" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3">
         <v>257018</v>
       </c>
@@ -32274,7 +32276,7 @@
       <c r="Y346" s="3"/>
       <c r="Z346" s="8"/>
     </row>
-    <row r="347" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3">
         <v>259020</v>
       </c>
@@ -32336,7 +32338,7 @@
       <c r="Y347" s="3"/>
       <c r="Z347" s="8"/>
     </row>
-    <row r="348" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3">
         <v>443003</v>
       </c>
@@ -32402,7 +32404,7 @@
       <c r="Y348" s="3"/>
       <c r="Z348" s="8"/>
     </row>
-    <row r="349" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3">
         <v>467002</v>
       </c>
@@ -32458,7 +32460,7 @@
       <c r="Y349" s="3"/>
       <c r="Z349" s="8"/>
     </row>
-    <row r="350" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3">
         <v>467003</v>
       </c>
@@ -32514,7 +32516,7 @@
       <c r="Y350" s="3"/>
       <c r="Z350" s="8"/>
     </row>
-    <row r="351" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3">
         <v>254057</v>
       </c>
@@ -32580,7 +32582,7 @@
       <c r="Y351" s="3"/>
       <c r="Z351" s="8"/>
     </row>
-    <row r="352" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3">
         <v>237011</v>
       </c>
@@ -32646,7 +32648,7 @@
       <c r="Y352" s="3"/>
       <c r="Z352" s="8"/>
     </row>
-    <row r="353" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3">
         <v>249058</v>
       </c>
@@ -32708,7 +32710,7 @@
       <c r="Y353" s="3"/>
       <c r="Z353" s="8"/>
     </row>
-    <row r="354" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3">
         <v>254037</v>
       </c>
@@ -32770,7 +32772,7 @@
       <c r="Y354" s="3"/>
       <c r="Z354" s="8"/>
     </row>
-    <row r="355" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3">
         <v>261014</v>
       </c>
@@ -32830,7 +32832,7 @@
       <c r="Y355" s="3"/>
       <c r="Z355" s="8"/>
     </row>
-    <row r="356" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3">
         <v>265066</v>
       </c>
@@ -32890,7 +32892,7 @@
       <c r="Y356" s="3"/>
       <c r="Z356" s="8"/>
     </row>
-    <row r="357" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3">
         <v>266031</v>
       </c>
@@ -32950,7 +32952,7 @@
       <c r="Y357" s="3"/>
       <c r="Z357" s="8"/>
     </row>
-    <row r="358" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3">
         <v>268088</v>
       </c>
@@ -33010,7 +33012,7 @@
       <c r="Y358" s="3"/>
       <c r="Z358" s="8"/>
     </row>
-    <row r="359" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3">
         <v>236069</v>
       </c>
@@ -33074,7 +33076,7 @@
       <c r="Y359" s="3"/>
       <c r="Z359" s="8"/>
     </row>
-    <row r="360" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3">
         <v>245001</v>
       </c>
@@ -33136,7 +33138,7 @@
       <c r="Y360" s="3"/>
       <c r="Z360" s="8"/>
     </row>
-    <row r="361" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3">
         <v>245006</v>
       </c>
@@ -33200,7 +33202,7 @@
       <c r="Y361" s="3"/>
       <c r="Z361" s="8"/>
     </row>
-    <row r="362" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3">
         <v>248043</v>
       </c>
@@ -33262,7 +33264,7 @@
       <c r="Y362" s="3"/>
       <c r="Z362" s="8"/>
     </row>
-    <row r="363" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3">
         <v>249036</v>
       </c>
@@ -33324,7 +33326,7 @@
       <c r="Y363" s="3"/>
       <c r="Z363" s="8"/>
     </row>
-    <row r="364" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3">
         <v>256042</v>
       </c>
@@ -33386,7 +33388,7 @@
       <c r="Y364" s="3"/>
       <c r="Z364" s="8"/>
     </row>
-    <row r="365" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3">
         <v>264008</v>
       </c>
@@ -33450,7 +33452,7 @@
       <c r="Y365" s="3"/>
       <c r="Z365" s="8"/>
     </row>
-    <row r="366" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3">
         <v>265103</v>
       </c>
@@ -33510,7 +33512,7 @@
       <c r="Y366" s="3"/>
       <c r="Z366" s="8"/>
     </row>
-    <row r="367" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3">
         <v>266090</v>
       </c>
@@ -33572,7 +33574,7 @@
       <c r="Y367" s="3"/>
       <c r="Z367" s="8"/>
     </row>
-    <row r="368" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3">
         <v>268074</v>
       </c>
@@ -33634,7 +33636,7 @@
       <c r="Y368" s="3"/>
       <c r="Z368" s="8"/>
     </row>
-    <row r="369" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3">
         <v>265128</v>
       </c>
@@ -33694,7 +33696,7 @@
       <c r="Y369" s="3"/>
       <c r="Z369" s="8"/>
     </row>
-    <row r="370" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3">
         <v>266083</v>
       </c>
@@ -33750,7 +33752,7 @@
       <c r="Y370" s="3"/>
       <c r="Z370" s="8"/>
     </row>
-    <row r="371" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3">
         <v>267052</v>
       </c>
@@ -33806,7 +33808,7 @@
       <c r="Y371" s="3"/>
       <c r="Z371" s="8"/>
     </row>
-    <row r="372" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3">
         <v>268028</v>
       </c>
@@ -33866,7 +33868,7 @@
       <c r="Y372" s="3"/>
       <c r="Z372" s="8"/>
     </row>
-    <row r="373" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3">
         <v>268053</v>
       </c>
@@ -33926,7 +33928,7 @@
       <c r="Y373" s="3"/>
       <c r="Z373" s="8"/>
     </row>
-    <row r="374" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3">
         <v>268062</v>
       </c>
@@ -33986,7 +33988,7 @@
       <c r="Y374" s="3"/>
       <c r="Z374" s="8"/>
     </row>
-    <row r="375" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3">
         <v>268076</v>
       </c>
@@ -34046,7 +34048,7 @@
       <c r="Y375" s="3"/>
       <c r="Z375" s="8"/>
     </row>
-    <row r="376" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3">
         <v>268092</v>
       </c>
@@ -34106,7 +34108,7 @@
       <c r="Y376" s="3"/>
       <c r="Z376" s="8"/>
     </row>
-    <row r="377" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3">
         <v>269003</v>
       </c>
@@ -34166,7 +34168,7 @@
       <c r="Y377" s="3"/>
       <c r="Z377" s="8"/>
     </row>
-    <row r="378" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3">
         <v>269006</v>
       </c>
@@ -34226,7 +34228,7 @@
       <c r="Y378" s="3"/>
       <c r="Z378" s="8"/>
     </row>
-    <row r="379" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3">
         <v>269018</v>
       </c>
@@ -34286,7 +34288,7 @@
       <c r="Y379" s="3"/>
       <c r="Z379" s="8"/>
     </row>
-    <row r="380" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3">
         <v>269019</v>
       </c>
@@ -34346,7 +34348,7 @@
       <c r="Y380" s="3"/>
       <c r="Z380" s="8"/>
     </row>
-    <row r="381" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3">
         <v>249086</v>
       </c>
@@ -34408,7 +34410,7 @@
       <c r="Y381" s="3"/>
       <c r="Z381" s="8"/>
     </row>
-    <row r="382" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3">
         <v>267096</v>
       </c>
@@ -34470,7 +34472,7 @@
       <c r="Y382" s="3"/>
       <c r="Z382" s="8"/>
     </row>
-    <row r="383" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3">
         <v>250062</v>
       </c>
@@ -34536,7 +34538,7 @@
       <c r="Y383" s="3"/>
       <c r="Z383" s="8"/>
     </row>
-    <row r="384" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3">
         <v>256015</v>
       </c>
@@ -34598,7 +34600,7 @@
       <c r="Y384" s="3"/>
       <c r="Z384" s="8"/>
     </row>
-    <row r="385" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3">
         <v>256016</v>
       </c>
@@ -34662,7 +34664,7 @@
       <c r="Y385" s="3"/>
       <c r="Z385" s="8"/>
     </row>
-    <row r="386" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3">
         <v>259024</v>
       </c>
@@ -34726,7 +34728,7 @@
       <c r="Y386" s="3"/>
       <c r="Z386" s="8"/>
     </row>
-    <row r="387" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3">
         <v>264045</v>
       </c>
@@ -34786,7 +34788,7 @@
       <c r="Y387" s="3"/>
       <c r="Z387" s="8"/>
     </row>
-    <row r="388" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3">
         <v>265111</v>
       </c>
@@ -34846,7 +34848,7 @@
       <c r="Y388" s="3"/>
       <c r="Z388" s="8"/>
     </row>
-    <row r="389" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3">
         <v>265124</v>
       </c>
@@ -34906,7 +34908,7 @@
       <c r="Y389" s="3"/>
       <c r="Z389" s="8"/>
     </row>
-    <row r="390" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3">
         <v>266030</v>
       </c>
@@ -34966,7 +34968,7 @@
       <c r="Y390" s="3"/>
       <c r="Z390" s="8"/>
     </row>
-    <row r="391" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3">
         <v>251029</v>
       </c>
@@ -35028,7 +35030,7 @@
       <c r="Y391" s="3"/>
       <c r="Z391" s="8"/>
     </row>
-    <row r="392" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3">
         <v>256004</v>
       </c>
@@ -35090,7 +35092,7 @@
       <c r="Y392" s="3"/>
       <c r="Z392" s="8"/>
     </row>
-    <row r="393" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3">
         <v>260016</v>
       </c>
@@ -35150,7 +35152,7 @@
       <c r="Y393" s="3"/>
       <c r="Z393" s="8"/>
     </row>
-    <row r="394" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3">
         <v>264022</v>
       </c>
@@ -35210,7 +35212,7 @@
       <c r="Y394" s="3"/>
       <c r="Z394" s="8"/>
     </row>
-    <row r="395" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3">
         <v>264083</v>
       </c>
@@ -35274,7 +35276,7 @@
       <c r="Y395" s="3"/>
       <c r="Z395" s="8"/>
     </row>
-    <row r="396" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3">
         <v>265010</v>
       </c>
@@ -35334,7 +35336,7 @@
       <c r="Y396" s="3"/>
       <c r="Z396" s="8"/>
     </row>
-    <row r="397" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3">
         <v>265013</v>
       </c>
@@ -35396,7 +35398,7 @@
       <c r="Y397" s="3"/>
       <c r="Z397" s="8"/>
     </row>
-    <row r="398" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3">
         <v>268038</v>
       </c>
@@ -35456,7 +35458,7 @@
       <c r="Y398" s="3"/>
       <c r="Z398" s="8"/>
     </row>
-    <row r="399" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3">
         <v>251050</v>
       </c>
@@ -35520,7 +35522,7 @@
       <c r="Y399" s="3"/>
       <c r="Z399" s="8"/>
     </row>
-    <row r="400" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3">
         <v>251058</v>
       </c>
@@ -35582,7 +35584,7 @@
       <c r="Y400" s="3"/>
       <c r="Z400" s="8"/>
     </row>
-    <row r="401" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3">
         <v>251062</v>
       </c>
@@ -35644,7 +35646,7 @@
       <c r="Y401" s="3"/>
       <c r="Z401" s="8"/>
     </row>
-    <row r="402" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3">
         <v>259022</v>
       </c>
@@ -35708,7 +35710,7 @@
       <c r="Y402" s="3"/>
       <c r="Z402" s="8"/>
     </row>
-    <row r="403" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3">
         <v>259038</v>
       </c>
@@ -35770,7 +35772,7 @@
       <c r="Y403" s="3"/>
       <c r="Z403" s="8"/>
     </row>
-    <row r="404" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3">
         <v>264048</v>
       </c>
@@ -35830,7 +35832,7 @@
       <c r="Y404" s="3"/>
       <c r="Z404" s="8"/>
     </row>
-    <row r="405" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3">
         <v>264051</v>
       </c>
@@ -35890,7 +35892,7 @@
       <c r="Y405" s="3"/>
       <c r="Z405" s="8"/>
     </row>
-    <row r="406" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3">
         <v>264089</v>
       </c>
@@ -35950,7 +35952,7 @@
       <c r="Y406" s="3"/>
       <c r="Z406" s="8"/>
     </row>
-    <row r="407" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3">
         <v>265024</v>
       </c>
@@ -36010,7 +36012,7 @@
       <c r="Y407" s="3"/>
       <c r="Z407" s="8"/>
     </row>
-    <row r="408" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3">
         <v>265061</v>
       </c>
@@ -36070,7 +36072,7 @@
       <c r="Y408" s="3"/>
       <c r="Z408" s="8"/>
     </row>
-    <row r="409" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3">
         <v>265076</v>
       </c>
@@ -36130,7 +36132,7 @@
       <c r="Y409" s="3"/>
       <c r="Z409" s="8"/>
     </row>
-    <row r="410" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3">
         <v>266037</v>
       </c>
@@ -36190,7 +36192,7 @@
       <c r="Y410" s="3"/>
       <c r="Z410" s="8"/>
     </row>
-    <row r="411" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3">
         <v>441005</v>
       </c>
@@ -36256,7 +36258,7 @@
       <c r="Y411" s="3"/>
       <c r="Z411" s="8"/>
     </row>
-    <row r="412" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3">
         <v>268037</v>
       </c>
@@ -36316,7 +36318,7 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="8"/>
     </row>
-    <row r="413" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3">
         <v>268086</v>
       </c>
@@ -36376,7 +36378,7 @@
       <c r="Y413" s="3"/>
       <c r="Z413" s="8"/>
     </row>
-    <row r="414" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3">
         <v>250022</v>
       </c>
@@ -36440,7 +36442,7 @@
       <c r="Y414" s="3"/>
       <c r="Z414" s="8"/>
     </row>
-    <row r="415" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3">
         <v>251028</v>
       </c>
@@ -36502,7 +36504,7 @@
       <c r="Y415" s="3"/>
       <c r="Z415" s="8"/>
     </row>
-    <row r="416" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3">
         <v>253023</v>
       </c>
@@ -36564,7 +36566,7 @@
       <c r="Y416" s="3"/>
       <c r="Z416" s="8"/>
     </row>
-    <row r="417" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3">
         <v>264084</v>
       </c>
@@ -36626,7 +36628,7 @@
       <c r="Y417" s="3"/>
       <c r="Z417" s="8"/>
     </row>
-    <row r="418" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3">
         <v>265127</v>
       </c>
@@ -36686,7 +36688,7 @@
       <c r="Y418" s="3"/>
       <c r="Z418" s="8"/>
     </row>
-    <row r="419" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3">
         <v>266016</v>
       </c>
@@ -36746,7 +36748,7 @@
       <c r="Y419" s="3"/>
       <c r="Z419" s="8"/>
     </row>
-    <row r="420" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3">
         <v>247007</v>
       </c>
@@ -36808,7 +36810,7 @@
       <c r="Y420" s="3"/>
       <c r="Z420" s="8"/>
     </row>
-    <row r="421" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3">
         <v>251002</v>
       </c>
@@ -36872,7 +36874,7 @@
       <c r="Y421" s="3"/>
       <c r="Z421" s="8"/>
     </row>
-    <row r="422" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3">
         <v>251023</v>
       </c>
@@ -36934,7 +36936,7 @@
       <c r="Y422" s="3"/>
       <c r="Z422" s="8"/>
     </row>
-    <row r="423" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3">
         <v>262008</v>
       </c>
@@ -36996,7 +36998,7 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="8"/>
     </row>
-    <row r="424" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3">
         <v>265063</v>
       </c>
@@ -37056,7 +37058,7 @@
       <c r="Y424" s="3"/>
       <c r="Z424" s="8"/>
     </row>
-    <row r="425" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3">
         <v>266002</v>
       </c>
@@ -37116,7 +37118,7 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="8"/>
     </row>
-    <row r="426" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3">
         <v>246013</v>
       </c>
@@ -37178,7 +37180,7 @@
       <c r="Y426" s="3"/>
       <c r="Z426" s="8"/>
     </row>
-    <row r="427" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3">
         <v>249048</v>
       </c>
@@ -37244,7 +37246,7 @@
       <c r="Y427" s="3"/>
       <c r="Z427" s="8"/>
     </row>
-    <row r="428" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3">
         <v>250010</v>
       </c>
@@ -37306,7 +37308,7 @@
       <c r="Y428" s="3"/>
       <c r="Z428" s="8"/>
     </row>
-    <row r="429" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3">
         <v>251065</v>
       </c>
@@ -37368,7 +37370,7 @@
       <c r="Y429" s="3"/>
       <c r="Z429" s="8"/>
     </row>
-    <row r="430" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3">
         <v>265126</v>
       </c>
@@ -37432,7 +37434,7 @@
       <c r="Y430" s="3"/>
       <c r="Z430" s="8"/>
     </row>
-    <row r="431" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3">
         <v>267043</v>
       </c>
@@ -37492,7 +37494,7 @@
       <c r="Y431" s="3"/>
       <c r="Z431" s="8"/>
     </row>
-    <row r="432" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3">
         <v>267072</v>
       </c>
@@ -37554,7 +37556,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="8"/>
     </row>
-    <row r="433" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3">
         <v>467004</v>
       </c>
@@ -37614,7 +37616,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="8"/>
     </row>
-    <row r="434" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3">
         <v>467005</v>
       </c>
@@ -37674,7 +37676,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="8"/>
     </row>
-    <row r="435" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3">
         <v>242032</v>
       </c>
@@ -37740,7 +37742,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="8"/>
     </row>
-    <row r="436" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3">
         <v>266091</v>
       </c>
@@ -37804,7 +37806,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="8"/>
     </row>
-    <row r="437" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3">
         <v>268052</v>
       </c>
@@ -37866,7 +37868,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="8"/>
     </row>
-    <row r="438" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3">
         <v>255016</v>
       </c>
@@ -37932,7 +37934,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="8"/>
     </row>
-    <row r="439" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3">
         <v>269022</v>
       </c>
@@ -37994,7 +37996,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="8"/>
     </row>
-    <row r="440" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3">
         <v>236082</v>
       </c>
@@ -38058,7 +38060,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="8"/>
     </row>
-    <row r="441" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3">
         <v>244006</v>
       </c>
@@ -38116,7 +38118,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="8"/>
     </row>
-    <row r="442" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3">
         <v>251067</v>
       </c>
@@ -38180,7 +38182,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="8"/>
     </row>
-    <row r="443" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3">
         <v>257014</v>
       </c>
@@ -38236,7 +38238,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="8"/>
     </row>
-    <row r="444" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3">
         <v>258021</v>
       </c>
@@ -38294,7 +38296,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="8"/>
     </row>
-    <row r="445" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3">
         <v>265027</v>
       </c>
@@ -38352,7 +38354,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="8"/>
     </row>
-    <row r="446" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3">
         <v>265039</v>
       </c>
@@ -38410,7 +38412,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="8"/>
     </row>
-    <row r="447" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3">
         <v>265050</v>
       </c>
@@ -38466,7 +38468,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="8"/>
     </row>
-    <row r="448" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3">
         <v>265056</v>
       </c>
@@ -38524,7 +38526,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="8"/>
     </row>
-    <row r="449" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3">
         <v>265089</v>
       </c>
@@ -38580,7 +38582,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="8"/>
     </row>
-    <row r="450" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3">
         <v>265094</v>
       </c>
@@ -38638,7 +38640,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="8"/>
     </row>
-    <row r="451" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3">
         <v>265129</v>
       </c>
@@ -38696,7 +38698,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="8"/>
     </row>
-    <row r="452" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3">
         <v>265133</v>
       </c>
@@ -38752,7 +38754,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="8"/>
     </row>
-    <row r="453" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3">
         <v>266068</v>
       </c>
@@ -38808,7 +38810,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="8"/>
     </row>
-    <row r="454" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3">
         <v>267088</v>
       </c>
@@ -38864,7 +38866,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="8"/>
     </row>
-    <row r="455" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3">
         <v>267104</v>
       </c>
@@ -38920,7 +38922,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="8"/>
     </row>
-    <row r="456" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3">
         <v>268009</v>
       </c>
@@ -38976,7 +38978,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="8"/>
     </row>
-    <row r="457" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3">
         <v>268070</v>
       </c>
@@ -39036,7 +39038,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="8"/>
     </row>
-    <row r="458" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3">
         <v>268087</v>
       </c>
@@ -39096,7 +39098,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="8"/>
     </row>
-    <row r="459" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3">
         <v>257007</v>
       </c>
@@ -39152,7 +39154,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="8"/>
     </row>
-    <row r="460" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3">
         <v>257008</v>
       </c>
@@ -39208,7 +39210,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="8"/>
     </row>
-    <row r="461" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3">
         <v>257009</v>
       </c>
@@ -39272,7 +39274,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="8"/>
     </row>
-    <row r="462" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3">
         <v>264011</v>
       </c>
@@ -39330,7 +39332,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="8"/>
     </row>
-    <row r="463" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3">
         <v>268055</v>
       </c>
@@ -39390,7 +39392,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="8"/>
     </row>
-    <row r="464" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3">
         <v>442009</v>
       </c>
@@ -39448,7 +39450,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="8"/>
     </row>
-    <row r="465" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3">
         <v>239036</v>
       </c>
@@ -39512,7 +39514,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="8"/>
     </row>
-    <row r="466" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3">
         <v>245007</v>
       </c>
@@ -39570,7 +39572,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="8"/>
     </row>
-    <row r="467" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3">
         <v>245028</v>
       </c>
@@ -39628,7 +39630,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="8"/>
     </row>
-    <row r="468" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3">
         <v>245029</v>
       </c>
@@ -39686,7 +39688,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="8"/>
     </row>
-    <row r="469" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3">
         <v>249026</v>
       </c>
@@ -39744,7 +39746,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="8"/>
     </row>
-    <row r="470" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3">
         <v>251015</v>
       </c>
@@ -39804,7 +39806,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="8"/>
     </row>
-    <row r="471" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3">
         <v>251020</v>
       </c>
@@ -39864,7 +39866,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="8"/>
     </row>
-    <row r="472" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3">
         <v>253009</v>
       </c>
@@ -39922,7 +39924,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="8"/>
     </row>
-    <row r="473" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3">
         <v>254024</v>
       </c>
@@ -39978,7 +39980,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="8"/>
     </row>
-    <row r="474" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3">
         <v>256056</v>
       </c>
@@ -40040,7 +40042,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="8"/>
     </row>
-    <row r="475" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3">
         <v>257015</v>
       </c>
@@ -40096,7 +40098,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="8"/>
     </row>
-    <row r="476" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3">
         <v>257035</v>
       </c>
@@ -40154,7 +40156,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="8"/>
     </row>
-    <row r="477" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3">
         <v>258004</v>
       </c>
@@ -40216,7 +40218,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="8"/>
     </row>
-    <row r="478" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3">
         <v>260024</v>
       </c>
@@ -40272,7 +40274,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="8"/>
     </row>
-    <row r="479" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3">
         <v>260038</v>
       </c>
@@ -40332,7 +40334,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="8"/>
     </row>
-    <row r="480" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3">
         <v>264025</v>
       </c>
@@ -40388,7 +40390,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="8"/>
     </row>
-    <row r="481" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3">
         <v>265099</v>
       </c>
@@ -40444,7 +40446,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="8"/>
     </row>
-    <row r="482" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3">
         <v>269004</v>
       </c>
@@ -40504,7 +40506,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="8"/>
     </row>
-    <row r="483" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3">
         <v>253014</v>
       </c>
@@ -40570,7 +40572,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="8"/>
     </row>
-    <row r="484" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3">
         <v>237017</v>
       </c>
@@ -40634,7 +40636,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="8"/>
     </row>
-    <row r="485" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3">
         <v>241015</v>
       </c>
@@ -40698,7 +40700,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="8"/>
     </row>
-    <row r="486" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3">
         <v>250056</v>
       </c>
@@ -40762,7 +40764,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="8"/>
     </row>
-    <row r="487" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3">
         <v>254061</v>
       </c>
@@ -40822,7 +40824,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="8"/>
     </row>
-    <row r="488" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3">
         <v>260041</v>
       </c>
@@ -40886,7 +40888,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="8"/>
     </row>
-    <row r="489" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3">
         <v>242017</v>
       </c>
@@ -40946,7 +40948,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="8"/>
     </row>
-    <row r="490" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3">
         <v>246006</v>
       </c>
@@ -41010,7 +41012,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="8"/>
     </row>
-    <row r="491" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3">
         <v>246010</v>
       </c>
@@ -41074,7 +41076,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="8"/>
     </row>
-    <row r="492" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3">
         <v>248013</v>
       </c>
@@ -41138,7 +41140,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="8"/>
     </row>
-    <row r="493" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3">
         <v>248039</v>
       </c>
@@ -41198,7 +41200,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="8"/>
     </row>
-    <row r="494" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3">
         <v>256067</v>
       </c>
@@ -41262,7 +41264,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="8"/>
     </row>
-    <row r="495" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3">
         <v>260048</v>
       </c>
@@ -41324,7 +41326,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="8"/>
     </row>
-    <row r="496" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3">
         <v>261005</v>
       </c>
@@ -41386,7 +41388,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="8"/>
     </row>
-    <row r="497" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3">
         <v>261037</v>
       </c>
@@ -41452,7 +41454,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="8"/>
     </row>
-    <row r="498" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3">
         <v>267018</v>
       </c>
@@ -41512,7 +41514,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="8"/>
     </row>
-    <row r="499" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3">
         <v>268045</v>
       </c>
@@ -41572,7 +41574,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="8"/>
     </row>
-    <row r="500" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3">
         <v>248031</v>
       </c>
@@ -41638,7 +41640,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="8"/>
     </row>
-    <row r="501" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3">
         <v>268020</v>
       </c>
@@ -41700,7 +41702,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="8"/>
     </row>
-    <row r="502" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3">
         <v>268077</v>
       </c>
@@ -41762,7 +41764,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="8"/>
     </row>
-    <row r="503" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3">
         <v>233025</v>
       </c>
@@ -41826,7 +41828,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="8"/>
     </row>
-    <row r="504" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3">
         <v>265132</v>
       </c>
@@ -41890,7 +41892,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="8"/>
     </row>
-    <row r="505" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3">
         <v>266048</v>
       </c>
@@ -41952,7 +41954,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="8"/>
     </row>
-    <row r="506" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3">
         <v>266088</v>
       </c>
@@ -42010,7 +42012,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="8"/>
     </row>
-    <row r="507" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3">
         <v>469002</v>
       </c>
@@ -42072,7 +42074,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="8"/>
     </row>
-    <row r="508" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3">
         <v>268007</v>
       </c>
@@ -42132,7 +42134,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="8"/>
     </row>
-    <row r="509" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3">
         <v>251007</v>
       </c>
@@ -42198,7 +42200,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="8"/>
     </row>
-    <row r="510" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3">
         <v>268048</v>
       </c>
@@ -42260,7 +42262,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="8"/>
     </row>
-    <row r="511" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3">
         <v>252001</v>
       </c>
@@ -42326,7 +42328,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="8"/>
     </row>
-    <row r="512" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3">
         <v>264071</v>
       </c>
@@ -42384,7 +42386,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="8"/>
     </row>
-    <row r="513" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3">
         <v>264088</v>
       </c>
@@ -42446,7 +42448,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="8"/>
     </row>
-    <row r="514" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3">
         <v>268002</v>
       </c>
@@ -42508,7 +42510,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="8"/>
     </row>
-    <row r="515" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3">
         <v>232015</v>
       </c>
@@ -42566,7 +42568,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="8"/>
     </row>
-    <row r="516" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3">
         <v>237068</v>
       </c>
@@ -42626,7 +42628,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="8"/>
     </row>
-    <row r="517" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3">
         <v>242012</v>
       </c>
@@ -42692,7 +42694,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="8"/>
     </row>
-    <row r="518" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3">
         <v>250054</v>
       </c>
@@ -42750,7 +42752,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="8"/>
     </row>
-    <row r="519" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3">
         <v>254002</v>
       </c>
@@ -42808,7 +42810,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="8"/>
     </row>
-    <row r="520" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3">
         <v>254004</v>
       </c>
@@ -42868,7 +42870,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="8"/>
     </row>
-    <row r="521" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3">
         <v>254044</v>
       </c>
@@ -42928,7 +42930,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="8"/>
     </row>
-    <row r="522" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3">
         <v>258032</v>
       </c>
@@ -42988,7 +42990,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="8"/>
     </row>
-    <row r="523" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3">
         <v>265054</v>
       </c>
@@ -43052,7 +43054,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="8"/>
     </row>
-    <row r="524" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3">
         <v>265086</v>
       </c>
@@ -43108,7 +43110,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="8"/>
     </row>
-    <row r="525" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3">
         <v>266062</v>
       </c>
@@ -43164,7 +43166,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="8"/>
     </row>
-    <row r="526" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3">
         <v>266077</v>
       </c>
@@ -43226,7 +43228,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="8"/>
     </row>
-    <row r="527" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3">
         <v>269017</v>
       </c>
@@ -43286,7 +43288,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="8"/>
     </row>
-    <row r="528" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3">
         <v>235118</v>
       </c>
@@ -43344,7 +43346,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="8"/>
     </row>
-    <row r="529" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3">
         <v>268063</v>
       </c>
@@ -43404,7 +43406,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="8"/>
     </row>
-    <row r="530" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3">
         <v>268084</v>
       </c>
@@ -43466,7 +43468,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="8"/>
     </row>
-    <row r="531" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3">
         <v>469001</v>
       </c>
@@ -43524,7 +43526,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="8"/>
     </row>
-    <row r="532" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3">
         <v>149024</v>
       </c>
@@ -43586,7 +43588,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="8"/>
     </row>
-    <row r="533" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3">
         <v>146029</v>
       </c>
@@ -43652,7 +43654,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="8"/>
     </row>
-    <row r="534" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3">
         <v>233027</v>
       </c>
@@ -43716,7 +43718,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="8"/>
     </row>
-    <row r="535" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3">
         <v>257037</v>
       </c>
@@ -43778,7 +43780,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="8"/>
     </row>
-    <row r="536" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3">
         <v>257039</v>
       </c>
@@ -43844,7 +43846,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="8"/>
     </row>
-    <row r="537" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3">
         <v>260050</v>
       </c>
@@ -43908,7 +43910,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="8"/>
     </row>
-    <row r="538" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3">
         <v>266035</v>
       </c>
@@ -43972,7 +43974,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="8"/>
     </row>
-    <row r="539" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3">
         <v>267032</v>
       </c>
@@ -44034,7 +44036,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="8"/>
     </row>
-    <row r="540" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3">
         <v>268003</v>
       </c>
@@ -44096,7 +44098,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="8"/>
     </row>
-    <row r="541" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3">
         <v>269010</v>
       </c>
@@ -44158,7 +44160,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="8"/>
     </row>
-    <row r="542" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3">
         <v>233060</v>
       </c>
@@ -44216,7 +44218,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="8"/>
     </row>
-    <row r="543" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3">
         <v>244023</v>
       </c>
@@ -44282,7 +44284,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="8"/>
     </row>
-    <row r="544" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3">
         <v>256001</v>
       </c>
@@ -44342,7 +44344,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="8"/>
     </row>
-    <row r="545" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3">
         <v>265037</v>
       </c>
@@ -44406,7 +44408,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="8"/>
     </row>
-    <row r="546" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3">
         <v>266004</v>
       </c>
@@ -44470,7 +44472,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="8"/>
     </row>
-    <row r="547" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3">
         <v>266082</v>
       </c>
@@ -44534,7 +44536,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="8"/>
     </row>
-    <row r="548" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3">
         <v>166006</v>
       </c>
@@ -44592,7 +44594,7 @@
       </c>
       <c r="Z548" s="8"/>
     </row>
-    <row r="549" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3">
         <v>169012</v>
       </c>
@@ -44650,7 +44652,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="8"/>
     </row>
-    <row r="550" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3">
         <v>241009</v>
       </c>
@@ -44712,7 +44714,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="8"/>
     </row>
-    <row r="551" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3">
         <v>147029</v>
       </c>
@@ -44772,7 +44774,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="8"/>
     </row>
-    <row r="552" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3">
         <v>149039</v>
       </c>
@@ -44834,7 +44836,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="8"/>
     </row>
-    <row r="553" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3">
         <v>151015</v>
       </c>
@@ -44900,7 +44902,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="8"/>
     </row>
-    <row r="554" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3">
         <v>160004</v>
       </c>
@@ -44962,7 +44964,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="8"/>
     </row>
-    <row r="555" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3">
         <v>161010</v>
       </c>
@@ -45024,7 +45026,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="8"/>
     </row>
-    <row r="556" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3">
         <v>166026</v>
       </c>
@@ -45084,7 +45086,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="8"/>
     </row>
-    <row r="557" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3">
         <v>166034</v>
       </c>
@@ -45142,7 +45144,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="8"/>
     </row>
-    <row r="558" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3">
         <v>167009</v>
       </c>
@@ -45200,7 +45202,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="8"/>
     </row>
-    <row r="559" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3">
         <v>136028</v>
       </c>
@@ -45260,7 +45262,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="8"/>
     </row>
-    <row r="560" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3">
         <v>150029</v>
       </c>
@@ -45322,7 +45324,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="8"/>
     </row>
-    <row r="561" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3">
         <v>245017</v>
       </c>
@@ -45388,7 +45390,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="8"/>
     </row>
-    <row r="562" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3">
         <v>368001</v>
       </c>
@@ -45450,7 +45452,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="8"/>
     </row>
-    <row r="563" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3">
         <v>148005</v>
       </c>
@@ -45516,7 +45518,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="8"/>
     </row>
-    <row r="564" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3">
         <v>168003</v>
       </c>
@@ -45578,7 +45580,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="8"/>
     </row>
-    <row r="565" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3">
         <v>169014</v>
       </c>
@@ -45640,7 +45642,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="8"/>
     </row>
-    <row r="566" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3">
         <v>158053</v>
       </c>
@@ -45706,7 +45708,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="8"/>
     </row>
-    <row r="567" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3">
         <v>166018</v>
       </c>
@@ -45764,7 +45766,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="8"/>
     </row>
-    <row r="568" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3">
         <v>167010</v>
       </c>
@@ -45826,7 +45828,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="8"/>
     </row>
-    <row r="569" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3">
         <v>169019</v>
       </c>
@@ -45888,7 +45890,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="8"/>
     </row>
-    <row r="570" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3">
         <v>167007</v>
       </c>
@@ -45952,7 +45954,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="8"/>
     </row>
-    <row r="571" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3">
         <v>169013</v>
       </c>
@@ -46014,7 +46016,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="8"/>
     </row>
-    <row r="572" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3">
         <v>161014</v>
       </c>
@@ -46078,7 +46080,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="8"/>
     </row>
-    <row r="573" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3">
         <v>169016</v>
       </c>
@@ -46140,7 +46142,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="8"/>
     </row>
-    <row r="574" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3">
         <v>167036</v>
       </c>
@@ -46200,7 +46202,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="8"/>
     </row>
-    <row r="575" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
         <v>2912</v>
       </c>
@@ -46262,7 +46264,7 @@
       </c>
       <c r="Z575" s="8"/>
     </row>
-    <row r="576" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>2910</v>
       </c>
@@ -46325,7 +46327,13 @@
       <c r="Z576" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="OGC-FAD-PCM-PCM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>
@@ -47192,8 +47200,8 @@
       <c r="C43" s="3" t="s">
         <v>2821</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>2781</v>
+      <c r="D43" s="2" t="s">
+        <v>2304</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>34</v>
@@ -48683,6 +48691,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F117" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{015EE132-8702-492C-BC59-E6AE9B62D6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{CF5DC0C6-E4F6-4D03-85F9-BBF533AC946D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="3445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7594" uniqueCount="3446">
   <si>
     <t>emp_id</t>
   </si>
@@ -10373,6 +10373,9 @@
   </si>
   <si>
     <t>168001A.jpg</t>
+  </si>
+  <si>
+    <t>OGC-MFG-SPN-PCM</t>
   </si>
 </sst>
 </file>
@@ -10422,7 +10425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10442,6 +10445,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -10473,7 +10482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10508,6 +10517,9 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -46343,7 +46355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -47651,1047 +47663,1067 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="14" t="s">
+        <v>3445</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>2821</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>2387</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>2844</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>2844</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>2445</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+    <row r="68" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
         <v>2424</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>2845</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>2845</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>2445</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+    <row r="69" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
         <v>2457</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>2846</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>2846</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>2798</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+    <row r="70" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
         <v>2470</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>2847</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>2847</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>2798</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="2" t="s">
+    <row r="71" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
         <v>2489</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>2848</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>2848</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>2798</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+    <row r="72" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
         <v>2849</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>2804</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>2804</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>2774</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
+    <row r="73" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>2850</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>2850</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>2774</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+    <row r="74" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>2851</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>2851</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>2774</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>2852</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>2852</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>2774</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+    <row r="76" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
         <v>2853</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>2812</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>2812</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F76" s="3" t="s">
         <v>2774</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
+    <row r="78" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>2854</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>2854</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F78" s="3" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
+    <row r="79" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>2855</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>2855</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
+    <row r="80" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>2856</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>2856</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F80" s="3" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>2857</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>2857</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
+    <row r="82" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>2858</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>2858</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="2" t="s">
+    <row r="83" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>2859</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>2859</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
+    <row r="84" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B84" s="3" t="s">
         <v>2860</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>2860</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F84" s="3" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
+    <row r="85" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>2861</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>2861</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
+    <row r="86" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>2862</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>2862</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F86" s="3" t="s">
         <v>2776</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="2" t="s">
+    <row r="87" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>2863</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>2863</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
+    <row r="88" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>2864</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>2864</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F88" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="2" t="s">
+    <row r="89" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>2865</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>2865</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+    <row r="90" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
         <v>1826</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B90" s="3" t="s">
         <v>2866</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>2866</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>1975</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F90" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="2" t="s">
+    <row r="91" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
         <v>1890</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>2867</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>2867</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>1975</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
+    <row r="92" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
         <v>1914</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>1975</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F92" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
         <v>1988</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>2869</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>2869</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>2013</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
+    <row r="94" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
         <v>2870</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>2838</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>2838</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>2013</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E94" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F94" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="2" t="s">
+    <row r="95" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
         <v>2074</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>2871</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>2871</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D95" s="2" t="s">
         <v>2107</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
+    <row r="96" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
         <v>2124</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D96" s="3" t="s">
         <v>2210</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="2" t="s">
+    <row r="97" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
         <v>2144</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>2873</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>2873</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D97" s="2" t="s">
         <v>2210</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
+    <row r="98" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
         <v>2196</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B98" s="3" t="s">
         <v>2874</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>2874</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>2210</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F98" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="2" t="s">
+    <row r="99" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
         <v>2875</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B99" s="2" t="s">
         <v>2833</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>2833</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
+    <row r="100" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
         <v>2876</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B100" s="3" t="s">
         <v>2877</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>2877</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>1406</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="2" t="s">
+    <row r="101" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>2878</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B101" s="2" t="s">
         <v>2879</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>2879</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
+    <row r="102" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
         <v>2880</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B102" s="3" t="s">
         <v>2881</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>2881</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D102" s="3" t="s">
         <v>1406</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F102" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="2" t="s">
+    <row r="103" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>2882</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B103" s="2" t="s">
         <v>2883</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>2883</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
+    <row r="104" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
         <v>2884</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B104" s="3" t="s">
         <v>2885</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>2885</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D104" s="3" t="s">
         <v>1579</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F104" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="2" t="s">
+    <row r="105" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
         <v>2886</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B105" s="2" t="s">
         <v>2887</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>2887</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="F105" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="3" t="s">
+    <row r="106" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
         <v>2888</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B106" s="3" t="s">
         <v>2889</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>2889</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D106" s="3" t="s">
         <v>1579</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E106" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F106" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
+    <row r="107" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>2890</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>2891</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>2891</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="F107" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="3" t="s">
+    <row r="108" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="3" t="s">
         <v>2892</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B108" s="3" t="s">
         <v>2893</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>2893</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D108" s="3" t="s">
         <v>1759</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F108" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
         <v>2894</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>2895</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>2895</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E109" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F108" s="2" t="s">
+      <c r="F109" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="3" t="s">
+    <row r="110" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="3" t="s">
         <v>2896</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B110" s="3" t="s">
         <v>2835</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>2835</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D110" s="3" t="s">
         <v>1759</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E110" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F110" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
+    <row r="111" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
         <v>2897</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>2898</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>2898</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E111" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F111" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="3" t="s">
+    <row r="112" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="3" t="s">
         <v>2899</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B112" s="3" t="s">
         <v>2900</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>2900</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>1759</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E112" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F112" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="2" t="s">
+    <row r="113" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
         <v>2901</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>2902</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>2902</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E113" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>2778</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
+    <row r="114" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
         <v>2463</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B114" s="3" t="s">
         <v>2903</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>2903</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>2457</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E114" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F114" s="3" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="2" t="s">
+    <row r="115" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>2477</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>2904</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>2904</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D115" s="2" t="s">
         <v>2470</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E115" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="3" t="s">
+    <row r="116" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="3" t="s">
         <v>2484</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B116" s="3" t="s">
         <v>2905</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>2905</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D116" s="3" t="s">
         <v>2470</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E116" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F116" s="3" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="2" t="s">
+    <row r="117" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
         <v>2499</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>2906</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>2906</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D117" s="2" t="s">
         <v>2489</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="F117" s="2" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="3" t="s">
+    <row r="118" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="3" t="s">
         <v>2101</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B118" s="3" t="s">
         <v>2907</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>2907</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>2074</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>2908</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F118" s="3" t="s">
         <v>2778</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F117" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:F118" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{CF5DC0C6-E4F6-4D03-85F9-BBF533AC946D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{E50475B0-A2F7-4015-B377-5EC4E7B0F41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -10513,13 +10513,13 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10823,7 +10823,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z576"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10849,32 +10848,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>2914</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -10953,7 +10952,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>168001</v>
       </c>
@@ -11012,7 +11011,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>168016</v>
       </c>
@@ -11074,7 +11073,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="8"/>
     </row>
-    <row r="5" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>258026</v>
       </c>
@@ -11140,7 +11139,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>234064</v>
       </c>
@@ -11204,7 +11203,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>254019</v>
       </c>
@@ -11266,7 +11265,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>264004</v>
       </c>
@@ -11328,7 +11327,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="8"/>
     </row>
-    <row r="9" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>264018</v>
       </c>
@@ -11388,7 +11387,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="8"/>
     </row>
-    <row r="10" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>264024</v>
       </c>
@@ -11450,7 +11449,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="8"/>
     </row>
-    <row r="11" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>264034</v>
       </c>
@@ -11510,7 +11509,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="8"/>
     </row>
-    <row r="12" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>264050</v>
       </c>
@@ -11570,7 +11569,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="8"/>
     </row>
-    <row r="13" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>265038</v>
       </c>
@@ -11630,7 +11629,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>265122</v>
       </c>
@@ -11692,7 +11691,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="8"/>
     </row>
-    <row r="15" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>266005</v>
       </c>
@@ -11758,7 +11757,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="8"/>
     </row>
-    <row r="16" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>267010</v>
       </c>
@@ -11820,7 +11819,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>267071</v>
       </c>
@@ -11882,7 +11881,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>267082</v>
       </c>
@@ -11944,7 +11943,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="8"/>
     </row>
-    <row r="19" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>267089</v>
       </c>
@@ -12004,7 +12003,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="8"/>
     </row>
-    <row r="20" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>267090</v>
       </c>
@@ -12064,7 +12063,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>268010</v>
       </c>
@@ -12124,7 +12123,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>268011</v>
       </c>
@@ -12184,7 +12183,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>268051</v>
       </c>
@@ -12246,7 +12245,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>268060</v>
       </c>
@@ -12308,7 +12307,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>268065</v>
       </c>
@@ -12368,7 +12367,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>268066</v>
       </c>
@@ -12428,7 +12427,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>268067</v>
       </c>
@@ -12488,7 +12487,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>268085</v>
       </c>
@@ -12548,7 +12547,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>269023</v>
       </c>
@@ -12610,7 +12609,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>235035</v>
       </c>
@@ -12674,7 +12673,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="8"/>
     </row>
-    <row r="31" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>253020</v>
       </c>
@@ -12736,7 +12735,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="8"/>
     </row>
-    <row r="32" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>250051</v>
       </c>
@@ -12802,7 +12801,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="8"/>
     </row>
-    <row r="33" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>254009</v>
       </c>
@@ -12862,7 +12861,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="8"/>
     </row>
-    <row r="34" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>254054</v>
       </c>
@@ -12922,7 +12921,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="8"/>
     </row>
-    <row r="35" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>255001</v>
       </c>
@@ -12982,7 +12981,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="8"/>
     </row>
-    <row r="36" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>255023</v>
       </c>
@@ -13046,7 +13045,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="8"/>
     </row>
-    <row r="37" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>257010</v>
       </c>
@@ -13110,7 +13109,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="8"/>
     </row>
-    <row r="38" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>257029</v>
       </c>
@@ -13172,7 +13171,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="8"/>
     </row>
-    <row r="39" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>261023</v>
       </c>
@@ -13234,7 +13233,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="8"/>
     </row>
-    <row r="40" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>267025</v>
       </c>
@@ -13294,7 +13293,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="8"/>
     </row>
-    <row r="41" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>267026</v>
       </c>
@@ -13354,7 +13353,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="8"/>
     </row>
-    <row r="42" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>267028</v>
       </c>
@@ -13416,7 +13415,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="8"/>
     </row>
-    <row r="43" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>267079</v>
       </c>
@@ -13476,7 +13475,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="8"/>
     </row>
-    <row r="44" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>267100</v>
       </c>
@@ -13532,7 +13531,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="8"/>
     </row>
-    <row r="45" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>267101</v>
       </c>
@@ -13588,7 +13587,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="8"/>
     </row>
-    <row r="46" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>267105</v>
       </c>
@@ -13644,7 +13643,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="8"/>
     </row>
-    <row r="47" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>268016</v>
       </c>
@@ -13706,7 +13705,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="8"/>
     </row>
-    <row r="48" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>268059</v>
       </c>
@@ -13768,7 +13767,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="8"/>
     </row>
-    <row r="49" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>268061</v>
       </c>
@@ -13828,7 +13827,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>268079</v>
       </c>
@@ -13888,7 +13887,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="8"/>
     </row>
-    <row r="51" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>268082</v>
       </c>
@@ -13948,7 +13947,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="8"/>
     </row>
-    <row r="52" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>269020</v>
       </c>
@@ -14008,7 +14007,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="8"/>
     </row>
-    <row r="53" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>269025</v>
       </c>
@@ -14068,7 +14067,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="8"/>
     </row>
-    <row r="54" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>269026</v>
       </c>
@@ -14128,7 +14127,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="8"/>
     </row>
-    <row r="55" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>269027</v>
       </c>
@@ -14188,7 +14187,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="8"/>
     </row>
-    <row r="56" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>255012</v>
       </c>
@@ -14250,7 +14249,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="8"/>
     </row>
-    <row r="57" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>259025</v>
       </c>
@@ -14316,7 +14315,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="8"/>
     </row>
-    <row r="58" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>159029</v>
       </c>
@@ -14382,7 +14381,7 @@
       </c>
       <c r="Z58" s="8"/>
     </row>
-    <row r="59" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>164005</v>
       </c>
@@ -14448,7 +14447,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="8"/>
     </row>
-    <row r="60" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>152008</v>
       </c>
@@ -14512,7 +14511,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="8"/>
     </row>
-    <row r="61" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>267063</v>
       </c>
@@ -14574,7 +14573,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="8"/>
     </row>
-    <row r="62" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>168017</v>
       </c>
@@ -14636,7 +14635,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="8"/>
     </row>
-    <row r="63" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>167034</v>
       </c>
@@ -14698,7 +14697,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="8"/>
     </row>
-    <row r="64" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>266049</v>
       </c>
@@ -14764,7 +14763,7 @@
       </c>
       <c r="Z64" s="8"/>
     </row>
-    <row r="65" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>466004</v>
       </c>
@@ -14826,7 +14825,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="8"/>
     </row>
-    <row r="66" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>269013</v>
       </c>
@@ -14888,7 +14887,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="8"/>
     </row>
-    <row r="67" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>269001</v>
       </c>
@@ -14950,7 +14949,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="8"/>
     </row>
-    <row r="68" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>265088</v>
       </c>
@@ -15012,7 +15011,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="8"/>
     </row>
-    <row r="69" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>239005</v>
       </c>
@@ -15076,7 +15075,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="8"/>
     </row>
-    <row r="70" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>166027</v>
       </c>
@@ -15138,7 +15137,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="8"/>
     </row>
-    <row r="71" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>168018</v>
       </c>
@@ -15200,7 +15199,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="8"/>
     </row>
-    <row r="72" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>157033</v>
       </c>
@@ -15264,7 +15263,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="8"/>
     </row>
-    <row r="73" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>169001</v>
       </c>
@@ -15326,7 +15325,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="8"/>
     </row>
-    <row r="74" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>166035</v>
       </c>
@@ -15388,7 +15387,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="8"/>
     </row>
-    <row r="75" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>269014</v>
       </c>
@@ -15450,7 +15449,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="8"/>
     </row>
-    <row r="76" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>166032</v>
       </c>
@@ -15512,7 +15511,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="8"/>
     </row>
-    <row r="77" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>169017</v>
       </c>
@@ -15574,7 +15573,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="8"/>
     </row>
-    <row r="78" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>265011</v>
       </c>
@@ -15640,7 +15639,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="8"/>
     </row>
-    <row r="79" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>168015</v>
       </c>
@@ -15702,7 +15701,7 @@
       </c>
       <c r="Z79" s="8"/>
     </row>
-    <row r="80" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>168004</v>
       </c>
@@ -15764,7 +15763,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="8"/>
     </row>
-    <row r="81" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>168028</v>
       </c>
@@ -15826,7 +15825,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="8"/>
     </row>
-    <row r="82" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>160023</v>
       </c>
@@ -15892,7 +15891,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="8"/>
     </row>
-    <row r="83" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>150026</v>
       </c>
@@ -15958,7 +15957,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="8"/>
     </row>
-    <row r="84" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <v>161016</v>
       </c>
@@ -16024,7 +16023,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="8"/>
     </row>
-    <row r="85" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>167040</v>
       </c>
@@ -16086,7 +16085,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="8"/>
     </row>
-    <row r="86" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>161006</v>
       </c>
@@ -16152,7 +16151,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="8"/>
     </row>
-    <row r="87" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <v>164014</v>
       </c>
@@ -16210,7 +16209,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="8"/>
     </row>
-    <row r="88" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>165026</v>
       </c>
@@ -16274,7 +16273,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="8"/>
     </row>
-    <row r="89" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>166009</v>
       </c>
@@ -16336,7 +16335,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="8"/>
     </row>
-    <row r="90" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <v>166010</v>
       </c>
@@ -16398,7 +16397,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>168038</v>
       </c>
@@ -16460,7 +16459,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <v>168041</v>
       </c>
@@ -16522,7 +16521,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <v>169015</v>
       </c>
@@ -16584,7 +16583,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>169020</v>
       </c>
@@ -16646,7 +16645,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>169021</v>
       </c>
@@ -16708,7 +16707,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <v>147016</v>
       </c>
@@ -16774,7 +16773,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <v>148017</v>
       </c>
@@ -16836,7 +16835,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>150010</v>
       </c>
@@ -16902,7 +16901,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="8"/>
     </row>
-    <row r="99" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>166021</v>
       </c>
@@ -16966,7 +16965,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>167004</v>
       </c>
@@ -17028,7 +17027,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="8"/>
     </row>
-    <row r="101" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>167023</v>
       </c>
@@ -17090,7 +17089,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="8"/>
     </row>
-    <row r="102" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>169003</v>
       </c>
@@ -17152,7 +17151,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="8"/>
     </row>
-    <row r="103" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>147022</v>
       </c>
@@ -17218,7 +17217,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="8"/>
     </row>
-    <row r="104" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>165014</v>
       </c>
@@ -17280,7 +17279,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="8"/>
     </row>
-    <row r="105" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
         <v>166028</v>
       </c>
@@ -17344,7 +17343,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="8"/>
     </row>
-    <row r="106" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>167015</v>
       </c>
@@ -17406,7 +17405,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="8"/>
     </row>
-    <row r="107" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>168002</v>
       </c>
@@ -17464,7 +17463,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="8"/>
     </row>
-    <row r="108" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>168014</v>
       </c>
@@ -17526,7 +17525,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="8"/>
     </row>
-    <row r="109" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
         <v>168022</v>
       </c>
@@ -17590,7 +17589,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="8"/>
     </row>
-    <row r="110" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>168037</v>
       </c>
@@ -17652,7 +17651,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="8"/>
     </row>
-    <row r="111" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>333003</v>
       </c>
@@ -17710,7 +17709,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="8"/>
     </row>
-    <row r="112" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>168010</v>
       </c>
@@ -17772,7 +17771,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="8"/>
     </row>
-    <row r="113" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>136049</v>
       </c>
@@ -17840,7 +17839,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="8"/>
     </row>
-    <row r="114" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>135071</v>
       </c>
@@ -17902,7 +17901,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="8"/>
     </row>
-    <row r="115" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>156025</v>
       </c>
@@ -17964,7 +17963,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="8"/>
     </row>
-    <row r="116" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>165027</v>
       </c>
@@ -18028,7 +18027,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="8"/>
     </row>
-    <row r="117" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
         <v>169005</v>
       </c>
@@ -18090,7 +18089,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="8"/>
     </row>
-    <row r="118" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>155015</v>
       </c>
@@ -18156,7 +18155,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="8"/>
     </row>
-    <row r="119" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
         <v>166025</v>
       </c>
@@ -18220,7 +18219,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="8"/>
     </row>
-    <row r="120" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
         <v>167027</v>
       </c>
@@ -18278,7 +18277,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="8"/>
     </row>
-    <row r="121" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>168019</v>
       </c>
@@ -18336,7 +18335,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="8"/>
     </row>
-    <row r="122" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>169011</v>
       </c>
@@ -18394,7 +18393,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="8"/>
     </row>
-    <row r="123" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>139011</v>
       </c>
@@ -18452,7 +18451,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="8"/>
     </row>
-    <row r="124" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
         <v>159042</v>
       </c>
@@ -18518,7 +18517,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="8"/>
     </row>
-    <row r="125" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
         <v>164024</v>
       </c>
@@ -18584,7 +18583,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="8"/>
     </row>
-    <row r="126" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>166002</v>
       </c>
@@ -18648,7 +18647,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="8"/>
     </row>
-    <row r="127" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>167005</v>
       </c>
@@ -18710,7 +18709,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="8"/>
     </row>
-    <row r="128" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
         <v>167030</v>
       </c>
@@ -18768,7 +18767,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="8"/>
     </row>
-    <row r="129" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
         <v>168021</v>
       </c>
@@ -18830,7 +18829,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="8"/>
     </row>
-    <row r="130" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
         <v>168033</v>
       </c>
@@ -18888,7 +18887,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="8"/>
     </row>
-    <row r="131" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
         <v>168036</v>
       </c>
@@ -18950,7 +18949,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="8"/>
     </row>
-    <row r="132" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>169018</v>
       </c>
@@ -19012,7 +19011,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="8"/>
     </row>
-    <row r="133" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
         <v>161001</v>
       </c>
@@ -19078,7 +19077,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="8"/>
     </row>
-    <row r="134" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
         <v>166020</v>
       </c>
@@ -19142,7 +19141,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="8"/>
     </row>
-    <row r="135" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
         <v>167017</v>
       </c>
@@ -19206,7 +19205,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="8"/>
     </row>
-    <row r="136" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
         <v>168020</v>
       </c>
@@ -19268,7 +19267,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="8"/>
     </row>
-    <row r="137" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>168025</v>
       </c>
@@ -19326,7 +19325,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="8"/>
     </row>
-    <row r="138" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
         <v>169010</v>
       </c>
@@ -19388,7 +19387,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="8"/>
     </row>
-    <row r="139" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
         <v>154012</v>
       </c>
@@ -19450,7 +19449,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="8"/>
     </row>
-    <row r="140" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
         <v>165005</v>
       </c>
@@ -19512,7 +19511,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="8"/>
     </row>
-    <row r="141" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>166019</v>
       </c>
@@ -19574,7 +19573,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="8"/>
     </row>
-    <row r="142" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>168005</v>
       </c>
@@ -19632,7 +19631,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="8"/>
     </row>
-    <row r="143" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
         <v>168023</v>
       </c>
@@ -19694,7 +19693,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="8"/>
     </row>
-    <row r="144" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
         <v>168039</v>
       </c>
@@ -19756,7 +19755,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="8"/>
     </row>
-    <row r="145" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
         <v>168040</v>
       </c>
@@ -19818,7 +19817,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="8"/>
     </row>
-    <row r="146" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>169004</v>
       </c>
@@ -19880,7 +19879,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="8"/>
     </row>
-    <row r="147" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
         <v>156026</v>
       </c>
@@ -19946,7 +19945,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="8"/>
     </row>
-    <row r="148" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
         <v>166014</v>
       </c>
@@ -20010,7 +20009,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="8"/>
     </row>
-    <row r="149" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>166022</v>
       </c>
@@ -20070,7 +20069,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="8"/>
     </row>
-    <row r="150" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>156031</v>
       </c>
@@ -20134,7 +20133,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="8"/>
     </row>
-    <row r="151" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
         <v>161027</v>
       </c>
@@ -20200,7 +20199,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="8"/>
     </row>
-    <row r="152" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
         <v>164032</v>
       </c>
@@ -20266,7 +20265,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="8"/>
     </row>
-    <row r="153" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
         <v>168008</v>
       </c>
@@ -20328,7 +20327,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="8"/>
     </row>
-    <row r="154" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>146037</v>
       </c>
@@ -20390,7 +20389,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="8"/>
     </row>
-    <row r="155" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
         <v>139013</v>
       </c>
@@ -20454,7 +20453,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="8"/>
     </row>
-    <row r="156" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
         <v>145015</v>
       </c>
@@ -20520,7 +20519,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="8"/>
     </row>
-    <row r="157" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
         <v>161005</v>
       </c>
@@ -20584,7 +20583,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="8"/>
     </row>
-    <row r="158" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>163003</v>
       </c>
@@ -20650,7 +20649,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="8"/>
     </row>
-    <row r="159" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
         <v>166024</v>
       </c>
@@ -20714,7 +20713,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="8"/>
     </row>
-    <row r="160" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
         <v>167001</v>
       </c>
@@ -20778,7 +20777,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="8"/>
     </row>
-    <row r="161" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3">
         <v>167012</v>
       </c>
@@ -20836,7 +20835,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="8"/>
     </row>
-    <row r="162" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3">
         <v>260001</v>
       </c>
@@ -20902,7 +20901,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="8"/>
     </row>
-    <row r="163" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
         <v>267001</v>
       </c>
@@ -20966,7 +20965,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="8"/>
     </row>
-    <row r="164" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
         <v>160001</v>
       </c>
@@ -21034,7 +21033,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="8"/>
     </row>
-    <row r="165" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
         <v>135095</v>
       </c>
@@ -21096,7 +21095,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="8"/>
     </row>
-    <row r="166" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3">
         <v>159019</v>
       </c>
@@ -21158,7 +21157,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="8"/>
     </row>
-    <row r="167" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
         <v>160013</v>
       </c>
@@ -21224,7 +21223,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="8"/>
     </row>
-    <row r="168" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
         <v>164008</v>
       </c>
@@ -21290,7 +21289,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="8"/>
     </row>
-    <row r="169" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
         <v>165004</v>
       </c>
@@ -21354,7 +21353,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="8"/>
     </row>
-    <row r="170" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3">
         <v>167013</v>
       </c>
@@ -21418,7 +21417,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="8"/>
     </row>
-    <row r="171" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
         <v>167020</v>
       </c>
@@ -21480,7 +21479,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="8"/>
     </row>
-    <row r="172" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
         <v>167029</v>
       </c>
@@ -21542,7 +21541,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="8"/>
     </row>
-    <row r="173" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
         <v>167032</v>
       </c>
@@ -21604,7 +21603,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="8"/>
     </row>
-    <row r="174" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
         <v>168006</v>
       </c>
@@ -21666,7 +21665,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="8"/>
     </row>
-    <row r="175" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
         <v>168012</v>
       </c>
@@ -21728,7 +21727,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="8"/>
     </row>
-    <row r="176" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
         <v>168024</v>
       </c>
@@ -21790,7 +21789,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="8"/>
     </row>
-    <row r="177" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3">
         <v>168029</v>
       </c>
@@ -21852,7 +21851,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="8"/>
     </row>
-    <row r="178" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>168030</v>
       </c>
@@ -21914,7 +21913,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="8"/>
     </row>
-    <row r="179" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
         <v>169006</v>
       </c>
@@ -21976,7 +21975,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="8"/>
     </row>
-    <row r="180" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
         <v>337004</v>
       </c>
@@ -22040,7 +22039,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="8"/>
     </row>
-    <row r="181" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
         <v>364002</v>
       </c>
@@ -22125,7 +22124,7 @@
         <v>40</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I182" s="3">
         <v>149024</v>
@@ -22187,7 +22186,7 @@
         <v>40</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I183" s="3">
         <v>149024</v>
@@ -22253,7 +22252,7 @@
         <v>793</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I184" s="3">
         <v>149024</v>
@@ -22315,7 +22314,7 @@
         <v>58</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I185" s="3">
         <v>149024</v>
@@ -22377,7 +22376,7 @@
         <v>71</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I186" s="3">
         <v>149024</v>
@@ -22439,7 +22438,7 @@
         <v>71</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I187" s="3">
         <v>149024</v>
@@ -22501,7 +22500,7 @@
         <v>122</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I188" s="3">
         <v>149024</v>
@@ -22563,7 +22562,7 @@
         <v>115</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>781</v>
+        <v>3445</v>
       </c>
       <c r="I189" s="3">
         <v>149024</v>
@@ -22602,7 +22601,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="8"/>
     </row>
-    <row r="190" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
         <v>268029</v>
       </c>
@@ -22664,7 +22663,7 @@
       </c>
       <c r="Z190" s="8"/>
     </row>
-    <row r="191" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3">
         <v>232027</v>
       </c>
@@ -22728,7 +22727,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="8"/>
     </row>
-    <row r="192" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
         <v>234092</v>
       </c>
@@ -22794,7 +22793,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="8"/>
     </row>
-    <row r="193" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
         <v>240029</v>
       </c>
@@ -22860,7 +22859,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="8"/>
     </row>
-    <row r="194" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3">
         <v>247012</v>
       </c>
@@ -22926,7 +22925,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="8"/>
     </row>
-    <row r="195" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
         <v>434007</v>
       </c>
@@ -22992,7 +22991,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="8"/>
     </row>
-    <row r="196" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3">
         <v>435004</v>
       </c>
@@ -23058,7 +23057,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="8"/>
     </row>
-    <row r="197" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3">
         <v>442002</v>
       </c>
@@ -23124,7 +23123,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="8"/>
     </row>
-    <row r="198" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3">
         <v>442007</v>
       </c>
@@ -23190,7 +23189,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="8"/>
     </row>
-    <row r="199" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3">
         <v>256029</v>
       </c>
@@ -23254,7 +23253,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="8"/>
     </row>
-    <row r="200" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3">
         <v>269012</v>
       </c>
@@ -23316,7 +23315,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="8"/>
     </row>
-    <row r="201" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
         <v>236012</v>
       </c>
@@ -23380,7 +23379,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="8"/>
     </row>
-    <row r="202" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
         <v>240005</v>
       </c>
@@ -23446,7 +23445,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="8"/>
     </row>
-    <row r="203" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3">
         <v>258001</v>
       </c>
@@ -23512,7 +23511,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="8"/>
     </row>
-    <row r="204" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
         <v>264090</v>
       </c>
@@ -23578,7 +23577,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="8"/>
     </row>
-    <row r="205" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3">
         <v>264066</v>
       </c>
@@ -23644,7 +23643,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="8"/>
     </row>
-    <row r="206" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3">
         <v>266086</v>
       </c>
@@ -23708,7 +23707,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="8"/>
     </row>
-    <row r="207" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3">
         <v>239024</v>
       </c>
@@ -23770,7 +23769,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="8"/>
     </row>
-    <row r="208" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3">
         <v>269009</v>
       </c>
@@ -23830,7 +23829,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="8"/>
     </row>
-    <row r="209" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3">
         <v>251010</v>
       </c>
@@ -23888,7 +23887,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="8"/>
     </row>
-    <row r="210" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3">
         <v>256050</v>
       </c>
@@ -23946,7 +23945,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="8"/>
     </row>
-    <row r="211" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3">
         <v>256051</v>
       </c>
@@ -24004,7 +24003,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="8"/>
     </row>
-    <row r="212" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3">
         <v>258031</v>
       </c>
@@ -24062,7 +24061,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="8"/>
     </row>
-    <row r="213" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3">
         <v>258041</v>
       </c>
@@ -24120,7 +24119,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="8"/>
     </row>
-    <row r="214" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3">
         <v>264067</v>
       </c>
@@ -24176,7 +24175,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="8"/>
     </row>
-    <row r="215" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3">
         <v>266047</v>
       </c>
@@ -24232,7 +24231,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="8"/>
     </row>
-    <row r="216" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3">
         <v>242029</v>
       </c>
@@ -24294,7 +24293,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="8"/>
     </row>
-    <row r="217" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3">
         <v>245012</v>
       </c>
@@ -24356,7 +24355,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="8"/>
     </row>
-    <row r="218" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3">
         <v>251041</v>
       </c>
@@ -24416,7 +24415,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="8"/>
     </row>
-    <row r="219" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3">
         <v>264070</v>
       </c>
@@ -24472,7 +24471,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="8"/>
     </row>
-    <row r="220" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3">
         <v>266061</v>
       </c>
@@ -24530,7 +24529,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="8"/>
     </row>
-    <row r="221" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3">
         <v>267007</v>
       </c>
@@ -24586,7 +24585,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="8"/>
     </row>
-    <row r="222" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3">
         <v>440018</v>
       </c>
@@ -24650,7 +24649,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="8"/>
     </row>
-    <row r="223" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3">
         <v>251012</v>
       </c>
@@ -24710,7 +24709,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="8"/>
     </row>
-    <row r="224" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3">
         <v>265032</v>
       </c>
@@ -24768,7 +24767,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="8"/>
     </row>
-    <row r="225" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3">
         <v>265053</v>
       </c>
@@ -24824,7 +24823,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="8"/>
     </row>
-    <row r="226" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3">
         <v>268090</v>
       </c>
@@ -24884,7 +24883,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="8"/>
     </row>
-    <row r="227" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
         <v>250042</v>
       </c>
@@ -24944,7 +24943,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="8"/>
     </row>
-    <row r="228" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3">
         <v>252013</v>
       </c>
@@ -25006,7 +25005,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="8"/>
     </row>
-    <row r="229" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3">
         <v>253045</v>
       </c>
@@ -25066,7 +25065,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="8"/>
     </row>
-    <row r="230" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3">
         <v>264063</v>
       </c>
@@ -25122,7 +25121,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="8"/>
     </row>
-    <row r="231" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3">
         <v>267008</v>
       </c>
@@ -25178,7 +25177,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="8"/>
     </row>
-    <row r="232" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3">
         <v>438016</v>
       </c>
@@ -25240,7 +25239,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="8"/>
     </row>
-    <row r="233" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3">
         <v>239006</v>
       </c>
@@ -25306,7 +25305,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="8"/>
     </row>
-    <row r="234" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3">
         <v>233034</v>
       </c>
@@ -25368,7 +25367,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="8"/>
     </row>
-    <row r="235" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3">
         <v>240034</v>
       </c>
@@ -25434,7 +25433,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="8"/>
     </row>
-    <row r="236" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3">
         <v>245015</v>
       </c>
@@ -25500,7 +25499,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="8"/>
     </row>
-    <row r="237" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3">
         <v>247008</v>
       </c>
@@ -25566,7 +25565,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="8"/>
     </row>
-    <row r="238" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3">
         <v>249019</v>
       </c>
@@ -25632,7 +25631,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="8"/>
     </row>
-    <row r="239" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3">
         <v>249046</v>
       </c>
@@ -25694,7 +25693,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="8"/>
     </row>
-    <row r="240" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3">
         <v>250016</v>
       </c>
@@ -25756,7 +25755,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="8"/>
     </row>
-    <row r="241" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3">
         <v>250017</v>
       </c>
@@ -25820,7 +25819,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="8"/>
     </row>
-    <row r="242" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3">
         <v>250059</v>
       </c>
@@ -25882,7 +25881,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="8"/>
     </row>
-    <row r="243" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3">
         <v>253003</v>
       </c>
@@ -25938,7 +25937,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="8"/>
     </row>
-    <row r="244" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3">
         <v>254055</v>
       </c>
@@ -26002,7 +26001,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="8"/>
     </row>
-    <row r="245" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3">
         <v>261028</v>
       </c>
@@ -26066,7 +26065,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="8"/>
     </row>
-    <row r="246" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3">
         <v>264007</v>
       </c>
@@ -26130,7 +26129,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="8"/>
     </row>
-    <row r="247" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3">
         <v>265019</v>
       </c>
@@ -26196,7 +26195,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="8"/>
     </row>
-    <row r="248" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3">
         <v>265047</v>
       </c>
@@ -26260,7 +26259,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="8"/>
     </row>
-    <row r="249" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3">
         <v>266010</v>
       </c>
@@ -26320,7 +26319,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="8"/>
     </row>
-    <row r="250" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3">
         <v>266021</v>
       </c>
@@ -26380,7 +26379,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="8"/>
     </row>
-    <row r="251" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3">
         <v>266052</v>
       </c>
@@ -26440,7 +26439,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="8"/>
     </row>
-    <row r="252" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3">
         <v>266060</v>
       </c>
@@ -26500,7 +26499,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="8"/>
     </row>
-    <row r="253" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3">
         <v>267047</v>
       </c>
@@ -26560,7 +26559,7 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="8"/>
     </row>
-    <row r="254" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3">
         <v>267048</v>
       </c>
@@ -26620,7 +26619,7 @@
       <c r="Y254" s="3"/>
       <c r="Z254" s="8"/>
     </row>
-    <row r="255" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3">
         <v>268013</v>
       </c>
@@ -26682,7 +26681,7 @@
       <c r="Y255" s="3"/>
       <c r="Z255" s="8"/>
     </row>
-    <row r="256" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3">
         <v>268056</v>
       </c>
@@ -26742,7 +26741,7 @@
       <c r="Y256" s="3"/>
       <c r="Z256" s="8"/>
     </row>
-    <row r="257" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3">
         <v>244005</v>
       </c>
@@ -26804,7 +26803,7 @@
       <c r="Y257" s="3"/>
       <c r="Z257" s="8"/>
     </row>
-    <row r="258" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3">
         <v>259005</v>
       </c>
@@ -26866,7 +26865,7 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="8"/>
     </row>
-    <row r="259" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3">
         <v>260003</v>
       </c>
@@ -26926,7 +26925,7 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="8"/>
     </row>
-    <row r="260" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3">
         <v>267003</v>
       </c>
@@ -26984,7 +26983,7 @@
       <c r="Y260" s="3"/>
       <c r="Z260" s="8"/>
     </row>
-    <row r="261" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3">
         <v>268083</v>
       </c>
@@ -27046,7 +27045,7 @@
       <c r="Y261" s="3"/>
       <c r="Z261" s="8"/>
     </row>
-    <row r="262" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3">
         <v>269016</v>
       </c>
@@ -27108,7 +27107,7 @@
       <c r="Y262" s="3"/>
       <c r="Z262" s="8"/>
     </row>
-    <row r="263" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3">
         <v>233010</v>
       </c>
@@ -27172,7 +27171,7 @@
       <c r="Y263" s="3"/>
       <c r="Z263" s="8"/>
     </row>
-    <row r="264" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3">
         <v>259013</v>
       </c>
@@ -27236,7 +27235,7 @@
       <c r="Y264" s="3"/>
       <c r="Z264" s="8"/>
     </row>
-    <row r="265" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3">
         <v>268091</v>
       </c>
@@ -27296,7 +27295,7 @@
       <c r="Y265" s="3"/>
       <c r="Z265" s="8"/>
     </row>
-    <row r="266" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3">
         <v>248035</v>
       </c>
@@ -27362,7 +27361,7 @@
       <c r="Y266" s="3"/>
       <c r="Z266" s="8"/>
     </row>
-    <row r="267" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3">
         <v>249010</v>
       </c>
@@ -27428,7 +27427,7 @@
       <c r="Y267" s="3"/>
       <c r="Z267" s="8"/>
     </row>
-    <row r="268" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3">
         <v>249053</v>
       </c>
@@ -27494,7 +27493,7 @@
       <c r="Y268" s="3"/>
       <c r="Z268" s="8"/>
     </row>
-    <row r="269" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3">
         <v>251019</v>
       </c>
@@ -27558,7 +27557,7 @@
       <c r="Y269" s="3"/>
       <c r="Z269" s="8"/>
     </row>
-    <row r="270" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3">
         <v>252004</v>
       </c>
@@ -27624,7 +27623,7 @@
       <c r="Y270" s="3"/>
       <c r="Z270" s="8"/>
     </row>
-    <row r="271" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3">
         <v>252009</v>
       </c>
@@ -27686,7 +27685,7 @@
       <c r="Y271" s="3"/>
       <c r="Z271" s="8"/>
     </row>
-    <row r="272" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3">
         <v>253037</v>
       </c>
@@ -27748,7 +27747,7 @@
       <c r="Y272" s="3"/>
       <c r="Z272" s="8"/>
     </row>
-    <row r="273" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3">
         <v>254018</v>
       </c>
@@ -27808,7 +27807,7 @@
       <c r="Y273" s="3"/>
       <c r="Z273" s="8"/>
     </row>
-    <row r="274" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3">
         <v>254035</v>
       </c>
@@ -27872,7 +27871,7 @@
       <c r="Y274" s="3"/>
       <c r="Z274" s="8"/>
     </row>
-    <row r="275" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3">
         <v>254049</v>
       </c>
@@ -27934,7 +27933,7 @@
       <c r="Y275" s="3"/>
       <c r="Z275" s="8"/>
     </row>
-    <row r="276" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3">
         <v>256032</v>
       </c>
@@ -27998,7 +27997,7 @@
       <c r="Y276" s="3"/>
       <c r="Z276" s="8"/>
     </row>
-    <row r="277" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3">
         <v>260018</v>
       </c>
@@ -28060,7 +28059,7 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="8"/>
     </row>
-    <row r="278" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3">
         <v>260045</v>
       </c>
@@ -28122,7 +28121,7 @@
       <c r="Y278" s="3"/>
       <c r="Z278" s="8"/>
     </row>
-    <row r="279" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3">
         <v>264040</v>
       </c>
@@ -28184,7 +28183,7 @@
       <c r="Y279" s="3"/>
       <c r="Z279" s="8"/>
     </row>
-    <row r="280" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3">
         <v>264091</v>
       </c>
@@ -28246,7 +28245,7 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="8"/>
     </row>
-    <row r="281" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3">
         <v>265012</v>
       </c>
@@ -28306,7 +28305,7 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="8"/>
     </row>
-    <row r="282" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3">
         <v>265040</v>
       </c>
@@ -28366,7 +28365,7 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="8"/>
     </row>
-    <row r="283" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3">
         <v>266050</v>
       </c>
@@ -28430,7 +28429,7 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="8"/>
     </row>
-    <row r="284" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3">
         <v>266072</v>
       </c>
@@ -28490,7 +28489,7 @@
       <c r="Y284" s="3"/>
       <c r="Z284" s="8"/>
     </row>
-    <row r="285" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3">
         <v>267022</v>
       </c>
@@ -28550,7 +28549,7 @@
       <c r="Y285" s="3"/>
       <c r="Z285" s="8"/>
     </row>
-    <row r="286" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3">
         <v>267035</v>
       </c>
@@ -28612,7 +28611,7 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="8"/>
     </row>
-    <row r="287" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3">
         <v>267074</v>
       </c>
@@ -28674,7 +28673,7 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="8"/>
     </row>
-    <row r="288" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3">
         <v>267083</v>
       </c>
@@ -28734,7 +28733,7 @@
       <c r="Y288" s="3"/>
       <c r="Z288" s="8"/>
     </row>
-    <row r="289" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3">
         <v>267099</v>
       </c>
@@ -28794,7 +28793,7 @@
       <c r="Y289" s="3"/>
       <c r="Z289" s="8"/>
     </row>
-    <row r="290" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3">
         <v>268012</v>
       </c>
@@ -28856,7 +28855,7 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="8"/>
     </row>
-    <row r="291" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3">
         <v>268042</v>
       </c>
@@ -28916,7 +28915,7 @@
       <c r="Y291" s="3"/>
       <c r="Z291" s="8"/>
     </row>
-    <row r="292" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3">
         <v>268073</v>
       </c>
@@ -28976,7 +28975,7 @@
       <c r="Y292" s="3"/>
       <c r="Z292" s="8"/>
     </row>
-    <row r="293" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3">
         <v>269011</v>
       </c>
@@ -29038,7 +29037,7 @@
       <c r="Y293" s="3"/>
       <c r="Z293" s="8"/>
     </row>
-    <row r="294" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3">
         <v>269024</v>
       </c>
@@ -29098,7 +29097,7 @@
       <c r="Y294" s="3"/>
       <c r="Z294" s="8"/>
     </row>
-    <row r="295" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3">
         <v>238030</v>
       </c>
@@ -29164,7 +29163,7 @@
       <c r="Y295" s="3"/>
       <c r="Z295" s="8"/>
     </row>
-    <row r="296" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3">
         <v>240018</v>
       </c>
@@ -29228,7 +29227,7 @@
       <c r="Y296" s="3"/>
       <c r="Z296" s="8"/>
     </row>
-    <row r="297" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3">
         <v>251006</v>
       </c>
@@ -29294,7 +29293,7 @@
       <c r="Y297" s="3"/>
       <c r="Z297" s="8"/>
     </row>
-    <row r="298" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3">
         <v>251025</v>
       </c>
@@ -29358,7 +29357,7 @@
       <c r="Y298" s="3"/>
       <c r="Z298" s="8"/>
     </row>
-    <row r="299" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3">
         <v>252027</v>
       </c>
@@ -29424,7 +29423,7 @@
       <c r="Y299" s="3"/>
       <c r="Z299" s="8"/>
     </row>
-    <row r="300" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3">
         <v>253042</v>
       </c>
@@ -29488,7 +29487,7 @@
       <c r="Y300" s="3"/>
       <c r="Z300" s="8"/>
     </row>
-    <row r="301" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3">
         <v>256036</v>
       </c>
@@ -29550,7 +29549,7 @@
       <c r="Y301" s="3"/>
       <c r="Z301" s="8"/>
     </row>
-    <row r="302" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3">
         <v>256038</v>
       </c>
@@ -29612,7 +29611,7 @@
       <c r="Y302" s="3"/>
       <c r="Z302" s="8"/>
     </row>
-    <row r="303" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3">
         <v>266057</v>
       </c>
@@ -29676,7 +29675,7 @@
       <c r="Y303" s="3"/>
       <c r="Z303" s="8"/>
     </row>
-    <row r="304" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3">
         <v>266065</v>
       </c>
@@ -29736,7 +29735,7 @@
       <c r="Y304" s="3"/>
       <c r="Z304" s="8"/>
     </row>
-    <row r="305" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3">
         <v>246004</v>
       </c>
@@ -29802,7 +29801,7 @@
       <c r="Y305" s="3"/>
       <c r="Z305" s="8"/>
     </row>
-    <row r="306" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3">
         <v>256014</v>
       </c>
@@ -29868,7 +29867,7 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="8"/>
     </row>
-    <row r="307" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3">
         <v>244028</v>
       </c>
@@ -29932,7 +29931,7 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="8"/>
     </row>
-    <row r="308" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3">
         <v>251048</v>
       </c>
@@ -29996,7 +29995,7 @@
       <c r="Y308" s="3"/>
       <c r="Z308" s="8"/>
     </row>
-    <row r="309" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3">
         <v>255003</v>
       </c>
@@ -30058,7 +30057,7 @@
       <c r="Y309" s="3"/>
       <c r="Z309" s="8"/>
     </row>
-    <row r="310" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3">
         <v>257021</v>
       </c>
@@ -30122,7 +30121,7 @@
       <c r="Y310" s="3"/>
       <c r="Z310" s="8"/>
     </row>
-    <row r="311" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3">
         <v>258035</v>
       </c>
@@ -30184,7 +30183,7 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="8"/>
     </row>
-    <row r="312" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3">
         <v>260029</v>
       </c>
@@ -30244,7 +30243,7 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="8"/>
     </row>
-    <row r="313" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3">
         <v>264019</v>
       </c>
@@ -30304,7 +30303,7 @@
       <c r="Y313" s="3"/>
       <c r="Z313" s="8"/>
     </row>
-    <row r="314" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3">
         <v>264039</v>
       </c>
@@ -30366,7 +30365,7 @@
       <c r="Y314" s="3"/>
       <c r="Z314" s="8"/>
     </row>
-    <row r="315" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3">
         <v>265043</v>
       </c>
@@ -30422,7 +30421,7 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="8"/>
     </row>
-    <row r="316" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3">
         <v>265058</v>
       </c>
@@ -30478,7 +30477,7 @@
       <c r="Y316" s="3"/>
       <c r="Z316" s="8"/>
     </row>
-    <row r="317" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3">
         <v>267017</v>
       </c>
@@ -30534,7 +30533,7 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="8"/>
     </row>
-    <row r="318" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3">
         <v>267080</v>
       </c>
@@ -30590,7 +30589,7 @@
       <c r="Y318" s="3"/>
       <c r="Z318" s="8"/>
     </row>
-    <row r="319" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3">
         <v>243010</v>
       </c>
@@ -30652,7 +30651,7 @@
       <c r="Y319" s="3"/>
       <c r="Z319" s="8"/>
     </row>
-    <row r="320" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3">
         <v>255004</v>
       </c>
@@ -30714,7 +30713,7 @@
       <c r="Y320" s="3"/>
       <c r="Z320" s="8"/>
     </row>
-    <row r="321" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3">
         <v>258022</v>
       </c>
@@ -30776,7 +30775,7 @@
       <c r="Y321" s="3"/>
       <c r="Z321" s="8"/>
     </row>
-    <row r="322" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3">
         <v>265023</v>
       </c>
@@ -30832,7 +30831,7 @@
       <c r="Y322" s="3"/>
       <c r="Z322" s="8"/>
     </row>
-    <row r="323" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3">
         <v>267005</v>
       </c>
@@ -30888,7 +30887,7 @@
       <c r="Y323" s="3"/>
       <c r="Z323" s="8"/>
     </row>
-    <row r="324" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3">
         <v>267060</v>
       </c>
@@ -30948,7 +30947,7 @@
       <c r="Y324" s="3"/>
       <c r="Z324" s="8"/>
     </row>
-    <row r="325" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3">
         <v>439003</v>
       </c>
@@ -31010,7 +31009,7 @@
       <c r="Y325" s="3"/>
       <c r="Z325" s="8"/>
     </row>
-    <row r="326" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3">
         <v>244011</v>
       </c>
@@ -31072,7 +31071,7 @@
       <c r="Y326" s="3"/>
       <c r="Z326" s="8"/>
     </row>
-    <row r="327" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3">
         <v>247019</v>
       </c>
@@ -31136,7 +31135,7 @@
       <c r="Y327" s="3"/>
       <c r="Z327" s="8"/>
     </row>
-    <row r="328" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3">
         <v>252038</v>
       </c>
@@ -31200,7 +31199,7 @@
       <c r="Y328" s="3"/>
       <c r="Z328" s="8"/>
     </row>
-    <row r="329" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3">
         <v>259016</v>
       </c>
@@ -31262,7 +31261,7 @@
       <c r="Y329" s="3"/>
       <c r="Z329" s="8"/>
     </row>
-    <row r="330" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3">
         <v>264044</v>
       </c>
@@ -31324,7 +31323,7 @@
       <c r="Y330" s="3"/>
       <c r="Z330" s="8"/>
     </row>
-    <row r="331" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3">
         <v>264074</v>
       </c>
@@ -31382,7 +31381,7 @@
       <c r="Y331" s="3"/>
       <c r="Z331" s="8"/>
     </row>
-    <row r="332" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3">
         <v>264075</v>
       </c>
@@ -31440,7 +31439,7 @@
       <c r="Y332" s="3"/>
       <c r="Z332" s="8"/>
     </row>
-    <row r="333" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3">
         <v>265110</v>
       </c>
@@ -31496,7 +31495,7 @@
       <c r="Y333" s="3"/>
       <c r="Z333" s="8"/>
     </row>
-    <row r="334" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3">
         <v>266013</v>
       </c>
@@ -31552,7 +31551,7 @@
       <c r="Y334" s="3"/>
       <c r="Z334" s="8"/>
     </row>
-    <row r="335" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3">
         <v>267014</v>
       </c>
@@ -31608,7 +31607,7 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="8"/>
     </row>
-    <row r="336" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3">
         <v>267015</v>
       </c>
@@ -31664,7 +31663,7 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="8"/>
     </row>
-    <row r="337" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3">
         <v>267086</v>
       </c>
@@ -31724,7 +31723,7 @@
       <c r="Y337" s="3"/>
       <c r="Z337" s="8"/>
     </row>
-    <row r="338" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3">
         <v>268030</v>
       </c>
@@ -31784,7 +31783,7 @@
       <c r="Y338" s="3"/>
       <c r="Z338" s="8"/>
     </row>
-    <row r="339" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3">
         <v>268031</v>
       </c>
@@ -31844,7 +31843,7 @@
       <c r="Y339" s="3"/>
       <c r="Z339" s="8"/>
     </row>
-    <row r="340" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3">
         <v>268041</v>
       </c>
@@ -31904,7 +31903,7 @@
       <c r="Y340" s="3"/>
       <c r="Z340" s="8"/>
     </row>
-    <row r="341" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3">
         <v>257019</v>
       </c>
@@ -31966,7 +31965,7 @@
       <c r="Y341" s="3"/>
       <c r="Z341" s="8"/>
     </row>
-    <row r="342" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3">
         <v>242025</v>
       </c>
@@ -32032,7 +32031,7 @@
       <c r="Y342" s="3"/>
       <c r="Z342" s="8"/>
     </row>
-    <row r="343" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3">
         <v>243003</v>
       </c>
@@ -32098,7 +32097,7 @@
       <c r="Y343" s="3"/>
       <c r="Z343" s="8"/>
     </row>
-    <row r="344" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3">
         <v>247020</v>
       </c>
@@ -32160,7 +32159,7 @@
       <c r="Y344" s="3"/>
       <c r="Z344" s="8"/>
     </row>
-    <row r="345" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3">
         <v>249094</v>
       </c>
@@ -32224,7 +32223,7 @@
       <c r="Y345" s="3"/>
       <c r="Z345" s="8"/>
     </row>
-    <row r="346" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3">
         <v>257018</v>
       </c>
@@ -32288,7 +32287,7 @@
       <c r="Y346" s="3"/>
       <c r="Z346" s="8"/>
     </row>
-    <row r="347" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3">
         <v>259020</v>
       </c>
@@ -32350,7 +32349,7 @@
       <c r="Y347" s="3"/>
       <c r="Z347" s="8"/>
     </row>
-    <row r="348" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3">
         <v>443003</v>
       </c>
@@ -32416,7 +32415,7 @@
       <c r="Y348" s="3"/>
       <c r="Z348" s="8"/>
     </row>
-    <row r="349" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3">
         <v>467002</v>
       </c>
@@ -32472,7 +32471,7 @@
       <c r="Y349" s="3"/>
       <c r="Z349" s="8"/>
     </row>
-    <row r="350" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3">
         <v>467003</v>
       </c>
@@ -32528,7 +32527,7 @@
       <c r="Y350" s="3"/>
       <c r="Z350" s="8"/>
     </row>
-    <row r="351" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3">
         <v>254057</v>
       </c>
@@ -32594,7 +32593,7 @@
       <c r="Y351" s="3"/>
       <c r="Z351" s="8"/>
     </row>
-    <row r="352" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3">
         <v>237011</v>
       </c>
@@ -32660,7 +32659,7 @@
       <c r="Y352" s="3"/>
       <c r="Z352" s="8"/>
     </row>
-    <row r="353" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3">
         <v>249058</v>
       </c>
@@ -32722,7 +32721,7 @@
       <c r="Y353" s="3"/>
       <c r="Z353" s="8"/>
     </row>
-    <row r="354" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3">
         <v>254037</v>
       </c>
@@ -32784,7 +32783,7 @@
       <c r="Y354" s="3"/>
       <c r="Z354" s="8"/>
     </row>
-    <row r="355" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3">
         <v>261014</v>
       </c>
@@ -32844,7 +32843,7 @@
       <c r="Y355" s="3"/>
       <c r="Z355" s="8"/>
     </row>
-    <row r="356" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3">
         <v>265066</v>
       </c>
@@ -32904,7 +32903,7 @@
       <c r="Y356" s="3"/>
       <c r="Z356" s="8"/>
     </row>
-    <row r="357" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3">
         <v>266031</v>
       </c>
@@ -32964,7 +32963,7 @@
       <c r="Y357" s="3"/>
       <c r="Z357" s="8"/>
     </row>
-    <row r="358" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3">
         <v>268088</v>
       </c>
@@ -33024,7 +33023,7 @@
       <c r="Y358" s="3"/>
       <c r="Z358" s="8"/>
     </row>
-    <row r="359" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3">
         <v>236069</v>
       </c>
@@ -33088,7 +33087,7 @@
       <c r="Y359" s="3"/>
       <c r="Z359" s="8"/>
     </row>
-    <row r="360" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3">
         <v>245001</v>
       </c>
@@ -33150,7 +33149,7 @@
       <c r="Y360" s="3"/>
       <c r="Z360" s="8"/>
     </row>
-    <row r="361" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3">
         <v>245006</v>
       </c>
@@ -33214,7 +33213,7 @@
       <c r="Y361" s="3"/>
       <c r="Z361" s="8"/>
     </row>
-    <row r="362" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3">
         <v>248043</v>
       </c>
@@ -33276,7 +33275,7 @@
       <c r="Y362" s="3"/>
       <c r="Z362" s="8"/>
     </row>
-    <row r="363" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3">
         <v>249036</v>
       </c>
@@ -33338,7 +33337,7 @@
       <c r="Y363" s="3"/>
       <c r="Z363" s="8"/>
     </row>
-    <row r="364" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3">
         <v>256042</v>
       </c>
@@ -33400,7 +33399,7 @@
       <c r="Y364" s="3"/>
       <c r="Z364" s="8"/>
     </row>
-    <row r="365" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3">
         <v>264008</v>
       </c>
@@ -33464,7 +33463,7 @@
       <c r="Y365" s="3"/>
       <c r="Z365" s="8"/>
     </row>
-    <row r="366" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3">
         <v>265103</v>
       </c>
@@ -33524,7 +33523,7 @@
       <c r="Y366" s="3"/>
       <c r="Z366" s="8"/>
     </row>
-    <row r="367" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3">
         <v>266090</v>
       </c>
@@ -33586,7 +33585,7 @@
       <c r="Y367" s="3"/>
       <c r="Z367" s="8"/>
     </row>
-    <row r="368" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3">
         <v>268074</v>
       </c>
@@ -33648,7 +33647,7 @@
       <c r="Y368" s="3"/>
       <c r="Z368" s="8"/>
     </row>
-    <row r="369" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3">
         <v>265128</v>
       </c>
@@ -33708,7 +33707,7 @@
       <c r="Y369" s="3"/>
       <c r="Z369" s="8"/>
     </row>
-    <row r="370" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3">
         <v>266083</v>
       </c>
@@ -33764,7 +33763,7 @@
       <c r="Y370" s="3"/>
       <c r="Z370" s="8"/>
     </row>
-    <row r="371" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3">
         <v>267052</v>
       </c>
@@ -33820,7 +33819,7 @@
       <c r="Y371" s="3"/>
       <c r="Z371" s="8"/>
     </row>
-    <row r="372" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3">
         <v>268028</v>
       </c>
@@ -33880,7 +33879,7 @@
       <c r="Y372" s="3"/>
       <c r="Z372" s="8"/>
     </row>
-    <row r="373" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3">
         <v>268053</v>
       </c>
@@ -33940,7 +33939,7 @@
       <c r="Y373" s="3"/>
       <c r="Z373" s="8"/>
     </row>
-    <row r="374" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3">
         <v>268062</v>
       </c>
@@ -34000,7 +33999,7 @@
       <c r="Y374" s="3"/>
       <c r="Z374" s="8"/>
     </row>
-    <row r="375" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3">
         <v>268076</v>
       </c>
@@ -34060,7 +34059,7 @@
       <c r="Y375" s="3"/>
       <c r="Z375" s="8"/>
     </row>
-    <row r="376" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3">
         <v>268092</v>
       </c>
@@ -34120,7 +34119,7 @@
       <c r="Y376" s="3"/>
       <c r="Z376" s="8"/>
     </row>
-    <row r="377" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3">
         <v>269003</v>
       </c>
@@ -34180,7 +34179,7 @@
       <c r="Y377" s="3"/>
       <c r="Z377" s="8"/>
     </row>
-    <row r="378" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3">
         <v>269006</v>
       </c>
@@ -34240,7 +34239,7 @@
       <c r="Y378" s="3"/>
       <c r="Z378" s="8"/>
     </row>
-    <row r="379" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3">
         <v>269018</v>
       </c>
@@ -34300,7 +34299,7 @@
       <c r="Y379" s="3"/>
       <c r="Z379" s="8"/>
     </row>
-    <row r="380" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3">
         <v>269019</v>
       </c>
@@ -34360,7 +34359,7 @@
       <c r="Y380" s="3"/>
       <c r="Z380" s="8"/>
     </row>
-    <row r="381" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3">
         <v>249086</v>
       </c>
@@ -34422,7 +34421,7 @@
       <c r="Y381" s="3"/>
       <c r="Z381" s="8"/>
     </row>
-    <row r="382" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3">
         <v>267096</v>
       </c>
@@ -34484,7 +34483,7 @@
       <c r="Y382" s="3"/>
       <c r="Z382" s="8"/>
     </row>
-    <row r="383" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3">
         <v>250062</v>
       </c>
@@ -34550,7 +34549,7 @@
       <c r="Y383" s="3"/>
       <c r="Z383" s="8"/>
     </row>
-    <row r="384" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3">
         <v>256015</v>
       </c>
@@ -34612,7 +34611,7 @@
       <c r="Y384" s="3"/>
       <c r="Z384" s="8"/>
     </row>
-    <row r="385" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3">
         <v>256016</v>
       </c>
@@ -34676,7 +34675,7 @@
       <c r="Y385" s="3"/>
       <c r="Z385" s="8"/>
     </row>
-    <row r="386" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3">
         <v>259024</v>
       </c>
@@ -34740,7 +34739,7 @@
       <c r="Y386" s="3"/>
       <c r="Z386" s="8"/>
     </row>
-    <row r="387" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3">
         <v>264045</v>
       </c>
@@ -34800,7 +34799,7 @@
       <c r="Y387" s="3"/>
       <c r="Z387" s="8"/>
     </row>
-    <row r="388" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3">
         <v>265111</v>
       </c>
@@ -34860,7 +34859,7 @@
       <c r="Y388" s="3"/>
       <c r="Z388" s="8"/>
     </row>
-    <row r="389" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3">
         <v>265124</v>
       </c>
@@ -34920,7 +34919,7 @@
       <c r="Y389" s="3"/>
       <c r="Z389" s="8"/>
     </row>
-    <row r="390" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3">
         <v>266030</v>
       </c>
@@ -34980,7 +34979,7 @@
       <c r="Y390" s="3"/>
       <c r="Z390" s="8"/>
     </row>
-    <row r="391" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3">
         <v>251029</v>
       </c>
@@ -35042,7 +35041,7 @@
       <c r="Y391" s="3"/>
       <c r="Z391" s="8"/>
     </row>
-    <row r="392" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3">
         <v>256004</v>
       </c>
@@ -35104,7 +35103,7 @@
       <c r="Y392" s="3"/>
       <c r="Z392" s="8"/>
     </row>
-    <row r="393" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3">
         <v>260016</v>
       </c>
@@ -35164,7 +35163,7 @@
       <c r="Y393" s="3"/>
       <c r="Z393" s="8"/>
     </row>
-    <row r="394" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3">
         <v>264022</v>
       </c>
@@ -35224,7 +35223,7 @@
       <c r="Y394" s="3"/>
       <c r="Z394" s="8"/>
     </row>
-    <row r="395" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3">
         <v>264083</v>
       </c>
@@ -35288,7 +35287,7 @@
       <c r="Y395" s="3"/>
       <c r="Z395" s="8"/>
     </row>
-    <row r="396" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3">
         <v>265010</v>
       </c>
@@ -35348,7 +35347,7 @@
       <c r="Y396" s="3"/>
       <c r="Z396" s="8"/>
     </row>
-    <row r="397" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3">
         <v>265013</v>
       </c>
@@ -35410,7 +35409,7 @@
       <c r="Y397" s="3"/>
       <c r="Z397" s="8"/>
     </row>
-    <row r="398" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3">
         <v>268038</v>
       </c>
@@ -35470,7 +35469,7 @@
       <c r="Y398" s="3"/>
       <c r="Z398" s="8"/>
     </row>
-    <row r="399" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3">
         <v>251050</v>
       </c>
@@ -35534,7 +35533,7 @@
       <c r="Y399" s="3"/>
       <c r="Z399" s="8"/>
     </row>
-    <row r="400" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3">
         <v>251058</v>
       </c>
@@ -35596,7 +35595,7 @@
       <c r="Y400" s="3"/>
       <c r="Z400" s="8"/>
     </row>
-    <row r="401" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3">
         <v>251062</v>
       </c>
@@ -35658,7 +35657,7 @@
       <c r="Y401" s="3"/>
       <c r="Z401" s="8"/>
     </row>
-    <row r="402" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3">
         <v>259022</v>
       </c>
@@ -35722,7 +35721,7 @@
       <c r="Y402" s="3"/>
       <c r="Z402" s="8"/>
     </row>
-    <row r="403" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3">
         <v>259038</v>
       </c>
@@ -35784,7 +35783,7 @@
       <c r="Y403" s="3"/>
       <c r="Z403" s="8"/>
     </row>
-    <row r="404" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3">
         <v>264048</v>
       </c>
@@ -35844,7 +35843,7 @@
       <c r="Y404" s="3"/>
       <c r="Z404" s="8"/>
     </row>
-    <row r="405" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3">
         <v>264051</v>
       </c>
@@ -35904,7 +35903,7 @@
       <c r="Y405" s="3"/>
       <c r="Z405" s="8"/>
     </row>
-    <row r="406" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3">
         <v>264089</v>
       </c>
@@ -35964,7 +35963,7 @@
       <c r="Y406" s="3"/>
       <c r="Z406" s="8"/>
     </row>
-    <row r="407" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3">
         <v>265024</v>
       </c>
@@ -36024,7 +36023,7 @@
       <c r="Y407" s="3"/>
       <c r="Z407" s="8"/>
     </row>
-    <row r="408" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3">
         <v>265061</v>
       </c>
@@ -36084,7 +36083,7 @@
       <c r="Y408" s="3"/>
       <c r="Z408" s="8"/>
     </row>
-    <row r="409" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3">
         <v>265076</v>
       </c>
@@ -36144,7 +36143,7 @@
       <c r="Y409" s="3"/>
       <c r="Z409" s="8"/>
     </row>
-    <row r="410" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3">
         <v>266037</v>
       </c>
@@ -36204,7 +36203,7 @@
       <c r="Y410" s="3"/>
       <c r="Z410" s="8"/>
     </row>
-    <row r="411" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3">
         <v>441005</v>
       </c>
@@ -36270,7 +36269,7 @@
       <c r="Y411" s="3"/>
       <c r="Z411" s="8"/>
     </row>
-    <row r="412" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3">
         <v>268037</v>
       </c>
@@ -36330,7 +36329,7 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="8"/>
     </row>
-    <row r="413" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3">
         <v>268086</v>
       </c>
@@ -36390,7 +36389,7 @@
       <c r="Y413" s="3"/>
       <c r="Z413" s="8"/>
     </row>
-    <row r="414" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3">
         <v>250022</v>
       </c>
@@ -36454,7 +36453,7 @@
       <c r="Y414" s="3"/>
       <c r="Z414" s="8"/>
     </row>
-    <row r="415" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3">
         <v>251028</v>
       </c>
@@ -36516,7 +36515,7 @@
       <c r="Y415" s="3"/>
       <c r="Z415" s="8"/>
     </row>
-    <row r="416" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3">
         <v>253023</v>
       </c>
@@ -36578,7 +36577,7 @@
       <c r="Y416" s="3"/>
       <c r="Z416" s="8"/>
     </row>
-    <row r="417" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3">
         <v>264084</v>
       </c>
@@ -36640,7 +36639,7 @@
       <c r="Y417" s="3"/>
       <c r="Z417" s="8"/>
     </row>
-    <row r="418" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3">
         <v>265127</v>
       </c>
@@ -36700,7 +36699,7 @@
       <c r="Y418" s="3"/>
       <c r="Z418" s="8"/>
     </row>
-    <row r="419" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3">
         <v>266016</v>
       </c>
@@ -36760,7 +36759,7 @@
       <c r="Y419" s="3"/>
       <c r="Z419" s="8"/>
     </row>
-    <row r="420" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3">
         <v>247007</v>
       </c>
@@ -36822,7 +36821,7 @@
       <c r="Y420" s="3"/>
       <c r="Z420" s="8"/>
     </row>
-    <row r="421" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3">
         <v>251002</v>
       </c>
@@ -36886,7 +36885,7 @@
       <c r="Y421" s="3"/>
       <c r="Z421" s="8"/>
     </row>
-    <row r="422" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3">
         <v>251023</v>
       </c>
@@ -36948,7 +36947,7 @@
       <c r="Y422" s="3"/>
       <c r="Z422" s="8"/>
     </row>
-    <row r="423" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3">
         <v>262008</v>
       </c>
@@ -37010,7 +37009,7 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="8"/>
     </row>
-    <row r="424" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3">
         <v>265063</v>
       </c>
@@ -37070,7 +37069,7 @@
       <c r="Y424" s="3"/>
       <c r="Z424" s="8"/>
     </row>
-    <row r="425" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3">
         <v>266002</v>
       </c>
@@ -37130,7 +37129,7 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="8"/>
     </row>
-    <row r="426" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3">
         <v>246013</v>
       </c>
@@ -37192,7 +37191,7 @@
       <c r="Y426" s="3"/>
       <c r="Z426" s="8"/>
     </row>
-    <row r="427" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3">
         <v>249048</v>
       </c>
@@ -37258,7 +37257,7 @@
       <c r="Y427" s="3"/>
       <c r="Z427" s="8"/>
     </row>
-    <row r="428" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3">
         <v>250010</v>
       </c>
@@ -37320,7 +37319,7 @@
       <c r="Y428" s="3"/>
       <c r="Z428" s="8"/>
     </row>
-    <row r="429" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3">
         <v>251065</v>
       </c>
@@ -37382,7 +37381,7 @@
       <c r="Y429" s="3"/>
       <c r="Z429" s="8"/>
     </row>
-    <row r="430" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3">
         <v>265126</v>
       </c>
@@ -37446,7 +37445,7 @@
       <c r="Y430" s="3"/>
       <c r="Z430" s="8"/>
     </row>
-    <row r="431" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3">
         <v>267043</v>
       </c>
@@ -37506,7 +37505,7 @@
       <c r="Y431" s="3"/>
       <c r="Z431" s="8"/>
     </row>
-    <row r="432" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3">
         <v>267072</v>
       </c>
@@ -37568,7 +37567,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="8"/>
     </row>
-    <row r="433" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3">
         <v>467004</v>
       </c>
@@ -37628,7 +37627,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="8"/>
     </row>
-    <row r="434" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3">
         <v>467005</v>
       </c>
@@ -37688,7 +37687,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="8"/>
     </row>
-    <row r="435" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3">
         <v>242032</v>
       </c>
@@ -37754,7 +37753,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="8"/>
     </row>
-    <row r="436" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3">
         <v>266091</v>
       </c>
@@ -37818,7 +37817,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="8"/>
     </row>
-    <row r="437" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3">
         <v>268052</v>
       </c>
@@ -37880,7 +37879,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="8"/>
     </row>
-    <row r="438" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3">
         <v>255016</v>
       </c>
@@ -37946,7 +37945,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="8"/>
     </row>
-    <row r="439" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3">
         <v>269022</v>
       </c>
@@ -38008,7 +38007,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="8"/>
     </row>
-    <row r="440" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3">
         <v>236082</v>
       </c>
@@ -38072,7 +38071,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="8"/>
     </row>
-    <row r="441" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3">
         <v>244006</v>
       </c>
@@ -38130,7 +38129,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="8"/>
     </row>
-    <row r="442" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3">
         <v>251067</v>
       </c>
@@ -38194,7 +38193,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="8"/>
     </row>
-    <row r="443" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3">
         <v>257014</v>
       </c>
@@ -38250,7 +38249,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="8"/>
     </row>
-    <row r="444" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3">
         <v>258021</v>
       </c>
@@ -38308,7 +38307,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="8"/>
     </row>
-    <row r="445" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3">
         <v>265027</v>
       </c>
@@ -38366,7 +38365,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="8"/>
     </row>
-    <row r="446" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3">
         <v>265039</v>
       </c>
@@ -38424,7 +38423,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="8"/>
     </row>
-    <row r="447" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3">
         <v>265050</v>
       </c>
@@ -38480,7 +38479,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="8"/>
     </row>
-    <row r="448" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3">
         <v>265056</v>
       </c>
@@ -38538,7 +38537,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="8"/>
     </row>
-    <row r="449" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3">
         <v>265089</v>
       </c>
@@ -38594,7 +38593,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="8"/>
     </row>
-    <row r="450" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3">
         <v>265094</v>
       </c>
@@ -38652,7 +38651,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="8"/>
     </row>
-    <row r="451" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3">
         <v>265129</v>
       </c>
@@ -38710,7 +38709,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="8"/>
     </row>
-    <row r="452" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3">
         <v>265133</v>
       </c>
@@ -38766,7 +38765,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="8"/>
     </row>
-    <row r="453" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3">
         <v>266068</v>
       </c>
@@ -38822,7 +38821,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="8"/>
     </row>
-    <row r="454" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3">
         <v>267088</v>
       </c>
@@ -38878,7 +38877,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="8"/>
     </row>
-    <row r="455" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3">
         <v>267104</v>
       </c>
@@ -38934,7 +38933,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="8"/>
     </row>
-    <row r="456" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3">
         <v>268009</v>
       </c>
@@ -38990,7 +38989,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="8"/>
     </row>
-    <row r="457" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3">
         <v>268070</v>
       </c>
@@ -39050,7 +39049,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="8"/>
     </row>
-    <row r="458" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3">
         <v>268087</v>
       </c>
@@ -39110,7 +39109,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="8"/>
     </row>
-    <row r="459" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3">
         <v>257007</v>
       </c>
@@ -39166,7 +39165,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="8"/>
     </row>
-    <row r="460" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3">
         <v>257008</v>
       </c>
@@ -39222,7 +39221,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="8"/>
     </row>
-    <row r="461" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3">
         <v>257009</v>
       </c>
@@ -39286,7 +39285,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="8"/>
     </row>
-    <row r="462" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3">
         <v>264011</v>
       </c>
@@ -39344,7 +39343,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="8"/>
     </row>
-    <row r="463" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3">
         <v>268055</v>
       </c>
@@ -39404,7 +39403,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="8"/>
     </row>
-    <row r="464" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3">
         <v>442009</v>
       </c>
@@ -39462,7 +39461,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="8"/>
     </row>
-    <row r="465" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3">
         <v>239036</v>
       </c>
@@ -39526,7 +39525,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="8"/>
     </row>
-    <row r="466" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3">
         <v>245007</v>
       </c>
@@ -39584,7 +39583,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="8"/>
     </row>
-    <row r="467" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3">
         <v>245028</v>
       </c>
@@ -39642,7 +39641,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="8"/>
     </row>
-    <row r="468" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3">
         <v>245029</v>
       </c>
@@ -39700,7 +39699,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="8"/>
     </row>
-    <row r="469" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3">
         <v>249026</v>
       </c>
@@ -39758,7 +39757,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="8"/>
     </row>
-    <row r="470" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3">
         <v>251015</v>
       </c>
@@ -39818,7 +39817,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="8"/>
     </row>
-    <row r="471" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3">
         <v>251020</v>
       </c>
@@ -39878,7 +39877,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="8"/>
     </row>
-    <row r="472" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3">
         <v>253009</v>
       </c>
@@ -39936,7 +39935,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="8"/>
     </row>
-    <row r="473" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3">
         <v>254024</v>
       </c>
@@ -39992,7 +39991,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="8"/>
     </row>
-    <row r="474" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3">
         <v>256056</v>
       </c>
@@ -40054,7 +40053,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="8"/>
     </row>
-    <row r="475" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3">
         <v>257015</v>
       </c>
@@ -40110,7 +40109,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="8"/>
     </row>
-    <row r="476" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3">
         <v>257035</v>
       </c>
@@ -40168,7 +40167,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="8"/>
     </row>
-    <row r="477" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3">
         <v>258004</v>
       </c>
@@ -40230,7 +40229,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="8"/>
     </row>
-    <row r="478" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3">
         <v>260024</v>
       </c>
@@ -40286,7 +40285,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="8"/>
     </row>
-    <row r="479" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3">
         <v>260038</v>
       </c>
@@ -40346,7 +40345,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="8"/>
     </row>
-    <row r="480" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3">
         <v>264025</v>
       </c>
@@ -40402,7 +40401,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="8"/>
     </row>
-    <row r="481" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3">
         <v>265099</v>
       </c>
@@ -40458,7 +40457,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="8"/>
     </row>
-    <row r="482" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3">
         <v>269004</v>
       </c>
@@ -40518,7 +40517,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="8"/>
     </row>
-    <row r="483" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3">
         <v>253014</v>
       </c>
@@ -40584,7 +40583,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="8"/>
     </row>
-    <row r="484" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3">
         <v>237017</v>
       </c>
@@ -40648,7 +40647,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="8"/>
     </row>
-    <row r="485" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3">
         <v>241015</v>
       </c>
@@ -40712,7 +40711,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="8"/>
     </row>
-    <row r="486" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3">
         <v>250056</v>
       </c>
@@ -40776,7 +40775,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="8"/>
     </row>
-    <row r="487" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3">
         <v>254061</v>
       </c>
@@ -40836,7 +40835,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="8"/>
     </row>
-    <row r="488" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3">
         <v>260041</v>
       </c>
@@ -40900,7 +40899,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="8"/>
     </row>
-    <row r="489" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3">
         <v>242017</v>
       </c>
@@ -40960,7 +40959,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="8"/>
     </row>
-    <row r="490" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3">
         <v>246006</v>
       </c>
@@ -41024,7 +41023,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="8"/>
     </row>
-    <row r="491" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3">
         <v>246010</v>
       </c>
@@ -41088,7 +41087,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="8"/>
     </row>
-    <row r="492" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3">
         <v>248013</v>
       </c>
@@ -41152,7 +41151,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="8"/>
     </row>
-    <row r="493" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3">
         <v>248039</v>
       </c>
@@ -41212,7 +41211,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="8"/>
     </row>
-    <row r="494" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3">
         <v>256067</v>
       </c>
@@ -41276,7 +41275,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="8"/>
     </row>
-    <row r="495" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3">
         <v>260048</v>
       </c>
@@ -41338,7 +41337,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="8"/>
     </row>
-    <row r="496" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3">
         <v>261005</v>
       </c>
@@ -41400,7 +41399,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="8"/>
     </row>
-    <row r="497" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3">
         <v>261037</v>
       </c>
@@ -41466,7 +41465,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="8"/>
     </row>
-    <row r="498" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3">
         <v>267018</v>
       </c>
@@ -41526,7 +41525,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="8"/>
     </row>
-    <row r="499" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3">
         <v>268045</v>
       </c>
@@ -41586,7 +41585,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="8"/>
     </row>
-    <row r="500" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3">
         <v>248031</v>
       </c>
@@ -41652,7 +41651,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="8"/>
     </row>
-    <row r="501" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3">
         <v>268020</v>
       </c>
@@ -41714,7 +41713,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="8"/>
     </row>
-    <row r="502" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3">
         <v>268077</v>
       </c>
@@ -41776,7 +41775,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="8"/>
     </row>
-    <row r="503" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3">
         <v>233025</v>
       </c>
@@ -41840,7 +41839,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="8"/>
     </row>
-    <row r="504" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3">
         <v>265132</v>
       </c>
@@ -41904,7 +41903,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="8"/>
     </row>
-    <row r="505" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3">
         <v>266048</v>
       </c>
@@ -41966,7 +41965,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="8"/>
     </row>
-    <row r="506" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3">
         <v>266088</v>
       </c>
@@ -42024,7 +42023,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="8"/>
     </row>
-    <row r="507" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3">
         <v>469002</v>
       </c>
@@ -42086,7 +42085,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="8"/>
     </row>
-    <row r="508" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3">
         <v>268007</v>
       </c>
@@ -42146,7 +42145,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="8"/>
     </row>
-    <row r="509" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3">
         <v>251007</v>
       </c>
@@ -42212,7 +42211,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="8"/>
     </row>
-    <row r="510" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3">
         <v>268048</v>
       </c>
@@ -42274,7 +42273,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="8"/>
     </row>
-    <row r="511" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3">
         <v>252001</v>
       </c>
@@ -42340,7 +42339,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="8"/>
     </row>
-    <row r="512" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3">
         <v>264071</v>
       </c>
@@ -42398,7 +42397,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="8"/>
     </row>
-    <row r="513" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3">
         <v>264088</v>
       </c>
@@ -42460,7 +42459,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="8"/>
     </row>
-    <row r="514" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3">
         <v>268002</v>
       </c>
@@ -42522,7 +42521,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="8"/>
     </row>
-    <row r="515" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3">
         <v>232015</v>
       </c>
@@ -42580,7 +42579,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="8"/>
     </row>
-    <row r="516" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3">
         <v>237068</v>
       </c>
@@ -42640,7 +42639,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="8"/>
     </row>
-    <row r="517" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3">
         <v>242012</v>
       </c>
@@ -42706,7 +42705,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="8"/>
     </row>
-    <row r="518" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3">
         <v>250054</v>
       </c>
@@ -42764,7 +42763,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="8"/>
     </row>
-    <row r="519" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3">
         <v>254002</v>
       </c>
@@ -42822,7 +42821,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="8"/>
     </row>
-    <row r="520" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3">
         <v>254004</v>
       </c>
@@ -42882,7 +42881,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="8"/>
     </row>
-    <row r="521" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3">
         <v>254044</v>
       </c>
@@ -42942,7 +42941,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="8"/>
     </row>
-    <row r="522" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3">
         <v>258032</v>
       </c>
@@ -43002,7 +43001,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="8"/>
     </row>
-    <row r="523" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3">
         <v>265054</v>
       </c>
@@ -43066,7 +43065,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="8"/>
     </row>
-    <row r="524" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3">
         <v>265086</v>
       </c>
@@ -43122,7 +43121,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="8"/>
     </row>
-    <row r="525" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3">
         <v>266062</v>
       </c>
@@ -43178,7 +43177,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="8"/>
     </row>
-    <row r="526" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3">
         <v>266077</v>
       </c>
@@ -43240,7 +43239,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="8"/>
     </row>
-    <row r="527" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3">
         <v>269017</v>
       </c>
@@ -43300,7 +43299,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="8"/>
     </row>
-    <row r="528" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3">
         <v>235118</v>
       </c>
@@ -43358,7 +43357,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="8"/>
     </row>
-    <row r="529" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3">
         <v>268063</v>
       </c>
@@ -43418,7 +43417,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="8"/>
     </row>
-    <row r="530" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3">
         <v>268084</v>
       </c>
@@ -43480,7 +43479,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="8"/>
     </row>
-    <row r="531" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3">
         <v>469001</v>
       </c>
@@ -43538,7 +43537,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="8"/>
     </row>
-    <row r="532" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3">
         <v>149024</v>
       </c>
@@ -43600,7 +43599,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="8"/>
     </row>
-    <row r="533" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3">
         <v>146029</v>
       </c>
@@ -43666,7 +43665,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="8"/>
     </row>
-    <row r="534" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3">
         <v>233027</v>
       </c>
@@ -43730,7 +43729,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="8"/>
     </row>
-    <row r="535" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3">
         <v>257037</v>
       </c>
@@ -43792,7 +43791,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="8"/>
     </row>
-    <row r="536" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3">
         <v>257039</v>
       </c>
@@ -43858,7 +43857,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="8"/>
     </row>
-    <row r="537" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3">
         <v>260050</v>
       </c>
@@ -43922,7 +43921,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="8"/>
     </row>
-    <row r="538" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3">
         <v>266035</v>
       </c>
@@ -43986,7 +43985,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="8"/>
     </row>
-    <row r="539" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3">
         <v>267032</v>
       </c>
@@ -44048,7 +44047,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="8"/>
     </row>
-    <row r="540" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3">
         <v>268003</v>
       </c>
@@ -44110,7 +44109,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="8"/>
     </row>
-    <row r="541" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3">
         <v>269010</v>
       </c>
@@ -44172,7 +44171,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="8"/>
     </row>
-    <row r="542" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3">
         <v>233060</v>
       </c>
@@ -44230,7 +44229,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="8"/>
     </row>
-    <row r="543" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3">
         <v>244023</v>
       </c>
@@ -44296,7 +44295,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="8"/>
     </row>
-    <row r="544" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3">
         <v>256001</v>
       </c>
@@ -44356,7 +44355,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="8"/>
     </row>
-    <row r="545" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3">
         <v>265037</v>
       </c>
@@ -44420,7 +44419,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="8"/>
     </row>
-    <row r="546" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3">
         <v>266004</v>
       </c>
@@ -44484,7 +44483,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="8"/>
     </row>
-    <row r="547" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3">
         <v>266082</v>
       </c>
@@ -44548,7 +44547,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="8"/>
     </row>
-    <row r="548" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3">
         <v>166006</v>
       </c>
@@ -44606,7 +44605,7 @@
       </c>
       <c r="Z548" s="8"/>
     </row>
-    <row r="549" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3">
         <v>169012</v>
       </c>
@@ -44664,7 +44663,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="8"/>
     </row>
-    <row r="550" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3">
         <v>241009</v>
       </c>
@@ -44726,7 +44725,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="8"/>
     </row>
-    <row r="551" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3">
         <v>147029</v>
       </c>
@@ -44786,7 +44785,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="8"/>
     </row>
-    <row r="552" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3">
         <v>149039</v>
       </c>
@@ -44848,7 +44847,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="8"/>
     </row>
-    <row r="553" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3">
         <v>151015</v>
       </c>
@@ -44914,7 +44913,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="8"/>
     </row>
-    <row r="554" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3">
         <v>160004</v>
       </c>
@@ -44976,7 +44975,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="8"/>
     </row>
-    <row r="555" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3">
         <v>161010</v>
       </c>
@@ -45038,7 +45037,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="8"/>
     </row>
-    <row r="556" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3">
         <v>166026</v>
       </c>
@@ -45098,7 +45097,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="8"/>
     </row>
-    <row r="557" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3">
         <v>166034</v>
       </c>
@@ -45156,7 +45155,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="8"/>
     </row>
-    <row r="558" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3">
         <v>167009</v>
       </c>
@@ -45214,7 +45213,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="8"/>
     </row>
-    <row r="559" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3">
         <v>136028</v>
       </c>
@@ -45274,7 +45273,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="8"/>
     </row>
-    <row r="560" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3">
         <v>150029</v>
       </c>
@@ -45336,7 +45335,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="8"/>
     </row>
-    <row r="561" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3">
         <v>245017</v>
       </c>
@@ -45402,7 +45401,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="8"/>
     </row>
-    <row r="562" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3">
         <v>368001</v>
       </c>
@@ -45464,7 +45463,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="8"/>
     </row>
-    <row r="563" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3">
         <v>148005</v>
       </c>
@@ -45530,7 +45529,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="8"/>
     </row>
-    <row r="564" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3">
         <v>168003</v>
       </c>
@@ -45592,7 +45591,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="8"/>
     </row>
-    <row r="565" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3">
         <v>169014</v>
       </c>
@@ -45654,7 +45653,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="8"/>
     </row>
-    <row r="566" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3">
         <v>158053</v>
       </c>
@@ -45720,7 +45719,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="8"/>
     </row>
-    <row r="567" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3">
         <v>166018</v>
       </c>
@@ -45778,7 +45777,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="8"/>
     </row>
-    <row r="568" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3">
         <v>167010</v>
       </c>
@@ -45840,7 +45839,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="8"/>
     </row>
-    <row r="569" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3">
         <v>169019</v>
       </c>
@@ -45902,7 +45901,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="8"/>
     </row>
-    <row r="570" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3">
         <v>167007</v>
       </c>
@@ -45966,7 +45965,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="8"/>
     </row>
-    <row r="571" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3">
         <v>169013</v>
       </c>
@@ -46028,7 +46027,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="8"/>
     </row>
-    <row r="572" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3">
         <v>161014</v>
       </c>
@@ -46092,7 +46091,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="8"/>
     </row>
-    <row r="573" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3">
         <v>169016</v>
       </c>
@@ -46154,7 +46153,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="8"/>
     </row>
-    <row r="574" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3">
         <v>167036</v>
       </c>
@@ -46214,7 +46213,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="8"/>
     </row>
-    <row r="575" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
         <v>2912</v>
       </c>
@@ -46276,7 +46275,7 @@
       </c>
       <c r="Z575" s="8"/>
     </row>
-    <row r="576" spans="1:26" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>2910</v>
       </c>
@@ -46339,13 +46338,7 @@
       <c r="Z576" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="OGC-FAD-PCM-PCM"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:Y576" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>
@@ -47663,22 +47656,22 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="12" t="s">
         <v>3445</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="12" t="s">
         <v>2821</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="12" t="s">
         <v>2821</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="12" t="s">
         <v>2304</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="12" t="s">
         <v>2778</v>
       </c>
     </row>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{E50475B0-A2F7-4015-B377-5EC4E7B0F41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7594" uniqueCount="3446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7596" uniqueCount="3446">
   <si>
     <t>emp_id</t>
   </si>
@@ -41610,8 +41610,8 @@
       <c r="H500" s="3" t="s">
         <v>2107</v>
       </c>
-      <c r="I500" s="3">
-        <v>268029</v>
+      <c r="I500" s="3" t="s">
+        <v>2912</v>
       </c>
       <c r="J500" s="5">
         <v>29617</v>
@@ -42170,8 +42170,8 @@
       <c r="H509" s="3" t="s">
         <v>2210</v>
       </c>
-      <c r="I509" s="3">
-        <v>268029</v>
+      <c r="I509" s="3" t="s">
+        <v>2912</v>
       </c>
       <c r="J509" s="5">
         <v>30522</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4904F4E5-AD7B-421D-A1FE-90FE4FA383EE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7596" uniqueCount="3446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7597" uniqueCount="3446">
   <si>
     <t>emp_id</t>
   </si>
@@ -43500,8 +43500,8 @@
       <c r="H531" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="I531" s="3">
-        <v>268029</v>
+      <c r="I531" s="3" t="s">
+        <v>2912</v>
       </c>
       <c r="J531" s="5">
         <v>25892</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4904F4E5-AD7B-421D-A1FE-90FE4FA383EE}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7E0230-2149-4580-A9ED-400C93CF4956}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10536,6 +10536,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18290,7 +18294,7 @@
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>122</v>
@@ -23279,7 +23283,7 @@
         <v>2310</v>
       </c>
       <c r="I200" s="3">
-        <v>256029</v>
+        <v>236012</v>
       </c>
       <c r="J200" s="5">
         <v>37517</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7E0230-2149-4580-A9ED-400C93CF4956}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9442CE8-9327-4EA0-A2C3-6FE186671B7B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7597" uniqueCount="3446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7602" uniqueCount="3452">
   <si>
     <t>emp_id</t>
   </si>
@@ -10366,9 +10366,6 @@
     <t>86.31%</t>
   </si>
   <si>
-    <t>Critical Position</t>
-  </si>
-  <si>
     <t>Acting Department Manager - Batch and Furnace</t>
   </si>
   <si>
@@ -10376,6 +10373,27 @@
   </si>
   <si>
     <t>OGC-MFG-SPN-PCM</t>
+  </si>
+  <si>
+    <t>Key Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Level A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Level A- </t>
+  </si>
+  <si>
+    <t>Critical Level B+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Level B+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Level B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Level C+ </t>
   </si>
 </sst>
 </file>
@@ -17818,9 +17836,7 @@
         <v>420</v>
       </c>
       <c r="P113" s="3"/>
-      <c r="Q113" s="3" t="s">
-        <v>3442</v>
-      </c>
+      <c r="Q113" s="3"/>
       <c r="R113" s="3"/>
       <c r="S113" s="3" t="s">
         <v>421</v>
@@ -21012,9 +21028,7 @@
         <v>776</v>
       </c>
       <c r="P164" s="3"/>
-      <c r="Q164" s="3" t="s">
-        <v>3442</v>
-      </c>
+      <c r="Q164" s="3"/>
       <c r="R164" s="3"/>
       <c r="S164" s="3" t="s">
         <v>33</v>
@@ -22128,7 +22142,7 @@
         <v>40</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I182" s="3">
         <v>149024</v>
@@ -22190,7 +22204,7 @@
         <v>40</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I183" s="3">
         <v>149024</v>
@@ -22256,7 +22270,7 @@
         <v>793</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I184" s="3">
         <v>149024</v>
@@ -22318,7 +22332,7 @@
         <v>58</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I185" s="3">
         <v>149024</v>
@@ -22380,7 +22394,7 @@
         <v>71</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I186" s="3">
         <v>149024</v>
@@ -22442,7 +22456,7 @@
         <v>71</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I187" s="3">
         <v>149024</v>
@@ -22504,7 +22518,7 @@
         <v>122</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I188" s="3">
         <v>149024</v>
@@ -22566,7 +22580,7 @@
         <v>115</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I189" s="3">
         <v>149024</v>
@@ -23532,7 +23546,7 @@
         <v>942</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>515</v>
@@ -23559,7 +23573,7 @@
       </c>
       <c r="P204" s="3"/>
       <c r="Q204" s="3" t="s">
-        <v>3442</v>
+        <v>3446</v>
       </c>
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
@@ -25286,7 +25300,9 @@
         <v>1285</v>
       </c>
       <c r="P233" s="3"/>
-      <c r="Q233" s="3"/>
+      <c r="Q233" s="3" t="s">
+        <v>3448</v>
+      </c>
       <c r="R233" s="3"/>
       <c r="S233" s="3" t="s">
         <v>1286</v>
@@ -29782,7 +29798,9 @@
         <v>1809</v>
       </c>
       <c r="P305" s="3"/>
-      <c r="Q305" s="3"/>
+      <c r="Q305" s="3" t="s">
+        <v>3447</v>
+      </c>
       <c r="R305" s="3"/>
       <c r="S305" s="3" t="s">
         <v>52</v>
@@ -37734,7 +37752,9 @@
         <v>2069</v>
       </c>
       <c r="P435" s="3"/>
-      <c r="Q435" s="3"/>
+      <c r="Q435" s="3" t="s">
+        <v>3449</v>
+      </c>
       <c r="R435" s="3"/>
       <c r="S435" s="6" t="s">
         <v>2949</v>
@@ -43580,7 +43600,9 @@
         <v>2306</v>
       </c>
       <c r="P532" s="3"/>
-      <c r="Q532" s="3"/>
+      <c r="Q532" s="3" t="s">
+        <v>3451</v>
+      </c>
       <c r="R532" s="3"/>
       <c r="S532" s="3" t="s">
         <v>53</v>
@@ -44707,7 +44729,7 @@
       </c>
       <c r="P550" s="3"/>
       <c r="Q550" s="3" t="s">
-        <v>3442</v>
+        <v>3445</v>
       </c>
       <c r="R550" s="3"/>
       <c r="S550" s="3" t="s">
@@ -45448,7 +45470,9 @@
         <v>2442</v>
       </c>
       <c r="P562" s="3"/>
-      <c r="Q562" s="3"/>
+      <c r="Q562" s="3" t="s">
+        <v>3445</v>
+      </c>
       <c r="R562" s="3"/>
       <c r="S562" s="3"/>
       <c r="T562" s="3"/>
@@ -45510,7 +45534,9 @@
         <v>2507</v>
       </c>
       <c r="P563" s="3"/>
-      <c r="Q563" s="3"/>
+      <c r="Q563" s="3" t="s">
+        <v>3445</v>
+      </c>
       <c r="R563" s="3"/>
       <c r="S563" s="3" t="s">
         <v>232</v>
@@ -46260,7 +46286,9 @@
         <v>2383</v>
       </c>
       <c r="P575" s="3"/>
-      <c r="Q575" s="3"/>
+      <c r="Q575" s="3" t="s">
+        <v>3450</v>
+      </c>
       <c r="R575" s="3"/>
       <c r="S575" s="3"/>
       <c r="T575" s="3"/>
@@ -46316,7 +46344,7 @@
       <c r="L576" s="4"/>
       <c r="M576" s="4"/>
       <c r="N576" s="3" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="O576" s="3" t="s">
         <v>2765</v>
@@ -47661,7 +47689,7 @@
     </row>
     <row r="66" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>2821</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82E15371-813B-47EA-B658-28CBBAE83986}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E15E93DE-65E0-4A52-AD2E-3B35A4F8E100}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$577</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Y$579</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7657" uniqueCount="3475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7659" uniqueCount="3475">
   <si>
     <t>emp_id</t>
   </si>
@@ -10604,10 +10604,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -10620,6 +10616,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10927,14 +10927,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z579"/>
+  <dimension ref="A1:Z583"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="36" style="18" customWidth="1"/>
+    <col min="6" max="6" width="36" style="16" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
@@ -10952,32 +10952,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="17" t="s">
         <v>2914</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -10995,7 +10995,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -11072,7 +11072,7 @@
       <c r="E3" s="3" t="s">
         <v>2758</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>2759</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -11131,7 +11131,7 @@
       <c r="E4" s="3" t="s">
         <v>2751</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="15" t="s">
         <v>2752</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -11193,7 +11193,7 @@
       <c r="E5" s="3" t="s">
         <v>2744</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="15" t="s">
         <v>2745</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -11259,7 +11259,7 @@
       <c r="E6" s="3" t="s">
         <v>2525</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="15" t="s">
         <v>2526</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -11323,7 +11323,7 @@
       <c r="E7" s="3" t="s">
         <v>2532</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="15" t="s">
         <v>2533</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -11385,7 +11385,7 @@
       <c r="E8" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -11447,7 +11447,7 @@
       <c r="E9" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -11507,7 +11507,7 @@
       <c r="E10" s="3" t="s">
         <v>2544</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="15" t="s">
         <v>2545</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -11569,7 +11569,7 @@
       <c r="E11" s="3" t="s">
         <v>2549</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -11629,7 +11629,7 @@
       <c r="E12" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -11689,7 +11689,7 @@
       <c r="E13" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -11749,7 +11749,7 @@
       <c r="E14" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="15" t="s">
         <v>2559</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -11811,7 +11811,7 @@
       <c r="E15" s="3" t="s">
         <v>2564</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="15" t="s">
         <v>2559</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -11877,7 +11877,7 @@
       <c r="E16" s="3" t="s">
         <v>2569</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -11939,7 +11939,7 @@
       <c r="E17" s="3" t="s">
         <v>2574</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="15" t="s">
         <v>2575</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -12001,7 +12001,7 @@
       <c r="E18" s="3" t="s">
         <v>2580</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="15" t="s">
         <v>2533</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -12063,7 +12063,7 @@
       <c r="E19" s="3" t="s">
         <v>2585</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="15" t="s">
         <v>2559</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -12123,7 +12123,7 @@
       <c r="E20" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="15" t="s">
         <v>2559</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -12183,7 +12183,7 @@
       <c r="E21" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="15" t="s">
         <v>2559</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -12243,7 +12243,7 @@
       <c r="E22" s="3" t="s">
         <v>2596</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -12303,7 +12303,7 @@
       <c r="E23" s="3" t="s">
         <v>1411</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="15" t="s">
         <v>2600</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -12365,7 +12365,7 @@
       <c r="E24" s="3" t="s">
         <v>2605</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="15" t="s">
         <v>2533</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -12427,7 +12427,7 @@
       <c r="E25" s="3" t="s">
         <v>2610</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="15" t="s">
         <v>2611</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -12487,7 +12487,7 @@
       <c r="E26" s="3" t="s">
         <v>2615</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="15" t="s">
         <v>2611</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -12547,7 +12547,7 @@
       <c r="E27" s="3" t="s">
         <v>2321</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="15" t="s">
         <v>2611</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -12607,7 +12607,7 @@
       <c r="E28" s="3" t="s">
         <v>2622</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="15" t="s">
         <v>2537</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -12667,7 +12667,7 @@
       <c r="E29" s="3" t="s">
         <v>2626</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="15" t="s">
         <v>2600</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="15" t="s">
         <v>2732</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -12791,7 +12791,7 @@
       <c r="E31" s="3" t="s">
         <v>2738</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="15" t="s">
         <v>2739</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -12857,7 +12857,7 @@
       <c r="E32" s="3" t="s">
         <v>2328</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="15" t="s">
         <v>2631</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -12921,7 +12921,7 @@
       <c r="E33" s="3" t="s">
         <v>2637</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="15" t="s">
         <v>2631</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -12983,7 +12983,7 @@
       <c r="E34" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="15" t="s">
         <v>3457</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -13006,7 +13006,7 @@
       <c r="N34" s="3" t="s">
         <v>3459</v>
       </c>
-      <c r="O34" s="15" t="s">
+      <c r="O34" s="13" t="s">
         <v>3460</v>
       </c>
       <c r="P34" s="3"/>
@@ -13045,7 +13045,7 @@
       <c r="E35" s="3" t="s">
         <v>2642</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="15" t="s">
         <v>2643</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -13111,7 +13111,7 @@
       <c r="E36" s="3" t="s">
         <v>1945</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="15" t="s">
         <v>2649</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -13171,7 +13171,7 @@
       <c r="E37" s="3" t="s">
         <v>2653</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="15" t="s">
         <v>2649</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -13291,7 +13291,7 @@
       <c r="E39" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="15" t="s">
         <v>2661</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -13355,7 +13355,7 @@
       <c r="E40" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="15" t="s">
         <v>2649</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -13419,7 +13419,7 @@
       <c r="E41" s="3" t="s">
         <v>1695</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="15" t="s">
         <v>2649</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -13481,7 +13481,7 @@
       <c r="E42" s="3" t="s">
         <v>1269</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -13543,7 +13543,7 @@
       <c r="E43" s="3" t="s">
         <v>2676</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -13603,7 +13603,7 @@
       <c r="E44" s="3" t="s">
         <v>2680</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -13663,7 +13663,7 @@
       <c r="E45" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -13725,7 +13725,7 @@
       <c r="E46" s="3" t="s">
         <v>1639</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -13953,7 +13953,7 @@
       <c r="E50" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="15" t="s">
         <v>2699</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -14015,7 +14015,7 @@
       <c r="E51" s="3" t="s">
         <v>1411</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="15" t="s">
         <v>2699</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -14077,7 +14077,7 @@
       <c r="E52" s="3" t="s">
         <v>2708</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -14137,7 +14137,7 @@
       <c r="E53" s="3" t="s">
         <v>2712</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -14197,7 +14197,7 @@
       <c r="E54" s="3" t="s">
         <v>2292</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -14257,7 +14257,7 @@
       <c r="E55" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G55" s="3" t="s">
@@ -14317,7 +14317,7 @@
       <c r="E56" s="3" t="s">
         <v>2722</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="15" t="s">
         <v>2649</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -14377,7 +14377,7 @@
       <c r="E57" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G57" s="3" t="s">
@@ -14437,7 +14437,7 @@
       <c r="E58" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F58" s="15" t="s">
         <v>2654</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -14497,7 +14497,7 @@
       <c r="E59" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="15" t="s">
         <v>183</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -14563,7 +14563,7 @@
       <c r="E60" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="15" t="s">
         <v>48</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -14629,7 +14629,7 @@
       <c r="E61" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="15" t="s">
         <v>28</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -14693,7 +14693,7 @@
       <c r="E62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="15" t="s">
         <v>39</v>
       </c>
       <c r="G62" s="3" t="s">
@@ -14755,7 +14755,7 @@
       <c r="E63" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="15" t="s">
         <v>65</v>
       </c>
       <c r="G63" s="3" t="s">
@@ -14817,7 +14817,7 @@
       <c r="E64" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G64" s="3" t="s">
@@ -14879,7 +14879,7 @@
       <c r="E65" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="15" t="s">
         <v>106</v>
       </c>
       <c r="G65" s="3" t="s">
@@ -14945,7 +14945,7 @@
       <c r="E66" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="15" t="s">
         <v>2915</v>
       </c>
       <c r="G66" s="3" t="s">
@@ -15007,7 +15007,7 @@
       <c r="E67" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="15" t="s">
         <v>70</v>
       </c>
       <c r="G67" s="3" t="s">
@@ -15069,7 +15069,7 @@
       <c r="E68" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="15" t="s">
         <v>83</v>
       </c>
       <c r="G68" s="3" t="s">
@@ -15131,7 +15131,7 @@
       <c r="E69" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F69" s="15" t="s">
         <v>91</v>
       </c>
       <c r="G69" s="3" t="s">
@@ -15193,7 +15193,7 @@
       <c r="E70" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="F70" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G70" s="3" t="s">
@@ -15257,7 +15257,7 @@
       <c r="E71" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F71" s="15" t="s">
         <v>176</v>
       </c>
       <c r="G71" s="3" t="s">
@@ -15319,7 +15319,7 @@
       <c r="E72" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="15" t="s">
         <v>121</v>
       </c>
       <c r="G72" s="3" t="s">
@@ -15381,7 +15381,7 @@
       <c r="E73" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="15" t="s">
         <v>129</v>
       </c>
       <c r="G73" s="3" t="s">
@@ -15445,7 +15445,7 @@
       <c r="E74" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="15" t="s">
         <v>137</v>
       </c>
       <c r="G74" s="3" t="s">
@@ -15507,7 +15507,7 @@
       <c r="E75" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="15" t="s">
         <v>143</v>
       </c>
       <c r="G75" s="3" t="s">
@@ -15569,7 +15569,7 @@
       <c r="E76" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="15" t="s">
         <v>150</v>
       </c>
       <c r="G76" s="3" t="s">
@@ -15631,7 +15631,7 @@
       <c r="E77" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="15" t="s">
         <v>156</v>
       </c>
       <c r="G77" s="3" t="s">
@@ -15693,7 +15693,7 @@
       <c r="E78" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F78" s="15" t="s">
         <v>163</v>
       </c>
       <c r="G78" s="3" t="s">
@@ -15755,7 +15755,7 @@
       <c r="E79" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="15" t="s">
         <v>169</v>
       </c>
       <c r="G79" s="3" t="s">
@@ -15821,7 +15821,7 @@
       <c r="E80" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="F80" s="15" t="s">
         <v>611</v>
       </c>
       <c r="G80" s="3" t="s">
@@ -15883,7 +15883,7 @@
       <c r="E81" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="15" t="s">
         <v>432</v>
       </c>
       <c r="G81" s="3" t="s">
@@ -15945,7 +15945,7 @@
       <c r="E82" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="15" t="s">
         <v>438</v>
       </c>
       <c r="G82" s="3" t="s">
@@ -16009,7 +16009,7 @@
       <c r="E83" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="15" t="s">
         <v>425</v>
       </c>
       <c r="G83" s="3" t="s">
@@ -16075,7 +16075,7 @@
       <c r="E84" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="15" t="s">
         <v>468</v>
       </c>
       <c r="G84" s="3" t="s">
@@ -16143,7 +16143,7 @@
       <c r="E85" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="15" t="s">
         <v>443</v>
       </c>
       <c r="G85" s="3" t="s">
@@ -16209,7 +16209,7 @@
       <c r="E86" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="F86" s="17" t="s">
+      <c r="F86" s="15" t="s">
         <v>432</v>
       </c>
       <c r="G86" s="3" t="s">
@@ -16271,7 +16271,7 @@
       <c r="E87" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="15" t="s">
         <v>457</v>
       </c>
       <c r="G87" s="3" t="s">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
-      <c r="F88" s="17" t="s">
+      <c r="F88" s="15" t="s">
         <v>300</v>
       </c>
       <c r="G88" s="3" t="s">
@@ -16395,7 +16395,7 @@
       <c r="E89" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="F89" s="17" t="s">
+      <c r="F89" s="15" t="s">
         <v>475</v>
       </c>
       <c r="G89" s="3" t="s">
@@ -16459,7 +16459,7 @@
       <c r="E90" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="F90" s="17" t="s">
+      <c r="F90" s="15" t="s">
         <v>475</v>
       </c>
       <c r="G90" s="3" t="s">
@@ -16521,7 +16521,7 @@
       <c r="E91" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="F91" s="17" t="s">
+      <c r="F91" s="15" t="s">
         <v>475</v>
       </c>
       <c r="G91" s="3" t="s">
@@ -16583,7 +16583,7 @@
       <c r="E92" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="F92" s="17" t="s">
+      <c r="F92" s="15" t="s">
         <v>492</v>
       </c>
       <c r="G92" s="3" t="s">
@@ -16645,7 +16645,7 @@
       <c r="E93" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F93" s="17" t="s">
+      <c r="F93" s="15" t="s">
         <v>498</v>
       </c>
       <c r="G93" s="3" t="s">
@@ -16707,7 +16707,7 @@
       <c r="E94" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="F94" s="17" t="s">
+      <c r="F94" s="15" t="s">
         <v>498</v>
       </c>
       <c r="G94" s="3" t="s">
@@ -16769,7 +16769,7 @@
       <c r="E95" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F95" s="15" t="s">
         <v>508</v>
       </c>
       <c r="G95" s="3" t="s">
@@ -16831,7 +16831,7 @@
       <c r="E96" s="3" t="s">
         <v>2918</v>
       </c>
-      <c r="F96" s="17" t="s">
+      <c r="F96" s="15" t="s">
         <v>2919</v>
       </c>
       <c r="G96" s="3" t="s">
@@ -16893,7 +16893,7 @@
       <c r="E97" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="F97" s="17" t="s">
+      <c r="F97" s="15" t="s">
         <v>514</v>
       </c>
       <c r="G97" s="3" t="s">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="15" t="s">
         <v>523</v>
       </c>
       <c r="G98" s="3" t="s">
@@ -17021,7 +17021,7 @@
       <c r="E99" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F99" s="17" t="s">
+      <c r="F99" s="15" t="s">
         <v>523</v>
       </c>
       <c r="G99" s="3" t="s">
@@ -17087,7 +17087,7 @@
       <c r="E100" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="F100" s="17" t="s">
+      <c r="F100" s="15" t="s">
         <v>533</v>
       </c>
       <c r="G100" s="3" t="s">
@@ -17151,7 +17151,7 @@
       <c r="E101" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="15" t="s">
         <v>533</v>
       </c>
       <c r="G101" s="3" t="s">
@@ -17213,7 +17213,7 @@
       <c r="E102" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="15" t="s">
         <v>544</v>
       </c>
       <c r="G102" s="3" t="s">
@@ -17275,7 +17275,7 @@
       <c r="E103" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="F103" s="17" t="s">
+      <c r="F103" s="15" t="s">
         <v>550</v>
       </c>
       <c r="G103" s="3" t="s">
@@ -17337,7 +17337,7 @@
       <c r="E104" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="F104" s="17" t="s">
+      <c r="F104" s="15" t="s">
         <v>564</v>
       </c>
       <c r="G104" s="3" t="s">
@@ -17405,7 +17405,7 @@
       <c r="E105" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F105" s="17" t="s">
+      <c r="F105" s="15" t="s">
         <v>318</v>
       </c>
       <c r="G105" s="3" t="s">
@@ -17467,7 +17467,7 @@
       <c r="E106" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="F106" s="17" t="s">
+      <c r="F106" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G106" s="3" t="s">
@@ -17531,7 +17531,7 @@
       <c r="E107" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G107" s="3" t="s">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
-      <c r="F108" s="17" t="s">
+      <c r="F108" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G108" s="3" t="s">
@@ -17651,7 +17651,7 @@
       <c r="E109" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F109" s="17" t="s">
+      <c r="F109" s="15" t="s">
         <v>590</v>
       </c>
       <c r="G109" s="3" t="s">
@@ -17713,7 +17713,7 @@
       <c r="E110" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G110" s="3" t="s">
@@ -17777,7 +17777,7 @@
       <c r="E111" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="15" t="s">
         <v>601</v>
       </c>
       <c r="G111" s="3" t="s">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="15" t="s">
         <v>318</v>
       </c>
       <c r="G112" s="3" t="s">
@@ -17897,7 +17897,7 @@
       <c r="E113" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="F113" s="17" t="s">
+      <c r="F113" s="15" t="s">
         <v>556</v>
       </c>
       <c r="G113" s="3" t="s">
@@ -17959,7 +17959,7 @@
       <c r="E114" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F114" s="17" t="s">
+      <c r="F114" s="15" t="s">
         <v>417</v>
       </c>
       <c r="G114" s="3" t="s">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="17" t="s">
+      <c r="F115" s="15" t="s">
         <v>393</v>
       </c>
       <c r="G115" s="3" t="s">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
-      <c r="F116" s="17" t="s">
+      <c r="F116" s="15" t="s">
         <v>400</v>
       </c>
       <c r="G116" s="3" t="s">
@@ -18151,7 +18151,7 @@
       <c r="E117" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F117" s="17" t="s">
+      <c r="F117" s="15" t="s">
         <v>366</v>
       </c>
       <c r="G117" s="3" t="s">
@@ -18215,7 +18215,7 @@
       <c r="E118" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F118" s="17" t="s">
+      <c r="F118" s="15" t="s">
         <v>411</v>
       </c>
       <c r="G118" s="3" t="s">
@@ -18277,7 +18277,7 @@
       <c r="E119" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F119" s="17" t="s">
+      <c r="F119" s="15" t="s">
         <v>193</v>
       </c>
       <c r="G119" s="3" t="s">
@@ -18343,7 +18343,7 @@
       <c r="E120" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F120" s="17" t="s">
+      <c r="F120" s="15" t="s">
         <v>200</v>
       </c>
       <c r="G120" s="3" t="s">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="17" t="s">
+      <c r="F121" s="15" t="s">
         <v>206</v>
       </c>
       <c r="G121" s="3" t="s">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="17" t="s">
+      <c r="F122" s="15" t="s">
         <v>216</v>
       </c>
       <c r="G122" s="3" t="s">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="17" t="s">
+      <c r="F123" s="15" t="s">
         <v>216</v>
       </c>
       <c r="G123" s="3" t="s">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="17" t="s">
+      <c r="F124" s="15" t="s">
         <v>221</v>
       </c>
       <c r="G124" s="3" t="s">
@@ -18639,7 +18639,7 @@
       <c r="E125" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F125" s="17" t="s">
+      <c r="F125" s="15" t="s">
         <v>229</v>
       </c>
       <c r="G125" s="3" t="s">
@@ -18705,7 +18705,7 @@
       <c r="E126" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F126" s="17" t="s">
+      <c r="F126" s="15" t="s">
         <v>236</v>
       </c>
       <c r="G126" s="3" t="s">
@@ -18771,7 +18771,7 @@
       <c r="E127" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F127" s="17" t="s">
+      <c r="F127" s="15" t="s">
         <v>236</v>
       </c>
       <c r="G127" s="3" t="s">
@@ -18835,7 +18835,7 @@
       <c r="E128" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F128" s="17" t="s">
+      <c r="F128" s="15" t="s">
         <v>211</v>
       </c>
       <c r="G128" s="3" t="s">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="17" t="s">
+      <c r="F129" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G129" s="3" t="s">
@@ -18955,7 +18955,7 @@
       <c r="E130" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F130" s="17" t="s">
+      <c r="F130" s="15" t="s">
         <v>221</v>
       </c>
       <c r="G130" s="3" t="s">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="17" t="s">
+      <c r="F131" s="15" t="s">
         <v>264</v>
       </c>
       <c r="G131" s="3" t="s">
@@ -19075,7 +19075,7 @@
       <c r="E132" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F132" s="17" t="s">
+      <c r="F132" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G132" s="3" t="s">
@@ -19137,7 +19137,7 @@
       <c r="E133" s="3" t="s">
         <v>2924</v>
       </c>
-      <c r="F133" s="17" t="s">
+      <c r="F133" s="15" t="s">
         <v>221</v>
       </c>
       <c r="G133" s="3" t="s">
@@ -19199,7 +19199,7 @@
       <c r="E134" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F134" s="17" t="s">
+      <c r="F134" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G134" s="3" t="s">
@@ -19265,7 +19265,7 @@
       <c r="E135" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F135" s="17" t="s">
+      <c r="F135" s="15" t="s">
         <v>285</v>
       </c>
       <c r="G135" s="3" t="s">
@@ -19329,7 +19329,7 @@
       <c r="E136" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F136" s="17" t="s">
+      <c r="F136" s="15" t="s">
         <v>285</v>
       </c>
       <c r="G136" s="3" t="s">
@@ -19393,7 +19393,7 @@
       <c r="E137" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F137" s="17" t="s">
+      <c r="F137" s="15" t="s">
         <v>221</v>
       </c>
       <c r="G137" s="3" t="s">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="17" t="s">
+      <c r="F138" s="15" t="s">
         <v>300</v>
       </c>
       <c r="G138" s="3" t="s">
@@ -19513,7 +19513,7 @@
       <c r="E139" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F139" s="17" t="s">
+      <c r="F139" s="15" t="s">
         <v>300</v>
       </c>
       <c r="G139" s="3" t="s">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="17" t="s">
+      <c r="F140" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G140" s="3" t="s">
@@ -19637,7 +19637,7 @@
       <c r="E141" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F141" s="17" t="s">
+      <c r="F141" s="15" t="s">
         <v>318</v>
       </c>
       <c r="G141" s="3" t="s">
@@ -19699,7 +19699,7 @@
       <c r="E142" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F142" s="17" t="s">
+      <c r="F142" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G142" s="3" t="s">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="17" t="s">
+      <c r="F143" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G143" s="3" t="s">
@@ -19819,7 +19819,7 @@
       <c r="E144" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F144" s="17" t="s">
+      <c r="F144" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G144" s="3" t="s">
@@ -19881,7 +19881,7 @@
       <c r="E145" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F145" s="17" t="s">
+      <c r="F145" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G145" s="3" t="s">
@@ -19943,7 +19943,7 @@
       <c r="E146" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F146" s="17" t="s">
+      <c r="F146" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G146" s="3" t="s">
@@ -20005,7 +20005,7 @@
       <c r="E147" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F147" s="17" t="s">
+      <c r="F147" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G147" s="3" t="s">
@@ -20067,7 +20067,7 @@
       <c r="E148" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="F148" s="17" t="s">
+      <c r="F148" s="15" t="s">
         <v>360</v>
       </c>
       <c r="G148" s="3" t="s">
@@ -20133,7 +20133,7 @@
       <c r="E149" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="F149" s="17" t="s">
+      <c r="F149" s="15" t="s">
         <v>366</v>
       </c>
       <c r="G149" s="3" t="s">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="17" t="s">
+      <c r="F150" s="15" t="s">
         <v>371</v>
       </c>
       <c r="G150" s="3" t="s">
@@ -20257,7 +20257,7 @@
       <c r="E151" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="F151" s="17" t="s">
+      <c r="F151" s="15" t="s">
         <v>353</v>
       </c>
       <c r="G151" s="3" t="s">
@@ -20321,7 +20321,7 @@
       <c r="E152" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F152" s="17" t="s">
+      <c r="F152" s="15" t="s">
         <v>2927</v>
       </c>
       <c r="G152" s="3" t="s">
@@ -20389,7 +20389,7 @@
       <c r="E153" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F153" s="17" t="s">
+      <c r="F153" s="15" t="s">
         <v>383</v>
       </c>
       <c r="G153" s="3" t="s">
@@ -20455,7 +20455,7 @@
       <c r="E154" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F154" s="17" t="s">
+      <c r="F154" s="15" t="s">
         <v>285</v>
       </c>
       <c r="G154" s="3" t="s">
@@ -20517,7 +20517,7 @@
       <c r="E155" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="F155" s="17" t="s">
+      <c r="F155" s="15" t="s">
         <v>672</v>
       </c>
       <c r="G155" s="3" t="s">
@@ -20579,7 +20579,7 @@
       <c r="E156" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="F156" s="17" t="s">
+      <c r="F156" s="15" t="s">
         <v>619</v>
       </c>
       <c r="G156" s="3" t="s">
@@ -20643,7 +20643,7 @@
       <c r="E157" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="F157" s="17" t="s">
+      <c r="F157" s="15" t="s">
         <v>626</v>
       </c>
       <c r="G157" s="3" t="s">
@@ -20709,7 +20709,7 @@
       <c r="E158" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="F158" s="17" t="s">
+      <c r="F158" s="15" t="s">
         <v>632</v>
       </c>
       <c r="G158" s="3" t="s">
@@ -20773,7 +20773,7 @@
       <c r="E159" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F159" s="17" t="s">
+      <c r="F159" s="15" t="s">
         <v>637</v>
       </c>
       <c r="G159" s="3" t="s">
@@ -20839,7 +20839,7 @@
       <c r="E160" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="F160" s="17" t="s">
+      <c r="F160" s="15" t="s">
         <v>2928</v>
       </c>
       <c r="G160" s="3" t="s">
@@ -20903,7 +20903,7 @@
       <c r="E161" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="F161" s="17" t="s">
+      <c r="F161" s="15" t="s">
         <v>648</v>
       </c>
       <c r="G161" s="3" t="s">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
-      <c r="F162" s="17" t="s">
+      <c r="F162" s="15" t="s">
         <v>653</v>
       </c>
       <c r="G162" s="3" t="s">
@@ -21025,7 +21025,7 @@
       <c r="E163" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="F163" s="17" t="s">
+      <c r="F163" s="15" t="s">
         <v>659</v>
       </c>
       <c r="G163" s="3" t="s">
@@ -21091,7 +21091,7 @@
       <c r="E164" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="F164" s="17" t="s">
+      <c r="F164" s="15" t="s">
         <v>666</v>
       </c>
       <c r="G164" s="3" t="s">
@@ -21155,7 +21155,7 @@
       <c r="E165" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="F165" s="17" t="s">
+      <c r="F165" s="15" t="s">
         <v>774</v>
       </c>
       <c r="G165" s="3" t="s">
@@ -21221,7 +21221,7 @@
       <c r="E166" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F166" s="17" t="s">
+      <c r="F166" s="15" t="s">
         <v>677</v>
       </c>
       <c r="G166" s="3" t="s">
@@ -21283,7 +21283,7 @@
       <c r="E167" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="F167" s="17" t="s">
+      <c r="F167" s="15" t="s">
         <v>318</v>
       </c>
       <c r="G167" s="3" t="s">
@@ -21345,7 +21345,7 @@
       <c r="E168" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="F168" s="17" t="s">
+      <c r="F168" s="15" t="s">
         <v>687</v>
       </c>
       <c r="G168" s="3" t="s">
@@ -21411,7 +21411,7 @@
       <c r="E169" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F169" s="17" t="s">
+      <c r="F169" s="15" t="s">
         <v>693</v>
       </c>
       <c r="G169" s="3" t="s">
@@ -21477,7 +21477,7 @@
       <c r="E170" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F170" s="17" t="s">
+      <c r="F170" s="15" t="s">
         <v>699</v>
       </c>
       <c r="G170" s="3" t="s">
@@ -21541,7 +21541,7 @@
       <c r="E171" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="F171" s="17" t="s">
+      <c r="F171" s="15" t="s">
         <v>705</v>
       </c>
       <c r="G171" s="3" t="s">
@@ -21605,7 +21605,7 @@
       <c r="E172" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="F172" s="17" t="s">
+      <c r="F172" s="15" t="s">
         <v>711</v>
       </c>
       <c r="G172" s="3" t="s">
@@ -21667,7 +21667,7 @@
       <c r="E173" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="F173" s="17" t="s">
+      <c r="F173" s="15" t="s">
         <v>717</v>
       </c>
       <c r="G173" s="3" t="s">
@@ -21729,7 +21729,7 @@
       <c r="E174" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="F174" s="17" t="s">
+      <c r="F174" s="15" t="s">
         <v>723</v>
       </c>
       <c r="G174" s="3" t="s">
@@ -21791,7 +21791,7 @@
       <c r="E175" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="F175" s="17" t="s">
+      <c r="F175" s="15" t="s">
         <v>729</v>
       </c>
       <c r="G175" s="3" t="s">
@@ -21853,7 +21853,7 @@
       <c r="E176" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="F176" s="17" t="s">
+      <c r="F176" s="15" t="s">
         <v>735</v>
       </c>
       <c r="G176" s="3" t="s">
@@ -21915,7 +21915,7 @@
       <c r="E177" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="F177" s="17" t="s">
+      <c r="F177" s="15" t="s">
         <v>741</v>
       </c>
       <c r="G177" s="3" t="s">
@@ -21977,7 +21977,7 @@
       <c r="E178" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F178" s="17" t="s">
+      <c r="F178" s="15" t="s">
         <v>746</v>
       </c>
       <c r="G178" s="3" t="s">
@@ -22039,7 +22039,7 @@
       <c r="E179" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="F179" s="17" t="s">
+      <c r="F179" s="15" t="s">
         <v>2929</v>
       </c>
       <c r="G179" s="3" t="s">
@@ -22101,7 +22101,7 @@
       <c r="E180" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="F180" s="17" t="s">
+      <c r="F180" s="15" t="s">
         <v>757</v>
       </c>
       <c r="G180" s="3" t="s">
@@ -22163,7 +22163,7 @@
       <c r="E181" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F181" s="17" t="s">
+      <c r="F181" s="15" t="s">
         <v>762</v>
       </c>
       <c r="G181" s="3" t="s">
@@ -22227,7 +22227,7 @@
       <c r="E182" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="F182" s="17" t="s">
+      <c r="F182" s="15" t="s">
         <v>768</v>
       </c>
       <c r="G182" s="3" t="s">
@@ -22289,7 +22289,7 @@
       <c r="E183" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="F183" s="17" t="s">
+      <c r="F183" s="15" t="s">
         <v>780</v>
       </c>
       <c r="G183" s="3" t="s">
@@ -22351,7 +22351,7 @@
       <c r="E184" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="F184" s="17" t="s">
+      <c r="F184" s="15" t="s">
         <v>780</v>
       </c>
       <c r="G184" s="3" t="s">
@@ -22417,7 +22417,7 @@
       <c r="E185" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="F185" s="17" t="s">
+      <c r="F185" s="15" t="s">
         <v>787</v>
       </c>
       <c r="G185" s="3" t="s">
@@ -22479,7 +22479,7 @@
       <c r="E186" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="F186" s="17" t="s">
+      <c r="F186" s="15" t="s">
         <v>787</v>
       </c>
       <c r="G186" s="3" t="s">
@@ -22541,7 +22541,7 @@
       <c r="E187" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="F187" s="17" t="s">
+      <c r="F187" s="15" t="s">
         <v>787</v>
       </c>
       <c r="G187" s="3" t="s">
@@ -22603,7 +22603,7 @@
       <c r="E188" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F188" s="17" t="s">
+      <c r="F188" s="15" t="s">
         <v>787</v>
       </c>
       <c r="G188" s="3" t="s">
@@ -22665,7 +22665,7 @@
       <c r="E189" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="F189" s="17" t="s">
+      <c r="F189" s="15" t="s">
         <v>812</v>
       </c>
       <c r="G189" s="3" t="s">
@@ -22727,7 +22727,7 @@
       <c r="E190" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="F190" s="17" t="s">
+      <c r="F190" s="15" t="s">
         <v>818</v>
       </c>
       <c r="G190" s="3" t="s">
@@ -22789,7 +22789,7 @@
       <c r="E191" s="3" t="s">
         <v>1709</v>
       </c>
-      <c r="F191" s="17" t="s">
+      <c r="F191" s="15" t="s">
         <v>2379</v>
       </c>
       <c r="G191" s="3" t="s">
@@ -22851,7 +22851,7 @@
       <c r="E192" s="3" t="s">
         <v>2340</v>
       </c>
-      <c r="F192" s="17" t="s">
+      <c r="F192" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G192" s="3" t="s">
@@ -22915,7 +22915,7 @@
       <c r="E193" s="3" t="s">
         <v>2347</v>
       </c>
-      <c r="F193" s="17" t="s">
+      <c r="F193" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G193" s="3" t="s">
@@ -22981,7 +22981,7 @@
       <c r="E194" s="3" t="s">
         <v>2352</v>
       </c>
-      <c r="F194" s="17" t="s">
+      <c r="F194" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G194" s="3" t="s">
@@ -23047,7 +23047,7 @@
       <c r="E195" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F195" s="17" t="s">
+      <c r="F195" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G195" s="3" t="s">
@@ -23113,7 +23113,7 @@
       <c r="E196" s="3" t="s">
         <v>2226</v>
       </c>
-      <c r="F196" s="17" t="s">
+      <c r="F196" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G196" s="3" t="s">
@@ -23179,7 +23179,7 @@
       <c r="E197" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F197" s="17" t="s">
+      <c r="F197" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G197" s="3" t="s">
@@ -23245,7 +23245,7 @@
       <c r="E198" s="3" t="s">
         <v>2369</v>
       </c>
-      <c r="F198" s="17" t="s">
+      <c r="F198" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G198" s="3" t="s">
@@ -23311,7 +23311,7 @@
       <c r="E199" s="3" t="s">
         <v>2374</v>
       </c>
-      <c r="F199" s="17" t="s">
+      <c r="F199" s="15" t="s">
         <v>2341</v>
       </c>
       <c r="G199" s="3" t="s">
@@ -23377,7 +23377,7 @@
       <c r="E200" s="3" t="s">
         <v>1650</v>
       </c>
-      <c r="F200" s="17" t="s">
+      <c r="F200" s="15" t="s">
         <v>2309</v>
       </c>
       <c r="G200" s="3" t="s">
@@ -23441,7 +23441,7 @@
       <c r="E201" s="3" t="s">
         <v>2315</v>
       </c>
-      <c r="F201" s="17" t="s">
+      <c r="F201" s="15" t="s">
         <v>2316</v>
       </c>
       <c r="G201" s="3" t="s">
@@ -23503,7 +23503,7 @@
       <c r="E202" s="3" t="s">
         <v>2321</v>
       </c>
-      <c r="F202" s="17" t="s">
+      <c r="F202" s="15" t="s">
         <v>2322</v>
       </c>
       <c r="G202" s="3" t="s">
@@ -23567,7 +23567,7 @@
       <c r="E203" s="3" t="s">
         <v>2328</v>
       </c>
-      <c r="F203" s="17" t="s">
+      <c r="F203" s="15" t="s">
         <v>2329</v>
       </c>
       <c r="G203" s="3" t="s">
@@ -23633,7 +23633,7 @@
       <c r="E204" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="F204" s="17" t="s">
+      <c r="F204" s="15" t="s">
         <v>2335</v>
       </c>
       <c r="G204" s="3" t="s">
@@ -23699,7 +23699,7 @@
       <c r="E205" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="F205" s="17" t="s">
+      <c r="F205" s="15" t="s">
         <v>3442</v>
       </c>
       <c r="G205" s="3" t="s">
@@ -23765,7 +23765,7 @@
       <c r="E206" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="F206" s="17" t="s">
+      <c r="F206" s="15" t="s">
         <v>824</v>
       </c>
       <c r="G206" s="3" t="s">
@@ -23831,7 +23831,7 @@
       <c r="E207" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="F207" s="17" t="s">
+      <c r="F207" s="15" t="s">
         <v>824</v>
       </c>
       <c r="G207" s="3" t="s">
@@ -23895,7 +23895,7 @@
       <c r="E208" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="F208" s="17" t="s">
+      <c r="F208" s="15" t="s">
         <v>836</v>
       </c>
       <c r="G208" s="3" t="s">
@@ -23957,7 +23957,7 @@
       <c r="E209" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="F209" s="17" t="s">
+      <c r="F209" s="15" t="s">
         <v>843</v>
       </c>
       <c r="G209" s="3" t="s">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
-      <c r="F210" s="17" t="s">
+      <c r="F210" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G210" s="3" t="s">
@@ -24071,7 +24071,7 @@
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
-      <c r="F211" s="17" t="s">
+      <c r="F211" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G211" s="3" t="s">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
-      <c r="F212" s="17" t="s">
+      <c r="F212" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G212" s="3" t="s">
@@ -24187,7 +24187,7 @@
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
-      <c r="F213" s="17" t="s">
+      <c r="F213" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G213" s="3" t="s">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
-      <c r="F214" s="17" t="s">
+      <c r="F214" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G214" s="3" t="s">
@@ -24303,7 +24303,7 @@
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
-      <c r="F215" s="17" t="s">
+      <c r="F215" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G215" s="3" t="s">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
-      <c r="F216" s="17" t="s">
+      <c r="F216" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G216" s="3" t="s">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
-      <c r="F217" s="17" t="s">
+      <c r="F217" s="15" t="s">
         <v>870</v>
       </c>
       <c r="G217" s="3" t="s">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
-      <c r="F218" s="17" t="s">
+      <c r="F218" s="15" t="s">
         <v>870</v>
       </c>
       <c r="G218" s="3" t="s">
@@ -24539,7 +24539,7 @@
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
-      <c r="F219" s="17" t="s">
+      <c r="F219" s="15" t="s">
         <v>870</v>
       </c>
       <c r="G219" s="3" t="s">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
-      <c r="F220" s="17" t="s">
+      <c r="F220" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G220" s="3" t="s">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
-      <c r="F221" s="17" t="s">
+      <c r="F221" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G221" s="3" t="s">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
-      <c r="F222" s="17" t="s">
+      <c r="F222" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G222" s="3" t="s">
@@ -24773,7 +24773,7 @@
       <c r="E223" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="F223" s="17" t="s">
+      <c r="F223" s="15" t="s">
         <v>870</v>
       </c>
       <c r="G223" s="3" t="s">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
-      <c r="F224" s="17" t="s">
+      <c r="F224" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G224" s="3" t="s">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
-      <c r="F225" s="17" t="s">
+      <c r="F225" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G225" s="3" t="s">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
-      <c r="F226" s="17" t="s">
+      <c r="F226" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G226" s="3" t="s">
@@ -25011,7 +25011,7 @@
       <c r="E227" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="F227" s="17" t="s">
+      <c r="F227" s="15" t="s">
         <v>847</v>
       </c>
       <c r="G227" s="3" t="s">
@@ -25067,7 +25067,7 @@
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
-      <c r="F228" s="17" t="s">
+      <c r="F228" s="15" t="s">
         <v>914</v>
       </c>
       <c r="G228" s="3" t="s">
@@ -25127,7 +25127,7 @@
       </c>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
-      <c r="F229" s="17" t="s">
+      <c r="F229" s="15" t="s">
         <v>922</v>
       </c>
       <c r="G229" s="3" t="s">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
-      <c r="F230" s="17" t="s">
+      <c r="F230" s="15" t="s">
         <v>922</v>
       </c>
       <c r="G230" s="3" t="s">
@@ -25249,7 +25249,7 @@
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
-      <c r="F231" s="17" t="s">
+      <c r="F231" s="15" t="s">
         <v>922</v>
       </c>
       <c r="G231" s="3" t="s">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
-      <c r="F232" s="17" t="s">
+      <c r="F232" s="15" t="s">
         <v>922</v>
       </c>
       <c r="G232" s="3" t="s">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
-      <c r="F233" s="17" t="s">
+      <c r="F233" s="15" t="s">
         <v>936</v>
       </c>
       <c r="G233" s="3" t="s">
@@ -25427,7 +25427,7 @@
       <c r="E234" s="3" t="s">
         <v>1039</v>
       </c>
-      <c r="F234" s="17" t="s">
+      <c r="F234" s="15" t="s">
         <v>1282</v>
       </c>
       <c r="G234" s="3" t="s">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
-      <c r="F235" s="17" t="s">
+      <c r="F235" s="15" t="s">
         <v>947</v>
       </c>
       <c r="G235" s="3" t="s">
@@ -25557,7 +25557,7 @@
       <c r="E236" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F236" s="17" t="s">
+      <c r="F236" s="15" t="s">
         <v>954</v>
       </c>
       <c r="G236" s="3" t="s">
@@ -25623,7 +25623,7 @@
       <c r="E237" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="F237" s="17" t="s">
+      <c r="F237" s="15" t="s">
         <v>961</v>
       </c>
       <c r="G237" s="3" t="s">
@@ -25689,7 +25689,7 @@
       <c r="E238" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="F238" s="17" t="s">
+      <c r="F238" s="15" t="s">
         <v>954</v>
       </c>
       <c r="G238" s="3" t="s">
@@ -25755,7 +25755,7 @@
       <c r="E239" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="F239" s="17" t="s">
+      <c r="F239" s="15" t="s">
         <v>961</v>
       </c>
       <c r="G239" s="3" t="s">
@@ -25821,7 +25821,7 @@
       <c r="E240" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="F240" s="17" t="s">
+      <c r="F240" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G240" s="3" t="s">
@@ -25883,7 +25883,7 @@
       <c r="E241" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="F241" s="17" t="s">
+      <c r="F241" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G241" s="3" t="s">
@@ -25945,7 +25945,7 @@
       <c r="E242" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="F242" s="17" t="s">
+      <c r="F242" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G242" s="3" t="s">
@@ -26009,7 +26009,7 @@
       <c r="E243" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="F243" s="17" t="s">
+      <c r="F243" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G243" s="3" t="s">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
-      <c r="F244" s="17" t="s">
+      <c r="F244" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G244" s="3" t="s">
@@ -26127,7 +26127,7 @@
       <c r="E245" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="F245" s="17" t="s">
+      <c r="F245" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G245" s="3" t="s">
@@ -26191,7 +26191,7 @@
       <c r="E246" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="F246" s="17" t="s">
+      <c r="F246" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G246" s="3" t="s">
@@ -26255,7 +26255,7 @@
       <c r="E247" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="F247" s="17" t="s">
+      <c r="F247" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G247" s="3" t="s">
@@ -26319,7 +26319,7 @@
       <c r="E248" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="F248" s="17" t="s">
+      <c r="F248" s="15" t="s">
         <v>1010</v>
       </c>
       <c r="G248" s="3" t="s">
@@ -26385,7 +26385,7 @@
       <c r="E249" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="F249" s="17" t="s">
+      <c r="F249" s="15" t="s">
         <v>1010</v>
       </c>
       <c r="G249" s="3" t="s">
@@ -26449,7 +26449,7 @@
       <c r="E250" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="F250" s="17" t="s">
+      <c r="F250" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G250" s="3" t="s">
@@ -26509,7 +26509,7 @@
       <c r="E251" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="F251" s="17" t="s">
+      <c r="F251" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G251" s="3" t="s">
@@ -26569,7 +26569,7 @@
       <c r="E252" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F252" s="17" t="s">
+      <c r="F252" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G252" s="3" t="s">
@@ -26629,7 +26629,7 @@
       <c r="E253" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="F253" s="17" t="s">
+      <c r="F253" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G253" s="3" t="s">
@@ -26689,7 +26689,7 @@
       <c r="E254" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="F254" s="17" t="s">
+      <c r="F254" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G254" s="3" t="s">
@@ -26749,7 +26749,7 @@
       <c r="E255" s="3" t="s">
         <v>1039</v>
       </c>
-      <c r="F255" s="17" t="s">
+      <c r="F255" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G255" s="3" t="s">
@@ -26809,7 +26809,7 @@
       <c r="E256" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="F256" s="17" t="s">
+      <c r="F256" s="15" t="s">
         <v>1044</v>
       </c>
       <c r="G256" s="3" t="s">
@@ -26871,7 +26871,7 @@
       <c r="E257" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="F257" s="17" t="s">
+      <c r="F257" s="15" t="s">
         <v>978</v>
       </c>
       <c r="G257" s="3" t="s">
@@ -26927,7 +26927,7 @@
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
-      <c r="F258" s="17" t="s">
+      <c r="F258" s="15" t="s">
         <v>1053</v>
       </c>
       <c r="G258" s="3" t="s">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
-      <c r="F259" s="17" t="s">
+      <c r="F259" s="15" t="s">
         <v>2931</v>
       </c>
       <c r="G259" s="3" t="s">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
-      <c r="F260" s="17" t="s">
+      <c r="F260" s="15" t="s">
         <v>1064</v>
       </c>
       <c r="G260" s="3" t="s">
@@ -27111,7 +27111,7 @@
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
-      <c r="F261" s="17" t="s">
+      <c r="F261" s="15" t="s">
         <v>1069</v>
       </c>
       <c r="G261" s="3" t="s">
@@ -27173,7 +27173,7 @@
       <c r="E262" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="F262" s="17" t="s">
+      <c r="F262" s="15" t="s">
         <v>1075</v>
       </c>
       <c r="G262" s="3" t="s">
@@ -27235,7 +27235,7 @@
       <c r="E263" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F263" s="17" t="s">
+      <c r="F263" s="15" t="s">
         <v>1053</v>
       </c>
       <c r="G263" s="3" t="s">
@@ -27297,7 +27297,7 @@
       <c r="E264" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="F264" s="17" t="s">
+      <c r="F264" s="15" t="s">
         <v>1085</v>
       </c>
       <c r="G264" s="3" t="s">
@@ -27361,7 +27361,7 @@
       <c r="E265" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="F265" s="17" t="s">
+      <c r="F265" s="15" t="s">
         <v>1092</v>
       </c>
       <c r="G265" s="3" t="s">
@@ -27425,7 +27425,7 @@
       <c r="E266" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="F266" s="17" t="s">
+      <c r="F266" s="15" t="s">
         <v>1092</v>
       </c>
       <c r="G266" s="3" t="s">
@@ -27485,7 +27485,7 @@
       <c r="E267" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F267" s="17" t="s">
+      <c r="F267" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="G267" s="3" t="s">
@@ -27551,7 +27551,7 @@
       <c r="E268" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="F268" s="17" t="s">
+      <c r="F268" s="15" t="s">
         <v>1108</v>
       </c>
       <c r="G268" s="3" t="s">
@@ -27617,7 +27617,7 @@
       <c r="E269" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="F269" s="17" t="s">
+      <c r="F269" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="G269" s="3" t="s">
@@ -27683,7 +27683,7 @@
       <c r="E270" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="F270" s="17" t="s">
+      <c r="F270" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G270" s="3" t="s">
@@ -27747,7 +27747,7 @@
       <c r="E271" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="F271" s="17" t="s">
+      <c r="F271" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="G271" s="3" t="s">
@@ -27813,7 +27813,7 @@
       <c r="E272" s="3" t="s">
         <v>1128</v>
       </c>
-      <c r="F272" s="17" t="s">
+      <c r="F272" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G272" s="3" t="s">
@@ -27875,7 +27875,7 @@
       <c r="E273" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="F273" s="17" t="s">
+      <c r="F273" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G273" s="3" t="s">
@@ -27937,7 +27937,7 @@
       <c r="E274" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="F274" s="17" t="s">
+      <c r="F274" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G274" s="3" t="s">
@@ -27997,7 +27997,7 @@
       <c r="E275" s="3" t="s">
         <v>1140</v>
       </c>
-      <c r="F275" s="17" t="s">
+      <c r="F275" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G275" s="3" t="s">
@@ -28061,7 +28061,7 @@
       <c r="E276" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="F276" s="17" t="s">
+      <c r="F276" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G276" s="3" t="s">
@@ -28123,7 +28123,7 @@
       <c r="E277" s="3" t="s">
         <v>1148</v>
       </c>
-      <c r="F277" s="17" t="s">
+      <c r="F277" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G277" s="3" t="s">
@@ -28187,7 +28187,7 @@
       <c r="E278" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="F278" s="17" t="s">
+      <c r="F278" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G278" s="3" t="s">
@@ -28249,7 +28249,7 @@
       <c r="E279" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="F279" s="17" t="s">
+      <c r="F279" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G279" s="3" t="s">
@@ -28311,7 +28311,7 @@
       <c r="E280" s="3" t="s">
         <v>1161</v>
       </c>
-      <c r="F280" s="17" t="s">
+      <c r="F280" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G280" s="3" t="s">
@@ -28373,7 +28373,7 @@
       <c r="E281" s="3" t="s">
         <v>1165</v>
       </c>
-      <c r="F281" s="17" t="s">
+      <c r="F281" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G281" s="3" t="s">
@@ -28435,7 +28435,7 @@
       <c r="E282" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="F282" s="17" t="s">
+      <c r="F282" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G282" s="3" t="s">
@@ -28495,7 +28495,7 @@
       <c r="E283" s="3" t="s">
         <v>1173</v>
       </c>
-      <c r="F283" s="17" t="s">
+      <c r="F283" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G283" s="3" t="s">
@@ -28555,7 +28555,7 @@
       <c r="E284" s="3" t="s">
         <v>1177</v>
       </c>
-      <c r="F284" s="17" t="s">
+      <c r="F284" s="15" t="s">
         <v>1178</v>
       </c>
       <c r="G284" s="3" t="s">
@@ -28619,7 +28619,7 @@
       <c r="E285" s="3" t="s">
         <v>1183</v>
       </c>
-      <c r="F285" s="17" t="s">
+      <c r="F285" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G285" s="3" t="s">
@@ -28679,7 +28679,7 @@
       <c r="E286" s="3" t="s">
         <v>1187</v>
       </c>
-      <c r="F286" s="17" t="s">
+      <c r="F286" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G286" s="3" t="s">
@@ -28739,7 +28739,7 @@
       <c r="E287" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="F287" s="17" t="s">
+      <c r="F287" s="15" t="s">
         <v>1192</v>
       </c>
       <c r="G287" s="3" t="s">
@@ -28801,7 +28801,7 @@
       <c r="E288" s="3" t="s">
         <v>1197</v>
       </c>
-      <c r="F288" s="17" t="s">
+      <c r="F288" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="G288" s="3" t="s">
@@ -28863,7 +28863,7 @@
       <c r="E289" s="3" t="s">
         <v>1202</v>
       </c>
-      <c r="F289" s="17" t="s">
+      <c r="F289" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G289" s="3" t="s">
@@ -28923,7 +28923,7 @@
       <c r="E290" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F290" s="17" t="s">
+      <c r="F290" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G290" s="3" t="s">
@@ -28983,7 +28983,7 @@
       <c r="E291" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F291" s="17" t="s">
+      <c r="F291" s="15" t="s">
         <v>1209</v>
       </c>
       <c r="G291" s="3" t="s">
@@ -29045,7 +29045,7 @@
       <c r="E292" s="3" t="s">
         <v>1214</v>
       </c>
-      <c r="F292" s="17" t="s">
+      <c r="F292" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G292" s="3" t="s">
@@ -29105,7 +29105,7 @@
       <c r="E293" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="F293" s="17" t="s">
+      <c r="F293" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G293" s="3" t="s">
@@ -29165,7 +29165,7 @@
       <c r="E294" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="F294" s="17" t="s">
+      <c r="F294" s="15" t="s">
         <v>1192</v>
       </c>
       <c r="G294" s="3" t="s">
@@ -29227,7 +29227,7 @@
       <c r="E295" s="3" t="s">
         <v>1227</v>
       </c>
-      <c r="F295" s="17" t="s">
+      <c r="F295" s="15" t="s">
         <v>1119</v>
       </c>
       <c r="G295" s="3" t="s">
@@ -29287,7 +29287,7 @@
       <c r="E296" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="F296" s="17" t="s">
+      <c r="F296" s="15" t="s">
         <v>1232</v>
       </c>
       <c r="G296" s="3" t="s">
@@ -29353,7 +29353,7 @@
       <c r="E297" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="F297" s="17" t="s">
+      <c r="F297" s="15" t="s">
         <v>1240</v>
       </c>
       <c r="G297" s="3" t="s">
@@ -29417,7 +29417,7 @@
       <c r="E298" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="F298" s="17" t="s">
+      <c r="F298" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G298" s="3" t="s">
@@ -29483,7 +29483,7 @@
       <c r="E299" s="3" t="s">
         <v>1252</v>
       </c>
-      <c r="F299" s="17" t="s">
+      <c r="F299" s="15" t="s">
         <v>1240</v>
       </c>
       <c r="G299" s="3" t="s">
@@ -29547,7 +29547,7 @@
       <c r="E300" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="F300" s="17" t="s">
+      <c r="F300" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G300" s="3" t="s">
@@ -29613,7 +29613,7 @@
       <c r="E301" s="3" t="s">
         <v>1262</v>
       </c>
-      <c r="F301" s="17" t="s">
+      <c r="F301" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G301" s="3" t="s">
@@ -29677,7 +29677,7 @@
       <c r="E302" s="3" t="s">
         <v>1262</v>
       </c>
-      <c r="F302" s="17" t="s">
+      <c r="F302" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G302" s="3" t="s">
@@ -29739,7 +29739,7 @@
       <c r="E303" s="3" t="s">
         <v>1269</v>
       </c>
-      <c r="F303" s="17" t="s">
+      <c r="F303" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G303" s="3" t="s">
@@ -29801,7 +29801,7 @@
       <c r="E304" s="3" t="s">
         <v>1273</v>
       </c>
-      <c r="F304" s="17" t="s">
+      <c r="F304" s="15" t="s">
         <v>1274</v>
       </c>
       <c r="G304" s="3" t="s">
@@ -29865,7 +29865,7 @@
       <c r="E305" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F305" s="17" t="s">
+      <c r="F305" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="G305" s="3" t="s">
@@ -29925,7 +29925,7 @@
       <c r="E306" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F306" s="17" t="s">
+      <c r="F306" s="15" t="s">
         <v>1806</v>
       </c>
       <c r="G306" s="3" t="s">
@@ -29993,7 +29993,7 @@
       <c r="E307" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="F307" s="17" t="s">
+      <c r="F307" s="15" t="s">
         <v>1481</v>
       </c>
       <c r="G307" s="3" t="s">
@@ -30059,7 +30059,7 @@
       <c r="E308" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="F308" s="17" t="s">
+      <c r="F308" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G308" s="3" t="s">
@@ -30123,7 +30123,7 @@
       <c r="E309" s="3" t="s">
         <v>1295</v>
       </c>
-      <c r="F309" s="17" t="s">
+      <c r="F309" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G309" s="3" t="s">
@@ -30187,7 +30187,7 @@
       <c r="E310" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="F310" s="17" t="s">
+      <c r="F310" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G310" s="3" t="s">
@@ -30249,7 +30249,7 @@
       <c r="E311" s="3" t="s">
         <v>1301</v>
       </c>
-      <c r="F311" s="17" t="s">
+      <c r="F311" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G311" s="3" t="s">
@@ -30313,7 +30313,7 @@
       <c r="E312" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="F312" s="17" t="s">
+      <c r="F312" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G312" s="3" t="s">
@@ -30375,7 +30375,7 @@
       <c r="E313" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="F313" s="17" t="s">
+      <c r="F313" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G313" s="3" t="s">
@@ -30435,7 +30435,7 @@
       <c r="E314" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="F314" s="17" t="s">
+      <c r="F314" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G314" s="3" t="s">
@@ -30495,7 +30495,7 @@
       <c r="E315" s="3" t="s">
         <v>1318</v>
       </c>
-      <c r="F315" s="17" t="s">
+      <c r="F315" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G315" s="3" t="s">
@@ -30553,7 +30553,7 @@
       </c>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
-      <c r="F316" s="17" t="s">
+      <c r="F316" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G316" s="3" t="s">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
-      <c r="F317" s="17" t="s">
+      <c r="F317" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G317" s="3" t="s">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
-      <c r="F318" s="17" t="s">
+      <c r="F318" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G318" s="3" t="s">
@@ -30721,7 +30721,7 @@
       </c>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
-      <c r="F319" s="17" t="s">
+      <c r="F319" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G319" s="3" t="s">
@@ -30781,7 +30781,7 @@
       <c r="E320" s="3" t="s">
         <v>1342</v>
       </c>
-      <c r="F320" s="17" t="s">
+      <c r="F320" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G320" s="3" t="s">
@@ -30843,7 +30843,7 @@
       <c r="E321" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="F321" s="17" t="s">
+      <c r="F321" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G321" s="3" t="s">
@@ -30905,7 +30905,7 @@
       <c r="E322" s="3" t="s">
         <v>1347</v>
       </c>
-      <c r="F322" s="17" t="s">
+      <c r="F322" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G322" s="3" t="s">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
-      <c r="F323" s="17" t="s">
+      <c r="F323" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G323" s="3" t="s">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
-      <c r="F324" s="17" t="s">
+      <c r="F324" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G324" s="3" t="s">
@@ -31079,7 +31079,7 @@
       <c r="E325" s="3" t="s">
         <v>1400</v>
       </c>
-      <c r="F325" s="17" t="s">
+      <c r="F325" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G325" s="3" t="s">
@@ -31139,7 +31139,7 @@
       <c r="E326" s="3" t="s">
         <v>1368</v>
       </c>
-      <c r="F326" s="17" t="s">
+      <c r="F326" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G326" s="3" t="s">
@@ -31201,7 +31201,7 @@
       <c r="E327" s="3" t="s">
         <v>1416</v>
       </c>
-      <c r="F327" s="17" t="s">
+      <c r="F327" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G327" s="3" t="s">
@@ -31263,7 +31263,7 @@
       <c r="E328" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F328" s="17" t="s">
+      <c r="F328" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G328" s="3" t="s">
@@ -31327,7 +31327,7 @@
       <c r="E329" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="F329" s="17" t="s">
+      <c r="F329" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G329" s="3" t="s">
@@ -31391,7 +31391,7 @@
       <c r="E330" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="F330" s="17" t="s">
+      <c r="F330" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G330" s="3" t="s">
@@ -31453,7 +31453,7 @@
       <c r="E331" s="3" t="s">
         <v>1269</v>
       </c>
-      <c r="F331" s="17" t="s">
+      <c r="F331" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G331" s="3" t="s">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
-      <c r="F332" s="17" t="s">
+      <c r="F332" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G332" s="3" t="s">
@@ -31569,7 +31569,7 @@
       </c>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
-      <c r="F333" s="17" t="s">
+      <c r="F333" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G333" s="3" t="s">
@@ -31627,7 +31627,7 @@
       </c>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
-      <c r="F334" s="17" t="s">
+      <c r="F334" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G334" s="3" t="s">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
-      <c r="F335" s="17" t="s">
+      <c r="F335" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G335" s="3" t="s">
@@ -31739,7 +31739,7 @@
       </c>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
-      <c r="F336" s="17" t="s">
+      <c r="F336" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G336" s="3" t="s">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
-      <c r="F337" s="17" t="s">
+      <c r="F337" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G337" s="3" t="s">
@@ -31855,7 +31855,7 @@
       <c r="E338" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F338" s="17" t="s">
+      <c r="F338" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G338" s="3" t="s">
@@ -31915,7 +31915,7 @@
       <c r="E339" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="F339" s="17" t="s">
+      <c r="F339" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G339" s="3" t="s">
@@ -31975,7 +31975,7 @@
       <c r="E340" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="F340" s="17" t="s">
+      <c r="F340" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G340" s="3" t="s">
@@ -32035,7 +32035,7 @@
       <c r="E341" s="3" t="s">
         <v>1338</v>
       </c>
-      <c r="F341" s="17" t="s">
+      <c r="F341" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G341" s="3" t="s">
@@ -32095,7 +32095,7 @@
       <c r="E342" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F342" s="17" t="s">
+      <c r="F342" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G342" s="3" t="s">
@@ -32157,7 +32157,7 @@
       <c r="E343" s="3" t="s">
         <v>1404</v>
       </c>
-      <c r="F343" s="17" t="s">
+      <c r="F343" s="15" t="s">
         <v>1405</v>
       </c>
       <c r="G343" s="3" t="s">
@@ -32223,7 +32223,7 @@
       <c r="E344" s="3" t="s">
         <v>1411</v>
       </c>
-      <c r="F344" s="17" t="s">
+      <c r="F344" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G344" s="3" t="s">
@@ -32289,7 +32289,7 @@
       <c r="E345" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F345" s="17" t="s">
+      <c r="F345" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G345" s="3" t="s">
@@ -32351,7 +32351,7 @@
       <c r="E346" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="F346" s="17" t="s">
+      <c r="F346" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G346" s="3" t="s">
@@ -32415,7 +32415,7 @@
       <c r="E347" s="3" t="s">
         <v>1430</v>
       </c>
-      <c r="F347" s="17" t="s">
+      <c r="F347" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G347" s="3" t="s">
@@ -32479,7 +32479,7 @@
       <c r="E348" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="F348" s="17" t="s">
+      <c r="F348" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G348" s="3" t="s">
@@ -32541,7 +32541,7 @@
       <c r="E349" s="3" t="s">
         <v>1467</v>
       </c>
-      <c r="F349" s="17" t="s">
+      <c r="F349" s="15" t="s">
         <v>1468</v>
       </c>
       <c r="G349" s="3" t="s">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
-      <c r="F350" s="17" t="s">
+      <c r="F350" s="15" t="s">
         <v>1473</v>
       </c>
       <c r="G350" s="3" t="s">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
-      <c r="F351" s="17" t="s">
+      <c r="F351" s="15" t="s">
         <v>1473</v>
       </c>
       <c r="G351" s="3" t="s">
@@ -32719,7 +32719,7 @@
       <c r="E352" s="3" t="s">
         <v>1577</v>
       </c>
-      <c r="F352" s="17" t="s">
+      <c r="F352" s="15" t="s">
         <v>1578</v>
       </c>
       <c r="G352" s="3" t="s">
@@ -32785,7 +32785,7 @@
       <c r="E353" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="F353" s="17" t="s">
+      <c r="F353" s="15" t="s">
         <v>1468</v>
       </c>
       <c r="G353" s="3" t="s">
@@ -32851,7 +32851,7 @@
       <c r="E354" s="3" t="s">
         <v>1492</v>
       </c>
-      <c r="F354" s="17" t="s">
+      <c r="F354" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G354" s="3" t="s">
@@ -32913,7 +32913,7 @@
       <c r="E355" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="F355" s="17" t="s">
+      <c r="F355" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G355" s="3" t="s">
@@ -32975,7 +32975,7 @@
       <c r="E356" s="3" t="s">
         <v>1442</v>
       </c>
-      <c r="F356" s="17" t="s">
+      <c r="F356" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G356" s="3" t="s">
@@ -33035,7 +33035,7 @@
       <c r="E357" s="3" t="s">
         <v>1500</v>
       </c>
-      <c r="F357" s="17" t="s">
+      <c r="F357" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G357" s="3" t="s">
@@ -33095,7 +33095,7 @@
       <c r="E358" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="F358" s="17" t="s">
+      <c r="F358" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G358" s="3" t="s">
@@ -33155,7 +33155,7 @@
       <c r="E359" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="F359" s="17" t="s">
+      <c r="F359" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G359" s="3" t="s">
@@ -33215,7 +33215,7 @@
       <c r="E360" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="F360" s="17" t="s">
+      <c r="F360" s="15" t="s">
         <v>1405</v>
       </c>
       <c r="G360" s="3" t="s">
@@ -33279,7 +33279,7 @@
       <c r="E361" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F361" s="17" t="s">
+      <c r="F361" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G361" s="3" t="s">
@@ -33341,7 +33341,7 @@
       <c r="E362" s="3" t="s">
         <v>1520</v>
       </c>
-      <c r="F362" s="17" t="s">
+      <c r="F362" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G362" s="3" t="s">
@@ -33405,7 +33405,7 @@
       <c r="E363" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="F363" s="17" t="s">
+      <c r="F363" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G363" s="3" t="s">
@@ -33467,7 +33467,7 @@
       <c r="E364" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F364" s="17" t="s">
+      <c r="F364" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G364" s="3" t="s">
@@ -33529,7 +33529,7 @@
       <c r="E365" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F365" s="17" t="s">
+      <c r="F365" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G365" s="3" t="s">
@@ -33591,7 +33591,7 @@
       <c r="E366" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="F366" s="17" t="s">
+      <c r="F366" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G366" s="3" t="s">
@@ -33655,7 +33655,7 @@
       <c r="E367" s="3" t="s">
         <v>1536</v>
       </c>
-      <c r="F367" s="17" t="s">
+      <c r="F367" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G367" s="3" t="s">
@@ -33715,7 +33715,7 @@
       <c r="E368" s="3" t="s">
         <v>1404</v>
       </c>
-      <c r="F368" s="17" t="s">
+      <c r="F368" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G368" s="3" t="s">
@@ -33777,7 +33777,7 @@
       <c r="E369" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="F369" s="17" t="s">
+      <c r="F369" s="15" t="s">
         <v>1543</v>
       </c>
       <c r="G369" s="3" t="s">
@@ -33839,7 +33839,7 @@
       <c r="E370" s="3" t="s">
         <v>1548</v>
       </c>
-      <c r="F370" s="17" t="s">
+      <c r="F370" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G370" s="3" t="s">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
-      <c r="F371" s="17" t="s">
+      <c r="F371" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G371" s="3" t="s">
@@ -33951,7 +33951,7 @@
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
-      <c r="F372" s="17" t="s">
+      <c r="F372" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G372" s="3" t="s">
@@ -34011,7 +34011,7 @@
       <c r="E373" s="3" t="s">
         <v>1459</v>
       </c>
-      <c r="F373" s="17" t="s">
+      <c r="F373" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G373" s="3" t="s">
@@ -34071,7 +34071,7 @@
       <c r="E374" s="3" t="s">
         <v>1404</v>
       </c>
-      <c r="F374" s="17" t="s">
+      <c r="F374" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G374" s="3" t="s">
@@ -34131,7 +34131,7 @@
       <c r="E375" s="3" t="s">
         <v>1463</v>
       </c>
-      <c r="F375" s="17" t="s">
+      <c r="F375" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G375" s="3" t="s">
@@ -34191,7 +34191,7 @@
       <c r="E376" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="F376" s="17" t="s">
+      <c r="F376" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G376" s="3" t="s">
@@ -34251,7 +34251,7 @@
       <c r="E377" s="3" t="s">
         <v>1559</v>
       </c>
-      <c r="F377" s="17" t="s">
+      <c r="F377" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G377" s="3" t="s">
@@ -34311,7 +34311,7 @@
       <c r="E378" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="F378" s="17" t="s">
+      <c r="F378" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G378" s="3" t="s">
@@ -34371,7 +34371,7 @@
       <c r="E379" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F379" s="17" t="s">
+      <c r="F379" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G379" s="3" t="s">
@@ -34431,7 +34431,7 @@
       <c r="E380" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="F380" s="17" t="s">
+      <c r="F380" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G380" s="3" t="s">
@@ -34491,7 +34491,7 @@
       <c r="E381" s="3" t="s">
         <v>1573</v>
       </c>
-      <c r="F381" s="17" t="s">
+      <c r="F381" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G381" s="3" t="s">
@@ -34551,7 +34551,7 @@
       <c r="E382" s="3" t="s">
         <v>1768</v>
       </c>
-      <c r="F382" s="17" t="s">
+      <c r="F382" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G382" s="3" t="s">
@@ -34613,7 +34613,7 @@
       <c r="E383" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="F383" s="17" t="s">
+      <c r="F383" s="15" t="s">
         <v>1801</v>
       </c>
       <c r="G383" s="3" t="s">
@@ -34675,7 +34675,7 @@
       <c r="E384" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F384" s="17" t="s">
+      <c r="F384" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G384" s="3" t="s">
@@ -34741,7 +34741,7 @@
       <c r="E385" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="F385" s="17" t="s">
+      <c r="F385" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G385" s="3" t="s">
@@ -34803,7 +34803,7 @@
       <c r="E386" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="F386" s="17" t="s">
+      <c r="F386" s="15" t="s">
         <v>1405</v>
       </c>
       <c r="G386" s="3" t="s">
@@ -34867,7 +34867,7 @@
       <c r="E387" s="3" t="s">
         <v>1598</v>
       </c>
-      <c r="F387" s="17" t="s">
+      <c r="F387" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G387" s="3" t="s">
@@ -34931,7 +34931,7 @@
       <c r="E388" s="3" t="s">
         <v>1602</v>
       </c>
-      <c r="F388" s="17" t="s">
+      <c r="F388" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G388" s="3" t="s">
@@ -34991,7 +34991,7 @@
       <c r="E389" s="3" t="s">
         <v>1606</v>
       </c>
-      <c r="F389" s="17" t="s">
+      <c r="F389" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G389" s="3" t="s">
@@ -35051,7 +35051,7 @@
       <c r="E390" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="F390" s="17" t="s">
+      <c r="F390" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G390" s="3" t="s">
@@ -35111,7 +35111,7 @@
       <c r="E391" s="3" t="s">
         <v>1613</v>
       </c>
-      <c r="F391" s="17" t="s">
+      <c r="F391" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G391" s="3" t="s">
@@ -35171,7 +35171,7 @@
       <c r="E392" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="F392" s="17" t="s">
+      <c r="F392" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G392" s="3" t="s">
@@ -35233,7 +35233,7 @@
       <c r="E393" s="3" t="s">
         <v>1622</v>
       </c>
-      <c r="F393" s="17" t="s">
+      <c r="F393" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G393" s="3" t="s">
@@ -35295,7 +35295,7 @@
       <c r="E394" s="3" t="s">
         <v>1626</v>
       </c>
-      <c r="F394" s="17" t="s">
+      <c r="F394" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G394" s="3" t="s">
@@ -35355,7 +35355,7 @@
       <c r="E395" s="3" t="s">
         <v>1630</v>
       </c>
-      <c r="F395" s="17" t="s">
+      <c r="F395" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G395" s="3" t="s">
@@ -35415,7 +35415,7 @@
       <c r="E396" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="F396" s="17" t="s">
+      <c r="F396" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G396" s="3" t="s">
@@ -35479,7 +35479,7 @@
       <c r="E397" s="3" t="s">
         <v>1639</v>
       </c>
-      <c r="F397" s="17" t="s">
+      <c r="F397" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G397" s="3" t="s">
@@ -35539,7 +35539,7 @@
       <c r="E398" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="F398" s="17" t="s">
+      <c r="F398" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G398" s="3" t="s">
@@ -35601,7 +35601,7 @@
       <c r="E399" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F399" s="17" t="s">
+      <c r="F399" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G399" s="3" t="s">
@@ -35661,7 +35661,7 @@
       <c r="E400" s="3" t="s">
         <v>1650</v>
       </c>
-      <c r="F400" s="17" t="s">
+      <c r="F400" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G400" s="3" t="s">
@@ -35725,7 +35725,7 @@
       <c r="E401" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F401" s="17" t="s">
+      <c r="F401" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G401" s="3" t="s">
@@ -35787,7 +35787,7 @@
       <c r="E402" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="F402" s="17" t="s">
+      <c r="F402" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G402" s="3" t="s">
@@ -35849,7 +35849,7 @@
       <c r="E403" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F403" s="17" t="s">
+      <c r="F403" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G403" s="3" t="s">
@@ -35913,7 +35913,7 @@
       <c r="E404" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="F404" s="17" t="s">
+      <c r="F404" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G404" s="3" t="s">
@@ -35975,7 +35975,7 @@
       <c r="E405" s="3" t="s">
         <v>1670</v>
       </c>
-      <c r="F405" s="17" t="s">
+      <c r="F405" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G405" s="3" t="s">
@@ -36035,7 +36035,7 @@
       <c r="E406" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="F406" s="17" t="s">
+      <c r="F406" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G406" s="3" t="s">
@@ -36095,7 +36095,7 @@
       <c r="E407" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F407" s="17" t="s">
+      <c r="F407" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G407" s="3" t="s">
@@ -36155,7 +36155,7 @@
       <c r="E408" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="F408" s="17" t="s">
+      <c r="F408" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G408" s="3" t="s">
@@ -36215,7 +36215,7 @@
       <c r="E409" s="3" t="s">
         <v>1683</v>
       </c>
-      <c r="F409" s="17" t="s">
+      <c r="F409" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G409" s="3" t="s">
@@ -36275,7 +36275,7 @@
       <c r="E410" s="3" t="s">
         <v>1687</v>
       </c>
-      <c r="F410" s="17" t="s">
+      <c r="F410" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G410" s="3" t="s">
@@ -36335,7 +36335,7 @@
       <c r="E411" s="3" t="s">
         <v>1691</v>
       </c>
-      <c r="F411" s="17" t="s">
+      <c r="F411" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G411" s="3" t="s">
@@ -36395,7 +36395,7 @@
       <c r="E412" s="3" t="s">
         <v>1695</v>
       </c>
-      <c r="F412" s="17" t="s">
+      <c r="F412" s="15" t="s">
         <v>1696</v>
       </c>
       <c r="G412" s="3" t="s">
@@ -36461,7 +36461,7 @@
       <c r="E413" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="F413" s="17" t="s">
+      <c r="F413" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G413" s="3" t="s">
@@ -36521,7 +36521,7 @@
       <c r="E414" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F414" s="17" t="s">
+      <c r="F414" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G414" s="3" t="s">
@@ -36581,7 +36581,7 @@
       <c r="E415" s="3" t="s">
         <v>1709</v>
       </c>
-      <c r="F415" s="17" t="s">
+      <c r="F415" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G415" s="3" t="s">
@@ -36645,7 +36645,7 @@
       <c r="E416" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="F416" s="17" t="s">
+      <c r="F416" s="15" t="s">
         <v>1715</v>
       </c>
       <c r="G416" s="3" t="s">
@@ -36707,7 +36707,7 @@
       <c r="E417" s="3" t="s">
         <v>1719</v>
       </c>
-      <c r="F417" s="17" t="s">
+      <c r="F417" s="15" t="s">
         <v>1720</v>
       </c>
       <c r="G417" s="3" t="s">
@@ -36769,7 +36769,7 @@
       <c r="E418" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="F418" s="17" t="s">
+      <c r="F418" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G418" s="3" t="s">
@@ -36831,7 +36831,7 @@
       <c r="E419" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="F419" s="17" t="s">
+      <c r="F419" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G419" s="3" t="s">
@@ -36891,7 +36891,7 @@
       <c r="E420" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F420" s="17" t="s">
+      <c r="F420" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G420" s="3" t="s">
@@ -36951,7 +36951,7 @@
       <c r="E421" s="3" t="s">
         <v>1736</v>
       </c>
-      <c r="F421" s="17" t="s">
+      <c r="F421" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G421" s="3" t="s">
@@ -37013,7 +37013,7 @@
       <c r="E422" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F422" s="17" t="s">
+      <c r="F422" s="15" t="s">
         <v>1720</v>
       </c>
       <c r="G422" s="3" t="s">
@@ -37077,7 +37077,7 @@
       <c r="E423" s="3" t="s">
         <v>1744</v>
       </c>
-      <c r="F423" s="17" t="s">
+      <c r="F423" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G423" s="3" t="s">
@@ -37139,7 +37139,7 @@
       <c r="E424" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F424" s="17" t="s">
+      <c r="F424" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G424" s="3" t="s">
@@ -37201,7 +37201,7 @@
       <c r="E425" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F425" s="17" t="s">
+      <c r="F425" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G425" s="3" t="s">
@@ -37261,7 +37261,7 @@
       <c r="E426" s="3" t="s">
         <v>1754</v>
       </c>
-      <c r="F426" s="17" t="s">
+      <c r="F426" s="15" t="s">
         <v>1701</v>
       </c>
       <c r="G426" s="3" t="s">
@@ -37321,7 +37321,7 @@
       <c r="E427" s="3" t="s">
         <v>1758</v>
       </c>
-      <c r="F427" s="17" t="s">
+      <c r="F427" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G427" s="3" t="s">
@@ -37383,7 +37383,7 @@
       <c r="E428" s="3" t="s">
         <v>1763</v>
       </c>
-      <c r="F428" s="17" t="s">
+      <c r="F428" s="15" t="s">
         <v>1468</v>
       </c>
       <c r="G428" s="3" t="s">
@@ -37449,7 +37449,7 @@
       <c r="E429" s="3" t="s">
         <v>1772</v>
       </c>
-      <c r="F429" s="17" t="s">
+      <c r="F429" s="15" t="s">
         <v>1290</v>
       </c>
       <c r="G429" s="3" t="s">
@@ -37511,7 +37511,7 @@
       <c r="E430" s="3" t="s">
         <v>1776</v>
       </c>
-      <c r="F430" s="17" t="s">
+      <c r="F430" s="15" t="s">
         <v>1405</v>
       </c>
       <c r="G430" s="3" t="s">
@@ -37573,7 +37573,7 @@
       <c r="E431" s="3" t="s">
         <v>1780</v>
       </c>
-      <c r="F431" s="17" t="s">
+      <c r="F431" s="15" t="s">
         <v>1781</v>
       </c>
       <c r="G431" s="3" t="s">
@@ -37637,7 +37637,7 @@
       <c r="E432" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="F432" s="17" t="s">
+      <c r="F432" s="15" t="s">
         <v>1296</v>
       </c>
       <c r="G432" s="3" t="s">
@@ -37697,7 +37697,7 @@
       <c r="E433" s="3" t="s">
         <v>1262</v>
       </c>
-      <c r="F433" s="17" t="s">
+      <c r="F433" s="15" t="s">
         <v>1781</v>
       </c>
       <c r="G433" s="3" t="s">
@@ -37759,7 +37759,7 @@
       <c r="E434" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="F434" s="17" t="s">
+      <c r="F434" s="15" t="s">
         <v>1473</v>
       </c>
       <c r="G434" s="3" t="s">
@@ -37819,7 +37819,7 @@
       <c r="E435" s="3" t="s">
         <v>1797</v>
       </c>
-      <c r="F435" s="17" t="s">
+      <c r="F435" s="15" t="s">
         <v>1473</v>
       </c>
       <c r="G435" s="3" t="s">
@@ -37879,7 +37879,7 @@
       <c r="E436" s="3" t="s">
         <v>2065</v>
       </c>
-      <c r="F436" s="17" t="s">
+      <c r="F436" s="15" t="s">
         <v>2066</v>
       </c>
       <c r="G436" s="3" t="s">
@@ -37947,7 +37947,7 @@
       <c r="E437" s="3" t="s">
         <v>1812</v>
       </c>
-      <c r="F437" s="17" t="s">
+      <c r="F437" s="15" t="s">
         <v>1813</v>
       </c>
       <c r="G437" s="3" t="s">
@@ -38011,7 +38011,7 @@
       <c r="E438" s="3" t="s">
         <v>1819</v>
       </c>
-      <c r="F438" s="17" t="s">
+      <c r="F438" s="15" t="s">
         <v>1813</v>
       </c>
       <c r="G438" s="3" t="s">
@@ -38073,7 +38073,7 @@
       <c r="E439" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F439" s="17" t="s">
+      <c r="F439" s="15" t="s">
         <v>1974</v>
       </c>
       <c r="G439" s="3" t="s">
@@ -38139,7 +38139,7 @@
       <c r="E440" s="3" t="s">
         <v>1981</v>
       </c>
-      <c r="F440" s="17" t="s">
+      <c r="F440" s="15" t="s">
         <v>1974</v>
       </c>
       <c r="G440" s="3" t="s">
@@ -38201,7 +38201,7 @@
       <c r="E441" s="3" t="s">
         <v>1824</v>
       </c>
-      <c r="F441" s="17" t="s">
+      <c r="F441" s="15" t="s">
         <v>1825</v>
       </c>
       <c r="G441" s="3" t="s">
@@ -38261,7 +38261,7 @@
       </c>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
-      <c r="F442" s="17" t="s">
+      <c r="F442" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G442" s="3" t="s">
@@ -38323,7 +38323,7 @@
       <c r="E443" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="F443" s="17" t="s">
+      <c r="F443" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G443" s="3" t="s">
@@ -38383,7 +38383,7 @@
       </c>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
-      <c r="F444" s="17" t="s">
+      <c r="F444" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G444" s="3" t="s">
@@ -38439,7 +38439,7 @@
       </c>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
-      <c r="F445" s="17" t="s">
+      <c r="F445" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G445" s="3" t="s">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
-      <c r="F446" s="17" t="s">
+      <c r="F446" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G446" s="3" t="s">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
-      <c r="F447" s="17" t="s">
+      <c r="F447" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G447" s="3" t="s">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
-      <c r="F448" s="17" t="s">
+      <c r="F448" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G448" s="3" t="s">
@@ -38669,7 +38669,7 @@
       </c>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
-      <c r="F449" s="17" t="s">
+      <c r="F449" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G449" s="3" t="s">
@@ -38727,7 +38727,7 @@
       </c>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
-      <c r="F450" s="17" t="s">
+      <c r="F450" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G450" s="3" t="s">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
-      <c r="F451" s="17" t="s">
+      <c r="F451" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G451" s="3" t="s">
@@ -38841,7 +38841,7 @@
       </c>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
-      <c r="F452" s="17" t="s">
+      <c r="F452" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G452" s="3" t="s">
@@ -38899,7 +38899,7 @@
       </c>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
-      <c r="F453" s="17" t="s">
+      <c r="F453" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G453" s="3" t="s">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
-      <c r="F454" s="17" t="s">
+      <c r="F454" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G454" s="3" t="s">
@@ -39011,7 +39011,7 @@
       </c>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
-      <c r="F455" s="17" t="s">
+      <c r="F455" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G455" s="3" t="s">
@@ -39067,7 +39067,7 @@
       </c>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
-      <c r="F456" s="17" t="s">
+      <c r="F456" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G456" s="3" t="s">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
-      <c r="F457" s="17" t="s">
+      <c r="F457" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G457" s="3" t="s">
@@ -39183,7 +39183,7 @@
       <c r="E458" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="F458" s="17" t="s">
+      <c r="F458" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G458" s="3" t="s">
@@ -39243,7 +39243,7 @@
       <c r="E459" s="3" t="s">
         <v>1885</v>
       </c>
-      <c r="F459" s="17" t="s">
+      <c r="F459" s="15" t="s">
         <v>1831</v>
       </c>
       <c r="G459" s="3" t="s">
@@ -39299,7 +39299,7 @@
       </c>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
-      <c r="F460" s="17" t="s">
+      <c r="F460" s="15" t="s">
         <v>1889</v>
       </c>
       <c r="G460" s="3" t="s">
@@ -39355,7 +39355,7 @@
       </c>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
-      <c r="F461" s="17" t="s">
+      <c r="F461" s="15" t="s">
         <v>1889</v>
       </c>
       <c r="G461" s="3" t="s">
@@ -39415,7 +39415,7 @@
       <c r="E462" s="3" t="s">
         <v>1897</v>
       </c>
-      <c r="F462" s="17" t="s">
+      <c r="F462" s="15" t="s">
         <v>1889</v>
       </c>
       <c r="G462" s="3" t="s">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="D463" s="3"/>
       <c r="E463" s="3"/>
-      <c r="F463" s="17" t="s">
+      <c r="F463" s="15" t="s">
         <v>1889</v>
       </c>
       <c r="G463" s="3" t="s">
@@ -39537,7 +39537,7 @@
       <c r="E464" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F464" s="17" t="s">
+      <c r="F464" s="15" t="s">
         <v>1889</v>
       </c>
       <c r="G464" s="3" t="s">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="D465" s="3"/>
       <c r="E465" s="3"/>
-      <c r="F465" s="17" t="s">
+      <c r="F465" s="15" t="s">
         <v>1907</v>
       </c>
       <c r="G465" s="3" t="s">
@@ -39655,7 +39655,7 @@
       <c r="E466" s="3" t="s">
         <v>1912</v>
       </c>
-      <c r="F466" s="17" t="s">
+      <c r="F466" s="15" t="s">
         <v>1913</v>
       </c>
       <c r="G466" s="3" t="s">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="D467" s="3"/>
       <c r="E467" s="3"/>
-      <c r="F467" s="17" t="s">
+      <c r="F467" s="15" t="s">
         <v>1919</v>
       </c>
       <c r="G467" s="3" t="s">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
-      <c r="F468" s="17" t="s">
+      <c r="F468" s="15" t="s">
         <v>1919</v>
       </c>
       <c r="G468" s="3" t="s">
@@ -39831,7 +39831,7 @@
       </c>
       <c r="D469" s="3"/>
       <c r="E469" s="3"/>
-      <c r="F469" s="17" t="s">
+      <c r="F469" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G469" s="3" t="s">
@@ -39889,7 +39889,7 @@
       </c>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
-      <c r="F470" s="17" t="s">
+      <c r="F470" s="15" t="s">
         <v>1919</v>
       </c>
       <c r="G470" s="3" t="s">
@@ -39947,7 +39947,7 @@
       </c>
       <c r="D471" s="3"/>
       <c r="E471" s="3"/>
-      <c r="F471" s="17" t="s">
+      <c r="F471" s="15" t="s">
         <v>1919</v>
       </c>
       <c r="G471" s="3" t="s">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
-      <c r="F472" s="17" t="s">
+      <c r="F472" s="15" t="s">
         <v>1919</v>
       </c>
       <c r="G472" s="3" t="s">
@@ -40067,7 +40067,7 @@
       </c>
       <c r="D473" s="3"/>
       <c r="E473" s="3"/>
-      <c r="F473" s="17" t="s">
+      <c r="F473" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G473" s="3" t="s">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
-      <c r="F474" s="17" t="s">
+      <c r="F474" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G474" s="3" t="s">
@@ -40185,7 +40185,7 @@
       <c r="E475" s="3" t="s">
         <v>1945</v>
       </c>
-      <c r="F475" s="17" t="s">
+      <c r="F475" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G475" s="3" t="s">
@@ -40243,7 +40243,7 @@
       </c>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
-      <c r="F476" s="17" t="s">
+      <c r="F476" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G476" s="3" t="s">
@@ -40299,7 +40299,7 @@
       </c>
       <c r="D477" s="3"/>
       <c r="E477" s="3"/>
-      <c r="F477" s="17" t="s">
+      <c r="F477" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G477" s="3" t="s">
@@ -40361,7 +40361,7 @@
       <c r="E478" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="F478" s="17" t="s">
+      <c r="F478" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G478" s="3" t="s">
@@ -40419,7 +40419,7 @@
       </c>
       <c r="D479" s="3"/>
       <c r="E479" s="3"/>
-      <c r="F479" s="17" t="s">
+      <c r="F479" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G479" s="3" t="s">
@@ -40479,7 +40479,7 @@
       <c r="E480" s="3" t="s">
         <v>1961</v>
       </c>
-      <c r="F480" s="17" t="s">
+      <c r="F480" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G480" s="3" t="s">
@@ -40535,7 +40535,7 @@
       </c>
       <c r="D481" s="3"/>
       <c r="E481" s="3"/>
-      <c r="F481" s="17" t="s">
+      <c r="F481" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G481" s="3" t="s">
@@ -40591,7 +40591,7 @@
       </c>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
-      <c r="F482" s="17" t="s">
+      <c r="F482" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G482" s="3" t="s">
@@ -40651,7 +40651,7 @@
       <c r="E483" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="F483" s="17" t="s">
+      <c r="F483" s="15" t="s">
         <v>1926</v>
       </c>
       <c r="G483" s="3" t="s">
@@ -40711,7 +40711,7 @@
       <c r="E484" s="3" t="s">
         <v>2059</v>
       </c>
-      <c r="F484" s="17" t="s">
+      <c r="F484" s="15" t="s">
         <v>2060</v>
       </c>
       <c r="G484" s="3" t="s">
@@ -40777,7 +40777,7 @@
       <c r="E485" s="3" t="s">
         <v>1986</v>
       </c>
-      <c r="F485" s="17" t="s">
+      <c r="F485" s="15" t="s">
         <v>1987</v>
       </c>
       <c r="G485" s="3" t="s">
@@ -40841,7 +40841,7 @@
       <c r="E486" s="3" t="s">
         <v>1993</v>
       </c>
-      <c r="F486" s="17" t="s">
+      <c r="F486" s="15" t="s">
         <v>1987</v>
       </c>
       <c r="G486" s="3" t="s">
@@ -40905,7 +40905,7 @@
       <c r="E487" s="3" t="s">
         <v>1998</v>
       </c>
-      <c r="F487" s="17" t="s">
+      <c r="F487" s="15" t="s">
         <v>1987</v>
       </c>
       <c r="G487" s="3" t="s">
@@ -40969,7 +40969,7 @@
       <c r="E488" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="F488" s="17" t="s">
+      <c r="F488" s="15" t="s">
         <v>1987</v>
       </c>
       <c r="G488" s="3" t="s">
@@ -41029,7 +41029,7 @@
       <c r="E489" s="3" t="s">
         <v>2006</v>
       </c>
-      <c r="F489" s="17" t="s">
+      <c r="F489" s="15" t="s">
         <v>1987</v>
       </c>
       <c r="G489" s="3" t="s">
@@ -41093,7 +41093,7 @@
       <c r="E490" s="3" t="s">
         <v>2011</v>
       </c>
-      <c r="F490" s="17" t="s">
+      <c r="F490" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G490" s="3" t="s">
@@ -41153,7 +41153,7 @@
       <c r="E491" s="3" t="s">
         <v>2017</v>
       </c>
-      <c r="F491" s="17" t="s">
+      <c r="F491" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G491" s="3" t="s">
@@ -41217,7 +41217,7 @@
       <c r="E492" s="3" t="s">
         <v>2022</v>
       </c>
-      <c r="F492" s="17" t="s">
+      <c r="F492" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G492" s="3" t="s">
@@ -41281,7 +41281,7 @@
       <c r="E493" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="F493" s="17" t="s">
+      <c r="F493" s="15" t="s">
         <v>2027</v>
       </c>
       <c r="G493" s="3" t="s">
@@ -41341,7 +41341,7 @@
       </c>
       <c r="D494" s="3"/>
       <c r="E494" s="3"/>
-      <c r="F494" s="17" t="s">
+      <c r="F494" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G494" s="3" t="s">
@@ -41405,7 +41405,7 @@
       <c r="E495" s="3" t="s">
         <v>2035</v>
       </c>
-      <c r="F495" s="17" t="s">
+      <c r="F495" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G495" s="3" t="s">
@@ -41469,7 +41469,7 @@
       <c r="E496" s="3" t="s">
         <v>2039</v>
       </c>
-      <c r="F496" s="17" t="s">
+      <c r="F496" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G496" s="3" t="s">
@@ -41531,7 +41531,7 @@
       <c r="E497" s="3" t="s">
         <v>1650</v>
       </c>
-      <c r="F497" s="17" t="s">
+      <c r="F497" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G497" s="3" t="s">
@@ -41593,7 +41593,7 @@
       <c r="E498" s="3" t="s">
         <v>2046</v>
       </c>
-      <c r="F498" s="17" t="s">
+      <c r="F498" s="15" t="s">
         <v>2047</v>
       </c>
       <c r="G498" s="3" t="s">
@@ -41659,7 +41659,7 @@
       <c r="E499" s="3" t="s">
         <v>2052</v>
       </c>
-      <c r="F499" s="17" t="s">
+      <c r="F499" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G499" s="3" t="s">
@@ -41719,7 +41719,7 @@
       <c r="E500" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="F500" s="17" t="s">
+      <c r="F500" s="15" t="s">
         <v>2012</v>
       </c>
       <c r="G500" s="3" t="s">
@@ -41779,7 +41779,7 @@
       <c r="E501" s="3" t="s">
         <v>2105</v>
       </c>
-      <c r="F501" s="17" t="s">
+      <c r="F501" s="15" t="s">
         <v>2106</v>
       </c>
       <c r="G501" s="3" t="s">
@@ -41845,7 +41845,7 @@
       <c r="E502" s="3" t="s">
         <v>2113</v>
       </c>
-      <c r="F502" s="17" t="s">
+      <c r="F502" s="15" t="s">
         <v>2114</v>
       </c>
       <c r="G502" s="3" t="s">
@@ -41907,7 +41907,7 @@
       <c r="E503" s="3" t="s">
         <v>2119</v>
       </c>
-      <c r="F503" s="17" t="s">
+      <c r="F503" s="15" t="s">
         <v>2114</v>
       </c>
       <c r="G503" s="3" t="s">
@@ -41969,7 +41969,7 @@
       <c r="E504" s="3" t="s">
         <v>2073</v>
       </c>
-      <c r="F504" s="17" t="s">
+      <c r="F504" s="15" t="s">
         <v>590</v>
       </c>
       <c r="G504" s="3" t="s">
@@ -42033,7 +42033,7 @@
       <c r="E505" s="3" t="s">
         <v>2079</v>
       </c>
-      <c r="F505" s="17" t="s">
+      <c r="F505" s="15" t="s">
         <v>2080</v>
       </c>
       <c r="G505" s="3" t="s">
@@ -42097,7 +42097,7 @@
       <c r="E506" s="3" t="s">
         <v>2085</v>
       </c>
-      <c r="F506" s="17" t="s">
+      <c r="F506" s="15" t="s">
         <v>2080</v>
       </c>
       <c r="G506" s="3" t="s">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="D507" s="3"/>
       <c r="E507" s="3"/>
-      <c r="F507" s="17" t="s">
+      <c r="F507" s="15" t="s">
         <v>2080</v>
       </c>
       <c r="G507" s="3" t="s">
@@ -42217,7 +42217,7 @@
       <c r="E508" s="3" t="s">
         <v>2094</v>
       </c>
-      <c r="F508" s="17" t="s">
+      <c r="F508" s="15" t="s">
         <v>2095</v>
       </c>
       <c r="G508" s="3" t="s">
@@ -42279,7 +42279,7 @@
       <c r="E509" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="F509" s="17" t="s">
+      <c r="F509" s="15" t="s">
         <v>2080</v>
       </c>
       <c r="G509" s="3" t="s">
@@ -42339,7 +42339,7 @@
       <c r="E510" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F510" s="17" t="s">
+      <c r="F510" s="15" t="s">
         <v>2209</v>
       </c>
       <c r="G510" s="3" t="s">
@@ -42405,7 +42405,7 @@
       <c r="E511" s="3" t="s">
         <v>1998</v>
       </c>
-      <c r="F511" s="17" t="s">
+      <c r="F511" s="15" t="s">
         <v>2215</v>
       </c>
       <c r="G511" s="3" t="s">
@@ -42467,7 +42467,7 @@
       <c r="E512" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="F512" s="17" t="s">
+      <c r="F512" s="15" t="s">
         <v>2932</v>
       </c>
       <c r="G512" s="3" t="s">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="D513" s="3"/>
       <c r="E513" s="3"/>
-      <c r="F513" s="17" t="s">
+      <c r="F513" s="15" t="s">
         <v>2129</v>
       </c>
       <c r="G513" s="3" t="s">
@@ -42591,7 +42591,7 @@
       <c r="E514" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="F514" s="17" t="s">
+      <c r="F514" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G514" s="3" t="s">
@@ -42653,7 +42653,7 @@
       <c r="E515" s="3" t="s">
         <v>2137</v>
       </c>
-      <c r="F515" s="17" t="s">
+      <c r="F515" s="15" t="s">
         <v>2138</v>
       </c>
       <c r="G515" s="3" t="s">
@@ -42711,7 +42711,7 @@
       </c>
       <c r="D516" s="3"/>
       <c r="E516" s="3"/>
-      <c r="F516" s="17" t="s">
+      <c r="F516" s="15" t="s">
         <v>2143</v>
       </c>
       <c r="G516" s="3" t="s">
@@ -42769,7 +42769,7 @@
       </c>
       <c r="D517" s="3"/>
       <c r="E517" s="3"/>
-      <c r="F517" s="17" t="s">
+      <c r="F517" s="15" t="s">
         <v>2148</v>
       </c>
       <c r="G517" s="3" t="s">
@@ -42833,7 +42833,7 @@
       <c r="E518" s="3" t="s">
         <v>2153</v>
       </c>
-      <c r="F518" s="17" t="s">
+      <c r="F518" s="15" t="s">
         <v>2154</v>
       </c>
       <c r="G518" s="3" t="s">
@@ -42895,7 +42895,7 @@
       </c>
       <c r="D519" s="3"/>
       <c r="E519" s="3"/>
-      <c r="F519" s="17" t="s">
+      <c r="F519" s="15" t="s">
         <v>2159</v>
       </c>
       <c r="G519" s="3" t="s">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="D520" s="3"/>
       <c r="E520" s="3"/>
-      <c r="F520" s="17" t="s">
+      <c r="F520" s="15" t="s">
         <v>2159</v>
       </c>
       <c r="G520" s="3" t="s">
@@ -43011,7 +43011,7 @@
       </c>
       <c r="D521" s="3"/>
       <c r="E521" s="3"/>
-      <c r="F521" s="17" t="s">
+      <c r="F521" s="15" t="s">
         <v>2159</v>
       </c>
       <c r="G521" s="3" t="s">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="D522" s="3"/>
       <c r="E522" s="3"/>
-      <c r="F522" s="17" t="s">
+      <c r="F522" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G522" s="3" t="s">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="D523" s="3"/>
       <c r="E523" s="3"/>
-      <c r="F523" s="17" t="s">
+      <c r="F523" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G523" s="3" t="s">
@@ -43195,7 +43195,7 @@
       <c r="E524" s="3" t="s">
         <v>2175</v>
       </c>
-      <c r="F524" s="17" t="s">
+      <c r="F524" s="15" t="s">
         <v>2176</v>
       </c>
       <c r="G524" s="3" t="s">
@@ -43255,7 +43255,7 @@
       </c>
       <c r="D525" s="3"/>
       <c r="E525" s="3"/>
-      <c r="F525" s="17" t="s">
+      <c r="F525" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G525" s="3" t="s">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="D526" s="3"/>
       <c r="E526" s="3"/>
-      <c r="F526" s="17" t="s">
+      <c r="F526" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G526" s="3" t="s">
@@ -43371,7 +43371,7 @@
       <c r="E527" s="3" t="s">
         <v>2187</v>
       </c>
-      <c r="F527" s="17" t="s">
+      <c r="F527" s="15" t="s">
         <v>2143</v>
       </c>
       <c r="G527" s="3" t="s">
@@ -43433,7 +43433,7 @@
       <c r="E528" s="3" t="s">
         <v>2192</v>
       </c>
-      <c r="F528" s="17" t="s">
+      <c r="F528" s="15" t="s">
         <v>2133</v>
       </c>
       <c r="G528" s="3" t="s">
@@ -43489,7 +43489,7 @@
       </c>
       <c r="D529" s="3"/>
       <c r="E529" s="3"/>
-      <c r="F529" s="17" t="s">
+      <c r="F529" s="15" t="s">
         <v>2143</v>
       </c>
       <c r="G529" s="3" t="s">
@@ -43551,7 +43551,7 @@
       <c r="E530" s="3" t="s">
         <v>2187</v>
       </c>
-      <c r="F530" s="17" t="s">
+      <c r="F530" s="15" t="s">
         <v>2200</v>
       </c>
       <c r="G530" s="3" t="s">
@@ -43611,7 +43611,7 @@
       <c r="E531" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F531" s="17" t="s">
+      <c r="F531" s="15" t="s">
         <v>2204</v>
       </c>
       <c r="G531" s="3" t="s">
@@ -43669,7 +43669,7 @@
       </c>
       <c r="D532" s="3"/>
       <c r="E532" s="3"/>
-      <c r="F532" s="17" t="s">
+      <c r="F532" s="15" t="s">
         <v>2220</v>
       </c>
       <c r="G532" s="3" t="s">
@@ -43727,7 +43727,7 @@
       </c>
       <c r="D533" s="3"/>
       <c r="E533" s="3"/>
-      <c r="F533" s="17" t="s">
+      <c r="F533" s="15" t="s">
         <v>2303</v>
       </c>
       <c r="G533" s="3" t="s">
@@ -43795,7 +43795,7 @@
       <c r="E534" s="3" t="s">
         <v>2226</v>
       </c>
-      <c r="F534" s="17" t="s">
+      <c r="F534" s="15" t="s">
         <v>2227</v>
       </c>
       <c r="G534" s="3" t="s">
@@ -43861,7 +43861,7 @@
       <c r="E535" s="3" t="s">
         <v>2233</v>
       </c>
-      <c r="F535" s="17" t="s">
+      <c r="F535" s="15" t="s">
         <v>2234</v>
       </c>
       <c r="G535" s="3" t="s">
@@ -43925,7 +43925,7 @@
       <c r="E536" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="F536" s="17" t="s">
+      <c r="F536" s="15" t="s">
         <v>2234</v>
       </c>
       <c r="G536" s="3" t="s">
@@ -43987,7 +43987,7 @@
       <c r="E537" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="F537" s="17" t="s">
+      <c r="F537" s="15" t="s">
         <v>2933</v>
       </c>
       <c r="G537" s="3" t="s">
@@ -44053,7 +44053,7 @@
       <c r="E538" s="3" t="s">
         <v>2248</v>
       </c>
-      <c r="F538" s="17" t="s">
+      <c r="F538" s="15" t="s">
         <v>2234</v>
       </c>
       <c r="G538" s="3" t="s">
@@ -44117,7 +44117,7 @@
       <c r="E539" s="3" t="s">
         <v>2253</v>
       </c>
-      <c r="F539" s="17" t="s">
+      <c r="F539" s="15" t="s">
         <v>2254</v>
       </c>
       <c r="G539" s="3" t="s">
@@ -44181,7 +44181,7 @@
       <c r="E540" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="F540" s="17" t="s">
+      <c r="F540" s="15" t="s">
         <v>2934</v>
       </c>
       <c r="G540" s="3" t="s">
@@ -44243,7 +44243,7 @@
       <c r="E541" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="F541" s="17" t="s">
+      <c r="F541" s="15" t="s">
         <v>2263</v>
       </c>
       <c r="G541" s="3" t="s">
@@ -44305,7 +44305,7 @@
       <c r="E542" s="3" t="s">
         <v>2094</v>
       </c>
-      <c r="F542" s="17" t="s">
+      <c r="F542" s="15" t="s">
         <v>2234</v>
       </c>
       <c r="G542" s="3" t="s">
@@ -44363,7 +44363,7 @@
       </c>
       <c r="D543" s="3"/>
       <c r="E543" s="3"/>
-      <c r="F543" s="17" t="s">
+      <c r="F543" s="15" t="s">
         <v>2272</v>
       </c>
       <c r="G543" s="3" t="s">
@@ -44425,7 +44425,7 @@
       <c r="E544" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="F544" s="17" t="s">
+      <c r="F544" s="15" t="s">
         <v>2278</v>
       </c>
       <c r="G544" s="3" t="s">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="D545" s="3"/>
       <c r="E545" s="3"/>
-      <c r="F545" s="17" t="s">
+      <c r="F545" s="15" t="s">
         <v>2283</v>
       </c>
       <c r="G545" s="3" t="s">
@@ -44551,7 +44551,7 @@
       <c r="E546" s="3" t="s">
         <v>1622</v>
       </c>
-      <c r="F546" s="17" t="s">
+      <c r="F546" s="15" t="s">
         <v>2272</v>
       </c>
       <c r="G546" s="3" t="s">
@@ -44615,7 +44615,7 @@
       <c r="E547" s="3" t="s">
         <v>2292</v>
       </c>
-      <c r="F547" s="17" t="s">
+      <c r="F547" s="15" t="s">
         <v>2293</v>
       </c>
       <c r="G547" s="3" t="s">
@@ -44679,7 +44679,7 @@
       <c r="E548" s="3" t="s">
         <v>2298</v>
       </c>
-      <c r="F548" s="17" t="s">
+      <c r="F548" s="15" t="s">
         <v>2935</v>
       </c>
       <c r="G548" s="3" t="s">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="D549" s="3"/>
       <c r="E549" s="3"/>
-      <c r="F549" s="17" t="s">
+      <c r="F549" s="15" t="s">
         <v>2520</v>
       </c>
       <c r="G549" s="3" t="s">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="D550" s="3"/>
       <c r="E550" s="3"/>
-      <c r="F550" s="17" t="s">
+      <c r="F550" s="15" t="s">
         <v>2937</v>
       </c>
       <c r="G550" s="3" t="s">
@@ -44855,7 +44855,7 @@
       </c>
       <c r="D551" s="3"/>
       <c r="E551" s="3"/>
-      <c r="F551" s="17" t="s">
+      <c r="F551" s="15" t="s">
         <v>2450</v>
       </c>
       <c r="G551" s="3" t="s">
@@ -44917,7 +44917,7 @@
       </c>
       <c r="D552" s="3"/>
       <c r="E552" s="3"/>
-      <c r="F552" s="17" t="s">
+      <c r="F552" s="15" t="s">
         <v>2386</v>
       </c>
       <c r="G552" s="3" t="s">
@@ -44977,7 +44977,7 @@
       </c>
       <c r="D553" s="3"/>
       <c r="E553" s="3"/>
-      <c r="F553" s="17" t="s">
+      <c r="F553" s="15" t="s">
         <v>2392</v>
       </c>
       <c r="G553" s="3" t="s">
@@ -45043,7 +45043,7 @@
       <c r="E554" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F554" s="17" t="s">
+      <c r="F554" s="15" t="s">
         <v>2397</v>
       </c>
       <c r="G554" s="3" t="s">
@@ -45105,7 +45105,7 @@
       </c>
       <c r="D555" s="3"/>
       <c r="E555" s="3"/>
-      <c r="F555" s="17" t="s">
+      <c r="F555" s="15" t="s">
         <v>2392</v>
       </c>
       <c r="G555" s="3" t="s">
@@ -45167,7 +45167,7 @@
       </c>
       <c r="D556" s="3"/>
       <c r="E556" s="3"/>
-      <c r="F556" s="17" t="s">
+      <c r="F556" s="15" t="s">
         <v>2938</v>
       </c>
       <c r="G556" s="3" t="s">
@@ -45229,7 +45229,7 @@
       </c>
       <c r="D557" s="3"/>
       <c r="E557" s="3"/>
-      <c r="F557" s="17" t="s">
+      <c r="F557" s="15" t="s">
         <v>2410</v>
       </c>
       <c r="G557" s="3" t="s">
@@ -45289,7 +45289,7 @@
       </c>
       <c r="D558" s="3"/>
       <c r="E558" s="3"/>
-      <c r="F558" s="17" t="s">
+      <c r="F558" s="15" t="s">
         <v>2410</v>
       </c>
       <c r="G558" s="3" t="s">
@@ -45347,7 +45347,7 @@
       </c>
       <c r="D559" s="3"/>
       <c r="E559" s="3"/>
-      <c r="F559" s="17" t="s">
+      <c r="F559" s="15" t="s">
         <v>2410</v>
       </c>
       <c r="G559" s="3" t="s">
@@ -45405,7 +45405,7 @@
       </c>
       <c r="D560" s="3"/>
       <c r="E560" s="3"/>
-      <c r="F560" s="17" t="s">
+      <c r="F560" s="15" t="s">
         <v>2423</v>
       </c>
       <c r="G560" s="3" t="s">
@@ -45465,7 +45465,7 @@
       </c>
       <c r="D561" s="3"/>
       <c r="E561" s="3"/>
-      <c r="F561" s="17" t="s">
+      <c r="F561" s="15" t="s">
         <v>2429</v>
       </c>
       <c r="G561" s="3" t="s">
@@ -45531,7 +45531,7 @@
       <c r="E562" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="F562" s="17" t="s">
+      <c r="F562" s="15" t="s">
         <v>2434</v>
       </c>
       <c r="G562" s="3" t="s">
@@ -45597,7 +45597,7 @@
       <c r="E563" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="F563" s="17" t="s">
+      <c r="F563" s="15" t="s">
         <v>2440</v>
       </c>
       <c r="G563" s="3" t="s">
@@ -45661,7 +45661,7 @@
       <c r="E564" s="3" t="s">
         <v>2233</v>
       </c>
-      <c r="F564" s="17" t="s">
+      <c r="F564" s="15" t="s">
         <v>2504</v>
       </c>
       <c r="G564" s="3" t="s">
@@ -45729,7 +45729,7 @@
       <c r="E565" s="3" t="s">
         <v>2094</v>
       </c>
-      <c r="F565" s="17" t="s">
+      <c r="F565" s="15" t="s">
         <v>2510</v>
       </c>
       <c r="G565" s="3" t="s">
@@ -45791,7 +45791,7 @@
       <c r="E566" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F566" s="17" t="s">
+      <c r="F566" s="15" t="s">
         <v>2515</v>
       </c>
       <c r="G566" s="3" t="s">
@@ -45853,7 +45853,7 @@
       <c r="E567" s="3" t="s">
         <v>1670</v>
       </c>
-      <c r="F567" s="17" t="s">
+      <c r="F567" s="15" t="s">
         <v>2456</v>
       </c>
       <c r="G567" s="3" t="s">
@@ -45915,7 +45915,7 @@
       </c>
       <c r="D568" s="3"/>
       <c r="E568" s="3"/>
-      <c r="F568" s="17" t="s">
+      <c r="F568" s="15" t="s">
         <v>2462</v>
       </c>
       <c r="G568" s="3" t="s">
@@ -45977,7 +45977,7 @@
       <c r="E569" s="3" t="s">
         <v>2468</v>
       </c>
-      <c r="F569" s="17" t="s">
+      <c r="F569" s="15" t="s">
         <v>2469</v>
       </c>
       <c r="G569" s="3" t="s">
@@ -46039,7 +46039,7 @@
       <c r="E570" s="3" t="s">
         <v>2941</v>
       </c>
-      <c r="F570" s="17" t="s">
+      <c r="F570" s="15" t="s">
         <v>2942</v>
       </c>
       <c r="G570" s="3" t="s">
@@ -46101,7 +46101,7 @@
       <c r="E571" s="3" t="s">
         <v>2475</v>
       </c>
-      <c r="F571" s="17" t="s">
+      <c r="F571" s="15" t="s">
         <v>2476</v>
       </c>
       <c r="G571" s="3" t="s">
@@ -46165,7 +46165,7 @@
       <c r="E572" s="3" t="s">
         <v>2482</v>
       </c>
-      <c r="F572" s="17" t="s">
+      <c r="F572" s="15" t="s">
         <v>2483</v>
       </c>
       <c r="G572" s="3" t="s">
@@ -46227,7 +46227,7 @@
       <c r="E573" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="F573" s="17" t="s">
+      <c r="F573" s="15" t="s">
         <v>2946</v>
       </c>
       <c r="G573" s="3" t="s">
@@ -46291,7 +46291,7 @@
       <c r="E574" s="3" t="s">
         <v>2248</v>
       </c>
-      <c r="F574" s="17" t="s">
+      <c r="F574" s="15" t="s">
         <v>2947</v>
       </c>
       <c r="G574" s="3" t="s">
@@ -46349,7 +46349,7 @@
       </c>
       <c r="D575" s="3"/>
       <c r="E575" s="3"/>
-      <c r="F575" s="17" t="s">
+      <c r="F575" s="15" t="s">
         <v>2498</v>
       </c>
       <c r="G575" s="3" t="s">
@@ -46413,7 +46413,7 @@
       <c r="E576" s="3" t="s">
         <v>1709</v>
       </c>
-      <c r="F576" s="17" t="s">
+      <c r="F576" s="15" t="s">
         <v>2913</v>
       </c>
       <c r="G576" s="3" t="s">
@@ -46477,7 +46477,7 @@
       <c r="E577" s="3" t="s">
         <v>2758</v>
       </c>
-      <c r="F577" s="17" t="s">
+      <c r="F577" s="15" t="s">
         <v>2911</v>
       </c>
       <c r="G577" s="3" t="s">
@@ -46535,7 +46535,7 @@
       </c>
       <c r="D578" s="3"/>
       <c r="E578" s="3"/>
-      <c r="F578" s="17" t="s">
+      <c r="F578" s="15" t="s">
         <v>3462</v>
       </c>
       <c r="G578" s="3" t="s">
@@ -46562,7 +46562,9 @@
         <v>3469</v>
       </c>
       <c r="P578" s="3"/>
-      <c r="Q578" s="3"/>
+      <c r="Q578" s="3" t="s">
+        <v>3452</v>
+      </c>
       <c r="R578" s="3"/>
       <c r="S578" s="3"/>
       <c r="T578" s="3"/>
@@ -46597,7 +46599,7 @@
       <c r="E579" s="3" t="s">
         <v>3471</v>
       </c>
-      <c r="F579" s="17" t="s">
+      <c r="F579" s="15" t="s">
         <v>3472</v>
       </c>
       <c r="G579" s="3" t="s">
@@ -46624,7 +46626,9 @@
         <v>3474</v>
       </c>
       <c r="P579" s="3"/>
-      <c r="Q579" s="3"/>
+      <c r="Q579" s="3" t="s">
+        <v>3449</v>
+      </c>
       <c r="R579" s="3"/>
       <c r="S579" s="3"/>
       <c r="T579" s="3"/>
@@ -46643,8 +46647,14 @@
       <c r="Y579" s="3"/>
       <c r="Z579" s="8"/>
     </row>
+    <row r="582" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="U582"/>
+    </row>
+    <row r="583" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="U583"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Y577" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Y579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E15E93DE-65E0-4A52-AD2E-3B35A4F8E100}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1839F530-4751-4A73-948F-BBE841F18F10}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10417,9 +10417,6 @@
     <t>18/052026</t>
   </si>
   <si>
-    <t>239032.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">	
 s_winai@oceanglass.com</t>
   </si>
@@ -10464,6 +10461,9 @@
   </si>
   <si>
     <t>linqing@oceanglass.com</t>
+  </si>
+  <si>
+    <t>269032.jpg</t>
   </si>
 </sst>
 </file>
@@ -13004,10 +13004,10 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="3" t="s">
+        <v>3474</v>
+      </c>
+      <c r="O34" s="13" t="s">
         <v>3459</v>
-      </c>
-      <c r="O34" s="13" t="s">
-        <v>3460</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
@@ -46528,21 +46528,21 @@
         <v>656001</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="D578" s="3"/>
       <c r="E578" s="3"/>
       <c r="F578" s="15" t="s">
+        <v>3461</v>
+      </c>
+      <c r="G578" s="3" t="s">
         <v>3462</v>
       </c>
-      <c r="G578" s="3" t="s">
+      <c r="H578" s="3" t="s">
         <v>3463</v>
-      </c>
-      <c r="H578" s="3" t="s">
-        <v>3464</v>
       </c>
       <c r="I578" s="3">
         <v>168015</v>
@@ -46556,10 +46556,10 @@
       <c r="L578" s="4"/>
       <c r="M578" s="4"/>
       <c r="N578" s="3" t="s">
+        <v>3467</v>
+      </c>
+      <c r="O578" s="3" t="s">
         <v>3468</v>
-      </c>
-      <c r="O578" s="3" t="s">
-        <v>3469</v>
       </c>
       <c r="P578" s="3"/>
       <c r="Q578" s="3" t="s">
@@ -46588,25 +46588,25 @@
         <v>656008</v>
       </c>
       <c r="B579" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>3469</v>
+      </c>
+      <c r="D579" s="3" t="s">
         <v>3470</v>
       </c>
-      <c r="C579" s="3" t="s">
+      <c r="E579" s="3" t="s">
         <v>3470</v>
       </c>
-      <c r="D579" s="3" t="s">
+      <c r="F579" s="15" t="s">
         <v>3471</v>
-      </c>
-      <c r="E579" s="3" t="s">
-        <v>3471</v>
-      </c>
-      <c r="F579" s="15" t="s">
-        <v>3472</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H579" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="I579" s="3">
         <v>168015</v>
@@ -46620,10 +46620,10 @@
       <c r="L579" s="4"/>
       <c r="M579" s="4"/>
       <c r="N579" s="3" t="s">
+        <v>3472</v>
+      </c>
+      <c r="O579" s="3" t="s">
         <v>3473</v>
-      </c>
-      <c r="O579" s="3" t="s">
-        <v>3474</v>
       </c>
       <c r="P579" s="3"/>
       <c r="Q579" s="3" t="s">
@@ -47057,13 +47057,13 @@
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>612</v>
@@ -47077,13 +47077,13 @@
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>612</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3614FC8E-4F97-47FF-8F73-480C5B2762F6}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4674B2-0EE3-405A-A3B8-F9BBF89FBC8C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7701" uniqueCount="3489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7702" uniqueCount="3489">
   <si>
     <t>emp_id</t>
   </si>
@@ -10664,19 +10664,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -11003,32 +11014,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>2911</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -22857,8 +22868,8 @@
       <c r="H191" s="3" t="s">
         <v>3488</v>
       </c>
-      <c r="I191" s="3">
-        <v>149024</v>
+      <c r="I191" s="3" t="s">
+        <v>3484</v>
       </c>
       <c r="J191" s="5">
         <v>29660</v>
@@ -22919,7 +22930,7 @@
       <c r="H192" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="I192" s="19" t="s">
+      <c r="I192" s="17" t="s">
         <v>2908</v>
       </c>
       <c r="J192" s="5">
@@ -46655,7 +46666,7 @@
       <c r="Z578" s="8"/>
     </row>
     <row r="579" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A579" s="19" t="s">
+      <c r="A579" s="17" t="s">
         <v>2908</v>
       </c>
       <c r="B579" s="3" t="s">
@@ -49313,6 +49324,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F122">
     <sortCondition ref="A2:A122"/>
   </sortState>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4674B2-0EE3-405A-A3B8-F9BBF89FBC8C}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96CB9631-8CFC-42A1-8ABF-62B51256C9A8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7702" uniqueCount="3489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7701" uniqueCount="3488">
   <si>
     <t>emp_id</t>
   </si>
@@ -10360,9 +10360,6 @@
     <t>Acting Department Manager - Batch and Furnace</t>
   </si>
   <si>
-    <t>168001A.jpg</t>
-  </si>
-  <si>
     <t>OGC-MFG-SPN-PCM</t>
   </si>
   <si>
@@ -10487,12 +10484,6 @@
     <t>Executive Director - Finance Accounting, Information Technology and Procurement</t>
   </si>
   <si>
-    <t>04/06/202</t>
-  </si>
-  <si>
-    <t>Sathien@oceanglass.com</t>
-  </si>
-  <si>
     <t>149024 A</t>
   </si>
   <si>
@@ -10506,6 +10497,12 @@
   </si>
   <si>
     <t>OGC-FAD-PCM</t>
+  </si>
+  <si>
+    <t>168001 A.jpg</t>
+  </si>
+  <si>
+    <t>s_sathien@Oceanglass.com</t>
   </si>
 </sst>
 </file>
@@ -12029,7 +12026,7 @@
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -12395,7 +12392,7 @@
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -13038,10 +13035,10 @@
         <v>269032</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>3444</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>3445</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>3446</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>728</v>
@@ -13050,13 +13047,13 @@
         <v>728</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="I34" s="3">
         <v>258026</v>
@@ -13065,19 +13062,19 @@
         <v>30484</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -13141,7 +13138,7 @@
       </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3" t="s">
@@ -16043,7 +16040,7 @@
       </c>
       <c r="P82" s="3"/>
       <c r="Q82" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
@@ -16173,7 +16170,7 @@
       </c>
       <c r="P84" s="3"/>
       <c r="Q84" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R84" s="3"/>
       <c r="S84" s="3" t="s">
@@ -17435,7 +17432,7 @@
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R104" s="3"/>
       <c r="S104" s="3" t="s">
@@ -18057,7 +18054,7 @@
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R114" s="3"/>
       <c r="S114" s="3" t="s">
@@ -20419,7 +20416,7 @@
       </c>
       <c r="P152" s="3"/>
       <c r="Q152" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R152" s="3"/>
       <c r="S152" s="6" t="s">
@@ -22848,28 +22845,28 @@
         <v>269040</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>3472</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="D191" s="3" t="s">
         <v>3473</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="E191" s="3" t="s">
+        <v>3473</v>
+      </c>
+      <c r="F191" s="15" t="s">
         <v>3474</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>3474</v>
-      </c>
-      <c r="F191" s="15" t="s">
-        <v>3475</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>3488</v>
+        <v>3485</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>3484</v>
+        <v>3481</v>
       </c>
       <c r="J191" s="5">
         <v>29660</v>
@@ -22880,10 +22877,10 @@
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
       <c r="N191" s="3" t="s">
+        <v>3475</v>
+      </c>
+      <c r="O191" s="3" t="s">
         <v>3476</v>
-      </c>
-      <c r="O191" s="3" t="s">
-        <v>3477</v>
       </c>
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
@@ -22907,7 +22904,7 @@
     </row>
     <row r="192" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>3484</v>
+        <v>3481</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>2301</v>
@@ -22916,13 +22913,13 @@
         <v>2302</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>3485</v>
+        <v>3482</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>3485</v>
+        <v>3482</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>3486</v>
+        <v>3483</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>66</v>
@@ -22942,7 +22939,7 @@
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
       <c r="N192" s="3" t="s">
-        <v>3487</v>
+        <v>3484</v>
       </c>
       <c r="O192" s="3" t="s">
         <v>2306</v>
@@ -23923,7 +23920,7 @@
       </c>
       <c r="P207" s="3"/>
       <c r="Q207" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R207" s="3"/>
       <c r="S207" s="3"/>
@@ -25651,7 +25648,7 @@
       </c>
       <c r="P236" s="3"/>
       <c r="Q236" s="3" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="R236" s="3"/>
       <c r="S236" s="3" t="s">
@@ -30149,7 +30146,7 @@
       </c>
       <c r="P308" s="3"/>
       <c r="Q308" s="3" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="R308" s="3"/>
       <c r="S308" s="3" t="s">
@@ -38103,7 +38100,7 @@
       </c>
       <c r="P438" s="3"/>
       <c r="Q438" s="3" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="R438" s="3"/>
       <c r="S438" s="6" t="s">
@@ -43922,10 +43919,10 @@
         <v>2302</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>3485</v>
+        <v>3482</v>
       </c>
       <c r="E535" s="3" t="s">
-        <v>3485</v>
+        <v>3482</v>
       </c>
       <c r="F535" s="15" t="s">
         <v>2303</v>
@@ -43955,7 +43952,7 @@
       </c>
       <c r="P535" s="3"/>
       <c r="Q535" s="3" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="R535" s="3"/>
       <c r="S535" s="3" t="s">
@@ -45087,7 +45084,7 @@
       </c>
       <c r="P553" s="3"/>
       <c r="Q553" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R553" s="3"/>
       <c r="S553" s="3" t="s">
@@ -45829,7 +45826,7 @@
       </c>
       <c r="P565" s="3"/>
       <c r="Q565" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R565" s="3"/>
       <c r="S565" s="3"/>
@@ -45893,7 +45890,7 @@
       </c>
       <c r="P566" s="3"/>
       <c r="Q566" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="R566" s="3"/>
       <c r="S566" s="3" t="s">
@@ -46645,7 +46642,7 @@
       </c>
       <c r="P578" s="3"/>
       <c r="Q578" s="3" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="R578" s="3"/>
       <c r="S578" s="3"/>
@@ -46670,19 +46667,19 @@
         <v>2908</v>
       </c>
       <c r="B579" s="3" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C579" s="3" t="s">
         <v>3478</v>
       </c>
-      <c r="C579" s="3" t="s">
+      <c r="D579" s="3" t="s">
         <v>3479</v>
       </c>
-      <c r="D579" s="3" t="s">
+      <c r="E579" s="3" t="s">
+        <v>3479</v>
+      </c>
+      <c r="F579" s="15" t="s">
         <v>3480</v>
-      </c>
-      <c r="E579" s="3" t="s">
-        <v>3480</v>
-      </c>
-      <c r="F579" s="15" t="s">
-        <v>3481</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>2945</v>
@@ -46696,16 +46693,16 @@
       <c r="J579" s="5">
         <v>24322</v>
       </c>
-      <c r="K579" s="5" t="s">
-        <v>3482</v>
+      <c r="K579" s="5">
+        <v>46177</v>
       </c>
       <c r="L579" s="4"/>
       <c r="M579" s="4"/>
       <c r="N579" s="12" t="s">
-        <v>3440</v>
+        <v>3486</v>
       </c>
       <c r="O579" s="3" t="s">
-        <v>3483</v>
+        <v>3487</v>
       </c>
       <c r="P579" s="3"/>
       <c r="Q579" s="3"/>
@@ -46730,21 +46727,21 @@
         <v>656001</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="D580" s="3"/>
       <c r="E580" s="3"/>
       <c r="F580" s="15" t="s">
+        <v>3450</v>
+      </c>
+      <c r="G580" s="3" t="s">
         <v>3451</v>
       </c>
-      <c r="G580" s="3" t="s">
+      <c r="H580" s="3" t="s">
         <v>3452</v>
-      </c>
-      <c r="H580" s="3" t="s">
-        <v>3453</v>
       </c>
       <c r="I580" s="3">
         <v>168015</v>
@@ -46758,14 +46755,14 @@
       <c r="L580" s="4"/>
       <c r="M580" s="4"/>
       <c r="N580" s="3" t="s">
+        <v>3456</v>
+      </c>
+      <c r="O580" s="3" t="s">
         <v>3457</v>
-      </c>
-      <c r="O580" s="3" t="s">
-        <v>3458</v>
       </c>
       <c r="P580" s="3"/>
       <c r="Q580" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R580" s="3"/>
       <c r="S580" s="3"/>
@@ -46790,25 +46787,25 @@
         <v>656008</v>
       </c>
       <c r="B581" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="D581" s="3" t="s">
         <v>3459</v>
       </c>
-      <c r="C581" s="3" t="s">
+      <c r="E581" s="3" t="s">
         <v>3459</v>
       </c>
-      <c r="D581" s="3" t="s">
+      <c r="F581" s="15" t="s">
         <v>3460</v>
-      </c>
-      <c r="E581" s="3" t="s">
-        <v>3460</v>
-      </c>
-      <c r="F581" s="15" t="s">
-        <v>3461</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H581" s="3" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="I581" s="3">
         <v>168015</v>
@@ -46822,14 +46819,14 @@
       <c r="L581" s="4"/>
       <c r="M581" s="4"/>
       <c r="N581" s="3" t="s">
+        <v>3461</v>
+      </c>
+      <c r="O581" s="3" t="s">
         <v>3462</v>
-      </c>
-      <c r="O581" s="3" t="s">
-        <v>3463</v>
       </c>
       <c r="P581" s="3"/>
       <c r="Q581" s="3" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="R581" s="3"/>
       <c r="S581" s="3"/>
@@ -46990,7 +46987,7 @@
         <v>2799</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>272</v>
@@ -47001,13 +46998,13 @@
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>3443</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>3444</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>2746</v>
@@ -47050,7 +47047,7 @@
         <v>2801</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>272</v>
@@ -47261,13 +47258,13 @@
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>612</v>
@@ -47281,13 +47278,13 @@
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>612</v>
@@ -47881,7 +47878,7 @@
     </row>
     <row r="51" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>3488</v>
+        <v>3485</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>2819</v>
@@ -47910,7 +47907,7 @@
         <v>2819</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>3488</v>
+        <v>3485</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>34</v>
@@ -49021,7 +49018,7 @@
     </row>
     <row r="108" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="12" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>2819</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96CB9631-8CFC-42A1-8ABF-62B51256C9A8}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BF266DF-17A4-4424-A3AB-86AEE74BBD90}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7701" uniqueCount="3488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7695" uniqueCount="3486">
   <si>
     <t>emp_id</t>
   </si>
@@ -8760,9 +8760,6 @@
   </si>
   <si>
     <t>RP90</t>
-  </si>
-  <si>
-    <t>168001 A</t>
   </si>
   <si>
     <t>268029 A</t>
@@ -10497,9 +10494,6 @@
   </si>
   <si>
     <t>OGC-FAD-PCM</t>
-  </si>
-  <si>
-    <t>168001 A.jpg</t>
   </si>
   <si>
     <t>s_sathien@Oceanglass.com</t>
@@ -10509,7 +10503,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10551,14 +10545,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10583,6 +10571,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10661,13 +10655,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11011,32 +11005,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
-        <v>2911</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
+      <c r="A1" s="17" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -11222,7 +11216,7 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="11" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="V4" s="3">
         <v>4</v>
@@ -11288,7 +11282,7 @@
         <v>74</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="V5" s="3">
         <v>3</v>
@@ -11352,7 +11346,7 @@
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="7" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="V6" s="3">
         <v>2</v>
@@ -11414,7 +11408,7 @@
         <v>1325</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="V7" s="3">
         <v>3</v>
@@ -11476,7 +11470,7 @@
         <v>314</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="V8" s="3">
         <v>3</v>
@@ -11536,7 +11530,7 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="7" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="V9" s="3">
         <v>3</v>
@@ -11598,7 +11592,7 @@
         <v>74</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="V10" s="3">
         <v>3</v>
@@ -11658,7 +11652,7 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="7" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="V11" s="3">
         <v>3</v>
@@ -11718,7 +11712,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="7" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="V12" s="3">
         <v>2</v>
@@ -11778,7 +11772,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="7" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="V13" s="3">
         <v>3</v>
@@ -11840,7 +11834,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="7" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="V14" s="3">
         <v>3</v>
@@ -11900,13 +11894,13 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="V15" s="3">
         <v>3</v>
@@ -11968,7 +11962,7 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="7" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="V16" s="3">
         <v>3</v>
@@ -12026,13 +12020,13 @@
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="7" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="V17" s="3">
         <v>2</v>
@@ -12094,7 +12088,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="7" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="V18" s="3">
         <v>4</v>
@@ -12154,7 +12148,7 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="7" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="V19" s="3">
         <v>3</v>
@@ -12214,7 +12208,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="7" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="V20" s="3">
         <v>3</v>
@@ -12274,7 +12268,7 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="7" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="V21" s="3">
         <v>3</v>
@@ -12334,7 +12328,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="7" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="V22" s="3">
         <v>3</v>
@@ -12392,13 +12386,13 @@
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="7" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="V23" s="3">
         <v>3</v>
@@ -12460,7 +12454,7 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="7" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="V24" s="3">
         <v>3</v>
@@ -12520,7 +12514,7 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="7" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="V25" s="3">
         <v>3</v>
@@ -12580,7 +12574,7 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="7" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="V26" s="3">
         <v>3</v>
@@ -12640,7 +12634,7 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="7" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="V27" s="3">
         <v>3</v>
@@ -12700,7 +12694,7 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>44</v>
@@ -12762,7 +12756,7 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="7" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>44</v>
@@ -12824,7 +12818,7 @@
         <v>445</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="V30" s="3">
         <v>3</v>
@@ -12890,7 +12884,7 @@
         <v>314</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="V31" s="3">
         <v>3</v>
@@ -12954,7 +12948,7 @@
       </c>
       <c r="T32" s="3"/>
       <c r="U32" s="7" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="V32" s="3">
         <v>3</v>
@@ -13016,7 +13010,7 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="7" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="V33" s="3">
         <v>3</v>
@@ -13035,10 +13029,10 @@
         <v>269032</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>3444</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>3445</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>728</v>
@@ -13047,13 +13041,13 @@
         <v>728</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="I34" s="3">
         <v>258026</v>
@@ -13062,25 +13056,25 @@
         <v>30484</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="3" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="7" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="V34" s="3" t="s">
         <v>44</v>
@@ -13138,7 +13132,7 @@
       </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3" t="s">
@@ -13148,7 +13142,7 @@
         <v>314</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="V35" s="3">
         <v>3</v>
@@ -13208,7 +13202,7 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="7" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="V36" s="3">
         <v>3</v>
@@ -13268,7 +13262,7 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="7" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="V37" s="3">
         <v>3</v>
@@ -13328,7 +13322,7 @@
         <v>397</v>
       </c>
       <c r="U38" s="7" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="V38" s="3">
         <v>3</v>
@@ -13392,7 +13386,7 @@
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="7" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="V39" s="3">
         <v>3</v>
@@ -13456,7 +13450,7 @@
       </c>
       <c r="T40" s="3"/>
       <c r="U40" s="7" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="V40" s="3">
         <v>3</v>
@@ -13518,7 +13512,7 @@
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="7" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="V41" s="3">
         <v>3</v>
@@ -13580,7 +13574,7 @@
       </c>
       <c r="T42" s="3"/>
       <c r="U42" s="7" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="V42" s="3">
         <v>3</v>
@@ -13640,7 +13634,7 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="7" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="V43" s="3">
         <v>2</v>
@@ -13700,7 +13694,7 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="7" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="V44" s="3">
         <v>3</v>
@@ -13758,11 +13752,11 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="7" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="V45" s="3">
         <v>3</v>
@@ -13822,7 +13816,7 @@
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="7" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="V46" s="3">
         <v>3</v>
@@ -13878,7 +13872,7 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="7" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="V47" s="3">
         <v>3</v>
@@ -13934,7 +13928,7 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="7" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="V48" s="3">
         <v>3</v>
@@ -13990,7 +13984,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="7" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="V49" s="3">
         <v>3</v>
@@ -14052,7 +14046,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="7" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="V50" s="3">
         <v>3</v>
@@ -14114,7 +14108,7 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="7" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="V51" s="3">
         <v>3</v>
@@ -14174,7 +14168,7 @@
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="7" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="V52" s="3">
         <v>3</v>
@@ -14234,7 +14228,7 @@
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
       <c r="U53" s="7" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="V53" s="3">
         <v>3</v>
@@ -14294,7 +14288,7 @@
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="7" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="V54" s="3">
         <v>3</v>
@@ -14354,7 +14348,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="7" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="V55" s="3" t="s">
         <v>44</v>
@@ -14414,7 +14408,7 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="7" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="V56" s="3" t="s">
         <v>44</v>
@@ -14474,7 +14468,7 @@
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
       <c r="U57" s="7" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>44</v>
@@ -14534,7 +14528,7 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="7" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>44</v>
@@ -14598,7 +14592,7 @@
       </c>
       <c r="T59" s="3"/>
       <c r="U59" s="7" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="V59" s="3">
         <v>3</v>
@@ -14666,7 +14660,7 @@
         <v>53</v>
       </c>
       <c r="U60" s="7" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="V60" s="3">
         <v>3</v>
@@ -14730,7 +14724,7 @@
         <v>33</v>
       </c>
       <c r="U61" s="7" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="V61" s="3">
         <v>4</v>
@@ -14792,7 +14786,7 @@
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="7" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="V62" s="3">
         <v>3</v>
@@ -14854,7 +14848,7 @@
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
       <c r="U63" s="7" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="V63" s="3">
         <v>3</v>
@@ -14916,7 +14910,7 @@
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="7" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="V64" s="3">
         <v>3</v>
@@ -14980,7 +14974,7 @@
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="7" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="V65" s="3">
         <v>3</v>
@@ -15013,7 +15007,7 @@
         <v>114</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>115</v>
@@ -15106,7 +15100,7 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="7" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="V67" s="3" t="s">
         <v>44</v>
@@ -15168,7 +15162,7 @@
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="7" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="V68" s="3">
         <v>3</v>
@@ -15230,7 +15224,7 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="7" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="V69" s="3">
         <v>3</v>
@@ -15294,7 +15288,7 @@
       </c>
       <c r="T70" s="3"/>
       <c r="U70" s="7" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="V70" s="3">
         <v>3</v>
@@ -15356,7 +15350,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
       <c r="U71" s="7" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="V71" s="3">
         <v>3</v>
@@ -15418,7 +15412,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="7" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="V72" s="3">
         <v>3</v>
@@ -15479,10 +15473,10 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
       <c r="T73" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U73" s="7" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="V73" s="3">
         <v>3</v>
@@ -15544,7 +15538,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="7" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="V74" s="3" t="s">
         <v>44</v>
@@ -15606,7 +15600,7 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
       <c r="U75" s="7" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="V75" s="3">
         <v>3</v>
@@ -15668,7 +15662,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
       <c r="U76" s="7" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>44</v>
@@ -15730,7 +15724,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
       <c r="U77" s="7" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="V77" s="3">
         <v>3</v>
@@ -15792,7 +15786,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
       <c r="U78" s="7" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="V78" s="3" t="s">
         <v>44</v>
@@ -15858,7 +15852,7 @@
         <v>74</v>
       </c>
       <c r="U79" s="7" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="V79" s="3">
         <v>3</v>
@@ -15892,7 +15886,7 @@
         <v>611</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>612</v>
@@ -15982,7 +15976,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="7" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="V81" s="3">
         <v>2</v>
@@ -16040,13 +16034,13 @@
       </c>
       <c r="P82" s="3"/>
       <c r="Q82" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="7" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="V82" s="3">
         <v>2</v>
@@ -16112,7 +16106,7 @@
         <v>53</v>
       </c>
       <c r="U83" s="7" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="V83" s="3">
         <v>3</v>
@@ -16170,7 +16164,7 @@
       </c>
       <c r="P84" s="3"/>
       <c r="Q84" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R84" s="3"/>
       <c r="S84" s="3" t="s">
@@ -16180,7 +16174,7 @@
         <v>74</v>
       </c>
       <c r="U84" s="7" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="V84" s="3">
         <v>3</v>
@@ -16246,7 +16240,7 @@
         <v>74</v>
       </c>
       <c r="U85" s="7" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="V85" s="3">
         <v>3</v>
@@ -16308,7 +16302,7 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="7" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="V86" s="3">
         <v>3</v>
@@ -16374,7 +16368,7 @@
         <v>53</v>
       </c>
       <c r="U87" s="7" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="V87" s="3">
         <v>3</v>
@@ -16432,7 +16426,7 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
       <c r="U88" s="7" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="V88" s="3">
         <v>3</v>
@@ -16496,7 +16490,7 @@
         <v>74</v>
       </c>
       <c r="U89" s="7" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="V89" s="3">
         <v>3</v>
@@ -16558,7 +16552,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="7" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="V90" s="3">
         <v>3</v>
@@ -16620,7 +16614,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
       <c r="U91" s="7" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="V91" s="3">
         <v>3</v>
@@ -16682,7 +16676,7 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
       <c r="U92" s="7" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="V92" s="3" t="s">
         <v>44</v>
@@ -16744,7 +16738,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
       <c r="U93" s="7" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="V93" s="3" t="s">
         <v>44</v>
@@ -16806,7 +16800,7 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
       <c r="U94" s="7" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>44</v>
@@ -16868,7 +16862,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="7" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="V95" s="3" t="s">
         <v>44</v>
@@ -16887,19 +16881,19 @@
         <v>169021</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>2913</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="3" t="s">
         <v>2914</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="E96" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="F96" s="15" t="s">
         <v>2915</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>2915</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>2916</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>71</v>
@@ -16919,10 +16913,10 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
       <c r="N96" s="3" t="s">
+        <v>2916</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>2917</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>2918</v>
       </c>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
@@ -16930,7 +16924,7 @@
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
       <c r="U96" s="7" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="V96" s="3" t="s">
         <v>44</v>
@@ -16996,7 +16990,7 @@
         <v>520</v>
       </c>
       <c r="U97" s="7" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="V97" s="3">
         <v>3</v>
@@ -17058,7 +17052,7 @@
         <v>74</v>
       </c>
       <c r="U98" s="7" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="V98" s="3">
         <v>3</v>
@@ -17124,7 +17118,7 @@
         <v>74</v>
       </c>
       <c r="U99" s="7" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="V99" s="3">
         <v>3</v>
@@ -17184,11 +17178,11 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
       <c r="S100" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T100" s="3"/>
       <c r="U100" s="7" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="V100" s="3">
         <v>3</v>
@@ -17250,7 +17244,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="7" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="V101" s="3">
         <v>3</v>
@@ -17312,7 +17306,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="7" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="V102" s="3">
         <v>3</v>
@@ -17374,7 +17368,7 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="7" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="V103" s="3" t="s">
         <v>44</v>
@@ -17432,7 +17426,7 @@
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="R104" s="3"/>
       <c r="S104" s="3" t="s">
@@ -17442,7 +17436,7 @@
         <v>33</v>
       </c>
       <c r="U104" s="7" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="V104" s="3">
         <v>3</v>
@@ -17504,7 +17498,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="7" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="V105" s="3">
         <v>3</v>
@@ -17568,7 +17562,7 @@
       </c>
       <c r="T106" s="3"/>
       <c r="U106" s="7" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="V106" s="3">
         <v>3</v>
@@ -17630,7 +17624,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="7" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="V107" s="3">
         <v>3</v>
@@ -17688,7 +17682,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="7" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="V108" s="3">
         <v>2</v>
@@ -17750,7 +17744,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="7" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="V109" s="3">
         <v>3</v>
@@ -17811,10 +17805,10 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
       <c r="T110" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U110" s="7" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="V110" s="3">
         <v>3</v>
@@ -17876,7 +17870,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="7" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="V111" s="3">
         <v>3</v>
@@ -17934,7 +17928,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="7" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="V112" s="3">
         <v>3</v>
@@ -17996,7 +17990,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="7" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="V113" s="3">
         <v>3</v>
@@ -18054,7 +18048,7 @@
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R114" s="3"/>
       <c r="S114" s="3" t="s">
@@ -18064,7 +18058,7 @@
         <v>240</v>
       </c>
       <c r="U114" s="7" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="V114" s="3">
         <v>3</v>
@@ -18126,7 +18120,7 @@
         <v>397</v>
       </c>
       <c r="U115" s="7" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="V115" s="3">
         <v>3</v>
@@ -18188,7 +18182,7 @@
         <v>397</v>
       </c>
       <c r="U116" s="7" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="V116" s="3">
         <v>3</v>
@@ -18252,7 +18246,7 @@
         <v>33</v>
       </c>
       <c r="U117" s="7" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="V117" s="3">
         <v>3</v>
@@ -18314,7 +18308,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
       <c r="U118" s="7" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="V118" s="3" t="s">
         <v>44</v>
@@ -18380,7 +18374,7 @@
         <v>74</v>
       </c>
       <c r="U119" s="7" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="V119" s="3">
         <v>3</v>
@@ -18444,7 +18438,7 @@
       </c>
       <c r="T120" s="3"/>
       <c r="U120" s="7" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="V120" s="3">
         <v>3</v>
@@ -18502,7 +18496,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="7" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="V121" s="3">
         <v>3</v>
@@ -18560,7 +18554,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="7" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="V122" s="3">
         <v>3</v>
@@ -18618,7 +18612,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="7" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="V123" s="3" t="s">
         <v>44</v>
@@ -18676,7 +18670,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="7" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="V124" s="3">
         <v>3</v>
@@ -18742,7 +18736,7 @@
         <v>53</v>
       </c>
       <c r="U125" s="7" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="V125" s="3">
         <v>3</v>
@@ -18808,7 +18802,7 @@
         <v>240</v>
       </c>
       <c r="U126" s="7" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="V126" s="3">
         <v>4</v>
@@ -18872,7 +18866,7 @@
         <v>33</v>
       </c>
       <c r="U127" s="7" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="V127" s="3">
         <v>3</v>
@@ -18934,7 +18928,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="7" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="V128" s="3">
         <v>3</v>
@@ -18992,7 +18986,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="7" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="V129" s="3">
         <v>3</v>
@@ -19054,7 +19048,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="7" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="V130" s="3">
         <v>3</v>
@@ -19112,7 +19106,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
       <c r="U131" s="7" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="V131" s="3">
         <v>3</v>
@@ -19174,7 +19168,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
       <c r="U132" s="7" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="V132" s="3">
         <v>3</v>
@@ -19193,16 +19187,16 @@
         <v>169018</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>2919</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="3" t="s">
         <v>2920</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>2921</v>
-      </c>
       <c r="E133" s="3" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="F133" s="15" t="s">
         <v>221</v>
@@ -19225,10 +19219,10 @@
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
       <c r="N133" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="O133" s="3" t="s">
         <v>2922</v>
-      </c>
-      <c r="O133" s="3" t="s">
-        <v>2923</v>
       </c>
       <c r="P133" s="3"/>
       <c r="Q133" s="3"/>
@@ -19236,7 +19230,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="7" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="V133" s="3" t="s">
         <v>44</v>
@@ -19302,7 +19296,7 @@
         <v>240</v>
       </c>
       <c r="U134" s="7" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="V134" s="3">
         <v>3</v>
@@ -19366,7 +19360,7 @@
         <v>33</v>
       </c>
       <c r="U135" s="7" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="V135" s="3">
         <v>3</v>
@@ -19430,7 +19424,7 @@
         <v>33</v>
       </c>
       <c r="U136" s="7" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="V136" s="3">
         <v>3</v>
@@ -19492,7 +19486,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="7" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="V137" s="3">
         <v>3</v>
@@ -19550,7 +19544,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="7" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="V138" s="3">
         <v>3</v>
@@ -19612,7 +19606,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="7" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="V139" s="3" t="s">
         <v>44</v>
@@ -19674,7 +19668,7 @@
         <v>314</v>
       </c>
       <c r="U140" s="7" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="V140" s="3">
         <v>3</v>
@@ -19736,7 +19730,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="7" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="V141" s="3">
         <v>3</v>
@@ -19798,7 +19792,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="7" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="V142" s="3">
         <v>3</v>
@@ -19856,7 +19850,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="7" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="V143" s="3">
         <v>3</v>
@@ -19918,7 +19912,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="7" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="V144" s="3">
         <v>3</v>
@@ -19980,7 +19974,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="V145" s="3" t="s">
         <v>44</v>
@@ -20042,7 +20036,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="V146" s="3" t="s">
         <v>44</v>
@@ -20104,7 +20098,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="7" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="V147" s="3" t="s">
         <v>44</v>
@@ -20170,7 +20164,7 @@
         <v>52</v>
       </c>
       <c r="U148" s="7" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="V148" s="3">
         <v>2</v>
@@ -20234,7 +20228,7 @@
         <v>239</v>
       </c>
       <c r="U149" s="7" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="V149" s="3">
         <v>2</v>
@@ -20294,7 +20288,7 @@
       </c>
       <c r="T150" s="3"/>
       <c r="U150" s="7" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="V150" s="3">
         <v>3</v>
@@ -20358,7 +20352,7 @@
       </c>
       <c r="T151" s="3"/>
       <c r="U151" s="7" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="V151" s="3">
         <v>2</v>
@@ -20389,7 +20383,7 @@
         <v>376</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>66</v>
@@ -20416,17 +20410,17 @@
       </c>
       <c r="P152" s="3"/>
       <c r="Q152" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="R152" s="3"/>
       <c r="S152" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T152" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U152" s="7" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="V152" s="3">
         <v>2</v>
@@ -20492,7 +20486,7 @@
         <v>33</v>
       </c>
       <c r="U153" s="7" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="V153" s="3">
         <v>3</v>
@@ -20554,7 +20548,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="7" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="V154" s="3">
         <v>3</v>
@@ -20593,8 +20587,8 @@
       <c r="H155" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="I155" s="12" t="s">
-        <v>2908</v>
+      <c r="I155" s="19">
+        <v>169024</v>
       </c>
       <c r="J155" s="5">
         <v>24215</v>
@@ -20616,7 +20610,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="7" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="V155" s="3">
         <v>3</v>
@@ -20680,7 +20674,7 @@
       </c>
       <c r="T156" s="3"/>
       <c r="U156" s="7" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="V156" s="3">
         <v>3</v>
@@ -20746,7 +20740,7 @@
         <v>33</v>
       </c>
       <c r="U157" s="7" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="V157" s="3">
         <v>3</v>
@@ -20810,7 +20804,7 @@
       </c>
       <c r="T158" s="3"/>
       <c r="U158" s="7" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="V158" s="3">
         <v>2</v>
@@ -20876,7 +20870,7 @@
         <v>33</v>
       </c>
       <c r="U159" s="7" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="V159" s="3">
         <v>3</v>
@@ -20907,7 +20901,7 @@
         <v>642</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>40</v>
@@ -20936,11 +20930,11 @@
       <c r="Q160" s="3"/>
       <c r="R160" s="3"/>
       <c r="S160" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T160" s="3"/>
       <c r="U160" s="7" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="V160" s="3">
         <v>3</v>
@@ -21004,7 +20998,7 @@
       </c>
       <c r="T161" s="3"/>
       <c r="U161" s="7" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="V161" s="3">
         <v>3</v>
@@ -21062,7 +21056,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="7" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="V162" s="3">
         <v>3</v>
@@ -21128,7 +21122,7 @@
         <v>314</v>
       </c>
       <c r="U163" s="7" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="V163" s="3">
         <v>3</v>
@@ -21192,7 +21186,7 @@
       </c>
       <c r="T164" s="3"/>
       <c r="U164" s="7" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="V164" s="3">
         <v>3</v>
@@ -21231,8 +21225,8 @@
       <c r="H165" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I165" s="12" t="s">
-        <v>2908</v>
+      <c r="I165" s="19">
+        <v>169024</v>
       </c>
       <c r="J165" s="5">
         <v>29389</v>
@@ -21258,7 +21252,7 @@
         <v>74</v>
       </c>
       <c r="U165" s="7" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="V165" s="3">
         <v>3</v>
@@ -21320,7 +21314,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="7" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="V166" s="3">
         <v>3</v>
@@ -21382,7 +21376,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="7" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="V167" s="3">
         <v>2</v>
@@ -21448,7 +21442,7 @@
         <v>314</v>
       </c>
       <c r="U168" s="7" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="V168" s="3">
         <v>2</v>
@@ -21514,7 +21508,7 @@
         <v>74</v>
       </c>
       <c r="U169" s="7" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="V169" s="3">
         <v>3</v>
@@ -21578,7 +21572,7 @@
       </c>
       <c r="T170" s="3"/>
       <c r="U170" s="7" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="V170" s="3">
         <v>3</v>
@@ -21639,10 +21633,10 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
       <c r="T171" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U171" s="7" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="V171" s="3">
         <v>3</v>
@@ -21704,7 +21698,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="7" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="V172" s="3">
         <v>3</v>
@@ -21766,7 +21760,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="7" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="V173" s="3">
         <v>3</v>
@@ -21828,7 +21822,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="7" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="V174" s="3">
         <v>3</v>
@@ -21890,7 +21884,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="7" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="V175" s="3">
         <v>3</v>
@@ -21952,7 +21946,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="7" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="V176" s="3">
         <v>3</v>
@@ -21991,8 +21985,8 @@
       <c r="H177" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I177" s="12" t="s">
-        <v>2908</v>
+      <c r="I177" s="19">
+        <v>169024</v>
       </c>
       <c r="J177" s="5">
         <v>29553</v>
@@ -22014,7 +22008,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="7" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="V177" s="3">
         <v>3</v>
@@ -22076,7 +22070,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="7" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="V178" s="3">
         <v>3</v>
@@ -22107,7 +22101,7 @@
         <v>751</v>
       </c>
       <c r="F179" s="15" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>557</v>
@@ -22115,8 +22109,8 @@
       <c r="H179" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I179" s="12" t="s">
-        <v>2908</v>
+      <c r="I179" s="19">
+        <v>169024</v>
       </c>
       <c r="J179" s="5">
         <v>32000</v>
@@ -22138,7 +22132,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="7" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="V179" s="3">
         <v>2</v>
@@ -22200,7 +22194,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="7" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="V180" s="3" t="s">
         <v>44</v>
@@ -22264,7 +22258,7 @@
         <v>33</v>
       </c>
       <c r="U181" s="7" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="V181" s="3">
         <v>3</v>
@@ -22388,7 +22382,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="7" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="V183" s="3">
         <v>3</v>
@@ -22448,13 +22442,13 @@
       <c r="Q184" s="3"/>
       <c r="R184" s="3"/>
       <c r="S184" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T184" s="3" t="s">
         <v>240</v>
       </c>
       <c r="U184" s="7" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="V184" s="3">
         <v>4</v>
@@ -22516,7 +22510,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="7" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="V185" s="3">
         <v>3</v>
@@ -22578,7 +22572,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="7" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="V186" s="3">
         <v>3</v>
@@ -22640,7 +22634,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="7" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="V187" s="3">
         <v>3</v>
@@ -22702,7 +22696,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="7" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="V188" s="3">
         <v>3</v>
@@ -22764,7 +22758,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="7" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="V189" s="3" t="s">
         <v>44</v>
@@ -22845,28 +22839,28 @@
         <v>269040</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>3470</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>3471</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="D191" s="3" t="s">
         <v>3472</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="E191" s="3" t="s">
+        <v>3472</v>
+      </c>
+      <c r="F191" s="15" t="s">
         <v>3473</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>3473</v>
-      </c>
-      <c r="F191" s="15" t="s">
-        <v>3474</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="J191" s="5">
         <v>29660</v>
@@ -22877,10 +22871,10 @@
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
       <c r="N191" s="3" t="s">
+        <v>3474</v>
+      </c>
+      <c r="O191" s="3" t="s">
         <v>3475</v>
-      </c>
-      <c r="O191" s="3" t="s">
-        <v>3476</v>
       </c>
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
@@ -22888,7 +22882,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="7" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="V191" s="3" t="s">
         <v>44</v>
@@ -22904,7 +22898,7 @@
     </row>
     <row r="192" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>2301</v>
@@ -22913,13 +22907,13 @@
         <v>2302</v>
       </c>
       <c r="D192" s="3" t="s">
+        <v>3481</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>3481</v>
+      </c>
+      <c r="F192" s="15" t="s">
         <v>3482</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>3482</v>
-      </c>
-      <c r="F192" s="15" t="s">
-        <v>3483</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>66</v>
@@ -22927,8 +22921,8 @@
       <c r="H192" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="I192" s="17" t="s">
-        <v>2908</v>
+      <c r="I192" s="19">
+        <v>169024</v>
       </c>
       <c r="J192" s="5">
         <v>26070</v>
@@ -22939,7 +22933,7 @@
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
       <c r="N192" s="3" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="O192" s="3" t="s">
         <v>2306</v>
@@ -22986,7 +22980,7 @@
         <v>2379</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>2380</v>
@@ -23024,7 +23018,7 @@
         <v>44</v>
       </c>
       <c r="Y193" s="3" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="Z193" s="8"/>
     </row>
@@ -23078,7 +23072,7 @@
         <v>448</v>
       </c>
       <c r="U194" s="7" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="V194" s="3">
         <v>3</v>
@@ -23138,13 +23132,13 @@
       <c r="Q195" s="3"/>
       <c r="R195" s="3"/>
       <c r="S195" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T195" s="3" t="s">
         <v>445</v>
       </c>
       <c r="U195" s="7" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="V195" s="3">
         <v>3</v>
@@ -23210,7 +23204,7 @@
         <v>448</v>
       </c>
       <c r="U196" s="7" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="V196" s="3">
         <v>3</v>
@@ -23276,7 +23270,7 @@
         <v>240</v>
       </c>
       <c r="U197" s="7" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="V197" s="3">
         <v>3</v>
@@ -23342,7 +23336,7 @@
         <v>448</v>
       </c>
       <c r="U198" s="7" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="V198" s="3">
         <v>3</v>
@@ -23408,7 +23402,7 @@
         <v>448</v>
       </c>
       <c r="U199" s="7" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="V199" s="3">
         <v>3</v>
@@ -23474,7 +23468,7 @@
         <v>1236</v>
       </c>
       <c r="U200" s="7" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="V200" s="3">
         <v>3</v>
@@ -23540,7 +23534,7 @@
         <v>281</v>
       </c>
       <c r="U201" s="7" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="V201" s="3">
         <v>3</v>
@@ -23604,7 +23598,7 @@
       </c>
       <c r="T202" s="3"/>
       <c r="U202" s="7" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="V202" s="3">
         <v>3</v>
@@ -23666,7 +23660,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="7" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="V203" s="3" t="s">
         <v>44</v>
@@ -23730,7 +23724,7 @@
         <v>397</v>
       </c>
       <c r="U204" s="7" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="V204" s="3">
         <v>3</v>
@@ -23796,7 +23790,7 @@
         <v>397</v>
       </c>
       <c r="U205" s="7" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="V205" s="3">
         <v>4</v>
@@ -23862,7 +23856,7 @@
         <v>314</v>
       </c>
       <c r="U206" s="7" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="V206" s="3">
         <v>4</v>
@@ -23893,7 +23887,7 @@
         <v>942</v>
       </c>
       <c r="F207" s="15" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>515</v>
@@ -23920,7 +23914,7 @@
       </c>
       <c r="P207" s="3"/>
       <c r="Q207" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R207" s="3"/>
       <c r="S207" s="3"/>
@@ -23928,7 +23922,7 @@
         <v>240</v>
       </c>
       <c r="U207" s="7" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="V207" s="3">
         <v>4</v>
@@ -23994,7 +23988,7 @@
         <v>74</v>
       </c>
       <c r="U208" s="7" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="V208" s="3">
         <v>4</v>
@@ -24054,11 +24048,11 @@
       <c r="Q209" s="3"/>
       <c r="R209" s="3"/>
       <c r="S209" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T209" s="3"/>
       <c r="U209" s="7" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="V209" s="3">
         <v>3</v>
@@ -24120,7 +24114,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="7" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="V210" s="3">
         <v>3</v>
@@ -24180,7 +24174,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V211" s="3" t="s">
         <v>44</v>
@@ -24238,7 +24232,7 @@
         <v>281</v>
       </c>
       <c r="U212" s="7" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="V212" s="3">
         <v>3</v>
@@ -24296,7 +24290,7 @@
       </c>
       <c r="T213" s="3"/>
       <c r="U213" s="7" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="V213" s="3">
         <v>3</v>
@@ -24354,7 +24348,7 @@
       </c>
       <c r="T214" s="3"/>
       <c r="U214" s="7" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="V214" s="3">
         <v>3</v>
@@ -24412,7 +24406,7 @@
       </c>
       <c r="T215" s="3"/>
       <c r="U215" s="7" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="V215" s="3">
         <v>3</v>
@@ -24470,7 +24464,7 @@
       </c>
       <c r="T216" s="3"/>
       <c r="U216" s="7" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="V216" s="3">
         <v>3</v>
@@ -24526,7 +24520,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="7" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="V217" s="3">
         <v>3</v>
@@ -24582,7 +24576,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="7" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="V218" s="3">
         <v>3</v>
@@ -24644,7 +24638,7 @@
         <v>240</v>
       </c>
       <c r="U219" s="7" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="V219" s="3">
         <v>3</v>
@@ -24706,7 +24700,7 @@
         <v>74</v>
       </c>
       <c r="U220" s="7" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="V220" s="3">
         <v>3</v>
@@ -24766,7 +24760,7 @@
         <v>445</v>
       </c>
       <c r="U221" s="7" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="V221" s="3">
         <v>3</v>
@@ -24822,7 +24816,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="7" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="V222" s="3">
         <v>3</v>
@@ -24880,7 +24874,7 @@
         <v>33</v>
       </c>
       <c r="U223" s="7" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="V223" s="3">
         <v>2</v>
@@ -24936,7 +24930,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="7" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="V224" s="3">
         <v>3</v>
@@ -24996,11 +24990,11 @@
       <c r="Q225" s="3"/>
       <c r="R225" s="3"/>
       <c r="S225" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T225" s="3"/>
       <c r="U225" s="7" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="V225" s="3">
         <v>4</v>
@@ -25060,7 +25054,7 @@
         <v>281</v>
       </c>
       <c r="U226" s="7" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="V226" s="3">
         <v>3</v>
@@ -25118,7 +25112,7 @@
         <v>281</v>
       </c>
       <c r="U227" s="7" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="V227" s="3">
         <v>3</v>
@@ -25174,7 +25168,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="7" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="V228" s="3">
         <v>2</v>
@@ -25234,7 +25228,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="7" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="V229" s="3" t="s">
         <v>44</v>
@@ -25294,7 +25288,7 @@
       </c>
       <c r="T230" s="3"/>
       <c r="U230" s="7" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="V230" s="3">
         <v>3</v>
@@ -25350,13 +25344,13 @@
       <c r="Q231" s="3"/>
       <c r="R231" s="3"/>
       <c r="S231" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T231" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U231" s="7" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="V231" s="3">
         <v>3</v>
@@ -25416,7 +25410,7 @@
         <v>281</v>
       </c>
       <c r="U232" s="7" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="V232" s="3">
         <v>3</v>
@@ -25472,7 +25466,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="7" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="V233" s="3">
         <v>3</v>
@@ -25528,7 +25522,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="7" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="V234" s="3">
         <v>3</v>
@@ -25590,7 +25584,7 @@
         <v>33</v>
       </c>
       <c r="U235" s="7" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="V235" s="3">
         <v>3</v>
@@ -25648,7 +25642,7 @@
       </c>
       <c r="P236" s="3"/>
       <c r="Q236" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R236" s="3"/>
       <c r="S236" s="3" t="s">
@@ -25658,7 +25652,7 @@
         <v>445</v>
       </c>
       <c r="U236" s="7" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="V236" s="3">
         <v>3</v>
@@ -25720,7 +25714,7 @@
         <v>111</v>
       </c>
       <c r="U237" s="7" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="V237" s="3">
         <v>3</v>
@@ -25786,7 +25780,7 @@
         <v>957</v>
       </c>
       <c r="U238" s="7" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="V238" s="3">
         <v>3</v>
@@ -25852,7 +25846,7 @@
         <v>74</v>
       </c>
       <c r="U239" s="7" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="V239" s="3">
         <v>3</v>
@@ -25918,7 +25912,7 @@
         <v>53</v>
       </c>
       <c r="U240" s="7" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="V240" s="3">
         <v>4</v>
@@ -25984,7 +25978,7 @@
         <v>33</v>
       </c>
       <c r="U241" s="7" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="V241" s="3">
         <v>4</v>
@@ -26046,7 +26040,7 @@
       </c>
       <c r="T242" s="3"/>
       <c r="U242" s="7" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="V242" s="3">
         <v>3</v>
@@ -26108,7 +26102,7 @@
       </c>
       <c r="T243" s="3"/>
       <c r="U243" s="7" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="V243" s="3">
         <v>3</v>
@@ -26172,7 +26166,7 @@
         <v>445</v>
       </c>
       <c r="U244" s="7" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="V244" s="3">
         <v>4</v>
@@ -26234,7 +26228,7 @@
       </c>
       <c r="T245" s="3"/>
       <c r="U245" s="7" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="V245" s="3">
         <v>3</v>
@@ -26290,7 +26284,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="7" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="V246" s="3">
         <v>2</v>
@@ -26354,7 +26348,7 @@
         <v>240</v>
       </c>
       <c r="U247" s="7" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="V247" s="3">
         <v>3</v>
@@ -26412,13 +26406,13 @@
       <c r="Q248" s="3"/>
       <c r="R248" s="3"/>
       <c r="S248" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T248" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U248" s="7" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="V248" s="3">
         <v>3</v>
@@ -26482,7 +26476,7 @@
         <v>74</v>
       </c>
       <c r="U249" s="7" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="V249" s="3">
         <v>4</v>
@@ -26548,7 +26542,7 @@
         <v>240</v>
       </c>
       <c r="U250" s="7" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="V250" s="3">
         <v>3</v>
@@ -26612,7 +26606,7 @@
       </c>
       <c r="T251" s="3"/>
       <c r="U251" s="7" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="V251" s="3">
         <v>3</v>
@@ -26672,7 +26666,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="7" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="V252" s="3">
         <v>3</v>
@@ -26732,7 +26726,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="7" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="V253" s="3">
         <v>3</v>
@@ -26792,7 +26786,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="7" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="V254" s="3">
         <v>3</v>
@@ -26852,7 +26846,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="7" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="V255" s="3">
         <v>3</v>
@@ -26912,7 +26906,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="7" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="V256" s="3">
         <v>3</v>
@@ -26972,7 +26966,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="7" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="V257" s="3">
         <v>3</v>
@@ -27034,7 +27028,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="7" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="V258" s="3">
         <v>3</v>
@@ -27094,7 +27088,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="7" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="V259" s="3">
         <v>2</v>
@@ -27156,7 +27150,7 @@
         <v>964</v>
       </c>
       <c r="U260" s="7" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="V260" s="3">
         <v>4</v>
@@ -27183,7 +27177,7 @@
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
       <c r="F261" s="15" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>29</v>
@@ -27212,13 +27206,13 @@
       <c r="Q261" s="3"/>
       <c r="R261" s="3"/>
       <c r="S261" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T261" s="3" t="s">
         <v>1061</v>
       </c>
       <c r="U261" s="7" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="V261" s="3">
         <v>4</v>
@@ -27278,7 +27272,7 @@
       </c>
       <c r="T262" s="3"/>
       <c r="U262" s="7" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="V262" s="3">
         <v>4</v>
@@ -27336,7 +27330,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="7" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="V263" s="3">
         <v>4</v>
@@ -27398,7 +27392,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="7" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="V264" s="3" t="s">
         <v>44</v>
@@ -27460,7 +27454,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="7" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="V265" s="3" t="s">
         <v>44</v>
@@ -27524,7 +27518,7 @@
       </c>
       <c r="T266" s="3"/>
       <c r="U266" s="7" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="V266" s="3">
         <v>3</v>
@@ -27588,7 +27582,7 @@
       </c>
       <c r="T267" s="3"/>
       <c r="U267" s="7" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="V267" s="3">
         <v>4</v>
@@ -27648,7 +27642,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V268" s="3" t="s">
         <v>44</v>
@@ -27714,7 +27708,7 @@
         <v>314</v>
       </c>
       <c r="U269" s="7" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="V269" s="3">
         <v>4</v>
@@ -27780,7 +27774,7 @@
         <v>74</v>
       </c>
       <c r="U270" s="7" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="V270" s="3">
         <v>3</v>
@@ -27846,7 +27840,7 @@
         <v>314</v>
       </c>
       <c r="U271" s="7" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="V271" s="3">
         <v>4</v>
@@ -27904,13 +27898,13 @@
       <c r="Q272" s="3"/>
       <c r="R272" s="3"/>
       <c r="S272" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T272" s="3" t="s">
         <v>281</v>
       </c>
       <c r="U272" s="7" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="V272" s="3">
         <v>3</v>
@@ -27976,7 +27970,7 @@
         <v>314</v>
       </c>
       <c r="U273" s="7" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="V273" s="3">
         <v>4</v>
@@ -28038,7 +28032,7 @@
       </c>
       <c r="T274" s="3"/>
       <c r="U274" s="7" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="V274" s="3">
         <v>3</v>
@@ -28100,7 +28094,7 @@
       </c>
       <c r="T275" s="3"/>
       <c r="U275" s="7" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="V275" s="3">
         <v>3</v>
@@ -28160,7 +28154,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="7" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="V276" s="3">
         <v>2</v>
@@ -28224,7 +28218,7 @@
         <v>240</v>
       </c>
       <c r="U277" s="7" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="V277" s="3">
         <v>3</v>
@@ -28282,11 +28276,11 @@
       <c r="Q278" s="3"/>
       <c r="R278" s="3"/>
       <c r="S278" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T278" s="3"/>
       <c r="U278" s="7" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="V278" s="3">
         <v>3</v>
@@ -28350,7 +28344,7 @@
         <v>314</v>
       </c>
       <c r="U279" s="7" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="V279" s="3">
         <v>2</v>
@@ -28412,7 +28406,7 @@
       </c>
       <c r="T280" s="3"/>
       <c r="U280" s="7" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="V280" s="3">
         <v>3</v>
@@ -28474,7 +28468,7 @@
       </c>
       <c r="T281" s="3"/>
       <c r="U281" s="7" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="V281" s="3">
         <v>3</v>
@@ -28536,7 +28530,7 @@
       </c>
       <c r="T282" s="3"/>
       <c r="U282" s="7" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="V282" s="3">
         <v>3</v>
@@ -28595,10 +28589,10 @@
       <c r="R283" s="3"/>
       <c r="S283" s="3"/>
       <c r="T283" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U283" s="7" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="V283" s="3">
         <v>3</v>
@@ -28658,7 +28652,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="7" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="V284" s="3">
         <v>2</v>
@@ -28718,7 +28712,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="7" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="V285" s="3">
         <v>3</v>
@@ -28782,7 +28776,7 @@
       </c>
       <c r="T286" s="3"/>
       <c r="U286" s="7" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="V286" s="3">
         <v>4</v>
@@ -28842,7 +28836,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="7" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="V287" s="3">
         <v>3</v>
@@ -28902,7 +28896,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="7" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="V288" s="3">
         <v>3</v>
@@ -28964,7 +28958,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="7" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="V289" s="3">
         <v>3</v>
@@ -29026,7 +29020,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="7" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="V290" s="3">
         <v>3</v>
@@ -29086,7 +29080,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="7" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="V291" s="3">
         <v>3</v>
@@ -29146,7 +29140,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="V292" s="3">
         <v>2</v>
@@ -29208,7 +29202,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="7" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="V293" s="3">
         <v>3</v>
@@ -29268,7 +29262,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="7" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="V294" s="3">
         <v>1</v>
@@ -29328,7 +29322,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="7" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="V295" s="3">
         <v>1</v>
@@ -29390,7 +29384,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="7" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="V296" s="3" t="s">
         <v>44</v>
@@ -29450,7 +29444,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V297" s="3" t="s">
         <v>44</v>
@@ -29516,7 +29510,7 @@
         <v>1236</v>
       </c>
       <c r="U298" s="7" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="V298" s="3">
         <v>3</v>
@@ -29580,7 +29574,7 @@
       </c>
       <c r="T299" s="3"/>
       <c r="U299" s="7" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="V299" s="3">
         <v>3</v>
@@ -29646,7 +29640,7 @@
         <v>314</v>
       </c>
       <c r="U300" s="7" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="V300" s="3">
         <v>3</v>
@@ -29710,7 +29704,7 @@
       </c>
       <c r="T301" s="3"/>
       <c r="U301" s="7" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="V301" s="3">
         <v>3</v>
@@ -29776,7 +29770,7 @@
         <v>445</v>
       </c>
       <c r="U302" s="7" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="V302" s="3">
         <v>3</v>
@@ -29840,7 +29834,7 @@
         <v>397</v>
       </c>
       <c r="U303" s="7" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="V303" s="3">
         <v>3</v>
@@ -29902,7 +29896,7 @@
       </c>
       <c r="T304" s="3"/>
       <c r="U304" s="7" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="V304" s="3">
         <v>3</v>
@@ -29964,7 +29958,7 @@
       </c>
       <c r="T305" s="3"/>
       <c r="U305" s="7" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="V305" s="3">
         <v>3</v>
@@ -30028,7 +30022,7 @@
       </c>
       <c r="T306" s="3"/>
       <c r="U306" s="7" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="V306" s="3">
         <v>4</v>
@@ -30088,7 +30082,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="7" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="V307" s="3">
         <v>3</v>
@@ -30146,7 +30140,7 @@
       </c>
       <c r="P308" s="3"/>
       <c r="Q308" s="3" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="R308" s="3"/>
       <c r="S308" s="3" t="s">
@@ -30156,7 +30150,7 @@
         <v>74</v>
       </c>
       <c r="U308" s="7" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="V308" s="3">
         <v>3</v>
@@ -30222,7 +30216,7 @@
         <v>281</v>
       </c>
       <c r="U309" s="7" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="V309" s="3">
         <v>3</v>
@@ -30286,7 +30280,7 @@
         <v>314</v>
       </c>
       <c r="U310" s="7" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="V310" s="3">
         <v>3</v>
@@ -30350,7 +30344,7 @@
       </c>
       <c r="T311" s="3"/>
       <c r="U311" s="7" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="V311" s="3">
         <v>4</v>
@@ -30412,7 +30406,7 @@
       </c>
       <c r="T312" s="3"/>
       <c r="U312" s="7" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="V312" s="3">
         <v>3</v>
@@ -30476,7 +30470,7 @@
         <v>445</v>
       </c>
       <c r="U313" s="7" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="V313" s="3">
         <v>3</v>
@@ -30538,7 +30532,7 @@
       </c>
       <c r="T314" s="3"/>
       <c r="U314" s="7" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="V314" s="3">
         <v>4</v>
@@ -30598,7 +30592,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="7" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="V315" s="3">
         <v>3</v>
@@ -30658,7 +30652,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="7" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="V316" s="3">
         <v>3</v>
@@ -30717,10 +30711,10 @@
       <c r="R317" s="3"/>
       <c r="S317" s="3"/>
       <c r="T317" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U317" s="7" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="V317" s="3">
         <v>4</v>
@@ -30776,7 +30770,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="7" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="V318" s="3">
         <v>3</v>
@@ -30832,7 +30826,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="7" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="V319" s="3">
         <v>3</v>
@@ -30888,7 +30882,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="7" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="V320" s="3">
         <v>3</v>
@@ -30944,7 +30938,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="7" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="V321" s="3">
         <v>2</v>
@@ -31006,7 +31000,7 @@
       </c>
       <c r="T322" s="3"/>
       <c r="U322" s="7" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="V322" s="3">
         <v>3</v>
@@ -31064,11 +31058,11 @@
       <c r="Q323" s="3"/>
       <c r="R323" s="3"/>
       <c r="S323" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T323" s="3"/>
       <c r="U323" s="7" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="V323" s="3">
         <v>3</v>
@@ -31130,7 +31124,7 @@
       </c>
       <c r="T324" s="3"/>
       <c r="U324" s="7" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="V324" s="3">
         <v>4</v>
@@ -31186,7 +31180,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="7" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="V325" s="3">
         <v>3</v>
@@ -31242,7 +31236,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="7" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="V326" s="3">
         <v>3</v>
@@ -31302,7 +31296,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="7" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="V327" s="3">
         <v>3</v>
@@ -31364,7 +31358,7 @@
       </c>
       <c r="T328" s="3"/>
       <c r="U328" s="7" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="V328" s="3">
         <v>3</v>
@@ -31426,7 +31420,7 @@
       </c>
       <c r="T329" s="3"/>
       <c r="U329" s="7" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="V329" s="3">
         <v>3</v>
@@ -31490,7 +31484,7 @@
         <v>1236</v>
       </c>
       <c r="U330" s="7" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="V330" s="3">
         <v>3</v>
@@ -31554,7 +31548,7 @@
         <v>314</v>
       </c>
       <c r="U331" s="7" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="V331" s="3">
         <v>3</v>
@@ -31616,7 +31610,7 @@
         <v>74</v>
       </c>
       <c r="U332" s="7" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="V332" s="3">
         <v>3</v>
@@ -31678,7 +31672,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="7" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="V333" s="3">
         <v>3</v>
@@ -31736,7 +31730,7 @@
         <v>240</v>
       </c>
       <c r="U334" s="7" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="V334" s="3">
         <v>3</v>
@@ -31794,7 +31788,7 @@
         <v>33</v>
       </c>
       <c r="U335" s="7" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="V335" s="3">
         <v>3</v>
@@ -31850,7 +31844,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="7" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="V336" s="3">
         <v>4</v>
@@ -31906,7 +31900,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="7" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="V337" s="3">
         <v>3</v>
@@ -31962,7 +31956,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="7" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="V338" s="3">
         <v>2</v>
@@ -32018,7 +32012,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="7" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="V339" s="3">
         <v>3</v>
@@ -32078,7 +32072,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="7" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="V340" s="3">
         <v>3</v>
@@ -32138,7 +32132,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="V341" s="3">
         <v>2</v>
@@ -32198,7 +32192,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="V342" s="3">
         <v>2</v>
@@ -32258,7 +32252,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="7" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="V343" s="3">
         <v>2</v>
@@ -32320,7 +32314,7 @@
       </c>
       <c r="T344" s="3"/>
       <c r="U344" s="7" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="V344" s="3">
         <v>4</v>
@@ -32386,7 +32380,7 @@
         <v>397</v>
       </c>
       <c r="U345" s="7" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="V345" s="3">
         <v>3</v>
@@ -32449,10 +32443,10 @@
         <v>1111</v>
       </c>
       <c r="T346" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U346" s="7" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="V346" s="3">
         <v>4</v>
@@ -32510,11 +32504,11 @@
       <c r="Q347" s="3"/>
       <c r="R347" s="3"/>
       <c r="S347" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T347" s="3"/>
       <c r="U347" s="7" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="V347" s="3">
         <v>3</v>
@@ -32578,7 +32572,7 @@
         <v>314</v>
       </c>
       <c r="U348" s="7" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="V348" s="3">
         <v>4</v>
@@ -32642,7 +32636,7 @@
         <v>397</v>
       </c>
       <c r="U349" s="7" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="V349" s="3">
         <v>3</v>
@@ -32704,7 +32698,7 @@
       </c>
       <c r="T350" s="3"/>
       <c r="U350" s="7" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="V350" s="3">
         <v>4</v>
@@ -32770,7 +32764,7 @@
         <v>53</v>
       </c>
       <c r="U351" s="7" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="V351" s="3">
         <v>3</v>
@@ -32942,13 +32936,13 @@
       <c r="Q354" s="3"/>
       <c r="R354" s="3"/>
       <c r="S354" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T354" s="3" t="s">
         <v>281</v>
       </c>
       <c r="U354" s="7" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="V354" s="3">
         <v>3</v>
@@ -33014,7 +33008,7 @@
         <v>74</v>
       </c>
       <c r="U355" s="7" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="V355" s="3">
         <v>3</v>
@@ -33076,7 +33070,7 @@
       </c>
       <c r="T356" s="3"/>
       <c r="U356" s="7" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="V356" s="3">
         <v>2</v>
@@ -33138,7 +33132,7 @@
       </c>
       <c r="T357" s="3"/>
       <c r="U357" s="7" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="V357" s="3">
         <v>3</v>
@@ -33198,7 +33192,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="7" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="V358" s="3">
         <v>3</v>
@@ -33258,7 +33252,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="7" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="V359" s="3">
         <v>3</v>
@@ -33318,7 +33312,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="7" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="V360" s="3">
         <v>3</v>
@@ -33378,7 +33372,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V361" s="3" t="s">
         <v>44</v>
@@ -33442,7 +33436,7 @@
         <v>1514</v>
       </c>
       <c r="U362" s="7" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="V362" s="3">
         <v>3</v>
@@ -33504,7 +33498,7 @@
       </c>
       <c r="T363" s="3"/>
       <c r="U363" s="7" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="V363" s="3">
         <v>4</v>
@@ -33568,7 +33562,7 @@
         <v>1243</v>
       </c>
       <c r="U364" s="7" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="V364" s="3">
         <v>4</v>
@@ -33630,7 +33624,7 @@
       </c>
       <c r="T365" s="3"/>
       <c r="U365" s="7" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="V365" s="3">
         <v>3</v>
@@ -33692,7 +33686,7 @@
       </c>
       <c r="T366" s="3"/>
       <c r="U366" s="7" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="V366" s="3">
         <v>3</v>
@@ -33754,7 +33748,7 @@
       </c>
       <c r="T367" s="3"/>
       <c r="U367" s="7" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="V367" s="3">
         <v>3</v>
@@ -33818,7 +33812,7 @@
         <v>314</v>
       </c>
       <c r="U368" s="7" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="V368" s="3">
         <v>3</v>
@@ -33878,7 +33872,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="7" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="V369" s="3">
         <v>2</v>
@@ -33936,11 +33930,11 @@
       <c r="Q370" s="3"/>
       <c r="R370" s="3"/>
       <c r="S370" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T370" s="3"/>
       <c r="U370" s="7" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="V370" s="3">
         <v>4</v>
@@ -34002,7 +33996,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="7" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="V371" s="3">
         <v>3</v>
@@ -34062,7 +34056,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="7" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="V372" s="3">
         <v>3</v>
@@ -34118,7 +34112,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="7" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="V373" s="3">
         <v>3</v>
@@ -34174,7 +34168,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="7" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="V374" s="3">
         <v>3</v>
@@ -34234,7 +34228,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="7" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="V375" s="3">
         <v>2</v>
@@ -34294,7 +34288,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="7" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="V376" s="3">
         <v>3</v>
@@ -34354,7 +34348,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="7" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="V377" s="3">
         <v>2</v>
@@ -34414,7 +34408,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="7" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="V378" s="3">
         <v>3</v>
@@ -34474,7 +34468,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="7" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="V379" s="3" t="s">
         <v>44</v>
@@ -34534,7 +34528,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V380" s="3" t="s">
         <v>44</v>
@@ -34594,7 +34588,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V381" s="3" t="s">
         <v>44</v>
@@ -34654,7 +34648,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V382" s="3" t="s">
         <v>44</v>
@@ -34714,7 +34708,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V383" s="3" t="s">
         <v>44</v>
@@ -34772,11 +34766,11 @@
       <c r="Q384" s="3"/>
       <c r="R384" s="3"/>
       <c r="S384" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T384" s="3"/>
       <c r="U384" s="7" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="V384" s="3">
         <v>3</v>
@@ -34838,7 +34832,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="7" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="V385" s="3">
         <v>3</v>
@@ -34904,7 +34898,7 @@
         <v>53</v>
       </c>
       <c r="U386" s="7" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="V386" s="3">
         <v>3</v>
@@ -34966,7 +34960,7 @@
       </c>
       <c r="T387" s="3"/>
       <c r="U387" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="V387" s="3">
         <v>4</v>
@@ -35030,7 +35024,7 @@
       </c>
       <c r="T388" s="3"/>
       <c r="U388" s="7" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="V388" s="3">
         <v>3</v>
@@ -35094,7 +35088,7 @@
         <v>1325</v>
       </c>
       <c r="U389" s="7" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="V389" s="3">
         <v>4</v>
@@ -35154,7 +35148,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="7" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="V390" s="3">
         <v>3</v>
@@ -35214,7 +35208,7 @@
       <c r="S391" s="3"/>
       <c r="T391" s="3"/>
       <c r="U391" s="7" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="V391" s="3">
         <v>3</v>
@@ -35274,7 +35268,7 @@
       <c r="S392" s="3"/>
       <c r="T392" s="3"/>
       <c r="U392" s="7" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="V392" s="3">
         <v>3</v>
@@ -35334,7 +35328,7 @@
       <c r="S393" s="3"/>
       <c r="T393" s="3"/>
       <c r="U393" s="7" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="V393" s="3">
         <v>4</v>
@@ -35392,11 +35386,11 @@
       <c r="Q394" s="3"/>
       <c r="R394" s="3"/>
       <c r="S394" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T394" s="3"/>
       <c r="U394" s="7" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="V394" s="3">
         <v>3</v>
@@ -35458,7 +35452,7 @@
       </c>
       <c r="T395" s="3"/>
       <c r="U395" s="7" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="V395" s="3">
         <v>3</v>
@@ -35518,7 +35512,7 @@
       <c r="S396" s="3"/>
       <c r="T396" s="3"/>
       <c r="U396" s="7" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="V396" s="3">
         <v>3</v>
@@ -35578,7 +35572,7 @@
       <c r="S397" s="3"/>
       <c r="T397" s="3"/>
       <c r="U397" s="7" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="V397" s="3">
         <v>3</v>
@@ -35642,7 +35636,7 @@
         <v>33</v>
       </c>
       <c r="U398" s="7" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="V398" s="3">
         <v>3</v>
@@ -35702,7 +35696,7 @@
       <c r="S399" s="3"/>
       <c r="T399" s="3"/>
       <c r="U399" s="7" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="V399" s="3">
         <v>2</v>
@@ -35764,7 +35758,7 @@
       </c>
       <c r="T400" s="3"/>
       <c r="U400" s="7" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="V400" s="3">
         <v>3</v>
@@ -35824,7 +35818,7 @@
       <c r="S401" s="3"/>
       <c r="T401" s="3"/>
       <c r="U401" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="V401" s="3">
         <v>3</v>
@@ -35884,11 +35878,11 @@
       <c r="Q402" s="3"/>
       <c r="R402" s="3"/>
       <c r="S402" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T402" s="3"/>
       <c r="U402" s="7" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="V402" s="3">
         <v>3</v>
@@ -35950,7 +35944,7 @@
       </c>
       <c r="T403" s="3"/>
       <c r="U403" s="7" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="V403" s="3">
         <v>3</v>
@@ -36012,7 +36006,7 @@
       </c>
       <c r="T404" s="3"/>
       <c r="U404" s="7" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="V404" s="3">
         <v>3</v>
@@ -36076,7 +36070,7 @@
         <v>33</v>
       </c>
       <c r="U405" s="7" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="V405" s="3">
         <v>3</v>
@@ -36138,7 +36132,7 @@
         <v>1325</v>
       </c>
       <c r="U406" s="7" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="V406" s="3">
         <v>3</v>
@@ -36198,7 +36192,7 @@
       <c r="S407" s="3"/>
       <c r="T407" s="3"/>
       <c r="U407" s="7" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="V407" s="3">
         <v>3</v>
@@ -36258,7 +36252,7 @@
       <c r="S408" s="3"/>
       <c r="T408" s="3"/>
       <c r="U408" s="7" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="V408" s="3">
         <v>3</v>
@@ -36318,7 +36312,7 @@
       <c r="S409" s="3"/>
       <c r="T409" s="3"/>
       <c r="U409" s="7" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="V409" s="3">
         <v>3</v>
@@ -36378,7 +36372,7 @@
       <c r="S410" s="3"/>
       <c r="T410" s="3"/>
       <c r="U410" s="7" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="V410" s="3">
         <v>3</v>
@@ -36438,7 +36432,7 @@
       <c r="S411" s="3"/>
       <c r="T411" s="3"/>
       <c r="U411" s="7" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="V411" s="3">
         <v>3</v>
@@ -36498,7 +36492,7 @@
       <c r="S412" s="3"/>
       <c r="T412" s="3"/>
       <c r="U412" s="7" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="V412" s="3">
         <v>3</v>
@@ -36558,7 +36552,7 @@
       <c r="S413" s="3"/>
       <c r="T413" s="3"/>
       <c r="U413" s="7" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="V413" s="3">
         <v>3</v>
@@ -36624,7 +36618,7 @@
         <v>240</v>
       </c>
       <c r="U414" s="7" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="V414" s="3">
         <v>3</v>
@@ -36684,7 +36678,7 @@
       <c r="S415" s="3"/>
       <c r="T415" s="3"/>
       <c r="U415" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="V415" s="3">
         <v>3</v>
@@ -36744,7 +36738,7 @@
       <c r="S416" s="3"/>
       <c r="T416" s="3"/>
       <c r="U416" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V416" s="3" t="s">
         <v>44</v>
@@ -36805,10 +36799,10 @@
         <v>1061</v>
       </c>
       <c r="T417" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U417" s="7" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="V417" s="3">
         <v>3</v>
@@ -36870,7 +36864,7 @@
       </c>
       <c r="T418" s="3"/>
       <c r="U418" s="7" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="V418" s="3">
         <v>3</v>
@@ -36932,7 +36926,7 @@
       </c>
       <c r="T419" s="3"/>
       <c r="U419" s="7" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="V419" s="3">
         <v>3</v>
@@ -36994,7 +36988,7 @@
       <c r="S420" s="3"/>
       <c r="T420" s="3"/>
       <c r="U420" s="7" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="V420" s="3">
         <v>3</v>
@@ -37054,7 +37048,7 @@
       <c r="S421" s="3"/>
       <c r="T421" s="3"/>
       <c r="U421" s="7" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="V421" s="3">
         <v>3</v>
@@ -37114,7 +37108,7 @@
       <c r="S422" s="3"/>
       <c r="T422" s="3"/>
       <c r="U422" s="7" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="V422" s="3">
         <v>2</v>
@@ -37176,7 +37170,7 @@
       </c>
       <c r="T423" s="3"/>
       <c r="U423" s="7" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="V423" s="3">
         <v>3</v>
@@ -37240,7 +37234,7 @@
         <v>314</v>
       </c>
       <c r="U424" s="7" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="V424" s="3">
         <v>3</v>
@@ -37302,7 +37296,7 @@
       </c>
       <c r="T425" s="3"/>
       <c r="U425" s="7" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="V425" s="3">
         <v>3</v>
@@ -37360,11 +37354,11 @@
       <c r="Q426" s="3"/>
       <c r="R426" s="3"/>
       <c r="S426" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T426" s="3"/>
       <c r="U426" s="7" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="V426" s="3">
         <v>3</v>
@@ -37424,7 +37418,7 @@
       <c r="S427" s="3"/>
       <c r="T427" s="3"/>
       <c r="U427" s="7" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="V427" s="3">
         <v>3</v>
@@ -37484,7 +37478,7 @@
       <c r="S428" s="3"/>
       <c r="T428" s="3"/>
       <c r="U428" s="7" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="V428" s="3">
         <v>3</v>
@@ -37546,7 +37540,7 @@
       </c>
       <c r="T429" s="3"/>
       <c r="U429" s="7" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="V429" s="3">
         <v>3</v>
@@ -37612,7 +37606,7 @@
         <v>53</v>
       </c>
       <c r="U430" s="7" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="V430" s="3">
         <v>3</v>
@@ -37674,7 +37668,7 @@
       </c>
       <c r="T431" s="3"/>
       <c r="U431" s="7" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="V431" s="3">
         <v>3</v>
@@ -37736,7 +37730,7 @@
         <v>53</v>
       </c>
       <c r="U432" s="7" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="V432" s="3">
         <v>3</v>
@@ -37800,7 +37794,7 @@
       </c>
       <c r="T433" s="3"/>
       <c r="U433" s="7" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="V433" s="3">
         <v>4</v>
@@ -37860,7 +37854,7 @@
       <c r="S434" s="3"/>
       <c r="T434" s="3"/>
       <c r="U434" s="7" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="V434" s="3">
         <v>3</v>
@@ -37922,7 +37916,7 @@
       <c r="S435" s="3"/>
       <c r="T435" s="3"/>
       <c r="U435" s="7" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="V435" s="3">
         <v>3</v>
@@ -38100,17 +38094,17 @@
       </c>
       <c r="P438" s="3"/>
       <c r="Q438" s="3" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="R438" s="3"/>
       <c r="S438" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T438" s="3" t="s">
         <v>2070</v>
       </c>
       <c r="U438" s="7" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="V438" s="3">
         <v>3</v>
@@ -38170,11 +38164,11 @@
       <c r="Q439" s="3"/>
       <c r="R439" s="3"/>
       <c r="S439" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T439" s="3"/>
       <c r="U439" s="7" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="V439" s="3">
         <v>3</v>
@@ -38236,7 +38230,7 @@
       <c r="S440" s="3"/>
       <c r="T440" s="3"/>
       <c r="U440" s="7" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="V440" s="3">
         <v>3</v>
@@ -38302,7 +38296,7 @@
         <v>74</v>
       </c>
       <c r="U441" s="7" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="V441" s="3">
         <v>3</v>
@@ -38364,7 +38358,7 @@
       <c r="S442" s="3"/>
       <c r="T442" s="3"/>
       <c r="U442" s="7" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="V442" s="3" t="s">
         <v>44</v>
@@ -38424,11 +38418,11 @@
       <c r="Q443" s="3"/>
       <c r="R443" s="3"/>
       <c r="S443" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T443" s="3"/>
       <c r="U443" s="7" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="V443" s="3">
         <v>4</v>
@@ -38486,7 +38480,7 @@
       </c>
       <c r="T444" s="3"/>
       <c r="U444" s="7" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="V444" s="3">
         <v>3</v>
@@ -38550,7 +38544,7 @@
       </c>
       <c r="T445" s="3"/>
       <c r="U445" s="7" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="V445" s="3">
         <v>4</v>
@@ -38606,7 +38600,7 @@
       <c r="S446" s="3"/>
       <c r="T446" s="3"/>
       <c r="U446" s="7" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="V446" s="3">
         <v>3</v>
@@ -38664,7 +38658,7 @@
       </c>
       <c r="T447" s="3"/>
       <c r="U447" s="7" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="V447" s="3">
         <v>3</v>
@@ -38722,7 +38716,7 @@
         <v>240</v>
       </c>
       <c r="U448" s="7" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="V448" s="3">
         <v>4</v>
@@ -38780,7 +38774,7 @@
         <v>281</v>
       </c>
       <c r="U449" s="7" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="V449" s="3">
         <v>3</v>
@@ -38836,7 +38830,7 @@
       <c r="S450" s="3"/>
       <c r="T450" s="3"/>
       <c r="U450" s="7" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="V450" s="3">
         <v>2</v>
@@ -38894,7 +38888,7 @@
         <v>281</v>
       </c>
       <c r="U451" s="7" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="V451" s="3">
         <v>3</v>
@@ -38950,7 +38944,7 @@
       <c r="S452" s="3"/>
       <c r="T452" s="3"/>
       <c r="U452" s="7" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="V452" s="3">
         <v>3</v>
@@ -39008,7 +39002,7 @@
         <v>33</v>
       </c>
       <c r="U453" s="7" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="V453" s="3">
         <v>3</v>
@@ -39066,7 +39060,7 @@
         <v>281</v>
       </c>
       <c r="U454" s="7" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="V454" s="3">
         <v>3</v>
@@ -39122,7 +39116,7 @@
       <c r="S455" s="3"/>
       <c r="T455" s="3"/>
       <c r="U455" s="7" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="V455" s="3">
         <v>2</v>
@@ -39178,7 +39172,7 @@
       <c r="S456" s="3"/>
       <c r="T456" s="3"/>
       <c r="U456" s="7" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="V456" s="3">
         <v>3</v>
@@ -39234,7 +39228,7 @@
       <c r="S457" s="3"/>
       <c r="T457" s="3"/>
       <c r="U457" s="7" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="V457" s="3">
         <v>3</v>
@@ -39290,7 +39284,7 @@
       <c r="S458" s="3"/>
       <c r="T458" s="3"/>
       <c r="U458" s="7" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="V458" s="3">
         <v>3</v>
@@ -39346,7 +39340,7 @@
       <c r="S459" s="3"/>
       <c r="T459" s="3"/>
       <c r="U459" s="7" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="V459" s="3">
         <v>3</v>
@@ -39406,7 +39400,7 @@
       <c r="S460" s="3"/>
       <c r="T460" s="3"/>
       <c r="U460" s="7" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="V460" s="3">
         <v>3</v>
@@ -39466,7 +39460,7 @@
       <c r="S461" s="3"/>
       <c r="T461" s="3"/>
       <c r="U461" s="7" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="V461" s="3" t="s">
         <v>44</v>
@@ -39522,7 +39516,7 @@
       <c r="S462" s="3"/>
       <c r="T462" s="3"/>
       <c r="U462" s="7" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="V462" s="3">
         <v>3</v>
@@ -39578,7 +39572,7 @@
       <c r="S463" s="3"/>
       <c r="T463" s="3"/>
       <c r="U463" s="7" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="V463" s="3">
         <v>3</v>
@@ -39642,7 +39636,7 @@
         <v>397</v>
       </c>
       <c r="U464" s="7" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="V464" s="3">
         <v>3</v>
@@ -39696,11 +39690,11 @@
       <c r="Q465" s="3"/>
       <c r="R465" s="3"/>
       <c r="S465" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T465" s="3"/>
       <c r="U465" s="7" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="V465" s="3">
         <v>4</v>
@@ -39760,7 +39754,7 @@
       <c r="S466" s="3"/>
       <c r="T466" s="3"/>
       <c r="U466" s="7" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="V466" s="3">
         <v>2</v>
@@ -39818,7 +39812,7 @@
       <c r="S467" s="3"/>
       <c r="T467" s="3"/>
       <c r="U467" s="7" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="V467" s="3">
         <v>3</v>
@@ -39882,7 +39876,7 @@
       </c>
       <c r="T468" s="3"/>
       <c r="U468" s="7" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="V468" s="3">
         <v>3</v>
@@ -39940,7 +39934,7 @@
       </c>
       <c r="T469" s="3"/>
       <c r="U469" s="7" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="V469" s="3">
         <v>3</v>
@@ -39998,7 +39992,7 @@
       </c>
       <c r="T470" s="3"/>
       <c r="U470" s="7" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="V470" s="3">
         <v>3</v>
@@ -40056,7 +40050,7 @@
       </c>
       <c r="T471" s="3"/>
       <c r="U471" s="7" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="V471" s="3">
         <v>3</v>
@@ -40114,7 +40108,7 @@
       </c>
       <c r="T472" s="3"/>
       <c r="U472" s="7" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="V472" s="3">
         <v>3</v>
@@ -40174,7 +40168,7 @@
         <v>314</v>
       </c>
       <c r="U473" s="7" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="V473" s="3">
         <v>4</v>
@@ -40234,7 +40228,7 @@
         <v>314</v>
       </c>
       <c r="U474" s="7" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="V474" s="3">
         <v>3</v>
@@ -40292,7 +40286,7 @@
       </c>
       <c r="T475" s="3"/>
       <c r="U475" s="7" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="V475" s="3">
         <v>3</v>
@@ -40348,7 +40342,7 @@
       <c r="S476" s="3"/>
       <c r="T476" s="3"/>
       <c r="U476" s="7" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="V476" s="3">
         <v>3</v>
@@ -40410,7 +40404,7 @@
       </c>
       <c r="T477" s="3"/>
       <c r="U477" s="7" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="V477" s="3">
         <v>3</v>
@@ -40466,7 +40460,7 @@
       <c r="S478" s="3"/>
       <c r="T478" s="3"/>
       <c r="U478" s="7" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="V478" s="3">
         <v>3</v>
@@ -40524,7 +40518,7 @@
       </c>
       <c r="T479" s="3"/>
       <c r="U479" s="7" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="V479" s="3">
         <v>3</v>
@@ -40582,11 +40576,11 @@
       <c r="Q480" s="3"/>
       <c r="R480" s="3"/>
       <c r="S480" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T480" s="3"/>
       <c r="U480" s="7" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="V480" s="3">
         <v>3</v>
@@ -40642,7 +40636,7 @@
       <c r="S481" s="3"/>
       <c r="T481" s="3"/>
       <c r="U481" s="7" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="V481" s="3">
         <v>3</v>
@@ -40702,7 +40696,7 @@
       <c r="S482" s="3"/>
       <c r="T482" s="3"/>
       <c r="U482" s="7" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="V482" s="3">
         <v>2</v>
@@ -40758,7 +40752,7 @@
       <c r="S483" s="3"/>
       <c r="T483" s="3"/>
       <c r="U483" s="7" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="V483" s="3">
         <v>3</v>
@@ -40814,7 +40808,7 @@
       <c r="S484" s="3"/>
       <c r="T484" s="3"/>
       <c r="U484" s="7" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="V484" s="3">
         <v>3</v>
@@ -40874,7 +40868,7 @@
       <c r="S485" s="3"/>
       <c r="T485" s="3"/>
       <c r="U485" s="7" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="V485" s="3" t="s">
         <v>44</v>
@@ -40940,7 +40934,7 @@
         <v>445</v>
       </c>
       <c r="U486" s="7" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="V486" s="3">
         <v>2</v>
@@ -41004,7 +40998,7 @@
       </c>
       <c r="T487" s="3"/>
       <c r="U487" s="7" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="V487" s="3">
         <v>3</v>
@@ -41068,7 +41062,7 @@
       </c>
       <c r="T488" s="3"/>
       <c r="U488" s="7" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="V488" s="3">
         <v>3</v>
@@ -41132,7 +41126,7 @@
       </c>
       <c r="T489" s="3"/>
       <c r="U489" s="7" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="V489" s="3">
         <v>3</v>
@@ -41192,7 +41186,7 @@
       <c r="S490" s="3"/>
       <c r="T490" s="3"/>
       <c r="U490" s="7" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="V490" s="3">
         <v>3</v>
@@ -41253,10 +41247,10 @@
       <c r="R491" s="3"/>
       <c r="S491" s="3"/>
       <c r="T491" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U491" s="7" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="V491" s="3">
         <v>3</v>
@@ -41316,7 +41310,7 @@
       <c r="S492" s="3"/>
       <c r="T492" s="3"/>
       <c r="U492" s="7" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="V492" s="3">
         <v>3</v>
@@ -41380,7 +41374,7 @@
       </c>
       <c r="T493" s="3"/>
       <c r="U493" s="7" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="V493" s="3">
         <v>3</v>
@@ -41444,7 +41438,7 @@
       </c>
       <c r="T494" s="3"/>
       <c r="U494" s="7" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="V494" s="3">
         <v>3</v>
@@ -41508,7 +41502,7 @@
       </c>
       <c r="T495" s="3"/>
       <c r="U495" s="7" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="V495" s="3">
         <v>3</v>
@@ -41568,7 +41562,7 @@
         <v>240</v>
       </c>
       <c r="U496" s="7" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="V496" s="3">
         <v>3</v>
@@ -41629,10 +41623,10 @@
         <v>74</v>
       </c>
       <c r="T497" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U497" s="7" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="V497" s="3">
         <v>3</v>
@@ -41694,7 +41688,7 @@
         <v>240</v>
       </c>
       <c r="U498" s="7" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="V498" s="3">
         <v>3</v>
@@ -41756,7 +41750,7 @@
         <v>74</v>
       </c>
       <c r="U499" s="7" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="V499" s="3">
         <v>3</v>
@@ -41822,7 +41816,7 @@
         <v>53</v>
       </c>
       <c r="U500" s="7" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="V500" s="3">
         <v>3</v>
@@ -41882,7 +41876,7 @@
       <c r="S501" s="3"/>
       <c r="T501" s="3"/>
       <c r="U501" s="7" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="V501" s="3">
         <v>3</v>
@@ -41942,7 +41936,7 @@
       <c r="S502" s="3"/>
       <c r="T502" s="3"/>
       <c r="U502" s="7" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="V502" s="3">
         <v>3</v>
@@ -41982,7 +41976,7 @@
         <v>2107</v>
       </c>
       <c r="I503" s="3" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="J503" s="5">
         <v>29617</v>
@@ -42008,7 +42002,7 @@
         <v>281</v>
       </c>
       <c r="U503" s="7" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="V503" s="3">
         <v>3</v>
@@ -42070,7 +42064,7 @@
       <c r="S504" s="3"/>
       <c r="T504" s="3"/>
       <c r="U504" s="7" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="V504" s="3">
         <v>3</v>
@@ -42132,7 +42126,7 @@
       <c r="S505" s="3"/>
       <c r="T505" s="3"/>
       <c r="U505" s="7" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="V505" s="3">
         <v>3</v>
@@ -42196,7 +42190,7 @@
       </c>
       <c r="T506" s="3"/>
       <c r="U506" s="7" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="V506" s="3">
         <v>3</v>
@@ -42260,7 +42254,7 @@
         <v>33</v>
       </c>
       <c r="U507" s="7" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="V507" s="3">
         <v>3</v>
@@ -42322,7 +42316,7 @@
       <c r="S508" s="3"/>
       <c r="T508" s="3"/>
       <c r="U508" s="7" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="V508" s="3">
         <v>3</v>
@@ -42380,7 +42374,7 @@
       <c r="S509" s="3"/>
       <c r="T509" s="3"/>
       <c r="U509" s="7" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="V509" s="3">
         <v>3</v>
@@ -42502,7 +42496,7 @@
       <c r="S511" s="3"/>
       <c r="T511" s="3"/>
       <c r="U511" s="7" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="V511" s="3">
         <v>3</v>
@@ -42542,7 +42536,7 @@
         <v>2210</v>
       </c>
       <c r="I512" s="3" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="J512" s="5">
         <v>30522</v>
@@ -42568,7 +42562,7 @@
         <v>1236</v>
       </c>
       <c r="U512" s="7" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="V512" s="3">
         <v>3</v>
@@ -42630,7 +42624,7 @@
       <c r="S513" s="3"/>
       <c r="T513" s="3"/>
       <c r="U513" s="7" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="V513" s="3">
         <v>3</v>
@@ -42661,7 +42655,7 @@
         <v>1153</v>
       </c>
       <c r="F514" s="15" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="G514" s="3" t="s">
         <v>29</v>
@@ -42690,13 +42684,13 @@
       <c r="Q514" s="3"/>
       <c r="R514" s="3"/>
       <c r="S514" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T514" s="3" t="s">
         <v>240</v>
       </c>
       <c r="U514" s="7" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="V514" s="3">
         <v>3</v>
@@ -42754,7 +42748,7 @@
         <v>281</v>
       </c>
       <c r="U515" s="7" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="V515" s="3">
         <v>3</v>
@@ -42812,11 +42806,11 @@
       <c r="Q516" s="3"/>
       <c r="R516" s="3"/>
       <c r="S516" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T516" s="3"/>
       <c r="U516" s="7" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="V516" s="3">
         <v>4</v>
@@ -42878,7 +42872,7 @@
       <c r="S517" s="3"/>
       <c r="T517" s="3"/>
       <c r="U517" s="7" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="V517" s="3">
         <v>3</v>
@@ -42936,7 +42930,7 @@
       </c>
       <c r="T518" s="3"/>
       <c r="U518" s="7" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="V518" s="3">
         <v>3</v>
@@ -42996,7 +42990,7 @@
       </c>
       <c r="T519" s="3"/>
       <c r="U519" s="7" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="V519" s="3">
         <v>3</v>
@@ -43059,10 +43053,10 @@
         <v>916</v>
       </c>
       <c r="T520" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U520" s="7" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="V520" s="3">
         <v>3</v>
@@ -43120,7 +43114,7 @@
       </c>
       <c r="T521" s="3"/>
       <c r="U521" s="7" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="V521" s="3">
         <v>3</v>
@@ -43178,7 +43172,7 @@
       </c>
       <c r="T522" s="3"/>
       <c r="U522" s="7" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="V522" s="3">
         <v>3</v>
@@ -43238,7 +43232,7 @@
         <v>74</v>
       </c>
       <c r="U523" s="7" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="V523" s="3">
         <v>3</v>
@@ -43298,7 +43292,7 @@
         <v>314</v>
       </c>
       <c r="U524" s="7" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="V524" s="3">
         <v>3</v>
@@ -43358,7 +43352,7 @@
         <v>1325</v>
       </c>
       <c r="U525" s="7" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="V525" s="3">
         <v>3</v>
@@ -43419,10 +43413,10 @@
       <c r="R526" s="3"/>
       <c r="S526" s="3"/>
       <c r="T526" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U526" s="7" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="V526" s="3">
         <v>3</v>
@@ -43478,7 +43472,7 @@
       <c r="S527" s="3"/>
       <c r="T527" s="3"/>
       <c r="U527" s="7" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="V527" s="3">
         <v>3</v>
@@ -43534,7 +43528,7 @@
       <c r="S528" s="3"/>
       <c r="T528" s="3"/>
       <c r="U528" s="7" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="V528" s="3">
         <v>3</v>
@@ -43596,7 +43590,7 @@
       <c r="S529" s="3"/>
       <c r="T529" s="3"/>
       <c r="U529" s="7" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="V529" s="3">
         <v>3</v>
@@ -43656,7 +43650,7 @@
       <c r="S530" s="3"/>
       <c r="T530" s="3"/>
       <c r="U530" s="7" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="V530" s="3" t="s">
         <v>44</v>
@@ -43714,7 +43708,7 @@
       </c>
       <c r="T531" s="3"/>
       <c r="U531" s="7" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="V531" s="3">
         <v>3</v>
@@ -43774,7 +43768,7 @@
       <c r="S532" s="3"/>
       <c r="T532" s="3"/>
       <c r="U532" s="7" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="V532" s="3">
         <v>3</v>
@@ -43836,7 +43830,7 @@
       <c r="S533" s="3"/>
       <c r="T533" s="3"/>
       <c r="U533" s="7" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="V533" s="3" t="s">
         <v>44</v>
@@ -43872,7 +43866,7 @@
         <v>2221</v>
       </c>
       <c r="I534" s="3" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="J534" s="5">
         <v>25892</v>
@@ -43919,10 +43913,10 @@
         <v>2302</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="E535" s="3" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="F535" s="15" t="s">
         <v>2303</v>
@@ -43952,7 +43946,7 @@
       </c>
       <c r="P535" s="3"/>
       <c r="Q535" s="3" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="R535" s="3"/>
       <c r="S535" s="3" t="s">
@@ -43962,7 +43956,7 @@
         <v>1976</v>
       </c>
       <c r="U535" s="7" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="V535" s="3">
         <v>3</v>
@@ -44028,7 +44022,7 @@
         <v>397</v>
       </c>
       <c r="U536" s="7" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="V536" s="3">
         <v>3</v>
@@ -44092,7 +44086,7 @@
       </c>
       <c r="T537" s="3"/>
       <c r="U537" s="7" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="V537" s="3">
         <v>3</v>
@@ -44154,7 +44148,7 @@
       <c r="S538" s="3"/>
       <c r="T538" s="3"/>
       <c r="U538" s="7" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="V538" s="3">
         <v>3</v>
@@ -44185,7 +44179,7 @@
         <v>2243</v>
       </c>
       <c r="F539" s="15" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>66</v>
@@ -44214,13 +44208,13 @@
       <c r="Q539" s="3"/>
       <c r="R539" s="3"/>
       <c r="S539" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T539" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U539" s="7" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="V539" s="3">
         <v>3</v>
@@ -44284,7 +44278,7 @@
       </c>
       <c r="T540" s="3"/>
       <c r="U540" s="7" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="V540" s="3">
         <v>3</v>
@@ -44348,7 +44342,7 @@
       </c>
       <c r="T541" s="3"/>
       <c r="U541" s="7" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="V541" s="3">
         <v>3</v>
@@ -44379,7 +44373,7 @@
         <v>1191</v>
       </c>
       <c r="F542" s="15" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="G542" s="3" t="s">
         <v>122</v>
@@ -44410,7 +44404,7 @@
       <c r="S542" s="3"/>
       <c r="T542" s="3"/>
       <c r="U542" s="7" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="V542" s="3">
         <v>2</v>
@@ -44472,7 +44466,7 @@
       <c r="S543" s="3"/>
       <c r="T543" s="3"/>
       <c r="U543" s="7" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="V543" s="3">
         <v>4</v>
@@ -44534,7 +44528,7 @@
       <c r="S544" s="3"/>
       <c r="T544" s="3"/>
       <c r="U544" s="7" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="V544" s="3" t="s">
         <v>44</v>
@@ -44592,7 +44586,7 @@
       <c r="S545" s="3"/>
       <c r="T545" s="3"/>
       <c r="U545" s="7" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="V545" s="3">
         <v>3</v>
@@ -44658,7 +44652,7 @@
         <v>74</v>
       </c>
       <c r="U546" s="7" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="V546" s="3">
         <v>3</v>
@@ -44714,11 +44708,11 @@
       <c r="Q547" s="3"/>
       <c r="R547" s="3"/>
       <c r="S547" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T547" s="3"/>
       <c r="U547" s="7" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="V547" s="3">
         <v>3</v>
@@ -44782,7 +44776,7 @@
       </c>
       <c r="T548" s="3"/>
       <c r="U548" s="7" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="V548" s="3">
         <v>3</v>
@@ -44846,7 +44840,7 @@
         <v>33</v>
       </c>
       <c r="U549" s="7" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="V549" s="3">
         <v>3</v>
@@ -44877,7 +44871,7 @@
         <v>2298</v>
       </c>
       <c r="F550" s="15" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="G550" s="3" t="s">
         <v>29</v>
@@ -44906,11 +44900,11 @@
       <c r="Q550" s="3"/>
       <c r="R550" s="3"/>
       <c r="S550" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T550" s="3"/>
       <c r="U550" s="7" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="V550" s="3">
         <v>4</v>
@@ -44944,7 +44938,7 @@
         <v>2520</v>
       </c>
       <c r="G551" s="3" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="H551" s="3" t="s">
         <v>2505</v>
@@ -44982,7 +44976,7 @@
         <v>35</v>
       </c>
       <c r="Y551" s="3" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="Z551" s="8"/>
     </row>
@@ -44999,7 +44993,7 @@
       <c r="D552" s="3"/>
       <c r="E552" s="3"/>
       <c r="F552" s="15" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="G552" s="3" t="s">
         <v>40</v>
@@ -45030,7 +45024,7 @@
       <c r="S552" s="3"/>
       <c r="T552" s="3"/>
       <c r="U552" s="7" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="V552" s="3" t="s">
         <v>44</v>
@@ -45084,7 +45078,7 @@
       </c>
       <c r="P553" s="3"/>
       <c r="Q553" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R553" s="3"/>
       <c r="S553" s="3" t="s">
@@ -45092,7 +45086,7 @@
       </c>
       <c r="T553" s="3"/>
       <c r="U553" s="7" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="V553" s="3">
         <v>3</v>
@@ -45152,7 +45146,7 @@
         <v>33</v>
       </c>
       <c r="U554" s="7" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="V554" s="3">
         <v>3</v>
@@ -45214,7 +45208,7 @@
         <v>445</v>
       </c>
       <c r="U555" s="7" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="V555" s="3">
         <v>3</v>
@@ -45280,7 +45274,7 @@
         <v>53</v>
       </c>
       <c r="U556" s="7" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="V556" s="3">
         <v>3</v>
@@ -45342,7 +45336,7 @@
         <v>1111</v>
       </c>
       <c r="U557" s="7" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="V557" s="3">
         <v>3</v>
@@ -45369,7 +45363,7 @@
       <c r="D558" s="3"/>
       <c r="E558" s="3"/>
       <c r="F558" s="15" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>29</v>
@@ -45398,13 +45392,13 @@
       <c r="Q558" s="3"/>
       <c r="R558" s="3"/>
       <c r="S558" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T558" s="3" t="s">
         <v>53</v>
       </c>
       <c r="U558" s="7" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="V558" s="3">
         <v>3</v>
@@ -45464,7 +45458,7 @@
         <v>33</v>
       </c>
       <c r="U559" s="7" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="V559" s="3">
         <v>3</v>
@@ -45522,7 +45516,7 @@
       <c r="S560" s="3"/>
       <c r="T560" s="3"/>
       <c r="U560" s="7" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="V560" s="3">
         <v>3</v>
@@ -45580,7 +45574,7 @@
       <c r="S561" s="3"/>
       <c r="T561" s="3"/>
       <c r="U561" s="7" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="V561" s="3">
         <v>3</v>
@@ -45640,7 +45634,7 @@
         <v>240</v>
       </c>
       <c r="U562" s="7" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="V562" s="3">
         <v>3</v>
@@ -45702,7 +45696,7 @@
         <v>102</v>
       </c>
       <c r="U563" s="7" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="V563" s="3">
         <v>3</v>
@@ -45768,7 +45762,7 @@
         <v>2437</v>
       </c>
       <c r="U564" s="7" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="V564" s="3">
         <v>3</v>
@@ -45826,7 +45820,7 @@
       </c>
       <c r="P565" s="3"/>
       <c r="Q565" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R565" s="3"/>
       <c r="S565" s="3"/>
@@ -45890,7 +45884,7 @@
       </c>
       <c r="P566" s="3"/>
       <c r="Q566" s="3" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="R566" s="3"/>
       <c r="S566" s="3" t="s">
@@ -45900,7 +45894,7 @@
         <v>74</v>
       </c>
       <c r="U566" s="7" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="V566" s="3">
         <v>3</v>
@@ -45962,7 +45956,7 @@
       <c r="S567" s="3"/>
       <c r="T567" s="3"/>
       <c r="U567" s="7" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="V567" s="3">
         <v>3</v>
@@ -46024,7 +46018,7 @@
       <c r="S568" s="3"/>
       <c r="T568" s="3"/>
       <c r="U568" s="7" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="V568" s="3" t="s">
         <v>44</v>
@@ -46090,7 +46084,7 @@
         <v>33</v>
       </c>
       <c r="U569" s="7" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="V569" s="3">
         <v>3</v>
@@ -46148,7 +46142,7 @@
       <c r="S570" s="3"/>
       <c r="T570" s="3"/>
       <c r="U570" s="7" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="V570" s="3">
         <v>3</v>
@@ -46210,7 +46204,7 @@
       <c r="S571" s="3"/>
       <c r="T571" s="3"/>
       <c r="U571" s="7" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="V571" s="3">
         <v>3</v>
@@ -46229,25 +46223,25 @@
         <v>169019</v>
       </c>
       <c r="B572" s="3" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C572" s="3" t="s">
         <v>2936</v>
       </c>
-      <c r="C572" s="3" t="s">
+      <c r="D572" s="3" t="s">
         <v>2937</v>
       </c>
-      <c r="D572" s="3" t="s">
+      <c r="E572" s="3" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F572" s="15" t="s">
         <v>2938</v>
-      </c>
-      <c r="E572" s="3" t="s">
-        <v>2938</v>
-      </c>
-      <c r="F572" s="15" t="s">
-        <v>2939</v>
       </c>
       <c r="G572" s="3" t="s">
         <v>122</v>
       </c>
       <c r="H572" s="3" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="I572" s="3">
         <v>167010</v>
@@ -46261,10 +46255,10 @@
       <c r="L572" s="4"/>
       <c r="M572" s="4"/>
       <c r="N572" s="3" t="s">
+        <v>2940</v>
+      </c>
+      <c r="O572" s="3" t="s">
         <v>2941</v>
-      </c>
-      <c r="O572" s="3" t="s">
-        <v>2942</v>
       </c>
       <c r="P572" s="3"/>
       <c r="Q572" s="3"/>
@@ -46272,7 +46266,7 @@
       <c r="S572" s="3"/>
       <c r="T572" s="3"/>
       <c r="U572" s="7" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="V572" s="3" t="s">
         <v>44</v>
@@ -46333,10 +46327,10 @@
       <c r="R573" s="3"/>
       <c r="S573" s="3"/>
       <c r="T573" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="U573" s="7" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="V573" s="3">
         <v>4</v>
@@ -46398,7 +46392,7 @@
       <c r="S574" s="3"/>
       <c r="T574" s="3"/>
       <c r="U574" s="7" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="V574" s="3" t="s">
         <v>44</v>
@@ -46429,7 +46423,7 @@
         <v>1364</v>
       </c>
       <c r="F575" s="15" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="G575" s="3" t="s">
         <v>66</v>
@@ -46458,11 +46452,11 @@
       <c r="Q575" s="3"/>
       <c r="R575" s="3"/>
       <c r="S575" s="6" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="T575" s="3"/>
       <c r="U575" s="7" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="V575" s="3">
         <v>4</v>
@@ -46493,7 +46487,7 @@
         <v>2248</v>
       </c>
       <c r="F576" s="15" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="G576" s="3" t="s">
         <v>122</v>
@@ -46524,7 +46518,7 @@
       <c r="S576" s="3"/>
       <c r="T576" s="3"/>
       <c r="U576" s="7" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="V576" s="3" t="s">
         <v>44</v>
@@ -46584,7 +46578,7 @@
         <v>33</v>
       </c>
       <c r="U577" s="7" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="V577" s="3">
         <v>4</v>
@@ -46600,7 +46594,7 @@
     </row>
     <row r="578" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>2377</v>
@@ -46615,7 +46609,7 @@
         <v>1709</v>
       </c>
       <c r="F578" s="15" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="G578" s="3" t="s">
         <v>107</v>
@@ -46642,7 +46636,7 @@
       </c>
       <c r="P578" s="3"/>
       <c r="Q578" s="3" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="R578" s="3"/>
       <c r="S578" s="3"/>
@@ -46658,31 +46652,31 @@
         <v>44</v>
       </c>
       <c r="Y578" s="3" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="Z578" s="8"/>
     </row>
     <row r="579" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A579" s="17" t="s">
-        <v>2908</v>
+      <c r="A579" s="3">
+        <v>169024</v>
       </c>
       <c r="B579" s="3" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C579" s="3" t="s">
         <v>3477</v>
       </c>
-      <c r="C579" s="3" t="s">
+      <c r="D579" s="3" t="s">
         <v>3478</v>
       </c>
-      <c r="D579" s="3" t="s">
+      <c r="E579" s="3" t="s">
+        <v>3478</v>
+      </c>
+      <c r="F579" s="15" t="s">
         <v>3479</v>
       </c>
-      <c r="E579" s="3" t="s">
-        <v>3479</v>
-      </c>
-      <c r="F579" s="15" t="s">
-        <v>3480</v>
-      </c>
       <c r="G579" s="3" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="H579" s="3" t="s">
         <v>2779</v>
@@ -46698,11 +46692,11 @@
       </c>
       <c r="L579" s="4"/>
       <c r="M579" s="4"/>
-      <c r="N579" s="12" t="s">
-        <v>3486</v>
+      <c r="N579" s="3" t="s">
+        <v>742</v>
       </c>
       <c r="O579" s="3" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="P579" s="3"/>
       <c r="Q579" s="3"/>
@@ -46727,21 +46721,21 @@
         <v>656001</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="D580" s="3"/>
       <c r="E580" s="3"/>
       <c r="F580" s="15" t="s">
+        <v>3449</v>
+      </c>
+      <c r="G580" s="3" t="s">
         <v>3450</v>
       </c>
-      <c r="G580" s="3" t="s">
+      <c r="H580" s="3" t="s">
         <v>3451</v>
-      </c>
-      <c r="H580" s="3" t="s">
-        <v>3452</v>
       </c>
       <c r="I580" s="3">
         <v>168015</v>
@@ -46755,14 +46749,14 @@
       <c r="L580" s="4"/>
       <c r="M580" s="4"/>
       <c r="N580" s="3" t="s">
+        <v>3455</v>
+      </c>
+      <c r="O580" s="3" t="s">
         <v>3456</v>
-      </c>
-      <c r="O580" s="3" t="s">
-        <v>3457</v>
       </c>
       <c r="P580" s="3"/>
       <c r="Q580" s="3" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="R580" s="3"/>
       <c r="S580" s="3"/>
@@ -46787,25 +46781,25 @@
         <v>656008</v>
       </c>
       <c r="B581" s="3" t="s">
+        <v>3457</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>3457</v>
+      </c>
+      <c r="D581" s="3" t="s">
         <v>3458</v>
       </c>
-      <c r="C581" s="3" t="s">
+      <c r="E581" s="3" t="s">
         <v>3458</v>
       </c>
-      <c r="D581" s="3" t="s">
+      <c r="F581" s="15" t="s">
         <v>3459</v>
-      </c>
-      <c r="E581" s="3" t="s">
-        <v>3459</v>
-      </c>
-      <c r="F581" s="15" t="s">
-        <v>3460</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H581" s="3" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="I581" s="3">
         <v>168015</v>
@@ -46819,20 +46813,20 @@
       <c r="L581" s="4"/>
       <c r="M581" s="4"/>
       <c r="N581" s="3" t="s">
+        <v>3460</v>
+      </c>
+      <c r="O581" s="3" t="s">
         <v>3461</v>
-      </c>
-      <c r="O581" s="3" t="s">
-        <v>3462</v>
       </c>
       <c r="P581" s="3"/>
       <c r="Q581" s="3" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="R581" s="3"/>
       <c r="S581" s="3"/>
       <c r="T581" s="3"/>
       <c r="U581" s="7" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="V581" s="3" t="s">
         <v>44</v>
@@ -46987,7 +46981,7 @@
         <v>2799</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>272</v>
@@ -46998,13 +46992,13 @@
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>3442</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>3443</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>2746</v>
@@ -47047,7 +47041,7 @@
         <v>2801</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>272</v>
@@ -47258,13 +47252,13 @@
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>612</v>
@@ -47278,13 +47272,13 @@
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>612</v>
@@ -47878,7 +47872,7 @@
     </row>
     <row r="51" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>2819</v>
@@ -47907,7 +47901,7 @@
         <v>2819</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>34</v>
@@ -49018,7 +49012,7 @@
     </row>
     <row r="108" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="12" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>2819</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BF266DF-17A4-4424-A3AB-86AEE74BBD90}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="14_{E8FD2294-C7B9-49B0-ADFF-C5BA30F5B6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{320A8B98-6A1C-4B6B-B04F-D59F5CDDB85E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7695" uniqueCount="3486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7695" uniqueCount="3487">
   <si>
     <t>emp_id</t>
   </si>
@@ -10497,6 +10497,9 @@
   </si>
   <si>
     <t>s_sathien@Oceanglass.com</t>
+  </si>
+  <si>
+    <t>169024.jpg</t>
   </si>
 </sst>
 </file>
@@ -10655,13 +10658,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11005,32 +11008,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>2910</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -20587,7 +20590,7 @@
       <c r="H155" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="I155" s="19">
+      <c r="I155" s="17">
         <v>169024</v>
       </c>
       <c r="J155" s="5">
@@ -21225,7 +21228,7 @@
       <c r="H165" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I165" s="19">
+      <c r="I165" s="17">
         <v>169024</v>
       </c>
       <c r="J165" s="5">
@@ -21985,7 +21988,7 @@
       <c r="H177" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I177" s="19">
+      <c r="I177" s="17">
         <v>169024</v>
       </c>
       <c r="J177" s="5">
@@ -22109,7 +22112,7 @@
       <c r="H179" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I179" s="19">
+      <c r="I179" s="17">
         <v>169024</v>
       </c>
       <c r="J179" s="5">
@@ -22921,7 +22924,7 @@
       <c r="H192" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="I192" s="19">
+      <c r="I192" s="17">
         <v>169024</v>
       </c>
       <c r="J192" s="5">
@@ -46693,7 +46696,7 @@
       <c r="L579" s="4"/>
       <c r="M579" s="4"/>
       <c r="N579" s="3" t="s">
-        <v>742</v>
+        <v>3486</v>
       </c>
       <c r="O579" s="3" t="s">
         <v>3485</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B84B35-1E74-42AA-8AD6-45BC4653BBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{681C522B-376D-48B0-A19E-4B9F4F29C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10506,7 +10506,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10569,19 +10569,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -10649,7 +10636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10765,27 +10752,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10813,6 +10779,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45541,7 +45511,9 @@
       <c r="X567" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y567" s="30"/>
+      <c r="Y567" s="30">
+        <v>169024</v>
+      </c>
       <c r="Z567" s="14"/>
     </row>
     <row r="568" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -45601,7 +45573,7 @@
       <c r="X568" s="26">
         <v>3</v>
       </c>
-      <c r="Y568" s="30"/>
+      <c r="Y568" s="26"/>
       <c r="Z568" s="14"/>
     </row>
     <row r="569" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -45665,774 +45637,761 @@
       <c r="X569" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y569" s="30"/>
+      <c r="Y569" s="26"/>
       <c r="Z569" s="14"/>
     </row>
-    <row r="570" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A570" s="39">
+    <row r="570" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A570" s="35">
         <v>269029</v>
       </c>
-      <c r="B570" s="40" t="s">
+      <c r="B570" s="26" t="s">
         <v>3466</v>
       </c>
-      <c r="C570" s="40" t="s">
+      <c r="C570" s="26" t="s">
         <v>3437</v>
       </c>
-      <c r="D570" s="40" t="s">
+      <c r="D570" s="26" t="s">
         <v>3428</v>
       </c>
-      <c r="E570" s="40" t="s">
+      <c r="E570" s="26" t="s">
         <v>3428</v>
       </c>
-      <c r="F570" s="41" t="s">
+      <c r="F570" s="9" t="s">
         <v>1089</v>
       </c>
-      <c r="G570" s="40" t="s">
+      <c r="G570" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H570" s="40" t="s">
+      <c r="H570" s="26" t="s">
         <v>1072</v>
       </c>
-      <c r="I570" s="40">
+      <c r="I570" s="26">
         <v>249010</v>
       </c>
-      <c r="J570" s="42">
+      <c r="J570" s="10">
         <v>38583</v>
       </c>
-      <c r="K570" s="42">
+      <c r="K570" s="10">
         <v>46147</v>
       </c>
-      <c r="L570" s="43"/>
-      <c r="M570" s="43"/>
-      <c r="N570" s="40" t="s">
+      <c r="L570" s="28"/>
+      <c r="M570" s="28"/>
+      <c r="N570" s="26" t="s">
         <v>3467</v>
       </c>
-      <c r="O570" s="40"/>
-      <c r="P570" s="40"/>
-      <c r="Q570" s="40"/>
-      <c r="R570" s="40"/>
-      <c r="S570" s="40"/>
-      <c r="T570" s="40"/>
-      <c r="U570" s="44"/>
-      <c r="V570" s="40" t="s">
+      <c r="O570" s="26"/>
+      <c r="P570" s="26"/>
+      <c r="Q570" s="26"/>
+      <c r="R570" s="26"/>
+      <c r="S570" s="26"/>
+      <c r="T570" s="26"/>
+      <c r="U570" s="29"/>
+      <c r="V570" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W570" s="40" t="s">
+      <c r="W570" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X570" s="40" t="s">
+      <c r="X570" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y570" s="15"/>
-      <c r="Z570" s="14"/>
-    </row>
-    <row r="571" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A571" s="39">
+      <c r="Y570" s="26"/>
+    </row>
+    <row r="571" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A571" s="35">
         <v>269030</v>
       </c>
-      <c r="B571" s="40" t="s">
+      <c r="B571" s="26" t="s">
         <v>3454</v>
       </c>
-      <c r="C571" s="40" t="s">
+      <c r="C571" s="26" t="s">
         <v>3438</v>
       </c>
-      <c r="D571" s="40" t="s">
+      <c r="D571" s="26" t="s">
         <v>3429</v>
       </c>
-      <c r="E571" s="40" t="s">
+      <c r="E571" s="26" t="s">
         <v>3429</v>
       </c>
-      <c r="F571" s="41" t="s">
+      <c r="F571" s="9" t="s">
         <v>1974</v>
       </c>
-      <c r="G571" s="40" t="s">
+      <c r="G571" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H571" s="40" t="s">
+      <c r="H571" s="26" t="s">
         <v>1975</v>
       </c>
-      <c r="I571" s="40">
+      <c r="I571" s="26">
         <v>253014</v>
       </c>
-      <c r="J571" s="42">
+      <c r="J571" s="10">
         <v>38427</v>
       </c>
-      <c r="K571" s="42">
+      <c r="K571" s="10">
         <v>46149</v>
       </c>
-      <c r="L571" s="43"/>
-      <c r="M571" s="43"/>
-      <c r="N571" s="40" t="s">
+      <c r="L571" s="28"/>
+      <c r="M571" s="28"/>
+      <c r="N571" s="26" t="s">
         <v>3468</v>
       </c>
-      <c r="O571" s="40"/>
-      <c r="P571" s="40"/>
-      <c r="Q571" s="40"/>
-      <c r="R571" s="40"/>
-      <c r="S571" s="40"/>
-      <c r="T571" s="40"/>
-      <c r="U571" s="44"/>
-      <c r="V571" s="40" t="s">
+      <c r="O571" s="26"/>
+      <c r="P571" s="26"/>
+      <c r="Q571" s="26"/>
+      <c r="R571" s="26"/>
+      <c r="S571" s="26"/>
+      <c r="T571" s="26"/>
+      <c r="U571" s="29"/>
+      <c r="V571" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W571" s="40" t="s">
+      <c r="W571" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X571" s="40" t="s">
+      <c r="X571" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y571" s="15"/>
-      <c r="Z571" s="14"/>
-    </row>
-    <row r="572" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A572" s="39">
+      <c r="Y571" s="26"/>
+    </row>
+    <row r="572" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A572" s="35">
         <v>169022</v>
       </c>
-      <c r="B572" s="40" t="s">
+      <c r="B572" s="26" t="s">
         <v>3463</v>
       </c>
-      <c r="C572" s="40" t="s">
+      <c r="C572" s="26" t="s">
         <v>3439</v>
       </c>
-      <c r="D572" s="40" t="s">
+      <c r="D572" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="E572" s="40" t="s">
+      <c r="E572" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="F572" s="41" t="s">
+      <c r="F572" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="G572" s="40" t="s">
+      <c r="G572" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H572" s="40" t="s">
+      <c r="H572" s="26" t="s">
         <v>472</v>
       </c>
-      <c r="I572" s="40">
+      <c r="I572" s="26">
         <v>168038</v>
       </c>
-      <c r="J572" s="42">
+      <c r="J572" s="10">
         <v>35374</v>
       </c>
-      <c r="K572" s="42">
+      <c r="K572" s="10">
         <v>46153</v>
       </c>
-      <c r="L572" s="43"/>
-      <c r="M572" s="43"/>
-      <c r="N572" s="40" t="s">
+      <c r="L572" s="28"/>
+      <c r="M572" s="28"/>
+      <c r="N572" s="26" t="s">
         <v>3469</v>
       </c>
-      <c r="O572" s="40" t="s">
+      <c r="O572" s="26" t="s">
         <v>3480</v>
       </c>
-      <c r="P572" s="40"/>
-      <c r="Q572" s="40"/>
-      <c r="R572" s="40"/>
-      <c r="S572" s="40"/>
-      <c r="T572" s="40"/>
-      <c r="U572" s="44"/>
-      <c r="V572" s="40" t="s">
+      <c r="P572" s="26"/>
+      <c r="Q572" s="26"/>
+      <c r="R572" s="26"/>
+      <c r="S572" s="26"/>
+      <c r="T572" s="26"/>
+      <c r="U572" s="29"/>
+      <c r="V572" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W572" s="40" t="s">
+      <c r="W572" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X572" s="40" t="s">
+      <c r="X572" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y572" s="15"/>
-      <c r="Z572" s="14"/>
-    </row>
-    <row r="573" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A573" s="39">
+      <c r="Y572" s="26"/>
+    </row>
+    <row r="573" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A573" s="35">
         <v>269034</v>
       </c>
-      <c r="B573" s="40" t="s">
+      <c r="B573" s="26" t="s">
         <v>3464</v>
       </c>
-      <c r="C573" s="40" t="s">
+      <c r="C573" s="26" t="s">
         <v>3440</v>
       </c>
-      <c r="D573" s="40" t="s">
+      <c r="D573" s="26" t="s">
         <v>3430</v>
       </c>
-      <c r="E573" s="40" t="s">
+      <c r="E573" s="26" t="s">
         <v>3430</v>
       </c>
-      <c r="F573" s="41" t="s">
+      <c r="F573" s="9" t="s">
         <v>3450</v>
       </c>
-      <c r="G573" s="40" t="s">
+      <c r="G573" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H573" s="40" t="s">
+      <c r="H573" s="26" t="s">
         <v>2684</v>
       </c>
-      <c r="I573" s="40">
+      <c r="I573" s="26">
         <v>269032</v>
       </c>
-      <c r="J573" s="42">
+      <c r="J573" s="10">
         <v>37273</v>
       </c>
-      <c r="K573" s="42">
+      <c r="K573" s="10">
         <v>46160</v>
       </c>
-      <c r="L573" s="43"/>
-      <c r="M573" s="43"/>
-      <c r="N573" s="40" t="s">
+      <c r="L573" s="28"/>
+      <c r="M573" s="28"/>
+      <c r="N573" s="26" t="s">
         <v>3470</v>
       </c>
-      <c r="O573" s="40" t="s">
+      <c r="O573" s="26" t="s">
         <v>3481</v>
       </c>
-      <c r="P573" s="40"/>
-      <c r="Q573" s="40"/>
-      <c r="R573" s="40"/>
-      <c r="S573" s="40"/>
-      <c r="T573" s="40"/>
-      <c r="U573" s="44"/>
-      <c r="V573" s="40" t="s">
+      <c r="P573" s="26"/>
+      <c r="Q573" s="26"/>
+      <c r="R573" s="26"/>
+      <c r="S573" s="26"/>
+      <c r="T573" s="26"/>
+      <c r="U573" s="29"/>
+      <c r="V573" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W573" s="40" t="s">
+      <c r="W573" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X573" s="40" t="s">
+      <c r="X573" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y573" s="15"/>
-      <c r="Z573" s="14"/>
-    </row>
-    <row r="574" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A574" s="39">
+      <c r="Y573" s="26"/>
+    </row>
+    <row r="574" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A574" s="35">
         <v>269038</v>
       </c>
-      <c r="B574" s="40" t="s">
+      <c r="B574" s="26" t="s">
         <v>3455</v>
       </c>
-      <c r="C574" s="40" t="s">
+      <c r="C574" s="26" t="s">
         <v>3441</v>
       </c>
-      <c r="D574" s="40" t="s">
+      <c r="D574" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="E574" s="40" t="s">
+      <c r="E574" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="F574" s="41" t="s">
+      <c r="F574" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="G574" s="40" t="s">
+      <c r="G574" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H574" s="40" t="s">
+      <c r="H574" s="26" t="s">
         <v>895</v>
       </c>
-      <c r="I574" s="40">
+      <c r="I574" s="26">
         <v>264090</v>
       </c>
-      <c r="J574" s="42">
+      <c r="J574" s="10">
         <v>35478</v>
       </c>
-      <c r="K574" s="42">
+      <c r="K574" s="10">
         <v>46160</v>
       </c>
-      <c r="L574" s="43"/>
-      <c r="M574" s="43"/>
-      <c r="N574" s="40" t="s">
+      <c r="L574" s="28"/>
+      <c r="M574" s="28"/>
+      <c r="N574" s="26" t="s">
         <v>3471</v>
       </c>
-      <c r="O574" s="40"/>
-      <c r="P574" s="40"/>
-      <c r="Q574" s="40"/>
-      <c r="R574" s="40"/>
-      <c r="S574" s="40"/>
-      <c r="T574" s="40"/>
-      <c r="U574" s="44"/>
-      <c r="V574" s="40" t="s">
+      <c r="O574" s="26"/>
+      <c r="P574" s="26"/>
+      <c r="Q574" s="26"/>
+      <c r="R574" s="26"/>
+      <c r="S574" s="26"/>
+      <c r="T574" s="26"/>
+      <c r="U574" s="29"/>
+      <c r="V574" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W574" s="40" t="s">
+      <c r="W574" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X574" s="40" t="s">
+      <c r="X574" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y574" s="15"/>
-      <c r="Z574" s="14"/>
-    </row>
-    <row r="575" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="39">
+      <c r="Y574" s="26"/>
+    </row>
+    <row r="575" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="35">
         <v>269033</v>
       </c>
-      <c r="B575" s="40" t="s">
+      <c r="B575" s="26" t="s">
         <v>3456</v>
       </c>
-      <c r="C575" s="40" t="s">
+      <c r="C575" s="26" t="s">
         <v>3442</v>
       </c>
-      <c r="D575" s="40" t="s">
+      <c r="D575" s="26" t="s">
         <v>3431</v>
       </c>
-      <c r="E575" s="40" t="s">
+      <c r="E575" s="26" t="s">
         <v>3431</v>
       </c>
-      <c r="F575" s="41" t="s">
+      <c r="F575" s="9" t="s">
         <v>3451</v>
       </c>
-      <c r="G575" s="40" t="s">
+      <c r="G575" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H575" s="40" t="s">
+      <c r="H575" s="26" t="s">
         <v>1376</v>
       </c>
-      <c r="I575" s="40">
+      <c r="I575" s="26">
         <v>256014</v>
       </c>
-      <c r="J575" s="42">
+      <c r="J575" s="10">
         <v>37980</v>
       </c>
-      <c r="K575" s="42">
+      <c r="K575" s="10">
         <v>46160</v>
       </c>
-      <c r="L575" s="43"/>
-      <c r="M575" s="43"/>
-      <c r="N575" s="40" t="s">
+      <c r="L575" s="28"/>
+      <c r="M575" s="28"/>
+      <c r="N575" s="26" t="s">
         <v>3472</v>
       </c>
-      <c r="O575" s="40" t="s">
+      <c r="O575" s="26" t="s">
         <v>3482</v>
       </c>
-      <c r="P575" s="40"/>
-      <c r="Q575" s="40"/>
-      <c r="R575" s="40"/>
-      <c r="S575" s="40"/>
-      <c r="T575" s="40"/>
-      <c r="U575" s="44"/>
-      <c r="V575" s="40" t="s">
+      <c r="P575" s="26"/>
+      <c r="Q575" s="26"/>
+      <c r="R575" s="26"/>
+      <c r="S575" s="26"/>
+      <c r="T575" s="26"/>
+      <c r="U575" s="29"/>
+      <c r="V575" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W575" s="40" t="s">
+      <c r="W575" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X575" s="40" t="s">
+      <c r="X575" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y575" s="15"/>
-      <c r="Z575" s="14"/>
-    </row>
-    <row r="576" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A576" s="39">
+      <c r="Y575" s="26"/>
+    </row>
+    <row r="576" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A576" s="35">
         <v>269037</v>
       </c>
-      <c r="B576" s="40" t="s">
+      <c r="B576" s="26" t="s">
         <v>3457</v>
       </c>
-      <c r="C576" s="40" t="s">
+      <c r="C576" s="26" t="s">
         <v>3443</v>
       </c>
-      <c r="D576" s="40" t="s">
+      <c r="D576" s="26" t="s">
         <v>3432</v>
       </c>
-      <c r="E576" s="40" t="s">
+      <c r="E576" s="26" t="s">
         <v>3432</v>
       </c>
-      <c r="F576" s="41" t="s">
+      <c r="F576" s="9" t="s">
         <v>1266</v>
       </c>
-      <c r="G576" s="40" t="s">
+      <c r="G576" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H576" s="40" t="s">
+      <c r="H576" s="26" t="s">
         <v>1456</v>
       </c>
-      <c r="I576" s="40">
+      <c r="I576" s="26">
         <v>254057</v>
       </c>
-      <c r="J576" s="42">
+      <c r="J576" s="10">
         <v>36424</v>
       </c>
-      <c r="K576" s="42">
+      <c r="K576" s="10">
         <v>46160</v>
       </c>
-      <c r="L576" s="43"/>
-      <c r="M576" s="43"/>
-      <c r="N576" s="40" t="s">
+      <c r="L576" s="28"/>
+      <c r="M576" s="28"/>
+      <c r="N576" s="26" t="s">
         <v>3473</v>
       </c>
-      <c r="O576" s="40"/>
-      <c r="P576" s="40"/>
-      <c r="Q576" s="40"/>
-      <c r="R576" s="40"/>
-      <c r="S576" s="40"/>
-      <c r="T576" s="40"/>
-      <c r="U576" s="44"/>
-      <c r="V576" s="40" t="s">
+      <c r="O576" s="26"/>
+      <c r="P576" s="26"/>
+      <c r="Q576" s="26"/>
+      <c r="R576" s="26"/>
+      <c r="S576" s="26"/>
+      <c r="T576" s="26"/>
+      <c r="U576" s="29"/>
+      <c r="V576" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W576" s="40" t="s">
+      <c r="W576" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X576" s="40" t="s">
+      <c r="X576" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y576" s="15"/>
-      <c r="Z576" s="14"/>
-    </row>
-    <row r="577" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A577" s="39">
+      <c r="Y576" s="26"/>
+    </row>
+    <row r="577" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A577" s="35">
         <v>269036</v>
       </c>
-      <c r="B577" s="40" t="s">
+      <c r="B577" s="26" t="s">
         <v>3458</v>
       </c>
-      <c r="C577" s="40" t="s">
+      <c r="C577" s="26" t="s">
         <v>3444</v>
       </c>
-      <c r="D577" s="40" t="s">
+      <c r="D577" s="26" t="s">
         <v>3433</v>
       </c>
-      <c r="E577" s="40" t="s">
+      <c r="E577" s="26" t="s">
         <v>3433</v>
       </c>
-      <c r="F577" s="41" t="s">
+      <c r="F577" s="9" t="s">
         <v>1266</v>
       </c>
-      <c r="G577" s="40" t="s">
+      <c r="G577" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H577" s="40" t="s">
+      <c r="H577" s="26" t="s">
         <v>1481</v>
       </c>
-      <c r="I577" s="40">
+      <c r="I577" s="26">
         <v>254057</v>
       </c>
-      <c r="J577" s="42">
+      <c r="J577" s="10">
         <v>35656</v>
       </c>
-      <c r="K577" s="42">
+      <c r="K577" s="10">
         <v>46160</v>
       </c>
-      <c r="L577" s="43"/>
-      <c r="M577" s="43"/>
-      <c r="N577" s="40" t="s">
+      <c r="L577" s="28"/>
+      <c r="M577" s="28"/>
+      <c r="N577" s="26" t="s">
         <v>3474</v>
       </c>
-      <c r="O577" s="40"/>
-      <c r="P577" s="40"/>
-      <c r="Q577" s="40"/>
-      <c r="R577" s="40"/>
-      <c r="S577" s="40"/>
-      <c r="T577" s="40"/>
-      <c r="U577" s="44"/>
-      <c r="V577" s="40" t="s">
+      <c r="O577" s="26"/>
+      <c r="P577" s="26"/>
+      <c r="Q577" s="26"/>
+      <c r="R577" s="26"/>
+      <c r="S577" s="26"/>
+      <c r="T577" s="26"/>
+      <c r="U577" s="29"/>
+      <c r="V577" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W577" s="40" t="s">
+      <c r="W577" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X577" s="40" t="s">
+      <c r="X577" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y577" s="15"/>
-      <c r="Z577" s="14"/>
-    </row>
-    <row r="578" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A578" s="39">
+      <c r="Y577" s="26"/>
+    </row>
+    <row r="578" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A578" s="35">
         <v>269035</v>
       </c>
-      <c r="B578" s="40" t="s">
+      <c r="B578" s="26" t="s">
         <v>3459</v>
       </c>
-      <c r="C578" s="40" t="s">
+      <c r="C578" s="26" t="s">
         <v>3445</v>
       </c>
-      <c r="D578" s="40" t="s">
+      <c r="D578" s="26" t="s">
         <v>3434</v>
       </c>
-      <c r="E578" s="40" t="s">
+      <c r="E578" s="26" t="s">
         <v>3434</v>
       </c>
-      <c r="F578" s="41" t="s">
+      <c r="F578" s="9" t="s">
         <v>1797</v>
       </c>
-      <c r="G578" s="40" t="s">
+      <c r="G578" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H578" s="40" t="s">
+      <c r="H578" s="26" t="s">
         <v>1792</v>
       </c>
-      <c r="I578" s="40">
+      <c r="I578" s="26">
         <v>269022</v>
       </c>
-      <c r="J578" s="42">
+      <c r="J578" s="10">
         <v>38540</v>
       </c>
-      <c r="K578" s="42">
+      <c r="K578" s="10">
         <v>46160</v>
       </c>
-      <c r="L578" s="43"/>
-      <c r="M578" s="43"/>
-      <c r="N578" s="40" t="s">
+      <c r="L578" s="28"/>
+      <c r="M578" s="28"/>
+      <c r="N578" s="26" t="s">
         <v>3475</v>
       </c>
-      <c r="O578" s="40"/>
-      <c r="P578" s="40"/>
-      <c r="Q578" s="40"/>
-      <c r="R578" s="40"/>
-      <c r="S578" s="40"/>
-      <c r="T578" s="40"/>
-      <c r="U578" s="44"/>
-      <c r="V578" s="40" t="s">
+      <c r="O578" s="26"/>
+      <c r="P578" s="26"/>
+      <c r="Q578" s="26"/>
+      <c r="R578" s="26"/>
+      <c r="S578" s="26"/>
+      <c r="T578" s="26"/>
+      <c r="U578" s="29"/>
+      <c r="V578" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W578" s="40" t="s">
+      <c r="W578" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X578" s="40" t="s">
+      <c r="X578" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y578" s="15"/>
-      <c r="Z578" s="14"/>
-    </row>
-    <row r="579" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A579" s="39">
+      <c r="Y578" s="26"/>
+    </row>
+    <row r="579" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A579" s="35">
         <v>269039</v>
       </c>
-      <c r="B579" s="40" t="s">
+      <c r="B579" s="26" t="s">
         <v>3465</v>
       </c>
-      <c r="C579" s="40" t="s">
+      <c r="C579" s="26" t="s">
         <v>3446</v>
       </c>
-      <c r="D579" s="40" t="s">
+      <c r="D579" s="26" t="s">
         <v>713</v>
       </c>
-      <c r="E579" s="40" t="s">
+      <c r="E579" s="26" t="s">
         <v>713</v>
       </c>
-      <c r="F579" s="41" t="s">
+      <c r="F579" s="9" t="s">
         <v>3452</v>
       </c>
-      <c r="G579" s="40" t="s">
+      <c r="G579" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H579" s="40" t="s">
+      <c r="H579" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="I579" s="40">
+      <c r="I579" s="26">
         <v>266049</v>
       </c>
-      <c r="J579" s="42">
+      <c r="J579" s="10">
         <v>35685</v>
       </c>
-      <c r="K579" s="42">
+      <c r="K579" s="10">
         <v>46167</v>
       </c>
-      <c r="L579" s="43"/>
-      <c r="M579" s="43"/>
-      <c r="N579" s="40" t="s">
+      <c r="L579" s="28"/>
+      <c r="M579" s="28"/>
+      <c r="N579" s="26" t="s">
         <v>3476</v>
       </c>
-      <c r="O579" s="40" t="s">
+      <c r="O579" s="26" t="s">
         <v>3483</v>
       </c>
-      <c r="P579" s="40"/>
-      <c r="Q579" s="40"/>
-      <c r="R579" s="40"/>
-      <c r="S579" s="40"/>
-      <c r="T579" s="40"/>
-      <c r="U579" s="44"/>
-      <c r="V579" s="40" t="s">
+      <c r="P579" s="26"/>
+      <c r="Q579" s="26"/>
+      <c r="R579" s="26"/>
+      <c r="S579" s="26"/>
+      <c r="T579" s="26"/>
+      <c r="U579" s="29"/>
+      <c r="V579" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W579" s="40" t="s">
+      <c r="W579" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X579" s="40" t="s">
+      <c r="X579" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y579" s="15"/>
-      <c r="Z579" s="14"/>
-    </row>
-    <row r="580" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A580" s="39">
+      <c r="Y579" s="26"/>
+    </row>
+    <row r="580" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A580" s="35">
         <v>269043</v>
       </c>
-      <c r="B580" s="40" t="s">
+      <c r="B580" s="26" t="s">
         <v>3460</v>
       </c>
-      <c r="C580" s="40" t="s">
+      <c r="C580" s="26" t="s">
         <v>3447</v>
       </c>
-      <c r="D580" s="40" t="s">
+      <c r="D580" s="26" t="s">
         <v>3435</v>
       </c>
-      <c r="E580" s="40" t="s">
+      <c r="E580" s="26" t="s">
         <v>3435</v>
       </c>
-      <c r="F580" s="41" t="s">
+      <c r="F580" s="9" t="s">
         <v>1266</v>
       </c>
-      <c r="G580" s="40" t="s">
+      <c r="G580" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H580" s="40" t="s">
+      <c r="H580" s="26" t="s">
         <v>3485</v>
       </c>
-      <c r="I580" s="40">
+      <c r="I580" s="26">
         <v>267096</v>
       </c>
-      <c r="J580" s="42">
+      <c r="J580" s="10">
         <v>37640</v>
       </c>
-      <c r="K580" s="42">
+      <c r="K580" s="10">
         <v>46177</v>
       </c>
-      <c r="L580" s="43"/>
-      <c r="M580" s="43"/>
-      <c r="N580" s="40" t="s">
+      <c r="L580" s="28"/>
+      <c r="M580" s="28"/>
+      <c r="N580" s="26" t="s">
         <v>3477</v>
       </c>
-      <c r="O580" s="40"/>
-      <c r="P580" s="40"/>
-      <c r="Q580" s="40"/>
-      <c r="R580" s="40"/>
-      <c r="S580" s="40"/>
-      <c r="T580" s="40"/>
-      <c r="U580" s="44"/>
-      <c r="V580" s="40" t="s">
+      <c r="O580" s="26"/>
+      <c r="P580" s="26"/>
+      <c r="Q580" s="26"/>
+      <c r="R580" s="26"/>
+      <c r="S580" s="26"/>
+      <c r="T580" s="26"/>
+      <c r="U580" s="29"/>
+      <c r="V580" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W580" s="40" t="s">
+      <c r="W580" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X580" s="40" t="s">
+      <c r="X580" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y580" s="15"/>
-      <c r="Z580" s="14"/>
-    </row>
-    <row r="581" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A581" s="39">
+      <c r="Y580" s="26"/>
+    </row>
+    <row r="581" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A581" s="35">
         <v>269041</v>
       </c>
-      <c r="B581" s="40" t="s">
+      <c r="B581" s="26" t="s">
         <v>3461</v>
       </c>
-      <c r="C581" s="40" t="s">
+      <c r="C581" s="26" t="s">
         <v>3448</v>
       </c>
-      <c r="D581" s="40" t="s">
+      <c r="D581" s="26" t="s">
         <v>1381</v>
       </c>
-      <c r="E581" s="40" t="s">
+      <c r="E581" s="26" t="s">
         <v>1381</v>
       </c>
-      <c r="F581" s="41" t="s">
+      <c r="F581" s="9" t="s">
         <v>3453</v>
       </c>
-      <c r="G581" s="40" t="s">
+      <c r="G581" s="26" t="s">
         <v>3436</v>
       </c>
-      <c r="H581" s="40" t="s">
+      <c r="H581" s="26" t="s">
         <v>1782</v>
       </c>
-      <c r="I581" s="40">
+      <c r="I581" s="26">
         <v>242032</v>
       </c>
-      <c r="J581" s="42">
+      <c r="J581" s="10">
         <v>35824</v>
       </c>
-      <c r="K581" s="42">
+      <c r="K581" s="10">
         <v>46177</v>
       </c>
-      <c r="L581" s="43"/>
-      <c r="M581" s="43"/>
-      <c r="N581" s="40" t="s">
+      <c r="L581" s="28"/>
+      <c r="M581" s="28"/>
+      <c r="N581" s="26" t="s">
         <v>3478</v>
       </c>
-      <c r="O581" s="40" t="s">
+      <c r="O581" s="26" t="s">
         <v>3484</v>
       </c>
-      <c r="P581" s="40"/>
-      <c r="Q581" s="40"/>
-      <c r="R581" s="40"/>
-      <c r="S581" s="40"/>
-      <c r="T581" s="40"/>
-      <c r="U581" s="44"/>
-      <c r="V581" s="40" t="s">
+      <c r="P581" s="26"/>
+      <c r="Q581" s="26"/>
+      <c r="R581" s="26"/>
+      <c r="S581" s="26"/>
+      <c r="T581" s="26"/>
+      <c r="U581" s="29"/>
+      <c r="V581" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W581" s="40" t="s">
+      <c r="W581" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X581" s="40" t="s">
+      <c r="X581" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y581" s="15"/>
-      <c r="Z581" s="14"/>
-    </row>
-    <row r="582" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A582" s="39">
+      <c r="Y581" s="26"/>
+    </row>
+    <row r="582" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A582" s="35">
         <v>269042</v>
       </c>
-      <c r="B582" s="40" t="s">
+      <c r="B582" s="26" t="s">
         <v>3462</v>
       </c>
-      <c r="C582" s="40" t="s">
+      <c r="C582" s="26" t="s">
         <v>3449</v>
       </c>
-      <c r="D582" s="40" t="s">
+      <c r="D582" s="26" t="s">
         <v>1780</v>
       </c>
-      <c r="E582" s="40" t="s">
+      <c r="E582" s="26" t="s">
         <v>1780</v>
       </c>
-      <c r="F582" s="41" t="s">
+      <c r="F582" s="9" t="s">
         <v>1892</v>
       </c>
-      <c r="G582" s="40" t="s">
+      <c r="G582" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="H582" s="40" t="s">
+      <c r="H582" s="26" t="s">
         <v>1880</v>
       </c>
-      <c r="I582" s="40">
+      <c r="I582" s="26">
         <v>269022</v>
       </c>
-      <c r="J582" s="42">
+      <c r="J582" s="10">
         <v>38231</v>
       </c>
-      <c r="K582" s="42">
+      <c r="K582" s="10">
         <v>46177</v>
       </c>
-      <c r="L582" s="43"/>
-      <c r="M582" s="43"/>
-      <c r="N582" s="40" t="s">
+      <c r="L582" s="28"/>
+      <c r="M582" s="28"/>
+      <c r="N582" s="26" t="s">
         <v>3479</v>
       </c>
-      <c r="O582" s="40"/>
-      <c r="P582" s="40"/>
-      <c r="Q582" s="40"/>
-      <c r="R582" s="40"/>
-      <c r="S582" s="40"/>
-      <c r="T582" s="40"/>
-      <c r="U582" s="44"/>
-      <c r="V582" s="40" t="s">
+      <c r="O582" s="26"/>
+      <c r="P582" s="26"/>
+      <c r="Q582" s="26"/>
+      <c r="R582" s="26"/>
+      <c r="S582" s="26"/>
+      <c r="T582" s="26"/>
+      <c r="U582" s="29"/>
+      <c r="V582" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W582" s="40" t="s">
+      <c r="W582" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X582" s="40" t="s">
+      <c r="X582" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y582" s="15"/>
-      <c r="Z582" s="14"/>
-    </row>
-    <row r="583" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y582" s="26"/>
+    </row>
+    <row r="583" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E583" s="31"/>
       <c r="F583" s="14"/>
       <c r="T583" s="32"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{681C522B-376D-48B0-A19E-4B9F4F29C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{FB43BE3C-E866-400C-8C88-4ADFB1894538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10636,7 +10636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10725,9 +10725,6 @@
     <xf numFmtId="10" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -10779,10 +10776,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11073,11 +11066,11 @@
   <dimension ref="A1:Z583"/>
   <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" style="36" customWidth="1"/>
+    <col min="1" max="1" width="12" style="35" customWidth="1"/>
     <col min="2" max="3" width="28" style="14" customWidth="1"/>
     <col min="4" max="4" width="19.453125" style="14" customWidth="1"/>
     <col min="5" max="5" width="17.54296875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="37.1796875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="37.1796875" style="30" customWidth="1"/>
     <col min="7" max="7" width="12" style="14" customWidth="1"/>
     <col min="8" max="8" width="28" style="14" customWidth="1"/>
     <col min="9" max="9" width="13" style="14" customWidth="1"/>
@@ -11089,7 +11082,7 @@
     <col min="16" max="16" width="14" style="14" customWidth="1"/>
     <col min="17" max="18" width="18" style="14" customWidth="1"/>
     <col min="19" max="20" width="14" style="14" customWidth="1"/>
-    <col min="21" max="21" width="14" style="32" customWidth="1"/>
+    <col min="21" max="21" width="14" style="31" customWidth="1"/>
     <col min="22" max="22" width="15.08984375" style="14" customWidth="1"/>
     <col min="23" max="23" width="15.453125" style="14" customWidth="1"/>
     <col min="24" max="24" width="13.54296875" style="14" customWidth="1"/>
@@ -11098,32 +11091,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>3486</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -11203,7 +11196,7 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33">
+      <c r="A3" s="32">
         <v>168001</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -11262,7 +11255,7 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33">
+      <c r="A4" s="32">
         <v>168016</v>
       </c>
       <c r="B4" s="15" t="s">
@@ -11323,7 +11316,7 @@
       <c r="Y4" s="15"/>
     </row>
     <row r="5" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="33">
+      <c r="A5" s="32">
         <v>258026</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -11388,7 +11381,7 @@
       <c r="Y5" s="15"/>
     </row>
     <row r="6" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="33">
+      <c r="A6" s="32">
         <v>234064</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -11451,7 +11444,7 @@
       <c r="Y6" s="15"/>
     </row>
     <row r="7" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33">
+      <c r="A7" s="32">
         <v>254019</v>
       </c>
       <c r="B7" s="15" t="s">
@@ -11512,7 +11505,7 @@
       <c r="Y7" s="15"/>
     </row>
     <row r="8" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33">
+      <c r="A8" s="32">
         <v>264004</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -11573,7 +11566,7 @@
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33">
+      <c r="A9" s="32">
         <v>264018</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -11632,7 +11625,7 @@
       <c r="Y9" s="15"/>
     </row>
     <row r="10" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="33">
+      <c r="A10" s="32">
         <v>264024</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -11693,7 +11686,7 @@
       <c r="Y10" s="15"/>
     </row>
     <row r="11" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33">
+      <c r="A11" s="32">
         <v>264034</v>
       </c>
       <c r="B11" s="15" t="s">
@@ -11752,7 +11745,7 @@
       <c r="Y11" s="15"/>
     </row>
     <row r="12" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="32">
         <v>264050</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -11811,7 +11804,7 @@
       <c r="Y12" s="15"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="33">
+      <c r="A13" s="32">
         <v>265038</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -11870,7 +11863,7 @@
       <c r="Y13" s="15"/>
     </row>
     <row r="14" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="33">
+      <c r="A14" s="32">
         <v>265122</v>
       </c>
       <c r="B14" s="15" t="s">
@@ -11931,7 +11924,7 @@
       <c r="Y14" s="15"/>
     </row>
     <row r="15" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="33">
+      <c r="A15" s="32">
         <v>266005</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -11996,7 +11989,7 @@
       <c r="Y15" s="15"/>
     </row>
     <row r="16" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="33">
+      <c r="A16" s="32">
         <v>267010</v>
       </c>
       <c r="B16" s="15" t="s">
@@ -12057,7 +12050,7 @@
       <c r="Y16" s="15"/>
     </row>
     <row r="17" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="33">
+      <c r="A17" s="32">
         <v>267071</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -12120,7 +12113,7 @@
       <c r="Y17" s="15"/>
     </row>
     <row r="18" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="33">
+      <c r="A18" s="32">
         <v>267082</v>
       </c>
       <c r="B18" s="15" t="s">
@@ -12181,7 +12174,7 @@
       <c r="Y18" s="15"/>
     </row>
     <row r="19" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="33">
+      <c r="A19" s="32">
         <v>267089</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -12240,7 +12233,7 @@
       <c r="Y19" s="15"/>
     </row>
     <row r="20" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="33">
+      <c r="A20" s="32">
         <v>267090</v>
       </c>
       <c r="B20" s="15" t="s">
@@ -12299,7 +12292,7 @@
       <c r="Y20" s="15"/>
     </row>
     <row r="21" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>268010</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -12358,7 +12351,7 @@
       <c r="Y21" s="15"/>
     </row>
     <row r="22" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="33">
+      <c r="A22" s="32">
         <v>268011</v>
       </c>
       <c r="B22" s="15" t="s">
@@ -12417,7 +12410,7 @@
       <c r="Y22" s="15"/>
     </row>
     <row r="23" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="33">
+      <c r="A23" s="32">
         <v>268051</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -12480,7 +12473,7 @@
       <c r="Y23" s="15"/>
     </row>
     <row r="24" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="33">
+      <c r="A24" s="32">
         <v>268060</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -12541,7 +12534,7 @@
       <c r="Y24" s="15"/>
     </row>
     <row r="25" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="33">
+      <c r="A25" s="32">
         <v>268065</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -12600,7 +12593,7 @@
       <c r="Y25" s="15"/>
     </row>
     <row r="26" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="33">
+      <c r="A26" s="32">
         <v>268066</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -12659,7 +12652,7 @@
       <c r="Y26" s="15"/>
     </row>
     <row r="27" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33">
+      <c r="A27" s="32">
         <v>268067</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -12718,7 +12711,7 @@
       <c r="Y27" s="15"/>
     </row>
     <row r="28" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="33">
+      <c r="A28" s="32">
         <v>268085</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -12777,7 +12770,7 @@
       <c r="Y28" s="15"/>
     </row>
     <row r="29" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>269023</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -12838,7 +12831,7 @@
       <c r="Y29" s="15"/>
     </row>
     <row r="30" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="33">
+      <c r="A30" s="32">
         <v>255012</v>
       </c>
       <c r="B30" s="15" t="s">
@@ -12899,7 +12892,7 @@
       <c r="Y30" s="15"/>
     </row>
     <row r="31" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="33">
+      <c r="A31" s="32">
         <v>259025</v>
       </c>
       <c r="B31" s="15" t="s">
@@ -12964,7 +12957,7 @@
       <c r="Y31" s="15"/>
     </row>
     <row r="32" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="33">
+      <c r="A32" s="32">
         <v>235035</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -13027,7 +13020,7 @@
       <c r="Y32" s="15"/>
     </row>
     <row r="33" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="33">
+      <c r="A33" s="32">
         <v>253020</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -13088,7 +13081,7 @@
       <c r="Y33" s="15"/>
     </row>
     <row r="34" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="33">
+      <c r="A34" s="32">
         <v>269032</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -13151,7 +13144,7 @@
       <c r="Y34" s="15"/>
     </row>
     <row r="35" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="33">
+      <c r="A35" s="32">
         <v>250051</v>
       </c>
       <c r="B35" s="15" t="s">
@@ -13218,7 +13211,7 @@
       <c r="Y35" s="15"/>
     </row>
     <row r="36" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="33">
+      <c r="A36" s="32">
         <v>254009</v>
       </c>
       <c r="B36" s="15" t="s">
@@ -13277,7 +13270,7 @@
       <c r="Y36" s="15"/>
     </row>
     <row r="37" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="33">
+      <c r="A37" s="32">
         <v>254054</v>
       </c>
       <c r="B37" s="15" t="s">
@@ -13336,7 +13329,7 @@
       <c r="Y37" s="15"/>
     </row>
     <row r="38" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="33">
+      <c r="A38" s="32">
         <v>255001</v>
       </c>
       <c r="B38" s="15" t="s">
@@ -13395,7 +13388,7 @@
       <c r="Y38" s="15"/>
     </row>
     <row r="39" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="33">
+      <c r="A39" s="32">
         <v>255023</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -13458,7 +13451,7 @@
       <c r="Y39" s="15"/>
     </row>
     <row r="40" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="33">
+      <c r="A40" s="32">
         <v>257010</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -13521,7 +13514,7 @@
       <c r="Y40" s="15"/>
     </row>
     <row r="41" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="33">
+      <c r="A41" s="32">
         <v>257029</v>
       </c>
       <c r="B41" s="15" t="s">
@@ -13582,7 +13575,7 @@
       <c r="Y41" s="15"/>
     </row>
     <row r="42" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="33">
+      <c r="A42" s="32">
         <v>261023</v>
       </c>
       <c r="B42" s="15" t="s">
@@ -13643,7 +13636,7 @@
       <c r="Y42" s="15"/>
     </row>
     <row r="43" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="33">
+      <c r="A43" s="32">
         <v>267025</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -13702,7 +13695,7 @@
       <c r="Y43" s="15"/>
     </row>
     <row r="44" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="33">
+      <c r="A44" s="32">
         <v>267026</v>
       </c>
       <c r="B44" s="15" t="s">
@@ -13761,7 +13754,7 @@
       <c r="Y44" s="15"/>
     </row>
     <row r="45" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="33">
+      <c r="A45" s="32">
         <v>267028</v>
       </c>
       <c r="B45" s="15" t="s">
@@ -13822,7 +13815,7 @@
       <c r="Y45" s="15"/>
     </row>
     <row r="46" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="33">
+      <c r="A46" s="32">
         <v>267079</v>
       </c>
       <c r="B46" s="15" t="s">
@@ -13881,7 +13874,7 @@
       <c r="Y46" s="15"/>
     </row>
     <row r="47" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="33">
+      <c r="A47" s="32">
         <v>267100</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -13936,7 +13929,7 @@
       <c r="Y47" s="15"/>
     </row>
     <row r="48" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="33">
+      <c r="A48" s="32">
         <v>267101</v>
       </c>
       <c r="B48" s="15" t="s">
@@ -13991,7 +13984,7 @@
       <c r="Y48" s="15"/>
     </row>
     <row r="49" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="33">
+      <c r="A49" s="32">
         <v>267105</v>
       </c>
       <c r="B49" s="15" t="s">
@@ -14046,7 +14039,7 @@
       <c r="Y49" s="15"/>
     </row>
     <row r="50" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="33">
+      <c r="A50" s="32">
         <v>268016</v>
       </c>
       <c r="B50" s="15" t="s">
@@ -14107,7 +14100,7 @@
       <c r="Y50" s="15"/>
     </row>
     <row r="51" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="33">
+      <c r="A51" s="32">
         <v>268059</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -14168,7 +14161,7 @@
       <c r="Y51" s="15"/>
     </row>
     <row r="52" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="33">
+      <c r="A52" s="32">
         <v>268061</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -14227,7 +14220,7 @@
       <c r="Y52" s="15"/>
     </row>
     <row r="53" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="33">
+      <c r="A53" s="32">
         <v>268079</v>
       </c>
       <c r="B53" s="15" t="s">
@@ -14286,7 +14279,7 @@
       <c r="Y53" s="15"/>
     </row>
     <row r="54" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="33">
+      <c r="A54" s="32">
         <v>268082</v>
       </c>
       <c r="B54" s="15" t="s">
@@ -14345,7 +14338,7 @@
       <c r="Y54" s="15"/>
     </row>
     <row r="55" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="33">
+      <c r="A55" s="32">
         <v>269025</v>
       </c>
       <c r="B55" s="15" t="s">
@@ -14404,7 +14397,7 @@
       <c r="Y55" s="15"/>
     </row>
     <row r="56" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="33">
+      <c r="A56" s="32">
         <v>269027</v>
       </c>
       <c r="B56" s="15" t="s">
@@ -14463,7 +14456,7 @@
       <c r="Y56" s="15"/>
     </row>
     <row r="57" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="33">
+      <c r="A57" s="32">
         <v>159029</v>
       </c>
       <c r="B57" s="15" t="s">
@@ -14528,7 +14521,7 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="33">
+      <c r="A58" s="32">
         <v>164005</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -14593,7 +14586,7 @@
       <c r="Y58" s="15"/>
     </row>
     <row r="59" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="33">
+      <c r="A59" s="32">
         <v>152008</v>
       </c>
       <c r="B59" s="15" t="s">
@@ -14656,7 +14649,7 @@
       <c r="Y59" s="15"/>
     </row>
     <row r="60" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="33">
+      <c r="A60" s="32">
         <v>267063</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -14717,7 +14710,7 @@
       <c r="Y60" s="15"/>
     </row>
     <row r="61" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="33">
+      <c r="A61" s="32">
         <v>168017</v>
       </c>
       <c r="B61" s="15" t="s">
@@ -14778,7 +14771,7 @@
       <c r="Y61" s="15"/>
     </row>
     <row r="62" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="33">
+      <c r="A62" s="32">
         <v>167034</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -14839,7 +14832,7 @@
       <c r="Y62" s="15"/>
     </row>
     <row r="63" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="33">
+      <c r="A63" s="32">
         <v>266049</v>
       </c>
       <c r="B63" s="15" t="s">
@@ -14904,7 +14897,7 @@
       </c>
     </row>
     <row r="64" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="33">
+      <c r="A64" s="32">
         <v>466004</v>
       </c>
       <c r="B64" s="15" t="s">
@@ -14965,7 +14958,7 @@
       <c r="Y64" s="15"/>
     </row>
     <row r="65" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="33">
+      <c r="A65" s="32">
         <v>269013</v>
       </c>
       <c r="B65" s="15" t="s">
@@ -15026,7 +15019,7 @@
       <c r="Y65" s="15"/>
     </row>
     <row r="66" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="33">
+      <c r="A66" s="32">
         <v>269001</v>
       </c>
       <c r="B66" s="15" t="s">
@@ -15087,7 +15080,7 @@
       <c r="Y66" s="15"/>
     </row>
     <row r="67" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="33">
+      <c r="A67" s="32">
         <v>265088</v>
       </c>
       <c r="B67" s="15" t="s">
@@ -15148,7 +15141,7 @@
       <c r="Y67" s="15"/>
     </row>
     <row r="68" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="33">
+      <c r="A68" s="32">
         <v>239005</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -15211,7 +15204,7 @@
       <c r="Y68" s="15"/>
     </row>
     <row r="69" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="33">
+      <c r="A69" s="32">
         <v>166027</v>
       </c>
       <c r="B69" s="15" t="s">
@@ -15272,7 +15265,7 @@
       <c r="Y69" s="15"/>
     </row>
     <row r="70" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="33">
+      <c r="A70" s="32">
         <v>168018</v>
       </c>
       <c r="B70" s="15" t="s">
@@ -15333,7 +15326,7 @@
       <c r="Y70" s="15"/>
     </row>
     <row r="71" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="33">
+      <c r="A71" s="32">
         <v>157033</v>
       </c>
       <c r="B71" s="15" t="s">
@@ -15396,7 +15389,7 @@
       <c r="Y71" s="15"/>
     </row>
     <row r="72" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="33">
+      <c r="A72" s="32">
         <v>169001</v>
       </c>
       <c r="B72" s="15" t="s">
@@ -15457,7 +15450,7 @@
       <c r="Y72" s="15"/>
     </row>
     <row r="73" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="33">
+      <c r="A73" s="32">
         <v>166035</v>
       </c>
       <c r="B73" s="15" t="s">
@@ -15518,7 +15511,7 @@
       <c r="Y73" s="15"/>
     </row>
     <row r="74" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="33">
+      <c r="A74" s="32">
         <v>269014</v>
       </c>
       <c r="B74" s="15" t="s">
@@ -15579,7 +15572,7 @@
       <c r="Y74" s="15"/>
     </row>
     <row r="75" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="33">
+      <c r="A75" s="32">
         <v>166032</v>
       </c>
       <c r="B75" s="15" t="s">
@@ -15640,7 +15633,7 @@
       <c r="Y75" s="15"/>
     </row>
     <row r="76" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="33">
+      <c r="A76" s="32">
         <v>169017</v>
       </c>
       <c r="B76" s="15" t="s">
@@ -15701,7 +15694,7 @@
       <c r="Y76" s="15"/>
     </row>
     <row r="77" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="33">
+      <c r="A77" s="32">
         <v>265011</v>
       </c>
       <c r="B77" s="15" t="s">
@@ -15766,7 +15759,7 @@
       <c r="Y77" s="15"/>
     </row>
     <row r="78" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="33">
+      <c r="A78" s="32">
         <v>168015</v>
       </c>
       <c r="B78" s="15" t="s">
@@ -15827,7 +15820,7 @@
       </c>
     </row>
     <row r="79" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="33">
+      <c r="A79" s="32">
         <v>168004</v>
       </c>
       <c r="B79" s="15" t="s">
@@ -15888,7 +15881,7 @@
       <c r="Y79" s="15"/>
     </row>
     <row r="80" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="33">
+      <c r="A80" s="32">
         <v>168028</v>
       </c>
       <c r="B80" s="15" t="s">
@@ -15951,7 +15944,7 @@
       <c r="Y80" s="15"/>
     </row>
     <row r="81" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="33">
+      <c r="A81" s="32">
         <v>160023</v>
       </c>
       <c r="B81" s="15" t="s">
@@ -16016,7 +16009,7 @@
       <c r="Y81" s="15"/>
     </row>
     <row r="82" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="33">
+      <c r="A82" s="32">
         <v>150026</v>
       </c>
       <c r="B82" s="15" t="s">
@@ -16083,7 +16076,7 @@
       <c r="Y82" s="15"/>
     </row>
     <row r="83" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="33">
+      <c r="A83" s="32">
         <v>161016</v>
       </c>
       <c r="B83" s="15" t="s">
@@ -16148,7 +16141,7 @@
       <c r="Y83" s="15"/>
     </row>
     <row r="84" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="33">
+      <c r="A84" s="32">
         <v>167040</v>
       </c>
       <c r="B84" s="15" t="s">
@@ -16209,7 +16202,7 @@
       <c r="Y84" s="15"/>
     </row>
     <row r="85" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="33">
+      <c r="A85" s="32">
         <v>161006</v>
       </c>
       <c r="B85" s="15" t="s">
@@ -16274,7 +16267,7 @@
       <c r="Y85" s="15"/>
     </row>
     <row r="86" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="33">
+      <c r="A86" s="32">
         <v>164014</v>
       </c>
       <c r="B86" s="15" t="s">
@@ -16331,7 +16324,7 @@
       <c r="Y86" s="15"/>
     </row>
     <row r="87" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="33">
+      <c r="A87" s="32">
         <v>165026</v>
       </c>
       <c r="B87" s="15" t="s">
@@ -16394,7 +16387,7 @@
       <c r="Y87" s="15"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="33">
+      <c r="A88" s="32">
         <v>166009</v>
       </c>
       <c r="B88" s="15" t="s">
@@ -16455,7 +16448,7 @@
       <c r="Y88" s="15"/>
     </row>
     <row r="89" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="33">
+      <c r="A89" s="32">
         <v>168038</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -16516,7 +16509,7 @@
       <c r="Y89" s="15"/>
     </row>
     <row r="90" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="33">
+      <c r="A90" s="32">
         <v>168041</v>
       </c>
       <c r="B90" s="15" t="s">
@@ -16577,7 +16570,7 @@
       <c r="Y90" s="15"/>
     </row>
     <row r="91" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="33">
+      <c r="A91" s="32">
         <v>169015</v>
       </c>
       <c r="B91" s="15" t="s">
@@ -16638,7 +16631,7 @@
       <c r="Y91" s="15"/>
     </row>
     <row r="92" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="33">
+      <c r="A92" s="32">
         <v>169020</v>
       </c>
       <c r="B92" s="15" t="s">
@@ -16699,7 +16692,7 @@
       <c r="Y92" s="15"/>
     </row>
     <row r="93" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="33">
+      <c r="A93" s="32">
         <v>169021</v>
       </c>
       <c r="B93" s="15" t="s">
@@ -16760,7 +16753,7 @@
       <c r="Y93" s="15"/>
     </row>
     <row r="94" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="33">
+      <c r="A94" s="32">
         <v>147016</v>
       </c>
       <c r="B94" s="15" t="s">
@@ -16825,7 +16818,7 @@
       <c r="Y94" s="15"/>
     </row>
     <row r="95" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="33">
+      <c r="A95" s="32">
         <v>148017</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -16886,7 +16879,7 @@
       <c r="Y95" s="15"/>
     </row>
     <row r="96" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="33">
+      <c r="A96" s="32">
         <v>150010</v>
       </c>
       <c r="B96" s="15" t="s">
@@ -16951,7 +16944,7 @@
       <c r="Y96" s="15"/>
     </row>
     <row r="97" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="33">
+      <c r="A97" s="32">
         <v>166021</v>
       </c>
       <c r="B97" s="15" t="s">
@@ -17014,7 +17007,7 @@
       <c r="Y97" s="15"/>
     </row>
     <row r="98" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="33">
+      <c r="A98" s="32">
         <v>167004</v>
       </c>
       <c r="B98" s="15" t="s">
@@ -17075,7 +17068,7 @@
       <c r="Y98" s="15"/>
     </row>
     <row r="99" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="33">
+      <c r="A99" s="32">
         <v>167023</v>
       </c>
       <c r="B99" s="15" t="s">
@@ -17136,7 +17129,7 @@
       <c r="Y99" s="15"/>
     </row>
     <row r="100" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="33">
+      <c r="A100" s="32">
         <v>169003</v>
       </c>
       <c r="B100" s="15" t="s">
@@ -17197,7 +17190,7 @@
       <c r="Y100" s="15"/>
     </row>
     <row r="101" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="33">
+      <c r="A101" s="32">
         <v>147022</v>
       </c>
       <c r="B101" s="15" t="s">
@@ -17264,7 +17257,7 @@
       <c r="Y101" s="15"/>
     </row>
     <row r="102" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="33">
+      <c r="A102" s="32">
         <v>165014</v>
       </c>
       <c r="B102" s="15" t="s">
@@ -17325,7 +17318,7 @@
       <c r="Y102" s="15"/>
     </row>
     <row r="103" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="33">
+      <c r="A103" s="32">
         <v>166028</v>
       </c>
       <c r="B103" s="15" t="s">
@@ -17388,7 +17381,7 @@
       <c r="Y103" s="15"/>
     </row>
     <row r="104" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="33">
+      <c r="A104" s="32">
         <v>167015</v>
       </c>
       <c r="B104" s="15" t="s">
@@ -17449,7 +17442,7 @@
       <c r="Y104" s="15"/>
     </row>
     <row r="105" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="34">
+      <c r="A105" s="33">
         <v>168002</v>
       </c>
       <c r="B105" s="21" t="s">
@@ -17507,7 +17500,7 @@
       <c r="Z105" s="14"/>
     </row>
     <row r="106" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="33">
+      <c r="A106" s="32">
         <v>168014</v>
       </c>
       <c r="B106" s="15" t="s">
@@ -17568,7 +17561,7 @@
       <c r="Y106" s="15"/>
     </row>
     <row r="107" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="33">
+      <c r="A107" s="32">
         <v>168022</v>
       </c>
       <c r="B107" s="15" t="s">
@@ -17631,7 +17624,7 @@
       <c r="Y107" s="15"/>
     </row>
     <row r="108" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="33">
+      <c r="A108" s="32">
         <v>168037</v>
       </c>
       <c r="B108" s="15" t="s">
@@ -17692,7 +17685,7 @@
       <c r="Y108" s="15"/>
     </row>
     <row r="109" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="33">
+      <c r="A109" s="32">
         <v>333003</v>
       </c>
       <c r="B109" s="15" t="s">
@@ -17749,7 +17742,7 @@
       <c r="Y109" s="15"/>
     </row>
     <row r="110" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="33">
+      <c r="A110" s="32">
         <v>168010</v>
       </c>
       <c r="B110" s="15" t="s">
@@ -17810,7 +17803,7 @@
       <c r="Y110" s="15"/>
     </row>
     <row r="111" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="33">
+      <c r="A111" s="32">
         <v>136049</v>
       </c>
       <c r="B111" s="15" t="s">
@@ -17877,7 +17870,7 @@
       <c r="Y111" s="15"/>
     </row>
     <row r="112" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="33">
+      <c r="A112" s="32">
         <v>135071</v>
       </c>
       <c r="B112" s="15" t="s">
@@ -17938,7 +17931,7 @@
       <c r="Y112" s="15"/>
     </row>
     <row r="113" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="33">
+      <c r="A113" s="32">
         <v>156025</v>
       </c>
       <c r="B113" s="15" t="s">
@@ -17999,7 +17992,7 @@
       <c r="Y113" s="15"/>
     </row>
     <row r="114" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="33">
+      <c r="A114" s="32">
         <v>165027</v>
       </c>
       <c r="B114" s="15" t="s">
@@ -18062,7 +18055,7 @@
       <c r="Y114" s="15"/>
     </row>
     <row r="115" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="33">
+      <c r="A115" s="32">
         <v>169005</v>
       </c>
       <c r="B115" s="15" t="s">
@@ -18123,7 +18116,7 @@
       <c r="Y115" s="15"/>
     </row>
     <row r="116" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="33">
+      <c r="A116" s="32">
         <v>155015</v>
       </c>
       <c r="B116" s="15" t="s">
@@ -18188,7 +18181,7 @@
       <c r="Y116" s="15"/>
     </row>
     <row r="117" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="33">
+      <c r="A117" s="32">
         <v>166025</v>
       </c>
       <c r="B117" s="15" t="s">
@@ -18251,7 +18244,7 @@
       <c r="Y117" s="15"/>
     </row>
     <row r="118" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="33">
+      <c r="A118" s="32">
         <v>167027</v>
       </c>
       <c r="B118" s="15" t="s">
@@ -18308,7 +18301,7 @@
       <c r="Y118" s="15"/>
     </row>
     <row r="119" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="33">
+      <c r="A119" s="32">
         <v>168019</v>
       </c>
       <c r="B119" s="15" t="s">
@@ -18365,7 +18358,7 @@
       <c r="Y119" s="15"/>
     </row>
     <row r="120" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="33">
+      <c r="A120" s="32">
         <v>169011</v>
       </c>
       <c r="B120" s="15" t="s">
@@ -18422,7 +18415,7 @@
       <c r="Y120" s="15"/>
     </row>
     <row r="121" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="33">
+      <c r="A121" s="32">
         <v>139011</v>
       </c>
       <c r="B121" s="15" t="s">
@@ -18479,7 +18472,7 @@
       <c r="Y121" s="15"/>
     </row>
     <row r="122" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="33">
+      <c r="A122" s="32">
         <v>159042</v>
       </c>
       <c r="B122" s="15" t="s">
@@ -18544,7 +18537,7 @@
       <c r="Y122" s="15"/>
     </row>
     <row r="123" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="33">
+      <c r="A123" s="32">
         <v>164024</v>
       </c>
       <c r="B123" s="15" t="s">
@@ -18609,7 +18602,7 @@
       <c r="Y123" s="15"/>
     </row>
     <row r="124" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="33">
+      <c r="A124" s="32">
         <v>166002</v>
       </c>
       <c r="B124" s="15" t="s">
@@ -18672,7 +18665,7 @@
       <c r="Y124" s="15"/>
     </row>
     <row r="125" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="33">
+      <c r="A125" s="32">
         <v>167005</v>
       </c>
       <c r="B125" s="15" t="s">
@@ -18733,7 +18726,7 @@
       <c r="Y125" s="15"/>
     </row>
     <row r="126" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="33">
+      <c r="A126" s="32">
         <v>168021</v>
       </c>
       <c r="B126" s="15" t="s">
@@ -18794,7 +18787,7 @@
       <c r="Y126" s="15"/>
     </row>
     <row r="127" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="33">
+      <c r="A127" s="32">
         <v>168033</v>
       </c>
       <c r="B127" s="15" t="s">
@@ -18851,7 +18844,7 @@
       <c r="Y127" s="15"/>
     </row>
     <row r="128" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="33">
+      <c r="A128" s="32">
         <v>168036</v>
       </c>
       <c r="B128" s="15" t="s">
@@ -18912,7 +18905,7 @@
       <c r="Y128" s="15"/>
     </row>
     <row r="129" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="33">
+      <c r="A129" s="32">
         <v>169018</v>
       </c>
       <c r="B129" s="15" t="s">
@@ -18973,7 +18966,7 @@
       <c r="Y129" s="15"/>
     </row>
     <row r="130" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="33">
+      <c r="A130" s="32">
         <v>161001</v>
       </c>
       <c r="B130" s="15" t="s">
@@ -19038,7 +19031,7 @@
       <c r="Y130" s="15"/>
     </row>
     <row r="131" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="33">
+      <c r="A131" s="32">
         <v>166020</v>
       </c>
       <c r="B131" s="15" t="s">
@@ -19101,7 +19094,7 @@
       <c r="Y131" s="15"/>
     </row>
     <row r="132" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="33">
+      <c r="A132" s="32">
         <v>167017</v>
       </c>
       <c r="B132" s="15" t="s">
@@ -19164,7 +19157,7 @@
       <c r="Y132" s="15"/>
     </row>
     <row r="133" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="33">
+      <c r="A133" s="32">
         <v>168020</v>
       </c>
       <c r="B133" s="15" t="s">
@@ -19225,7 +19218,7 @@
       <c r="Y133" s="15"/>
     </row>
     <row r="134" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="33">
+      <c r="A134" s="32">
         <v>168025</v>
       </c>
       <c r="B134" s="15" t="s">
@@ -19282,7 +19275,7 @@
       <c r="Y134" s="15"/>
     </row>
     <row r="135" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="33">
+      <c r="A135" s="32">
         <v>169010</v>
       </c>
       <c r="B135" s="15" t="s">
@@ -19343,7 +19336,7 @@
       <c r="Y135" s="15"/>
     </row>
     <row r="136" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="33">
+      <c r="A136" s="32">
         <v>154012</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -19404,7 +19397,7 @@
       <c r="Y136" s="15"/>
     </row>
     <row r="137" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="33">
+      <c r="A137" s="32">
         <v>165005</v>
       </c>
       <c r="B137" s="15" t="s">
@@ -19465,7 +19458,7 @@
       <c r="Y137" s="15"/>
     </row>
     <row r="138" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="33">
+      <c r="A138" s="32">
         <v>166019</v>
       </c>
       <c r="B138" s="15" t="s">
@@ -19526,7 +19519,7 @@
       <c r="Y138" s="15"/>
     </row>
     <row r="139" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="33">
+      <c r="A139" s="32">
         <v>168005</v>
       </c>
       <c r="B139" s="15" t="s">
@@ -19583,7 +19576,7 @@
       <c r="Y139" s="15"/>
     </row>
     <row r="140" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="33">
+      <c r="A140" s="32">
         <v>168023</v>
       </c>
       <c r="B140" s="15" t="s">
@@ -19644,7 +19637,7 @@
       <c r="Y140" s="15"/>
     </row>
     <row r="141" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="34">
+      <c r="A141" s="33">
         <v>168039</v>
       </c>
       <c r="B141" s="21" t="s">
@@ -19706,7 +19699,7 @@
       <c r="Z141" s="14"/>
     </row>
     <row r="142" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="33">
+      <c r="A142" s="32">
         <v>168040</v>
       </c>
       <c r="B142" s="15" t="s">
@@ -19767,7 +19760,7 @@
       <c r="Y142" s="15"/>
     </row>
     <row r="143" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="33">
+      <c r="A143" s="32">
         <v>169004</v>
       </c>
       <c r="B143" s="15" t="s">
@@ -19828,7 +19821,7 @@
       <c r="Y143" s="15"/>
     </row>
     <row r="144" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="33">
+      <c r="A144" s="32">
         <v>156026</v>
       </c>
       <c r="B144" s="15" t="s">
@@ -19893,7 +19886,7 @@
       <c r="Y144" s="15"/>
     </row>
     <row r="145" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="33">
+      <c r="A145" s="32">
         <v>166014</v>
       </c>
       <c r="B145" s="15" t="s">
@@ -19956,7 +19949,7 @@
       <c r="Y145" s="15"/>
     </row>
     <row r="146" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="33">
+      <c r="A146" s="32">
         <v>166022</v>
       </c>
       <c r="B146" s="15" t="s">
@@ -20015,7 +20008,7 @@
       <c r="Y146" s="15"/>
     </row>
     <row r="147" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="33">
+      <c r="A147" s="32">
         <v>156031</v>
       </c>
       <c r="B147" s="15" t="s">
@@ -20078,7 +20071,7 @@
       <c r="Y147" s="15"/>
     </row>
     <row r="148" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="33">
+      <c r="A148" s="32">
         <v>161027</v>
       </c>
       <c r="B148" s="15" t="s">
@@ -20145,7 +20138,7 @@
       <c r="Y148" s="15"/>
     </row>
     <row r="149" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="33">
+      <c r="A149" s="32">
         <v>164032</v>
       </c>
       <c r="B149" s="15" t="s">
@@ -20210,7 +20203,7 @@
       <c r="Y149" s="15"/>
     </row>
     <row r="150" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="33">
+      <c r="A150" s="32">
         <v>168008</v>
       </c>
       <c r="B150" s="15" t="s">
@@ -20271,7 +20264,7 @@
       <c r="Y150" s="15"/>
     </row>
     <row r="151" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="33">
+      <c r="A151" s="32">
         <v>146037</v>
       </c>
       <c r="B151" s="15" t="s">
@@ -20332,7 +20325,7 @@
       <c r="Y151" s="15"/>
     </row>
     <row r="152" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="33">
+      <c r="A152" s="32">
         <v>139013</v>
       </c>
       <c r="B152" s="15" t="s">
@@ -20395,7 +20388,7 @@
       <c r="Y152" s="15"/>
     </row>
     <row r="153" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="33">
+      <c r="A153" s="32">
         <v>145015</v>
       </c>
       <c r="B153" s="15" t="s">
@@ -20460,7 +20453,7 @@
       <c r="Y153" s="15"/>
     </row>
     <row r="154" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="33">
+      <c r="A154" s="32">
         <v>161005</v>
       </c>
       <c r="B154" s="15" t="s">
@@ -20523,7 +20516,7 @@
       <c r="Y154" s="15"/>
     </row>
     <row r="155" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="33">
+      <c r="A155" s="32">
         <v>163003</v>
       </c>
       <c r="B155" s="15" t="s">
@@ -20588,7 +20581,7 @@
       <c r="Y155" s="15"/>
     </row>
     <row r="156" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="33">
+      <c r="A156" s="32">
         <v>166024</v>
       </c>
       <c r="B156" s="15" t="s">
@@ -20651,7 +20644,7 @@
       <c r="Y156" s="15"/>
     </row>
     <row r="157" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="33">
+      <c r="A157" s="32">
         <v>167001</v>
       </c>
       <c r="B157" s="15" t="s">
@@ -20714,7 +20707,7 @@
       <c r="Y157" s="15"/>
     </row>
     <row r="158" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="33">
+      <c r="A158" s="32">
         <v>167012</v>
       </c>
       <c r="B158" s="15" t="s">
@@ -20771,7 +20764,7 @@
       <c r="Y158" s="15"/>
     </row>
     <row r="159" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="33">
+      <c r="A159" s="32">
         <v>260001</v>
       </c>
       <c r="B159" s="15" t="s">
@@ -20836,7 +20829,7 @@
       <c r="Y159" s="15"/>
     </row>
     <row r="160" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="33">
+      <c r="A160" s="32">
         <v>267001</v>
       </c>
       <c r="B160" s="15" t="s">
@@ -20899,7 +20892,7 @@
       <c r="Y160" s="15"/>
     </row>
     <row r="161" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="33">
+      <c r="A161" s="32">
         <v>160001</v>
       </c>
       <c r="B161" s="15" t="s">
@@ -20964,7 +20957,7 @@
       <c r="Y161" s="15"/>
     </row>
     <row r="162" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="33">
+      <c r="A162" s="32">
         <v>135095</v>
       </c>
       <c r="B162" s="15" t="s">
@@ -21025,7 +21018,7 @@
       <c r="Y162" s="15"/>
     </row>
     <row r="163" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="33">
+      <c r="A163" s="32">
         <v>159019</v>
       </c>
       <c r="B163" s="15" t="s">
@@ -21086,7 +21079,7 @@
       <c r="Y163" s="15"/>
     </row>
     <row r="164" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="33">
+      <c r="A164" s="32">
         <v>160013</v>
       </c>
       <c r="B164" s="15" t="s">
@@ -21151,7 +21144,7 @@
       <c r="Y164" s="15"/>
     </row>
     <row r="165" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="33">
+      <c r="A165" s="32">
         <v>164008</v>
       </c>
       <c r="B165" s="15" t="s">
@@ -21216,7 +21209,7 @@
       <c r="Y165" s="15"/>
     </row>
     <row r="166" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="33">
+      <c r="A166" s="32">
         <v>165004</v>
       </c>
       <c r="B166" s="15" t="s">
@@ -21279,7 +21272,7 @@
       <c r="Y166" s="15"/>
     </row>
     <row r="167" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="33">
+      <c r="A167" s="32">
         <v>167013</v>
       </c>
       <c r="B167" s="15" t="s">
@@ -21342,7 +21335,7 @@
       <c r="Y167" s="15"/>
     </row>
     <row r="168" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="33">
+      <c r="A168" s="32">
         <v>167020</v>
       </c>
       <c r="B168" s="15" t="s">
@@ -21403,7 +21396,7 @@
       <c r="Y168" s="15"/>
     </row>
     <row r="169" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="33">
+      <c r="A169" s="32">
         <v>167029</v>
       </c>
       <c r="B169" s="15" t="s">
@@ -21464,7 +21457,7 @@
       <c r="Y169" s="15"/>
     </row>
     <row r="170" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="33">
+      <c r="A170" s="32">
         <v>167032</v>
       </c>
       <c r="B170" s="15" t="s">
@@ -21525,7 +21518,7 @@
       <c r="Y170" s="15"/>
     </row>
     <row r="171" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="33">
+      <c r="A171" s="32">
         <v>168006</v>
       </c>
       <c r="B171" s="15" t="s">
@@ -21586,7 +21579,7 @@
       <c r="Y171" s="15"/>
     </row>
     <row r="172" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="33">
+      <c r="A172" s="32">
         <v>168024</v>
       </c>
       <c r="B172" s="15" t="s">
@@ -21647,7 +21640,7 @@
       <c r="Y172" s="15"/>
     </row>
     <row r="173" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="33">
+      <c r="A173" s="32">
         <v>168029</v>
       </c>
       <c r="B173" s="15" t="s">
@@ -21708,7 +21701,7 @@
       <c r="Y173" s="15"/>
     </row>
     <row r="174" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="34">
+      <c r="A174" s="33">
         <v>168030</v>
       </c>
       <c r="B174" s="21" t="s">
@@ -21770,7 +21763,7 @@
       <c r="Z174" s="14"/>
     </row>
     <row r="175" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="33">
+      <c r="A175" s="32">
         <v>169006</v>
       </c>
       <c r="B175" s="15" t="s">
@@ -21831,7 +21824,7 @@
       <c r="Y175" s="15"/>
     </row>
     <row r="176" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="33">
+      <c r="A176" s="32">
         <v>337004</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -21894,7 +21887,7 @@
       <c r="Y176" s="15"/>
     </row>
     <row r="177" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="33">
+      <c r="A177" s="32">
         <v>364002</v>
       </c>
       <c r="B177" s="15" t="s">
@@ -21955,7 +21948,7 @@
       <c r="Y177" s="15"/>
     </row>
     <row r="178" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="33">
+      <c r="A178" s="32">
         <v>168032</v>
       </c>
       <c r="B178" s="15" t="s">
@@ -22016,7 +22009,7 @@
       <c r="Y178" s="15"/>
     </row>
     <row r="179" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="33">
+      <c r="A179" s="32">
         <v>266001</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -22081,7 +22074,7 @@
       <c r="Y179" s="15"/>
     </row>
     <row r="180" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="33">
+      <c r="A180" s="32">
         <v>267085</v>
       </c>
       <c r="B180" s="15" t="s">
@@ -22142,7 +22135,7 @@
       <c r="Y180" s="15"/>
     </row>
     <row r="181" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="33">
+      <c r="A181" s="32">
         <v>268014</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -22203,7 +22196,7 @@
       <c r="Y181" s="15"/>
     </row>
     <row r="182" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="33">
+      <c r="A182" s="32">
         <v>268044</v>
       </c>
       <c r="B182" s="15" t="s">
@@ -22264,7 +22257,7 @@
       <c r="Y182" s="15"/>
     </row>
     <row r="183" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="33">
+      <c r="A183" s="32">
         <v>268047</v>
       </c>
       <c r="B183" s="15" t="s">
@@ -22325,7 +22318,7 @@
       <c r="Y183" s="15"/>
     </row>
     <row r="184" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="33">
+      <c r="A184" s="32">
         <v>368004</v>
       </c>
       <c r="B184" s="15" t="s">
@@ -22386,7 +22379,7 @@
       <c r="Y184" s="15"/>
     </row>
     <row r="185" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="33">
+      <c r="A185" s="32">
         <v>269040</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -22447,7 +22440,7 @@
       <c r="Y185" s="15"/>
     </row>
     <row r="186" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="35" t="s">
+      <c r="A186" s="34" t="s">
         <v>3421</v>
       </c>
       <c r="B186" s="26" t="s">
@@ -22511,7 +22504,7 @@
       <c r="Z186" s="14"/>
     </row>
     <row r="187" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="33">
+      <c r="A187" s="32">
         <v>268029</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -22572,7 +22565,7 @@
       </c>
     </row>
     <row r="188" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="33">
+      <c r="A188" s="32">
         <v>232027</v>
       </c>
       <c r="B188" s="15" t="s">
@@ -22635,7 +22628,7 @@
       <c r="Y188" s="15"/>
     </row>
     <row r="189" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="33">
+      <c r="A189" s="32">
         <v>234092</v>
       </c>
       <c r="B189" s="15" t="s">
@@ -22700,7 +22693,7 @@
       <c r="Y189" s="15"/>
     </row>
     <row r="190" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="33">
+      <c r="A190" s="32">
         <v>240029</v>
       </c>
       <c r="B190" s="15" t="s">
@@ -22765,7 +22758,7 @@
       <c r="Y190" s="15"/>
     </row>
     <row r="191" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="33">
+      <c r="A191" s="32">
         <v>247012</v>
       </c>
       <c r="B191" s="15" t="s">
@@ -22830,7 +22823,7 @@
       <c r="Y191" s="15"/>
     </row>
     <row r="192" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="33">
+      <c r="A192" s="32">
         <v>434007</v>
       </c>
       <c r="B192" s="15" t="s">
@@ -22895,7 +22888,7 @@
       <c r="Y192" s="15"/>
     </row>
     <row r="193" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="33">
+      <c r="A193" s="32">
         <v>435004</v>
       </c>
       <c r="B193" s="15" t="s">
@@ -22960,7 +22953,7 @@
       <c r="Y193" s="15"/>
     </row>
     <row r="194" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="33">
+      <c r="A194" s="32">
         <v>442002</v>
       </c>
       <c r="B194" s="15" t="s">
@@ -23025,7 +23018,7 @@
       <c r="Y194" s="15"/>
     </row>
     <row r="195" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="33">
+      <c r="A195" s="32">
         <v>442007</v>
       </c>
       <c r="B195" s="15" t="s">
@@ -23090,7 +23083,7 @@
       <c r="Y195" s="15"/>
     </row>
     <row r="196" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="33">
+      <c r="A196" s="32">
         <v>256029</v>
       </c>
       <c r="B196" s="15" t="s">
@@ -23153,7 +23146,7 @@
       <c r="Y196" s="15"/>
     </row>
     <row r="197" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="33">
+      <c r="A197" s="32">
         <v>269012</v>
       </c>
       <c r="B197" s="15" t="s">
@@ -23214,7 +23207,7 @@
       <c r="Y197" s="15"/>
     </row>
     <row r="198" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="33">
+      <c r="A198" s="32">
         <v>236012</v>
       </c>
       <c r="B198" s="15" t="s">
@@ -23277,7 +23270,7 @@
       <c r="Y198" s="15"/>
     </row>
     <row r="199" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="33">
+      <c r="A199" s="32">
         <v>240005</v>
       </c>
       <c r="B199" s="15" t="s">
@@ -23342,7 +23335,7 @@
       <c r="Y199" s="15"/>
     </row>
     <row r="200" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="33">
+      <c r="A200" s="32">
         <v>258001</v>
       </c>
       <c r="B200" s="15" t="s">
@@ -23407,7 +23400,7 @@
       <c r="Y200" s="15"/>
     </row>
     <row r="201" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="33">
+      <c r="A201" s="32">
         <v>264090</v>
       </c>
       <c r="B201" s="15" t="s">
@@ -23472,7 +23465,7 @@
       <c r="Y201" s="15"/>
     </row>
     <row r="202" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="33">
+      <c r="A202" s="32">
         <v>264066</v>
       </c>
       <c r="B202" s="15" t="s">
@@ -23537,7 +23530,7 @@
       <c r="Y202" s="15"/>
     </row>
     <row r="203" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="33">
+      <c r="A203" s="32">
         <v>266086</v>
       </c>
       <c r="B203" s="15" t="s">
@@ -23600,7 +23593,7 @@
       <c r="Y203" s="15"/>
     </row>
     <row r="204" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="33">
+      <c r="A204" s="32">
         <v>239024</v>
       </c>
       <c r="B204" s="15" t="s">
@@ -23661,7 +23654,7 @@
       <c r="Y204" s="15"/>
     </row>
     <row r="205" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="33">
+      <c r="A205" s="32">
         <v>269009</v>
       </c>
       <c r="B205" s="15" t="s">
@@ -23720,7 +23713,7 @@
       <c r="Y205" s="15"/>
     </row>
     <row r="206" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="33">
+      <c r="A206" s="32">
         <v>251010</v>
       </c>
       <c r="B206" s="15" t="s">
@@ -23777,7 +23770,7 @@
       <c r="Y206" s="15"/>
     </row>
     <row r="207" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="33">
+      <c r="A207" s="32">
         <v>256050</v>
       </c>
       <c r="B207" s="15" t="s">
@@ -23834,7 +23827,7 @@
       <c r="Y207" s="15"/>
     </row>
     <row r="208" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="33">
+      <c r="A208" s="32">
         <v>256051</v>
       </c>
       <c r="B208" s="15" t="s">
@@ -23891,7 +23884,7 @@
       <c r="Y208" s="15"/>
     </row>
     <row r="209" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="33">
+      <c r="A209" s="32">
         <v>258031</v>
       </c>
       <c r="B209" s="15" t="s">
@@ -23948,7 +23941,7 @@
       <c r="Y209" s="15"/>
     </row>
     <row r="210" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="33">
+      <c r="A210" s="32">
         <v>258041</v>
       </c>
       <c r="B210" s="15" t="s">
@@ -24005,7 +23998,7 @@
       <c r="Y210" s="15"/>
     </row>
     <row r="211" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="33">
+      <c r="A211" s="32">
         <v>264067</v>
       </c>
       <c r="B211" s="15" t="s">
@@ -24060,7 +24053,7 @@
       <c r="Y211" s="15"/>
     </row>
     <row r="212" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="33">
+      <c r="A212" s="32">
         <v>266047</v>
       </c>
       <c r="B212" s="15" t="s">
@@ -24115,7 +24108,7 @@
       <c r="Y212" s="15"/>
     </row>
     <row r="213" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="33">
+      <c r="A213" s="32">
         <v>242029</v>
       </c>
       <c r="B213" s="15" t="s">
@@ -24176,7 +24169,7 @@
       <c r="Y213" s="15"/>
     </row>
     <row r="214" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="33">
+      <c r="A214" s="32">
         <v>245012</v>
       </c>
       <c r="B214" s="15" t="s">
@@ -24237,7 +24230,7 @@
       <c r="Y214" s="15"/>
     </row>
     <row r="215" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="33">
+      <c r="A215" s="32">
         <v>251041</v>
       </c>
       <c r="B215" s="15" t="s">
@@ -24296,7 +24289,7 @@
       <c r="Y215" s="15"/>
     </row>
     <row r="216" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="33">
+      <c r="A216" s="32">
         <v>264070</v>
       </c>
       <c r="B216" s="15" t="s">
@@ -24351,7 +24344,7 @@
       <c r="Y216" s="15"/>
     </row>
     <row r="217" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="33">
+      <c r="A217" s="32">
         <v>266061</v>
       </c>
       <c r="B217" s="15" t="s">
@@ -24408,7 +24401,7 @@
       <c r="Y217" s="15"/>
     </row>
     <row r="218" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="33">
+      <c r="A218" s="32">
         <v>267007</v>
       </c>
       <c r="B218" s="15" t="s">
@@ -24463,7 +24456,7 @@
       <c r="Y218" s="15"/>
     </row>
     <row r="219" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="33">
+      <c r="A219" s="32">
         <v>440018</v>
       </c>
       <c r="B219" s="15" t="s">
@@ -24526,7 +24519,7 @@
       <c r="Y219" s="15"/>
     </row>
     <row r="220" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="33">
+      <c r="A220" s="32">
         <v>251012</v>
       </c>
       <c r="B220" s="15" t="s">
@@ -24585,7 +24578,7 @@
       <c r="Y220" s="15"/>
     </row>
     <row r="221" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="33">
+      <c r="A221" s="32">
         <v>265032</v>
       </c>
       <c r="B221" s="15" t="s">
@@ -24642,7 +24635,7 @@
       <c r="Y221" s="15"/>
     </row>
     <row r="222" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="33">
+      <c r="A222" s="32">
         <v>265053</v>
       </c>
       <c r="B222" s="15" t="s">
@@ -24697,7 +24690,7 @@
       <c r="Y222" s="15"/>
     </row>
     <row r="223" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="33">
+      <c r="A223" s="32">
         <v>268090</v>
       </c>
       <c r="B223" s="15" t="s">
@@ -24756,7 +24749,7 @@
       <c r="Y223" s="15"/>
     </row>
     <row r="224" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="33">
+      <c r="A224" s="32">
         <v>250042</v>
       </c>
       <c r="B224" s="15" t="s">
@@ -24815,7 +24808,7 @@
       <c r="Y224" s="15"/>
     </row>
     <row r="225" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="33">
+      <c r="A225" s="32">
         <v>252013</v>
       </c>
       <c r="B225" s="15" t="s">
@@ -24876,7 +24869,7 @@
       <c r="Y225" s="15"/>
     </row>
     <row r="226" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="33">
+      <c r="A226" s="32">
         <v>253045</v>
       </c>
       <c r="B226" s="15" t="s">
@@ -24935,7 +24928,7 @@
       <c r="Y226" s="15"/>
     </row>
     <row r="227" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="33">
+      <c r="A227" s="32">
         <v>264063</v>
       </c>
       <c r="B227" s="15" t="s">
@@ -24990,7 +24983,7 @@
       <c r="Y227" s="15"/>
     </row>
     <row r="228" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="33">
+      <c r="A228" s="32">
         <v>267008</v>
       </c>
       <c r="B228" s="15" t="s">
@@ -25045,7 +25038,7 @@
       <c r="Y228" s="15"/>
     </row>
     <row r="229" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="33">
+      <c r="A229" s="32">
         <v>438016</v>
       </c>
       <c r="B229" s="15" t="s">
@@ -25106,7 +25099,7 @@
       <c r="Y229" s="15"/>
     </row>
     <row r="230" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="33">
+      <c r="A230" s="32">
         <v>239006</v>
       </c>
       <c r="B230" s="15" t="s">
@@ -25173,7 +25166,7 @@
       <c r="Y230" s="15"/>
     </row>
     <row r="231" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="33">
+      <c r="A231" s="32">
         <v>233034</v>
       </c>
       <c r="B231" s="15" t="s">
@@ -25234,7 +25227,7 @@
       <c r="Y231" s="15"/>
     </row>
     <row r="232" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="33">
+      <c r="A232" s="32">
         <v>240034</v>
       </c>
       <c r="B232" s="15" t="s">
@@ -25299,7 +25292,7 @@
       <c r="Y232" s="15"/>
     </row>
     <row r="233" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="33">
+      <c r="A233" s="32">
         <v>245015</v>
       </c>
       <c r="B233" s="15" t="s">
@@ -25364,7 +25357,7 @@
       <c r="Y233" s="15"/>
     </row>
     <row r="234" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="33">
+      <c r="A234" s="32">
         <v>247008</v>
       </c>
       <c r="B234" s="15" t="s">
@@ -25429,7 +25422,7 @@
       <c r="Y234" s="15"/>
     </row>
     <row r="235" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="33">
+      <c r="A235" s="32">
         <v>249019</v>
       </c>
       <c r="B235" s="15" t="s">
@@ -25494,7 +25487,7 @@
       <c r="Y235" s="15"/>
     </row>
     <row r="236" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="33">
+      <c r="A236" s="32">
         <v>249046</v>
       </c>
       <c r="B236" s="15" t="s">
@@ -25555,7 +25548,7 @@
       <c r="Y236" s="15"/>
     </row>
     <row r="237" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="33">
+      <c r="A237" s="32">
         <v>250016</v>
       </c>
       <c r="B237" s="15" t="s">
@@ -25616,7 +25609,7 @@
       <c r="Y237" s="15"/>
     </row>
     <row r="238" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="33">
+      <c r="A238" s="32">
         <v>250017</v>
       </c>
       <c r="B238" s="15" t="s">
@@ -25679,7 +25672,7 @@
       <c r="Y238" s="15"/>
     </row>
     <row r="239" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="33">
+      <c r="A239" s="32">
         <v>250059</v>
       </c>
       <c r="B239" s="15" t="s">
@@ -25740,7 +25733,7 @@
       <c r="Y239" s="15"/>
     </row>
     <row r="240" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="33">
+      <c r="A240" s="32">
         <v>253003</v>
       </c>
       <c r="B240" s="15" t="s">
@@ -25795,7 +25788,7 @@
       <c r="Y240" s="15"/>
     </row>
     <row r="241" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="33">
+      <c r="A241" s="32">
         <v>254055</v>
       </c>
       <c r="B241" s="15" t="s">
@@ -25858,7 +25851,7 @@
       <c r="Y241" s="15"/>
     </row>
     <row r="242" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="33">
+      <c r="A242" s="32">
         <v>261028</v>
       </c>
       <c r="B242" s="15" t="s">
@@ -25921,7 +25914,7 @@
       <c r="Y242" s="15"/>
     </row>
     <row r="243" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="33">
+      <c r="A243" s="32">
         <v>264007</v>
       </c>
       <c r="B243" s="15" t="s">
@@ -25984,7 +25977,7 @@
       <c r="Y243" s="15"/>
     </row>
     <row r="244" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="33">
+      <c r="A244" s="32">
         <v>265019</v>
       </c>
       <c r="B244" s="15" t="s">
@@ -26049,7 +26042,7 @@
       <c r="Y244" s="15"/>
     </row>
     <row r="245" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="33">
+      <c r="A245" s="32">
         <v>265047</v>
       </c>
       <c r="B245" s="15" t="s">
@@ -26112,7 +26105,7 @@
       <c r="Y245" s="15"/>
     </row>
     <row r="246" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="33">
+      <c r="A246" s="32">
         <v>266010</v>
       </c>
       <c r="B246" s="15" t="s">
@@ -26171,7 +26164,7 @@
       <c r="Y246" s="15"/>
     </row>
     <row r="247" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="33">
+      <c r="A247" s="32">
         <v>266052</v>
       </c>
       <c r="B247" s="15" t="s">
@@ -26230,7 +26223,7 @@
       <c r="Y247" s="15"/>
     </row>
     <row r="248" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="33">
+      <c r="A248" s="32">
         <v>266060</v>
       </c>
       <c r="B248" s="15" t="s">
@@ -26289,7 +26282,7 @@
       <c r="Y248" s="15"/>
     </row>
     <row r="249" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="33">
+      <c r="A249" s="32">
         <v>267047</v>
       </c>
       <c r="B249" s="15" t="s">
@@ -26348,7 +26341,7 @@
       <c r="Y249" s="15"/>
     </row>
     <row r="250" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="33">
+      <c r="A250" s="32">
         <v>268013</v>
       </c>
       <c r="B250" s="15" t="s">
@@ -26409,7 +26402,7 @@
       <c r="Y250" s="15"/>
     </row>
     <row r="251" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="33">
+      <c r="A251" s="32">
         <v>268056</v>
       </c>
       <c r="B251" s="15" t="s">
@@ -26468,7 +26461,7 @@
       <c r="Y251" s="15"/>
     </row>
     <row r="252" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="33">
+      <c r="A252" s="32">
         <v>244005</v>
       </c>
       <c r="B252" s="15" t="s">
@@ -26529,7 +26522,7 @@
       <c r="Y252" s="15"/>
     </row>
     <row r="253" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="33">
+      <c r="A253" s="32">
         <v>259005</v>
       </c>
       <c r="B253" s="15" t="s">
@@ -26590,7 +26583,7 @@
       <c r="Y253" s="15"/>
     </row>
     <row r="254" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="33">
+      <c r="A254" s="32">
         <v>260003</v>
       </c>
       <c r="B254" s="15" t="s">
@@ -26649,7 +26642,7 @@
       <c r="Y254" s="15"/>
     </row>
     <row r="255" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="33">
+      <c r="A255" s="32">
         <v>267003</v>
       </c>
       <c r="B255" s="15" t="s">
@@ -26706,7 +26699,7 @@
       <c r="Y255" s="15"/>
     </row>
     <row r="256" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="33">
+      <c r="A256" s="32">
         <v>268083</v>
       </c>
       <c r="B256" s="15" t="s">
@@ -26767,7 +26760,7 @@
       <c r="Y256" s="15"/>
     </row>
     <row r="257" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="33">
+      <c r="A257" s="32">
         <v>233010</v>
       </c>
       <c r="B257" s="15" t="s">
@@ -26830,7 +26823,7 @@
       <c r="Y257" s="15"/>
     </row>
     <row r="258" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="33">
+      <c r="A258" s="32">
         <v>259013</v>
       </c>
       <c r="B258" s="15" t="s">
@@ -26893,7 +26886,7 @@
       <c r="Y258" s="15"/>
     </row>
     <row r="259" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="33">
+      <c r="A259" s="32">
         <v>268091</v>
       </c>
       <c r="B259" s="15" t="s">
@@ -26952,7 +26945,7 @@
       <c r="Y259" s="15"/>
     </row>
     <row r="260" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="33">
+      <c r="A260" s="32">
         <v>248035</v>
       </c>
       <c r="B260" s="15" t="s">
@@ -27017,7 +27010,7 @@
       <c r="Y260" s="15"/>
     </row>
     <row r="261" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="33">
+      <c r="A261" s="32">
         <v>249010</v>
       </c>
       <c r="B261" s="15" t="s">
@@ -27082,7 +27075,7 @@
       <c r="Y261" s="15"/>
     </row>
     <row r="262" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A262" s="33">
+      <c r="A262" s="32">
         <v>249053</v>
       </c>
       <c r="B262" s="15" t="s">
@@ -27147,7 +27140,7 @@
       <c r="Y262" s="15"/>
     </row>
     <row r="263" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="33">
+      <c r="A263" s="32">
         <v>251019</v>
       </c>
       <c r="B263" s="15" t="s">
@@ -27210,7 +27203,7 @@
       <c r="Y263" s="15"/>
     </row>
     <row r="264" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="33">
+      <c r="A264" s="32">
         <v>252004</v>
       </c>
       <c r="B264" s="15" t="s">
@@ -27275,7 +27268,7 @@
       <c r="Y264" s="15"/>
     </row>
     <row r="265" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="33">
+      <c r="A265" s="32">
         <v>252009</v>
       </c>
       <c r="B265" s="15" t="s">
@@ -27336,7 +27329,7 @@
       <c r="Y265" s="15"/>
     </row>
     <row r="266" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="33">
+      <c r="A266" s="32">
         <v>253037</v>
       </c>
       <c r="B266" s="15" t="s">
@@ -27397,7 +27390,7 @@
       <c r="Y266" s="15"/>
     </row>
     <row r="267" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="33">
+      <c r="A267" s="32">
         <v>254018</v>
       </c>
       <c r="B267" s="15" t="s">
@@ -27456,7 +27449,7 @@
       <c r="Y267" s="15"/>
     </row>
     <row r="268" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="33">
+      <c r="A268" s="32">
         <v>254035</v>
       </c>
       <c r="B268" s="15" t="s">
@@ -27519,7 +27512,7 @@
       <c r="Y268" s="15"/>
     </row>
     <row r="269" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="33">
+      <c r="A269" s="32">
         <v>254049</v>
       </c>
       <c r="B269" s="15" t="s">
@@ -27580,7 +27573,7 @@
       <c r="Y269" s="15"/>
     </row>
     <row r="270" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="33">
+      <c r="A270" s="32">
         <v>256032</v>
       </c>
       <c r="B270" s="15" t="s">
@@ -27643,7 +27636,7 @@
       <c r="Y270" s="15"/>
     </row>
     <row r="271" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="33">
+      <c r="A271" s="32">
         <v>260018</v>
       </c>
       <c r="B271" s="15" t="s">
@@ -27704,7 +27697,7 @@
       <c r="Y271" s="15"/>
     </row>
     <row r="272" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="33">
+      <c r="A272" s="32">
         <v>260045</v>
       </c>
       <c r="B272" s="15" t="s">
@@ -27765,7 +27758,7 @@
       <c r="Y272" s="15"/>
     </row>
     <row r="273" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="33">
+      <c r="A273" s="32">
         <v>264040</v>
       </c>
       <c r="B273" s="15" t="s">
@@ -27826,7 +27819,7 @@
       <c r="Y273" s="15"/>
     </row>
     <row r="274" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="33">
+      <c r="A274" s="32">
         <v>264091</v>
       </c>
       <c r="B274" s="15" t="s">
@@ -27887,7 +27880,7 @@
       <c r="Y274" s="15"/>
     </row>
     <row r="275" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="33">
+      <c r="A275" s="32">
         <v>265012</v>
       </c>
       <c r="B275" s="15" t="s">
@@ -27946,7 +27939,7 @@
       <c r="Y275" s="15"/>
     </row>
     <row r="276" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="33">
+      <c r="A276" s="32">
         <v>265040</v>
       </c>
       <c r="B276" s="15" t="s">
@@ -28005,7 +27998,7 @@
       <c r="Y276" s="15"/>
     </row>
     <row r="277" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="34">
+      <c r="A277" s="33">
         <v>266050</v>
       </c>
       <c r="B277" s="21" t="s">
@@ -28069,7 +28062,7 @@
       <c r="Z277" s="14"/>
     </row>
     <row r="278" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="33">
+      <c r="A278" s="32">
         <v>266072</v>
       </c>
       <c r="B278" s="15" t="s">
@@ -28128,7 +28121,7 @@
       <c r="Y278" s="15"/>
     </row>
     <row r="279" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="33">
+      <c r="A279" s="32">
         <v>267022</v>
       </c>
       <c r="B279" s="15" t="s">
@@ -28187,7 +28180,7 @@
       <c r="Y279" s="15"/>
     </row>
     <row r="280" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="33">
+      <c r="A280" s="32">
         <v>267035</v>
       </c>
       <c r="B280" s="15" t="s">
@@ -28248,7 +28241,7 @@
       <c r="Y280" s="15"/>
     </row>
     <row r="281" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="33">
+      <c r="A281" s="32">
         <v>267074</v>
       </c>
       <c r="B281" s="15" t="s">
@@ -28309,7 +28302,7 @@
       <c r="Y281" s="15"/>
     </row>
     <row r="282" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="33">
+      <c r="A282" s="32">
         <v>267083</v>
       </c>
       <c r="B282" s="15" t="s">
@@ -28368,7 +28361,7 @@
       <c r="Y282" s="15"/>
     </row>
     <row r="283" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="33">
+      <c r="A283" s="32">
         <v>267099</v>
       </c>
       <c r="B283" s="15" t="s">
@@ -28427,7 +28420,7 @@
       <c r="Y283" s="15"/>
     </row>
     <row r="284" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="33">
+      <c r="A284" s="32">
         <v>268012</v>
       </c>
       <c r="B284" s="15" t="s">
@@ -28488,7 +28481,7 @@
       <c r="Y284" s="15"/>
     </row>
     <row r="285" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="33">
+      <c r="A285" s="32">
         <v>268042</v>
       </c>
       <c r="B285" s="15" t="s">
@@ -28547,7 +28540,7 @@
       <c r="Y285" s="15"/>
     </row>
     <row r="286" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="33">
+      <c r="A286" s="32">
         <v>268073</v>
       </c>
       <c r="B286" s="15" t="s">
@@ -28606,7 +28599,7 @@
       <c r="Y286" s="15"/>
     </row>
     <row r="287" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="33">
+      <c r="A287" s="32">
         <v>269011</v>
       </c>
       <c r="B287" s="15" t="s">
@@ -28667,7 +28660,7 @@
       <c r="Y287" s="15"/>
     </row>
     <row r="288" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="33">
+      <c r="A288" s="32">
         <v>269024</v>
       </c>
       <c r="B288" s="15" t="s">
@@ -28726,7 +28719,7 @@
       <c r="Y288" s="15"/>
     </row>
     <row r="289" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="33">
+      <c r="A289" s="32">
         <v>238030</v>
       </c>
       <c r="B289" s="15" t="s">
@@ -28791,7 +28784,7 @@
       <c r="Y289" s="15"/>
     </row>
     <row r="290" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="33">
+      <c r="A290" s="32">
         <v>240018</v>
       </c>
       <c r="B290" s="15" t="s">
@@ -28854,7 +28847,7 @@
       <c r="Y290" s="15"/>
     </row>
     <row r="291" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A291" s="33">
+      <c r="A291" s="32">
         <v>251006</v>
       </c>
       <c r="B291" s="15" t="s">
@@ -28919,7 +28912,7 @@
       <c r="Y291" s="15"/>
     </row>
     <row r="292" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A292" s="33">
+      <c r="A292" s="32">
         <v>251025</v>
       </c>
       <c r="B292" s="15" t="s">
@@ -28982,7 +28975,7 @@
       <c r="Y292" s="15"/>
     </row>
     <row r="293" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A293" s="33">
+      <c r="A293" s="32">
         <v>252027</v>
       </c>
       <c r="B293" s="15" t="s">
@@ -29047,7 +29040,7 @@
       <c r="Y293" s="15"/>
     </row>
     <row r="294" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A294" s="33">
+      <c r="A294" s="32">
         <v>253042</v>
       </c>
       <c r="B294" s="15" t="s">
@@ -29110,7 +29103,7 @@
       <c r="Y294" s="15"/>
     </row>
     <row r="295" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A295" s="33">
+      <c r="A295" s="32">
         <v>256036</v>
       </c>
       <c r="B295" s="15" t="s">
@@ -29171,7 +29164,7 @@
       <c r="Y295" s="15"/>
     </row>
     <row r="296" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A296" s="33">
+      <c r="A296" s="32">
         <v>256038</v>
       </c>
       <c r="B296" s="15" t="s">
@@ -29232,7 +29225,7 @@
       <c r="Y296" s="15"/>
     </row>
     <row r="297" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="33">
+      <c r="A297" s="32">
         <v>266057</v>
       </c>
       <c r="B297" s="15" t="s">
@@ -29295,7 +29288,7 @@
       <c r="Y297" s="15"/>
     </row>
     <row r="298" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A298" s="33">
+      <c r="A298" s="32">
         <v>266065</v>
       </c>
       <c r="B298" s="15" t="s">
@@ -29354,7 +29347,7 @@
       <c r="Y298" s="15"/>
     </row>
     <row r="299" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="33">
+      <c r="A299" s="32">
         <v>246004</v>
       </c>
       <c r="B299" s="15" t="s">
@@ -29421,7 +29414,7 @@
       <c r="Y299" s="15"/>
     </row>
     <row r="300" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A300" s="33">
+      <c r="A300" s="32">
         <v>256014</v>
       </c>
       <c r="B300" s="15" t="s">
@@ -29486,7 +29479,7 @@
       <c r="Y300" s="15"/>
     </row>
     <row r="301" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A301" s="33">
+      <c r="A301" s="32">
         <v>244028</v>
       </c>
       <c r="B301" s="15" t="s">
@@ -29549,7 +29542,7 @@
       <c r="Y301" s="15"/>
     </row>
     <row r="302" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A302" s="33">
+      <c r="A302" s="32">
         <v>251048</v>
       </c>
       <c r="B302" s="15" t="s">
@@ -29612,7 +29605,7 @@
       <c r="Y302" s="15"/>
     </row>
     <row r="303" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A303" s="33">
+      <c r="A303" s="32">
         <v>255003</v>
       </c>
       <c r="B303" s="15" t="s">
@@ -29673,7 +29666,7 @@
       <c r="Y303" s="15"/>
     </row>
     <row r="304" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A304" s="33">
+      <c r="A304" s="32">
         <v>257021</v>
       </c>
       <c r="B304" s="15" t="s">
@@ -29736,7 +29729,7 @@
       <c r="Y304" s="15"/>
     </row>
     <row r="305" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A305" s="33">
+      <c r="A305" s="32">
         <v>258035</v>
       </c>
       <c r="B305" s="15" t="s">
@@ -29797,7 +29790,7 @@
       <c r="Y305" s="15"/>
     </row>
     <row r="306" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A306" s="33">
+      <c r="A306" s="32">
         <v>260029</v>
       </c>
       <c r="B306" s="15" t="s">
@@ -29856,7 +29849,7 @@
       <c r="Y306" s="15"/>
     </row>
     <row r="307" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A307" s="33">
+      <c r="A307" s="32">
         <v>264019</v>
       </c>
       <c r="B307" s="15" t="s">
@@ -29915,7 +29908,7 @@
       <c r="Y307" s="15"/>
     </row>
     <row r="308" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A308" s="33">
+      <c r="A308" s="32">
         <v>264039</v>
       </c>
       <c r="B308" s="15" t="s">
@@ -29976,7 +29969,7 @@
       <c r="Y308" s="15"/>
     </row>
     <row r="309" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A309" s="33">
+      <c r="A309" s="32">
         <v>265043</v>
       </c>
       <c r="B309" s="15" t="s">
@@ -30031,7 +30024,7 @@
       <c r="Y309" s="15"/>
     </row>
     <row r="310" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A310" s="33">
+      <c r="A310" s="32">
         <v>265058</v>
       </c>
       <c r="B310" s="15" t="s">
@@ -30086,7 +30079,7 @@
       <c r="Y310" s="15"/>
     </row>
     <row r="311" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A311" s="33">
+      <c r="A311" s="32">
         <v>267017</v>
       </c>
       <c r="B311" s="15" t="s">
@@ -30141,7 +30134,7 @@
       <c r="Y311" s="15"/>
     </row>
     <row r="312" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A312" s="33">
+      <c r="A312" s="32">
         <v>267080</v>
       </c>
       <c r="B312" s="15" t="s">
@@ -30196,7 +30189,7 @@
       <c r="Y312" s="15"/>
     </row>
     <row r="313" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A313" s="33">
+      <c r="A313" s="32">
         <v>243010</v>
       </c>
       <c r="B313" s="15" t="s">
@@ -30257,7 +30250,7 @@
       <c r="Y313" s="15"/>
     </row>
     <row r="314" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A314" s="33">
+      <c r="A314" s="32">
         <v>255004</v>
       </c>
       <c r="B314" s="15" t="s">
@@ -30318,7 +30311,7 @@
       <c r="Y314" s="15"/>
     </row>
     <row r="315" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A315" s="33">
+      <c r="A315" s="32">
         <v>258022</v>
       </c>
       <c r="B315" s="15" t="s">
@@ -30379,7 +30372,7 @@
       <c r="Y315" s="15"/>
     </row>
     <row r="316" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A316" s="33">
+      <c r="A316" s="32">
         <v>265023</v>
       </c>
       <c r="B316" s="15" t="s">
@@ -30434,7 +30427,7 @@
       <c r="Y316" s="15"/>
     </row>
     <row r="317" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A317" s="33">
+      <c r="A317" s="32">
         <v>267005</v>
       </c>
       <c r="B317" s="15" t="s">
@@ -30489,7 +30482,7 @@
       <c r="Y317" s="15"/>
     </row>
     <row r="318" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A318" s="33">
+      <c r="A318" s="32">
         <v>267060</v>
       </c>
       <c r="B318" s="15" t="s">
@@ -30548,7 +30541,7 @@
       <c r="Y318" s="15"/>
     </row>
     <row r="319" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A319" s="33">
+      <c r="A319" s="32">
         <v>439003</v>
       </c>
       <c r="B319" s="15" t="s">
@@ -30609,7 +30602,7 @@
       <c r="Y319" s="15"/>
     </row>
     <row r="320" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A320" s="33">
+      <c r="A320" s="32">
         <v>244011</v>
       </c>
       <c r="B320" s="15" t="s">
@@ -30670,7 +30663,7 @@
       <c r="Y320" s="15"/>
     </row>
     <row r="321" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A321" s="33">
+      <c r="A321" s="32">
         <v>247019</v>
       </c>
       <c r="B321" s="15" t="s">
@@ -30733,7 +30726,7 @@
       <c r="Y321" s="15"/>
     </row>
     <row r="322" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A322" s="33">
+      <c r="A322" s="32">
         <v>252038</v>
       </c>
       <c r="B322" s="15" t="s">
@@ -30796,7 +30789,7 @@
       <c r="Y322" s="15"/>
     </row>
     <row r="323" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A323" s="33">
+      <c r="A323" s="32">
         <v>259016</v>
       </c>
       <c r="B323" s="15" t="s">
@@ -30857,7 +30850,7 @@
       <c r="Y323" s="15"/>
     </row>
     <row r="324" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A324" s="33">
+      <c r="A324" s="32">
         <v>264044</v>
       </c>
       <c r="B324" s="15" t="s">
@@ -30918,7 +30911,7 @@
       <c r="Y324" s="15"/>
     </row>
     <row r="325" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A325" s="33">
+      <c r="A325" s="32">
         <v>264074</v>
       </c>
       <c r="B325" s="15" t="s">
@@ -30975,7 +30968,7 @@
       <c r="Y325" s="15"/>
     </row>
     <row r="326" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A326" s="33">
+      <c r="A326" s="32">
         <v>264075</v>
       </c>
       <c r="B326" s="15" t="s">
@@ -31032,7 +31025,7 @@
       <c r="Y326" s="15"/>
     </row>
     <row r="327" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A327" s="33">
+      <c r="A327" s="32">
         <v>265110</v>
       </c>
       <c r="B327" s="15" t="s">
@@ -31087,7 +31080,7 @@
       <c r="Y327" s="15"/>
     </row>
     <row r="328" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A328" s="33">
+      <c r="A328" s="32">
         <v>266013</v>
       </c>
       <c r="B328" s="15" t="s">
@@ -31142,7 +31135,7 @@
       <c r="Y328" s="15"/>
     </row>
     <row r="329" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A329" s="33">
+      <c r="A329" s="32">
         <v>267014</v>
       </c>
       <c r="B329" s="15" t="s">
@@ -31197,7 +31190,7 @@
       <c r="Y329" s="15"/>
     </row>
     <row r="330" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A330" s="33">
+      <c r="A330" s="32">
         <v>267015</v>
       </c>
       <c r="B330" s="15" t="s">
@@ -31252,7 +31245,7 @@
       <c r="Y330" s="15"/>
     </row>
     <row r="331" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A331" s="33">
+      <c r="A331" s="32">
         <v>267086</v>
       </c>
       <c r="B331" s="15" t="s">
@@ -31311,7 +31304,7 @@
       <c r="Y331" s="15"/>
     </row>
     <row r="332" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A332" s="33">
+      <c r="A332" s="32">
         <v>268030</v>
       </c>
       <c r="B332" s="15" t="s">
@@ -31370,7 +31363,7 @@
       <c r="Y332" s="15"/>
     </row>
     <row r="333" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A333" s="33">
+      <c r="A333" s="32">
         <v>268031</v>
       </c>
       <c r="B333" s="15" t="s">
@@ -31429,7 +31422,7 @@
       <c r="Y333" s="15"/>
     </row>
     <row r="334" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A334" s="33">
+      <c r="A334" s="32">
         <v>268041</v>
       </c>
       <c r="B334" s="15" t="s">
@@ -31488,7 +31481,7 @@
       <c r="Y334" s="15"/>
     </row>
     <row r="335" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A335" s="33">
+      <c r="A335" s="32">
         <v>257019</v>
       </c>
       <c r="B335" s="15" t="s">
@@ -31549,7 +31542,7 @@
       <c r="Y335" s="15"/>
     </row>
     <row r="336" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A336" s="33">
+      <c r="A336" s="32">
         <v>242025</v>
       </c>
       <c r="B336" s="15" t="s">
@@ -31614,7 +31607,7 @@
       <c r="Y336" s="15"/>
     </row>
     <row r="337" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A337" s="33">
+      <c r="A337" s="32">
         <v>243003</v>
       </c>
       <c r="B337" s="15" t="s">
@@ -31679,7 +31672,7 @@
       <c r="Y337" s="15"/>
     </row>
     <row r="338" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A338" s="33">
+      <c r="A338" s="32">
         <v>247020</v>
       </c>
       <c r="B338" s="15" t="s">
@@ -31740,7 +31733,7 @@
       <c r="Y338" s="15"/>
     </row>
     <row r="339" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A339" s="33">
+      <c r="A339" s="32">
         <v>249094</v>
       </c>
       <c r="B339" s="15" t="s">
@@ -31803,7 +31796,7 @@
       <c r="Y339" s="15"/>
     </row>
     <row r="340" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A340" s="33">
+      <c r="A340" s="32">
         <v>257018</v>
       </c>
       <c r="B340" s="15" t="s">
@@ -31866,7 +31859,7 @@
       <c r="Y340" s="15"/>
     </row>
     <row r="341" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A341" s="33">
+      <c r="A341" s="32">
         <v>259020</v>
       </c>
       <c r="B341" s="15" t="s">
@@ -31927,7 +31920,7 @@
       <c r="Y341" s="15"/>
     </row>
     <row r="342" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A342" s="33">
+      <c r="A342" s="32">
         <v>443003</v>
       </c>
       <c r="B342" s="15" t="s">
@@ -31992,7 +31985,7 @@
       <c r="Y342" s="15"/>
     </row>
     <row r="343" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A343" s="33">
+      <c r="A343" s="32">
         <v>467002</v>
       </c>
       <c r="B343" s="15" t="s">
@@ -32047,7 +32040,7 @@
       <c r="Y343" s="15"/>
     </row>
     <row r="344" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A344" s="33">
+      <c r="A344" s="32">
         <v>467003</v>
       </c>
       <c r="B344" s="15" t="s">
@@ -32102,7 +32095,7 @@
       <c r="Y344" s="15"/>
     </row>
     <row r="345" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A345" s="33">
+      <c r="A345" s="32">
         <v>254057</v>
       </c>
       <c r="B345" s="15" t="s">
@@ -32167,7 +32160,7 @@
       <c r="Y345" s="15"/>
     </row>
     <row r="346" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A346" s="33">
+      <c r="A346" s="32">
         <v>237011</v>
       </c>
       <c r="B346" s="15" t="s">
@@ -32232,7 +32225,7 @@
       <c r="Y346" s="15"/>
     </row>
     <row r="347" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A347" s="33">
+      <c r="A347" s="32">
         <v>249058</v>
       </c>
       <c r="B347" s="15" t="s">
@@ -32293,7 +32286,7 @@
       <c r="Y347" s="15"/>
     </row>
     <row r="348" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A348" s="33">
+      <c r="A348" s="32">
         <v>254037</v>
       </c>
       <c r="B348" s="15" t="s">
@@ -32354,7 +32347,7 @@
       <c r="Y348" s="15"/>
     </row>
     <row r="349" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A349" s="33">
+      <c r="A349" s="32">
         <v>261014</v>
       </c>
       <c r="B349" s="15" t="s">
@@ -32413,7 +32406,7 @@
       <c r="Y349" s="15"/>
     </row>
     <row r="350" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A350" s="33">
+      <c r="A350" s="32">
         <v>265066</v>
       </c>
       <c r="B350" s="15" t="s">
@@ -32472,7 +32465,7 @@
       <c r="Y350" s="15"/>
     </row>
     <row r="351" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A351" s="33">
+      <c r="A351" s="32">
         <v>266031</v>
       </c>
       <c r="B351" s="15" t="s">
@@ -32531,7 +32524,7 @@
       <c r="Y351" s="15"/>
     </row>
     <row r="352" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A352" s="33">
+      <c r="A352" s="32">
         <v>268088</v>
       </c>
       <c r="B352" s="15" t="s">
@@ -32590,7 +32583,7 @@
       <c r="Y352" s="15"/>
     </row>
     <row r="353" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A353" s="33">
+      <c r="A353" s="32">
         <v>236069</v>
       </c>
       <c r="B353" s="15" t="s">
@@ -32653,7 +32646,7 @@
       <c r="Y353" s="15"/>
     </row>
     <row r="354" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A354" s="33">
+      <c r="A354" s="32">
         <v>245001</v>
       </c>
       <c r="B354" s="15" t="s">
@@ -32714,7 +32707,7 @@
       <c r="Y354" s="15"/>
     </row>
     <row r="355" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A355" s="33">
+      <c r="A355" s="32">
         <v>245006</v>
       </c>
       <c r="B355" s="15" t="s">
@@ -32777,7 +32770,7 @@
       <c r="Y355" s="15"/>
     </row>
     <row r="356" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A356" s="33">
+      <c r="A356" s="32">
         <v>248043</v>
       </c>
       <c r="B356" s="15" t="s">
@@ -32838,7 +32831,7 @@
       <c r="Y356" s="15"/>
     </row>
     <row r="357" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A357" s="33">
+      <c r="A357" s="32">
         <v>249036</v>
       </c>
       <c r="B357" s="15" t="s">
@@ -32899,7 +32892,7 @@
       <c r="Y357" s="15"/>
     </row>
     <row r="358" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A358" s="33">
+      <c r="A358" s="32">
         <v>256042</v>
       </c>
       <c r="B358" s="15" t="s">
@@ -32960,7 +32953,7 @@
       <c r="Y358" s="15"/>
     </row>
     <row r="359" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A359" s="33">
+      <c r="A359" s="32">
         <v>264008</v>
       </c>
       <c r="B359" s="15" t="s">
@@ -33023,7 +33016,7 @@
       <c r="Y359" s="15"/>
     </row>
     <row r="360" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A360" s="33">
+      <c r="A360" s="32">
         <v>265103</v>
       </c>
       <c r="B360" s="15" t="s">
@@ -33082,7 +33075,7 @@
       <c r="Y360" s="15"/>
     </row>
     <row r="361" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A361" s="33">
+      <c r="A361" s="32">
         <v>266090</v>
       </c>
       <c r="B361" s="15" t="s">
@@ -33143,7 +33136,7 @@
       <c r="Y361" s="15"/>
     </row>
     <row r="362" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A362" s="33">
+      <c r="A362" s="32">
         <v>268074</v>
       </c>
       <c r="B362" s="15" t="s">
@@ -33204,7 +33197,7 @@
       <c r="Y362" s="15"/>
     </row>
     <row r="363" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A363" s="33">
+      <c r="A363" s="32">
         <v>265128</v>
       </c>
       <c r="B363" s="15" t="s">
@@ -33263,7 +33256,7 @@
       <c r="Y363" s="15"/>
     </row>
     <row r="364" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A364" s="33">
+      <c r="A364" s="32">
         <v>266083</v>
       </c>
       <c r="B364" s="15" t="s">
@@ -33318,7 +33311,7 @@
       <c r="Y364" s="15"/>
     </row>
     <row r="365" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A365" s="33">
+      <c r="A365" s="32">
         <v>267052</v>
       </c>
       <c r="B365" s="15" t="s">
@@ -33373,7 +33366,7 @@
       <c r="Y365" s="15"/>
     </row>
     <row r="366" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A366" s="33">
+      <c r="A366" s="32">
         <v>268028</v>
       </c>
       <c r="B366" s="15" t="s">
@@ -33432,7 +33425,7 @@
       <c r="Y366" s="15"/>
     </row>
     <row r="367" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A367" s="33">
+      <c r="A367" s="32">
         <v>268053</v>
       </c>
       <c r="B367" s="15" t="s">
@@ -33491,7 +33484,7 @@
       <c r="Y367" s="15"/>
     </row>
     <row r="368" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A368" s="33">
+      <c r="A368" s="32">
         <v>268062</v>
       </c>
       <c r="B368" s="15" t="s">
@@ -33550,7 +33543,7 @@
       <c r="Y368" s="15"/>
     </row>
     <row r="369" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A369" s="33">
+      <c r="A369" s="32">
         <v>268076</v>
       </c>
       <c r="B369" s="15" t="s">
@@ -33609,7 +33602,7 @@
       <c r="Y369" s="15"/>
     </row>
     <row r="370" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A370" s="33">
+      <c r="A370" s="32">
         <v>268092</v>
       </c>
       <c r="B370" s="15" t="s">
@@ -33668,7 +33661,7 @@
       <c r="Y370" s="15"/>
     </row>
     <row r="371" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A371" s="33">
+      <c r="A371" s="32">
         <v>269003</v>
       </c>
       <c r="B371" s="15" t="s">
@@ -33727,7 +33720,7 @@
       <c r="Y371" s="15"/>
     </row>
     <row r="372" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A372" s="33">
+      <c r="A372" s="32">
         <v>269006</v>
       </c>
       <c r="B372" s="15" t="s">
@@ -33786,7 +33779,7 @@
       <c r="Y372" s="15"/>
     </row>
     <row r="373" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A373" s="33">
+      <c r="A373" s="32">
         <v>269018</v>
       </c>
       <c r="B373" s="15" t="s">
@@ -33845,7 +33838,7 @@
       <c r="Y373" s="15"/>
     </row>
     <row r="374" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A374" s="33">
+      <c r="A374" s="32">
         <v>269019</v>
       </c>
       <c r="B374" s="15" t="s">
@@ -33904,7 +33897,7 @@
       <c r="Y374" s="15"/>
     </row>
     <row r="375" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A375" s="33">
+      <c r="A375" s="32">
         <v>249086</v>
       </c>
       <c r="B375" s="15" t="s">
@@ -33965,7 +33958,7 @@
       <c r="Y375" s="15"/>
     </row>
     <row r="376" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A376" s="33">
+      <c r="A376" s="32">
         <v>267096</v>
       </c>
       <c r="B376" s="15" t="s">
@@ -34026,7 +34019,7 @@
       <c r="Y376" s="15"/>
     </row>
     <row r="377" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A377" s="33">
+      <c r="A377" s="32">
         <v>250062</v>
       </c>
       <c r="B377" s="15" t="s">
@@ -34091,7 +34084,7 @@
       <c r="Y377" s="15"/>
     </row>
     <row r="378" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A378" s="33">
+      <c r="A378" s="32">
         <v>256015</v>
       </c>
       <c r="B378" s="15" t="s">
@@ -34152,7 +34145,7 @@
       <c r="Y378" s="15"/>
     </row>
     <row r="379" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A379" s="33">
+      <c r="A379" s="32">
         <v>256016</v>
       </c>
       <c r="B379" s="15" t="s">
@@ -34215,7 +34208,7 @@
       <c r="Y379" s="15"/>
     </row>
     <row r="380" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A380" s="33">
+      <c r="A380" s="32">
         <v>259024</v>
       </c>
       <c r="B380" s="15" t="s">
@@ -34278,7 +34271,7 @@
       <c r="Y380" s="15"/>
     </row>
     <row r="381" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A381" s="33">
+      <c r="A381" s="32">
         <v>264045</v>
       </c>
       <c r="B381" s="15" t="s">
@@ -34337,7 +34330,7 @@
       <c r="Y381" s="15"/>
     </row>
     <row r="382" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A382" s="33">
+      <c r="A382" s="32">
         <v>265111</v>
       </c>
       <c r="B382" s="15" t="s">
@@ -34396,7 +34389,7 @@
       <c r="Y382" s="15"/>
     </row>
     <row r="383" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A383" s="33">
+      <c r="A383" s="32">
         <v>265124</v>
       </c>
       <c r="B383" s="15" t="s">
@@ -34455,7 +34448,7 @@
       <c r="Y383" s="15"/>
     </row>
     <row r="384" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A384" s="33">
+      <c r="A384" s="32">
         <v>266030</v>
       </c>
       <c r="B384" s="15" t="s">
@@ -34514,7 +34507,7 @@
       <c r="Y384" s="15"/>
     </row>
     <row r="385" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A385" s="33">
+      <c r="A385" s="32">
         <v>251029</v>
       </c>
       <c r="B385" s="15" t="s">
@@ -34575,7 +34568,7 @@
       <c r="Y385" s="15"/>
     </row>
     <row r="386" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A386" s="33">
+      <c r="A386" s="32">
         <v>256004</v>
       </c>
       <c r="B386" s="15" t="s">
@@ -34636,7 +34629,7 @@
       <c r="Y386" s="15"/>
     </row>
     <row r="387" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A387" s="33">
+      <c r="A387" s="32">
         <v>260016</v>
       </c>
       <c r="B387" s="15" t="s">
@@ -34695,7 +34688,7 @@
       <c r="Y387" s="15"/>
     </row>
     <row r="388" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A388" s="33">
+      <c r="A388" s="32">
         <v>264022</v>
       </c>
       <c r="B388" s="15" t="s">
@@ -34754,7 +34747,7 @@
       <c r="Y388" s="15"/>
     </row>
     <row r="389" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A389" s="33">
+      <c r="A389" s="32">
         <v>264083</v>
       </c>
       <c r="B389" s="15" t="s">
@@ -34817,7 +34810,7 @@
       <c r="Y389" s="15"/>
     </row>
     <row r="390" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A390" s="33">
+      <c r="A390" s="32">
         <v>265010</v>
       </c>
       <c r="B390" s="15" t="s">
@@ -34876,7 +34869,7 @@
       <c r="Y390" s="15"/>
     </row>
     <row r="391" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A391" s="33">
+      <c r="A391" s="32">
         <v>265013</v>
       </c>
       <c r="B391" s="15" t="s">
@@ -34937,7 +34930,7 @@
       <c r="Y391" s="15"/>
     </row>
     <row r="392" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A392" s="33">
+      <c r="A392" s="32">
         <v>268038</v>
       </c>
       <c r="B392" s="15" t="s">
@@ -34996,7 +34989,7 @@
       <c r="Y392" s="15"/>
     </row>
     <row r="393" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A393" s="33">
+      <c r="A393" s="32">
         <v>251050</v>
       </c>
       <c r="B393" s="15" t="s">
@@ -35059,7 +35052,7 @@
       <c r="Y393" s="15"/>
     </row>
     <row r="394" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A394" s="33">
+      <c r="A394" s="32">
         <v>251058</v>
       </c>
       <c r="B394" s="15" t="s">
@@ -35120,7 +35113,7 @@
       <c r="Y394" s="15"/>
     </row>
     <row r="395" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A395" s="33">
+      <c r="A395" s="32">
         <v>251062</v>
       </c>
       <c r="B395" s="15" t="s">
@@ -35181,7 +35174,7 @@
       <c r="Y395" s="15"/>
     </row>
     <row r="396" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A396" s="33">
+      <c r="A396" s="32">
         <v>259022</v>
       </c>
       <c r="B396" s="15" t="s">
@@ -35244,7 +35237,7 @@
       <c r="Y396" s="15"/>
     </row>
     <row r="397" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A397" s="33">
+      <c r="A397" s="32">
         <v>259038</v>
       </c>
       <c r="B397" s="15" t="s">
@@ -35305,7 +35298,7 @@
       <c r="Y397" s="15"/>
     </row>
     <row r="398" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A398" s="33">
+      <c r="A398" s="32">
         <v>264048</v>
       </c>
       <c r="B398" s="15" t="s">
@@ -35364,7 +35357,7 @@
       <c r="Y398" s="15"/>
     </row>
     <row r="399" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A399" s="33">
+      <c r="A399" s="32">
         <v>264051</v>
       </c>
       <c r="B399" s="15" t="s">
@@ -35423,7 +35416,7 @@
       <c r="Y399" s="15"/>
     </row>
     <row r="400" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A400" s="33">
+      <c r="A400" s="32">
         <v>264089</v>
       </c>
       <c r="B400" s="15" t="s">
@@ -35482,7 +35475,7 @@
       <c r="Y400" s="15"/>
     </row>
     <row r="401" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A401" s="33">
+      <c r="A401" s="32">
         <v>265024</v>
       </c>
       <c r="B401" s="15" t="s">
@@ -35541,7 +35534,7 @@
       <c r="Y401" s="15"/>
     </row>
     <row r="402" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A402" s="33">
+      <c r="A402" s="32">
         <v>265061</v>
       </c>
       <c r="B402" s="15" t="s">
@@ -35600,7 +35593,7 @@
       <c r="Y402" s="15"/>
     </row>
     <row r="403" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A403" s="33">
+      <c r="A403" s="32">
         <v>265076</v>
       </c>
       <c r="B403" s="15" t="s">
@@ -35659,7 +35652,7 @@
       <c r="Y403" s="15"/>
     </row>
     <row r="404" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A404" s="33">
+      <c r="A404" s="32">
         <v>266037</v>
       </c>
       <c r="B404" s="15" t="s">
@@ -35718,7 +35711,7 @@
       <c r="Y404" s="15"/>
     </row>
     <row r="405" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A405" s="33">
+      <c r="A405" s="32">
         <v>441005</v>
       </c>
       <c r="B405" s="15" t="s">
@@ -35783,7 +35776,7 @@
       <c r="Y405" s="15"/>
     </row>
     <row r="406" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A406" s="33">
+      <c r="A406" s="32">
         <v>268037</v>
       </c>
       <c r="B406" s="15" t="s">
@@ -35842,7 +35835,7 @@
       <c r="Y406" s="15"/>
     </row>
     <row r="407" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A407" s="33">
+      <c r="A407" s="32">
         <v>268086</v>
       </c>
       <c r="B407" s="15" t="s">
@@ -35901,7 +35894,7 @@
       <c r="Y407" s="15"/>
     </row>
     <row r="408" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A408" s="33">
+      <c r="A408" s="32">
         <v>250022</v>
       </c>
       <c r="B408" s="15" t="s">
@@ -35964,7 +35957,7 @@
       <c r="Y408" s="15"/>
     </row>
     <row r="409" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A409" s="33">
+      <c r="A409" s="32">
         <v>251028</v>
       </c>
       <c r="B409" s="15" t="s">
@@ -36025,7 +36018,7 @@
       <c r="Y409" s="15"/>
     </row>
     <row r="410" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A410" s="33">
+      <c r="A410" s="32">
         <v>253023</v>
       </c>
       <c r="B410" s="15" t="s">
@@ -36086,7 +36079,7 @@
       <c r="Y410" s="15"/>
     </row>
     <row r="411" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A411" s="33">
+      <c r="A411" s="32">
         <v>264084</v>
       </c>
       <c r="B411" s="15" t="s">
@@ -36147,7 +36140,7 @@
       <c r="Y411" s="15"/>
     </row>
     <row r="412" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A412" s="33">
+      <c r="A412" s="32">
         <v>265127</v>
       </c>
       <c r="B412" s="15" t="s">
@@ -36206,7 +36199,7 @@
       <c r="Y412" s="15"/>
     </row>
     <row r="413" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A413" s="33">
+      <c r="A413" s="32">
         <v>266016</v>
       </c>
       <c r="B413" s="15" t="s">
@@ -36265,7 +36258,7 @@
       <c r="Y413" s="15"/>
     </row>
     <row r="414" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A414" s="33">
+      <c r="A414" s="32">
         <v>247007</v>
       </c>
       <c r="B414" s="15" t="s">
@@ -36326,7 +36319,7 @@
       <c r="Y414" s="15"/>
     </row>
     <row r="415" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A415" s="33">
+      <c r="A415" s="32">
         <v>251002</v>
       </c>
       <c r="B415" s="15" t="s">
@@ -36389,7 +36382,7 @@
       <c r="Y415" s="15"/>
     </row>
     <row r="416" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A416" s="33">
+      <c r="A416" s="32">
         <v>251023</v>
       </c>
       <c r="B416" s="15" t="s">
@@ -36450,7 +36443,7 @@
       <c r="Y416" s="15"/>
     </row>
     <row r="417" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A417" s="33">
+      <c r="A417" s="32">
         <v>262008</v>
       </c>
       <c r="B417" s="15" t="s">
@@ -36511,7 +36504,7 @@
       <c r="Y417" s="15"/>
     </row>
     <row r="418" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A418" s="33">
+      <c r="A418" s="32">
         <v>265063</v>
       </c>
       <c r="B418" s="15" t="s">
@@ -36570,7 +36563,7 @@
       <c r="Y418" s="15"/>
     </row>
     <row r="419" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A419" s="33">
+      <c r="A419" s="32">
         <v>266002</v>
       </c>
       <c r="B419" s="15" t="s">
@@ -36629,7 +36622,7 @@
       <c r="Y419" s="15"/>
     </row>
     <row r="420" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A420" s="33">
+      <c r="A420" s="32">
         <v>246013</v>
       </c>
       <c r="B420" s="15" t="s">
@@ -36690,7 +36683,7 @@
       <c r="Y420" s="15"/>
     </row>
     <row r="421" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A421" s="33">
+      <c r="A421" s="32">
         <v>249048</v>
       </c>
       <c r="B421" s="15" t="s">
@@ -36755,7 +36748,7 @@
       <c r="Y421" s="15"/>
     </row>
     <row r="422" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A422" s="33">
+      <c r="A422" s="32">
         <v>250010</v>
       </c>
       <c r="B422" s="15" t="s">
@@ -36816,7 +36809,7 @@
       <c r="Y422" s="15"/>
     </row>
     <row r="423" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A423" s="33">
+      <c r="A423" s="32">
         <v>251065</v>
       </c>
       <c r="B423" s="15" t="s">
@@ -36877,7 +36870,7 @@
       <c r="Y423" s="15"/>
     </row>
     <row r="424" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A424" s="33">
+      <c r="A424" s="32">
         <v>265126</v>
       </c>
       <c r="B424" s="15" t="s">
@@ -36940,7 +36933,7 @@
       <c r="Y424" s="15"/>
     </row>
     <row r="425" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A425" s="33">
+      <c r="A425" s="32">
         <v>267043</v>
       </c>
       <c r="B425" s="15" t="s">
@@ -36999,7 +36992,7 @@
       <c r="Y425" s="15"/>
     </row>
     <row r="426" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A426" s="33">
+      <c r="A426" s="32">
         <v>267072</v>
       </c>
       <c r="B426" s="15" t="s">
@@ -37060,7 +37053,7 @@
       <c r="Y426" s="15"/>
     </row>
     <row r="427" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A427" s="33">
+      <c r="A427" s="32">
         <v>467004</v>
       </c>
       <c r="B427" s="15" t="s">
@@ -37119,7 +37112,7 @@
       <c r="Y427" s="15"/>
     </row>
     <row r="428" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A428" s="33">
+      <c r="A428" s="32">
         <v>467005</v>
       </c>
       <c r="B428" s="15" t="s">
@@ -37178,7 +37171,7 @@
       <c r="Y428" s="15"/>
     </row>
     <row r="429" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A429" s="33">
+      <c r="A429" s="32">
         <v>242032</v>
       </c>
       <c r="B429" s="15" t="s">
@@ -37245,7 +37238,7 @@
       <c r="Y429" s="15"/>
     </row>
     <row r="430" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A430" s="33">
+      <c r="A430" s="32">
         <v>268052</v>
       </c>
       <c r="B430" s="15" t="s">
@@ -37306,7 +37299,7 @@
       <c r="Y430" s="15"/>
     </row>
     <row r="431" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A431" s="33">
+      <c r="A431" s="32">
         <v>269022</v>
       </c>
       <c r="B431" s="15" t="s">
@@ -37367,7 +37360,7 @@
       <c r="Y431" s="15"/>
     </row>
     <row r="432" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A432" s="33">
+      <c r="A432" s="32">
         <v>236082</v>
       </c>
       <c r="B432" s="15" t="s">
@@ -37430,7 +37423,7 @@
       <c r="Y432" s="15"/>
     </row>
     <row r="433" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A433" s="33">
+      <c r="A433" s="32">
         <v>244006</v>
       </c>
       <c r="B433" s="15" t="s">
@@ -37487,7 +37480,7 @@
       <c r="Y433" s="15"/>
     </row>
     <row r="434" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A434" s="33">
+      <c r="A434" s="32">
         <v>251067</v>
       </c>
       <c r="B434" s="15" t="s">
@@ -37550,7 +37543,7 @@
       <c r="Y434" s="15"/>
     </row>
     <row r="435" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A435" s="33">
+      <c r="A435" s="32">
         <v>257014</v>
       </c>
       <c r="B435" s="15" t="s">
@@ -37605,7 +37598,7 @@
       <c r="Y435" s="15"/>
     </row>
     <row r="436" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A436" s="33">
+      <c r="A436" s="32">
         <v>258021</v>
       </c>
       <c r="B436" s="15" t="s">
@@ -37662,7 +37655,7 @@
       <c r="Y436" s="15"/>
     </row>
     <row r="437" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A437" s="33">
+      <c r="A437" s="32">
         <v>265027</v>
       </c>
       <c r="B437" s="15" t="s">
@@ -37719,7 +37712,7 @@
       <c r="Y437" s="15"/>
     </row>
     <row r="438" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A438" s="33">
+      <c r="A438" s="32">
         <v>265039</v>
       </c>
       <c r="B438" s="15" t="s">
@@ -37776,7 +37769,7 @@
       <c r="Y438" s="15"/>
     </row>
     <row r="439" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A439" s="33">
+      <c r="A439" s="32">
         <v>265050</v>
       </c>
       <c r="B439" s="15" t="s">
@@ -37831,7 +37824,7 @@
       <c r="Y439" s="15"/>
     </row>
     <row r="440" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A440" s="33">
+      <c r="A440" s="32">
         <v>265056</v>
       </c>
       <c r="B440" s="15" t="s">
@@ -37888,7 +37881,7 @@
       <c r="Y440" s="15"/>
     </row>
     <row r="441" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A441" s="33">
+      <c r="A441" s="32">
         <v>265089</v>
       </c>
       <c r="B441" s="15" t="s">
@@ -37943,7 +37936,7 @@
       <c r="Y441" s="15"/>
     </row>
     <row r="442" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A442" s="33">
+      <c r="A442" s="32">
         <v>265094</v>
       </c>
       <c r="B442" s="15" t="s">
@@ -38000,7 +37993,7 @@
       <c r="Y442" s="15"/>
     </row>
     <row r="443" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A443" s="33">
+      <c r="A443" s="32">
         <v>265129</v>
       </c>
       <c r="B443" s="15" t="s">
@@ -38057,7 +38050,7 @@
       <c r="Y443" s="15"/>
     </row>
     <row r="444" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A444" s="33">
+      <c r="A444" s="32">
         <v>265133</v>
       </c>
       <c r="B444" s="15" t="s">
@@ -38112,7 +38105,7 @@
       <c r="Y444" s="15"/>
     </row>
     <row r="445" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A445" s="33">
+      <c r="A445" s="32">
         <v>266068</v>
       </c>
       <c r="B445" s="15" t="s">
@@ -38167,7 +38160,7 @@
       <c r="Y445" s="15"/>
     </row>
     <row r="446" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A446" s="33">
+      <c r="A446" s="32">
         <v>267088</v>
       </c>
       <c r="B446" s="15" t="s">
@@ -38222,7 +38215,7 @@
       <c r="Y446" s="15"/>
     </row>
     <row r="447" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A447" s="33">
+      <c r="A447" s="32">
         <v>267104</v>
       </c>
       <c r="B447" s="15" t="s">
@@ -38277,7 +38270,7 @@
       <c r="Y447" s="15"/>
     </row>
     <row r="448" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A448" s="33">
+      <c r="A448" s="32">
         <v>268009</v>
       </c>
       <c r="B448" s="15" t="s">
@@ -38332,7 +38325,7 @@
       <c r="Y448" s="15"/>
     </row>
     <row r="449" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A449" s="33">
+      <c r="A449" s="32">
         <v>268070</v>
       </c>
       <c r="B449" s="15" t="s">
@@ -38391,7 +38384,7 @@
       <c r="Y449" s="15"/>
     </row>
     <row r="450" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A450" s="33">
+      <c r="A450" s="32">
         <v>268087</v>
       </c>
       <c r="B450" s="15" t="s">
@@ -38450,7 +38443,7 @@
       <c r="Y450" s="15"/>
     </row>
     <row r="451" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A451" s="33">
+      <c r="A451" s="32">
         <v>257007</v>
       </c>
       <c r="B451" s="15" t="s">
@@ -38505,7 +38498,7 @@
       <c r="Y451" s="15"/>
     </row>
     <row r="452" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A452" s="33">
+      <c r="A452" s="32">
         <v>257008</v>
       </c>
       <c r="B452" s="15" t="s">
@@ -38560,7 +38553,7 @@
       <c r="Y452" s="15"/>
     </row>
     <row r="453" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A453" s="33">
+      <c r="A453" s="32">
         <v>257009</v>
       </c>
       <c r="B453" s="15" t="s">
@@ -38623,7 +38616,7 @@
       <c r="Y453" s="15"/>
     </row>
     <row r="454" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A454" s="33">
+      <c r="A454" s="32">
         <v>264011</v>
       </c>
       <c r="B454" s="15" t="s">
@@ -38680,7 +38673,7 @@
       <c r="Y454" s="15"/>
     </row>
     <row r="455" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A455" s="33">
+      <c r="A455" s="32">
         <v>268055</v>
       </c>
       <c r="B455" s="15" t="s">
@@ -38739,7 +38732,7 @@
       <c r="Y455" s="15"/>
     </row>
     <row r="456" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A456" s="33">
+      <c r="A456" s="32">
         <v>442009</v>
       </c>
       <c r="B456" s="15" t="s">
@@ -38796,7 +38789,7 @@
       <c r="Y456" s="15"/>
     </row>
     <row r="457" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A457" s="33">
+      <c r="A457" s="32">
         <v>239036</v>
       </c>
       <c r="B457" s="15" t="s">
@@ -38859,7 +38852,7 @@
       <c r="Y457" s="15"/>
     </row>
     <row r="458" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A458" s="33">
+      <c r="A458" s="32">
         <v>245007</v>
       </c>
       <c r="B458" s="15" t="s">
@@ -38916,7 +38909,7 @@
       <c r="Y458" s="15"/>
     </row>
     <row r="459" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A459" s="33">
+      <c r="A459" s="32">
         <v>245028</v>
       </c>
       <c r="B459" s="15" t="s">
@@ -38973,7 +38966,7 @@
       <c r="Y459" s="15"/>
     </row>
     <row r="460" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A460" s="33">
+      <c r="A460" s="32">
         <v>245029</v>
       </c>
       <c r="B460" s="15" t="s">
@@ -39030,7 +39023,7 @@
       <c r="Y460" s="15"/>
     </row>
     <row r="461" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A461" s="33">
+      <c r="A461" s="32">
         <v>249026</v>
       </c>
       <c r="B461" s="15" t="s">
@@ -39087,7 +39080,7 @@
       <c r="Y461" s="15"/>
     </row>
     <row r="462" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A462" s="33">
+      <c r="A462" s="32">
         <v>251015</v>
       </c>
       <c r="B462" s="15" t="s">
@@ -39146,7 +39139,7 @@
       <c r="Y462" s="15"/>
     </row>
     <row r="463" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A463" s="33">
+      <c r="A463" s="32">
         <v>251020</v>
       </c>
       <c r="B463" s="15" t="s">
@@ -39205,7 +39198,7 @@
       <c r="Y463" s="15"/>
     </row>
     <row r="464" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A464" s="33">
+      <c r="A464" s="32">
         <v>253009</v>
       </c>
       <c r="B464" s="15" t="s">
@@ -39262,7 +39255,7 @@
       <c r="Y464" s="15"/>
     </row>
     <row r="465" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A465" s="33">
+      <c r="A465" s="32">
         <v>254024</v>
       </c>
       <c r="B465" s="15" t="s">
@@ -39317,7 +39310,7 @@
       <c r="Y465" s="15"/>
     </row>
     <row r="466" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A466" s="33">
+      <c r="A466" s="32">
         <v>256056</v>
       </c>
       <c r="B466" s="15" t="s">
@@ -39378,7 +39371,7 @@
       <c r="Y466" s="15"/>
     </row>
     <row r="467" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A467" s="33">
+      <c r="A467" s="32">
         <v>257015</v>
       </c>
       <c r="B467" s="15" t="s">
@@ -39433,7 +39426,7 @@
       <c r="Y467" s="15"/>
     </row>
     <row r="468" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A468" s="33">
+      <c r="A468" s="32">
         <v>257035</v>
       </c>
       <c r="B468" s="15" t="s">
@@ -39490,7 +39483,7 @@
       <c r="Y468" s="15"/>
     </row>
     <row r="469" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A469" s="33">
+      <c r="A469" s="32">
         <v>258004</v>
       </c>
       <c r="B469" s="15" t="s">
@@ -39551,7 +39544,7 @@
       <c r="Y469" s="15"/>
     </row>
     <row r="470" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A470" s="33">
+      <c r="A470" s="32">
         <v>260024</v>
       </c>
       <c r="B470" s="15" t="s">
@@ -39606,7 +39599,7 @@
       <c r="Y470" s="15"/>
     </row>
     <row r="471" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A471" s="33">
+      <c r="A471" s="32">
         <v>260038</v>
       </c>
       <c r="B471" s="15" t="s">
@@ -39665,7 +39658,7 @@
       <c r="Y471" s="15"/>
     </row>
     <row r="472" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A472" s="33">
+      <c r="A472" s="32">
         <v>264025</v>
       </c>
       <c r="B472" s="15" t="s">
@@ -39720,7 +39713,7 @@
       <c r="Y472" s="15"/>
     </row>
     <row r="473" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A473" s="33">
+      <c r="A473" s="32">
         <v>265099</v>
       </c>
       <c r="B473" s="15" t="s">
@@ -39775,7 +39768,7 @@
       <c r="Y473" s="15"/>
     </row>
     <row r="474" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A474" s="33">
+      <c r="A474" s="32">
         <v>269004</v>
       </c>
       <c r="B474" s="15" t="s">
@@ -39834,7 +39827,7 @@
       <c r="Y474" s="15"/>
     </row>
     <row r="475" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A475" s="33">
+      <c r="A475" s="32">
         <v>253014</v>
       </c>
       <c r="B475" s="15" t="s">
@@ -39899,7 +39892,7 @@
       <c r="Y475" s="15"/>
     </row>
     <row r="476" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A476" s="33">
+      <c r="A476" s="32">
         <v>237017</v>
       </c>
       <c r="B476" s="15" t="s">
@@ -39962,7 +39955,7 @@
       <c r="Y476" s="15"/>
     </row>
     <row r="477" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A477" s="33">
+      <c r="A477" s="32">
         <v>241015</v>
       </c>
       <c r="B477" s="15" t="s">
@@ -40025,7 +40018,7 @@
       <c r="Y477" s="15"/>
     </row>
     <row r="478" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A478" s="33">
+      <c r="A478" s="32">
         <v>250056</v>
       </c>
       <c r="B478" s="15" t="s">
@@ -40088,7 +40081,7 @@
       <c r="Y478" s="15"/>
     </row>
     <row r="479" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A479" s="33">
+      <c r="A479" s="32">
         <v>254061</v>
       </c>
       <c r="B479" s="15" t="s">
@@ -40147,7 +40140,7 @@
       <c r="Y479" s="15"/>
     </row>
     <row r="480" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A480" s="33">
+      <c r="A480" s="32">
         <v>260041</v>
       </c>
       <c r="B480" s="15" t="s">
@@ -40210,7 +40203,7 @@
       <c r="Y480" s="15"/>
     </row>
     <row r="481" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A481" s="33">
+      <c r="A481" s="32">
         <v>242017</v>
       </c>
       <c r="B481" s="15" t="s">
@@ -40269,7 +40262,7 @@
       <c r="Y481" s="15"/>
     </row>
     <row r="482" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A482" s="33">
+      <c r="A482" s="32">
         <v>246006</v>
       </c>
       <c r="B482" s="15" t="s">
@@ -40332,7 +40325,7 @@
       <c r="Y482" s="15"/>
     </row>
     <row r="483" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A483" s="33">
+      <c r="A483" s="32">
         <v>246010</v>
       </c>
       <c r="B483" s="15" t="s">
@@ -40395,7 +40388,7 @@
       <c r="Y483" s="15"/>
     </row>
     <row r="484" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A484" s="33">
+      <c r="A484" s="32">
         <v>248013</v>
       </c>
       <c r="B484" s="15" t="s">
@@ -40458,7 +40451,7 @@
       <c r="Y484" s="15"/>
     </row>
     <row r="485" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A485" s="33">
+      <c r="A485" s="32">
         <v>248039</v>
       </c>
       <c r="B485" s="15" t="s">
@@ -40517,7 +40510,7 @@
       <c r="Y485" s="15"/>
     </row>
     <row r="486" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A486" s="33">
+      <c r="A486" s="32">
         <v>256067</v>
       </c>
       <c r="B486" s="15" t="s">
@@ -40580,7 +40573,7 @@
       <c r="Y486" s="15"/>
     </row>
     <row r="487" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A487" s="33">
+      <c r="A487" s="32">
         <v>260048</v>
       </c>
       <c r="B487" s="15" t="s">
@@ -40641,7 +40634,7 @@
       <c r="Y487" s="15"/>
     </row>
     <row r="488" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A488" s="33">
+      <c r="A488" s="32">
         <v>261005</v>
       </c>
       <c r="B488" s="15" t="s">
@@ -40702,7 +40695,7 @@
       <c r="Y488" s="15"/>
     </row>
     <row r="489" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A489" s="33">
+      <c r="A489" s="32">
         <v>261037</v>
       </c>
       <c r="B489" s="15" t="s">
@@ -40767,7 +40760,7 @@
       <c r="Y489" s="15"/>
     </row>
     <row r="490" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A490" s="33">
+      <c r="A490" s="32">
         <v>267018</v>
       </c>
       <c r="B490" s="15" t="s">
@@ -40826,7 +40819,7 @@
       <c r="Y490" s="15"/>
     </row>
     <row r="491" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A491" s="33">
+      <c r="A491" s="32">
         <v>268045</v>
       </c>
       <c r="B491" s="15" t="s">
@@ -40885,7 +40878,7 @@
       <c r="Y491" s="15"/>
     </row>
     <row r="492" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A492" s="33">
+      <c r="A492" s="32">
         <v>248031</v>
       </c>
       <c r="B492" s="15" t="s">
@@ -40950,7 +40943,7 @@
       <c r="Y492" s="15"/>
     </row>
     <row r="493" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A493" s="33">
+      <c r="A493" s="32">
         <v>268020</v>
       </c>
       <c r="B493" s="15" t="s">
@@ -41011,7 +41004,7 @@
       <c r="Y493" s="15"/>
     </row>
     <row r="494" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A494" s="33">
+      <c r="A494" s="32">
         <v>268077</v>
       </c>
       <c r="B494" s="15" t="s">
@@ -41072,7 +41065,7 @@
       <c r="Y494" s="15"/>
     </row>
     <row r="495" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A495" s="33">
+      <c r="A495" s="32">
         <v>233025</v>
       </c>
       <c r="B495" s="15" t="s">
@@ -41135,7 +41128,7 @@
       <c r="Y495" s="15"/>
     </row>
     <row r="496" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A496" s="33">
+      <c r="A496" s="32">
         <v>265132</v>
       </c>
       <c r="B496" s="15" t="s">
@@ -41198,7 +41191,7 @@
       <c r="Y496" s="15"/>
     </row>
     <row r="497" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A497" s="33">
+      <c r="A497" s="32">
         <v>266048</v>
       </c>
       <c r="B497" s="15" t="s">
@@ -41259,7 +41252,7 @@
       <c r="Y497" s="15"/>
     </row>
     <row r="498" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A498" s="33">
+      <c r="A498" s="32">
         <v>266088</v>
       </c>
       <c r="B498" s="15" t="s">
@@ -41316,7 +41309,7 @@
       <c r="Y498" s="15"/>
     </row>
     <row r="499" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A499" s="33">
+      <c r="A499" s="32">
         <v>469002</v>
       </c>
       <c r="B499" s="15" t="s">
@@ -41377,7 +41370,7 @@
       <c r="Y499" s="15"/>
     </row>
     <row r="500" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A500" s="33">
+      <c r="A500" s="32">
         <v>268007</v>
       </c>
       <c r="B500" s="15" t="s">
@@ -41436,7 +41429,7 @@
       <c r="Y500" s="15"/>
     </row>
     <row r="501" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A501" s="33">
+      <c r="A501" s="32">
         <v>251007</v>
       </c>
       <c r="B501" s="15" t="s">
@@ -41501,7 +41494,7 @@
       <c r="Y501" s="15"/>
     </row>
     <row r="502" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A502" s="33">
+      <c r="A502" s="32">
         <v>268048</v>
       </c>
       <c r="B502" s="15" t="s">
@@ -41562,7 +41555,7 @@
       <c r="Y502" s="15"/>
     </row>
     <row r="503" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A503" s="33">
+      <c r="A503" s="32">
         <v>252001</v>
       </c>
       <c r="B503" s="15" t="s">
@@ -41627,7 +41620,7 @@
       <c r="Y503" s="15"/>
     </row>
     <row r="504" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A504" s="33">
+      <c r="A504" s="32">
         <v>264071</v>
       </c>
       <c r="B504" s="15" t="s">
@@ -41684,7 +41677,7 @@
       <c r="Y504" s="15"/>
     </row>
     <row r="505" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A505" s="33">
+      <c r="A505" s="32">
         <v>264088</v>
       </c>
       <c r="B505" s="15" t="s">
@@ -41745,7 +41738,7 @@
       <c r="Y505" s="15"/>
     </row>
     <row r="506" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A506" s="33">
+      <c r="A506" s="32">
         <v>268002</v>
       </c>
       <c r="B506" s="15" t="s">
@@ -41806,7 +41799,7 @@
       <c r="Y506" s="15"/>
     </row>
     <row r="507" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A507" s="33">
+      <c r="A507" s="32">
         <v>232015</v>
       </c>
       <c r="B507" s="15" t="s">
@@ -41863,7 +41856,7 @@
       <c r="Y507" s="15"/>
     </row>
     <row r="508" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A508" s="33">
+      <c r="A508" s="32">
         <v>237068</v>
       </c>
       <c r="B508" s="15" t="s">
@@ -41922,7 +41915,7 @@
       <c r="Y508" s="15"/>
     </row>
     <row r="509" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A509" s="33">
+      <c r="A509" s="32">
         <v>242012</v>
       </c>
       <c r="B509" s="15" t="s">
@@ -41987,7 +41980,7 @@
       <c r="Y509" s="15"/>
     </row>
     <row r="510" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A510" s="33">
+      <c r="A510" s="32">
         <v>250054</v>
       </c>
       <c r="B510" s="15" t="s">
@@ -42044,7 +42037,7 @@
       <c r="Y510" s="15"/>
     </row>
     <row r="511" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A511" s="33">
+      <c r="A511" s="32">
         <v>254002</v>
       </c>
       <c r="B511" s="15" t="s">
@@ -42101,7 +42094,7 @@
       <c r="Y511" s="15"/>
     </row>
     <row r="512" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A512" s="33">
+      <c r="A512" s="32">
         <v>254004</v>
       </c>
       <c r="B512" s="15" t="s">
@@ -42160,7 +42153,7 @@
       <c r="Y512" s="15"/>
     </row>
     <row r="513" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A513" s="33">
+      <c r="A513" s="32">
         <v>254044</v>
       </c>
       <c r="B513" s="15" t="s">
@@ -42219,7 +42212,7 @@
       <c r="Y513" s="15"/>
     </row>
     <row r="514" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A514" s="33">
+      <c r="A514" s="32">
         <v>258032</v>
       </c>
       <c r="B514" s="15" t="s">
@@ -42278,7 +42271,7 @@
       <c r="Y514" s="15"/>
     </row>
     <row r="515" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A515" s="33">
+      <c r="A515" s="32">
         <v>265054</v>
       </c>
       <c r="B515" s="15" t="s">
@@ -42341,7 +42334,7 @@
       <c r="Y515" s="15"/>
     </row>
     <row r="516" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A516" s="33">
+      <c r="A516" s="32">
         <v>265086</v>
       </c>
       <c r="B516" s="15" t="s">
@@ -42396,7 +42389,7 @@
       <c r="Y516" s="15"/>
     </row>
     <row r="517" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A517" s="33">
+      <c r="A517" s="32">
         <v>266062</v>
       </c>
       <c r="B517" s="15" t="s">
@@ -42451,7 +42444,7 @@
       <c r="Y517" s="15"/>
     </row>
     <row r="518" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A518" s="33">
+      <c r="A518" s="32">
         <v>266077</v>
       </c>
       <c r="B518" s="15" t="s">
@@ -42512,7 +42505,7 @@
       <c r="Y518" s="15"/>
     </row>
     <row r="519" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A519" s="33">
+      <c r="A519" s="32">
         <v>269017</v>
       </c>
       <c r="B519" s="15" t="s">
@@ -42571,7 +42564,7 @@
       <c r="Y519" s="15"/>
     </row>
     <row r="520" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A520" s="33">
+      <c r="A520" s="32">
         <v>235118</v>
       </c>
       <c r="B520" s="15" t="s">
@@ -42628,7 +42621,7 @@
       <c r="Y520" s="15"/>
     </row>
     <row r="521" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A521" s="33">
+      <c r="A521" s="32">
         <v>268063</v>
       </c>
       <c r="B521" s="15" t="s">
@@ -42687,7 +42680,7 @@
       <c r="Y521" s="15"/>
     </row>
     <row r="522" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A522" s="33">
+      <c r="A522" s="32">
         <v>268084</v>
       </c>
       <c r="B522" s="15" t="s">
@@ -42748,7 +42741,7 @@
       <c r="Y522" s="15"/>
     </row>
     <row r="523" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A523" s="33">
+      <c r="A523" s="32">
         <v>469001</v>
       </c>
       <c r="B523" s="15" t="s">
@@ -42805,7 +42798,7 @@
       <c r="Y523" s="15"/>
     </row>
     <row r="524" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A524" s="33">
+      <c r="A524" s="32">
         <v>149024</v>
       </c>
       <c r="B524" s="15" t="s">
@@ -42872,7 +42865,7 @@
       <c r="Y524" s="15"/>
     </row>
     <row r="525" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A525" s="33">
+      <c r="A525" s="32">
         <v>146029</v>
       </c>
       <c r="B525" s="15" t="s">
@@ -42937,7 +42930,7 @@
       <c r="Y525" s="15"/>
     </row>
     <row r="526" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A526" s="33">
+      <c r="A526" s="32">
         <v>233027</v>
       </c>
       <c r="B526" s="15" t="s">
@@ -43000,7 +42993,7 @@
       <c r="Y526" s="15"/>
     </row>
     <row r="527" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A527" s="33">
+      <c r="A527" s="32">
         <v>257037</v>
       </c>
       <c r="B527" s="15" t="s">
@@ -43061,7 +43054,7 @@
       <c r="Y527" s="15"/>
     </row>
     <row r="528" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A528" s="33">
+      <c r="A528" s="32">
         <v>257039</v>
       </c>
       <c r="B528" s="15" t="s">
@@ -43126,7 +43119,7 @@
       <c r="Y528" s="15"/>
     </row>
     <row r="529" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A529" s="33">
+      <c r="A529" s="32">
         <v>260050</v>
       </c>
       <c r="B529" s="15" t="s">
@@ -43189,7 +43182,7 @@
       <c r="Y529" s="15"/>
     </row>
     <row r="530" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A530" s="33">
+      <c r="A530" s="32">
         <v>266035</v>
       </c>
       <c r="B530" s="15" t="s">
@@ -43252,7 +43245,7 @@
       <c r="Y530" s="15"/>
     </row>
     <row r="531" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A531" s="33">
+      <c r="A531" s="32">
         <v>267032</v>
       </c>
       <c r="B531" s="15" t="s">
@@ -43313,7 +43306,7 @@
       <c r="Y531" s="15"/>
     </row>
     <row r="532" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A532" s="33">
+      <c r="A532" s="32">
         <v>269010</v>
       </c>
       <c r="B532" s="15" t="s">
@@ -43374,7 +43367,7 @@
       <c r="Y532" s="15"/>
     </row>
     <row r="533" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A533" s="33">
+      <c r="A533" s="32">
         <v>233060</v>
       </c>
       <c r="B533" s="15" t="s">
@@ -43431,7 +43424,7 @@
       <c r="Y533" s="15"/>
     </row>
     <row r="534" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A534" s="33">
+      <c r="A534" s="32">
         <v>244023</v>
       </c>
       <c r="B534" s="15" t="s">
@@ -43496,7 +43489,7 @@
       <c r="Y534" s="15"/>
     </row>
     <row r="535" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A535" s="33">
+      <c r="A535" s="32">
         <v>256001</v>
       </c>
       <c r="B535" s="15" t="s">
@@ -43555,7 +43548,7 @@
       <c r="Y535" s="15"/>
     </row>
     <row r="536" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A536" s="33">
+      <c r="A536" s="32">
         <v>265037</v>
       </c>
       <c r="B536" s="15" t="s">
@@ -43618,7 +43611,7 @@
       <c r="Y536" s="15"/>
     </row>
     <row r="537" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A537" s="33">
+      <c r="A537" s="32">
         <v>266004</v>
       </c>
       <c r="B537" s="15" t="s">
@@ -43681,7 +43674,7 @@
       <c r="Y537" s="15"/>
     </row>
     <row r="538" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A538" s="33">
+      <c r="A538" s="32">
         <v>266082</v>
       </c>
       <c r="B538" s="15" t="s">
@@ -43744,7 +43737,7 @@
       <c r="Y538" s="15"/>
     </row>
     <row r="539" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A539" s="33">
+      <c r="A539" s="32">
         <v>166006</v>
       </c>
       <c r="B539" s="15" t="s">
@@ -43805,7 +43798,7 @@
       </c>
     </row>
     <row r="540" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A540" s="33">
+      <c r="A540" s="32">
         <v>169012</v>
       </c>
       <c r="B540" s="15" t="s">
@@ -43862,7 +43855,7 @@
       <c r="Y540" s="15"/>
     </row>
     <row r="541" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A541" s="33">
+      <c r="A541" s="32">
         <v>241009</v>
       </c>
       <c r="B541" s="15" t="s">
@@ -43923,7 +43916,7 @@
       <c r="Y541" s="15"/>
     </row>
     <row r="542" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A542" s="33">
+      <c r="A542" s="32">
         <v>147029</v>
       </c>
       <c r="B542" s="15" t="s">
@@ -43982,7 +43975,7 @@
       <c r="Y542" s="15"/>
     </row>
     <row r="543" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A543" s="33">
+      <c r="A543" s="32">
         <v>149039</v>
       </c>
       <c r="B543" s="15" t="s">
@@ -44043,7 +44036,7 @@
       <c r="Y543" s="15"/>
     </row>
     <row r="544" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A544" s="33">
+      <c r="A544" s="32">
         <v>151015</v>
       </c>
       <c r="B544" s="15" t="s">
@@ -44108,7 +44101,7 @@
       <c r="Y544" s="15"/>
     </row>
     <row r="545" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A545" s="33">
+      <c r="A545" s="32">
         <v>160004</v>
       </c>
       <c r="B545" s="15" t="s">
@@ -44169,7 +44162,7 @@
       <c r="Y545" s="15"/>
     </row>
     <row r="546" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A546" s="33">
+      <c r="A546" s="32">
         <v>161010</v>
       </c>
       <c r="B546" s="15" t="s">
@@ -44230,7 +44223,7 @@
       <c r="Y546" s="15"/>
     </row>
     <row r="547" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A547" s="33">
+      <c r="A547" s="32">
         <v>166026</v>
       </c>
       <c r="B547" s="15" t="s">
@@ -44289,7 +44282,7 @@
       <c r="Y547" s="15"/>
     </row>
     <row r="548" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A548" s="33">
+      <c r="A548" s="32">
         <v>166034</v>
       </c>
       <c r="B548" s="15" t="s">
@@ -44346,7 +44339,7 @@
       <c r="Y548" s="15"/>
     </row>
     <row r="549" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A549" s="33">
+      <c r="A549" s="32">
         <v>167009</v>
       </c>
       <c r="B549" s="15" t="s">
@@ -44403,7 +44396,7 @@
       <c r="Y549" s="15"/>
     </row>
     <row r="550" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A550" s="33">
+      <c r="A550" s="32">
         <v>136028</v>
       </c>
       <c r="B550" s="15" t="s">
@@ -44462,7 +44455,7 @@
       <c r="Y550" s="15"/>
     </row>
     <row r="551" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A551" s="33">
+      <c r="A551" s="32">
         <v>150029</v>
       </c>
       <c r="B551" s="15" t="s">
@@ -44523,7 +44516,7 @@
       <c r="Y551" s="15"/>
     </row>
     <row r="552" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A552" s="33">
+      <c r="A552" s="32">
         <v>245017</v>
       </c>
       <c r="B552" s="15" t="s">
@@ -44588,7 +44581,7 @@
       <c r="Y552" s="15"/>
     </row>
     <row r="553" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A553" s="33">
+      <c r="A553" s="32">
         <v>368001</v>
       </c>
       <c r="B553" s="15" t="s">
@@ -44651,7 +44644,7 @@
       <c r="Y553" s="15"/>
     </row>
     <row r="554" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A554" s="33">
+      <c r="A554" s="32">
         <v>148005</v>
       </c>
       <c r="B554" s="15" t="s">
@@ -44718,7 +44711,7 @@
       <c r="Y554" s="15"/>
     </row>
     <row r="555" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A555" s="33">
+      <c r="A555" s="32">
         <v>168003</v>
       </c>
       <c r="B555" s="15" t="s">
@@ -44779,7 +44772,7 @@
       <c r="Y555" s="15"/>
     </row>
     <row r="556" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A556" s="33">
+      <c r="A556" s="32">
         <v>169014</v>
       </c>
       <c r="B556" s="15" t="s">
@@ -44840,7 +44833,7 @@
       <c r="Y556" s="15"/>
     </row>
     <row r="557" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A557" s="33">
+      <c r="A557" s="32">
         <v>158053</v>
       </c>
       <c r="B557" s="15" t="s">
@@ -44905,7 +44898,7 @@
       <c r="Y557" s="15"/>
     </row>
     <row r="558" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A558" s="33">
+      <c r="A558" s="32">
         <v>166018</v>
       </c>
       <c r="B558" s="15" t="s">
@@ -44962,7 +44955,7 @@
       <c r="Y558" s="15"/>
     </row>
     <row r="559" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A559" s="33">
+      <c r="A559" s="32">
         <v>167010</v>
       </c>
       <c r="B559" s="15" t="s">
@@ -45023,7 +45016,7 @@
       <c r="Y559" s="15"/>
     </row>
     <row r="560" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A560" s="33">
+      <c r="A560" s="32">
         <v>169019</v>
       </c>
       <c r="B560" s="15" t="s">
@@ -45084,7 +45077,7 @@
       <c r="Y560" s="15"/>
     </row>
     <row r="561" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A561" s="33">
+      <c r="A561" s="32">
         <v>167007</v>
       </c>
       <c r="B561" s="15" t="s">
@@ -45147,7 +45140,7 @@
       <c r="Y561" s="15"/>
     </row>
     <row r="562" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A562" s="33">
+      <c r="A562" s="32">
         <v>169013</v>
       </c>
       <c r="B562" s="15" t="s">
@@ -45208,7 +45201,7 @@
       <c r="Y562" s="15"/>
     </row>
     <row r="563" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A563" s="33">
+      <c r="A563" s="32">
         <v>161014</v>
       </c>
       <c r="B563" s="15" t="s">
@@ -45271,7 +45264,7 @@
       <c r="Y563" s="15"/>
     </row>
     <row r="564" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A564" s="33">
+      <c r="A564" s="32">
         <v>169016</v>
       </c>
       <c r="B564" s="15" t="s">
@@ -45332,7 +45325,7 @@
       <c r="Y564" s="15"/>
     </row>
     <row r="565" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A565" s="33">
+      <c r="A565" s="32">
         <v>167036</v>
       </c>
       <c r="B565" s="15" t="s">
@@ -45391,7 +45384,7 @@
       <c r="Y565" s="15"/>
     </row>
     <row r="566" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A566" s="35" t="s">
+      <c r="A566" s="34" t="s">
         <v>2859</v>
       </c>
       <c r="B566" s="26" t="s">
@@ -45455,7 +45448,7 @@
       <c r="Z566" s="14"/>
     </row>
     <row r="567" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A567" s="35">
+      <c r="A567" s="34">
         <v>169024</v>
       </c>
       <c r="B567" s="26" t="s">
@@ -45511,13 +45504,13 @@
       <c r="X567" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y567" s="30">
+      <c r="Y567" s="26">
         <v>169024</v>
       </c>
       <c r="Z567" s="14"/>
     </row>
     <row r="568" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A568" s="35">
+      <c r="A568" s="34">
         <v>656001</v>
       </c>
       <c r="B568" s="26" t="s">
@@ -45577,7 +45570,7 @@
       <c r="Z568" s="14"/>
     </row>
     <row r="569" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A569" s="35">
+      <c r="A569" s="34">
         <v>656008</v>
       </c>
       <c r="B569" s="26" t="s">
@@ -45641,7 +45634,7 @@
       <c r="Z569" s="14"/>
     </row>
     <row r="570" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A570" s="35">
+      <c r="A570" s="34">
         <v>269029</v>
       </c>
       <c r="B570" s="26" t="s">
@@ -45698,7 +45691,7 @@
       <c r="Y570" s="26"/>
     </row>
     <row r="571" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A571" s="35">
+      <c r="A571" s="34">
         <v>269030</v>
       </c>
       <c r="B571" s="26" t="s">
@@ -45755,7 +45748,7 @@
       <c r="Y571" s="26"/>
     </row>
     <row r="572" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A572" s="35">
+      <c r="A572" s="34">
         <v>169022</v>
       </c>
       <c r="B572" s="26" t="s">
@@ -45814,7 +45807,7 @@
       <c r="Y572" s="26"/>
     </row>
     <row r="573" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A573" s="35">
+      <c r="A573" s="34">
         <v>269034</v>
       </c>
       <c r="B573" s="26" t="s">
@@ -45873,7 +45866,7 @@
       <c r="Y573" s="26"/>
     </row>
     <row r="574" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A574" s="35">
+      <c r="A574" s="34">
         <v>269038</v>
       </c>
       <c r="B574" s="26" t="s">
@@ -45930,7 +45923,7 @@
       <c r="Y574" s="26"/>
     </row>
     <row r="575" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="35">
+      <c r="A575" s="34">
         <v>269033</v>
       </c>
       <c r="B575" s="26" t="s">
@@ -45989,7 +45982,7 @@
       <c r="Y575" s="26"/>
     </row>
     <row r="576" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A576" s="35">
+      <c r="A576" s="34">
         <v>269037</v>
       </c>
       <c r="B576" s="26" t="s">
@@ -46046,7 +46039,7 @@
       <c r="Y576" s="26"/>
     </row>
     <row r="577" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A577" s="35">
+      <c r="A577" s="34">
         <v>269036</v>
       </c>
       <c r="B577" s="26" t="s">
@@ -46103,7 +46096,7 @@
       <c r="Y577" s="26"/>
     </row>
     <row r="578" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A578" s="35">
+      <c r="A578" s="34">
         <v>269035</v>
       </c>
       <c r="B578" s="26" t="s">
@@ -46160,7 +46153,7 @@
       <c r="Y578" s="26"/>
     </row>
     <row r="579" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A579" s="35">
+      <c r="A579" s="34">
         <v>269039</v>
       </c>
       <c r="B579" s="26" t="s">
@@ -46219,7 +46212,7 @@
       <c r="Y579" s="26"/>
     </row>
     <row r="580" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A580" s="35">
+      <c r="A580" s="34">
         <v>269043</v>
       </c>
       <c r="B580" s="26" t="s">
@@ -46276,7 +46269,7 @@
       <c r="Y580" s="26"/>
     </row>
     <row r="581" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A581" s="35">
+      <c r="A581" s="34">
         <v>269041</v>
       </c>
       <c r="B581" s="26" t="s">
@@ -46335,7 +46328,7 @@
       <c r="Y581" s="26"/>
     </row>
     <row r="582" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A582" s="35">
+      <c r="A582" s="34">
         <v>269042</v>
       </c>
       <c r="B582" s="26" t="s">
@@ -46392,9 +46385,9 @@
       <c r="Y582" s="26"/>
     </row>
     <row r="583" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E583" s="31"/>
+      <c r="E583" s="30"/>
       <c r="F583" s="14"/>
-      <c r="T583" s="32"/>
+      <c r="T583" s="31"/>
       <c r="U583" s="14"/>
     </row>
   </sheetData>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{FB43BE3C-E866-400C-8C88-4ADFB1894538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{E2C2FA33-E5BA-4F38-AEF1-52C21C644E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7698" uniqueCount="3487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7699" uniqueCount="3488">
   <si>
     <t>emp_id</t>
   </si>
@@ -10500,6 +10500,9 @@
   </si>
   <si>
     <t>as_of_date=12 มิถุนายน 2569</t>
+  </si>
+  <si>
+    <t>FAIP</t>
   </si>
 </sst>
 </file>
@@ -45504,8 +45507,8 @@
       <c r="X567" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y567" s="26">
-        <v>169024</v>
+      <c r="Y567" s="26" t="s">
+        <v>3487</v>
       </c>
       <c r="Z567" s="14"/>
     </row>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6A32FA-4903-4480-A4BC-C4F12CF6FD85}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="3491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7717" uniqueCount="3491">
   <si>
     <t>emp_id</t>
   </si>
@@ -10801,6 +10801,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14777,7 +14781,9 @@
         <v>69</v>
       </c>
       <c r="P61" s="15"/>
-      <c r="Q61" s="15"/>
+      <c r="Q61" s="15" t="s">
+        <v>3380</v>
+      </c>
       <c r="R61" s="15"/>
       <c r="S61" s="15"/>
       <c r="T61" s="15"/>
@@ -14899,7 +14905,9 @@
         <v>110</v>
       </c>
       <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
+      <c r="Q63" s="15" t="s">
+        <v>3380</v>
+      </c>
       <c r="R63" s="15"/>
       <c r="S63" s="15" t="s">
         <v>111</v>
@@ -15271,7 +15279,9 @@
         <v>179</v>
       </c>
       <c r="P69" s="15"/>
-      <c r="Q69" s="15"/>
+      <c r="Q69" s="15" t="s">
+        <v>3380</v>
+      </c>
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
       <c r="T69" s="15"/>
@@ -15332,7 +15342,9 @@
         <v>125</v>
       </c>
       <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
+      <c r="Q70" s="15" t="s">
+        <v>3380</v>
+      </c>
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
       <c r="T70" s="15"/>
@@ -24974,7 +24986,7 @@
         <v>895</v>
       </c>
       <c r="I227" s="15">
-        <v>250042</v>
+        <v>264090</v>
       </c>
       <c r="J227" s="4">
         <v>34794</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6A32FA-4903-4480-A4BC-C4F12CF6FD85}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F83A7B2-1983-44F4-8D5A-93926C979D50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7717" uniqueCount="3491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7746" uniqueCount="3486">
   <si>
     <t>emp_id</t>
   </si>
@@ -10250,27 +10250,6 @@
     <t>269032.jpg</t>
   </si>
   <si>
-    <t>Key Position Level B</t>
-  </si>
-  <si>
-    <t>Key Position Level A</t>
-  </si>
-  <si>
-    <t>Key Position Level B+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Position Level A- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Position Level B+ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Position Level C+ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Position Level B </t>
-  </si>
-  <si>
     <t>อรุณี อุปนันท์</t>
   </si>
   <si>
@@ -10512,13 +10491,19 @@
   </si>
   <si>
     <t>97.78%</t>
+  </si>
+  <si>
+    <t>Key Position (B)</t>
+  </si>
+  <si>
+    <t>Key Position (A)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10581,6 +10566,19 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -10648,7 +10646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10762,6 +10760,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11098,7 +11123,7 @@
     <col min="1" max="1" width="12" style="35" customWidth="1"/>
     <col min="2" max="3" width="28" style="14" customWidth="1"/>
     <col min="4" max="4" width="19.453125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" style="14" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="37.1796875" style="30" customWidth="1"/>
     <col min="7" max="7" width="12" style="14" customWidth="1"/>
     <col min="8" max="8" width="28" style="14" customWidth="1"/>
@@ -11121,7 +11146,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
-        <v>3486</v>
+        <v>3479</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -15961,7 +15986,7 @@
       </c>
       <c r="P80" s="15"/>
       <c r="Q80" s="15" t="s">
-        <v>3403</v>
+        <v>3484</v>
       </c>
       <c r="R80" s="15"/>
       <c r="S80" s="15"/>
@@ -16089,7 +16114,7 @@
       </c>
       <c r="P82" s="15"/>
       <c r="Q82" s="15" t="s">
-        <v>3404</v>
+        <v>3485</v>
       </c>
       <c r="R82" s="15"/>
       <c r="S82" s="15" t="s">
@@ -17270,7 +17295,7 @@
       </c>
       <c r="P101" s="15"/>
       <c r="Q101" s="15" t="s">
-        <v>3403</v>
+        <v>3484</v>
       </c>
       <c r="R101" s="15"/>
       <c r="S101" s="15" t="s">
@@ -17883,7 +17908,7 @@
       </c>
       <c r="P111" s="15"/>
       <c r="Q111" s="15" t="s">
-        <v>3404</v>
+        <v>3485</v>
       </c>
       <c r="R111" s="15"/>
       <c r="S111" s="15" t="s">
@@ -19117,7 +19142,7 @@
         <v>33</v>
       </c>
       <c r="U131" s="18" t="s">
-        <v>3487</v>
+        <v>3480</v>
       </c>
       <c r="V131" s="15">
         <v>3</v>
@@ -20151,7 +20176,7 @@
       </c>
       <c r="P148" s="15"/>
       <c r="Q148" s="15" t="s">
-        <v>3403</v>
+        <v>3484</v>
       </c>
       <c r="R148" s="15"/>
       <c r="S148" s="19" t="s">
@@ -22420,28 +22445,28 @@
         <v>269040</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>3410</v>
+        <v>3403</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>3413</v>
+        <v>3406</v>
       </c>
       <c r="G185" s="15" t="s">
         <v>29</v>
       </c>
       <c r="H185" s="15" t="s">
-        <v>3424</v>
+        <v>3417</v>
       </c>
       <c r="I185" s="15" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="J185" s="4">
         <v>29660</v>
@@ -22452,10 +22477,10 @@
       <c r="L185" s="16"/>
       <c r="M185" s="16"/>
       <c r="N185" s="15" t="s">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="O185" s="15" t="s">
-        <v>3415</v>
+        <v>3408</v>
       </c>
       <c r="P185" s="15"/>
       <c r="Q185" s="15"/>
@@ -22478,7 +22503,7 @@
     </row>
     <row r="186" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="34" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="B186" s="26" t="s">
         <v>2258</v>
@@ -22487,13 +22512,13 @@
         <v>2259</v>
       </c>
       <c r="D186" s="26" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="E186" s="26" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="F186" s="9" t="s">
-        <v>3422</v>
+        <v>3415</v>
       </c>
       <c r="G186" s="26" t="s">
         <v>66</v>
@@ -22513,7 +22538,7 @@
       <c r="L186" s="28"/>
       <c r="M186" s="28"/>
       <c r="N186" s="26" t="s">
-        <v>3423</v>
+        <v>3416</v>
       </c>
       <c r="O186" s="26" t="s">
         <v>2263</v>
@@ -22644,7 +22669,9 @@
         <v>2301</v>
       </c>
       <c r="P188" s="15"/>
-      <c r="Q188" s="15"/>
+      <c r="Q188" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R188" s="15"/>
       <c r="S188" s="15"/>
       <c r="T188" s="15" t="s">
@@ -22707,7 +22734,9 @@
         <v>2306</v>
       </c>
       <c r="P189" s="15"/>
-      <c r="Q189" s="15"/>
+      <c r="Q189" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R189" s="15"/>
       <c r="S189" s="19" t="s">
         <v>2895</v>
@@ -22772,7 +22801,9 @@
         <v>2311</v>
       </c>
       <c r="P190" s="15"/>
-      <c r="Q190" s="15"/>
+      <c r="Q190" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R190" s="15"/>
       <c r="S190" s="15" t="s">
         <v>1459</v>
@@ -22837,7 +22868,9 @@
         <v>2315</v>
       </c>
       <c r="P191" s="15"/>
-      <c r="Q191" s="15"/>
+      <c r="Q191" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R191" s="15"/>
       <c r="S191" s="15" t="s">
         <v>883</v>
@@ -22902,7 +22935,9 @@
         <v>2319</v>
       </c>
       <c r="P192" s="15"/>
-      <c r="Q192" s="15"/>
+      <c r="Q192" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R192" s="15"/>
       <c r="S192" s="15" t="s">
         <v>1459</v>
@@ -22967,7 +23002,9 @@
         <v>2323</v>
       </c>
       <c r="P193" s="15"/>
-      <c r="Q193" s="15"/>
+      <c r="Q193" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R193" s="15"/>
       <c r="S193" s="15" t="s">
         <v>1295</v>
@@ -23032,7 +23069,9 @@
         <v>2328</v>
       </c>
       <c r="P194" s="15"/>
-      <c r="Q194" s="15"/>
+      <c r="Q194" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R194" s="15"/>
       <c r="S194" s="15" t="s">
         <v>277</v>
@@ -23097,7 +23136,9 @@
         <v>2333</v>
       </c>
       <c r="P195" s="15"/>
-      <c r="Q195" s="15"/>
+      <c r="Q195" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R195" s="15"/>
       <c r="S195" s="15" t="s">
         <v>441</v>
@@ -23162,7 +23203,9 @@
         <v>2269</v>
       </c>
       <c r="P196" s="15"/>
-      <c r="Q196" s="15"/>
+      <c r="Q196" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R196" s="15"/>
       <c r="S196" s="15" t="s">
         <v>53</v>
@@ -23286,7 +23329,9 @@
         <v>2282</v>
       </c>
       <c r="P198" s="15"/>
-      <c r="Q198" s="15"/>
+      <c r="Q198" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R198" s="15"/>
       <c r="S198" s="15"/>
       <c r="T198" s="15" t="s">
@@ -23480,7 +23525,7 @@
       </c>
       <c r="P201" s="15"/>
       <c r="Q201" s="15" t="s">
-        <v>3404</v>
+        <v>3485</v>
       </c>
       <c r="R201" s="15"/>
       <c r="S201" s="15"/>
@@ -23501,133 +23546,133 @@
       </c>
       <c r="Y201" s="15"/>
     </row>
-    <row r="202" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="32">
+    <row r="202" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="39">
         <v>264066</v>
       </c>
-      <c r="B202" s="15" t="s">
+      <c r="B202" s="40" t="s">
         <v>801</v>
       </c>
-      <c r="C202" s="15" t="s">
+      <c r="C202" s="40" t="s">
         <v>802</v>
       </c>
-      <c r="D202" s="15" t="s">
+      <c r="D202" s="40" t="s">
         <v>803</v>
       </c>
-      <c r="E202" s="15" t="s">
+      <c r="E202" s="40" t="s">
         <v>803</v>
       </c>
-      <c r="F202" s="6" t="s">
+      <c r="F202" s="41" t="s">
         <v>804</v>
       </c>
-      <c r="G202" s="15" t="s">
+      <c r="G202" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H202" s="15" t="s">
+      <c r="H202" s="40" t="s">
         <v>805</v>
       </c>
-      <c r="I202" s="15">
+      <c r="I202" s="40">
         <v>250042</v>
       </c>
-      <c r="J202" s="4">
+      <c r="J202" s="42">
         <v>36285</v>
       </c>
-      <c r="K202" s="4">
+      <c r="K202" s="42">
         <v>44440</v>
       </c>
-      <c r="L202" s="16"/>
-      <c r="M202" s="16"/>
-      <c r="N202" s="15" t="s">
+      <c r="L202" s="43"/>
+      <c r="M202" s="43"/>
+      <c r="N202" s="40" t="s">
         <v>806</v>
       </c>
-      <c r="O202" s="15" t="s">
+      <c r="O202" s="40" t="s">
         <v>807</v>
       </c>
-      <c r="P202" s="15"/>
-      <c r="Q202" s="15"/>
-      <c r="R202" s="15"/>
-      <c r="S202" s="15" t="s">
+      <c r="P202" s="40"/>
+      <c r="Q202" s="40"/>
+      <c r="R202" s="40"/>
+      <c r="S202" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="T202" s="15" t="s">
+      <c r="T202" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="U202" s="17" t="s">
+      <c r="U202" s="44" t="s">
         <v>3080</v>
       </c>
-      <c r="V202" s="15">
+      <c r="V202" s="40">
         <v>4</v>
       </c>
-      <c r="W202" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X202" s="15" t="s">
+      <c r="W202" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X202" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Y202" s="15"/>
-    </row>
-    <row r="203" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="32">
+      <c r="Y202" s="40"/>
+    </row>
+    <row r="203" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="39">
         <v>266086</v>
       </c>
-      <c r="B203" s="15" t="s">
+      <c r="B203" s="40" t="s">
         <v>808</v>
       </c>
-      <c r="C203" s="15" t="s">
+      <c r="C203" s="40" t="s">
         <v>809</v>
       </c>
-      <c r="D203" s="15" t="s">
+      <c r="D203" s="40" t="s">
         <v>810</v>
       </c>
-      <c r="E203" s="15" t="s">
+      <c r="E203" s="40" t="s">
         <v>810</v>
       </c>
-      <c r="F203" s="6" t="s">
+      <c r="F203" s="41" t="s">
         <v>804</v>
       </c>
-      <c r="G203" s="15" t="s">
+      <c r="G203" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H203" s="15" t="s">
+      <c r="H203" s="40" t="s">
         <v>805</v>
       </c>
-      <c r="I203" s="15">
+      <c r="I203" s="40">
         <v>264090</v>
       </c>
-      <c r="J203" s="4">
+      <c r="J203" s="42">
         <v>36896</v>
       </c>
-      <c r="K203" s="4">
+      <c r="K203" s="42">
         <v>45187</v>
       </c>
-      <c r="L203" s="16"/>
-      <c r="M203" s="16"/>
-      <c r="N203" s="15" t="s">
+      <c r="L203" s="43"/>
+      <c r="M203" s="43"/>
+      <c r="N203" s="40" t="s">
         <v>811</v>
       </c>
-      <c r="O203" s="15" t="s">
+      <c r="O203" s="40" t="s">
         <v>812</v>
       </c>
-      <c r="P203" s="15"/>
-      <c r="Q203" s="15"/>
-      <c r="R203" s="15"/>
-      <c r="S203" s="19" t="s">
+      <c r="P203" s="40"/>
+      <c r="Q203" s="40"/>
+      <c r="R203" s="40"/>
+      <c r="S203" s="46" t="s">
         <v>2895</v>
       </c>
-      <c r="T203" s="15"/>
-      <c r="U203" s="17" t="s">
+      <c r="T203" s="40"/>
+      <c r="U203" s="44" t="s">
         <v>3081</v>
       </c>
-      <c r="V203" s="15">
+      <c r="V203" s="40">
         <v>3</v>
       </c>
-      <c r="W203" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X203" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y203" s="15"/>
+      <c r="W203" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X203" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y203" s="40"/>
     </row>
     <row r="204" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="32">
@@ -24824,7 +24869,9 @@
         <v>898</v>
       </c>
       <c r="P224" s="15"/>
-      <c r="Q224" s="15"/>
+      <c r="Q224" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R224" s="15"/>
       <c r="S224" s="15" t="s">
         <v>899</v>
@@ -25179,7 +25226,7 @@
       </c>
       <c r="P230" s="15"/>
       <c r="Q230" s="15" t="s">
-        <v>3405</v>
+        <v>3485</v>
       </c>
       <c r="R230" s="15"/>
       <c r="S230" s="15" t="s">
@@ -25241,7 +25288,9 @@
         <v>930</v>
       </c>
       <c r="P231" s="15"/>
-      <c r="Q231" s="15"/>
+      <c r="Q231" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R231" s="15"/>
       <c r="S231" s="15" t="s">
         <v>274</v>
@@ -26013,133 +26062,133 @@
       </c>
       <c r="Y243" s="15"/>
     </row>
-    <row r="244" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="32">
+    <row r="244" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="39">
         <v>265019</v>
       </c>
-      <c r="B244" s="15" t="s">
+      <c r="B244" s="40" t="s">
         <v>987</v>
       </c>
-      <c r="C244" s="15" t="s">
+      <c r="C244" s="40" t="s">
         <v>988</v>
       </c>
-      <c r="D244" s="15" t="s">
+      <c r="D244" s="40" t="s">
         <v>989</v>
       </c>
-      <c r="E244" s="15" t="s">
+      <c r="E244" s="40" t="s">
         <v>989</v>
       </c>
-      <c r="F244" s="6" t="s">
+      <c r="F244" s="41" t="s">
         <v>990</v>
       </c>
-      <c r="G244" s="15" t="s">
+      <c r="G244" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H244" s="15" t="s">
+      <c r="H244" s="40" t="s">
         <v>928</v>
       </c>
-      <c r="I244" s="15">
+      <c r="I244" s="40">
         <v>233034</v>
       </c>
-      <c r="J244" s="4">
+      <c r="J244" s="42">
         <v>36039</v>
       </c>
-      <c r="K244" s="4">
+      <c r="K244" s="42">
         <v>44608</v>
       </c>
-      <c r="L244" s="16"/>
-      <c r="M244" s="16"/>
-      <c r="N244" s="15" t="s">
+      <c r="L244" s="43"/>
+      <c r="M244" s="43"/>
+      <c r="N244" s="40" t="s">
         <v>991</v>
       </c>
-      <c r="O244" s="15" t="s">
+      <c r="O244" s="40" t="s">
         <v>992</v>
       </c>
-      <c r="P244" s="15"/>
-      <c r="Q244" s="15"/>
-      <c r="R244" s="15"/>
-      <c r="S244" s="15" t="s">
+      <c r="P244" s="40"/>
+      <c r="Q244" s="40"/>
+      <c r="R244" s="40"/>
+      <c r="S244" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="T244" s="15" t="s">
+      <c r="T244" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="U244" s="17" t="s">
+      <c r="U244" s="44" t="s">
         <v>3117</v>
       </c>
-      <c r="V244" s="15">
+      <c r="V244" s="40">
         <v>3</v>
       </c>
-      <c r="W244" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X244" s="15" t="s">
+      <c r="W244" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X244" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Y244" s="15"/>
-    </row>
-    <row r="245" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="32">
+      <c r="Y244" s="40"/>
+    </row>
+    <row r="245" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="39">
         <v>265047</v>
       </c>
-      <c r="B245" s="15" t="s">
+      <c r="B245" s="40" t="s">
         <v>993</v>
       </c>
-      <c r="C245" s="15" t="s">
+      <c r="C245" s="40" t="s">
         <v>994</v>
       </c>
-      <c r="D245" s="15" t="s">
+      <c r="D245" s="40" t="s">
         <v>995</v>
       </c>
-      <c r="E245" s="15" t="s">
+      <c r="E245" s="40" t="s">
         <v>995</v>
       </c>
-      <c r="F245" s="6" t="s">
+      <c r="F245" s="41" t="s">
         <v>990</v>
       </c>
-      <c r="G245" s="15" t="s">
+      <c r="G245" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H245" s="15" t="s">
+      <c r="H245" s="40" t="s">
         <v>928</v>
       </c>
-      <c r="I245" s="15">
+      <c r="I245" s="40">
         <v>268013</v>
       </c>
-      <c r="J245" s="4">
+      <c r="J245" s="42">
         <v>35453</v>
       </c>
-      <c r="K245" s="4">
+      <c r="K245" s="42">
         <v>44652</v>
       </c>
-      <c r="L245" s="16"/>
-      <c r="M245" s="16"/>
-      <c r="N245" s="15" t="s">
+      <c r="L245" s="43"/>
+      <c r="M245" s="43"/>
+      <c r="N245" s="40" t="s">
         <v>996</v>
       </c>
-      <c r="O245" s="15" t="s">
+      <c r="O245" s="40" t="s">
         <v>997</v>
       </c>
-      <c r="P245" s="15"/>
-      <c r="Q245" s="15"/>
-      <c r="R245" s="15"/>
-      <c r="S245" s="15" t="s">
+      <c r="P245" s="40"/>
+      <c r="Q245" s="40"/>
+      <c r="R245" s="40"/>
+      <c r="S245" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="T245" s="15"/>
-      <c r="U245" s="17" t="s">
+      <c r="T245" s="40"/>
+      <c r="U245" s="44" t="s">
         <v>3118</v>
       </c>
-      <c r="V245" s="15">
+      <c r="V245" s="40">
         <v>3</v>
       </c>
-      <c r="W245" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X245" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y245" s="15"/>
+      <c r="W245" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X245" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y245" s="40"/>
     </row>
     <row r="246" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="32">
@@ -26420,7 +26469,9 @@
         <v>1020</v>
       </c>
       <c r="P250" s="15"/>
-      <c r="Q250" s="15"/>
+      <c r="Q250" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R250" s="15"/>
       <c r="S250" s="15"/>
       <c r="T250" s="15"/>
@@ -26735,66 +26786,66 @@
       </c>
       <c r="Y255" s="15"/>
     </row>
-    <row r="256" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="32">
+    <row r="256" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="34">
         <v>268083</v>
       </c>
-      <c r="B256" s="15" t="s">
+      <c r="B256" s="26" t="s">
         <v>1046</v>
       </c>
-      <c r="C256" s="15" t="s">
+      <c r="C256" s="26" t="s">
         <v>1047</v>
       </c>
-      <c r="D256" s="15" t="s">
+      <c r="D256" s="26" t="s">
         <v>1048</v>
       </c>
-      <c r="E256" s="15" t="s">
+      <c r="E256" s="26" t="s">
         <v>1048</v>
       </c>
-      <c r="F256" s="6" t="s">
+      <c r="F256" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="G256" s="15" t="s">
+      <c r="G256" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H256" s="15" t="s">
+      <c r="H256" s="26" t="s">
         <v>1028</v>
       </c>
-      <c r="I256" s="15">
+      <c r="I256" s="26">
         <v>259005</v>
       </c>
-      <c r="J256" s="4">
+      <c r="J256" s="10">
         <v>34005</v>
       </c>
-      <c r="K256" s="4">
+      <c r="K256" s="10">
         <v>45964</v>
       </c>
-      <c r="L256" s="16"/>
-      <c r="M256" s="16"/>
-      <c r="N256" s="15" t="s">
+      <c r="L256" s="28"/>
+      <c r="M256" s="28"/>
+      <c r="N256" s="26" t="s">
         <v>1050</v>
       </c>
-      <c r="O256" s="15" t="s">
+      <c r="O256" s="26" t="s">
         <v>1051</v>
       </c>
-      <c r="P256" s="15"/>
-      <c r="Q256" s="15"/>
-      <c r="R256" s="15"/>
-      <c r="S256" s="15"/>
-      <c r="T256" s="15"/>
-      <c r="U256" s="17" t="s">
+      <c r="P256" s="26"/>
+      <c r="Q256" s="26"/>
+      <c r="R256" s="26"/>
+      <c r="S256" s="26"/>
+      <c r="T256" s="26"/>
+      <c r="U256" s="29" t="s">
         <v>2990</v>
       </c>
-      <c r="V256" s="15" t="s">
+      <c r="V256" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="W256" s="15" t="s">
+      <c r="W256" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X256" s="15" t="s">
+      <c r="X256" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Y256" s="15"/>
+      <c r="Y256" s="26"/>
     </row>
     <row r="257" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="32">
@@ -27089,7 +27140,9 @@
         <v>1080</v>
       </c>
       <c r="P261" s="15"/>
-      <c r="Q261" s="15"/>
+      <c r="Q261" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R261" s="15"/>
       <c r="S261" s="15" t="s">
         <v>1081</v>
@@ -27794,7 +27847,7 @@
       </c>
       <c r="Y272" s="15"/>
     </row>
-    <row r="273" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="32">
         <v>264040</v>
       </c>
@@ -27855,7 +27908,7 @@
       </c>
       <c r="Y273" s="15"/>
     </row>
-    <row r="274" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="32">
         <v>264091</v>
       </c>
@@ -27916,7 +27969,7 @@
       </c>
       <c r="Y274" s="15"/>
     </row>
-    <row r="275" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="32">
         <v>265012</v>
       </c>
@@ -27975,7 +28028,7 @@
       </c>
       <c r="Y275" s="15"/>
     </row>
-    <row r="276" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="32">
         <v>265040</v>
       </c>
@@ -28034,71 +28087,70 @@
       </c>
       <c r="Y276" s="15"/>
     </row>
-    <row r="277" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="33">
+    <row r="277" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="34">
         <v>266050</v>
       </c>
-      <c r="B277" s="21" t="s">
+      <c r="B277" s="26" t="s">
         <v>1145</v>
       </c>
-      <c r="C277" s="21" t="s">
+      <c r="C277" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="D277" s="21" t="s">
+      <c r="D277" s="26" t="s">
         <v>1147</v>
       </c>
-      <c r="E277" s="21" t="s">
+      <c r="E277" s="26" t="s">
         <v>1147</v>
       </c>
-      <c r="F277" s="7" t="s">
+      <c r="F277" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="G277" s="21" t="s">
+      <c r="G277" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="H277" s="21" t="s">
+      <c r="H277" s="26" t="s">
         <v>1072</v>
       </c>
-      <c r="I277" s="21">
+      <c r="I277" s="26">
         <v>249010</v>
       </c>
-      <c r="J277" s="8">
+      <c r="J277" s="10">
         <v>35723</v>
       </c>
-      <c r="K277" s="8">
+      <c r="K277" s="10">
         <v>45048</v>
       </c>
-      <c r="L277" s="22"/>
-      <c r="M277" s="22"/>
-      <c r="N277" s="21" t="s">
+      <c r="L277" s="28"/>
+      <c r="M277" s="28"/>
+      <c r="N277" s="26" t="s">
         <v>1149</v>
       </c>
-      <c r="O277" s="21" t="s">
+      <c r="O277" s="26" t="s">
         <v>1150</v>
       </c>
-      <c r="P277" s="21"/>
-      <c r="Q277" s="21"/>
-      <c r="R277" s="21"/>
-      <c r="S277" s="21" t="s">
+      <c r="P277" s="26"/>
+      <c r="Q277" s="26"/>
+      <c r="R277" s="26"/>
+      <c r="S277" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="T277" s="21"/>
-      <c r="U277" s="23" t="s">
+      <c r="T277" s="26"/>
+      <c r="U277" s="29" t="s">
         <v>3146</v>
       </c>
-      <c r="V277" s="21">
+      <c r="V277" s="26">
         <v>4</v>
       </c>
-      <c r="W277" s="21" t="s">
+      <c r="W277" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="X277" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y277" s="21"/>
-      <c r="Z277" s="14"/>
-    </row>
-    <row r="278" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X277" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y277" s="26"/>
+    </row>
+    <row r="278" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="32">
         <v>266072</v>
       </c>
@@ -28157,7 +28209,7 @@
       </c>
       <c r="Y278" s="15"/>
     </row>
-    <row r="279" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="32">
         <v>267022</v>
       </c>
@@ -28216,68 +28268,68 @@
       </c>
       <c r="Y279" s="15"/>
     </row>
-    <row r="280" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="32">
+    <row r="280" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="39">
         <v>267035</v>
       </c>
-      <c r="B280" s="15" t="s">
+      <c r="B280" s="40" t="s">
         <v>1159</v>
       </c>
-      <c r="C280" s="15" t="s">
+      <c r="C280" s="40" t="s">
         <v>1160</v>
       </c>
-      <c r="D280" s="15" t="s">
+      <c r="D280" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="E280" s="15" t="s">
+      <c r="E280" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="F280" s="6" t="s">
+      <c r="F280" s="41" t="s">
         <v>1162</v>
       </c>
-      <c r="G280" s="15" t="s">
+      <c r="G280" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H280" s="15" t="s">
+      <c r="H280" s="40" t="s">
         <v>1072</v>
       </c>
-      <c r="I280" s="15">
+      <c r="I280" s="40">
         <v>268012</v>
       </c>
-      <c r="J280" s="4">
+      <c r="J280" s="42">
         <v>36912</v>
       </c>
-      <c r="K280" s="4">
+      <c r="K280" s="42">
         <v>45366</v>
       </c>
-      <c r="L280" s="16"/>
-      <c r="M280" s="16"/>
-      <c r="N280" s="15" t="s">
+      <c r="L280" s="43"/>
+      <c r="M280" s="43"/>
+      <c r="N280" s="40" t="s">
         <v>1163</v>
       </c>
-      <c r="O280" s="15" t="s">
+      <c r="O280" s="40" t="s">
         <v>1164</v>
       </c>
-      <c r="P280" s="15"/>
-      <c r="Q280" s="15"/>
-      <c r="R280" s="15"/>
-      <c r="S280" s="15"/>
-      <c r="T280" s="15"/>
-      <c r="U280" s="17" t="s">
+      <c r="P280" s="40"/>
+      <c r="Q280" s="40"/>
+      <c r="R280" s="40"/>
+      <c r="S280" s="40"/>
+      <c r="T280" s="40"/>
+      <c r="U280" s="44" t="s">
         <v>3149</v>
       </c>
-      <c r="V280" s="15">
+      <c r="V280" s="40">
         <v>3</v>
       </c>
-      <c r="W280" s="15" t="s">
+      <c r="W280" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="X280" s="15" t="s">
+      <c r="X280" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y280" s="15"/>
-    </row>
-    <row r="281" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y280" s="40"/>
+    </row>
+    <row r="281" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="32">
         <v>267074</v>
       </c>
@@ -28338,7 +28390,7 @@
       </c>
       <c r="Y281" s="15"/>
     </row>
-    <row r="282" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="32">
         <v>267083</v>
       </c>
@@ -28397,7 +28449,7 @@
       </c>
       <c r="Y282" s="15"/>
     </row>
-    <row r="283" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="32">
         <v>267099</v>
       </c>
@@ -28456,7 +28508,7 @@
       </c>
       <c r="Y283" s="15"/>
     </row>
-    <row r="284" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="32">
         <v>268012</v>
       </c>
@@ -28499,7 +28551,9 @@
         <v>1181</v>
       </c>
       <c r="P284" s="15"/>
-      <c r="Q284" s="15"/>
+      <c r="Q284" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R284" s="15"/>
       <c r="S284" s="15"/>
       <c r="T284" s="15"/>
@@ -28517,7 +28571,7 @@
       </c>
       <c r="Y284" s="15"/>
     </row>
-    <row r="285" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="32">
         <v>268042</v>
       </c>
@@ -28576,7 +28630,7 @@
       </c>
       <c r="Y285" s="15"/>
     </row>
-    <row r="286" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="32">
         <v>268073</v>
       </c>
@@ -28635,68 +28689,68 @@
       </c>
       <c r="Y286" s="15"/>
     </row>
-    <row r="287" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="32">
+    <row r="287" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="39">
         <v>269011</v>
       </c>
-      <c r="B287" s="15" t="s">
+      <c r="B287" s="40" t="s">
         <v>1190</v>
       </c>
-      <c r="C287" s="15" t="s">
+      <c r="C287" s="40" t="s">
         <v>1191</v>
       </c>
-      <c r="D287" s="15" t="s">
+      <c r="D287" s="40" t="s">
         <v>1192</v>
       </c>
-      <c r="E287" s="15" t="s">
+      <c r="E287" s="40" t="s">
         <v>1192</v>
       </c>
-      <c r="F287" s="6" t="s">
+      <c r="F287" s="41" t="s">
         <v>1162</v>
       </c>
-      <c r="G287" s="15" t="s">
+      <c r="G287" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H287" s="15" t="s">
+      <c r="H287" s="40" t="s">
         <v>1072</v>
       </c>
-      <c r="I287" s="15">
+      <c r="I287" s="40">
         <v>268012</v>
       </c>
-      <c r="J287" s="4">
+      <c r="J287" s="42">
         <v>36580</v>
       </c>
-      <c r="K287" s="4">
+      <c r="K287" s="42">
         <v>46069</v>
       </c>
-      <c r="L287" s="16"/>
-      <c r="M287" s="16"/>
-      <c r="N287" s="15" t="s">
+      <c r="L287" s="43"/>
+      <c r="M287" s="43"/>
+      <c r="N287" s="40" t="s">
         <v>1193</v>
       </c>
-      <c r="O287" s="15" t="s">
+      <c r="O287" s="40" t="s">
         <v>1194</v>
       </c>
-      <c r="P287" s="15"/>
-      <c r="Q287" s="15"/>
-      <c r="R287" s="15"/>
-      <c r="S287" s="15"/>
-      <c r="T287" s="15"/>
-      <c r="U287" s="17" t="s">
+      <c r="P287" s="40"/>
+      <c r="Q287" s="40"/>
+      <c r="R287" s="40"/>
+      <c r="S287" s="40"/>
+      <c r="T287" s="40"/>
+      <c r="U287" s="44" t="s">
         <v>2919</v>
       </c>
-      <c r="V287" s="15" t="s">
+      <c r="V287" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="W287" s="15" t="s">
+      <c r="W287" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X287" s="15" t="s">
+      <c r="X287" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y287" s="15"/>
-    </row>
-    <row r="288" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y287" s="40"/>
+    </row>
+    <row r="288" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="32">
         <v>269024</v>
       </c>
@@ -28798,7 +28852,9 @@
         <v>1205</v>
       </c>
       <c r="P289" s="15"/>
-      <c r="Q289" s="15"/>
+      <c r="Q289" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R289" s="15"/>
       <c r="S289" s="15" t="s">
         <v>393</v>
@@ -29261,68 +29317,68 @@
       </c>
       <c r="Y296" s="15"/>
     </row>
-    <row r="297" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="32">
+    <row r="297" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A297" s="39">
         <v>266057</v>
       </c>
-      <c r="B297" s="15" t="s">
+      <c r="B297" s="40" t="s">
         <v>1241</v>
       </c>
-      <c r="C297" s="15" t="s">
+      <c r="C297" s="40" t="s">
         <v>1242</v>
       </c>
-      <c r="D297" s="15" t="s">
+      <c r="D297" s="40" t="s">
         <v>1243</v>
       </c>
-      <c r="E297" s="15" t="s">
+      <c r="E297" s="40" t="s">
         <v>1243</v>
       </c>
-      <c r="F297" s="6" t="s">
+      <c r="F297" s="41" t="s">
         <v>1244</v>
       </c>
-      <c r="G297" s="15" t="s">
+      <c r="G297" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H297" s="15" t="s">
+      <c r="H297" s="40" t="s">
         <v>1203</v>
       </c>
-      <c r="I297" s="15">
+      <c r="I297" s="40">
         <v>238030</v>
       </c>
-      <c r="J297" s="4">
+      <c r="J297" s="42">
         <v>35977</v>
       </c>
-      <c r="K297" s="4">
+      <c r="K297" s="42">
         <v>45078</v>
       </c>
-      <c r="L297" s="16"/>
-      <c r="M297" s="16"/>
-      <c r="N297" s="15" t="s">
+      <c r="L297" s="43"/>
+      <c r="M297" s="43"/>
+      <c r="N297" s="40" t="s">
         <v>1245</v>
       </c>
-      <c r="O297" s="15" t="s">
+      <c r="O297" s="40" t="s">
         <v>1246</v>
       </c>
-      <c r="P297" s="15"/>
-      <c r="Q297" s="15"/>
-      <c r="R297" s="15"/>
-      <c r="S297" s="15" t="s">
+      <c r="P297" s="40"/>
+      <c r="Q297" s="40"/>
+      <c r="R297" s="40"/>
+      <c r="S297" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="T297" s="15"/>
-      <c r="U297" s="17" t="s">
+      <c r="T297" s="40"/>
+      <c r="U297" s="44" t="s">
         <v>3163</v>
       </c>
-      <c r="V297" s="15">
+      <c r="V297" s="40">
         <v>4</v>
       </c>
-      <c r="W297" s="15" t="s">
+      <c r="W297" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="X297" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y297" s="15"/>
+      <c r="X297" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y297" s="40"/>
     </row>
     <row r="298" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="32">
@@ -29427,7 +29483,7 @@
       </c>
       <c r="P299" s="15"/>
       <c r="Q299" s="15" t="s">
-        <v>3406</v>
+        <v>3485</v>
       </c>
       <c r="R299" s="15"/>
       <c r="S299" s="15" t="s">
@@ -29493,7 +29549,9 @@
         <v>1453</v>
       </c>
       <c r="P300" s="15"/>
-      <c r="Q300" s="15"/>
+      <c r="Q300" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R300" s="15"/>
       <c r="S300" s="15" t="s">
         <v>111</v>
@@ -31999,7 +32057,9 @@
         <v>1440</v>
       </c>
       <c r="P342" s="15"/>
-      <c r="Q342" s="15"/>
+      <c r="Q342" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R342" s="15"/>
       <c r="S342" s="15" t="s">
         <v>277</v>
@@ -32043,7 +32103,7 @@
         <v>1376</v>
       </c>
       <c r="I343" s="15">
-        <v>265014</v>
+        <v>256014</v>
       </c>
       <c r="J343" s="4">
         <v>22583</v>
@@ -32098,7 +32158,7 @@
         <v>1376</v>
       </c>
       <c r="I344" s="15">
-        <v>265014</v>
+        <v>256014</v>
       </c>
       <c r="J344" s="4">
         <v>23968</v>
@@ -32174,7 +32234,9 @@
         <v>1551</v>
       </c>
       <c r="P345" s="15"/>
-      <c r="Q345" s="15"/>
+      <c r="Q345" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R345" s="15"/>
       <c r="S345" s="19" t="s">
         <v>2895</v>
@@ -32239,7 +32301,9 @@
         <v>1458</v>
       </c>
       <c r="P346" s="15"/>
-      <c r="Q346" s="15"/>
+      <c r="Q346" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R346" s="15"/>
       <c r="S346" s="15" t="s">
         <v>1459</v>
@@ -33172,66 +33236,66 @@
       </c>
       <c r="Y361" s="15"/>
     </row>
-    <row r="362" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A362" s="32">
+    <row r="362" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A362" s="39">
         <v>268074</v>
       </c>
-      <c r="B362" s="15" t="s">
+      <c r="B362" s="40" t="s">
         <v>1511</v>
       </c>
-      <c r="C362" s="15" t="s">
+      <c r="C362" s="40" t="s">
         <v>1512</v>
       </c>
-      <c r="D362" s="15" t="s">
+      <c r="D362" s="40" t="s">
         <v>1023</v>
       </c>
-      <c r="E362" s="15" t="s">
+      <c r="E362" s="40" t="s">
         <v>1023</v>
       </c>
-      <c r="F362" s="6" t="s">
+      <c r="F362" s="41" t="s">
         <v>1513</v>
       </c>
-      <c r="G362" s="15" t="s">
+      <c r="G362" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H362" s="15" t="s">
+      <c r="H362" s="40" t="s">
         <v>1481</v>
       </c>
-      <c r="I362" s="15">
+      <c r="I362" s="40">
         <v>254057</v>
       </c>
-      <c r="J362" s="4">
+      <c r="J362" s="42">
         <v>37531</v>
       </c>
-      <c r="K362" s="4">
+      <c r="K362" s="42">
         <v>45901</v>
       </c>
-      <c r="L362" s="16"/>
-      <c r="M362" s="16"/>
-      <c r="N362" s="15" t="s">
+      <c r="L362" s="43"/>
+      <c r="M362" s="43"/>
+      <c r="N362" s="40" t="s">
         <v>1514</v>
       </c>
-      <c r="O362" s="15" t="s">
+      <c r="O362" s="40" t="s">
         <v>1515</v>
       </c>
-      <c r="P362" s="15"/>
-      <c r="Q362" s="15"/>
-      <c r="R362" s="15"/>
-      <c r="S362" s="15"/>
-      <c r="T362" s="15"/>
-      <c r="U362" s="17" t="s">
+      <c r="P362" s="40"/>
+      <c r="Q362" s="40"/>
+      <c r="R362" s="40"/>
+      <c r="S362" s="40"/>
+      <c r="T362" s="40"/>
+      <c r="U362" s="44" t="s">
         <v>3216</v>
       </c>
-      <c r="V362" s="15">
+      <c r="V362" s="40">
         <v>3</v>
       </c>
-      <c r="W362" s="15" t="s">
+      <c r="W362" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X362" s="15" t="s">
+      <c r="X362" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y362" s="15"/>
+      <c r="Y362" s="40"/>
     </row>
     <row r="363" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="32">
@@ -34037,7 +34101,9 @@
         <v>1773</v>
       </c>
       <c r="P376" s="15"/>
-      <c r="Q376" s="15"/>
+      <c r="Q376" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R376" s="15"/>
       <c r="S376" s="15"/>
       <c r="T376" s="15"/>
@@ -36762,7 +36828,9 @@
         <v>1735</v>
       </c>
       <c r="P421" s="15"/>
-      <c r="Q421" s="15"/>
+      <c r="Q421" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R421" s="15"/>
       <c r="S421" s="15" t="s">
         <v>883</v>
@@ -36906,68 +36974,68 @@
       </c>
       <c r="Y423" s="15"/>
     </row>
-    <row r="424" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A424" s="32">
+    <row r="424" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="39">
         <v>265126</v>
       </c>
-      <c r="B424" s="15" t="s">
+      <c r="B424" s="40" t="s">
         <v>1748</v>
       </c>
-      <c r="C424" s="15" t="s">
+      <c r="C424" s="40" t="s">
         <v>1749</v>
       </c>
-      <c r="D424" s="15" t="s">
+      <c r="D424" s="40" t="s">
         <v>1750</v>
       </c>
-      <c r="E424" s="15" t="s">
+      <c r="E424" s="40" t="s">
         <v>1750</v>
       </c>
-      <c r="F424" s="6" t="s">
+      <c r="F424" s="41" t="s">
         <v>1751</v>
       </c>
-      <c r="G424" s="15" t="s">
+      <c r="G424" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H424" s="15" t="s">
+      <c r="H424" s="40" t="s">
         <v>1729</v>
       </c>
-      <c r="I424" s="15">
+      <c r="I424" s="40">
         <v>267096</v>
       </c>
-      <c r="J424" s="4">
+      <c r="J424" s="42">
         <v>34949</v>
       </c>
-      <c r="K424" s="4">
+      <c r="K424" s="42">
         <v>44881</v>
       </c>
-      <c r="L424" s="16"/>
-      <c r="M424" s="16"/>
-      <c r="N424" s="15" t="s">
+      <c r="L424" s="43"/>
+      <c r="M424" s="43"/>
+      <c r="N424" s="40" t="s">
         <v>1752</v>
       </c>
-      <c r="O424" s="15" t="s">
+      <c r="O424" s="40" t="s">
         <v>1753</v>
       </c>
-      <c r="P424" s="15"/>
-      <c r="Q424" s="15"/>
-      <c r="R424" s="15"/>
-      <c r="S424" s="15" t="s">
+      <c r="P424" s="40"/>
+      <c r="Q424" s="40"/>
+      <c r="R424" s="40"/>
+      <c r="S424" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="T424" s="15"/>
-      <c r="U424" s="17" t="s">
+      <c r="T424" s="40"/>
+      <c r="U424" s="44" t="s">
         <v>3118</v>
       </c>
-      <c r="V424" s="15">
+      <c r="V424" s="40">
         <v>4</v>
       </c>
-      <c r="W424" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X424" s="15" t="s">
+      <c r="W424" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X424" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Y424" s="15"/>
+      <c r="Y424" s="40"/>
     </row>
     <row r="425" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="32">
@@ -37028,66 +37096,66 @@
       </c>
       <c r="Y425" s="15"/>
     </row>
-    <row r="426" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A426" s="32">
+    <row r="426" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A426" s="39">
         <v>267072</v>
       </c>
-      <c r="B426" s="15" t="s">
+      <c r="B426" s="40" t="s">
         <v>1757</v>
       </c>
-      <c r="C426" s="15" t="s">
+      <c r="C426" s="40" t="s">
         <v>1758</v>
       </c>
-      <c r="D426" s="15" t="s">
+      <c r="D426" s="40" t="s">
         <v>1232</v>
       </c>
-      <c r="E426" s="15" t="s">
+      <c r="E426" s="40" t="s">
         <v>1232</v>
       </c>
-      <c r="F426" s="6" t="s">
+      <c r="F426" s="41" t="s">
         <v>1751</v>
       </c>
-      <c r="G426" s="15" t="s">
+      <c r="G426" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H426" s="15" t="s">
+      <c r="H426" s="40" t="s">
         <v>1729</v>
       </c>
-      <c r="I426" s="15">
+      <c r="I426" s="40">
         <v>267096</v>
       </c>
-      <c r="J426" s="4">
+      <c r="J426" s="42">
         <v>37176</v>
       </c>
-      <c r="K426" s="4">
+      <c r="K426" s="42">
         <v>45489</v>
       </c>
-      <c r="L426" s="16"/>
-      <c r="M426" s="16"/>
-      <c r="N426" s="15" t="s">
+      <c r="L426" s="43"/>
+      <c r="M426" s="43"/>
+      <c r="N426" s="40" t="s">
         <v>1759</v>
       </c>
-      <c r="O426" s="15" t="s">
+      <c r="O426" s="40" t="s">
         <v>1760</v>
       </c>
-      <c r="P426" s="15"/>
-      <c r="Q426" s="15"/>
-      <c r="R426" s="15"/>
-      <c r="S426" s="15"/>
-      <c r="T426" s="15"/>
-      <c r="U426" s="17" t="s">
+      <c r="P426" s="40"/>
+      <c r="Q426" s="40"/>
+      <c r="R426" s="40"/>
+      <c r="S426" s="40"/>
+      <c r="T426" s="40"/>
+      <c r="U426" s="44" t="s">
         <v>3260</v>
       </c>
-      <c r="V426" s="15">
+      <c r="V426" s="40">
         <v>3</v>
       </c>
-      <c r="W426" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X426" s="15" t="s">
+      <c r="W426" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X426" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y426" s="15"/>
+      <c r="Y426" s="40"/>
     </row>
     <row r="427" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="32">
@@ -37251,7 +37319,7 @@
       </c>
       <c r="P429" s="15"/>
       <c r="Q429" s="15" t="s">
-        <v>3407</v>
+        <v>3485</v>
       </c>
       <c r="R429" s="15"/>
       <c r="S429" s="19" t="s">
@@ -37274,66 +37342,66 @@
       </c>
       <c r="Y429" s="15"/>
     </row>
-    <row r="430" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A430" s="32">
+    <row r="430" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="39">
         <v>268052</v>
       </c>
-      <c r="B430" s="15" t="s">
+      <c r="B430" s="40" t="s">
         <v>1783</v>
       </c>
-      <c r="C430" s="15" t="s">
+      <c r="C430" s="40" t="s">
         <v>1784</v>
       </c>
-      <c r="D430" s="15" t="s">
+      <c r="D430" s="40" t="s">
         <v>1785</v>
       </c>
-      <c r="E430" s="15" t="s">
+      <c r="E430" s="40" t="s">
         <v>1785</v>
       </c>
-      <c r="F430" s="6" t="s">
+      <c r="F430" s="41" t="s">
         <v>1781</v>
       </c>
-      <c r="G430" s="15" t="s">
+      <c r="G430" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H430" s="15" t="s">
+      <c r="H430" s="40" t="s">
         <v>1782</v>
       </c>
-      <c r="I430" s="15">
+      <c r="I430" s="40">
         <v>242032</v>
       </c>
-      <c r="J430" s="4">
+      <c r="J430" s="42">
         <v>37194</v>
       </c>
-      <c r="K430" s="4">
+      <c r="K430" s="42">
         <v>45839</v>
       </c>
-      <c r="L430" s="16"/>
-      <c r="M430" s="16"/>
-      <c r="N430" s="15" t="s">
+      <c r="L430" s="43"/>
+      <c r="M430" s="43"/>
+      <c r="N430" s="40" t="s">
         <v>1786</v>
       </c>
-      <c r="O430" s="15" t="s">
+      <c r="O430" s="40" t="s">
         <v>1787</v>
       </c>
-      <c r="P430" s="15"/>
-      <c r="Q430" s="15"/>
-      <c r="R430" s="15"/>
-      <c r="S430" s="15"/>
-      <c r="T430" s="15"/>
-      <c r="U430" s="17" t="s">
+      <c r="P430" s="40"/>
+      <c r="Q430" s="40"/>
+      <c r="R430" s="40"/>
+      <c r="S430" s="40"/>
+      <c r="T430" s="40"/>
+      <c r="U430" s="44" t="s">
         <v>3262</v>
       </c>
-      <c r="V430" s="15">
+      <c r="V430" s="40">
         <v>3</v>
       </c>
-      <c r="W430" s="15" t="s">
+      <c r="W430" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X430" s="15" t="s">
+      <c r="X430" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y430" s="15"/>
+      <c r="Y430" s="40"/>
     </row>
     <row r="431" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="32">
@@ -37378,7 +37446,9 @@
         <v>1945</v>
       </c>
       <c r="P431" s="15"/>
-      <c r="Q431" s="15"/>
+      <c r="Q431" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R431" s="15"/>
       <c r="S431" s="15"/>
       <c r="T431" s="15"/>
@@ -39906,7 +39976,9 @@
         <v>2024</v>
       </c>
       <c r="P475" s="15"/>
-      <c r="Q475" s="15"/>
+      <c r="Q475" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R475" s="15"/>
       <c r="S475" s="15" t="s">
         <v>102</v>
@@ -40731,70 +40803,70 @@
       </c>
       <c r="Y488" s="15"/>
     </row>
-    <row r="489" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A489" s="32">
+    <row r="489" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A489" s="39">
         <v>261037</v>
       </c>
-      <c r="B489" s="15" t="s">
+      <c r="B489" s="40" t="s">
         <v>2006</v>
       </c>
-      <c r="C489" s="15" t="s">
+      <c r="C489" s="40" t="s">
         <v>2007</v>
       </c>
-      <c r="D489" s="15" t="s">
+      <c r="D489" s="40" t="s">
         <v>2008</v>
       </c>
-      <c r="E489" s="15" t="s">
+      <c r="E489" s="40" t="s">
         <v>2008</v>
       </c>
-      <c r="F489" s="6" t="s">
+      <c r="F489" s="41" t="s">
         <v>2009</v>
       </c>
-      <c r="G489" s="15" t="s">
+      <c r="G489" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="H489" s="15" t="s">
+      <c r="H489" s="40" t="s">
         <v>1975</v>
       </c>
-      <c r="I489" s="15">
+      <c r="I489" s="40">
         <v>253014</v>
       </c>
-      <c r="J489" s="4">
+      <c r="J489" s="42">
         <v>34893</v>
       </c>
-      <c r="K489" s="4">
+      <c r="K489" s="42">
         <v>43420</v>
       </c>
-      <c r="L489" s="16"/>
-      <c r="M489" s="16"/>
-      <c r="N489" s="15" t="s">
+      <c r="L489" s="43"/>
+      <c r="M489" s="43"/>
+      <c r="N489" s="40" t="s">
         <v>2010</v>
       </c>
-      <c r="O489" s="15" t="s">
+      <c r="O489" s="40" t="s">
         <v>2011</v>
       </c>
-      <c r="P489" s="15"/>
-      <c r="Q489" s="15"/>
-      <c r="R489" s="15"/>
-      <c r="S489" s="15" t="s">
+      <c r="P489" s="40"/>
+      <c r="Q489" s="40"/>
+      <c r="R489" s="40"/>
+      <c r="S489" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="T489" s="15" t="s">
+      <c r="T489" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="U489" s="17" t="s">
+      <c r="U489" s="44" t="s">
         <v>3312</v>
       </c>
-      <c r="V489" s="15">
+      <c r="V489" s="40">
         <v>3</v>
       </c>
-      <c r="W489" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X489" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y489" s="15"/>
+      <c r="W489" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X489" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y489" s="40"/>
     </row>
     <row r="490" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="32">
@@ -40957,7 +41029,9 @@
         <v>2071</v>
       </c>
       <c r="P492" s="15"/>
-      <c r="Q492" s="15"/>
+      <c r="Q492" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R492" s="15"/>
       <c r="S492" s="15" t="s">
         <v>2072</v>
@@ -40979,127 +41053,127 @@
       </c>
       <c r="Y492" s="15"/>
     </row>
-    <row r="493" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A493" s="32">
+    <row r="493" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A493" s="39">
         <v>268020</v>
       </c>
-      <c r="B493" s="15" t="s">
+      <c r="B493" s="40" t="s">
         <v>2073</v>
       </c>
-      <c r="C493" s="15" t="s">
+      <c r="C493" s="40" t="s">
         <v>2074</v>
       </c>
-      <c r="D493" s="15" t="s">
+      <c r="D493" s="40" t="s">
         <v>2075</v>
       </c>
-      <c r="E493" s="15" t="s">
+      <c r="E493" s="40" t="s">
         <v>2075</v>
       </c>
-      <c r="F493" s="6" t="s">
+      <c r="F493" s="41" t="s">
         <v>2076</v>
       </c>
-      <c r="G493" s="15" t="s">
+      <c r="G493" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H493" s="15" t="s">
+      <c r="H493" s="40" t="s">
         <v>2069</v>
       </c>
-      <c r="I493" s="15">
+      <c r="I493" s="40">
         <v>248031</v>
       </c>
-      <c r="J493" s="4">
+      <c r="J493" s="42">
         <v>37154</v>
       </c>
-      <c r="K493" s="4">
+      <c r="K493" s="42">
         <v>45733</v>
       </c>
-      <c r="L493" s="16"/>
-      <c r="M493" s="16"/>
-      <c r="N493" s="15" t="s">
+      <c r="L493" s="43"/>
+      <c r="M493" s="43"/>
+      <c r="N493" s="40" t="s">
         <v>2077</v>
       </c>
-      <c r="O493" s="15" t="s">
+      <c r="O493" s="40" t="s">
         <v>2078</v>
       </c>
-      <c r="P493" s="15"/>
-      <c r="Q493" s="15"/>
-      <c r="R493" s="15"/>
-      <c r="S493" s="15"/>
-      <c r="T493" s="15"/>
-      <c r="U493" s="17" t="s">
+      <c r="P493" s="40"/>
+      <c r="Q493" s="40"/>
+      <c r="R493" s="40"/>
+      <c r="S493" s="40"/>
+      <c r="T493" s="40"/>
+      <c r="U493" s="44" t="s">
         <v>3316</v>
       </c>
-      <c r="V493" s="15">
+      <c r="V493" s="40">
         <v>3</v>
       </c>
-      <c r="W493" s="15" t="s">
+      <c r="W493" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X493" s="15" t="s">
+      <c r="X493" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y493" s="15"/>
-    </row>
-    <row r="494" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A494" s="32">
+      <c r="Y493" s="40"/>
+    </row>
+    <row r="494" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A494" s="39">
         <v>268077</v>
       </c>
-      <c r="B494" s="15" t="s">
+      <c r="B494" s="40" t="s">
         <v>2079</v>
       </c>
-      <c r="C494" s="15" t="s">
+      <c r="C494" s="40" t="s">
         <v>2080</v>
       </c>
-      <c r="D494" s="15" t="s">
+      <c r="D494" s="40" t="s">
         <v>2081</v>
       </c>
-      <c r="E494" s="15" t="s">
+      <c r="E494" s="40" t="s">
         <v>2081</v>
       </c>
-      <c r="F494" s="6" t="s">
+      <c r="F494" s="41" t="s">
         <v>2076</v>
       </c>
-      <c r="G494" s="15" t="s">
+      <c r="G494" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H494" s="15" t="s">
+      <c r="H494" s="40" t="s">
         <v>2069</v>
       </c>
-      <c r="I494" s="15">
+      <c r="I494" s="40">
         <v>248031</v>
       </c>
-      <c r="J494" s="4">
+      <c r="J494" s="42">
         <v>37828</v>
       </c>
-      <c r="K494" s="4">
+      <c r="K494" s="42">
         <v>45931</v>
       </c>
-      <c r="L494" s="16"/>
-      <c r="M494" s="16"/>
-      <c r="N494" s="15" t="s">
+      <c r="L494" s="43"/>
+      <c r="M494" s="43"/>
+      <c r="N494" s="40" t="s">
         <v>2082</v>
       </c>
-      <c r="O494" s="15" t="s">
+      <c r="O494" s="40" t="s">
         <v>2083</v>
       </c>
-      <c r="P494" s="15"/>
-      <c r="Q494" s="15"/>
-      <c r="R494" s="15"/>
-      <c r="S494" s="15"/>
-      <c r="T494" s="15"/>
-      <c r="U494" s="17" t="s">
+      <c r="P494" s="40"/>
+      <c r="Q494" s="40"/>
+      <c r="R494" s="40"/>
+      <c r="S494" s="40"/>
+      <c r="T494" s="40"/>
+      <c r="U494" s="44" t="s">
         <v>3317</v>
       </c>
-      <c r="V494" s="15">
+      <c r="V494" s="40">
         <v>3</v>
       </c>
-      <c r="W494" s="15" t="s">
+      <c r="W494" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X494" s="15" t="s">
+      <c r="X494" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y494" s="15"/>
+      <c r="Y494" s="40"/>
     </row>
     <row r="495" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="32">
@@ -41508,7 +41582,9 @@
         <v>2174</v>
       </c>
       <c r="P501" s="15"/>
-      <c r="Q501" s="15"/>
+      <c r="Q501" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R501" s="15"/>
       <c r="S501" s="15" t="s">
         <v>33</v>
@@ -41530,66 +41606,66 @@
       </c>
       <c r="Y501" s="15"/>
     </row>
-    <row r="502" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A502" s="32">
+    <row r="502" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A502" s="39">
         <v>268048</v>
       </c>
-      <c r="B502" s="15" t="s">
+      <c r="B502" s="40" t="s">
         <v>2175</v>
       </c>
-      <c r="C502" s="15" t="s">
+      <c r="C502" s="40" t="s">
         <v>2176</v>
       </c>
-      <c r="D502" s="15" t="s">
+      <c r="D502" s="40" t="s">
         <v>1960</v>
       </c>
-      <c r="E502" s="15" t="s">
+      <c r="E502" s="40" t="s">
         <v>1960</v>
       </c>
-      <c r="F502" s="6" t="s">
+      <c r="F502" s="41" t="s">
         <v>2177</v>
       </c>
-      <c r="G502" s="15" t="s">
+      <c r="G502" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H502" s="15" t="s">
+      <c r="H502" s="40" t="s">
         <v>2172</v>
       </c>
-      <c r="I502" s="15">
+      <c r="I502" s="40">
         <v>251007</v>
       </c>
-      <c r="J502" s="4">
+      <c r="J502" s="42">
         <v>34526</v>
       </c>
-      <c r="K502" s="4">
+      <c r="K502" s="42">
         <v>45824</v>
       </c>
-      <c r="L502" s="16"/>
-      <c r="M502" s="16"/>
-      <c r="N502" s="15" t="s">
+      <c r="L502" s="43"/>
+      <c r="M502" s="43"/>
+      <c r="N502" s="40" t="s">
         <v>2178</v>
       </c>
-      <c r="O502" s="15" t="s">
+      <c r="O502" s="40" t="s">
         <v>2179</v>
       </c>
-      <c r="P502" s="15"/>
-      <c r="Q502" s="15"/>
-      <c r="R502" s="15"/>
-      <c r="S502" s="15"/>
-      <c r="T502" s="15"/>
-      <c r="U502" s="17" t="s">
+      <c r="P502" s="40"/>
+      <c r="Q502" s="40"/>
+      <c r="R502" s="40"/>
+      <c r="S502" s="40"/>
+      <c r="T502" s="40"/>
+      <c r="U502" s="44" t="s">
         <v>3323</v>
       </c>
-      <c r="V502" s="15">
+      <c r="V502" s="40">
         <v>3</v>
       </c>
-      <c r="W502" s="15" t="s">
+      <c r="W502" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X502" s="15" t="s">
+      <c r="X502" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y502" s="15"/>
+      <c r="Y502" s="40"/>
     </row>
     <row r="503" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="32">
@@ -41774,66 +41850,66 @@
       </c>
       <c r="Y505" s="15"/>
     </row>
-    <row r="506" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A506" s="32">
+    <row r="506" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A506" s="39">
         <v>268002</v>
       </c>
-      <c r="B506" s="15" t="s">
+      <c r="B506" s="40" t="s">
         <v>2097</v>
       </c>
-      <c r="C506" s="15" t="s">
+      <c r="C506" s="40" t="s">
         <v>2098</v>
       </c>
-      <c r="D506" s="15" t="s">
+      <c r="D506" s="40" t="s">
         <v>2099</v>
       </c>
-      <c r="E506" s="15" t="s">
+      <c r="E506" s="40" t="s">
         <v>2099</v>
       </c>
-      <c r="F506" s="6" t="s">
+      <c r="F506" s="41" t="s">
         <v>2100</v>
       </c>
-      <c r="G506" s="15" t="s">
+      <c r="G506" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H506" s="15" t="s">
+      <c r="H506" s="40" t="s">
         <v>2086</v>
       </c>
-      <c r="I506" s="15">
+      <c r="I506" s="40">
         <v>251007</v>
       </c>
-      <c r="J506" s="4">
+      <c r="J506" s="42">
         <v>37198</v>
       </c>
-      <c r="K506" s="4">
+      <c r="K506" s="42">
         <v>45659</v>
       </c>
-      <c r="L506" s="16"/>
-      <c r="M506" s="16"/>
-      <c r="N506" s="15" t="s">
+      <c r="L506" s="43"/>
+      <c r="M506" s="43"/>
+      <c r="N506" s="40" t="s">
         <v>2101</v>
       </c>
-      <c r="O506" s="15" t="s">
+      <c r="O506" s="40" t="s">
         <v>2102</v>
       </c>
-      <c r="P506" s="15"/>
-      <c r="Q506" s="15"/>
-      <c r="R506" s="15"/>
-      <c r="S506" s="15"/>
-      <c r="T506" s="15"/>
-      <c r="U506" s="17" t="s">
+      <c r="P506" s="40"/>
+      <c r="Q506" s="40"/>
+      <c r="R506" s="40"/>
+      <c r="S506" s="40"/>
+      <c r="T506" s="40"/>
+      <c r="U506" s="44" t="s">
         <v>3327</v>
       </c>
-      <c r="V506" s="15">
+      <c r="V506" s="40">
         <v>3</v>
       </c>
-      <c r="W506" s="15" t="s">
+      <c r="W506" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X506" s="15" t="s">
+      <c r="X506" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y506" s="15"/>
+      <c r="Y506" s="40"/>
     </row>
     <row r="507" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="32">
@@ -41994,7 +42070,9 @@
         <v>2118</v>
       </c>
       <c r="P509" s="15"/>
-      <c r="Q509" s="15"/>
+      <c r="Q509" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R509" s="15"/>
       <c r="S509" s="15" t="s">
         <v>896</v>
@@ -42845,10 +42923,10 @@
         <v>2259</v>
       </c>
       <c r="D524" s="15" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="E524" s="15" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="F524" s="6" t="s">
         <v>2260</v>
@@ -42878,7 +42956,7 @@
       </c>
       <c r="P524" s="15"/>
       <c r="Q524" s="15" t="s">
-        <v>3408</v>
+        <v>3484</v>
       </c>
       <c r="R524" s="15"/>
       <c r="S524" s="15" t="s">
@@ -43133,7 +43211,9 @@
         <v>2207</v>
       </c>
       <c r="P528" s="15"/>
-      <c r="Q528" s="15"/>
+      <c r="Q528" s="15" t="s">
+        <v>3485</v>
+      </c>
       <c r="R528" s="15"/>
       <c r="S528" s="19" t="s">
         <v>2895</v>
@@ -43281,66 +43361,66 @@
       </c>
       <c r="Y530" s="15"/>
     </row>
-    <row r="531" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A531" s="32">
+    <row r="531" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A531" s="39">
         <v>267032</v>
       </c>
-      <c r="B531" s="15" t="s">
+      <c r="B531" s="40" t="s">
         <v>2219</v>
       </c>
-      <c r="C531" s="15" t="s">
+      <c r="C531" s="40" t="s">
         <v>2220</v>
       </c>
-      <c r="D531" s="15" t="s">
+      <c r="D531" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="E531" s="15" t="s">
+      <c r="E531" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="F531" s="6" t="s">
+      <c r="F531" s="41" t="s">
         <v>2880</v>
       </c>
-      <c r="G531" s="15" t="s">
+      <c r="G531" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="H531" s="15" t="s">
+      <c r="H531" s="40" t="s">
         <v>2190</v>
       </c>
-      <c r="I531" s="15">
+      <c r="I531" s="40">
         <v>257039</v>
       </c>
-      <c r="J531" s="4">
+      <c r="J531" s="42">
         <v>34641</v>
       </c>
-      <c r="K531" s="4">
+      <c r="K531" s="42">
         <v>45352</v>
       </c>
-      <c r="L531" s="16"/>
-      <c r="M531" s="16"/>
-      <c r="N531" s="15" t="s">
+      <c r="L531" s="43"/>
+      <c r="M531" s="43"/>
+      <c r="N531" s="40" t="s">
         <v>2221</v>
       </c>
-      <c r="O531" s="15" t="s">
+      <c r="O531" s="40" t="s">
         <v>2222</v>
       </c>
-      <c r="P531" s="15"/>
-      <c r="Q531" s="15"/>
-      <c r="R531" s="15"/>
-      <c r="S531" s="15"/>
-      <c r="T531" s="15"/>
-      <c r="U531" s="17" t="s">
+      <c r="P531" s="40"/>
+      <c r="Q531" s="40"/>
+      <c r="R531" s="40"/>
+      <c r="S531" s="40"/>
+      <c r="T531" s="40"/>
+      <c r="U531" s="44" t="s">
         <v>3348</v>
       </c>
-      <c r="V531" s="15">
+      <c r="V531" s="40">
         <v>2</v>
       </c>
-      <c r="W531" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X531" s="15" t="s">
+      <c r="W531" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="X531" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y531" s="15"/>
+      <c r="Y531" s="40"/>
     </row>
     <row r="532" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="32">
@@ -43503,7 +43583,9 @@
         <v>2237</v>
       </c>
       <c r="P534" s="15"/>
-      <c r="Q534" s="15"/>
+      <c r="Q534" s="15" t="s">
+        <v>3484</v>
+      </c>
       <c r="R534" s="15"/>
       <c r="S534" s="15" t="s">
         <v>651</v>
@@ -45463,8 +45545,8 @@
         <v>2340</v>
       </c>
       <c r="P566" s="26"/>
-      <c r="Q566" s="26" t="s">
-        <v>3409</v>
+      <c r="Q566" s="15" t="s">
+        <v>3484</v>
       </c>
       <c r="R566" s="26"/>
       <c r="S566" s="26"/>
@@ -45489,19 +45571,19 @@
         <v>169024</v>
       </c>
       <c r="B567" s="26" t="s">
-        <v>3416</v>
+        <v>3409</v>
       </c>
       <c r="C567" s="26" t="s">
-        <v>3417</v>
+        <v>3410</v>
       </c>
       <c r="D567" s="26" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="E567" s="26" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="F567" s="9" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G567" s="26" t="s">
         <v>2894</v>
@@ -45521,10 +45603,10 @@
       <c r="L567" s="28"/>
       <c r="M567" s="28"/>
       <c r="N567" s="26" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
       <c r="O567" s="26" t="s">
-        <v>3425</v>
+        <v>3418</v>
       </c>
       <c r="P567" s="26"/>
       <c r="Q567" s="26"/>
@@ -45542,7 +45624,7 @@
         <v>44</v>
       </c>
       <c r="Y567" s="26" t="s">
-        <v>3485</v>
+        <v>3478</v>
       </c>
       <c r="Z567" s="14"/>
     </row>
@@ -45585,14 +45667,14 @@
         <v>3396</v>
       </c>
       <c r="P568" s="26"/>
-      <c r="Q568" s="26" t="s">
-        <v>3404</v>
+      <c r="Q568" s="15" t="s">
+        <v>3485</v>
       </c>
       <c r="R568" s="26"/>
       <c r="S568" s="26"/>
       <c r="T568" s="26"/>
       <c r="U568" s="36" t="s">
-        <v>3488</v>
+        <v>3481</v>
       </c>
       <c r="V568" s="26">
         <v>3</v>
@@ -45649,8 +45731,8 @@
         <v>3401</v>
       </c>
       <c r="P569" s="26"/>
-      <c r="Q569" s="26" t="s">
-        <v>3409</v>
+      <c r="Q569" s="15" t="s">
+        <v>3484</v>
       </c>
       <c r="R569" s="26"/>
       <c r="S569" s="26"/>
@@ -45675,16 +45757,16 @@
         <v>269029</v>
       </c>
       <c r="B570" s="26" t="s">
-        <v>3465</v>
+        <v>3458</v>
       </c>
       <c r="C570" s="26" t="s">
-        <v>3436</v>
+        <v>3429</v>
       </c>
       <c r="D570" s="26" t="s">
-        <v>3427</v>
+        <v>3420</v>
       </c>
       <c r="E570" s="26" t="s">
-        <v>3427</v>
+        <v>3420</v>
       </c>
       <c r="F570" s="9" t="s">
         <v>1089</v>
@@ -45707,7 +45789,7 @@
       <c r="L570" s="28"/>
       <c r="M570" s="28"/>
       <c r="N570" s="26" t="s">
-        <v>3466</v>
+        <v>3459</v>
       </c>
       <c r="O570" s="26"/>
       <c r="P570" s="26"/>
@@ -45734,16 +45816,16 @@
         <v>269030</v>
       </c>
       <c r="B571" s="26" t="s">
-        <v>3453</v>
+        <v>3446</v>
       </c>
       <c r="C571" s="26" t="s">
-        <v>3437</v>
+        <v>3430</v>
       </c>
       <c r="D571" s="26" t="s">
-        <v>3428</v>
+        <v>3421</v>
       </c>
       <c r="E571" s="26" t="s">
-        <v>3428</v>
+        <v>3421</v>
       </c>
       <c r="F571" s="9" t="s">
         <v>1974</v>
@@ -45766,7 +45848,7 @@
       <c r="L571" s="28"/>
       <c r="M571" s="28"/>
       <c r="N571" s="26" t="s">
-        <v>3467</v>
+        <v>3460</v>
       </c>
       <c r="O571" s="26"/>
       <c r="P571" s="26"/>
@@ -45793,10 +45875,10 @@
         <v>169022</v>
       </c>
       <c r="B572" s="26" t="s">
-        <v>3462</v>
+        <v>3455</v>
       </c>
       <c r="C572" s="26" t="s">
-        <v>3438</v>
+        <v>3431</v>
       </c>
       <c r="D572" s="26" t="s">
         <v>243</v>
@@ -45825,10 +45907,10 @@
       <c r="L572" s="28"/>
       <c r="M572" s="28"/>
       <c r="N572" s="26" t="s">
-        <v>3468</v>
+        <v>3461</v>
       </c>
       <c r="O572" s="26" t="s">
-        <v>3479</v>
+        <v>3472</v>
       </c>
       <c r="P572" s="26"/>
       <c r="Q572" s="26"/>
@@ -45854,19 +45936,19 @@
         <v>269034</v>
       </c>
       <c r="B573" s="26" t="s">
-        <v>3463</v>
+        <v>3456</v>
       </c>
       <c r="C573" s="26" t="s">
-        <v>3439</v>
+        <v>3432</v>
       </c>
       <c r="D573" s="26" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="E573" s="26" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="F573" s="9" t="s">
-        <v>3449</v>
+        <v>3442</v>
       </c>
       <c r="G573" s="26" t="s">
         <v>71</v>
@@ -45886,10 +45968,10 @@
       <c r="L573" s="28"/>
       <c r="M573" s="28"/>
       <c r="N573" s="26" t="s">
-        <v>3469</v>
+        <v>3462</v>
       </c>
       <c r="O573" s="26" t="s">
-        <v>3480</v>
+        <v>3473</v>
       </c>
       <c r="P573" s="26"/>
       <c r="Q573" s="26"/>
@@ -45897,7 +45979,7 @@
       <c r="S573" s="26"/>
       <c r="T573" s="26"/>
       <c r="U573" s="36" t="s">
-        <v>3489</v>
+        <v>3482</v>
       </c>
       <c r="V573" s="26" t="s">
         <v>44</v>
@@ -45915,10 +45997,10 @@
         <v>269038</v>
       </c>
       <c r="B574" s="26" t="s">
-        <v>3454</v>
+        <v>3447</v>
       </c>
       <c r="C574" s="26" t="s">
-        <v>3440</v>
+        <v>3433</v>
       </c>
       <c r="D574" s="26" t="s">
         <v>689</v>
@@ -45947,7 +46029,7 @@
       <c r="L574" s="28"/>
       <c r="M574" s="28"/>
       <c r="N574" s="26" t="s">
-        <v>3470</v>
+        <v>3463</v>
       </c>
       <c r="O574" s="26"/>
       <c r="P574" s="26"/>
@@ -45969,82 +46051,82 @@
       </c>
       <c r="Y574" s="26"/>
     </row>
-    <row r="575" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="34">
+    <row r="575" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="39">
         <v>269033</v>
       </c>
-      <c r="B575" s="26" t="s">
-        <v>3455</v>
-      </c>
-      <c r="C575" s="26" t="s">
-        <v>3441</v>
-      </c>
-      <c r="D575" s="26" t="s">
-        <v>3430</v>
-      </c>
-      <c r="E575" s="26" t="s">
-        <v>3430</v>
-      </c>
-      <c r="F575" s="9" t="s">
-        <v>3450</v>
-      </c>
-      <c r="G575" s="26" t="s">
+      <c r="B575" s="40" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C575" s="40" t="s">
+        <v>3434</v>
+      </c>
+      <c r="D575" s="40" t="s">
+        <v>3423</v>
+      </c>
+      <c r="E575" s="40" t="s">
+        <v>3423</v>
+      </c>
+      <c r="F575" s="41" t="s">
+        <v>3443</v>
+      </c>
+      <c r="G575" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H575" s="26" t="s">
+      <c r="H575" s="40" t="s">
         <v>1376</v>
       </c>
-      <c r="I575" s="26">
+      <c r="I575" s="40">
         <v>256014</v>
       </c>
-      <c r="J575" s="10">
+      <c r="J575" s="42">
         <v>37980</v>
       </c>
-      <c r="K575" s="10">
+      <c r="K575" s="42">
         <v>46160</v>
       </c>
-      <c r="L575" s="28"/>
-      <c r="M575" s="28"/>
-      <c r="N575" s="26" t="s">
-        <v>3471</v>
-      </c>
-      <c r="O575" s="26" t="s">
-        <v>3481</v>
-      </c>
-      <c r="P575" s="26"/>
-      <c r="Q575" s="26"/>
-      <c r="R575" s="26"/>
-      <c r="S575" s="26"/>
-      <c r="T575" s="26"/>
-      <c r="U575" s="36" t="s">
-        <v>3490</v>
-      </c>
-      <c r="V575" s="26" t="s">
+      <c r="L575" s="43"/>
+      <c r="M575" s="43"/>
+      <c r="N575" s="40" t="s">
+        <v>3464</v>
+      </c>
+      <c r="O575" s="40" t="s">
+        <v>3474</v>
+      </c>
+      <c r="P575" s="40"/>
+      <c r="Q575" s="40"/>
+      <c r="R575" s="40"/>
+      <c r="S575" s="40"/>
+      <c r="T575" s="40"/>
+      <c r="U575" s="47" t="s">
+        <v>3483</v>
+      </c>
+      <c r="V575" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="W575" s="26" t="s">
+      <c r="W575" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X575" s="26" t="s">
+      <c r="X575" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y575" s="26"/>
+      <c r="Y575" s="40"/>
     </row>
     <row r="576" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="34">
         <v>269037</v>
       </c>
       <c r="B576" s="26" t="s">
-        <v>3456</v>
+        <v>3449</v>
       </c>
       <c r="C576" s="26" t="s">
-        <v>3442</v>
+        <v>3435</v>
       </c>
       <c r="D576" s="26" t="s">
-        <v>3431</v>
+        <v>3424</v>
       </c>
       <c r="E576" s="26" t="s">
-        <v>3431</v>
+        <v>3424</v>
       </c>
       <c r="F576" s="9" t="s">
         <v>1266</v>
@@ -46067,7 +46149,7 @@
       <c r="L576" s="28"/>
       <c r="M576" s="28"/>
       <c r="N576" s="26" t="s">
-        <v>3472</v>
+        <v>3465</v>
       </c>
       <c r="O576" s="26"/>
       <c r="P576" s="26"/>
@@ -46094,16 +46176,16 @@
         <v>269036</v>
       </c>
       <c r="B577" s="26" t="s">
-        <v>3457</v>
+        <v>3450</v>
       </c>
       <c r="C577" s="26" t="s">
-        <v>3443</v>
+        <v>3436</v>
       </c>
       <c r="D577" s="26" t="s">
-        <v>3432</v>
+        <v>3425</v>
       </c>
       <c r="E577" s="26" t="s">
-        <v>3432</v>
+        <v>3425</v>
       </c>
       <c r="F577" s="9" t="s">
         <v>1266</v>
@@ -46126,7 +46208,7 @@
       <c r="L577" s="28"/>
       <c r="M577" s="28"/>
       <c r="N577" s="26" t="s">
-        <v>3473</v>
+        <v>3466</v>
       </c>
       <c r="O577" s="26"/>
       <c r="P577" s="26"/>
@@ -46153,16 +46235,16 @@
         <v>269035</v>
       </c>
       <c r="B578" s="26" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="C578" s="26" t="s">
-        <v>3444</v>
+        <v>3437</v>
       </c>
       <c r="D578" s="26" t="s">
-        <v>3433</v>
+        <v>3426</v>
       </c>
       <c r="E578" s="26" t="s">
-        <v>3433</v>
+        <v>3426</v>
       </c>
       <c r="F578" s="9" t="s">
         <v>1797</v>
@@ -46185,7 +46267,7 @@
       <c r="L578" s="28"/>
       <c r="M578" s="28"/>
       <c r="N578" s="26" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
       <c r="O578" s="26"/>
       <c r="P578" s="26"/>
@@ -46212,10 +46294,10 @@
         <v>269039</v>
       </c>
       <c r="B579" s="26" t="s">
-        <v>3464</v>
+        <v>3457</v>
       </c>
       <c r="C579" s="26" t="s">
-        <v>3445</v>
+        <v>3438</v>
       </c>
       <c r="D579" s="26" t="s">
         <v>713</v>
@@ -46224,7 +46306,7 @@
         <v>713</v>
       </c>
       <c r="F579" s="9" t="s">
-        <v>3451</v>
+        <v>3444</v>
       </c>
       <c r="G579" s="26" t="s">
         <v>40</v>
@@ -46244,10 +46326,10 @@
       <c r="L579" s="28"/>
       <c r="M579" s="28"/>
       <c r="N579" s="26" t="s">
+        <v>3468</v>
+      </c>
+      <c r="O579" s="26" t="s">
         <v>3475</v>
-      </c>
-      <c r="O579" s="26" t="s">
-        <v>3482</v>
       </c>
       <c r="P579" s="26"/>
       <c r="Q579" s="26"/>
@@ -46273,16 +46355,16 @@
         <v>269043</v>
       </c>
       <c r="B580" s="26" t="s">
-        <v>3459</v>
+        <v>3452</v>
       </c>
       <c r="C580" s="26" t="s">
-        <v>3446</v>
+        <v>3439</v>
       </c>
       <c r="D580" s="26" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
       <c r="E580" s="26" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
       <c r="F580" s="9" t="s">
         <v>1266</v>
@@ -46291,7 +46373,7 @@
         <v>779</v>
       </c>
       <c r="H580" s="26" t="s">
-        <v>3484</v>
+        <v>3477</v>
       </c>
       <c r="I580" s="26">
         <v>267096</v>
@@ -46305,7 +46387,7 @@
       <c r="L580" s="28"/>
       <c r="M580" s="28"/>
       <c r="N580" s="26" t="s">
-        <v>3476</v>
+        <v>3469</v>
       </c>
       <c r="O580" s="26"/>
       <c r="P580" s="26"/>
@@ -46327,76 +46409,76 @@
       </c>
       <c r="Y580" s="26"/>
     </row>
-    <row r="581" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A581" s="34">
+    <row r="581" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A581" s="39">
         <v>269041</v>
       </c>
-      <c r="B581" s="26" t="s">
-        <v>3460</v>
-      </c>
-      <c r="C581" s="26" t="s">
-        <v>3447</v>
-      </c>
-      <c r="D581" s="26" t="s">
+      <c r="B581" s="40" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C581" s="40" t="s">
+        <v>3440</v>
+      </c>
+      <c r="D581" s="40" t="s">
         <v>1381</v>
       </c>
-      <c r="E581" s="26" t="s">
+      <c r="E581" s="40" t="s">
         <v>1381</v>
       </c>
-      <c r="F581" s="9" t="s">
-        <v>3452</v>
-      </c>
-      <c r="G581" s="26" t="s">
-        <v>3435</v>
-      </c>
-      <c r="H581" s="26" t="s">
+      <c r="F581" s="41" t="s">
+        <v>3445</v>
+      </c>
+      <c r="G581" s="40" t="s">
+        <v>3428</v>
+      </c>
+      <c r="H581" s="40" t="s">
         <v>1782</v>
       </c>
-      <c r="I581" s="26">
+      <c r="I581" s="40">
         <v>242032</v>
       </c>
-      <c r="J581" s="10">
+      <c r="J581" s="42">
         <v>35824</v>
       </c>
-      <c r="K581" s="10">
+      <c r="K581" s="42">
         <v>46177</v>
       </c>
-      <c r="L581" s="28"/>
-      <c r="M581" s="28"/>
-      <c r="N581" s="26" t="s">
-        <v>3477</v>
-      </c>
-      <c r="O581" s="26" t="s">
-        <v>3483</v>
-      </c>
-      <c r="P581" s="26"/>
-      <c r="Q581" s="26"/>
-      <c r="R581" s="26"/>
-      <c r="S581" s="26"/>
-      <c r="T581" s="26"/>
-      <c r="U581" s="36" t="s">
+      <c r="L581" s="43"/>
+      <c r="M581" s="43"/>
+      <c r="N581" s="40" t="s">
+        <v>3470</v>
+      </c>
+      <c r="O581" s="40" t="s">
+        <v>3476</v>
+      </c>
+      <c r="P581" s="40"/>
+      <c r="Q581" s="40"/>
+      <c r="R581" s="40"/>
+      <c r="S581" s="40"/>
+      <c r="T581" s="40"/>
+      <c r="U581" s="47" t="s">
         <v>3135</v>
       </c>
-      <c r="V581" s="26" t="s">
+      <c r="V581" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="W581" s="26" t="s">
+      <c r="W581" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="X581" s="26" t="s">
+      <c r="X581" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Y581" s="26"/>
+      <c r="Y581" s="40"/>
     </row>
     <row r="582" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="34">
         <v>269042</v>
       </c>
       <c r="B582" s="26" t="s">
-        <v>3461</v>
+        <v>3454</v>
       </c>
       <c r="C582" s="26" t="s">
-        <v>3448</v>
+        <v>3441</v>
       </c>
       <c r="D582" s="26" t="s">
         <v>1780</v>
@@ -46425,7 +46507,7 @@
       <c r="L582" s="28"/>
       <c r="M582" s="28"/>
       <c r="N582" s="26" t="s">
-        <v>3478</v>
+        <v>3471</v>
       </c>
       <c r="O582" s="26"/>
       <c r="P582" s="26"/>
@@ -47476,7 +47558,7 @@
     </row>
     <row r="51" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>3424</v>
+        <v>3417</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>2770</v>
@@ -47505,7 +47587,7 @@
         <v>2770</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>3424</v>
+        <v>3417</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>34</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F83A7B2-1983-44F4-8D5A-93926C979D50}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:1_{637E4DE2-FF7F-4914-92A4-20424EF3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642BBED7-E1A2-48D1-A7BC-68361B6AB039}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7746" uniqueCount="3486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7739" uniqueCount="3486">
   <si>
     <t>emp_id</t>
   </si>
@@ -10756,12 +10756,6 @@
     <xf numFmtId="10" fontId="6" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10787,6 +10781,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11145,32 +11145,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="46" t="s">
         <v>3479</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -22734,9 +22734,7 @@
         <v>2306</v>
       </c>
       <c r="P189" s="15"/>
-      <c r="Q189" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q189" s="15"/>
       <c r="R189" s="15"/>
       <c r="S189" s="19" t="s">
         <v>2895</v>
@@ -22801,9 +22799,7 @@
         <v>2311</v>
       </c>
       <c r="P190" s="15"/>
-      <c r="Q190" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q190" s="15"/>
       <c r="R190" s="15"/>
       <c r="S190" s="15" t="s">
         <v>1459</v>
@@ -22868,9 +22864,7 @@
         <v>2315</v>
       </c>
       <c r="P191" s="15"/>
-      <c r="Q191" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q191" s="15"/>
       <c r="R191" s="15"/>
       <c r="S191" s="15" t="s">
         <v>883</v>
@@ -22935,9 +22929,7 @@
         <v>2319</v>
       </c>
       <c r="P192" s="15"/>
-      <c r="Q192" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q192" s="15"/>
       <c r="R192" s="15"/>
       <c r="S192" s="15" t="s">
         <v>1459</v>
@@ -23002,9 +22994,7 @@
         <v>2323</v>
       </c>
       <c r="P193" s="15"/>
-      <c r="Q193" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q193" s="15"/>
       <c r="R193" s="15"/>
       <c r="S193" s="15" t="s">
         <v>1295</v>
@@ -23069,9 +23059,7 @@
         <v>2328</v>
       </c>
       <c r="P194" s="15"/>
-      <c r="Q194" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q194" s="15"/>
       <c r="R194" s="15"/>
       <c r="S194" s="15" t="s">
         <v>277</v>
@@ -23136,9 +23124,7 @@
         <v>2333</v>
       </c>
       <c r="P195" s="15"/>
-      <c r="Q195" s="15" t="s">
-        <v>3485</v>
-      </c>
+      <c r="Q195" s="15"/>
       <c r="R195" s="15"/>
       <c r="S195" s="15" t="s">
         <v>441</v>
@@ -23546,133 +23532,133 @@
       </c>
       <c r="Y201" s="15"/>
     </row>
-    <row r="202" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="39">
+    <row r="202" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="37">
         <v>264066</v>
       </c>
-      <c r="B202" s="40" t="s">
+      <c r="B202" s="38" t="s">
         <v>801</v>
       </c>
-      <c r="C202" s="40" t="s">
+      <c r="C202" s="38" t="s">
         <v>802</v>
       </c>
-      <c r="D202" s="40" t="s">
+      <c r="D202" s="38" t="s">
         <v>803</v>
       </c>
-      <c r="E202" s="40" t="s">
+      <c r="E202" s="38" t="s">
         <v>803</v>
       </c>
-      <c r="F202" s="41" t="s">
+      <c r="F202" s="39" t="s">
         <v>804</v>
       </c>
-      <c r="G202" s="40" t="s">
+      <c r="G202" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H202" s="40" t="s">
+      <c r="H202" s="38" t="s">
         <v>805</v>
       </c>
-      <c r="I202" s="40">
+      <c r="I202" s="38">
         <v>250042</v>
       </c>
-      <c r="J202" s="42">
+      <c r="J202" s="40">
         <v>36285</v>
       </c>
-      <c r="K202" s="42">
+      <c r="K202" s="40">
         <v>44440</v>
       </c>
-      <c r="L202" s="43"/>
-      <c r="M202" s="43"/>
-      <c r="N202" s="40" t="s">
+      <c r="L202" s="41"/>
+      <c r="M202" s="41"/>
+      <c r="N202" s="38" t="s">
         <v>806</v>
       </c>
-      <c r="O202" s="40" t="s">
+      <c r="O202" s="38" t="s">
         <v>807</v>
       </c>
-      <c r="P202" s="40"/>
-      <c r="Q202" s="40"/>
-      <c r="R202" s="40"/>
-      <c r="S202" s="40" t="s">
+      <c r="P202" s="38"/>
+      <c r="Q202" s="38"/>
+      <c r="R202" s="38"/>
+      <c r="S202" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="T202" s="40" t="s">
+      <c r="T202" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="U202" s="44" t="s">
+      <c r="U202" s="42" t="s">
         <v>3080</v>
       </c>
-      <c r="V202" s="40">
+      <c r="V202" s="38">
         <v>4</v>
       </c>
-      <c r="W202" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X202" s="40" t="s">
+      <c r="W202" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X202" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="Y202" s="40"/>
-    </row>
-    <row r="203" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="39">
+      <c r="Y202" s="38"/>
+    </row>
+    <row r="203" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="37">
         <v>266086</v>
       </c>
-      <c r="B203" s="40" t="s">
+      <c r="B203" s="38" t="s">
         <v>808</v>
       </c>
-      <c r="C203" s="40" t="s">
+      <c r="C203" s="38" t="s">
         <v>809</v>
       </c>
-      <c r="D203" s="40" t="s">
+      <c r="D203" s="38" t="s">
         <v>810</v>
       </c>
-      <c r="E203" s="40" t="s">
+      <c r="E203" s="38" t="s">
         <v>810</v>
       </c>
-      <c r="F203" s="41" t="s">
+      <c r="F203" s="39" t="s">
         <v>804</v>
       </c>
-      <c r="G203" s="40" t="s">
+      <c r="G203" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H203" s="40" t="s">
+      <c r="H203" s="38" t="s">
         <v>805</v>
       </c>
-      <c r="I203" s="40">
+      <c r="I203" s="38">
         <v>264090</v>
       </c>
-      <c r="J203" s="42">
+      <c r="J203" s="40">
         <v>36896</v>
       </c>
-      <c r="K203" s="42">
+      <c r="K203" s="40">
         <v>45187</v>
       </c>
-      <c r="L203" s="43"/>
-      <c r="M203" s="43"/>
-      <c r="N203" s="40" t="s">
+      <c r="L203" s="41"/>
+      <c r="M203" s="41"/>
+      <c r="N203" s="38" t="s">
         <v>811</v>
       </c>
-      <c r="O203" s="40" t="s">
+      <c r="O203" s="38" t="s">
         <v>812</v>
       </c>
-      <c r="P203" s="40"/>
-      <c r="Q203" s="40"/>
-      <c r="R203" s="40"/>
-      <c r="S203" s="46" t="s">
+      <c r="P203" s="38"/>
+      <c r="Q203" s="38"/>
+      <c r="R203" s="38"/>
+      <c r="S203" s="44" t="s">
         <v>2895</v>
       </c>
-      <c r="T203" s="40"/>
-      <c r="U203" s="44" t="s">
+      <c r="T203" s="38"/>
+      <c r="U203" s="42" t="s">
         <v>3081</v>
       </c>
-      <c r="V203" s="40">
+      <c r="V203" s="38">
         <v>3</v>
       </c>
-      <c r="W203" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X203" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y203" s="40"/>
+      <c r="W203" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X203" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y203" s="38"/>
     </row>
     <row r="204" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="32">
@@ -26062,133 +26048,133 @@
       </c>
       <c r="Y243" s="15"/>
     </row>
-    <row r="244" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="39">
+    <row r="244" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="37">
         <v>265019</v>
       </c>
-      <c r="B244" s="40" t="s">
+      <c r="B244" s="38" t="s">
         <v>987</v>
       </c>
-      <c r="C244" s="40" t="s">
+      <c r="C244" s="38" t="s">
         <v>988</v>
       </c>
-      <c r="D244" s="40" t="s">
+      <c r="D244" s="38" t="s">
         <v>989</v>
       </c>
-      <c r="E244" s="40" t="s">
+      <c r="E244" s="38" t="s">
         <v>989</v>
       </c>
-      <c r="F244" s="41" t="s">
+      <c r="F244" s="39" t="s">
         <v>990</v>
       </c>
-      <c r="G244" s="40" t="s">
+      <c r="G244" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H244" s="40" t="s">
+      <c r="H244" s="38" t="s">
         <v>928</v>
       </c>
-      <c r="I244" s="40">
+      <c r="I244" s="38">
         <v>233034</v>
       </c>
-      <c r="J244" s="42">
+      <c r="J244" s="40">
         <v>36039</v>
       </c>
-      <c r="K244" s="42">
+      <c r="K244" s="40">
         <v>44608</v>
       </c>
-      <c r="L244" s="43"/>
-      <c r="M244" s="43"/>
-      <c r="N244" s="40" t="s">
+      <c r="L244" s="41"/>
+      <c r="M244" s="41"/>
+      <c r="N244" s="38" t="s">
         <v>991</v>
       </c>
-      <c r="O244" s="40" t="s">
+      <c r="O244" s="38" t="s">
         <v>992</v>
       </c>
-      <c r="P244" s="40"/>
-      <c r="Q244" s="40"/>
-      <c r="R244" s="40"/>
-      <c r="S244" s="40" t="s">
+      <c r="P244" s="38"/>
+      <c r="Q244" s="38"/>
+      <c r="R244" s="38"/>
+      <c r="S244" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="T244" s="40" t="s">
+      <c r="T244" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="U244" s="44" t="s">
+      <c r="U244" s="42" t="s">
         <v>3117</v>
       </c>
-      <c r="V244" s="40">
+      <c r="V244" s="38">
         <v>3</v>
       </c>
-      <c r="W244" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X244" s="40" t="s">
+      <c r="W244" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X244" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="Y244" s="40"/>
-    </row>
-    <row r="245" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="39">
+      <c r="Y244" s="38"/>
+    </row>
+    <row r="245" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="37">
         <v>265047</v>
       </c>
-      <c r="B245" s="40" t="s">
+      <c r="B245" s="38" t="s">
         <v>993</v>
       </c>
-      <c r="C245" s="40" t="s">
+      <c r="C245" s="38" t="s">
         <v>994</v>
       </c>
-      <c r="D245" s="40" t="s">
+      <c r="D245" s="38" t="s">
         <v>995</v>
       </c>
-      <c r="E245" s="40" t="s">
+      <c r="E245" s="38" t="s">
         <v>995</v>
       </c>
-      <c r="F245" s="41" t="s">
+      <c r="F245" s="39" t="s">
         <v>990</v>
       </c>
-      <c r="G245" s="40" t="s">
+      <c r="G245" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H245" s="40" t="s">
+      <c r="H245" s="38" t="s">
         <v>928</v>
       </c>
-      <c r="I245" s="40">
+      <c r="I245" s="38">
         <v>268013</v>
       </c>
-      <c r="J245" s="42">
+      <c r="J245" s="40">
         <v>35453</v>
       </c>
-      <c r="K245" s="42">
+      <c r="K245" s="40">
         <v>44652</v>
       </c>
-      <c r="L245" s="43"/>
-      <c r="M245" s="43"/>
-      <c r="N245" s="40" t="s">
+      <c r="L245" s="41"/>
+      <c r="M245" s="41"/>
+      <c r="N245" s="38" t="s">
         <v>996</v>
       </c>
-      <c r="O245" s="40" t="s">
+      <c r="O245" s="38" t="s">
         <v>997</v>
       </c>
-      <c r="P245" s="40"/>
-      <c r="Q245" s="40"/>
-      <c r="R245" s="40"/>
-      <c r="S245" s="40" t="s">
+      <c r="P245" s="38"/>
+      <c r="Q245" s="38"/>
+      <c r="R245" s="38"/>
+      <c r="S245" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="T245" s="40"/>
-      <c r="U245" s="44" t="s">
+      <c r="T245" s="38"/>
+      <c r="U245" s="42" t="s">
         <v>3118</v>
       </c>
-      <c r="V245" s="40">
+      <c r="V245" s="38">
         <v>3</v>
       </c>
-      <c r="W245" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X245" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y245" s="40"/>
+      <c r="W245" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X245" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y245" s="38"/>
     </row>
     <row r="246" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="32">
@@ -28268,66 +28254,66 @@
       </c>
       <c r="Y279" s="15"/>
     </row>
-    <row r="280" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="39">
+    <row r="280" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="37">
         <v>267035</v>
       </c>
-      <c r="B280" s="40" t="s">
+      <c r="B280" s="38" t="s">
         <v>1159</v>
       </c>
-      <c r="C280" s="40" t="s">
+      <c r="C280" s="38" t="s">
         <v>1160</v>
       </c>
-      <c r="D280" s="40" t="s">
+      <c r="D280" s="38" t="s">
         <v>1161</v>
       </c>
-      <c r="E280" s="40" t="s">
+      <c r="E280" s="38" t="s">
         <v>1161</v>
       </c>
-      <c r="F280" s="41" t="s">
+      <c r="F280" s="39" t="s">
         <v>1162</v>
       </c>
-      <c r="G280" s="40" t="s">
+      <c r="G280" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H280" s="40" t="s">
+      <c r="H280" s="38" t="s">
         <v>1072</v>
       </c>
-      <c r="I280" s="40">
+      <c r="I280" s="38">
         <v>268012</v>
       </c>
-      <c r="J280" s="42">
+      <c r="J280" s="40">
         <v>36912</v>
       </c>
-      <c r="K280" s="42">
+      <c r="K280" s="40">
         <v>45366</v>
       </c>
-      <c r="L280" s="43"/>
-      <c r="M280" s="43"/>
-      <c r="N280" s="40" t="s">
+      <c r="L280" s="41"/>
+      <c r="M280" s="41"/>
+      <c r="N280" s="38" t="s">
         <v>1163</v>
       </c>
-      <c r="O280" s="40" t="s">
+      <c r="O280" s="38" t="s">
         <v>1164</v>
       </c>
-      <c r="P280" s="40"/>
-      <c r="Q280" s="40"/>
-      <c r="R280" s="40"/>
-      <c r="S280" s="40"/>
-      <c r="T280" s="40"/>
-      <c r="U280" s="44" t="s">
+      <c r="P280" s="38"/>
+      <c r="Q280" s="38"/>
+      <c r="R280" s="38"/>
+      <c r="S280" s="38"/>
+      <c r="T280" s="38"/>
+      <c r="U280" s="42" t="s">
         <v>3149</v>
       </c>
-      <c r="V280" s="40">
+      <c r="V280" s="38">
         <v>3</v>
       </c>
-      <c r="W280" s="40" t="s">
+      <c r="W280" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="X280" s="40" t="s">
+      <c r="X280" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y280" s="40"/>
+      <c r="Y280" s="38"/>
     </row>
     <row r="281" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="32">
@@ -28689,66 +28675,66 @@
       </c>
       <c r="Y286" s="15"/>
     </row>
-    <row r="287" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="39">
+    <row r="287" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="37">
         <v>269011</v>
       </c>
-      <c r="B287" s="40" t="s">
+      <c r="B287" s="38" t="s">
         <v>1190</v>
       </c>
-      <c r="C287" s="40" t="s">
+      <c r="C287" s="38" t="s">
         <v>1191</v>
       </c>
-      <c r="D287" s="40" t="s">
+      <c r="D287" s="38" t="s">
         <v>1192</v>
       </c>
-      <c r="E287" s="40" t="s">
+      <c r="E287" s="38" t="s">
         <v>1192</v>
       </c>
-      <c r="F287" s="41" t="s">
+      <c r="F287" s="39" t="s">
         <v>1162</v>
       </c>
-      <c r="G287" s="40" t="s">
+      <c r="G287" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H287" s="40" t="s">
+      <c r="H287" s="38" t="s">
         <v>1072</v>
       </c>
-      <c r="I287" s="40">
+      <c r="I287" s="38">
         <v>268012</v>
       </c>
-      <c r="J287" s="42">
+      <c r="J287" s="40">
         <v>36580</v>
       </c>
-      <c r="K287" s="42">
+      <c r="K287" s="40">
         <v>46069</v>
       </c>
-      <c r="L287" s="43"/>
-      <c r="M287" s="43"/>
-      <c r="N287" s="40" t="s">
+      <c r="L287" s="41"/>
+      <c r="M287" s="41"/>
+      <c r="N287" s="38" t="s">
         <v>1193</v>
       </c>
-      <c r="O287" s="40" t="s">
+      <c r="O287" s="38" t="s">
         <v>1194</v>
       </c>
-      <c r="P287" s="40"/>
-      <c r="Q287" s="40"/>
-      <c r="R287" s="40"/>
-      <c r="S287" s="40"/>
-      <c r="T287" s="40"/>
-      <c r="U287" s="44" t="s">
+      <c r="P287" s="38"/>
+      <c r="Q287" s="38"/>
+      <c r="R287" s="38"/>
+      <c r="S287" s="38"/>
+      <c r="T287" s="38"/>
+      <c r="U287" s="42" t="s">
         <v>2919</v>
       </c>
-      <c r="V287" s="40" t="s">
+      <c r="V287" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="W287" s="40" t="s">
+      <c r="W287" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X287" s="40" t="s">
+      <c r="X287" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y287" s="40"/>
+      <c r="Y287" s="38"/>
     </row>
     <row r="288" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="32">
@@ -29317,68 +29303,68 @@
       </c>
       <c r="Y296" s="15"/>
     </row>
-    <row r="297" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="39">
+    <row r="297" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A297" s="37">
         <v>266057</v>
       </c>
-      <c r="B297" s="40" t="s">
+      <c r="B297" s="38" t="s">
         <v>1241</v>
       </c>
-      <c r="C297" s="40" t="s">
+      <c r="C297" s="38" t="s">
         <v>1242</v>
       </c>
-      <c r="D297" s="40" t="s">
+      <c r="D297" s="38" t="s">
         <v>1243</v>
       </c>
-      <c r="E297" s="40" t="s">
+      <c r="E297" s="38" t="s">
         <v>1243</v>
       </c>
-      <c r="F297" s="41" t="s">
+      <c r="F297" s="39" t="s">
         <v>1244</v>
       </c>
-      <c r="G297" s="40" t="s">
+      <c r="G297" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H297" s="40" t="s">
+      <c r="H297" s="38" t="s">
         <v>1203</v>
       </c>
-      <c r="I297" s="40">
+      <c r="I297" s="38">
         <v>238030</v>
       </c>
-      <c r="J297" s="42">
+      <c r="J297" s="40">
         <v>35977</v>
       </c>
-      <c r="K297" s="42">
+      <c r="K297" s="40">
         <v>45078</v>
       </c>
-      <c r="L297" s="43"/>
-      <c r="M297" s="43"/>
-      <c r="N297" s="40" t="s">
+      <c r="L297" s="41"/>
+      <c r="M297" s="41"/>
+      <c r="N297" s="38" t="s">
         <v>1245</v>
       </c>
-      <c r="O297" s="40" t="s">
+      <c r="O297" s="38" t="s">
         <v>1246</v>
       </c>
-      <c r="P297" s="40"/>
-      <c r="Q297" s="40"/>
-      <c r="R297" s="40"/>
-      <c r="S297" s="40" t="s">
+      <c r="P297" s="38"/>
+      <c r="Q297" s="38"/>
+      <c r="R297" s="38"/>
+      <c r="S297" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="T297" s="40"/>
-      <c r="U297" s="44" t="s">
+      <c r="T297" s="38"/>
+      <c r="U297" s="42" t="s">
         <v>3163</v>
       </c>
-      <c r="V297" s="40">
+      <c r="V297" s="38">
         <v>4</v>
       </c>
-      <c r="W297" s="40" t="s">
+      <c r="W297" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="X297" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y297" s="40"/>
+      <c r="X297" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y297" s="38"/>
     </row>
     <row r="298" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="32">
@@ -33236,66 +33222,66 @@
       </c>
       <c r="Y361" s="15"/>
     </row>
-    <row r="362" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A362" s="39">
+    <row r="362" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A362" s="37">
         <v>268074</v>
       </c>
-      <c r="B362" s="40" t="s">
+      <c r="B362" s="38" t="s">
         <v>1511</v>
       </c>
-      <c r="C362" s="40" t="s">
+      <c r="C362" s="38" t="s">
         <v>1512</v>
       </c>
-      <c r="D362" s="40" t="s">
+      <c r="D362" s="38" t="s">
         <v>1023</v>
       </c>
-      <c r="E362" s="40" t="s">
+      <c r="E362" s="38" t="s">
         <v>1023</v>
       </c>
-      <c r="F362" s="41" t="s">
+      <c r="F362" s="39" t="s">
         <v>1513</v>
       </c>
-      <c r="G362" s="40" t="s">
+      <c r="G362" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H362" s="40" t="s">
+      <c r="H362" s="38" t="s">
         <v>1481</v>
       </c>
-      <c r="I362" s="40">
+      <c r="I362" s="38">
         <v>254057</v>
       </c>
-      <c r="J362" s="42">
+      <c r="J362" s="40">
         <v>37531</v>
       </c>
-      <c r="K362" s="42">
+      <c r="K362" s="40">
         <v>45901</v>
       </c>
-      <c r="L362" s="43"/>
-      <c r="M362" s="43"/>
-      <c r="N362" s="40" t="s">
+      <c r="L362" s="41"/>
+      <c r="M362" s="41"/>
+      <c r="N362" s="38" t="s">
         <v>1514</v>
       </c>
-      <c r="O362" s="40" t="s">
+      <c r="O362" s="38" t="s">
         <v>1515</v>
       </c>
-      <c r="P362" s="40"/>
-      <c r="Q362" s="40"/>
-      <c r="R362" s="40"/>
-      <c r="S362" s="40"/>
-      <c r="T362" s="40"/>
-      <c r="U362" s="44" t="s">
+      <c r="P362" s="38"/>
+      <c r="Q362" s="38"/>
+      <c r="R362" s="38"/>
+      <c r="S362" s="38"/>
+      <c r="T362" s="38"/>
+      <c r="U362" s="42" t="s">
         <v>3216</v>
       </c>
-      <c r="V362" s="40">
+      <c r="V362" s="38">
         <v>3</v>
       </c>
-      <c r="W362" s="40" t="s">
+      <c r="W362" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X362" s="40" t="s">
+      <c r="X362" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y362" s="40"/>
+      <c r="Y362" s="38"/>
     </row>
     <row r="363" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="32">
@@ -36974,68 +36960,68 @@
       </c>
       <c r="Y423" s="15"/>
     </row>
-    <row r="424" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A424" s="39">
+    <row r="424" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="37">
         <v>265126</v>
       </c>
-      <c r="B424" s="40" t="s">
+      <c r="B424" s="38" t="s">
         <v>1748</v>
       </c>
-      <c r="C424" s="40" t="s">
+      <c r="C424" s="38" t="s">
         <v>1749</v>
       </c>
-      <c r="D424" s="40" t="s">
+      <c r="D424" s="38" t="s">
         <v>1750</v>
       </c>
-      <c r="E424" s="40" t="s">
+      <c r="E424" s="38" t="s">
         <v>1750</v>
       </c>
-      <c r="F424" s="41" t="s">
+      <c r="F424" s="39" t="s">
         <v>1751</v>
       </c>
-      <c r="G424" s="40" t="s">
+      <c r="G424" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H424" s="40" t="s">
+      <c r="H424" s="38" t="s">
         <v>1729</v>
       </c>
-      <c r="I424" s="40">
+      <c r="I424" s="38">
         <v>267096</v>
       </c>
-      <c r="J424" s="42">
+      <c r="J424" s="40">
         <v>34949</v>
       </c>
-      <c r="K424" s="42">
+      <c r="K424" s="40">
         <v>44881</v>
       </c>
-      <c r="L424" s="43"/>
-      <c r="M424" s="43"/>
-      <c r="N424" s="40" t="s">
+      <c r="L424" s="41"/>
+      <c r="M424" s="41"/>
+      <c r="N424" s="38" t="s">
         <v>1752</v>
       </c>
-      <c r="O424" s="40" t="s">
+      <c r="O424" s="38" t="s">
         <v>1753</v>
       </c>
-      <c r="P424" s="40"/>
-      <c r="Q424" s="40"/>
-      <c r="R424" s="40"/>
-      <c r="S424" s="40" t="s">
+      <c r="P424" s="38"/>
+      <c r="Q424" s="38"/>
+      <c r="R424" s="38"/>
+      <c r="S424" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="T424" s="40"/>
-      <c r="U424" s="44" t="s">
+      <c r="T424" s="38"/>
+      <c r="U424" s="42" t="s">
         <v>3118</v>
       </c>
-      <c r="V424" s="40">
+      <c r="V424" s="38">
         <v>4</v>
       </c>
-      <c r="W424" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X424" s="40" t="s">
+      <c r="W424" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X424" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="Y424" s="40"/>
+      <c r="Y424" s="38"/>
     </row>
     <row r="425" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="32">
@@ -37096,66 +37082,66 @@
       </c>
       <c r="Y425" s="15"/>
     </row>
-    <row r="426" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A426" s="39">
+    <row r="426" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A426" s="37">
         <v>267072</v>
       </c>
-      <c r="B426" s="40" t="s">
+      <c r="B426" s="38" t="s">
         <v>1757</v>
       </c>
-      <c r="C426" s="40" t="s">
+      <c r="C426" s="38" t="s">
         <v>1758</v>
       </c>
-      <c r="D426" s="40" t="s">
+      <c r="D426" s="38" t="s">
         <v>1232</v>
       </c>
-      <c r="E426" s="40" t="s">
+      <c r="E426" s="38" t="s">
         <v>1232</v>
       </c>
-      <c r="F426" s="41" t="s">
+      <c r="F426" s="39" t="s">
         <v>1751</v>
       </c>
-      <c r="G426" s="40" t="s">
+      <c r="G426" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H426" s="40" t="s">
+      <c r="H426" s="38" t="s">
         <v>1729</v>
       </c>
-      <c r="I426" s="40">
+      <c r="I426" s="38">
         <v>267096</v>
       </c>
-      <c r="J426" s="42">
+      <c r="J426" s="40">
         <v>37176</v>
       </c>
-      <c r="K426" s="42">
+      <c r="K426" s="40">
         <v>45489</v>
       </c>
-      <c r="L426" s="43"/>
-      <c r="M426" s="43"/>
-      <c r="N426" s="40" t="s">
+      <c r="L426" s="41"/>
+      <c r="M426" s="41"/>
+      <c r="N426" s="38" t="s">
         <v>1759</v>
       </c>
-      <c r="O426" s="40" t="s">
+      <c r="O426" s="38" t="s">
         <v>1760</v>
       </c>
-      <c r="P426" s="40"/>
-      <c r="Q426" s="40"/>
-      <c r="R426" s="40"/>
-      <c r="S426" s="40"/>
-      <c r="T426" s="40"/>
-      <c r="U426" s="44" t="s">
+      <c r="P426" s="38"/>
+      <c r="Q426" s="38"/>
+      <c r="R426" s="38"/>
+      <c r="S426" s="38"/>
+      <c r="T426" s="38"/>
+      <c r="U426" s="42" t="s">
         <v>3260</v>
       </c>
-      <c r="V426" s="40">
+      <c r="V426" s="38">
         <v>3</v>
       </c>
-      <c r="W426" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X426" s="40" t="s">
+      <c r="W426" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X426" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y426" s="40"/>
+      <c r="Y426" s="38"/>
     </row>
     <row r="427" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="32">
@@ -37342,66 +37328,66 @@
       </c>
       <c r="Y429" s="15"/>
     </row>
-    <row r="430" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A430" s="39">
+    <row r="430" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="37">
         <v>268052</v>
       </c>
-      <c r="B430" s="40" t="s">
+      <c r="B430" s="38" t="s">
         <v>1783</v>
       </c>
-      <c r="C430" s="40" t="s">
+      <c r="C430" s="38" t="s">
         <v>1784</v>
       </c>
-      <c r="D430" s="40" t="s">
+      <c r="D430" s="38" t="s">
         <v>1785</v>
       </c>
-      <c r="E430" s="40" t="s">
+      <c r="E430" s="38" t="s">
         <v>1785</v>
       </c>
-      <c r="F430" s="41" t="s">
+      <c r="F430" s="39" t="s">
         <v>1781</v>
       </c>
-      <c r="G430" s="40" t="s">
+      <c r="G430" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H430" s="40" t="s">
+      <c r="H430" s="38" t="s">
         <v>1782</v>
       </c>
-      <c r="I430" s="40">
+      <c r="I430" s="38">
         <v>242032</v>
       </c>
-      <c r="J430" s="42">
+      <c r="J430" s="40">
         <v>37194</v>
       </c>
-      <c r="K430" s="42">
+      <c r="K430" s="40">
         <v>45839</v>
       </c>
-      <c r="L430" s="43"/>
-      <c r="M430" s="43"/>
-      <c r="N430" s="40" t="s">
+      <c r="L430" s="41"/>
+      <c r="M430" s="41"/>
+      <c r="N430" s="38" t="s">
         <v>1786</v>
       </c>
-      <c r="O430" s="40" t="s">
+      <c r="O430" s="38" t="s">
         <v>1787</v>
       </c>
-      <c r="P430" s="40"/>
-      <c r="Q430" s="40"/>
-      <c r="R430" s="40"/>
-      <c r="S430" s="40"/>
-      <c r="T430" s="40"/>
-      <c r="U430" s="44" t="s">
+      <c r="P430" s="38"/>
+      <c r="Q430" s="38"/>
+      <c r="R430" s="38"/>
+      <c r="S430" s="38"/>
+      <c r="T430" s="38"/>
+      <c r="U430" s="42" t="s">
         <v>3262</v>
       </c>
-      <c r="V430" s="40">
+      <c r="V430" s="38">
         <v>3</v>
       </c>
-      <c r="W430" s="40" t="s">
+      <c r="W430" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X430" s="40" t="s">
+      <c r="X430" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y430" s="40"/>
+      <c r="Y430" s="38"/>
     </row>
     <row r="431" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="32">
@@ -40803,70 +40789,70 @@
       </c>
       <c r="Y488" s="15"/>
     </row>
-    <row r="489" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A489" s="39">
+    <row r="489" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A489" s="37">
         <v>261037</v>
       </c>
-      <c r="B489" s="40" t="s">
+      <c r="B489" s="38" t="s">
         <v>2006</v>
       </c>
-      <c r="C489" s="40" t="s">
+      <c r="C489" s="38" t="s">
         <v>2007</v>
       </c>
-      <c r="D489" s="40" t="s">
+      <c r="D489" s="38" t="s">
         <v>2008</v>
       </c>
-      <c r="E489" s="40" t="s">
+      <c r="E489" s="38" t="s">
         <v>2008</v>
       </c>
-      <c r="F489" s="41" t="s">
+      <c r="F489" s="39" t="s">
         <v>2009</v>
       </c>
-      <c r="G489" s="40" t="s">
+      <c r="G489" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="H489" s="40" t="s">
+      <c r="H489" s="38" t="s">
         <v>1975</v>
       </c>
-      <c r="I489" s="40">
+      <c r="I489" s="38">
         <v>253014</v>
       </c>
-      <c r="J489" s="42">
+      <c r="J489" s="40">
         <v>34893</v>
       </c>
-      <c r="K489" s="42">
+      <c r="K489" s="40">
         <v>43420</v>
       </c>
-      <c r="L489" s="43"/>
-      <c r="M489" s="43"/>
-      <c r="N489" s="40" t="s">
+      <c r="L489" s="41"/>
+      <c r="M489" s="41"/>
+      <c r="N489" s="38" t="s">
         <v>2010</v>
       </c>
-      <c r="O489" s="40" t="s">
+      <c r="O489" s="38" t="s">
         <v>2011</v>
       </c>
-      <c r="P489" s="40"/>
-      <c r="Q489" s="40"/>
-      <c r="R489" s="40"/>
-      <c r="S489" s="40" t="s">
+      <c r="P489" s="38"/>
+      <c r="Q489" s="38"/>
+      <c r="R489" s="38"/>
+      <c r="S489" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="T489" s="40" t="s">
+      <c r="T489" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="U489" s="44" t="s">
+      <c r="U489" s="42" t="s">
         <v>3312</v>
       </c>
-      <c r="V489" s="40">
+      <c r="V489" s="38">
         <v>3</v>
       </c>
-      <c r="W489" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X489" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y489" s="40"/>
+      <c r="W489" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X489" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y489" s="38"/>
     </row>
     <row r="490" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="32">
@@ -41053,127 +41039,127 @@
       </c>
       <c r="Y492" s="15"/>
     </row>
-    <row r="493" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A493" s="39">
+    <row r="493" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A493" s="37">
         <v>268020</v>
       </c>
-      <c r="B493" s="40" t="s">
+      <c r="B493" s="38" t="s">
         <v>2073</v>
       </c>
-      <c r="C493" s="40" t="s">
+      <c r="C493" s="38" t="s">
         <v>2074</v>
       </c>
-      <c r="D493" s="40" t="s">
+      <c r="D493" s="38" t="s">
         <v>2075</v>
       </c>
-      <c r="E493" s="40" t="s">
+      <c r="E493" s="38" t="s">
         <v>2075</v>
       </c>
-      <c r="F493" s="41" t="s">
+      <c r="F493" s="39" t="s">
         <v>2076</v>
       </c>
-      <c r="G493" s="40" t="s">
+      <c r="G493" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H493" s="40" t="s">
+      <c r="H493" s="38" t="s">
         <v>2069</v>
       </c>
-      <c r="I493" s="40">
+      <c r="I493" s="38">
         <v>248031</v>
       </c>
-      <c r="J493" s="42">
+      <c r="J493" s="40">
         <v>37154</v>
       </c>
-      <c r="K493" s="42">
+      <c r="K493" s="40">
         <v>45733</v>
       </c>
-      <c r="L493" s="43"/>
-      <c r="M493" s="43"/>
-      <c r="N493" s="40" t="s">
+      <c r="L493" s="41"/>
+      <c r="M493" s="41"/>
+      <c r="N493" s="38" t="s">
         <v>2077</v>
       </c>
-      <c r="O493" s="40" t="s">
+      <c r="O493" s="38" t="s">
         <v>2078</v>
       </c>
-      <c r="P493" s="40"/>
-      <c r="Q493" s="40"/>
-      <c r="R493" s="40"/>
-      <c r="S493" s="40"/>
-      <c r="T493" s="40"/>
-      <c r="U493" s="44" t="s">
+      <c r="P493" s="38"/>
+      <c r="Q493" s="38"/>
+      <c r="R493" s="38"/>
+      <c r="S493" s="38"/>
+      <c r="T493" s="38"/>
+      <c r="U493" s="42" t="s">
         <v>3316</v>
       </c>
-      <c r="V493" s="40">
+      <c r="V493" s="38">
         <v>3</v>
       </c>
-      <c r="W493" s="40" t="s">
+      <c r="W493" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X493" s="40" t="s">
+      <c r="X493" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y493" s="40"/>
-    </row>
-    <row r="494" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A494" s="39">
+      <c r="Y493" s="38"/>
+    </row>
+    <row r="494" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A494" s="37">
         <v>268077</v>
       </c>
-      <c r="B494" s="40" t="s">
+      <c r="B494" s="38" t="s">
         <v>2079</v>
       </c>
-      <c r="C494" s="40" t="s">
+      <c r="C494" s="38" t="s">
         <v>2080</v>
       </c>
-      <c r="D494" s="40" t="s">
+      <c r="D494" s="38" t="s">
         <v>2081</v>
       </c>
-      <c r="E494" s="40" t="s">
+      <c r="E494" s="38" t="s">
         <v>2081</v>
       </c>
-      <c r="F494" s="41" t="s">
+      <c r="F494" s="39" t="s">
         <v>2076</v>
       </c>
-      <c r="G494" s="40" t="s">
+      <c r="G494" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H494" s="40" t="s">
+      <c r="H494" s="38" t="s">
         <v>2069</v>
       </c>
-      <c r="I494" s="40">
+      <c r="I494" s="38">
         <v>248031</v>
       </c>
-      <c r="J494" s="42">
+      <c r="J494" s="40">
         <v>37828</v>
       </c>
-      <c r="K494" s="42">
+      <c r="K494" s="40">
         <v>45931</v>
       </c>
-      <c r="L494" s="43"/>
-      <c r="M494" s="43"/>
-      <c r="N494" s="40" t="s">
+      <c r="L494" s="41"/>
+      <c r="M494" s="41"/>
+      <c r="N494" s="38" t="s">
         <v>2082</v>
       </c>
-      <c r="O494" s="40" t="s">
+      <c r="O494" s="38" t="s">
         <v>2083</v>
       </c>
-      <c r="P494" s="40"/>
-      <c r="Q494" s="40"/>
-      <c r="R494" s="40"/>
-      <c r="S494" s="40"/>
-      <c r="T494" s="40"/>
-      <c r="U494" s="44" t="s">
+      <c r="P494" s="38"/>
+      <c r="Q494" s="38"/>
+      <c r="R494" s="38"/>
+      <c r="S494" s="38"/>
+      <c r="T494" s="38"/>
+      <c r="U494" s="42" t="s">
         <v>3317</v>
       </c>
-      <c r="V494" s="40">
+      <c r="V494" s="38">
         <v>3</v>
       </c>
-      <c r="W494" s="40" t="s">
+      <c r="W494" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X494" s="40" t="s">
+      <c r="X494" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y494" s="40"/>
+      <c r="Y494" s="38"/>
     </row>
     <row r="495" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="32">
@@ -41606,66 +41592,66 @@
       </c>
       <c r="Y501" s="15"/>
     </row>
-    <row r="502" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A502" s="39">
+    <row r="502" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A502" s="37">
         <v>268048</v>
       </c>
-      <c r="B502" s="40" t="s">
+      <c r="B502" s="38" t="s">
         <v>2175</v>
       </c>
-      <c r="C502" s="40" t="s">
+      <c r="C502" s="38" t="s">
         <v>2176</v>
       </c>
-      <c r="D502" s="40" t="s">
+      <c r="D502" s="38" t="s">
         <v>1960</v>
       </c>
-      <c r="E502" s="40" t="s">
+      <c r="E502" s="38" t="s">
         <v>1960</v>
       </c>
-      <c r="F502" s="41" t="s">
+      <c r="F502" s="39" t="s">
         <v>2177</v>
       </c>
-      <c r="G502" s="40" t="s">
+      <c r="G502" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H502" s="40" t="s">
+      <c r="H502" s="38" t="s">
         <v>2172</v>
       </c>
-      <c r="I502" s="40">
+      <c r="I502" s="38">
         <v>251007</v>
       </c>
-      <c r="J502" s="42">
+      <c r="J502" s="40">
         <v>34526</v>
       </c>
-      <c r="K502" s="42">
+      <c r="K502" s="40">
         <v>45824</v>
       </c>
-      <c r="L502" s="43"/>
-      <c r="M502" s="43"/>
-      <c r="N502" s="40" t="s">
+      <c r="L502" s="41"/>
+      <c r="M502" s="41"/>
+      <c r="N502" s="38" t="s">
         <v>2178</v>
       </c>
-      <c r="O502" s="40" t="s">
+      <c r="O502" s="38" t="s">
         <v>2179</v>
       </c>
-      <c r="P502" s="40"/>
-      <c r="Q502" s="40"/>
-      <c r="R502" s="40"/>
-      <c r="S502" s="40"/>
-      <c r="T502" s="40"/>
-      <c r="U502" s="44" t="s">
+      <c r="P502" s="38"/>
+      <c r="Q502" s="38"/>
+      <c r="R502" s="38"/>
+      <c r="S502" s="38"/>
+      <c r="T502" s="38"/>
+      <c r="U502" s="42" t="s">
         <v>3323</v>
       </c>
-      <c r="V502" s="40">
+      <c r="V502" s="38">
         <v>3</v>
       </c>
-      <c r="W502" s="40" t="s">
+      <c r="W502" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X502" s="40" t="s">
+      <c r="X502" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y502" s="40"/>
+      <c r="Y502" s="38"/>
     </row>
     <row r="503" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="32">
@@ -41850,66 +41836,66 @@
       </c>
       <c r="Y505" s="15"/>
     </row>
-    <row r="506" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A506" s="39">
+    <row r="506" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A506" s="37">
         <v>268002</v>
       </c>
-      <c r="B506" s="40" t="s">
+      <c r="B506" s="38" t="s">
         <v>2097</v>
       </c>
-      <c r="C506" s="40" t="s">
+      <c r="C506" s="38" t="s">
         <v>2098</v>
       </c>
-      <c r="D506" s="40" t="s">
+      <c r="D506" s="38" t="s">
         <v>2099</v>
       </c>
-      <c r="E506" s="40" t="s">
+      <c r="E506" s="38" t="s">
         <v>2099</v>
       </c>
-      <c r="F506" s="41" t="s">
+      <c r="F506" s="39" t="s">
         <v>2100</v>
       </c>
-      <c r="G506" s="40" t="s">
+      <c r="G506" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H506" s="40" t="s">
+      <c r="H506" s="38" t="s">
         <v>2086</v>
       </c>
-      <c r="I506" s="40">
+      <c r="I506" s="38">
         <v>251007</v>
       </c>
-      <c r="J506" s="42">
+      <c r="J506" s="40">
         <v>37198</v>
       </c>
-      <c r="K506" s="42">
+      <c r="K506" s="40">
         <v>45659</v>
       </c>
-      <c r="L506" s="43"/>
-      <c r="M506" s="43"/>
-      <c r="N506" s="40" t="s">
+      <c r="L506" s="41"/>
+      <c r="M506" s="41"/>
+      <c r="N506" s="38" t="s">
         <v>2101</v>
       </c>
-      <c r="O506" s="40" t="s">
+      <c r="O506" s="38" t="s">
         <v>2102</v>
       </c>
-      <c r="P506" s="40"/>
-      <c r="Q506" s="40"/>
-      <c r="R506" s="40"/>
-      <c r="S506" s="40"/>
-      <c r="T506" s="40"/>
-      <c r="U506" s="44" t="s">
+      <c r="P506" s="38"/>
+      <c r="Q506" s="38"/>
+      <c r="R506" s="38"/>
+      <c r="S506" s="38"/>
+      <c r="T506" s="38"/>
+      <c r="U506" s="42" t="s">
         <v>3327</v>
       </c>
-      <c r="V506" s="40">
+      <c r="V506" s="38">
         <v>3</v>
       </c>
-      <c r="W506" s="40" t="s">
+      <c r="W506" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X506" s="40" t="s">
+      <c r="X506" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y506" s="40"/>
+      <c r="Y506" s="38"/>
     </row>
     <row r="507" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="32">
@@ -43361,66 +43347,66 @@
       </c>
       <c r="Y530" s="15"/>
     </row>
-    <row r="531" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A531" s="39">
+    <row r="531" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A531" s="37">
         <v>267032</v>
       </c>
-      <c r="B531" s="40" t="s">
+      <c r="B531" s="38" t="s">
         <v>2219</v>
       </c>
-      <c r="C531" s="40" t="s">
+      <c r="C531" s="38" t="s">
         <v>2220</v>
       </c>
-      <c r="D531" s="40" t="s">
+      <c r="D531" s="38" t="s">
         <v>1161</v>
       </c>
-      <c r="E531" s="40" t="s">
+      <c r="E531" s="38" t="s">
         <v>1161</v>
       </c>
-      <c r="F531" s="41" t="s">
+      <c r="F531" s="39" t="s">
         <v>2880</v>
       </c>
-      <c r="G531" s="40" t="s">
+      <c r="G531" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="H531" s="40" t="s">
+      <c r="H531" s="38" t="s">
         <v>2190</v>
       </c>
-      <c r="I531" s="40">
+      <c r="I531" s="38">
         <v>257039</v>
       </c>
-      <c r="J531" s="42">
+      <c r="J531" s="40">
         <v>34641</v>
       </c>
-      <c r="K531" s="42">
+      <c r="K531" s="40">
         <v>45352</v>
       </c>
-      <c r="L531" s="43"/>
-      <c r="M531" s="43"/>
-      <c r="N531" s="40" t="s">
+      <c r="L531" s="41"/>
+      <c r="M531" s="41"/>
+      <c r="N531" s="38" t="s">
         <v>2221</v>
       </c>
-      <c r="O531" s="40" t="s">
+      <c r="O531" s="38" t="s">
         <v>2222</v>
       </c>
-      <c r="P531" s="40"/>
-      <c r="Q531" s="40"/>
-      <c r="R531" s="40"/>
-      <c r="S531" s="40"/>
-      <c r="T531" s="40"/>
-      <c r="U531" s="44" t="s">
+      <c r="P531" s="38"/>
+      <c r="Q531" s="38"/>
+      <c r="R531" s="38"/>
+      <c r="S531" s="38"/>
+      <c r="T531" s="38"/>
+      <c r="U531" s="42" t="s">
         <v>3348</v>
       </c>
-      <c r="V531" s="40">
+      <c r="V531" s="38">
         <v>2</v>
       </c>
-      <c r="W531" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X531" s="40" t="s">
+      <c r="W531" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X531" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y531" s="40"/>
+      <c r="Y531" s="38"/>
     </row>
     <row r="532" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="32">
@@ -46051,66 +46037,66 @@
       </c>
       <c r="Y574" s="26"/>
     </row>
-    <row r="575" spans="1:26" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A575" s="39">
+    <row r="575" spans="1:26" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="37">
         <v>269033</v>
       </c>
-      <c r="B575" s="40" t="s">
+      <c r="B575" s="38" t="s">
         <v>3448</v>
       </c>
-      <c r="C575" s="40" t="s">
+      <c r="C575" s="38" t="s">
         <v>3434</v>
       </c>
-      <c r="D575" s="40" t="s">
+      <c r="D575" s="38" t="s">
         <v>3423</v>
       </c>
-      <c r="E575" s="40" t="s">
+      <c r="E575" s="38" t="s">
         <v>3423</v>
       </c>
-      <c r="F575" s="41" t="s">
+      <c r="F575" s="39" t="s">
         <v>3443</v>
       </c>
-      <c r="G575" s="40" t="s">
+      <c r="G575" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H575" s="40" t="s">
+      <c r="H575" s="38" t="s">
         <v>1376</v>
       </c>
-      <c r="I575" s="40">
+      <c r="I575" s="38">
         <v>256014</v>
       </c>
-      <c r="J575" s="42">
+      <c r="J575" s="40">
         <v>37980</v>
       </c>
-      <c r="K575" s="42">
+      <c r="K575" s="40">
         <v>46160</v>
       </c>
-      <c r="L575" s="43"/>
-      <c r="M575" s="43"/>
-      <c r="N575" s="40" t="s">
+      <c r="L575" s="41"/>
+      <c r="M575" s="41"/>
+      <c r="N575" s="38" t="s">
         <v>3464</v>
       </c>
-      <c r="O575" s="40" t="s">
+      <c r="O575" s="38" t="s">
         <v>3474</v>
       </c>
-      <c r="P575" s="40"/>
-      <c r="Q575" s="40"/>
-      <c r="R575" s="40"/>
-      <c r="S575" s="40"/>
-      <c r="T575" s="40"/>
-      <c r="U575" s="47" t="s">
+      <c r="P575" s="38"/>
+      <c r="Q575" s="38"/>
+      <c r="R575" s="38"/>
+      <c r="S575" s="38"/>
+      <c r="T575" s="38"/>
+      <c r="U575" s="45" t="s">
         <v>3483</v>
       </c>
-      <c r="V575" s="40" t="s">
+      <c r="V575" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="W575" s="40" t="s">
+      <c r="W575" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X575" s="40" t="s">
+      <c r="X575" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y575" s="40"/>
+      <c r="Y575" s="38"/>
     </row>
     <row r="576" spans="1:26" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="34">
@@ -46409,66 +46395,66 @@
       </c>
       <c r="Y580" s="26"/>
     </row>
-    <row r="581" spans="1:25" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A581" s="39">
+    <row r="581" spans="1:25" s="43" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A581" s="37">
         <v>269041</v>
       </c>
-      <c r="B581" s="40" t="s">
+      <c r="B581" s="38" t="s">
         <v>3453</v>
       </c>
-      <c r="C581" s="40" t="s">
+      <c r="C581" s="38" t="s">
         <v>3440</v>
       </c>
-      <c r="D581" s="40" t="s">
+      <c r="D581" s="38" t="s">
         <v>1381</v>
       </c>
-      <c r="E581" s="40" t="s">
+      <c r="E581" s="38" t="s">
         <v>1381</v>
       </c>
-      <c r="F581" s="41" t="s">
+      <c r="F581" s="39" t="s">
         <v>3445</v>
       </c>
-      <c r="G581" s="40" t="s">
+      <c r="G581" s="38" t="s">
         <v>3428</v>
       </c>
-      <c r="H581" s="40" t="s">
+      <c r="H581" s="38" t="s">
         <v>1782</v>
       </c>
-      <c r="I581" s="40">
+      <c r="I581" s="38">
         <v>242032</v>
       </c>
-      <c r="J581" s="42">
+      <c r="J581" s="40">
         <v>35824</v>
       </c>
-      <c r="K581" s="42">
+      <c r="K581" s="40">
         <v>46177</v>
       </c>
-      <c r="L581" s="43"/>
-      <c r="M581" s="43"/>
-      <c r="N581" s="40" t="s">
+      <c r="L581" s="41"/>
+      <c r="M581" s="41"/>
+      <c r="N581" s="38" t="s">
         <v>3470</v>
       </c>
-      <c r="O581" s="40" t="s">
+      <c r="O581" s="38" t="s">
         <v>3476</v>
       </c>
-      <c r="P581" s="40"/>
-      <c r="Q581" s="40"/>
-      <c r="R581" s="40"/>
-      <c r="S581" s="40"/>
-      <c r="T581" s="40"/>
-      <c r="U581" s="47" t="s">
+      <c r="P581" s="38"/>
+      <c r="Q581" s="38"/>
+      <c r="R581" s="38"/>
+      <c r="S581" s="38"/>
+      <c r="T581" s="38"/>
+      <c r="U581" s="45" t="s">
         <v>3135</v>
       </c>
-      <c r="V581" s="40" t="s">
+      <c r="V581" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="W581" s="40" t="s">
+      <c r="W581" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="X581" s="40" t="s">
+      <c r="X581" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Y581" s="40"/>
+      <c r="Y581" s="38"/>
     </row>
     <row r="582" spans="1:25" s="24" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="34">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E1087AC-134A-40A4-8313-CFE5F5C425ED}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87ED839D-4967-4CC6-85C9-DC2A40226BFC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Z$574</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8211" uniqueCount="3523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8211" uniqueCount="3521">
   <si>
     <t>emp_id</t>
   </si>
@@ -10409,12 +10409,6 @@
   </si>
   <si>
     <t>3C(11)M</t>
-  </si>
-  <si>
-    <t>6(17C)</t>
-  </si>
-  <si>
-    <t>6(17A)</t>
   </si>
   <si>
     <t>as_of_date=15 กรกฎาคม 2569</t>
@@ -10900,6 +10894,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11216,7 +11214,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="36" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -11530,7 +11528,7 @@
         <v>2425</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J6" s="4">
         <v>26587</v>
@@ -11593,7 +11591,7 @@
         <v>2425</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J7" s="4">
         <v>31789</v>
@@ -11654,7 +11652,7 @@
         <v>2425</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J8" s="4">
         <v>36056</v>
@@ -11715,7 +11713,7 @@
         <v>2425</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J9" s="4">
         <v>35425</v>
@@ -11774,7 +11772,7 @@
         <v>2425</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J10" s="4">
         <v>33259</v>
@@ -11835,7 +11833,7 @@
         <v>2425</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J11" s="4">
         <v>36406</v>
@@ -11894,7 +11892,7 @@
         <v>2425</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J12" s="4">
         <v>35172</v>
@@ -11953,7 +11951,7 @@
         <v>2425</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J13" s="4">
         <v>35514</v>
@@ -12012,7 +12010,7 @@
         <v>2425</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J14" s="4">
         <v>34666</v>
@@ -12073,7 +12071,7 @@
         <v>2425</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J15" s="4">
         <v>30051</v>
@@ -12138,7 +12136,7 @@
         <v>2425</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J16" s="4">
         <v>36690</v>
@@ -12199,7 +12197,7 @@
         <v>2425</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="J17" s="4">
         <v>28726</v>
@@ -12262,7 +12260,7 @@
         <v>2425</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J18" s="4">
         <v>36118</v>
@@ -12323,7 +12321,7 @@
         <v>2425</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J19" s="4">
         <v>33626</v>
@@ -12382,7 +12380,7 @@
         <v>2425</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J20" s="4">
         <v>30717</v>
@@ -12441,7 +12439,7 @@
         <v>2425</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J21" s="4">
         <v>37624</v>
@@ -12500,7 +12498,7 @@
         <v>2425</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J22" s="4">
         <v>35758</v>
@@ -12559,7 +12557,7 @@
         <v>2425</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J23" s="4">
         <v>37469</v>
@@ -12622,7 +12620,7 @@
         <v>2425</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J24" s="4">
         <v>36279</v>
@@ -12683,7 +12681,7 @@
         <v>2425</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J25" s="4">
         <v>30770</v>
@@ -12742,7 +12740,7 @@
         <v>2425</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J26" s="4">
         <v>32482</v>
@@ -12801,7 +12799,7 @@
         <v>2425</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J27" s="4">
         <v>29280</v>
@@ -12860,7 +12858,7 @@
         <v>2425</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J28" s="4">
         <v>38120</v>
@@ -12919,7 +12917,7 @@
         <v>2425</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J29" s="4">
         <v>37469</v>
@@ -12976,7 +12974,7 @@
         <v>2625</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="J30" s="4">
         <v>28358</v>
@@ -13041,7 +13039,7 @@
         <v>2625</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="J31" s="4">
         <v>32145</v>
@@ -13106,7 +13104,7 @@
         <v>2530</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="J32" s="4">
         <v>26572</v>
@@ -13169,7 +13167,7 @@
         <v>2530</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="J33" s="4">
         <v>31053</v>
@@ -13230,7 +13228,7 @@
         <v>3444</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="J34" s="4">
         <v>30484</v>
@@ -13293,7 +13291,7 @@
         <v>2542</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="J35" s="4">
         <v>29866</v>
@@ -13360,7 +13358,7 @@
         <v>2542</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J36" s="4">
         <v>29667</v>
@@ -13419,7 +13417,7 @@
         <v>2542</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J37" s="4">
         <v>28931</v>
@@ -13474,7 +13472,7 @@
         <v>2542</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J38" s="4">
         <v>27527</v>
@@ -13537,7 +13535,7 @@
         <v>2542</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J39" s="4">
         <v>29703</v>
@@ -13600,7 +13598,7 @@
         <v>2542</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J40" s="4">
         <v>32306</v>
@@ -13663,7 +13661,7 @@
         <v>2542</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J41" s="4">
         <v>33449</v>
@@ -13724,7 +13722,7 @@
         <v>2542</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J42" s="4">
         <v>34355</v>
@@ -13785,7 +13783,7 @@
         <v>2542</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J43" s="4">
         <v>37860</v>
@@ -13844,7 +13842,7 @@
         <v>2542</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J44" s="4">
         <v>38178</v>
@@ -13903,7 +13901,7 @@
         <v>2542</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J45" s="4">
         <v>34818</v>
@@ -13964,7 +13962,7 @@
         <v>2542</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J46" s="4">
         <v>37891</v>
@@ -14019,7 +14017,7 @@
         <v>2542</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J47" s="4">
         <v>37147</v>
@@ -14074,7 +14072,7 @@
         <v>2542</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J48" s="4">
         <v>37140</v>
@@ -14129,7 +14127,7 @@
         <v>2542</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J49" s="4">
         <v>37600</v>
@@ -14188,7 +14186,7 @@
         <v>2542</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J50" s="4">
         <v>35267</v>
@@ -14249,7 +14247,7 @@
         <v>2542</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J51" s="4">
         <v>35865</v>
@@ -14310,7 +14308,7 @@
         <v>2542</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J52" s="4">
         <v>37610</v>
@@ -14369,7 +14367,7 @@
         <v>2542</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J53" s="4">
         <v>32012</v>
@@ -14428,7 +14426,7 @@
         <v>2542</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J54" s="4">
         <v>37390</v>
@@ -14487,7 +14485,7 @@
         <v>2542</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J55" s="4">
         <v>37615</v>
@@ -14546,7 +14544,7 @@
         <v>2542</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J56" s="4">
         <v>37367</v>
@@ -14670,7 +14668,7 @@
         <v>48</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J58" s="4">
         <v>35614</v>
@@ -14735,7 +14733,7 @@
         <v>29</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J59" s="4">
         <v>26183</v>
@@ -14798,7 +14796,7 @@
         <v>29</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J60" s="4">
         <v>32531</v>
@@ -14859,7 +14857,7 @@
         <v>66</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J61" s="4">
         <v>31953</v>
@@ -14922,7 +14920,7 @@
         <v>58</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="J62" s="4">
         <v>37743</v>
@@ -14983,7 +14981,7 @@
         <v>107</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J63" s="4">
         <v>28864</v>
@@ -15050,7 +15048,7 @@
         <v>107</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J64" s="4">
         <v>22134</v>
@@ -15357,7 +15355,7 @@
         <v>174</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J69" s="4">
         <v>29165</v>
@@ -15420,7 +15418,7 @@
         <v>121</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J70" s="4">
         <v>33417</v>
@@ -15483,7 +15481,7 @@
         <v>128</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J71" s="4">
         <v>29501</v>
@@ -15546,7 +15544,7 @@
         <v>128</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J72" s="4">
         <v>35831</v>
@@ -15607,7 +15605,7 @@
         <v>141</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J73" s="4">
         <v>35444</v>
@@ -15729,7 +15727,7 @@
         <v>154</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J75" s="4">
         <v>36960</v>
@@ -15790,7 +15788,7 @@
         <v>154</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J76" s="4">
         <v>37642</v>
@@ -15851,7 +15849,7 @@
         <v>154</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J77" s="4">
         <v>32000</v>
@@ -15977,7 +15975,7 @@
         <v>408</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="J79" s="4">
         <v>35766</v>
@@ -16038,7 +16036,7 @@
         <v>408</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J80" s="4">
         <v>31046</v>
@@ -16101,7 +16099,7 @@
         <v>2739</v>
       </c>
       <c r="I81" s="12" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="J81" s="4">
         <v>31947</v>
@@ -16166,7 +16164,7 @@
         <v>451</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J82" s="4">
         <v>29304</v>
@@ -16233,7 +16231,7 @@
         <v>426</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="J83" s="4">
         <v>30899</v>
@@ -16298,7 +16296,7 @@
         <v>426</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="J84" s="4">
         <v>36406</v>
@@ -16359,7 +16357,7 @@
         <v>440</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="J85" s="4">
         <v>33909</v>
@@ -16420,7 +16418,7 @@
         <v>440</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="J86" s="4">
         <v>34597</v>
@@ -16481,7 +16479,7 @@
         <v>458</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J87" s="4">
         <v>34175</v>
@@ -16544,7 +16542,7 @@
         <v>458</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J88" s="4">
         <v>34991</v>
@@ -16605,7 +16603,7 @@
         <v>458</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J89" s="4">
         <v>29097</v>
@@ -16666,7 +16664,7 @@
         <v>458</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J90" s="4">
         <v>35999</v>
@@ -16727,7 +16725,7 @@
         <v>458</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J91" s="4">
         <v>36286</v>
@@ -16788,7 +16786,7 @@
         <v>458</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J92" s="4">
         <v>33670</v>
@@ -16849,7 +16847,7 @@
         <v>458</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J93" s="4">
         <v>34739</v>
@@ -16910,7 +16908,7 @@
         <v>493</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J94" s="4">
         <v>27629</v>
@@ -16971,7 +16969,7 @@
         <v>493</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J95" s="4">
         <v>27534</v>
@@ -17036,7 +17034,7 @@
         <v>493</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J96" s="4">
         <v>29355</v>
@@ -17101,7 +17099,7 @@
         <v>493</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J97" s="4">
         <v>36365</v>
@@ -17164,7 +17162,7 @@
         <v>493</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J98" s="4">
         <v>35196</v>
@@ -17225,7 +17223,7 @@
         <v>493</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J99" s="4">
         <v>36224</v>
@@ -17286,7 +17284,7 @@
         <v>493</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J100" s="4">
         <v>32015</v>
@@ -17347,7 +17345,7 @@
         <v>541</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J101" s="4">
         <v>29168</v>
@@ -17902,7 +17900,7 @@
         <v>400</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J110" s="4">
         <v>25766</v>
@@ -17965,7 +17963,7 @@
         <v>376</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J111" s="4">
         <v>24185</v>
@@ -18026,7 +18024,7 @@
         <v>376</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J112" s="4">
         <v>30434</v>
@@ -18091,7 +18089,7 @@
         <v>376</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J113" s="4">
         <v>34256</v>
@@ -18154,7 +18152,7 @@
         <v>376</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="J114" s="4">
         <v>31086</v>
@@ -18215,7 +18213,7 @@
         <v>191</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="J115" s="4">
         <v>25240</v>
@@ -18280,7 +18278,7 @@
         <v>191</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J116" s="4">
         <v>27514</v>
@@ -18339,7 +18337,7 @@
         <v>266</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J117" s="4">
         <v>32033</v>
@@ -18396,7 +18394,7 @@
         <v>191</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="J118" s="4">
         <v>31239</v>
@@ -18453,7 +18451,7 @@
         <v>216</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J119" s="4">
         <v>26311</v>
@@ -18514,7 +18512,7 @@
         <v>216</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J120" s="4">
         <v>28351</v>
@@ -18579,7 +18577,7 @@
         <v>216</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J121" s="4">
         <v>33248</v>
@@ -18644,7 +18642,7 @@
         <v>216</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J122" s="4">
         <v>34891</v>
@@ -18707,7 +18705,7 @@
         <v>216</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J123" s="4">
         <v>32067</v>
@@ -18768,7 +18766,7 @@
         <v>216</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J124" s="4">
         <v>33565</v>
@@ -18825,7 +18823,7 @@
         <v>216</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J125" s="4">
         <v>33444</v>
@@ -18886,7 +18884,7 @@
         <v>216</v>
       </c>
       <c r="I126" s="12" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J126" s="4">
         <v>30060</v>
@@ -18947,7 +18945,7 @@
         <v>266</v>
       </c>
       <c r="I127" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J127" s="4">
         <v>29103</v>
@@ -19012,7 +19010,7 @@
         <v>360</v>
       </c>
       <c r="I128" s="12" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="J128" s="4">
         <v>32662</v>
@@ -19075,7 +19073,7 @@
         <v>266</v>
       </c>
       <c r="I129" s="12" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J129" s="4">
         <v>34910</v>
@@ -19138,7 +19136,7 @@
         <v>266</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J130" s="4">
         <v>29433</v>
@@ -19195,7 +19193,7 @@
         <v>266</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J131" s="4">
         <v>34484</v>
@@ -19256,7 +19254,7 @@
         <v>266</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J132" s="4">
         <v>35629</v>
@@ -19313,7 +19311,7 @@
         <v>299</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J133" s="4">
         <v>29668</v>
@@ -19378,7 +19376,7 @@
         <v>299</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J134" s="4">
         <v>26876</v>
@@ -19439,7 +19437,7 @@
         <v>299</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J135" s="4">
         <v>32805</v>
@@ -19496,7 +19494,7 @@
         <v>299</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J136" s="4">
         <v>31919</v>
@@ -19557,7 +19555,7 @@
         <v>299</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J137" s="4">
         <v>32945</v>
@@ -19618,7 +19616,7 @@
         <v>299</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J138" s="4">
         <v>36736</v>
@@ -19679,7 +19677,7 @@
         <v>299</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J139" s="4">
         <v>26686</v>
@@ -19740,7 +19738,7 @@
         <v>337</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J140" s="4">
         <v>29007</v>
@@ -19805,7 +19803,7 @@
         <v>337</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="J141" s="4">
         <v>34529</v>
@@ -19864,7 +19862,7 @@
         <v>337</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="J142" s="4">
         <v>35388</v>
@@ -19927,7 +19925,7 @@
         <v>376</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J143" s="4">
         <v>29491</v>
@@ -19990,7 +19988,7 @@
         <v>360</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J144" s="4">
         <v>31632</v>
@@ -20057,7 +20055,7 @@
         <v>360</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="J145" s="4">
         <v>35166</v>
@@ -20122,7 +20120,7 @@
         <v>360</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="J146" s="4">
         <v>33366</v>
@@ -20183,7 +20181,7 @@
         <v>592</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="J147" s="4">
         <v>24215</v>
@@ -20244,7 +20242,7 @@
         <v>2709</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J148" s="4">
         <v>24955</v>
@@ -20307,7 +20305,7 @@
         <v>2709</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J149" s="4">
         <v>27817</v>
@@ -20372,7 +20370,7 @@
         <v>2709</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J150" s="4">
         <v>29691</v>
@@ -20435,7 +20433,7 @@
         <v>2709</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J151" s="4">
         <v>33866</v>
@@ -20500,7 +20498,7 @@
         <v>2709</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J152" s="4">
         <v>36406</v>
@@ -20563,7 +20561,7 @@
         <v>2709</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="J153" s="4">
         <v>32895</v>
@@ -20622,7 +20620,7 @@
         <v>2709</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J154" s="4">
         <v>34809</v>
@@ -20683,7 +20681,7 @@
         <v>2709</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="J155" s="4">
         <v>33483</v>
@@ -20748,7 +20746,7 @@
         <v>2709</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="J156" s="4">
         <v>34978</v>
@@ -20811,7 +20809,7 @@
         <v>650</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="J157" s="4">
         <v>29389</v>
@@ -20876,7 +20874,7 @@
         <v>2710</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J158" s="4">
         <v>26018</v>
@@ -20937,7 +20935,7 @@
         <v>2710</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J159" s="4">
         <v>30302</v>
@@ -20998,7 +20996,7 @@
         <v>2710</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J160" s="4">
         <v>33830</v>
@@ -21063,7 +21061,7 @@
         <v>2710</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J161" s="4">
         <v>34916</v>
@@ -21128,7 +21126,7 @@
         <v>2710</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J162" s="4">
         <v>28346</v>
@@ -21191,7 +21189,7 @@
         <v>2710</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J163" s="4">
         <v>36404</v>
@@ -21254,7 +21252,7 @@
         <v>2710</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J164" s="4">
         <v>27470</v>
@@ -21315,7 +21313,7 @@
         <v>2710</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J165" s="4">
         <v>33266</v>
@@ -21376,7 +21374,7 @@
         <v>2710</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J166" s="4">
         <v>35796</v>
@@ -21437,7 +21435,7 @@
         <v>2710</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="J167" s="4">
         <v>29553</v>
@@ -21498,7 +21496,7 @@
         <v>2710</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J168" s="4">
         <v>34667</v>
@@ -21559,7 +21557,7 @@
         <v>2710</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J169" s="4">
         <v>35531</v>
@@ -21620,7 +21618,7 @@
         <v>2710</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J170" s="4">
         <v>26230</v>
@@ -22110,7 +22108,7 @@
         <v>739</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="J178" s="4">
         <v>29660</v>
@@ -22229,7 +22227,7 @@
         <v>2281</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>3457</v>
+        <v>2828</v>
       </c>
       <c r="H180" s="12" t="s">
         <v>2282</v>
@@ -22296,7 +22294,7 @@
         <v>2244</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J181" s="4">
         <v>24838</v>
@@ -22361,7 +22359,7 @@
         <v>2244</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J182" s="4">
         <v>26658</v>
@@ -22426,7 +22424,7 @@
         <v>2244</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J183" s="4">
         <v>27898</v>
@@ -22491,7 +22489,7 @@
         <v>2244</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J184" s="4">
         <v>29845</v>
@@ -22556,7 +22554,7 @@
         <v>2244</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J185" s="4">
         <v>25180</v>
@@ -22621,7 +22619,7 @@
         <v>2244</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J186" s="4">
         <v>26029</v>
@@ -22686,7 +22684,7 @@
         <v>2244</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J187" s="4">
         <v>27330</v>
@@ -22751,7 +22749,7 @@
         <v>2244</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J188" s="4">
         <v>27866</v>
@@ -22816,7 +22814,7 @@
         <v>2212</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J189" s="4">
         <v>31119</v>
@@ -22881,7 +22879,7 @@
         <v>2212</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="J190" s="4">
         <v>37517</v>
@@ -22942,7 +22940,7 @@
         <v>2225</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J191" s="4">
         <v>26421</v>
@@ -23007,7 +23005,7 @@
         <v>2225</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="J192" s="4">
         <v>29076</v>
@@ -23072,7 +23070,7 @@
         <v>2225</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="J193" s="4">
         <v>32757</v>
@@ -23137,7 +23135,7 @@
         <v>772</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J194" s="4">
         <v>31762</v>
@@ -23202,7 +23200,7 @@
         <v>2716</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J195" s="30">
         <v>36285</v>
@@ -23267,7 +23265,7 @@
         <v>2716</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J196" s="30">
         <v>36896</v>
@@ -23330,7 +23328,7 @@
         <v>784</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J197" s="4">
         <v>27730</v>
@@ -23387,7 +23385,7 @@
         <v>790</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J198" s="4">
         <v>30150</v>
@@ -23444,7 +23442,7 @@
         <v>790</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J199" s="4">
         <v>33891</v>
@@ -23501,7 +23499,7 @@
         <v>790</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J200" s="4">
         <v>32746</v>
@@ -23558,7 +23556,7 @@
         <v>790</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J201" s="4">
         <v>34242</v>
@@ -23615,7 +23613,7 @@
         <v>790</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J202" s="4">
         <v>33709</v>
@@ -23672,7 +23670,7 @@
         <v>790</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J203" s="4">
         <v>35646</v>
@@ -23727,7 +23725,7 @@
         <v>790</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J204" s="4">
         <v>35536</v>
@@ -23782,7 +23780,7 @@
         <v>813</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J205" s="4">
         <v>27911</v>
@@ -23843,7 +23841,7 @@
         <v>813</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J206" s="4">
         <v>29121</v>
@@ -23904,7 +23902,7 @@
         <v>813</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J207" s="4">
         <v>30230</v>
@@ -23963,7 +23961,7 @@
         <v>813</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J208" s="4">
         <v>34970</v>
@@ -24018,7 +24016,7 @@
         <v>813</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J209" s="4">
         <v>26789</v>
@@ -24077,7 +24075,7 @@
         <v>813</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J210" s="4">
         <v>27526</v>
@@ -24136,7 +24134,7 @@
         <v>837</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J211" s="4">
         <v>29793</v>
@@ -24195,7 +24193,7 @@
         <v>837</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J212" s="4">
         <v>32488</v>
@@ -24252,7 +24250,7 @@
         <v>837</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J213" s="4">
         <v>36020</v>
@@ -24311,7 +24309,7 @@
         <v>837</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J214" s="4">
         <v>31268</v>
@@ -24366,7 +24364,7 @@
         <v>854</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J215" s="4">
         <v>26738</v>
@@ -24427,7 +24425,7 @@
         <v>854</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J216" s="4">
         <v>31441</v>
@@ -24488,7 +24486,7 @@
         <v>854</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J217" s="4">
         <v>27104</v>
@@ -24547,7 +24545,7 @@
         <v>854</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J218" s="4">
         <v>34794</v>
@@ -24602,7 +24600,7 @@
         <v>854</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J219" s="4">
         <v>28145</v>
@@ -24657,7 +24655,7 @@
         <v>854</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J220" s="4">
         <v>26818</v>
@@ -24722,7 +24720,7 @@
         <v>1206</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J221" s="4">
         <v>26179</v>
@@ -24785,7 +24783,7 @@
         <v>887</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J222" s="4">
         <v>25245</v>
@@ -24852,7 +24850,7 @@
         <v>887</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J223" s="4">
         <v>27899</v>
@@ -24917,7 +24915,7 @@
         <v>887</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J224" s="4">
         <v>28810</v>
@@ -25112,7 +25110,7 @@
         <v>887</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J227" s="4">
         <v>29795</v>
@@ -25173,7 +25171,7 @@
         <v>887</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J228" s="4">
         <v>29784</v>
@@ -25354,7 +25352,7 @@
         <v>887</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J231" s="4">
         <v>30375</v>
@@ -25476,7 +25474,7 @@
         <v>887</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J233" s="4">
         <v>35566</v>
@@ -25667,7 +25665,7 @@
         <v>887</v>
       </c>
       <c r="I236" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J236" s="30">
         <v>35453</v>
@@ -25730,7 +25728,7 @@
         <v>887</v>
       </c>
       <c r="I237" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J237" s="4">
         <v>37092</v>
@@ -25789,7 +25787,7 @@
         <v>887</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J238" s="4">
         <v>37131</v>
@@ -25848,7 +25846,7 @@
         <v>887</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J239" s="4">
         <v>35222</v>
@@ -25966,7 +25964,7 @@
         <v>887</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J241" s="4">
         <v>29244</v>
@@ -26029,7 +26027,7 @@
         <v>887</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J242" s="4">
         <v>37667</v>
@@ -26084,7 +26082,7 @@
         <v>987</v>
       </c>
       <c r="I243" s="12" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="J243" s="4">
         <v>28773</v>
@@ -26145,7 +26143,7 @@
         <v>987</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J244" s="4">
         <v>32397</v>
@@ -26206,7 +26204,7 @@
         <v>987</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="J245" s="4">
         <v>29632</v>
@@ -26265,7 +26263,7 @@
         <v>987</v>
       </c>
       <c r="I246" s="12" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="J246" s="4">
         <v>32821</v>
@@ -26326,7 +26324,7 @@
         <v>987</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="J247" s="7">
         <v>34005</v>
@@ -26387,7 +26385,7 @@
         <v>1015</v>
       </c>
       <c r="I248" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J248" s="4">
         <v>25686</v>
@@ -26450,7 +26448,7 @@
         <v>1015</v>
       </c>
       <c r="I249" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J249" s="4">
         <v>34428</v>
@@ -26513,7 +26511,7 @@
         <v>1015</v>
       </c>
       <c r="I250" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J250" s="4">
         <v>38161</v>
@@ -26572,7 +26570,7 @@
         <v>1031</v>
       </c>
       <c r="I251" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J251" s="4">
         <v>29502</v>
@@ -26637,7 +26635,7 @@
         <v>1031</v>
       </c>
       <c r="I252" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J252" s="4">
         <v>27467</v>
@@ -26704,7 +26702,7 @@
         <v>1031</v>
       </c>
       <c r="I253" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J253" s="4">
         <v>31072</v>
@@ -26769,7 +26767,7 @@
         <v>1031</v>
       </c>
       <c r="I254" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J254" s="4">
         <v>28947</v>
@@ -26832,7 +26830,7 @@
         <v>1031</v>
       </c>
       <c r="I255" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J255" s="4">
         <v>30188</v>
@@ -26897,7 +26895,7 @@
         <v>1031</v>
       </c>
       <c r="I256" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J256" s="4">
         <v>30109</v>
@@ -26958,7 +26956,7 @@
         <v>1031</v>
       </c>
       <c r="I257" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J257" s="4">
         <v>30091</v>
@@ -27019,7 +27017,7 @@
         <v>1031</v>
       </c>
       <c r="I258" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J258" s="4">
         <v>32568</v>
@@ -27078,7 +27076,7 @@
         <v>1031</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J259" s="4">
         <v>32798</v>
@@ -27141,7 +27139,7 @@
         <v>1031</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J260" s="4">
         <v>28807</v>
@@ -27202,7 +27200,7 @@
         <v>1031</v>
       </c>
       <c r="I261" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J261" s="4">
         <v>31345</v>
@@ -27265,7 +27263,7 @@
         <v>1031</v>
       </c>
       <c r="I262" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J262" s="4">
         <v>32160</v>
@@ -27326,7 +27324,7 @@
         <v>1031</v>
       </c>
       <c r="I263" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J263" s="4">
         <v>34993</v>
@@ -27387,7 +27385,7 @@
         <v>1031</v>
       </c>
       <c r="I264" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J264" s="4">
         <v>34755</v>
@@ -27448,7 +27446,7 @@
         <v>1031</v>
       </c>
       <c r="I265" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J265" s="4">
         <v>35319</v>
@@ -27509,7 +27507,7 @@
         <v>1031</v>
       </c>
       <c r="I266" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J266" s="4">
         <v>36369</v>
@@ -27568,7 +27566,7 @@
         <v>1031</v>
       </c>
       <c r="I267" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J267" s="4">
         <v>36873</v>
@@ -27627,7 +27625,7 @@
         <v>1031</v>
       </c>
       <c r="I268" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J268" s="4">
         <v>37011</v>
@@ -27686,7 +27684,7 @@
         <v>1031</v>
       </c>
       <c r="I269" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J269" s="4">
         <v>36624</v>
@@ -27745,7 +27743,7 @@
         <v>1031</v>
       </c>
       <c r="I270" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J270" s="30">
         <v>36912</v>
@@ -27806,7 +27804,7 @@
         <v>1031</v>
       </c>
       <c r="I271" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J271" s="4">
         <v>27755</v>
@@ -27867,7 +27865,7 @@
         <v>1031</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J272" s="4">
         <v>36818</v>
@@ -27926,7 +27924,7 @@
         <v>1031</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J273" s="4">
         <v>37350</v>
@@ -27985,7 +27983,7 @@
         <v>1031</v>
       </c>
       <c r="I274" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J274" s="4">
         <v>31704</v>
@@ -28048,7 +28046,7 @@
         <v>1031</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J275" s="4">
         <v>38352</v>
@@ -28107,7 +28105,7 @@
         <v>1031</v>
       </c>
       <c r="I276" s="12" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J276" s="4">
         <v>37656</v>
@@ -28166,7 +28164,7 @@
         <v>1031</v>
       </c>
       <c r="I277" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J277" s="30">
         <v>36580</v>
@@ -28227,7 +28225,7 @@
         <v>1031</v>
       </c>
       <c r="I278" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J278" s="4">
         <v>37795</v>
@@ -28286,7 +28284,7 @@
         <v>1156</v>
       </c>
       <c r="I279" s="12" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J279" s="4">
         <v>27404</v>
@@ -28353,7 +28351,7 @@
         <v>1156</v>
       </c>
       <c r="I280" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J280" s="4">
         <v>27798</v>
@@ -28416,7 +28414,7 @@
         <v>1156</v>
       </c>
       <c r="I281" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J281" s="4">
         <v>31200</v>
@@ -28481,7 +28479,7 @@
         <v>1156</v>
       </c>
       <c r="I282" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J282" s="4">
         <v>31023</v>
@@ -28544,7 +28542,7 @@
         <v>1156</v>
       </c>
       <c r="I283" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J283" s="4">
         <v>29620</v>
@@ -28609,7 +28607,7 @@
         <v>1156</v>
       </c>
       <c r="I284" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J284" s="4">
         <v>31396</v>
@@ -28672,7 +28670,7 @@
         <v>1156</v>
       </c>
       <c r="I285" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J285" s="4">
         <v>33184</v>
@@ -28733,7 +28731,7 @@
         <v>1156</v>
       </c>
       <c r="I286" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J286" s="4">
         <v>31790</v>
@@ -28794,7 +28792,7 @@
         <v>1156</v>
       </c>
       <c r="I287" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J287" s="30">
         <v>35977</v>
@@ -28857,7 +28855,7 @@
         <v>1156</v>
       </c>
       <c r="I288" s="12" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J288" s="4">
         <v>36765</v>
@@ -28916,7 +28914,7 @@
         <v>1723</v>
       </c>
       <c r="I289" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J289" s="4">
         <v>28270</v>
@@ -28983,7 +28981,7 @@
         <v>1329</v>
       </c>
       <c r="I290" s="12" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="J290" s="4">
         <v>32349</v>
@@ -29050,7 +29048,7 @@
         <v>1214</v>
       </c>
       <c r="I291" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J291" s="4">
         <v>29258</v>
@@ -29113,7 +29111,7 @@
         <v>1214</v>
       </c>
       <c r="I292" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J292" s="4">
         <v>31799</v>
@@ -29176,7 +29174,7 @@
         <v>1214</v>
       </c>
       <c r="I293" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J293" s="4">
         <v>30570</v>
@@ -29237,7 +29235,7 @@
         <v>1225</v>
       </c>
       <c r="I294" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J294" s="4">
         <v>34055</v>
@@ -29300,7 +29298,7 @@
         <v>1225</v>
       </c>
       <c r="I295" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J295" s="4">
         <v>33479</v>
@@ -29361,7 +29359,7 @@
         <v>1225</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J296" s="4">
         <v>33491</v>
@@ -29420,7 +29418,7 @@
         <v>1225</v>
       </c>
       <c r="I297" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J297" s="4">
         <v>32261</v>
@@ -29479,7 +29477,7 @@
         <v>1225</v>
       </c>
       <c r="I298" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J298" s="4">
         <v>35528</v>
@@ -29536,7 +29534,7 @@
         <v>1225</v>
       </c>
       <c r="I299" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J299" s="4">
         <v>35749</v>
@@ -29591,7 +29589,7 @@
         <v>1225</v>
       </c>
       <c r="I300" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J300" s="4">
         <v>36477</v>
@@ -29646,7 +29644,7 @@
         <v>1225</v>
       </c>
       <c r="I301" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J301" s="4">
         <v>31975</v>
@@ -29701,7 +29699,7 @@
         <v>1225</v>
       </c>
       <c r="I302" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J302" s="4">
         <v>31758</v>
@@ -29760,7 +29758,7 @@
         <v>1266</v>
       </c>
       <c r="I303" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J303" s="4">
         <v>27833</v>
@@ -29821,7 +29819,7 @@
         <v>1214</v>
       </c>
       <c r="I304" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J304" s="4">
         <v>31620</v>
@@ -29882,7 +29880,7 @@
         <v>1266</v>
       </c>
       <c r="I305" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J305" s="4">
         <v>34301</v>
@@ -29939,7 +29937,7 @@
         <v>1266</v>
       </c>
       <c r="I306" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J306" s="4">
         <v>35899</v>
@@ -29994,7 +29992,7 @@
         <v>1266</v>
       </c>
       <c r="I307" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J307" s="4">
         <v>36282</v>
@@ -30053,7 +30051,7 @@
         <v>1266</v>
       </c>
       <c r="I308" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J308" s="4">
         <v>38032</v>
@@ -30112,7 +30110,7 @@
         <v>1266</v>
       </c>
       <c r="I309" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J309" s="4">
         <v>27731</v>
@@ -30173,7 +30171,7 @@
         <v>3448</v>
       </c>
       <c r="I310" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J310" s="4">
         <v>28905</v>
@@ -30234,7 +30232,7 @@
         <v>3448</v>
       </c>
       <c r="I311" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J311" s="4">
         <v>28927</v>
@@ -30297,7 +30295,7 @@
         <v>3448</v>
       </c>
       <c r="I312" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J312" s="4">
         <v>32480</v>
@@ -30360,7 +30358,7 @@
         <v>3448</v>
       </c>
       <c r="I313" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J313" s="4">
         <v>34495</v>
@@ -30421,7 +30419,7 @@
         <v>1214</v>
       </c>
       <c r="I314" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J314" s="4">
         <v>32921</v>
@@ -30478,7 +30476,7 @@
         <v>3448</v>
       </c>
       <c r="I315" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J315" s="4">
         <v>35702</v>
@@ -30535,7 +30533,7 @@
         <v>1214</v>
       </c>
       <c r="I316" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J316" s="4">
         <v>36717</v>
@@ -30592,7 +30590,7 @@
         <v>3448</v>
       </c>
       <c r="I317" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J317" s="4">
         <v>35612</v>
@@ -30647,7 +30645,7 @@
         <v>3448</v>
       </c>
       <c r="I318" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J318" s="4">
         <v>35680</v>
@@ -30702,7 +30700,7 @@
         <v>3448</v>
       </c>
       <c r="I319" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J319" s="4">
         <v>36642</v>
@@ -30757,7 +30755,7 @@
         <v>3448</v>
       </c>
       <c r="I320" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J320" s="4">
         <v>37705</v>
@@ -30816,7 +30814,7 @@
         <v>3448</v>
       </c>
       <c r="I321" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J321" s="4">
         <v>29261</v>
@@ -30875,7 +30873,7 @@
         <v>3448</v>
       </c>
       <c r="I322" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J322" s="4">
         <v>37533</v>
@@ -30934,7 +30932,7 @@
         <v>3448</v>
       </c>
       <c r="I323" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J323" s="4">
         <v>38243</v>
@@ -30993,7 +30991,7 @@
         <v>3448</v>
       </c>
       <c r="I324" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J324" s="4">
         <v>38145</v>
@@ -31052,7 +31050,7 @@
         <v>1296</v>
       </c>
       <c r="I325" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J325" s="4">
         <v>33869</v>
@@ -31113,7 +31111,7 @@
         <v>3449</v>
       </c>
       <c r="I326" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J326" s="4">
         <v>28361</v>
@@ -31178,7 +31176,7 @@
         <v>3449</v>
       </c>
       <c r="I327" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J327" s="4">
         <v>29049</v>
@@ -31243,7 +31241,7 @@
         <v>3449</v>
       </c>
       <c r="I328" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J328" s="4">
         <v>30185</v>
@@ -31304,7 +31302,7 @@
         <v>3449</v>
       </c>
       <c r="I329" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J329" s="4">
         <v>30108</v>
@@ -31367,7 +31365,7 @@
         <v>3449</v>
       </c>
       <c r="I330" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J330" s="4">
         <v>34089</v>
@@ -31430,7 +31428,7 @@
         <v>3449</v>
       </c>
       <c r="I331" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J331" s="4">
         <v>34568</v>
@@ -31491,7 +31489,7 @@
         <v>3449</v>
       </c>
       <c r="I332" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J332" s="4">
         <v>28572</v>
@@ -31554,7 +31552,7 @@
         <v>3449</v>
       </c>
       <c r="I333" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J333" s="4">
         <v>22583</v>
@@ -31609,7 +31607,7 @@
         <v>3449</v>
       </c>
       <c r="I334" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J334" s="4">
         <v>23968</v>
@@ -31668,7 +31666,7 @@
         <v>1498</v>
       </c>
       <c r="I335" s="12" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="J335" s="4">
         <v>32420</v>
@@ -31735,7 +31733,7 @@
         <v>1409</v>
       </c>
       <c r="I336" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J336" s="4">
         <v>25410</v>
@@ -31802,7 +31800,7 @@
         <v>1409</v>
       </c>
       <c r="I337" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J337" s="4">
         <v>30369</v>
@@ -31863,7 +31861,7 @@
         <v>1409</v>
       </c>
       <c r="I338" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J338" s="4">
         <v>31613</v>
@@ -31924,7 +31922,7 @@
         <v>1498</v>
       </c>
       <c r="I339" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J339" s="4">
         <v>35201</v>
@@ -31983,7 +31981,7 @@
         <v>1409</v>
       </c>
       <c r="I340" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J340" s="4">
         <v>36254</v>
@@ -32042,7 +32040,7 @@
         <v>1409</v>
       </c>
       <c r="I341" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J341" s="4">
         <v>36044</v>
@@ -32101,7 +32099,7 @@
         <v>1409</v>
       </c>
       <c r="I342" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J342" s="4">
         <v>37923</v>
@@ -32160,7 +32158,7 @@
         <v>1434</v>
       </c>
       <c r="I343" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J343" s="4">
         <v>26795</v>
@@ -32223,7 +32221,7 @@
         <v>1434</v>
       </c>
       <c r="I344" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J344" s="4">
         <v>29397</v>
@@ -32284,7 +32282,7 @@
         <v>1434</v>
       </c>
       <c r="I345" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J345" s="4">
         <v>29071</v>
@@ -32347,7 +32345,7 @@
         <v>1434</v>
       </c>
       <c r="I346" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J346" s="4">
         <v>29976</v>
@@ -32408,7 +32406,7 @@
         <v>1434</v>
       </c>
       <c r="I347" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J347" s="4">
         <v>30974</v>
@@ -32469,7 +32467,7 @@
         <v>1434</v>
       </c>
       <c r="I348" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J348" s="4">
         <v>33478</v>
@@ -32530,7 +32528,7 @@
         <v>1434</v>
       </c>
       <c r="I349" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J349" s="4">
         <v>35775</v>
@@ -32593,7 +32591,7 @@
         <v>1434</v>
       </c>
       <c r="I350" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J350" s="4">
         <v>36341</v>
@@ -32652,7 +32650,7 @@
         <v>1434</v>
       </c>
       <c r="I351" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J351" s="4">
         <v>30542</v>
@@ -32713,7 +32711,7 @@
         <v>1434</v>
       </c>
       <c r="I352" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J352" s="30">
         <v>37531</v>
@@ -32774,7 +32772,7 @@
         <v>1472</v>
       </c>
       <c r="I353" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J353" s="4">
         <v>31992</v>
@@ -32829,7 +32827,7 @@
         <v>1498</v>
       </c>
       <c r="I354" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J354" s="4">
         <v>35537</v>
@@ -32884,7 +32882,7 @@
         <v>1214</v>
       </c>
       <c r="I355" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J355" s="4">
         <v>35619</v>
@@ -32943,7 +32941,7 @@
         <v>1214</v>
       </c>
       <c r="I356" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J356" s="4">
         <v>38033</v>
@@ -33002,7 +33000,7 @@
         <v>1472</v>
       </c>
       <c r="I357" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J357" s="4">
         <v>38044</v>
@@ -33061,7 +33059,7 @@
         <v>1225</v>
       </c>
       <c r="I358" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J358" s="4">
         <v>38129</v>
@@ -33120,7 +33118,7 @@
         <v>1472</v>
       </c>
       <c r="I359" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J359" s="4">
         <v>38139</v>
@@ -33179,7 +33177,7 @@
         <v>1472</v>
       </c>
       <c r="I360" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J360" s="4">
         <v>37859</v>
@@ -33238,7 +33236,7 @@
         <v>1472</v>
       </c>
       <c r="I361" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J361" s="4">
         <v>36341</v>
@@ -33297,7 +33295,7 @@
         <v>1472</v>
       </c>
       <c r="I362" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J362" s="4">
         <v>37230</v>
@@ -33356,7 +33354,7 @@
         <v>1472</v>
       </c>
       <c r="I363" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J363" s="4">
         <v>37965</v>
@@ -33415,7 +33413,7 @@
         <v>1675</v>
       </c>
       <c r="I364" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J364" s="4">
         <v>29459</v>
@@ -33476,7 +33474,7 @@
         <v>1675</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="J365" s="4">
         <v>32140</v>
@@ -33539,7 +33537,7 @@
         <v>1503</v>
       </c>
       <c r="I366" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J366" s="4">
         <v>27813</v>
@@ -33604,7 +33602,7 @@
         <v>1503</v>
       </c>
       <c r="I367" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J367" s="4">
         <v>30068</v>
@@ -33665,7 +33663,7 @@
         <v>1503</v>
       </c>
       <c r="I368" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J368" s="4">
         <v>29601</v>
@@ -33728,7 +33726,7 @@
         <v>1503</v>
       </c>
       <c r="I369" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J369" s="4">
         <v>33914</v>
@@ -33791,7 +33789,7 @@
         <v>1503</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J370" s="4">
         <v>34401</v>
@@ -33850,7 +33848,7 @@
         <v>1503</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J371" s="4">
         <v>35614</v>
@@ -33909,7 +33907,7 @@
         <v>1503</v>
       </c>
       <c r="I372" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J372" s="4">
         <v>36996</v>
@@ -33968,7 +33966,7 @@
         <v>1503</v>
       </c>
       <c r="I373" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J373" s="4">
         <v>35814</v>
@@ -34027,7 +34025,7 @@
         <v>1537</v>
       </c>
       <c r="I374" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J374" s="4">
         <v>31140</v>
@@ -34088,7 +34086,7 @@
         <v>1537</v>
       </c>
       <c r="I375" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J375" s="4">
         <v>30816</v>
@@ -34149,7 +34147,7 @@
         <v>1537</v>
       </c>
       <c r="I376" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J376" s="4">
         <v>34262</v>
@@ -34208,7 +34206,7 @@
         <v>1537</v>
       </c>
       <c r="I377" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J377" s="4">
         <v>35425</v>
@@ -34267,7 +34265,7 @@
         <v>1537</v>
       </c>
       <c r="I378" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J378" s="4">
         <v>31180</v>
@@ -34330,7 +34328,7 @@
         <v>1537</v>
       </c>
       <c r="I379" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J379" s="4">
         <v>35887</v>
@@ -34389,7 +34387,7 @@
         <v>1537</v>
       </c>
       <c r="I380" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J380" s="4">
         <v>33745</v>
@@ -34450,7 +34448,7 @@
         <v>1537</v>
       </c>
       <c r="I381" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J381" s="4">
         <v>38077</v>
@@ -34509,7 +34507,7 @@
         <v>1570</v>
       </c>
       <c r="I382" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J382" s="4">
         <v>31470</v>
@@ -34572,7 +34570,7 @@
         <v>1570</v>
       </c>
       <c r="I383" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J383" s="4">
         <v>31841</v>
@@ -34633,7 +34631,7 @@
         <v>1570</v>
       </c>
       <c r="I384" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J384" s="4">
         <v>31098</v>
@@ -34694,7 +34692,7 @@
         <v>1570</v>
       </c>
       <c r="I385" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J385" s="4">
         <v>33088</v>
@@ -34757,7 +34755,7 @@
         <v>1570</v>
       </c>
       <c r="I386" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J386" s="4">
         <v>34083</v>
@@ -34818,7 +34816,7 @@
         <v>1570</v>
       </c>
       <c r="I387" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J387" s="4">
         <v>36721</v>
@@ -34877,7 +34875,7 @@
         <v>1570</v>
       </c>
       <c r="I388" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J388" s="4">
         <v>35697</v>
@@ -34936,7 +34934,7 @@
         <v>1570</v>
       </c>
       <c r="I389" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J389" s="4">
         <v>34669</v>
@@ -34995,7 +34993,7 @@
         <v>1570</v>
       </c>
       <c r="I390" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J390" s="4">
         <v>35874</v>
@@ -35054,7 +35052,7 @@
         <v>1570</v>
       </c>
       <c r="I391" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J391" s="4">
         <v>36275</v>
@@ -35113,7 +35111,7 @@
         <v>1570</v>
       </c>
       <c r="I392" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J392" s="4">
         <v>29105</v>
@@ -35172,7 +35170,7 @@
         <v>1570</v>
       </c>
       <c r="I393" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J393" s="4">
         <v>28167</v>
@@ -35237,7 +35235,7 @@
         <v>1618</v>
       </c>
       <c r="I394" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J394" s="4">
         <v>38188</v>
@@ -35296,7 +35294,7 @@
         <v>1618</v>
       </c>
       <c r="I395" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J395" s="4">
         <v>35897</v>
@@ -35355,7 +35353,7 @@
         <v>1626</v>
       </c>
       <c r="I396" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J396" s="4">
         <v>31103</v>
@@ -35418,7 +35416,7 @@
         <v>1626</v>
       </c>
       <c r="I397" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J397" s="4">
         <v>31247</v>
@@ -35479,7 +35477,7 @@
         <v>1626</v>
       </c>
       <c r="I398" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J398" s="4">
         <v>29253</v>
@@ -35540,7 +35538,7 @@
         <v>1626</v>
       </c>
       <c r="I399" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J399" s="4">
         <v>35737</v>
@@ -35601,7 +35599,7 @@
         <v>1626</v>
       </c>
       <c r="I400" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J400" s="4">
         <v>37140</v>
@@ -35660,7 +35658,7 @@
         <v>1626</v>
       </c>
       <c r="I401" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J401" s="4">
         <v>35078</v>
@@ -35719,7 +35717,7 @@
         <v>1653</v>
       </c>
       <c r="I402" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J402" s="4">
         <v>29524</v>
@@ -35780,7 +35778,7 @@
         <v>1653</v>
       </c>
       <c r="I403" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J403" s="4">
         <v>29926</v>
@@ -35843,7 +35841,7 @@
         <v>1653</v>
       </c>
       <c r="I404" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J404" s="4">
         <v>31429</v>
@@ -35904,7 +35902,7 @@
         <v>1653</v>
       </c>
       <c r="I405" s="12" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J405" s="4">
         <v>34418</v>
@@ -35965,7 +35963,7 @@
         <v>1653</v>
       </c>
       <c r="I406" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J406" s="4">
         <v>35726</v>
@@ -36024,7 +36022,7 @@
         <v>1653</v>
       </c>
       <c r="I407" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J407" s="4">
         <v>37098</v>
@@ -36083,7 +36081,7 @@
         <v>3399</v>
       </c>
       <c r="I408" s="12" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J408" s="4">
         <v>30270</v>
@@ -36144,7 +36142,7 @@
         <v>3399</v>
       </c>
       <c r="I409" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J409" s="4">
         <v>29299</v>
@@ -36211,7 +36209,7 @@
         <v>3399</v>
       </c>
       <c r="I410" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J410" s="4">
         <v>31102</v>
@@ -36272,7 +36270,7 @@
         <v>3399</v>
       </c>
       <c r="I411" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J411" s="4">
         <v>32000</v>
@@ -36333,7 +36331,7 @@
         <v>3399</v>
       </c>
       <c r="I412" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J412" s="30">
         <v>34949</v>
@@ -36396,7 +36394,7 @@
         <v>3399</v>
       </c>
       <c r="I413" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J413" s="4">
         <v>37012</v>
@@ -36455,7 +36453,7 @@
         <v>3399</v>
       </c>
       <c r="I414" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J414" s="30">
         <v>37176</v>
@@ -36516,7 +36514,7 @@
         <v>3399</v>
       </c>
       <c r="I415" s="12" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J415" s="4">
         <v>25767</v>
@@ -36575,7 +36573,7 @@
         <v>3399</v>
       </c>
       <c r="I416" s="12" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J416" s="4">
         <v>28101</v>
@@ -36634,7 +36632,7 @@
         <v>1975</v>
       </c>
       <c r="I417" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J417" s="4">
         <v>27745</v>
@@ -36825,7 +36823,7 @@
         <v>1738</v>
       </c>
       <c r="I420" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J420" s="4">
         <v>27594</v>
@@ -36884,7 +36882,7 @@
         <v>1738</v>
       </c>
       <c r="I421" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J421" s="4">
         <v>27831</v>
@@ -36945,7 +36943,7 @@
         <v>1738</v>
       </c>
       <c r="I422" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J422" s="4">
         <v>31765</v>
@@ -37004,7 +37002,7 @@
         <v>1738</v>
       </c>
       <c r="I423" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J423" s="4">
         <v>33774</v>
@@ -37059,7 +37057,7 @@
         <v>1738</v>
       </c>
       <c r="I424" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J424" s="4">
         <v>34572</v>
@@ -37116,7 +37114,7 @@
         <v>1738</v>
       </c>
       <c r="I425" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J425" s="4">
         <v>33751</v>
@@ -37173,7 +37171,7 @@
         <v>1738</v>
       </c>
       <c r="I426" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J426" s="4">
         <v>31858</v>
@@ -37230,7 +37228,7 @@
         <v>1738</v>
       </c>
       <c r="I427" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J427" s="4">
         <v>36545</v>
@@ -37285,7 +37283,7 @@
         <v>1738</v>
       </c>
       <c r="I428" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J428" s="4">
         <v>33919</v>
@@ -37342,7 +37340,7 @@
         <v>1738</v>
       </c>
       <c r="I429" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J429" s="4">
         <v>36014</v>
@@ -37397,7 +37395,7 @@
         <v>1738</v>
       </c>
       <c r="I430" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J430" s="4">
         <v>32650</v>
@@ -37454,7 +37452,7 @@
         <v>1738</v>
       </c>
       <c r="I431" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J431" s="4">
         <v>30554</v>
@@ -37511,7 +37509,7 @@
         <v>1738</v>
       </c>
       <c r="I432" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J432" s="4">
         <v>36820</v>
@@ -37566,7 +37564,7 @@
         <v>1738</v>
       </c>
       <c r="I433" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J433" s="4">
         <v>37579</v>
@@ -37621,7 +37619,7 @@
         <v>1738</v>
       </c>
       <c r="I434" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J434" s="4">
         <v>37796</v>
@@ -37676,7 +37674,7 @@
         <v>1738</v>
       </c>
       <c r="I435" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J435" s="4">
         <v>34171</v>
@@ -37731,7 +37729,7 @@
         <v>1738</v>
       </c>
       <c r="I436" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J436" s="4">
         <v>34141</v>
@@ -37790,7 +37788,7 @@
         <v>1738</v>
       </c>
       <c r="I437" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J437" s="4">
         <v>37643</v>
@@ -37849,7 +37847,7 @@
         <v>1738</v>
       </c>
       <c r="I438" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J438" s="4">
         <v>36897</v>
@@ -37904,7 +37902,7 @@
         <v>1802</v>
       </c>
       <c r="I439" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J439" s="4">
         <v>30416</v>
@@ -37959,7 +37957,7 @@
         <v>1802</v>
       </c>
       <c r="I440" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J440" s="4">
         <v>30919</v>
@@ -38018,7 +38016,7 @@
         <v>1802</v>
       </c>
       <c r="I441" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J441" s="4">
         <v>30195</v>
@@ -38077,7 +38075,7 @@
         <v>1802</v>
       </c>
       <c r="I442" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J442" s="4">
         <v>35171</v>
@@ -38138,7 +38136,7 @@
         <v>1802</v>
       </c>
       <c r="I443" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J443" s="4">
         <v>33666</v>
@@ -38193,7 +38191,7 @@
         <v>1802</v>
       </c>
       <c r="I444" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J444" s="4">
         <v>28370</v>
@@ -38254,7 +38252,7 @@
         <v>1826</v>
       </c>
       <c r="I445" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J445" s="4">
         <v>27692</v>
@@ -38313,7 +38311,7 @@
         <v>1826</v>
       </c>
       <c r="I446" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J446" s="4">
         <v>29222</v>
@@ -38370,7 +38368,7 @@
         <v>1826</v>
       </c>
       <c r="I447" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J447" s="4">
         <v>29052</v>
@@ -38427,7 +38425,7 @@
         <v>1826</v>
       </c>
       <c r="I448" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J448" s="4">
         <v>29813</v>
@@ -38484,7 +38482,7 @@
         <v>1826</v>
       </c>
       <c r="I449" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J449" s="4">
         <v>31380</v>
@@ -38541,7 +38539,7 @@
         <v>1826</v>
       </c>
       <c r="I450" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J450" s="4">
         <v>30670</v>
@@ -38600,7 +38598,7 @@
         <v>1826</v>
       </c>
       <c r="I451" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J451" s="4">
         <v>31889</v>
@@ -38659,7 +38657,7 @@
         <v>1826</v>
       </c>
       <c r="I452" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J452" s="4">
         <v>31878</v>
@@ -38716,7 +38714,7 @@
         <v>1826</v>
       </c>
       <c r="I453" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J453" s="4">
         <v>32202</v>
@@ -38775,7 +38773,7 @@
         <v>1826</v>
       </c>
       <c r="I454" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J454" s="4">
         <v>33901</v>
@@ -38832,7 +38830,7 @@
         <v>1826</v>
       </c>
       <c r="I455" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J455" s="4">
         <v>33809</v>
@@ -38887,7 +38885,7 @@
         <v>1826</v>
       </c>
       <c r="I456" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J456" s="4">
         <v>34100</v>
@@ -38948,7 +38946,7 @@
         <v>1826</v>
       </c>
       <c r="I457" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J457" s="4">
         <v>34072</v>
@@ -39005,7 +39003,7 @@
         <v>1826</v>
       </c>
       <c r="I458" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J458" s="4">
         <v>33789</v>
@@ -39064,7 +39062,7 @@
         <v>1826</v>
       </c>
       <c r="I459" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J459" s="4">
         <v>34390</v>
@@ -39119,7 +39117,7 @@
         <v>1826</v>
       </c>
       <c r="I460" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J460" s="4">
         <v>33309</v>
@@ -39174,7 +39172,7 @@
         <v>1826</v>
       </c>
       <c r="I461" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J461" s="4">
         <v>37198</v>
@@ -39233,7 +39231,7 @@
         <v>1826</v>
       </c>
       <c r="I462" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J462" s="4">
         <v>31754</v>
@@ -39359,7 +39357,7 @@
         <v>1896</v>
       </c>
       <c r="I464" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J464" s="4">
         <v>26094</v>
@@ -39422,7 +39420,7 @@
         <v>1896</v>
       </c>
       <c r="I465" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J465" s="4">
         <v>26816</v>
@@ -39485,7 +39483,7 @@
         <v>1896</v>
       </c>
       <c r="I466" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J466" s="4">
         <v>29766</v>
@@ -39548,7 +39546,7 @@
         <v>1896</v>
       </c>
       <c r="I467" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J467" s="4">
         <v>30486</v>
@@ -39607,7 +39605,7 @@
         <v>1896</v>
       </c>
       <c r="I468" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J468" s="4">
         <v>34789</v>
@@ -39670,7 +39668,7 @@
         <v>2760</v>
       </c>
       <c r="I469" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J469" s="4">
         <v>28904</v>
@@ -39729,7 +39727,7 @@
         <v>2760</v>
       </c>
       <c r="I470" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J470" s="4">
         <v>29999</v>
@@ -39792,7 +39790,7 @@
         <v>2760</v>
       </c>
       <c r="I471" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J471" s="4">
         <v>30073</v>
@@ -39855,7 +39853,7 @@
         <v>2760</v>
       </c>
       <c r="I472" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J472" s="4">
         <v>30853</v>
@@ -39914,7 +39912,7 @@
         <v>2760</v>
       </c>
       <c r="I473" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J473" s="4">
         <v>30377</v>
@@ -39977,7 +39975,7 @@
         <v>2760</v>
       </c>
       <c r="I474" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J474" s="4">
         <v>33920</v>
@@ -40040,7 +40038,7 @@
         <v>2760</v>
       </c>
       <c r="I475" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J475" s="4">
         <v>33521</v>
@@ -40101,7 +40099,7 @@
         <v>2760</v>
       </c>
       <c r="I476" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J476" s="4">
         <v>34768</v>
@@ -40162,7 +40160,7 @@
         <v>2760</v>
       </c>
       <c r="I477" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J477" s="30">
         <v>34893</v>
@@ -40227,7 +40225,7 @@
         <v>2760</v>
       </c>
       <c r="I478" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J478" s="4">
         <v>36207</v>
@@ -40286,7 +40284,7 @@
         <v>2760</v>
       </c>
       <c r="I479" s="12" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J479" s="4">
         <v>38304</v>
@@ -40345,7 +40343,7 @@
         <v>2015</v>
       </c>
       <c r="I480" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J480" s="4">
         <v>29617</v>
@@ -40412,7 +40410,7 @@
         <v>2015</v>
       </c>
       <c r="I481" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J481" s="30">
         <v>37154</v>
@@ -40473,7 +40471,7 @@
         <v>2015</v>
       </c>
       <c r="I482" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J482" s="30">
         <v>37828</v>
@@ -40534,7 +40532,7 @@
         <v>1982</v>
       </c>
       <c r="I483" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J483" s="4">
         <v>26226</v>
@@ -40597,7 +40595,7 @@
         <v>1982</v>
       </c>
       <c r="I484" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J484" s="4">
         <v>36399</v>
@@ -40660,7 +40658,7 @@
         <v>1982</v>
       </c>
       <c r="I485" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J485" s="4">
         <v>37014</v>
@@ -40717,7 +40715,7 @@
         <v>1982</v>
       </c>
       <c r="I486" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J486" s="4">
         <v>35213</v>
@@ -40778,7 +40776,7 @@
         <v>1982</v>
       </c>
       <c r="I487" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J487" s="4">
         <v>25866</v>
@@ -40839,7 +40837,7 @@
         <v>2009</v>
       </c>
       <c r="I488" s="12" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J488" s="4">
         <v>31698</v>
@@ -40898,7 +40896,7 @@
         <v>2118</v>
       </c>
       <c r="I489" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J489" s="4">
         <v>30522</v>
@@ -40965,7 +40963,7 @@
         <v>2118</v>
       </c>
       <c r="I490" s="12" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J490" s="30">
         <v>34526</v>
@@ -41026,7 +41024,7 @@
         <v>2032</v>
       </c>
       <c r="I491" s="12" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J491" s="4">
         <v>28251</v>
@@ -41087,7 +41085,7 @@
         <v>2032</v>
       </c>
       <c r="I492" s="12" t="s">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="J492" s="4">
         <v>35430</v>
@@ -41148,7 +41146,7 @@
         <v>2032</v>
       </c>
       <c r="I493" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J493" s="4">
         <v>35279</v>
@@ -41209,7 +41207,7 @@
         <v>2032</v>
       </c>
       <c r="I494" s="12" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J494" s="30">
         <v>37198</v>
@@ -41266,7 +41264,7 @@
         <v>2052</v>
       </c>
       <c r="I495" s="12" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="J495" s="4">
         <v>26456</v>
@@ -41323,7 +41321,7 @@
         <v>2052</v>
       </c>
       <c r="I496" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J496" s="4">
         <v>26793</v>
@@ -41386,7 +41384,7 @@
         <v>2052</v>
       </c>
       <c r="I497" s="12" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J497" s="4">
         <v>28064</v>
@@ -41449,7 +41447,7 @@
         <v>2052</v>
       </c>
       <c r="I498" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J498" s="4">
         <v>28597</v>
@@ -41506,7 +41504,7 @@
         <v>2052</v>
       </c>
       <c r="I499" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J499" s="4">
         <v>29686</v>
@@ -41563,7 +41561,7 @@
         <v>2052</v>
       </c>
       <c r="I500" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J500" s="4">
         <v>30180</v>
@@ -41622,7 +41620,7 @@
         <v>2052</v>
       </c>
       <c r="I501" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J501" s="4">
         <v>29575</v>
@@ -41681,7 +41679,7 @@
         <v>2052</v>
       </c>
       <c r="I502" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J502" s="4">
         <v>34176</v>
@@ -41744,7 +41742,7 @@
         <v>2052</v>
       </c>
       <c r="I503" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J503" s="4">
         <v>37252</v>
@@ -41803,7 +41801,7 @@
         <v>2052</v>
       </c>
       <c r="I504" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J504" s="4">
         <v>36951</v>
@@ -41858,7 +41856,7 @@
         <v>2052</v>
       </c>
       <c r="I505" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J505" s="4">
         <v>36365</v>
@@ -41917,7 +41915,7 @@
         <v>2052</v>
       </c>
       <c r="I506" s="12" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="J506" s="4">
         <v>35700</v>
@@ -41978,7 +41976,7 @@
         <v>2052</v>
       </c>
       <c r="I507" s="12" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J507" s="4">
         <v>33889</v>
@@ -42033,7 +42031,7 @@
         <v>2104</v>
       </c>
       <c r="I508" s="12" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="J508" s="4">
         <v>26354</v>
@@ -42094,7 +42092,7 @@
         <v>2104</v>
       </c>
       <c r="I509" s="12" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="J509" s="4">
         <v>30475</v>
@@ -42153,7 +42151,7 @@
         <v>2104</v>
       </c>
       <c r="I510" s="12" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J510" s="4">
         <v>36147</v>
@@ -42210,7 +42208,7 @@
         <v>2129</v>
       </c>
       <c r="I511" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J511" s="4">
         <v>25892</v>
@@ -42271,7 +42269,7 @@
         <v>3343</v>
       </c>
       <c r="I512" s="12" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J512" s="4">
         <v>26070</v>
@@ -42338,7 +42336,7 @@
         <v>2136</v>
       </c>
       <c r="I513" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J513" s="4">
         <v>28852</v>
@@ -42403,7 +42401,7 @@
         <v>2136</v>
       </c>
       <c r="I514" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J514" s="4">
         <v>26976</v>
@@ -42466,7 +42464,7 @@
         <v>2136</v>
       </c>
       <c r="I515" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J515" s="4">
         <v>28983</v>
@@ -42527,7 +42525,7 @@
         <v>2136</v>
       </c>
       <c r="I516" s="12" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="J516" s="4">
         <v>32578</v>
@@ -42594,7 +42592,7 @@
         <v>2136</v>
       </c>
       <c r="I517" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J517" s="4">
         <v>31446</v>
@@ -42657,7 +42655,7 @@
         <v>2136</v>
       </c>
       <c r="I518" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J518" s="4">
         <v>33734</v>
@@ -42720,7 +42718,7 @@
         <v>2136</v>
       </c>
       <c r="I519" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J519" s="30">
         <v>34641</v>
@@ -42781,7 +42779,7 @@
         <v>2136</v>
       </c>
       <c r="I520" s="12" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J520" s="4">
         <v>36436</v>
@@ -42838,7 +42836,7 @@
         <v>2176</v>
       </c>
       <c r="I521" s="12" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J521" s="4">
         <v>24894</v>
@@ -42899,7 +42897,7 @@
         <v>2176</v>
       </c>
       <c r="I522" s="12" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="J522" s="4">
         <v>27775</v>
@@ -42962,7 +42960,7 @@
         <v>2176</v>
       </c>
       <c r="I523" s="12" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J523" s="4">
         <v>26227</v>
@@ -43025,7 +43023,7 @@
         <v>2176</v>
       </c>
       <c r="I524" s="12" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J524" s="4">
         <v>32393</v>
@@ -43088,7 +43086,7 @@
         <v>2176</v>
       </c>
       <c r="I525" s="12" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J525" s="4">
         <v>35421</v>
@@ -43151,7 +43149,7 @@
         <v>2176</v>
       </c>
       <c r="I526" s="12" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J526" s="4">
         <v>34782</v>
@@ -43208,7 +43206,7 @@
         <v>2418</v>
       </c>
       <c r="G527" s="12" t="s">
-        <v>3458</v>
+        <v>2828</v>
       </c>
       <c r="H527" s="12" t="s">
         <v>2403</v>
@@ -43271,7 +43269,7 @@
         <v>2347</v>
       </c>
       <c r="I528" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J528" s="4">
         <v>35452</v>
@@ -43328,7 +43326,7 @@
         <v>2347</v>
       </c>
       <c r="I529" s="12" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="J529" s="4">
         <v>28315</v>
@@ -43389,7 +43387,7 @@
         <v>2289</v>
       </c>
       <c r="I530" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J530" s="4">
         <v>26205</v>
@@ -43448,7 +43446,7 @@
         <v>2289</v>
       </c>
       <c r="I531" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J531" s="4">
         <v>28247</v>
@@ -43513,7 +43511,7 @@
         <v>2289</v>
       </c>
       <c r="I532" s="12" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="J532" s="4">
         <v>28302</v>
@@ -43574,7 +43572,7 @@
         <v>2289</v>
       </c>
       <c r="I533" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J533" s="4">
         <v>32373</v>
@@ -43635,7 +43633,7 @@
         <v>2289</v>
       </c>
       <c r="I534" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J534" s="4">
         <v>32840</v>
@@ -43696,7 +43694,7 @@
         <v>2289</v>
       </c>
       <c r="I535" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J535" s="4">
         <v>34681</v>
@@ -43755,7 +43753,7 @@
         <v>2289</v>
       </c>
       <c r="I536" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J536" s="4">
         <v>34577</v>
@@ -43812,7 +43810,7 @@
         <v>2289</v>
       </c>
       <c r="I537" s="12" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J537" s="4">
         <v>35212</v>
@@ -43869,7 +43867,7 @@
         <v>2326</v>
       </c>
       <c r="I538" s="12" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="J538" s="4">
         <v>25938</v>
@@ -43928,7 +43926,7 @@
         <v>2326</v>
       </c>
       <c r="I539" s="12" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="J539" s="4">
         <v>27608</v>
@@ -43993,7 +43991,7 @@
         <v>2326</v>
       </c>
       <c r="I540" s="12" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="J540" s="4">
         <v>27860</v>
@@ -44058,7 +44056,7 @@
         <v>2326</v>
       </c>
       <c r="I541" s="12" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="J541" s="4">
         <v>30299</v>
@@ -44121,7 +44119,7 @@
         <v>2688</v>
       </c>
       <c r="I542" s="12" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="J542" s="4">
         <v>27329</v>
@@ -44188,7 +44186,7 @@
         <v>2688</v>
       </c>
       <c r="I543" s="12" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J543" s="4">
         <v>36931</v>
@@ -44249,7 +44247,7 @@
         <v>2688</v>
       </c>
       <c r="I544" s="12" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="J544" s="4">
         <v>36052</v>
@@ -44310,7 +44308,7 @@
         <v>2359</v>
       </c>
       <c r="I545" s="12" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J545" s="4">
         <v>30430</v>
@@ -44371,7 +44369,7 @@
         <v>2365</v>
       </c>
       <c r="I546" s="12" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="J546" s="4">
         <v>35226</v>
@@ -44432,7 +44430,7 @@
         <v>2372</v>
       </c>
       <c r="I547" s="12" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J547" s="4">
         <v>32700</v>
@@ -44493,7 +44491,7 @@
         <v>2824</v>
       </c>
       <c r="I548" s="12" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="J548" s="4">
         <v>35012</v>
@@ -44554,7 +44552,7 @@
         <v>2379</v>
       </c>
       <c r="I549" s="12" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="J549" s="4">
         <v>35932</v>
@@ -44617,7 +44615,7 @@
         <v>2386</v>
       </c>
       <c r="I550" s="12" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="J550" s="4">
         <v>35583</v>
@@ -44678,7 +44676,7 @@
         <v>2391</v>
       </c>
       <c r="I551" s="12" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J551" s="4">
         <v>32591</v>
@@ -44737,7 +44735,7 @@
         <v>2397</v>
       </c>
       <c r="I552" s="12" t="s">
-        <v>3522</v>
+        <v>3520</v>
       </c>
       <c r="J552" s="4">
         <v>34762</v>
@@ -45050,7 +45048,7 @@
         <v>1031</v>
       </c>
       <c r="I557" s="12" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J557" s="7">
         <v>38583</v>
@@ -45109,7 +45107,7 @@
         <v>458</v>
       </c>
       <c r="I558" s="12" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J558" s="7">
         <v>35374</v>
@@ -45170,7 +45168,7 @@
         <v>2625</v>
       </c>
       <c r="I559" s="12" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="J559" s="7">
         <v>37273</v>
@@ -45231,7 +45229,7 @@
         <v>854</v>
       </c>
       <c r="I560" s="12" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J560" s="7">
         <v>35478</v>
@@ -45290,7 +45288,7 @@
         <v>1329</v>
       </c>
       <c r="I561" s="12" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J561" s="30">
         <v>37980</v>
@@ -45351,7 +45349,7 @@
         <v>1472</v>
       </c>
       <c r="I562" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J562" s="7">
         <v>36424</v>
@@ -45410,7 +45408,7 @@
         <v>1434</v>
       </c>
       <c r="I563" s="12" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J563" s="7">
         <v>35656</v>
@@ -45469,7 +45467,7 @@
         <v>1738</v>
       </c>
       <c r="I564" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J564" s="7">
         <v>38540</v>
@@ -45589,7 +45587,7 @@
         <v>3399</v>
       </c>
       <c r="I566" s="12" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J566" s="7">
         <v>37640</v>
@@ -45709,7 +45707,7 @@
         <v>1826</v>
       </c>
       <c r="I568" s="12" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J568" s="7">
         <v>38231</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAC25442-26A1-4671-8B8C-408165039622}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C79C96DF-542B-4BF0-B606-88EC527ABC10}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22047,7 +22047,7 @@
         <v>739</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>3485</v>
+        <v>3339</v>
       </c>
       <c r="J178" s="5">
         <v>29660</v>
@@ -22105,7 +22105,7 @@
         <v>65</v>
       </c>
       <c r="H179" s="11" t="s">
-        <v>739</v>
+        <v>3343</v>
       </c>
       <c r="I179" s="11">
         <v>169024</v>
@@ -46042,7 +46042,6 @@
   <autoFilter ref="A2:Z574" xr:uid="{DD8121B7-54E2-413D-99D3-BAFD2DFC5806}">
     <filterColumn colId="7">
       <filters>
-        <filter val="OGC-FAD-PCM"/>
         <filter val="OGC-FAD-PCM-PCM"/>
       </filters>
     </filterColumn>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C79C96DF-542B-4BF0-B606-88EC527ABC10}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{3C42439E-EA8E-4849-A162-187942176D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99D2100F-6E62-4050-AD3C-7C9CAFB2BF0E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$Z$574</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -11123,7 +11123,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8121B7-54E2-413D-99D3-BAFD2DFC5806}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y574"/>
   <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11256,7 +11255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16">
         <v>168001</v>
       </c>
@@ -11315,7 +11314,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16">
         <v>168016</v>
       </c>
@@ -11376,7 +11375,7 @@
       </c>
       <c r="Y4" s="11"/>
     </row>
-    <row r="5" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16">
         <v>258026</v>
       </c>
@@ -11441,7 +11440,7 @@
       </c>
       <c r="Y5" s="11"/>
     </row>
-    <row r="6" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16">
         <v>234064</v>
       </c>
@@ -11504,7 +11503,7 @@
       </c>
       <c r="Y6" s="11"/>
     </row>
-    <row r="7" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>254019</v>
       </c>
@@ -11565,7 +11564,7 @@
       </c>
       <c r="Y7" s="11"/>
     </row>
-    <row r="8" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16">
         <v>264004</v>
       </c>
@@ -11626,7 +11625,7 @@
       </c>
       <c r="Y8" s="11"/>
     </row>
-    <row r="9" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16">
         <v>264018</v>
       </c>
@@ -11685,7 +11684,7 @@
       </c>
       <c r="Y9" s="11"/>
     </row>
-    <row r="10" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16">
         <v>264024</v>
       </c>
@@ -11746,7 +11745,7 @@
       </c>
       <c r="Y10" s="11"/>
     </row>
-    <row r="11" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16">
         <v>264034</v>
       </c>
@@ -11805,7 +11804,7 @@
       </c>
       <c r="Y11" s="11"/>
     </row>
-    <row r="12" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16">
         <v>264050</v>
       </c>
@@ -11864,7 +11863,7 @@
       </c>
       <c r="Y12" s="11"/>
     </row>
-    <row r="13" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16">
         <v>265038</v>
       </c>
@@ -11923,7 +11922,7 @@
       </c>
       <c r="Y13" s="11"/>
     </row>
-    <row r="14" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16">
         <v>265122</v>
       </c>
@@ -11984,7 +11983,7 @@
       </c>
       <c r="Y14" s="11"/>
     </row>
-    <row r="15" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16">
         <v>266005</v>
       </c>
@@ -12049,7 +12048,7 @@
       </c>
       <c r="Y15" s="11"/>
     </row>
-    <row r="16" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="16">
         <v>267010</v>
       </c>
@@ -12110,7 +12109,7 @@
       </c>
       <c r="Y16" s="11"/>
     </row>
-    <row r="17" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16">
         <v>267071</v>
       </c>
@@ -12173,7 +12172,7 @@
       </c>
       <c r="Y17" s="11"/>
     </row>
-    <row r="18" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16">
         <v>267082</v>
       </c>
@@ -12234,7 +12233,7 @@
       </c>
       <c r="Y18" s="11"/>
     </row>
-    <row r="19" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16">
         <v>267089</v>
       </c>
@@ -12293,7 +12292,7 @@
       </c>
       <c r="Y19" s="11"/>
     </row>
-    <row r="20" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="16">
         <v>267090</v>
       </c>
@@ -12352,7 +12351,7 @@
       </c>
       <c r="Y20" s="11"/>
     </row>
-    <row r="21" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16">
         <v>268010</v>
       </c>
@@ -12411,7 +12410,7 @@
       </c>
       <c r="Y21" s="11"/>
     </row>
-    <row r="22" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="16">
         <v>268011</v>
       </c>
@@ -12470,7 +12469,7 @@
       </c>
       <c r="Y22" s="11"/>
     </row>
-    <row r="23" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16">
         <v>268051</v>
       </c>
@@ -12533,7 +12532,7 @@
       </c>
       <c r="Y23" s="11"/>
     </row>
-    <row r="24" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16">
         <v>268060</v>
       </c>
@@ -12594,7 +12593,7 @@
       </c>
       <c r="Y24" s="11"/>
     </row>
-    <row r="25" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>268065</v>
       </c>
@@ -12653,7 +12652,7 @@
       </c>
       <c r="Y25" s="11"/>
     </row>
-    <row r="26" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="16">
         <v>268066</v>
       </c>
@@ -12712,7 +12711,7 @@
       </c>
       <c r="Y26" s="11"/>
     </row>
-    <row r="27" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="16">
         <v>268067</v>
       </c>
@@ -12771,7 +12770,7 @@
       </c>
       <c r="Y27" s="11"/>
     </row>
-    <row r="28" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16">
         <v>268085</v>
       </c>
@@ -12830,7 +12829,7 @@
       </c>
       <c r="Y28" s="11"/>
     </row>
-    <row r="29" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16">
         <v>269023</v>
       </c>
@@ -12891,7 +12890,7 @@
       </c>
       <c r="Y29" s="11"/>
     </row>
-    <row r="30" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16">
         <v>255012</v>
       </c>
@@ -12952,7 +12951,7 @@
       </c>
       <c r="Y30" s="11"/>
     </row>
-    <row r="31" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16">
         <v>259025</v>
       </c>
@@ -13017,7 +13016,7 @@
       </c>
       <c r="Y31" s="11"/>
     </row>
-    <row r="32" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16">
         <v>235035</v>
       </c>
@@ -13080,7 +13079,7 @@
       </c>
       <c r="Y32" s="11"/>
     </row>
-    <row r="33" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16">
         <v>253020</v>
       </c>
@@ -13141,7 +13140,7 @@
       </c>
       <c r="Y33" s="11"/>
     </row>
-    <row r="34" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="16">
         <v>269032</v>
       </c>
@@ -13204,7 +13203,7 @@
       </c>
       <c r="Y34" s="11"/>
     </row>
-    <row r="35" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>250051</v>
       </c>
@@ -13271,7 +13270,7 @@
       </c>
       <c r="Y35" s="11"/>
     </row>
-    <row r="36" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="16">
         <v>254009</v>
       </c>
@@ -13330,7 +13329,7 @@
       </c>
       <c r="Y36" s="11"/>
     </row>
-    <row r="37" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16">
         <v>254054</v>
       </c>
@@ -13389,7 +13388,7 @@
       </c>
       <c r="Y37" s="11"/>
     </row>
-    <row r="38" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="16">
         <v>255001</v>
       </c>
@@ -13448,7 +13447,7 @@
       </c>
       <c r="Y38" s="11"/>
     </row>
-    <row r="39" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16">
         <v>255023</v>
       </c>
@@ -13511,7 +13510,7 @@
       </c>
       <c r="Y39" s="11"/>
     </row>
-    <row r="40" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16">
         <v>257010</v>
       </c>
@@ -13574,7 +13573,7 @@
       </c>
       <c r="Y40" s="11"/>
     </row>
-    <row r="41" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="16">
         <v>257029</v>
       </c>
@@ -13635,7 +13634,7 @@
       </c>
       <c r="Y41" s="11"/>
     </row>
-    <row r="42" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="16">
         <v>261023</v>
       </c>
@@ -13696,7 +13695,7 @@
       </c>
       <c r="Y42" s="11"/>
     </row>
-    <row r="43" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="16">
         <v>267025</v>
       </c>
@@ -13755,7 +13754,7 @@
       </c>
       <c r="Y43" s="11"/>
     </row>
-    <row r="44" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16">
         <v>267026</v>
       </c>
@@ -13814,7 +13813,7 @@
       </c>
       <c r="Y44" s="11"/>
     </row>
-    <row r="45" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>267028</v>
       </c>
@@ -13875,7 +13874,7 @@
       </c>
       <c r="Y45" s="11"/>
     </row>
-    <row r="46" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="16">
         <v>267079</v>
       </c>
@@ -13934,7 +13933,7 @@
       </c>
       <c r="Y46" s="11"/>
     </row>
-    <row r="47" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="16">
         <v>267100</v>
       </c>
@@ -13989,7 +13988,7 @@
       </c>
       <c r="Y47" s="11"/>
     </row>
-    <row r="48" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16">
         <v>267101</v>
       </c>
@@ -14044,7 +14043,7 @@
       </c>
       <c r="Y48" s="11"/>
     </row>
-    <row r="49" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16">
         <v>267105</v>
       </c>
@@ -14099,7 +14098,7 @@
       </c>
       <c r="Y49" s="11"/>
     </row>
-    <row r="50" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="16">
         <v>268016</v>
       </c>
@@ -14160,7 +14159,7 @@
       </c>
       <c r="Y50" s="11"/>
     </row>
-    <row r="51" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="16">
         <v>268059</v>
       </c>
@@ -14221,7 +14220,7 @@
       </c>
       <c r="Y51" s="11"/>
     </row>
-    <row r="52" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="16">
         <v>268061</v>
       </c>
@@ -14280,7 +14279,7 @@
       </c>
       <c r="Y52" s="11"/>
     </row>
-    <row r="53" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="16">
         <v>268079</v>
       </c>
@@ -14339,7 +14338,7 @@
       </c>
       <c r="Y53" s="11"/>
     </row>
-    <row r="54" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="16">
         <v>268082</v>
       </c>
@@ -14398,7 +14397,7 @@
       </c>
       <c r="Y54" s="11"/>
     </row>
-    <row r="55" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="16">
         <v>269025</v>
       </c>
@@ -14457,7 +14456,7 @@
       </c>
       <c r="Y55" s="11"/>
     </row>
-    <row r="56" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16">
         <v>269027</v>
       </c>
@@ -14516,7 +14515,7 @@
       </c>
       <c r="Y56" s="11"/>
     </row>
-    <row r="57" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16">
         <v>159029</v>
       </c>
@@ -14581,7 +14580,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="58" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="16">
         <v>164005</v>
       </c>
@@ -14646,7 +14645,7 @@
       </c>
       <c r="Y58" s="11"/>
     </row>
-    <row r="59" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="16">
         <v>152008</v>
       </c>
@@ -14709,7 +14708,7 @@
       </c>
       <c r="Y59" s="11"/>
     </row>
-    <row r="60" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="16">
         <v>267063</v>
       </c>
@@ -14770,7 +14769,7 @@
       </c>
       <c r="Y60" s="11"/>
     </row>
-    <row r="61" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="16">
         <v>168017</v>
       </c>
@@ -14833,7 +14832,7 @@
       </c>
       <c r="Y61" s="11"/>
     </row>
-    <row r="62" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="16">
         <v>167034</v>
       </c>
@@ -14894,7 +14893,7 @@
       </c>
       <c r="Y62" s="11"/>
     </row>
-    <row r="63" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="16">
         <v>266049</v>
       </c>
@@ -14961,7 +14960,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="16">
         <v>466004</v>
       </c>
@@ -15022,7 +15021,7 @@
       </c>
       <c r="Y64" s="11"/>
     </row>
-    <row r="65" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="16">
         <v>269013</v>
       </c>
@@ -15083,7 +15082,7 @@
       </c>
       <c r="Y65" s="11"/>
     </row>
-    <row r="66" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="16">
         <v>269001</v>
       </c>
@@ -15144,7 +15143,7 @@
       </c>
       <c r="Y66" s="11"/>
     </row>
-    <row r="67" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="16">
         <v>265088</v>
       </c>
@@ -15205,7 +15204,7 @@
       </c>
       <c r="Y67" s="11"/>
     </row>
-    <row r="68" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="16">
         <v>239005</v>
       </c>
@@ -15268,7 +15267,7 @@
       </c>
       <c r="Y68" s="11"/>
     </row>
-    <row r="69" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="16">
         <v>166027</v>
       </c>
@@ -15331,7 +15330,7 @@
       </c>
       <c r="Y69" s="11"/>
     </row>
-    <row r="70" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="16">
         <v>168018</v>
       </c>
@@ -15394,7 +15393,7 @@
       </c>
       <c r="Y70" s="11"/>
     </row>
-    <row r="71" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="16">
         <v>157033</v>
       </c>
@@ -15457,7 +15456,7 @@
       </c>
       <c r="Y71" s="11"/>
     </row>
-    <row r="72" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="16">
         <v>169001</v>
       </c>
@@ -15518,7 +15517,7 @@
       </c>
       <c r="Y72" s="11"/>
     </row>
-    <row r="73" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="16">
         <v>166035</v>
       </c>
@@ -15579,7 +15578,7 @@
       </c>
       <c r="Y73" s="11"/>
     </row>
-    <row r="74" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="16">
         <v>269014</v>
       </c>
@@ -15640,7 +15639,7 @@
       </c>
       <c r="Y74" s="11"/>
     </row>
-    <row r="75" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="16">
         <v>166032</v>
       </c>
@@ -15701,7 +15700,7 @@
       </c>
       <c r="Y75" s="11"/>
     </row>
-    <row r="76" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="16">
         <v>169017</v>
       </c>
@@ -15762,7 +15761,7 @@
       </c>
       <c r="Y76" s="11"/>
     </row>
-    <row r="77" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="16">
         <v>265011</v>
       </c>
@@ -15827,7 +15826,7 @@
       </c>
       <c r="Y77" s="11"/>
     </row>
-    <row r="78" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="16">
         <v>168015</v>
       </c>
@@ -15888,7 +15887,7 @@
         <v>21062524</v>
       </c>
     </row>
-    <row r="79" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="16">
         <v>168004</v>
       </c>
@@ -15949,7 +15948,7 @@
       </c>
       <c r="Y79" s="11"/>
     </row>
-    <row r="80" spans="1:25" s="10" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:25" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="16">
         <v>168028</v>
       </c>
@@ -16012,7 +16011,7 @@
       </c>
       <c r="Y80" s="11"/>
     </row>
-    <row r="81" spans="1:25